--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I200"/>
+  <dimension ref="A1:I239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4652,8 +4652,8 @@
       <c r="I132" s="4" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n"/>
-      <c r="B133" s="5" t="n"/>
+      <c r="A133" s="4" t="n"/>
+      <c r="B133" s="4" t="n"/>
       <c r="C133" s="5" t="n"/>
       <c r="D133" s="5" t="n"/>
       <c r="E133" s="2" t="inlineStr">
@@ -4679,50 +4679,42 @@
       <c r="I133" s="5" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>検索・フィルタ</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>11-1</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>書籍のキーワード検索・ジャンル絞り込み</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>11-1-1</t>
-        </is>
-      </c>
-      <c r="F134" s="7" t="inlineStr">
-        <is>
-          <t>タイトルにキーワードを含む書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="G134" s="7" t="inlineStr">
-        <is>
-          <t>1.タイトルにキーワードを含む書籍を用意する
-2.書籍一覧ページでkeywordにそのキーワードを指定して検索する</t>
-        </is>
-      </c>
-      <c r="H134" s="7" t="inlineStr">
-        <is>
-          <t>該当する書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="I134" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Search/SearchTest.php</t>
+      <c r="A134" s="4" t="n"/>
+      <c r="B134" s="4" t="n"/>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>10-2</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>書籍一覧取得API(GET /api/v1/books)</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>10-2-1</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>認証なしでもアクセスでき、書籍一覧が返る</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>1.書籍を複数用意する
+2.認証情報を付与せずGET /api/v1/booksにアクセスする</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>200が返り、data・links・metaを含むJSONが返る</t>
+        </is>
+      </c>
+      <c r="I134" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiIndexTest.php</t>
         </is>
       </c>
     </row>
@@ -4731,25 +4723,25 @@
       <c r="B135" s="4" t="n"/>
       <c r="C135" s="4" t="n"/>
       <c r="D135" s="4" t="n"/>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>11-1-2</t>
-        </is>
-      </c>
-      <c r="F135" s="7" t="inlineStr">
-        <is>
-          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="G135" s="7" t="inlineStr">
-        <is>
-          <t>1.著者名にキーワードを含む書籍を用意する
-2.同キーワードで検索する</t>
-        </is>
-      </c>
-      <c r="H135" s="7" t="inlineStr">
-        <is>
-          <t>該当する書籍が検索結果に表示される</t>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>10-2-2</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="inlineStr">
+        <is>
+          <t>各書籍にジャンル・平均評価・レビュー件数が含まれる</t>
+        </is>
+      </c>
+      <c r="G135" s="3" t="inlineStr">
+        <is>
+          <t>1.ジャンルと、評価4・5のレビューを持つ書籍を用意する
+2.GET /api/v1/booksにアクセスする</t>
+        </is>
+      </c>
+      <c r="H135" s="3" t="inlineStr">
+        <is>
+          <t>dataの各書籍にgenres(id・name)、average_rating(4.5)、review_count(2)が含まれ、reviews(レビュー本文)は含まれない</t>
         </is>
       </c>
       <c r="I135" s="4" t="n"/>
@@ -4759,25 +4751,25 @@
       <c r="B136" s="4" t="n"/>
       <c r="C136" s="4" t="n"/>
       <c r="D136" s="4" t="n"/>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>11-1-3</t>
-        </is>
-      </c>
-      <c r="F136" s="7" t="inlineStr">
-        <is>
-          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
-        </is>
-      </c>
-      <c r="G136" s="7" t="inlineStr">
-        <is>
-          <t>1.キーワードに一致しない書籍を用意する
-2.検索する</t>
-        </is>
-      </c>
-      <c r="H136" s="7" t="inlineStr">
-        <is>
-          <t>その書籍は検索結果に表示されない</t>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>10-2-3</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="inlineStr">
+        <is>
+          <t>レビューが無い書籍はaverage_ratingがnull、review_countが0になる</t>
+        </is>
+      </c>
+      <c r="G136" s="3" t="inlineStr">
+        <is>
+          <t>1.レビューが1件もない書籍を用意する
+2.GET /api/v1/booksにアクセスする</t>
+        </is>
+      </c>
+      <c r="H136" s="3" t="inlineStr">
+        <is>
+          <t>その書籍のaverage_ratingがnull、review_countが0で返る</t>
         </is>
       </c>
       <c r="I136" s="4" t="n"/>
@@ -4787,24 +4779,25 @@
       <c r="B137" s="4" t="n"/>
       <c r="C137" s="4" t="n"/>
       <c r="D137" s="4" t="n"/>
-      <c r="E137" s="6" t="inlineStr">
-        <is>
-          <t>11-1-4</t>
-        </is>
-      </c>
-      <c r="F137" s="7" t="inlineStr">
-        <is>
-          <t>キーワード未入力の場合は全件が表示される</t>
-        </is>
-      </c>
-      <c r="G137" s="7" t="inlineStr">
-        <is>
-          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H137" s="7" t="inlineStr">
-        <is>
-          <t>登録されている全ての書籍が表示される</t>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>10-2-4</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>新しい順(登録日時の降順、同一なら idの降順)で返る</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>1.登録日時の異なる書籍を複数用意する
+2.GET /api/v1/booksにアクセスする</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>新しく登録された書籍から順に返る</t>
         </is>
       </c>
       <c r="I137" s="4" t="n"/>
@@ -4814,25 +4807,25 @@
       <c r="B138" s="4" t="n"/>
       <c r="C138" s="4" t="n"/>
       <c r="D138" s="4" t="n"/>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>11-1-5</t>
-        </is>
-      </c>
-      <c r="F138" s="7" t="inlineStr">
-        <is>
-          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
-        </is>
-      </c>
-      <c r="G138" s="7" t="inlineStr">
-        <is>
-          <t>1.複数ジャンルの書籍を用意する
-2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
-        </is>
-      </c>
-      <c r="H138" s="7" t="inlineStr">
-        <is>
-          <t>指定したジャンルに紐づく書籍のみ表示される</t>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>10-2-5</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>keywordでタイトル・著者名の部分一致検索ができる</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>1.タイトルにキーワードを含む書籍、著者名にキーワードを含む書籍、含まない書籍を用意する
+2.keywordを指定してGET /api/v1/booksにアクセスする</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>タイトルまたは著者名にキーワードを含む書籍のみが返る</t>
         </is>
       </c>
       <c r="I138" s="4" t="n"/>
@@ -4842,155 +4835,148 @@
       <c r="B139" s="4" t="n"/>
       <c r="C139" s="4" t="n"/>
       <c r="D139" s="4" t="n"/>
-      <c r="E139" s="6" t="inlineStr">
-        <is>
-          <t>11-1-6</t>
-        </is>
-      </c>
-      <c r="F139" s="7" t="inlineStr">
-        <is>
-          <t>キーワード検索とジャンル絞り込みを組み合わせて使用できる</t>
-        </is>
-      </c>
-      <c r="G139" s="7" t="inlineStr">
-        <is>
-          <t>1.keywordとgenreの両方を指定して一覧を開く</t>
-        </is>
-      </c>
-      <c r="H139" s="7" t="inlineStr">
-        <is>
-          <t>キーワードとジャンルの両方の条件に一致する書籍のみ表示される</t>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>10-2-6</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>genreでジャンルIDによる絞り込みができる</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>1.異なるジャンルの書籍を用意する
+2.genreにジャンルIDを指定してGET /api/v1/booksにアクセスする</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>指定したジャンルに属する書籍のみが返る</t>
         </is>
       </c>
       <c r="I139" s="4" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n"/>
-      <c r="B140" s="5" t="n"/>
-      <c r="C140" s="5" t="n"/>
-      <c r="D140" s="5" t="n"/>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>11-1-7</t>
-        </is>
-      </c>
-      <c r="F140" s="7" t="inlineStr">
-        <is>
-          <t>検索結果が0件の場合の表示を確認する</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="inlineStr">
-        <is>
-          <t>1.どの書籍にも一致しないキーワードで検索する</t>
-        </is>
-      </c>
-      <c r="H140" s="7" t="inlineStr">
-        <is>
-          <t>「書籍が登録されていません。」など0件である旨が表示される</t>
-        </is>
-      </c>
-      <c r="I140" s="5" t="n"/>
+      <c r="A140" s="4" t="n"/>
+      <c r="B140" s="4" t="n"/>
+      <c r="C140" s="4" t="n"/>
+      <c r="D140" s="4" t="n"/>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>10-2-7</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="inlineStr">
+        <is>
+          <t>per_page・pageでページネーションできる(指定なしの場合は1ページ9件)</t>
+        </is>
+      </c>
+      <c r="G140" s="3" t="inlineStr">
+        <is>
+          <t>1.10件以上の書籍を用意する
+2.パラメータなし、およびper_page・pageを指定してGET /api/v1/booksにアクセスする</t>
+        </is>
+      </c>
+      <c r="H140" s="3" t="inlineStr">
+        <is>
+          <t>パラメータなしでは9件、指定した場合は指定件数・指定ページの書籍が返り、meta・linksにページ情報が反映される</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B141" s="6" t="inlineStr">
-        <is>
-          <t>ソート</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>12-1</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>書籍一覧の並び替え</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>12-1-1</t>
-        </is>
-      </c>
-      <c r="F141" s="7" t="inlineStr">
-        <is>
-          <t>並び替え未指定時は新着順(登録が新しい順)で表示される</t>
-        </is>
-      </c>
-      <c r="G141" s="7" t="inlineStr">
-        <is>
-          <t>1.複数の書籍を異なる日時で登録する
-2.sortを指定せずに書籍一覧を開く</t>
-        </is>
-      </c>
-      <c r="H141" s="7" t="inlineStr">
-        <is>
-          <t>登録日時が新しい順に表示される</t>
-        </is>
-      </c>
-      <c r="I141" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Sort/SortTest.php</t>
-        </is>
-      </c>
+      <c r="A141" s="4" t="n"/>
+      <c r="B141" s="4" t="n"/>
+      <c r="C141" s="5" t="n"/>
+      <c r="D141" s="5" t="n"/>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>10-2-8</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="inlineStr">
+        <is>
+          <t>不正なクエリパラメータを指定すると422が返る</t>
+        </is>
+      </c>
+      <c r="G141" s="3" t="inlineStr">
+        <is>
+          <t>1.per_pageに101、genreに存在しないID、pageに0をそれぞれ指定してGET /api/v1/booksにアクセスする(Accept: application/json)</t>
+        </is>
+      </c>
+      <c r="H141" s="3" t="inlineStr">
+        <is>
+          <t>422が返り、「取得件数は100以下の値で指定してください」「指定されたジャンルは存在しません」「ページ番号は1以上の値で指定してください」が返る</t>
+        </is>
+      </c>
+      <c r="I141" s="5" t="n"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="n"/>
       <c r="B142" s="4" t="n"/>
-      <c r="C142" s="4" t="n"/>
-      <c r="D142" s="4" t="n"/>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>12-1-2</t>
-        </is>
-      </c>
-      <c r="F142" s="7" t="inlineStr">
-        <is>
-          <t>sort=oldestを指定すると登録が古い順に表示される</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="inlineStr">
-        <is>
-          <t>1.複数の書籍を異なる日時で登録する
-2.sort=oldestを指定して書籍一覧を開く</t>
-        </is>
-      </c>
-      <c r="H142" s="7" t="inlineStr">
-        <is>
-          <t>登録日時が古い順に表示される</t>
-        </is>
-      </c>
-      <c r="I142" s="4" t="n"/>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>10-3</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>書籍詳細取得API(GET /api/v1/books/{book})</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>10-3-1</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="inlineStr">
+        <is>
+          <t>認証なしでもアクセスでき、書籍の詳細が返る</t>
+        </is>
+      </c>
+      <c r="G142" s="3" t="inlineStr">
+        <is>
+          <t>1.ジャンルとレビューを持つ書籍を用意する
+2.認証情報を付与せずGET /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H142" s="3" t="inlineStr">
+        <is>
+          <t>200が返り、書籍情報・genres・average_rating・review_countを含むJSONが返る</t>
+        </is>
+      </c>
+      <c r="I142" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiShowTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n"/>
       <c r="B143" s="4" t="n"/>
       <c r="C143" s="4" t="n"/>
       <c r="D143" s="4" t="n"/>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>12-1-3</t>
-        </is>
-      </c>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>sort=titleを指定するとタイトルの昇順で表示される</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="inlineStr">
-        <is>
-          <t>1.複数の書籍を用意する
-2.sort=titleを指定して書籍一覧を開く</t>
-        </is>
-      </c>
-      <c r="H143" s="7" t="inlineStr">
-        <is>
-          <t>タイトルの昇順で表示される</t>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>10-3-2</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="inlineStr">
+        <is>
+          <t>レビュー(投稿者名・評価・コメント・投稿日時)が新しい順に含まれる</t>
+        </is>
+      </c>
+      <c r="G143" s="3" t="inlineStr">
+        <is>
+          <t>1.異なる日時に投稿された複数のレビューを持つ書籍を用意する
+2.GET /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H143" s="3" t="inlineStr">
+        <is>
+          <t>reviewsにuser_name・rating・comment・created_atが含まれ、投稿日時の新しい順に並ぶ</t>
         </is>
       </c>
       <c r="I143" s="4" t="n"/>
@@ -4998,129 +4984,120 @@
     <row r="144">
       <c r="A144" s="4" t="n"/>
       <c r="B144" s="4" t="n"/>
-      <c r="C144" s="4" t="n"/>
-      <c r="D144" s="4" t="n"/>
-      <c r="E144" s="6" t="inlineStr">
-        <is>
-          <t>12-1-4</t>
-        </is>
-      </c>
-      <c r="F144" s="7" t="inlineStr">
-        <is>
-          <t>sort=ratingを指定すると平均評価が高い順に表示される</t>
-        </is>
-      </c>
-      <c r="G144" s="7" t="inlineStr">
-        <is>
-          <t>1.平均評価が異なる複数の書籍を用意する
-2.sort=ratingを指定して書籍一覧を開く</t>
-        </is>
-      </c>
-      <c r="H144" s="7" t="inlineStr">
-        <is>
-          <t>平均評価が高い順に表示される</t>
-        </is>
-      </c>
-      <c r="I144" s="4" t="n"/>
+      <c r="C144" s="5" t="n"/>
+      <c r="D144" s="5" t="n"/>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>10-3-3</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="inlineStr">
+        <is>
+          <t>存在しないIDを指定すると404が返る</t>
+        </is>
+      </c>
+      <c r="G144" s="3" t="inlineStr">
+        <is>
+          <t>1.存在しない書籍IDでGET /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H144" s="3" t="inlineStr">
+        <is>
+          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
+        </is>
+      </c>
+      <c r="I144" s="5" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="n"/>
-      <c r="B145" s="5" t="n"/>
-      <c r="C145" s="5" t="n"/>
-      <c r="D145" s="5" t="n"/>
-      <c r="E145" s="6" t="inlineStr">
-        <is>
-          <t>12-1-5</t>
-        </is>
-      </c>
-      <c r="F145" s="7" t="inlineStr">
-        <is>
-          <t>sort=rating指定時、平均評価が同じ書籍は新着順で表示される</t>
-        </is>
-      </c>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>1.平均評価が同じ複数の書籍を、異なる登録日時で用意する
-2.sort=ratingを指定して書籍一覧を開く</t>
-        </is>
-      </c>
-      <c r="H145" s="7" t="inlineStr">
-        <is>
-          <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
-        </is>
-      </c>
-      <c r="I145" s="5" t="n"/>
+      <c r="A145" s="4" t="n"/>
+      <c r="B145" s="4" t="n"/>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>10-4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>書籍登録API(POST /api/v1/books)</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>10-4-1</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="inlineStr">
+        <is>
+          <t>認証なしでアクセスすると401が返る</t>
+        </is>
+      </c>
+      <c r="G145" s="3" t="inlineStr">
+        <is>
+          <t>1.認証情報を付与せずPOST /api/v1/booksにアクセスする(Accept: application/json)</t>
+        </is>
+      </c>
+      <c r="H145" s="3" t="inlineStr">
+        <is>
+          <t>401 Unauthorizedが返り、書籍は登録されない</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiStoreTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="146">
-      <c r="A146" s="6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B146" s="6" t="inlineStr">
-        <is>
-          <t>書籍CRUD（認可の詳細テスト）</t>
-        </is>
-      </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>13-1</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>BookPolicyの認可ロジック</t>
-        </is>
-      </c>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>13-1-1</t>
-        </is>
-      </c>
-      <c r="F146" s="7" t="inlineStr">
-        <is>
-          <t>ログインユーザーは誰でも書籍を作成できる</t>
-        </is>
-      </c>
-      <c r="G146" s="7" t="inlineStr">
-        <is>
-          <t>1.任意のログインユーザーで BookPolicy::create() を確認する</t>
-        </is>
-      </c>
-      <c r="H146" s="7" t="inlineStr">
-        <is>
-          <t>trueが返り、作成が許可される</t>
-        </is>
-      </c>
-      <c r="I146" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/BookAuthorization/BookAuthorizationTest.php</t>
-        </is>
-      </c>
+      <c r="A146" s="4" t="n"/>
+      <c r="B146" s="4" t="n"/>
+      <c r="C146" s="4" t="n"/>
+      <c r="D146" s="4" t="n"/>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>10-4-2</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="inlineStr">
+        <is>
+          <t>有効なトークンで書籍を登録できる</t>
+        </is>
+      </c>
+      <c r="G146" s="3" t="inlineStr">
+        <is>
+          <t>1.ユーザーのトークンを発行する
+2.必要項目を指定し、Bearerトークンを付与してPOST /api/v1/booksにアクセスする</t>
+        </is>
+      </c>
+      <c r="H146" s="3" t="inlineStr">
+        <is>
+          <t>201が返り、登録内容がJSONで返る。書籍がDBに保存される</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n"/>
       <c r="B147" s="4" t="n"/>
       <c r="C147" s="4" t="n"/>
       <c r="D147" s="4" t="n"/>
-      <c r="E147" s="6" t="inlineStr">
-        <is>
-          <t>13-1-2</t>
-        </is>
-      </c>
-      <c r="F147" s="7" t="inlineStr">
-        <is>
-          <t>書籍の登録者本人は更新が許可される</t>
-        </is>
-      </c>
-      <c r="G147" s="7" t="inlineStr">
-        <is>
-          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
-        </is>
-      </c>
-      <c r="H147" s="7" t="inlineStr">
-        <is>
-          <t>trueが返る</t>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>10-4-3</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="inlineStr">
+        <is>
+          <t>登録者(user_id)は、リクエストの値ではなく認証ユーザーになる</t>
+        </is>
+      </c>
+      <c r="G147" s="3" t="inlineStr">
+        <is>
+          <t>1.他のユーザーのIDをuser_idに含めて、トークンを付与しPOST /api/v1/booksにアクセスする</t>
+        </is>
+      </c>
+      <c r="H147" s="3" t="inlineStr">
+        <is>
+          <t>登録された書籍のuser_idは、トークンの持ち主(認証ユーザー)のIDになる</t>
         </is>
       </c>
       <c r="I147" s="4" t="n"/>
@@ -5130,24 +5107,24 @@
       <c r="B148" s="4" t="n"/>
       <c r="C148" s="4" t="n"/>
       <c r="D148" s="4" t="n"/>
-      <c r="E148" s="6" t="inlineStr">
-        <is>
-          <t>13-1-3</t>
-        </is>
-      </c>
-      <c r="F148" s="7" t="inlineStr">
-        <is>
-          <t>書籍の登録者以外は更新が許可されない</t>
-        </is>
-      </c>
-      <c r="G148" s="7" t="inlineStr">
-        <is>
-          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
-        </is>
-      </c>
-      <c r="H148" s="7" t="inlineStr">
-        <is>
-          <t>falseが返る</t>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>10-4-4</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="inlineStr">
+        <is>
+          <t>選択したジャンルが書籍に紐づけられる</t>
+        </is>
+      </c>
+      <c r="G148" s="3" t="inlineStr">
+        <is>
+          <t>1.複数のジャンルIDをgenresに指定してPOST /api/v1/booksにアクセスする</t>
+        </is>
+      </c>
+      <c r="H148" s="3" t="inlineStr">
+        <is>
+          <t>中間テーブル(book_genres)に指定したジャンルが保存され、レスポンスのgenresにも含まれる</t>
         </is>
       </c>
       <c r="I148" s="4" t="n"/>
@@ -5157,24 +5134,24 @@
       <c r="B149" s="4" t="n"/>
       <c r="C149" s="4" t="n"/>
       <c r="D149" s="4" t="n"/>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>13-1-4</t>
-        </is>
-      </c>
-      <c r="F149" s="7" t="inlineStr">
-        <is>
-          <t>書籍の登録者本人は削除が許可される</t>
-        </is>
-      </c>
-      <c r="G149" s="7" t="inlineStr">
-        <is>
-          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
-        </is>
-      </c>
-      <c r="H149" s="7" t="inlineStr">
-        <is>
-          <t>trueが返る</t>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>10-4-5</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="inlineStr">
+        <is>
+          <t>必須項目(title・author・genres)が未入力の場合、422が返る</t>
+        </is>
+      </c>
+      <c r="G149" s="3" t="inlineStr">
+        <is>
+          <t>1.title・author・genresを指定せずにPOST /api/v1/booksにアクセスする</t>
+        </is>
+      </c>
+      <c r="H149" s="3" t="inlineStr">
+        <is>
+          <t>422が返り、「書籍タイトルを入力してください」「著者名を入力してください」「ジャンルを1つ以上選択してください」が返る</t>
         </is>
       </c>
       <c r="I149" s="4" t="n"/>
@@ -5184,99 +5161,92 @@
       <c r="B150" s="4" t="n"/>
       <c r="C150" s="4" t="n"/>
       <c r="D150" s="4" t="n"/>
-      <c r="E150" s="6" t="inlineStr">
-        <is>
-          <t>13-1-5</t>
-        </is>
-      </c>
-      <c r="F150" s="7" t="inlineStr">
-        <is>
-          <t>書籍の登録者以外は削除が許可されない</t>
-        </is>
-      </c>
-      <c r="G150" s="7" t="inlineStr">
-        <is>
-          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
-        </is>
-      </c>
-      <c r="H150" s="7" t="inlineStr">
-        <is>
-          <t>falseが返る</t>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>10-4-6</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="inlineStr">
+        <is>
+          <t>ISBNが13桁の数字でない、または登録済みの場合、422が返る</t>
+        </is>
+      </c>
+      <c r="G150" s="3" t="inlineStr">
+        <is>
+          <t>1.ISBNに13桁でない値を指定してPOST /api/v1/booksにアクセスする
+2.登録済みのISBNを指定して同様にアクセスする</t>
+        </is>
+      </c>
+      <c r="H150" s="3" t="inlineStr">
+        <is>
+          <t>422が返り、「ISBNは13桁の数字で入力してください」「このISBNはすでに登録されています」が返る</t>
         </is>
       </c>
       <c r="I150" s="4" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="n"/>
-      <c r="B151" s="5" t="n"/>
+      <c r="A151" s="4" t="n"/>
+      <c r="B151" s="4" t="n"/>
       <c r="C151" s="5" t="n"/>
       <c r="D151" s="5" t="n"/>
-      <c r="E151" s="6" t="inlineStr">
-        <is>
-          <t>13-1-6</t>
-        </is>
-      </c>
-      <c r="F151" s="7" t="inlineStr">
-        <is>
-          <t>フォームを介さない直接のPUT/DELETEリクエストでも他人の書籍は操作できない</t>
-        </is>
-      </c>
-      <c r="G151" s="7" t="inlineStr">
-        <is>
-          <t>1.他人が登録した書籍に対して、直接PUT・DELETEリクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H151" s="7" t="inlineStr">
-        <is>
-          <t>いずれも403Forbiddenになり、データは変更されない</t>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>10-4-7</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="inlineStr">
+        <is>
+          <t>存在しないジャンルIDを指定すると422が返る</t>
+        </is>
+      </c>
+      <c r="G151" s="3" t="inlineStr">
+        <is>
+          <t>1.genresに存在しないジャンルIDを指定してPOST /api/v1/booksにアクセスする</t>
+        </is>
+      </c>
+      <c r="H151" s="3" t="inlineStr">
+        <is>
+          <t>422が返り、「選択されたジャンルは存在しません」が返る</t>
         </is>
       </c>
       <c r="I151" s="5" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B152" s="6" t="inlineStr">
-        <is>
-          <t>ISBN検索</t>
-        </is>
-      </c>
-      <c r="C152" s="6" t="inlineStr">
-        <is>
-          <t>14-1</t>
-        </is>
-      </c>
-      <c r="D152" s="6" t="inlineStr">
-        <is>
-          <t>ISBNからの書籍情報取得(外部API連携)</t>
-        </is>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>14-1-1</t>
-        </is>
-      </c>
-      <c r="F152" s="7" t="inlineStr">
-        <is>
-          <t>未ログインの場合、ISBN検索エンドポイントにアクセスできない</t>
-        </is>
-      </c>
-      <c r="G152" s="7" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態でGET /books/isbn/{isbn} にアクセスする</t>
-        </is>
-      </c>
-      <c r="H152" s="7" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I152" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Isbn/IsbnSearchTest.php</t>
+      <c r="A152" s="4" t="n"/>
+      <c r="B152" s="4" t="n"/>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>10-5</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>書籍更新API(PUT /api/v1/books/{book})</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>10-5-1</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="inlineStr">
+        <is>
+          <t>認証なしでアクセスすると401が返る</t>
+        </is>
+      </c>
+      <c r="G152" s="3" t="inlineStr">
+        <is>
+          <t>1.認証情報を付与せずPUT /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
+        </is>
+      </c>
+      <c r="H152" s="3" t="inlineStr">
+        <is>
+          <t>401 Unauthorizedが返り、書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I152" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiUpdateTest.php</t>
         </is>
       </c>
     </row>
@@ -5285,24 +5255,25 @@
       <c r="B153" s="4" t="n"/>
       <c r="C153" s="4" t="n"/>
       <c r="D153" s="4" t="n"/>
-      <c r="E153" s="6" t="inlineStr">
-        <is>
-          <t>14-1-2</t>
-        </is>
-      </c>
-      <c r="F153" s="7" t="inlineStr">
-        <is>
-          <t>ISBNが未入力(空文字)の場合、バリデーションエラーが返る</t>
-        </is>
-      </c>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>1.ログイン状態でISBN部分を空にしてリクエストする</t>
-        </is>
-      </c>
-      <c r="H153" s="7" t="inlineStr">
-        <is>
-          <t>422が返り、「ISBNを入力してください」が返る</t>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>10-5-2</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="inlineStr">
+        <is>
+          <t>自分が登録した書籍を更新できる</t>
+        </is>
+      </c>
+      <c r="G153" s="3" t="inlineStr">
+        <is>
+          <t>1.ユーザーが登録した書籍を用意する
+2.そのユーザーのトークンを付与し、変更内容・ジャンルを指定してPUT /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H153" s="3" t="inlineStr">
+        <is>
+          <t>200が返り、更新後の内容がJSONで返る。DBの書籍情報とジャンルの紐づけが更新される</t>
         </is>
       </c>
       <c r="I153" s="4" t="n"/>
@@ -5312,24 +5283,25 @@
       <c r="B154" s="4" t="n"/>
       <c r="C154" s="4" t="n"/>
       <c r="D154" s="4" t="n"/>
-      <c r="E154" s="6" t="inlineStr">
-        <is>
-          <t>14-1-3</t>
-        </is>
-      </c>
-      <c r="F154" s="7" t="inlineStr">
-        <is>
-          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
-        </is>
-      </c>
-      <c r="G154" s="7" t="inlineStr">
-        <is>
-          <t>1.13桁でないISBNでリクエストする</t>
-        </is>
-      </c>
-      <c r="H154" s="7" t="inlineStr">
-        <is>
-          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>10-5-3</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="inlineStr">
+        <is>
+          <t>自分の書籍のISBNを変更せずに更新しても、ISBNの重複エラーにならない</t>
+        </is>
+      </c>
+      <c r="G154" s="3" t="inlineStr">
+        <is>
+          <t>1.ユーザーが登録した書籍(ISBNあり)を用意する
+2.ISBNを変えずに他の項目を変更してPUT /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H154" s="3" t="inlineStr">
+        <is>
+          <t>200が返り、更新できる</t>
         </is>
       </c>
       <c r="I154" s="4" t="n"/>
@@ -5339,24 +5311,25 @@
       <c r="B155" s="4" t="n"/>
       <c r="C155" s="4" t="n"/>
       <c r="D155" s="4" t="n"/>
-      <c r="E155" s="6" t="inlineStr">
-        <is>
-          <t>14-1-4</t>
-        </is>
-      </c>
-      <c r="F155" s="7" t="inlineStr">
-        <is>
-          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
-        </is>
-      </c>
-      <c r="G155" s="7" t="inlineStr">
-        <is>
-          <t>1.登録済みのISBNでリクエストする</t>
-        </is>
-      </c>
-      <c r="H155" s="7" t="inlineStr">
-        <is>
-          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>10-5-4</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="inlineStr">
+        <is>
+          <t>他のユーザーが登録した書籍は更新できない</t>
+        </is>
+      </c>
+      <c r="G155" s="3" t="inlineStr">
+        <is>
+          <t>1.他のユーザーが登録した書籍を用意する
+2.別のユーザーのトークンを付与してPUT /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H155" s="3" t="inlineStr">
+        <is>
+          <t>403 Forbiddenが返り、書籍は更新されない</t>
         </is>
       </c>
       <c r="I155" s="4" t="n"/>
@@ -5366,25 +5339,24 @@
       <c r="B156" s="4" t="n"/>
       <c r="C156" s="4" t="n"/>
       <c r="D156" s="4" t="n"/>
-      <c r="E156" s="6" t="inlineStr">
-        <is>
-          <t>14-1-5</t>
-        </is>
-      </c>
-      <c r="F156" s="7" t="inlineStr">
-        <is>
-          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
-        </is>
-      </c>
-      <c r="G156" s="7" t="inlineStr">
-        <is>
-          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
-2.未登録ISBNでリクエストする</t>
-        </is>
-      </c>
-      <c r="H156" s="7" t="inlineStr">
-        <is>
-          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>10-5-5</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="inlineStr">
+        <is>
+          <t>存在しないIDを指定すると404が返る</t>
+        </is>
+      </c>
+      <c r="G156" s="3" t="inlineStr">
+        <is>
+          <t>1.トークンを付与し、存在しない書籍IDでPUT /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H156" s="3" t="inlineStr">
+        <is>
+          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
         </is>
       </c>
       <c r="I156" s="4" t="n"/>
@@ -5392,129 +5364,121 @@
     <row r="157">
       <c r="A157" s="4" t="n"/>
       <c r="B157" s="4" t="n"/>
-      <c r="C157" s="4" t="n"/>
-      <c r="D157" s="4" t="n"/>
-      <c r="E157" s="6" t="inlineStr">
-        <is>
-          <t>14-1-6</t>
-        </is>
-      </c>
-      <c r="F157" s="7" t="inlineStr">
-        <is>
-          <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
-        </is>
-      </c>
-      <c r="G157" s="7" t="inlineStr">
-        <is>
-          <t>1.Http::fake()でitemsが空のレスポンスをモックする
-2.未登録ISBNでリクエストする</t>
-        </is>
-      </c>
-      <c r="H157" s="7" t="inlineStr">
-        <is>
-          <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="n"/>
+      <c r="C157" s="5" t="n"/>
+      <c r="D157" s="5" t="n"/>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>10-5-6</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="inlineStr">
+        <is>
+          <t>入力内容が不正な場合、422が返る</t>
+        </is>
+      </c>
+      <c r="G157" s="3" t="inlineStr">
+        <is>
+          <t>1.自分の書籍に対し、titleを空にしてPUT /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H157" s="3" t="inlineStr">
+        <is>
+          <t>422が返り、「書籍タイトルを入力してください」が返る。書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I157" s="5" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="n"/>
-      <c r="B158" s="5" t="n"/>
-      <c r="C158" s="5" t="n"/>
-      <c r="D158" s="5" t="n"/>
-      <c r="E158" s="6" t="inlineStr">
-        <is>
-          <t>14-1-7</t>
-        </is>
-      </c>
-      <c r="F158" s="7" t="inlineStr">
-        <is>
-          <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
-        </is>
-      </c>
-      <c r="G158" s="7" t="inlineStr">
-        <is>
-          <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
-2.未登録ISBNでリクエストする</t>
-        </is>
-      </c>
-      <c r="H158" s="7" t="inlineStr">
-        <is>
-          <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
-        </is>
-      </c>
-      <c r="I158" s="5" t="n"/>
+      <c r="A158" s="4" t="n"/>
+      <c r="B158" s="4" t="n"/>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>10-6</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>書籍削除API(DELETE /api/v1/books/{book})</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>10-6-1</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="inlineStr">
+        <is>
+          <t>認証なしでアクセスすると401が返る</t>
+        </is>
+      </c>
+      <c r="G158" s="3" t="inlineStr">
+        <is>
+          <t>1.認証情報を付与せずDELETE /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
+        </is>
+      </c>
+      <c r="H158" s="3" t="inlineStr">
+        <is>
+          <t>401 Unauthorizedが返り、書籍は削除されない</t>
+        </is>
+      </c>
+      <c r="I158" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiDestroyTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B159" s="6" t="inlineStr">
-        <is>
-          <t>マイ読書レポート</t>
-        </is>
-      </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>15-1</t>
-        </is>
-      </c>
-      <c r="D159" s="6" t="inlineStr">
-        <is>
-          <t>読書統計の表示</t>
-        </is>
-      </c>
-      <c r="E159" s="6" t="inlineStr">
-        <is>
-          <t>15-1-1</t>
-        </is>
-      </c>
-      <c r="F159" s="7" t="inlineStr">
-        <is>
-          <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
-        </is>
-      </c>
-      <c r="G159" s="7" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態で/reportsを開く</t>
-        </is>
-      </c>
-      <c r="H159" s="7" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I159" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Report/ReportTest.php</t>
-        </is>
-      </c>
+      <c r="A159" s="4" t="n"/>
+      <c r="B159" s="4" t="n"/>
+      <c r="C159" s="4" t="n"/>
+      <c r="D159" s="4" t="n"/>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>10-6-2</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>自分が登録した書籍を削除できる</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>1.ユーザーが登録した書籍を用意する
+2.そのユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>204が返り(レスポンスボディなし)、書籍がDBから削除される</t>
+        </is>
+      </c>
+      <c r="I159" s="4" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="n"/>
       <c r="B160" s="4" t="n"/>
       <c r="C160" s="4" t="n"/>
       <c r="D160" s="4" t="n"/>
-      <c r="E160" s="6" t="inlineStr">
-        <is>
-          <t>15-1-2</t>
-        </is>
-      </c>
-      <c r="F160" s="7" t="inlineStr">
-        <is>
-          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
-        </is>
-      </c>
-      <c r="G160" s="7" t="inlineStr">
-        <is>
-          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
-        </is>
-      </c>
-      <c r="H160" s="7" t="inlineStr">
-        <is>
-          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>10-6-3</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="inlineStr">
+        <is>
+          <t>書籍を削除すると、関連するデータも一緒に削除される</t>
+        </is>
+      </c>
+      <c r="G160" s="3" t="inlineStr">
+        <is>
+          <t>1.ジャンルの紐づけ・レビュー・お気に入り・レビューへのいいねを持つ書籍を用意する
+2.所有者のトークンでDELETE /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>book_genres・reviews・favorites・review_likesの該当データも削除される</t>
         </is>
       </c>
       <c r="I160" s="4" t="n"/>
@@ -5524,156 +5488,159 @@
       <c r="B161" s="4" t="n"/>
       <c r="C161" s="4" t="n"/>
       <c r="D161" s="4" t="n"/>
-      <c r="E161" s="6" t="inlineStr">
-        <is>
-          <t>15-1-3</t>
-        </is>
-      </c>
-      <c r="F161" s="7" t="inlineStr">
-        <is>
-          <t>評価分布(★1〜★5)が正しく表示される</t>
-        </is>
-      </c>
-      <c r="G161" s="7" t="inlineStr">
-        <is>
-          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
-        </is>
-      </c>
-      <c r="H161" s="7" t="inlineStr">
-        <is>
-          <t>各評価の件数が実データと一致して表示される</t>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>10-6-4</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="inlineStr">
+        <is>
+          <t>他のユーザーが登録した書籍は削除できない</t>
+        </is>
+      </c>
+      <c r="G161" s="3" t="inlineStr">
+        <is>
+          <t>1.他のユーザーが登録した書籍を用意する
+2.別のユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H161" s="3" t="inlineStr">
+        <is>
+          <t>403 Forbiddenが返り、書籍は削除されない</t>
         </is>
       </c>
       <c r="I161" s="4" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="4" t="n"/>
-      <c r="B162" s="4" t="n"/>
-      <c r="C162" s="4" t="n"/>
-      <c r="D162" s="4" t="n"/>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>15-1-4</t>
-        </is>
-      </c>
-      <c r="F162" s="7" t="inlineStr">
-        <is>
-          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
-        </is>
-      </c>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
-        </is>
-      </c>
-      <c r="H162" s="7" t="inlineStr">
-        <is>
-          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
-        </is>
-      </c>
-      <c r="I162" s="4" t="n"/>
+      <c r="A162" s="5" t="n"/>
+      <c r="B162" s="5" t="n"/>
+      <c r="C162" s="5" t="n"/>
+      <c r="D162" s="5" t="n"/>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>10-6-5</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="inlineStr">
+        <is>
+          <t>存在しないIDを指定すると404が返る</t>
+        </is>
+      </c>
+      <c r="G162" s="3" t="inlineStr">
+        <is>
+          <t>1.トークンを付与し、存在しない書籍IDでDELETE /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H162" s="3" t="inlineStr">
+        <is>
+          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="4" t="n"/>
-      <c r="B163" s="4" t="n"/>
-      <c r="C163" s="4" t="n"/>
-      <c r="D163" s="4" t="n"/>
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>検索・フィルタ</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>11-1</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>書籍のキーワード検索・ジャンル絞り込み</t>
+        </is>
+      </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>15-1-5</t>
+          <t>11-1-1</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
+          <t>タイトルにキーワードを含む書籍が検索結果に表示される</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
+          <t>1.タイトルにキーワードを含む書籍を用意する
+2.書籍一覧ページでkeywordにそのキーワードを指定して検索する</t>
         </is>
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
-          <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
-        </is>
-      </c>
-      <c r="I163" s="4" t="n"/>
+          <t>該当する書籍が検索結果に表示される</t>
+        </is>
+      </c>
+      <c r="I163" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Search/SearchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="n"/>
-      <c r="B164" s="5" t="n"/>
-      <c r="C164" s="5" t="n"/>
-      <c r="D164" s="5" t="n"/>
+      <c r="A164" s="4" t="n"/>
+      <c r="B164" s="4" t="n"/>
+      <c r="C164" s="4" t="n"/>
+      <c r="D164" s="4" t="n"/>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>15-1-6</t>
+          <t>11-1-2</t>
         </is>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>レビューを1件も投稿していない場合の表示を確認する</t>
+          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
+          <t>1.著者名にキーワードを含む書籍を用意する
+2.同キーワードで検索する</t>
         </is>
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
-          <t>総レビュー数・読了冊数が0、平均評価が0として表示され、TOP5一覧は空になる</t>
-        </is>
-      </c>
-      <c r="I164" s="5" t="n"/>
+          <t>該当する書籍が検索結果に表示される</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B165" s="6" t="inlineStr">
-        <is>
-          <t>Sanctum認証</t>
-        </is>
-      </c>
-      <c r="C165" s="6" t="inlineStr">
-        <is>
-          <t>16-1</t>
-        </is>
-      </c>
-      <c r="D165" s="6" t="inlineStr">
-        <is>
-          <t>APIトークン認証</t>
-        </is>
-      </c>
+      <c r="A165" s="4" t="n"/>
+      <c r="B165" s="4" t="n"/>
+      <c r="C165" s="4" t="n"/>
+      <c r="D165" s="4" t="n"/>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>16-1-1</t>
+          <t>11-1-3</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>有効なpersonal access tokenを付与すると/api/userにアクセスできる</t>
+          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
         </is>
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>1.$user-&gt;createToken()でトークンを発行する
-2.Authorization: Bearer {token}を付与してGET /api/userにアクセスする</t>
+          <t>1.キーワードに一致しない書籍を用意する
+2.検索する</t>
         </is>
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
-          <t>200が返り、対象ユーザーの情報が返る</t>
-        </is>
-      </c>
-      <c r="I165" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
-        </is>
-      </c>
+          <t>その書籍は検索結果に表示されない</t>
+        </is>
+      </c>
+      <c r="I165" s="4" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="n"/>
@@ -5682,22 +5649,22 @@
       <c r="D166" s="4" t="n"/>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>16-1-2</t>
+          <t>11-1-4</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>トークンなしでアクセスすると401が返る</t>
+          <t>キーワード未入力の場合は全件が表示される</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>1.Authorizationヘッダーを付与せずにGET /api/userにアクセスする</t>
+          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
         </is>
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返る</t>
+          <t>登録されている全ての書籍が表示される</t>
         </is>
       </c>
       <c r="I166" s="4" t="n"/>
@@ -5709,128 +5676,128 @@
       <c r="D167" s="4" t="n"/>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>16-1-3</t>
+          <t>11-1-5</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>不正な(存在しない)トークンでアクセスすると401が返る</t>
+          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>1.ランダムな文字列をBearerトークンとして付与しGET /api/userにアクセスする</t>
+          <t>1.複数ジャンルの書籍を用意する
+2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
         </is>
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返る</t>
+          <t>指定したジャンルに紐づく書籍のみ表示される</t>
         </is>
       </c>
       <c r="I167" s="4" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="5" t="n"/>
-      <c r="B168" s="5" t="n"/>
-      <c r="C168" s="5" t="n"/>
-      <c r="D168" s="5" t="n"/>
+      <c r="A168" s="4" t="n"/>
+      <c r="B168" s="4" t="n"/>
+      <c r="C168" s="4" t="n"/>
+      <c r="D168" s="4" t="n"/>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>16-1-4</t>
+          <t>11-1-6</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>削除済み(失効済み)のトークンでアクセスすると401が返る</t>
+          <t>キーワード検索とジャンル絞り込みを組み合わせて使用できる</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>1.発行済みトークンを削除する
-2.そのトークンでGET /api/userにアクセスする</t>
+          <t>1.keywordとgenreの両方を指定して一覧を開く</t>
         </is>
       </c>
       <c r="H168" s="7" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返る</t>
-        </is>
-      </c>
-      <c r="I168" s="5" t="n"/>
+          <t>キーワードとジャンルの両方の条件に一致する書籍のみ表示される</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B169" s="6" t="inlineStr">
-        <is>
-          <t>読書計画</t>
-        </is>
-      </c>
-      <c r="C169" s="6" t="inlineStr">
-        <is>
-          <t>17-1</t>
-        </is>
-      </c>
-      <c r="D169" s="6" t="inlineStr">
-        <is>
-          <t>読書計画の作成・一覧・読了・削除</t>
-        </is>
-      </c>
+      <c r="A169" s="5" t="n"/>
+      <c r="B169" s="5" t="n"/>
+      <c r="C169" s="5" t="n"/>
+      <c r="D169" s="5" t="n"/>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>17-1-1</t>
+          <t>11-1-7</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
+          <t>検索結果が0件の場合の表示を確認する</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
+          <t>1.どの書籍にも一致しないキーワードで検索する</t>
         </is>
       </c>
       <c r="H169" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I169" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
-        </is>
-      </c>
+          <t>「書籍が登録されていません。」など0件である旨が表示される</t>
+        </is>
+      </c>
+      <c r="I169" s="5" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="4" t="n"/>
-      <c r="B170" s="4" t="n"/>
-      <c r="C170" s="4" t="n"/>
-      <c r="D170" s="4" t="n"/>
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>ソート</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>書籍一覧の並び替え</t>
+        </is>
+      </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>17-1-2</t>
+          <t>12-1-1</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
+          <t>並び替え未指定時は新着順(登録が新しい順)で表示される</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>1.自分と他人の読書計画をそれぞれ用意する
-2.読書計画一覧ページを開く</t>
+          <t>1.複数の書籍を異なる日時で登録する
+2.sortを指定せずに書籍一覧を開く</t>
         </is>
       </c>
       <c r="H170" s="7" t="inlineStr">
         <is>
-          <t>自分の計画のみが、target_dateの昇順で表示される</t>
-        </is>
-      </c>
-      <c r="I170" s="4" t="n"/>
+          <t>登録日時が新しい順に表示される</t>
+        </is>
+      </c>
+      <c r="I170" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Sort/SortTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
@@ -5839,23 +5806,23 @@
       <c r="D171" s="4" t="n"/>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>17-1-3</t>
+          <t>12-1-2</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>ステータスで絞り込んで表示できる</t>
+          <t>sort=oldestを指定すると登録が古い順に表示される</t>
         </is>
       </c>
       <c r="G171" s="7" t="inlineStr">
         <is>
-          <t>1.進行中・完了・期限超過の計画をそれぞれ用意する
-2.statusパラメータを指定して一覧を開く</t>
+          <t>1.複数の書籍を異なる日時で登録する
+2.sort=oldestを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H171" s="7" t="inlineStr">
         <is>
-          <t>指定したステータスの計画のみ表示される</t>
+          <t>登録日時が古い順に表示される</t>
         </is>
       </c>
       <c r="I171" s="4" t="n"/>
@@ -5867,23 +5834,23 @@
       <c r="D172" s="4" t="n"/>
       <c r="E172" s="6" t="inlineStr">
         <is>
-          <t>17-1-4</t>
+          <t>12-1-3</t>
         </is>
       </c>
       <c r="F172" s="7" t="inlineStr">
         <is>
-          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
+          <t>sort=titleを指定するとタイトルの昇順で表示される</t>
         </is>
       </c>
       <c r="G172" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍について進行中の計画を作成する
-2.計画作成ページを開く</t>
+          <t>1.複数の書籍を用意する
+2.sort=titleを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H172" s="7" t="inlineStr">
         <is>
-          <t>書籍選択肢にその書籍が表示されない</t>
+          <t>タイトルの昇順で表示される</t>
         </is>
       </c>
       <c r="I172" s="4" t="n"/>
@@ -5895,81 +5862,101 @@
       <c r="D173" s="4" t="n"/>
       <c r="E173" s="6" t="inlineStr">
         <is>
-          <t>17-1-5</t>
+          <t>12-1-4</t>
         </is>
       </c>
       <c r="F173" s="7" t="inlineStr">
         <is>
-          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
+          <t>sort=ratingを指定すると平均評価が高い順に表示される</t>
         </is>
       </c>
       <c r="G173" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
+          <t>1.平均評価が異なる複数の書籍を用意する
+2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H173" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、計画は作成されない</t>
+          <t>平均評価が高い順に表示される</t>
         </is>
       </c>
       <c r="I173" s="4" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="4" t="n"/>
-      <c r="B174" s="4" t="n"/>
-      <c r="C174" s="4" t="n"/>
-      <c r="D174" s="4" t="n"/>
+      <c r="A174" s="5" t="n"/>
+      <c r="B174" s="5" t="n"/>
+      <c r="C174" s="5" t="n"/>
+      <c r="D174" s="5" t="n"/>
       <c r="E174" s="6" t="inlineStr">
         <is>
-          <t>17-1-6</t>
+          <t>12-1-5</t>
         </is>
       </c>
       <c r="F174" s="7" t="inlineStr">
         <is>
-          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
+          <t>sort=rating指定時、平均評価が同じ書籍は新着順で表示される</t>
         </is>
       </c>
       <c r="G174" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を読了(完了)状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.平均評価が同じ複数の書籍を、異なる登録日時で用意する
+2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H174" s="7" t="inlineStr">
         <is>
-          <t>新しい計画が作成される</t>
-        </is>
-      </c>
-      <c r="I174" s="4" t="n"/>
+          <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
+        </is>
+      </c>
+      <c r="I174" s="5" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="4" t="n"/>
-      <c r="B175" s="4" t="n"/>
-      <c r="C175" s="4" t="n"/>
-      <c r="D175" s="4" t="n"/>
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>書籍CRUD（認可の詳細テスト）</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>13-1</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>BookPolicyの認可ロジック</t>
+        </is>
+      </c>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>17-1-7</t>
+          <t>13-1-1</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>ログインユーザーは誰でも書籍を作成できる</t>
         </is>
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.期日を入力せずに登録する</t>
+          <t>1.任意のログインユーザーで BookPolicy::create() を確認する</t>
         </is>
       </c>
       <c r="H175" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I175" s="4" t="n"/>
+          <t>trueが返り、作成が許可される</t>
+        </is>
+      </c>
+      <c r="I175" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/BookAuthorization/BookAuthorizationTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n"/>
@@ -5978,23 +5965,22 @@
       <c r="D176" s="4" t="n"/>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>17-1-8</t>
+          <t>13-1-2</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>書籍の登録者本人は更新が許可される</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.過去の日付を期日に指定して登録する</t>
+          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>trueが返る</t>
         </is>
       </c>
       <c r="I176" s="4" t="n"/>
@@ -6006,23 +5992,22 @@
       <c r="D177" s="4" t="n"/>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>17-1-9</t>
+          <t>13-1-3</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
+          <t>書籍の登録者以外は更新が許可されない</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍・期日を正しく入力して登録する</t>
+          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H177" s="7" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
+          <t>falseが返る</t>
         </is>
       </c>
       <c r="I177" s="4" t="n"/>
@@ -6034,22 +6019,22 @@
       <c r="D178" s="4" t="n"/>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>17-1-10</t>
+          <t>13-1-4</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
+          <t>書籍の登録者本人は削除が許可される</t>
         </is>
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画に対して読了操作を行う</t>
+          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
         </is>
       </c>
       <c r="H178" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
+          <t>trueが返る</t>
         </is>
       </c>
       <c r="I178" s="4" t="n"/>
@@ -6061,127 +6046,126 @@
       <c r="D179" s="4" t="n"/>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>17-1-11</t>
+          <t>13-1-5</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画は読了・削除できない</t>
+          <t>書籍の登録者以外は削除が許可されない</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
         </is>
       </c>
       <c r="H179" s="7" t="inlineStr">
         <is>
-          <t>いずれも403Forbiddenになる</t>
+          <t>falseが返る</t>
         </is>
       </c>
       <c r="I179" s="4" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="4" t="n"/>
-      <c r="B180" s="4" t="n"/>
-      <c r="C180" s="4" t="n"/>
-      <c r="D180" s="4" t="n"/>
+      <c r="A180" s="5" t="n"/>
+      <c r="B180" s="5" t="n"/>
+      <c r="C180" s="5" t="n"/>
+      <c r="D180" s="5" t="n"/>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>17-1-12</t>
+          <t>13-1-6</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>自分が作成した読書計画は削除できる</t>
+          <t>フォームを介さない直接のPUT/DELETEリクエストでも他人の書籍は操作できない</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の削除ボタンを押す</t>
+          <t>1.他人が登録した書籍に対して、直接PUT・DELETEリクエストを送信する</t>
         </is>
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
-          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
-        </is>
-      </c>
-      <c r="I180" s="4" t="n"/>
+          <t>いずれも403Forbiddenになり、データは変更されない</t>
+        </is>
+      </c>
+      <c r="I180" s="5" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="5" t="n"/>
-      <c r="B181" s="5" t="n"/>
-      <c r="C181" s="5" t="n"/>
-      <c r="D181" s="5" t="n"/>
-      <c r="E181" s="8" t="inlineStr">
-        <is>
-          <t>17-1-13</t>
-        </is>
-      </c>
-      <c r="F181" s="9" t="inlineStr">
-        <is>
-          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
-        </is>
-      </c>
-      <c r="G181" s="9" t="inlineStr">
-        <is>
-          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
-2.その読書計画を削除する</t>
-        </is>
-      </c>
-      <c r="H181" s="9" t="inlineStr">
-        <is>
-          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
-        </is>
-      </c>
-      <c r="I181" s="5" t="n"/>
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>ISBN検索</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>14-1</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t>ISBNからの書籍情報取得(外部API連携)</t>
+        </is>
+      </c>
+      <c r="E181" s="6" t="inlineStr">
+        <is>
+          <t>14-1-1</t>
+        </is>
+      </c>
+      <c r="F181" s="7" t="inlineStr">
+        <is>
+          <t>未ログインの場合、ISBN検索エンドポイントにアクセスできない</t>
+        </is>
+      </c>
+      <c r="G181" s="7" t="inlineStr">
+        <is>
+          <t>1.未ログイン状態でGET /books/isbn/{isbn} にアクセスする</t>
+        </is>
+      </c>
+      <c r="H181" s="7" t="inlineStr">
+        <is>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I181" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Isbn/IsbnSearchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="182">
-      <c r="A182" s="6" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B182" s="6" t="inlineStr">
-        <is>
-          <t>読書計画（期限変更）</t>
-        </is>
-      </c>
-      <c r="C182" s="6" t="inlineStr">
-        <is>
-          <t>18-1</t>
-        </is>
-      </c>
-      <c r="D182" s="6" t="inlineStr">
-        <is>
-          <t>読書計画の期日変更</t>
-        </is>
-      </c>
+      <c r="A182" s="4" t="n"/>
+      <c r="B182" s="4" t="n"/>
+      <c r="C182" s="4" t="n"/>
+      <c r="D182" s="4" t="n"/>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>18-1-1</t>
+          <t>14-1-2</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
+          <t>ISBNが未入力(空文字)の場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
+          <t>1.ログイン状態でISBN部分を空にしてリクエストする</t>
         </is>
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I182" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
-        </is>
-      </c>
+          <t>422が返り、「ISBNを入力してください」が返る</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n"/>
@@ -6190,22 +6174,22 @@
       <c r="D183" s="4" t="n"/>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>18-1-2</t>
+          <t>14-1-3</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画の期日は変更できない</t>
+          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
+          <t>1.13桁でないISBNでリクエストする</t>
         </is>
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
+          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
         </is>
       </c>
       <c r="I183" s="4" t="n"/>
@@ -6217,22 +6201,22 @@
       <c r="D184" s="4" t="n"/>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>18-1-3</t>
+          <t>14-1-4</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>編集画面を開くと現在の期日が初期表示される</t>
+          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の編集ページを開く</t>
+          <t>1.登録済みのISBNでリクエストする</t>
         </is>
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>現在登録されている期日が入力欄に表示される</t>
+          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
         </is>
       </c>
       <c r="I184" s="4" t="n"/>
@@ -6244,23 +6228,23 @@
       <c r="D185" s="4" t="n"/>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>18-1-4</t>
+          <t>14-1-5</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
         </is>
       </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.期日を空にして更新する</t>
+          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
+2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
         </is>
       </c>
       <c r="I185" s="4" t="n"/>
@@ -6272,157 +6256,155 @@
       <c r="D186" s="4" t="n"/>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>18-1-5</t>
+          <t>14-1-6</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.過去の日付に変更して更新する</t>
+          <t>1.Http::fake()でitemsが空のレスポンスをモックする
+2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
         </is>
       </c>
       <c r="I186" s="4" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="4" t="n"/>
-      <c r="B187" s="4" t="n"/>
-      <c r="C187" s="4" t="n"/>
-      <c r="D187" s="4" t="n"/>
+      <c r="A187" s="5" t="n"/>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="5" t="n"/>
+      <c r="D187" s="5" t="n"/>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>18-1-6</t>
+          <t>14-1-7</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
+          <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
         </is>
       </c>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.未来の日付に正しく変更して更新する</t>
+          <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
+2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H187" s="7" t="inlineStr">
         <is>
-          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
-        </is>
-      </c>
-      <c r="I187" s="4" t="n"/>
+          <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="4" t="n"/>
-      <c r="B188" s="4" t="n"/>
-      <c r="C188" s="4" t="n"/>
-      <c r="D188" s="4" t="n"/>
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>マイ読書レポート</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>15-1</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>読書統計の表示</t>
+        </is>
+      </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>18-1-7</t>
+          <t>15-1-1</t>
         </is>
       </c>
       <c r="F188" s="7" t="inlineStr">
         <is>
-          <t>一覧・編集画面表示時に、期日を過ぎた「進行中」の計画は自動的に「期限超過」に更新される</t>
+          <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
         </is>
       </c>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>1.期日が過去で「進行中」の計画を用意する
-2.読書計画一覧または編集ページを開く</t>
+          <t>1.未ログイン状態で/reportsを開く</t>
         </is>
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
-          <t>表示前に計画のステータスが「期限超過」に更新される</t>
-        </is>
-      </c>
-      <c r="I188" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I188" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Report/ReportTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="n"/>
-      <c r="B189" s="5" t="n"/>
-      <c r="C189" s="5" t="n"/>
-      <c r="D189" s="5" t="n"/>
+      <c r="A189" s="4" t="n"/>
+      <c r="B189" s="4" t="n"/>
+      <c r="C189" s="4" t="n"/>
+      <c r="D189" s="4" t="n"/>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>18-1-8</t>
+          <t>15-1-2</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は期日を変更できない</t>
+          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
+          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
-        </is>
-      </c>
-      <c r="I189" s="5" t="n"/>
+          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B190" s="6" t="inlineStr">
-        <is>
-          <t>リマインダーバッチ</t>
-        </is>
-      </c>
-      <c r="C190" s="6" t="inlineStr">
-        <is>
-          <t>19-1</t>
-        </is>
-      </c>
-      <c r="D190" s="6" t="inlineStr">
-        <is>
-          <t>reading-plans:remindコマンドによるリマインダー通知</t>
-        </is>
-      </c>
+      <c r="A190" s="4" t="n"/>
+      <c r="B190" s="4" t="n"/>
+      <c r="C190" s="4" t="n"/>
+      <c r="D190" s="4" t="n"/>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>19-1-1</t>
+          <t>15-1-3</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
+          <t>評価分布(★1〜★5)が正しく表示される</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが3日後・ステータス進行中の計画を用意する
-2.Notification::fake()を設定し reading-plans:remind を実行する</t>
+          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I190" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
-        </is>
-      </c>
+          <t>各評価の件数が実データと一致して表示される</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n"/>
@@ -6431,23 +6413,22 @@
       <c r="D191" s="4" t="n"/>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>19-1-2</t>
+          <t>15-1-4</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
+          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが本日・ステータス進行中の計画を用意する
-2.reading-plans:remindを実行する</t>
+          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される</t>
+          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
         </is>
       </c>
       <c r="I191" s="4" t="n"/>
@@ -6459,23 +6440,22 @@
       <c r="D192" s="4" t="n"/>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>19-1-3</t>
+          <t>15-1-5</t>
         </is>
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
-          <t>期限超過から3日後の計画に再エンゲージメント通知が送信される</t>
+          <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
         </is>
       </c>
       <c r="G192" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが3日前・ステータス期限超過の計画を用意する
-2.reading-plans:remindを実行する</t>
+          <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H192" s="7" t="inlineStr">
         <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される</t>
+          <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
         </is>
       </c>
       <c r="I192" s="4" t="n"/>
@@ -6487,23 +6467,22 @@
       <c r="D193" s="5" t="n"/>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>19-1-4</t>
+          <t>15-1-6</t>
         </is>
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>いずれの条件にも該当しない計画には通知が送信されない</t>
+          <t>レビューを1件も投稿していない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G193" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
-2.reading-plans:remindを実行する</t>
+          <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H193" s="7" t="inlineStr">
         <is>
-          <t>その計画のユーザーに通知が送信されない</t>
+          <t>総レビュー数・読了冊数が0、平均評価が0として表示され、TOP5一覧は空になる</t>
         </is>
       </c>
       <c r="I193" s="5" t="n"/>
@@ -6511,48 +6490,48 @@
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B194" s="6" t="inlineStr">
         <is>
-          <t>自動失効バッチ</t>
+          <t>Sanctum認証</t>
         </is>
       </c>
       <c r="C194" s="6" t="inlineStr">
         <is>
-          <t>20-1</t>
+          <t>16-1</t>
         </is>
       </c>
       <c r="D194" s="6" t="inlineStr">
         <is>
-          <t>reading-plans:expireコマンドによる自動失効処理</t>
+          <t>APIトークン認証</t>
         </is>
       </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>20-1-1</t>
+          <t>16-1-1</t>
         </is>
       </c>
       <c r="F194" s="7" t="inlineStr">
         <is>
-          <t>期日を過ぎた「進行中」の計画が「期限超過」に更新される</t>
+          <t>有効なpersonal access tokenを付与すると/api/userにアクセスできる</t>
         </is>
       </c>
       <c r="G194" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが過去・ステータス進行中の計画を用意する
-2.reading-plans:expireを実行する</t>
+          <t>1.$user-&gt;createToken()でトークンを発行する
+2.Authorization: Bearer {token}を付与してGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
-          <t>対象の計画のstatusが「期限超過」に更新される</t>
+          <t>200が返り、対象ユーザーの情報が返る</t>
         </is>
       </c>
       <c r="I194" s="7" t="inlineStr">
         <is>
-          <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
+          <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
         </is>
       </c>
     </row>
@@ -6563,23 +6542,22 @@
       <c r="D195" s="4" t="n"/>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>20-1-2</t>
+          <t>16-1-2</t>
         </is>
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
-          <t>期日が今日以降の「進行中」の計画は失効しない</t>
+          <t>トークンなしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G195" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
-2.reading-plans:expireを実行する</t>
+          <t>1.Authorizationヘッダーを付与せずにGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
-          <t>その計画のstatusは「進行中」のまま変化しない</t>
+          <t>401 Unauthorizedが返る</t>
         </is>
       </c>
       <c r="I195" s="4" t="n"/>
@@ -6591,99 +6569,91 @@
       <c r="D196" s="4" t="n"/>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>20-1-3</t>
+          <t>16-1-3</t>
         </is>
       </c>
       <c r="F196" s="7" t="inlineStr">
         <is>
-          <t>既に「完了」または「期限超過」の計画は対象外(重複更新されない)</t>
+          <t>不正な(存在しない)トークンでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>1.完了済み・期限超過済みの計画をそれぞれ用意する
-2.reading-plans:expireを実行する</t>
+          <t>1.ランダムな文字列をBearerトークンとして付与しGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
-          <t>いずれの計画もstatusが変化しない</t>
+          <t>401 Unauthorizedが返る</t>
         </is>
       </c>
       <c r="I196" s="4" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="5" t="n"/>
-      <c r="B197" s="5" t="n"/>
+      <c r="A197" s="4" t="n"/>
+      <c r="B197" s="4" t="n"/>
       <c r="C197" s="5" t="n"/>
       <c r="D197" s="5" t="n"/>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>20-1-4</t>
+          <t>16-1-4</t>
         </is>
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
-          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+          <t>削除済み(失効済み)のトークンでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>1.失効対象の計画を用意し reading-plans:expire を実行する
-2.DBを直接確認する</t>
+          <t>1.発行済みトークンを削除する
+2.そのトークンでGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
+          <t>401 Unauthorizedが返る</t>
         </is>
       </c>
       <c r="I197" s="5" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B198" s="8" t="inlineStr">
-        <is>
-          <t>通知</t>
-        </is>
-      </c>
-      <c r="C198" s="8" t="inlineStr">
-        <is>
-          <t>21-1</t>
-        </is>
-      </c>
-      <c r="D198" s="8" t="inlineStr">
-        <is>
-          <t>通知の既読化</t>
-        </is>
-      </c>
-      <c r="E198" s="8" t="inlineStr">
-        <is>
-          <t>21-1-1</t>
-        </is>
-      </c>
-      <c r="F198" s="9" t="inlineStr">
-        <is>
-          <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
-        </is>
-      </c>
-      <c r="G198" s="9" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態でPATCH /notifications/{id} に直接リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H198" s="9" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
-        </is>
-      </c>
-      <c r="I198" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationTest.php</t>
+      <c r="A198" s="4" t="n"/>
+      <c r="B198" s="4" t="n"/>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>16-2</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>アクセストークン発行API(POST /api/v1/auth/token)</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>16-2-1</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="inlineStr">
+        <is>
+          <t>正しいメールアドレス・パスワードでトークンが発行される</t>
+        </is>
+      </c>
+      <c r="G198" s="3" t="inlineStr">
+        <is>
+          <t>1.ユーザーを用意する
+2.そのユーザーのメールアドレス・パスワードでPOST /api/v1/auth/tokenにアクセスする(Accept: application/json)</t>
+        </is>
+      </c>
+      <c r="H198" s="3" t="inlineStr">
+        <is>
+          <t>201が返り、token(文字列)とtoken_type(Bearer)を含むJSONが返る</t>
+        </is>
+      </c>
+      <c r="I198" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/SanctumAuth/TokenIssueTest.php</t>
         </is>
       </c>
     </row>
@@ -6692,208 +6662,1402 @@
       <c r="B199" s="4" t="n"/>
       <c r="C199" s="4" t="n"/>
       <c r="D199" s="4" t="n"/>
-      <c r="E199" s="8" t="inlineStr">
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>16-2-2</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="inlineStr">
+        <is>
+          <t>発行されたトークンで、認証が必要なAPIにアクセスできる</t>
+        </is>
+      </c>
+      <c r="G199" s="3" t="inlineStr">
+        <is>
+          <t>1.POST /api/v1/auth/tokenでトークンを発行する
+2.そのトークンをBearerヘッダーに付与してGET /api/userにアクセスする</t>
+        </is>
+      </c>
+      <c r="H199" s="3" t="inlineStr">
+        <is>
+          <t>200が返り、トークンを発行したユーザーの情報が返る</t>
+        </is>
+      </c>
+      <c r="I199" s="4" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="n"/>
+      <c r="B200" s="4" t="n"/>
+      <c r="C200" s="4" t="n"/>
+      <c r="D200" s="4" t="n"/>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>16-2-3</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="inlineStr">
+        <is>
+          <t>発行したトークンが保存され、device_nameを指定するとトークン名になる(省略時は「api-token」)</t>
+        </is>
+      </c>
+      <c r="G200" s="3" t="inlineStr">
+        <is>
+          <t>1.device_nameを指定して、または省略してPOST /api/v1/auth/tokenにアクセスする
+2.personal_access_tokensテーブルを確認する</t>
+        </is>
+      </c>
+      <c r="H200" s="3" t="inlineStr">
+        <is>
+          <t>対象ユーザーのトークンが保存され、nameが指定したdevice_name(省略時はapi-token)になっている。平文のトークンは保存されない</t>
+        </is>
+      </c>
+      <c r="I200" s="4" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="n"/>
+      <c r="B201" s="4" t="n"/>
+      <c r="C201" s="4" t="n"/>
+      <c r="D201" s="4" t="n"/>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>16-2-4</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="inlineStr">
+        <is>
+          <t>同じユーザーが複数回発行でき、それぞれのトークンが有効</t>
+        </is>
+      </c>
+      <c r="G201" s="3" t="inlineStr">
+        <is>
+          <t>1.同じユーザーでPOST /api/v1/auth/tokenに2回アクセスする
+2.それぞれのトークンでGET /api/userにアクセスする</t>
+        </is>
+      </c>
+      <c r="H201" s="3" t="inlineStr">
+        <is>
+          <t>2つのトークンが発行され、どちらでも200が返る</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="n"/>
+      <c r="B202" s="4" t="n"/>
+      <c r="C202" s="4" t="n"/>
+      <c r="D202" s="4" t="n"/>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>16-2-5</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="inlineStr">
+        <is>
+          <t>パスワードが誤っている場合、422が返りトークンは発行されない</t>
+        </is>
+      </c>
+      <c r="G202" s="3" t="inlineStr">
+        <is>
+          <t>1.登録済みのメールアドレスと誤ったパスワードでPOST /api/v1/auth/tokenにアクセスする</t>
+        </is>
+      </c>
+      <c r="H202" s="3" t="inlineStr">
+        <is>
+          <t>422が返り、「会員情報が登録されていません」が返る。トークンは作成されない</t>
+        </is>
+      </c>
+      <c r="I202" s="4" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="n"/>
+      <c r="B203" s="4" t="n"/>
+      <c r="C203" s="4" t="n"/>
+      <c r="D203" s="4" t="n"/>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>16-2-6</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="inlineStr">
+        <is>
+          <t>登録されていないメールアドレスの場合、422が返る</t>
+        </is>
+      </c>
+      <c r="G203" s="3" t="inlineStr">
+        <is>
+          <t>1.未登録のメールアドレスでPOST /api/v1/auth/tokenにアクセスする</t>
+        </is>
+      </c>
+      <c r="H203" s="3" t="inlineStr">
+        <is>
+          <t>422が返り、「会員情報が登録されていません」が返る(パスワード誤りの場合と同じメッセージ)</t>
+        </is>
+      </c>
+      <c r="I203" s="4" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="n"/>
+      <c r="B204" s="4" t="n"/>
+      <c r="C204" s="4" t="n"/>
+      <c r="D204" s="4" t="n"/>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>16-2-7</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="inlineStr">
+        <is>
+          <t>メールアドレスが未入力の場合、422が返る</t>
+        </is>
+      </c>
+      <c r="G204" s="3" t="inlineStr">
+        <is>
+          <t>1.メールアドレスを指定せずPOST /api/v1/auth/tokenにアクセスする</t>
+        </is>
+      </c>
+      <c r="H204" s="3" t="inlineStr">
+        <is>
+          <t>422が返り、「メールアドレスを入力してください」が返る</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="n"/>
+      <c r="B205" s="4" t="n"/>
+      <c r="C205" s="4" t="n"/>
+      <c r="D205" s="4" t="n"/>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>16-2-8</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="inlineStr">
+        <is>
+          <t>メールアドレスがメール形式でない場合、422が返る</t>
+        </is>
+      </c>
+      <c r="G205" s="3" t="inlineStr">
+        <is>
+          <t>1.「abc」のようなメール形式でない値を指定してPOST /api/v1/auth/tokenにアクセスする</t>
+        </is>
+      </c>
+      <c r="H205" s="3" t="inlineStr">
+        <is>
+          <t>422が返り、「メールアドレスはメール形式で入力してください」が返る</t>
+        </is>
+      </c>
+      <c r="I205" s="4" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="n"/>
+      <c r="B206" s="4" t="n"/>
+      <c r="C206" s="4" t="n"/>
+      <c r="D206" s="4" t="n"/>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>16-2-9</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="inlineStr">
+        <is>
+          <t>パスワードが未入力の場合、422が返る</t>
+        </is>
+      </c>
+      <c r="G206" s="3" t="inlineStr">
+        <is>
+          <t>1.パスワードを指定せずPOST /api/v1/auth/tokenにアクセスする</t>
+        </is>
+      </c>
+      <c r="H206" s="3" t="inlineStr">
+        <is>
+          <t>422が返り、「パスワードを入力してください」が返る</t>
+        </is>
+      </c>
+      <c r="I206" s="4" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="n"/>
+      <c r="B207" s="5" t="n"/>
+      <c r="C207" s="5" t="n"/>
+      <c r="D207" s="5" t="n"/>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>16-2-10</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="inlineStr">
+        <is>
+          <t>device_nameが256文字以上の場合、422が返る</t>
+        </is>
+      </c>
+      <c r="G207" s="3" t="inlineStr">
+        <is>
+          <t>1.256文字のdevice_nameを指定してPOST /api/v1/auth/tokenにアクセスする</t>
+        </is>
+      </c>
+      <c r="H207" s="3" t="inlineStr">
+        <is>
+          <t>422が返り、「トークン名は255文字以内で入力してください」が返る</t>
+        </is>
+      </c>
+      <c r="I207" s="5" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B208" s="6" t="inlineStr">
+        <is>
+          <t>読書計画</t>
+        </is>
+      </c>
+      <c r="C208" s="6" t="inlineStr">
+        <is>
+          <t>17-1</t>
+        </is>
+      </c>
+      <c r="D208" s="6" t="inlineStr">
+        <is>
+          <t>読書計画の作成・一覧・読了・削除</t>
+        </is>
+      </c>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>17-1-1</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
+        </is>
+      </c>
+      <c r="H208" s="7" t="inlineStr">
+        <is>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I208" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="n"/>
+      <c r="B209" s="4" t="n"/>
+      <c r="C209" s="4" t="n"/>
+      <c r="D209" s="4" t="n"/>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>17-1-2</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>1.自分と他人の読書計画をそれぞれ用意する
+2.読書計画一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H209" s="7" t="inlineStr">
+        <is>
+          <t>自分の計画のみが、target_dateの昇順で表示される</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n"/>
+      <c r="B210" s="4" t="n"/>
+      <c r="C210" s="4" t="n"/>
+      <c r="D210" s="4" t="n"/>
+      <c r="E210" s="6" t="inlineStr">
+        <is>
+          <t>17-1-3</t>
+        </is>
+      </c>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>ステータスで絞り込んで表示できる</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="inlineStr">
+        <is>
+          <t>1.進行中・完了・期限超過の計画をそれぞれ用意する
+2.statusパラメータを指定して一覧を開く</t>
+        </is>
+      </c>
+      <c r="H210" s="7" t="inlineStr">
+        <is>
+          <t>指定したステータスの計画のみ表示される</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="n"/>
+      <c r="B211" s="4" t="n"/>
+      <c r="C211" s="4" t="n"/>
+      <c r="D211" s="4" t="n"/>
+      <c r="E211" s="6" t="inlineStr">
+        <is>
+          <t>17-1-4</t>
+        </is>
+      </c>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t>1.ある書籍について進行中の計画を作成する
+2.計画作成ページを開く</t>
+        </is>
+      </c>
+      <c r="H211" s="7" t="inlineStr">
+        <is>
+          <t>書籍選択肢にその書籍が表示されない</t>
+        </is>
+      </c>
+      <c r="I211" s="4" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="n"/>
+      <c r="B212" s="4" t="n"/>
+      <c r="C212" s="4" t="n"/>
+      <c r="D212" s="4" t="n"/>
+      <c r="E212" s="6" t="inlineStr">
+        <is>
+          <t>17-1-5</t>
+        </is>
+      </c>
+      <c r="F212" s="7" t="inlineStr">
+        <is>
+          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
+        </is>
+      </c>
+      <c r="G212" s="7" t="inlineStr">
+        <is>
+          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H212" s="7" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、計画は作成されない</t>
+        </is>
+      </c>
+      <c r="I212" s="4" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="n"/>
+      <c r="B213" s="4" t="n"/>
+      <c r="C213" s="4" t="n"/>
+      <c r="D213" s="4" t="n"/>
+      <c r="E213" s="6" t="inlineStr">
+        <is>
+          <t>17-1-6</t>
+        </is>
+      </c>
+      <c r="F213" s="7" t="inlineStr">
+        <is>
+          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
+        </is>
+      </c>
+      <c r="G213" s="7" t="inlineStr">
+        <is>
+          <t>1.ある書籍の計画を読了(完了)状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H213" s="7" t="inlineStr">
+        <is>
+          <t>新しい計画が作成される</t>
+        </is>
+      </c>
+      <c r="I213" s="4" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="n"/>
+      <c r="B214" s="4" t="n"/>
+      <c r="C214" s="4" t="n"/>
+      <c r="D214" s="4" t="n"/>
+      <c r="E214" s="6" t="inlineStr">
+        <is>
+          <t>17-1-7</t>
+        </is>
+      </c>
+      <c r="F214" s="7" t="inlineStr">
+        <is>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+        </is>
+      </c>
+      <c r="G214" s="7" t="inlineStr">
+        <is>
+          <t>1.計画作成ページを開く
+2.期日を入力せずに登録する</t>
+        </is>
+      </c>
+      <c r="H214" s="7" t="inlineStr">
+        <is>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="n"/>
+      <c r="B215" s="4" t="n"/>
+      <c r="C215" s="4" t="n"/>
+      <c r="D215" s="4" t="n"/>
+      <c r="E215" s="6" t="inlineStr">
+        <is>
+          <t>17-1-8</t>
+        </is>
+      </c>
+      <c r="F215" s="7" t="inlineStr">
+        <is>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+        </is>
+      </c>
+      <c r="G215" s="7" t="inlineStr">
+        <is>
+          <t>1.計画作成ページを開く
+2.過去の日付を期日に指定して登録する</t>
+        </is>
+      </c>
+      <c r="H215" s="7" t="inlineStr">
+        <is>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I215" s="4" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="n"/>
+      <c r="B216" s="4" t="n"/>
+      <c r="C216" s="4" t="n"/>
+      <c r="D216" s="4" t="n"/>
+      <c r="E216" s="6" t="inlineStr">
+        <is>
+          <t>17-1-9</t>
+        </is>
+      </c>
+      <c r="F216" s="7" t="inlineStr">
+        <is>
+          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="inlineStr">
+        <is>
+          <t>1.計画作成ページを開く
+2.書籍・期日を正しく入力して登録する</t>
+        </is>
+      </c>
+      <c r="H216" s="7" t="inlineStr">
+        <is>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
+        </is>
+      </c>
+      <c r="I216" s="4" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="n"/>
+      <c r="B217" s="4" t="n"/>
+      <c r="C217" s="4" t="n"/>
+      <c r="D217" s="4" t="n"/>
+      <c r="E217" s="6" t="inlineStr">
+        <is>
+          <t>17-1-10</t>
+        </is>
+      </c>
+      <c r="F217" s="7" t="inlineStr">
+        <is>
+          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="inlineStr">
+        <is>
+          <t>1.進行中の計画に対して読了操作を行う</t>
+        </is>
+      </c>
+      <c r="H217" s="7" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
+        </is>
+      </c>
+      <c r="I217" s="4" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="n"/>
+      <c r="B218" s="4" t="n"/>
+      <c r="C218" s="4" t="n"/>
+      <c r="D218" s="4" t="n"/>
+      <c r="E218" s="6" t="inlineStr">
+        <is>
+          <t>17-1-11</t>
+        </is>
+      </c>
+      <c r="F218" s="7" t="inlineStr">
+        <is>
+          <t>他人が作成した読書計画は読了・削除できない</t>
+        </is>
+      </c>
+      <c r="G218" s="7" t="inlineStr">
+        <is>
+          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+        </is>
+      </c>
+      <c r="H218" s="7" t="inlineStr">
+        <is>
+          <t>いずれも403Forbiddenになる</t>
+        </is>
+      </c>
+      <c r="I218" s="4" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="n"/>
+      <c r="B219" s="4" t="n"/>
+      <c r="C219" s="4" t="n"/>
+      <c r="D219" s="4" t="n"/>
+      <c r="E219" s="6" t="inlineStr">
+        <is>
+          <t>17-1-12</t>
+        </is>
+      </c>
+      <c r="F219" s="7" t="inlineStr">
+        <is>
+          <t>自分が作成した読書計画は削除できる</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="inlineStr">
+        <is>
+          <t>1.自分が作成した計画の削除ボタンを押す</t>
+        </is>
+      </c>
+      <c r="H219" s="7" t="inlineStr">
+        <is>
+          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
+        </is>
+      </c>
+      <c r="I219" s="4" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="5" t="n"/>
+      <c r="B220" s="5" t="n"/>
+      <c r="C220" s="5" t="n"/>
+      <c r="D220" s="5" t="n"/>
+      <c r="E220" s="8" t="inlineStr">
+        <is>
+          <t>17-1-13</t>
+        </is>
+      </c>
+      <c r="F220" s="9" t="inlineStr">
+        <is>
+          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
+        </is>
+      </c>
+      <c r="G220" s="9" t="inlineStr">
+        <is>
+          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
+2.その読書計画を削除する</t>
+        </is>
+      </c>
+      <c r="H220" s="9" t="inlineStr">
+        <is>
+          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
+        </is>
+      </c>
+      <c r="I220" s="5" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B221" s="6" t="inlineStr">
+        <is>
+          <t>読書計画（期限変更）</t>
+        </is>
+      </c>
+      <c r="C221" s="6" t="inlineStr">
+        <is>
+          <t>18-1</t>
+        </is>
+      </c>
+      <c r="D221" s="6" t="inlineStr">
+        <is>
+          <t>読書計画の期日変更</t>
+        </is>
+      </c>
+      <c r="E221" s="6" t="inlineStr">
+        <is>
+          <t>18-1-1</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="inlineStr">
+        <is>
+          <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
+        </is>
+      </c>
+      <c r="H221" s="7" t="inlineStr">
+        <is>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I221" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="n"/>
+      <c r="B222" s="4" t="n"/>
+      <c r="C222" s="4" t="n"/>
+      <c r="D222" s="4" t="n"/>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>18-1-2</t>
+        </is>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>他人が作成した読書計画の期日は変更できない</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H222" s="7" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、期日は変更されない</t>
+        </is>
+      </c>
+      <c r="I222" s="4" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="n"/>
+      <c r="B223" s="4" t="n"/>
+      <c r="C223" s="4" t="n"/>
+      <c r="D223" s="4" t="n"/>
+      <c r="E223" s="6" t="inlineStr">
+        <is>
+          <t>18-1-3</t>
+        </is>
+      </c>
+      <c r="F223" s="7" t="inlineStr">
+        <is>
+          <t>編集画面を開くと現在の期日が初期表示される</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="inlineStr">
+        <is>
+          <t>1.自分が作成した計画の編集ページを開く</t>
+        </is>
+      </c>
+      <c r="H223" s="7" t="inlineStr">
+        <is>
+          <t>現在登録されている期日が入力欄に表示される</t>
+        </is>
+      </c>
+      <c r="I223" s="4" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="n"/>
+      <c r="B224" s="4" t="n"/>
+      <c r="C224" s="4" t="n"/>
+      <c r="D224" s="4" t="n"/>
+      <c r="E224" s="6" t="inlineStr">
+        <is>
+          <t>18-1-4</t>
+        </is>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="inlineStr">
+        <is>
+          <t>1.編集ページを開く
+2.期日を空にして更新する</t>
+        </is>
+      </c>
+      <c r="H224" s="7" t="inlineStr">
+        <is>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="n"/>
+      <c r="B225" s="4" t="n"/>
+      <c r="C225" s="4" t="n"/>
+      <c r="D225" s="4" t="n"/>
+      <c r="E225" s="6" t="inlineStr">
+        <is>
+          <t>18-1-5</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>1.編集ページを開く
+2.過去の日付に変更して更新する</t>
+        </is>
+      </c>
+      <c r="H225" s="7" t="inlineStr">
+        <is>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="n"/>
+      <c r="B226" s="4" t="n"/>
+      <c r="C226" s="4" t="n"/>
+      <c r="D226" s="4" t="n"/>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>18-1-6</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr">
+        <is>
+          <t>1.編集ページを開く
+2.未来の日付に正しく変更して更新する</t>
+        </is>
+      </c>
+      <c r="H226" s="7" t="inlineStr">
+        <is>
+          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
+        </is>
+      </c>
+      <c r="I226" s="4" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="n"/>
+      <c r="B227" s="4" t="n"/>
+      <c r="C227" s="4" t="n"/>
+      <c r="D227" s="4" t="n"/>
+      <c r="E227" s="6" t="inlineStr">
+        <is>
+          <t>18-1-7</t>
+        </is>
+      </c>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>一覧・編集画面表示時に、期日を過ぎた「進行中」の計画は自動的に「期限超過」に更新される</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="inlineStr">
+        <is>
+          <t>1.期日が過去で「進行中」の計画を用意する
+2.読書計画一覧または編集ページを開く</t>
+        </is>
+      </c>
+      <c r="H227" s="7" t="inlineStr">
+        <is>
+          <t>表示前に計画のステータスが「期限超過」に更新される</t>
+        </is>
+      </c>
+      <c r="I227" s="4" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="n"/>
+      <c r="B228" s="5" t="n"/>
+      <c r="C228" s="5" t="n"/>
+      <c r="D228" s="5" t="n"/>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>18-1-8</t>
+        </is>
+      </c>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」の計画は期日を変更できない</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="inlineStr">
+        <is>
+          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H228" s="7" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、期日は変更されない</t>
+        </is>
+      </c>
+      <c r="I228" s="5" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B229" s="6" t="inlineStr">
+        <is>
+          <t>リマインダーバッチ</t>
+        </is>
+      </c>
+      <c r="C229" s="6" t="inlineStr">
+        <is>
+          <t>19-1</t>
+        </is>
+      </c>
+      <c r="D229" s="6" t="inlineStr">
+        <is>
+          <t>reading-plans:remindコマンドによるリマインダー通知</t>
+        </is>
+      </c>
+      <c r="E229" s="6" t="inlineStr">
+        <is>
+          <t>19-1-1</t>
+        </is>
+      </c>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日後・ステータス進行中の計画を用意する
+2.Notification::fake()を設定し reading-plans:remind を実行する</t>
+        </is>
+      </c>
+      <c r="H229" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I229" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="n"/>
+      <c r="B230" s="4" t="n"/>
+      <c r="C230" s="4" t="n"/>
+      <c r="D230" s="4" t="n"/>
+      <c r="E230" s="6" t="inlineStr">
+        <is>
+          <t>19-1-2</t>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが本日・ステータス進行中の計画を用意する
+2.reading-plans:remindを実行する</t>
+        </is>
+      </c>
+      <c r="H230" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I230" s="4" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="n"/>
+      <c r="B231" s="4" t="n"/>
+      <c r="C231" s="4" t="n"/>
+      <c r="D231" s="4" t="n"/>
+      <c r="E231" s="6" t="inlineStr">
+        <is>
+          <t>19-1-3</t>
+        </is>
+      </c>
+      <c r="F231" s="7" t="inlineStr">
+        <is>
+          <t>期限超過から3日後の計画に再エンゲージメント通知が送信される</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日前・ステータス期限超過の計画を用意する
+2.reading-plans:remindを実行する</t>
+        </is>
+      </c>
+      <c r="H231" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I231" s="4" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="n"/>
+      <c r="B232" s="5" t="n"/>
+      <c r="C232" s="5" t="n"/>
+      <c r="D232" s="5" t="n"/>
+      <c r="E232" s="6" t="inlineStr">
+        <is>
+          <t>19-1-4</t>
+        </is>
+      </c>
+      <c r="F232" s="7" t="inlineStr">
+        <is>
+          <t>いずれの条件にも該当しない計画には通知が送信されない</t>
+        </is>
+      </c>
+      <c r="G232" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
+2.reading-plans:remindを実行する</t>
+        </is>
+      </c>
+      <c r="H232" s="7" t="inlineStr">
+        <is>
+          <t>その計画のユーザーに通知が送信されない</t>
+        </is>
+      </c>
+      <c r="I232" s="5" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B233" s="6" t="inlineStr">
+        <is>
+          <t>自動失効バッチ</t>
+        </is>
+      </c>
+      <c r="C233" s="6" t="inlineStr">
+        <is>
+          <t>20-1</t>
+        </is>
+      </c>
+      <c r="D233" s="6" t="inlineStr">
+        <is>
+          <t>reading-plans:expireコマンドによる自動失効処理</t>
+        </is>
+      </c>
+      <c r="E233" s="6" t="inlineStr">
+        <is>
+          <t>20-1-1</t>
+        </is>
+      </c>
+      <c r="F233" s="7" t="inlineStr">
+        <is>
+          <t>期日を過ぎた「進行中」の計画が「期限超過」に更新される</t>
+        </is>
+      </c>
+      <c r="G233" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが過去・ステータス進行中の計画を用意する
+2.reading-plans:expireを実行する</t>
+        </is>
+      </c>
+      <c r="H233" s="7" t="inlineStr">
+        <is>
+          <t>対象の計画のstatusが「期限超過」に更新される</t>
+        </is>
+      </c>
+      <c r="I233" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="n"/>
+      <c r="B234" s="4" t="n"/>
+      <c r="C234" s="4" t="n"/>
+      <c r="D234" s="4" t="n"/>
+      <c r="E234" s="6" t="inlineStr">
+        <is>
+          <t>20-1-2</t>
+        </is>
+      </c>
+      <c r="F234" s="7" t="inlineStr">
+        <is>
+          <t>期日が今日以降の「進行中」の計画は失効しない</t>
+        </is>
+      </c>
+      <c r="G234" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
+2.reading-plans:expireを実行する</t>
+        </is>
+      </c>
+      <c r="H234" s="7" t="inlineStr">
+        <is>
+          <t>その計画のstatusは「進行中」のまま変化しない</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="n"/>
+      <c r="B235" s="4" t="n"/>
+      <c r="C235" s="4" t="n"/>
+      <c r="D235" s="4" t="n"/>
+      <c r="E235" s="6" t="inlineStr">
+        <is>
+          <t>20-1-3</t>
+        </is>
+      </c>
+      <c r="F235" s="7" t="inlineStr">
+        <is>
+          <t>既に「完了」または「期限超過」の計画は対象外(重複更新されない)</t>
+        </is>
+      </c>
+      <c r="G235" s="7" t="inlineStr">
+        <is>
+          <t>1.完了済み・期限超過済みの計画をそれぞれ用意する
+2.reading-plans:expireを実行する</t>
+        </is>
+      </c>
+      <c r="H235" s="7" t="inlineStr">
+        <is>
+          <t>いずれの計画もstatusが変化しない</t>
+        </is>
+      </c>
+      <c r="I235" s="4" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="n"/>
+      <c r="B236" s="5" t="n"/>
+      <c r="C236" s="5" t="n"/>
+      <c r="D236" s="5" t="n"/>
+      <c r="E236" s="6" t="inlineStr">
+        <is>
+          <t>20-1-4</t>
+        </is>
+      </c>
+      <c r="F236" s="7" t="inlineStr">
+        <is>
+          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+        </is>
+      </c>
+      <c r="G236" s="7" t="inlineStr">
+        <is>
+          <t>1.失効対象の計画を用意し reading-plans:expire を実行する
+2.DBを直接確認する</t>
+        </is>
+      </c>
+      <c r="H236" s="7" t="inlineStr">
+        <is>
+          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
+        </is>
+      </c>
+      <c r="I236" s="5" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B237" s="8" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="C237" s="8" t="inlineStr">
+        <is>
+          <t>21-1</t>
+        </is>
+      </c>
+      <c r="D237" s="8" t="inlineStr">
+        <is>
+          <t>通知の既読化</t>
+        </is>
+      </c>
+      <c r="E237" s="8" t="inlineStr">
+        <is>
+          <t>21-1-1</t>
+        </is>
+      </c>
+      <c r="F237" s="9" t="inlineStr">
+        <is>
+          <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
+        </is>
+      </c>
+      <c r="G237" s="9" t="inlineStr">
+        <is>
+          <t>1.未ログイン状態でPATCH /notifications/{id} に直接リクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H237" s="9" t="inlineStr">
+        <is>
+          <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
+        </is>
+      </c>
+      <c r="I237" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="n"/>
+      <c r="B238" s="4" t="n"/>
+      <c r="C238" s="4" t="n"/>
+      <c r="D238" s="4" t="n"/>
+      <c r="E238" s="8" t="inlineStr">
         <is>
           <t>21-1-2</t>
         </is>
       </c>
-      <c r="F199" s="9" t="inlineStr">
+      <c r="F238" s="9" t="inlineStr">
         <is>
           <t>自分の通知を既読にできる</t>
         </is>
       </c>
-      <c r="G199" s="9" t="inlineStr">
+      <c r="G238" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知を用意する
 2.その通知に対してPATCH /notifications/{id} を送信する</t>
         </is>
       </c>
-      <c r="H199" s="9" t="inlineStr">
+      <c r="H238" s="9" t="inlineStr">
         <is>
           <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）</t>
         </is>
       </c>
-      <c r="I199" s="4" t="n"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="5" t="n"/>
-      <c r="B200" s="5" t="n"/>
-      <c r="C200" s="5" t="n"/>
-      <c r="D200" s="5" t="n"/>
-      <c r="E200" s="8" t="inlineStr">
+      <c r="I238" s="4" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="n"/>
+      <c r="B239" s="5" t="n"/>
+      <c r="C239" s="5" t="n"/>
+      <c r="D239" s="5" t="n"/>
+      <c r="E239" s="8" t="inlineStr">
         <is>
           <t>21-1-3</t>
         </is>
       </c>
-      <c r="F200" s="9" t="inlineStr">
+      <c r="F239" s="9" t="inlineStr">
         <is>
           <t>他ユーザーの通知は既読にできない</t>
         </is>
       </c>
-      <c r="G200" s="9" t="inlineStr">
+      <c r="G239" s="9" t="inlineStr">
         <is>
           <t>1.他ユーザー宛ての通知を用意する
 2.そのIDに対してPATCH /notifications/{id} を送信する</t>
         </is>
       </c>
-      <c r="H200" s="9" t="inlineStr">
+      <c r="H239" s="9" t="inlineStr">
         <is>
           <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
         </is>
       </c>
-      <c r="I200" s="5" t="n"/>
+      <c r="I239" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="150">
-    <mergeCell ref="D141:D145"/>
+  <mergeCells count="168">
     <mergeCell ref="I30:I33"/>
     <mergeCell ref="I92:I96"/>
     <mergeCell ref="C131:C133"/>
     <mergeCell ref="D34:D39"/>
     <mergeCell ref="D59:D62"/>
     <mergeCell ref="C30:C33"/>
-    <mergeCell ref="A134:A140"/>
+    <mergeCell ref="D181:D187"/>
+    <mergeCell ref="B221:B228"/>
+    <mergeCell ref="I194:I197"/>
     <mergeCell ref="D67:D71"/>
-    <mergeCell ref="I194:I197"/>
+    <mergeCell ref="I10:I14"/>
     <mergeCell ref="C7:C9"/>
-    <mergeCell ref="I10:I14"/>
-    <mergeCell ref="I152:I158"/>
-    <mergeCell ref="I159:I164"/>
+    <mergeCell ref="B131:B162"/>
+    <mergeCell ref="C175:C180"/>
     <mergeCell ref="C125:C129"/>
     <mergeCell ref="I72:I77"/>
+    <mergeCell ref="B229:B232"/>
+    <mergeCell ref="A233:A236"/>
+    <mergeCell ref="A170:A174"/>
     <mergeCell ref="B16:B29"/>
+    <mergeCell ref="C170:C174"/>
+    <mergeCell ref="D229:D232"/>
+    <mergeCell ref="I198:I207"/>
     <mergeCell ref="D85:D89"/>
+    <mergeCell ref="I175:I180"/>
+    <mergeCell ref="B163:B169"/>
     <mergeCell ref="D78:D81"/>
-    <mergeCell ref="C141:C145"/>
+    <mergeCell ref="I237:I239"/>
+    <mergeCell ref="I134:I141"/>
+    <mergeCell ref="A237:A239"/>
     <mergeCell ref="C2:C5"/>
+    <mergeCell ref="I145:I151"/>
+    <mergeCell ref="C134:C141"/>
     <mergeCell ref="B2:B15"/>
-    <mergeCell ref="C165:C168"/>
+    <mergeCell ref="D221:D228"/>
+    <mergeCell ref="D158:D162"/>
     <mergeCell ref="I131:I133"/>
-    <mergeCell ref="I141:I145"/>
     <mergeCell ref="I100:I102"/>
-    <mergeCell ref="A165:A168"/>
+    <mergeCell ref="I109:I112"/>
+    <mergeCell ref="I85:I89"/>
     <mergeCell ref="C10:C14"/>
-    <mergeCell ref="I85:I89"/>
     <mergeCell ref="D7:D9"/>
-    <mergeCell ref="I109:I112"/>
     <mergeCell ref="I34:I39"/>
+    <mergeCell ref="I208:I220"/>
+    <mergeCell ref="I59:I62"/>
     <mergeCell ref="D63:D66"/>
-    <mergeCell ref="A198:A200"/>
-    <mergeCell ref="I59:I62"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="A169:A181"/>
-    <mergeCell ref="C198:C200"/>
-    <mergeCell ref="D134:D140"/>
+    <mergeCell ref="I181:I187"/>
+    <mergeCell ref="A229:A232"/>
+    <mergeCell ref="C229:C232"/>
     <mergeCell ref="B63:B81"/>
+    <mergeCell ref="A194:A207"/>
     <mergeCell ref="I67:I71"/>
-    <mergeCell ref="B159:B164"/>
     <mergeCell ref="C34:C39"/>
-    <mergeCell ref="D159:D164"/>
-    <mergeCell ref="D182:D189"/>
-    <mergeCell ref="A182:A189"/>
+    <mergeCell ref="I142:I144"/>
+    <mergeCell ref="D233:D236"/>
+    <mergeCell ref="A208:A220"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="A106:A108"/>
     <mergeCell ref="C106:C108"/>
-    <mergeCell ref="D152:D158"/>
-    <mergeCell ref="I165:I168"/>
+    <mergeCell ref="I188:I193"/>
+    <mergeCell ref="B237:B239"/>
+    <mergeCell ref="C158:C162"/>
+    <mergeCell ref="C152:C157"/>
     <mergeCell ref="C40:C52"/>
     <mergeCell ref="C109:C112"/>
-    <mergeCell ref="B131:B133"/>
-    <mergeCell ref="B141:B145"/>
+    <mergeCell ref="I158:I162"/>
+    <mergeCell ref="C92:C96"/>
+    <mergeCell ref="B113:B130"/>
     <mergeCell ref="D100:D102"/>
-    <mergeCell ref="A194:A197"/>
-    <mergeCell ref="B113:B130"/>
-    <mergeCell ref="C92:C96"/>
     <mergeCell ref="C113:C124"/>
-    <mergeCell ref="A152:A158"/>
+    <mergeCell ref="C145:C151"/>
+    <mergeCell ref="I152:I157"/>
     <mergeCell ref="D53:D58"/>
-    <mergeCell ref="D165:D168"/>
     <mergeCell ref="D30:D33"/>
     <mergeCell ref="A82:A99"/>
-    <mergeCell ref="D198:D200"/>
+    <mergeCell ref="I106:I108"/>
     <mergeCell ref="I63:I66"/>
-    <mergeCell ref="I106:I108"/>
+    <mergeCell ref="C198:C207"/>
     <mergeCell ref="D16:D29"/>
-    <mergeCell ref="I182:I189"/>
-    <mergeCell ref="C134:C140"/>
     <mergeCell ref="A63:A81"/>
+    <mergeCell ref="B208:B220"/>
     <mergeCell ref="D103:D105"/>
+    <mergeCell ref="D163:D169"/>
+    <mergeCell ref="D208:D220"/>
+    <mergeCell ref="D97:D99"/>
+    <mergeCell ref="B188:B193"/>
     <mergeCell ref="D90:D91"/>
-    <mergeCell ref="D97:D99"/>
-    <mergeCell ref="B169:B181"/>
     <mergeCell ref="D106:D108"/>
+    <mergeCell ref="D188:D193"/>
+    <mergeCell ref="A131:A162"/>
+    <mergeCell ref="C237:C239"/>
     <mergeCell ref="B109:B112"/>
     <mergeCell ref="D109:D112"/>
-    <mergeCell ref="A141:A145"/>
     <mergeCell ref="C82:C84"/>
+    <mergeCell ref="D142:D144"/>
     <mergeCell ref="C67:C71"/>
+    <mergeCell ref="A163:A169"/>
+    <mergeCell ref="C163:C169"/>
+    <mergeCell ref="I233:I236"/>
     <mergeCell ref="D82:D84"/>
+    <mergeCell ref="D131:D133"/>
     <mergeCell ref="I53:I58"/>
-    <mergeCell ref="D131:D133"/>
-    <mergeCell ref="I190:I193"/>
     <mergeCell ref="C59:C62"/>
-    <mergeCell ref="I198:I200"/>
+    <mergeCell ref="A221:A228"/>
+    <mergeCell ref="C221:C228"/>
+    <mergeCell ref="D198:D207"/>
+    <mergeCell ref="D237:D239"/>
+    <mergeCell ref="B175:B180"/>
     <mergeCell ref="C97:C99"/>
+    <mergeCell ref="D175:D180"/>
     <mergeCell ref="I113:I124"/>
-    <mergeCell ref="B182:B189"/>
+    <mergeCell ref="D134:D141"/>
     <mergeCell ref="I16:I29"/>
+    <mergeCell ref="I221:I228"/>
+    <mergeCell ref="A175:A180"/>
     <mergeCell ref="A16:A29"/>
-    <mergeCell ref="B146:B151"/>
     <mergeCell ref="C16:C29"/>
     <mergeCell ref="C194:C197"/>
-    <mergeCell ref="D146:D151"/>
-    <mergeCell ref="A159:A164"/>
+    <mergeCell ref="I163:I169"/>
+    <mergeCell ref="I97:I99"/>
     <mergeCell ref="I90:I91"/>
-    <mergeCell ref="I97:I99"/>
-    <mergeCell ref="C159:C164"/>
-    <mergeCell ref="C182:C189"/>
+    <mergeCell ref="I7:I9"/>
     <mergeCell ref="C78:C81"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="D169:D181"/>
-    <mergeCell ref="I134:I140"/>
+    <mergeCell ref="C233:C236"/>
     <mergeCell ref="A2:A15"/>
     <mergeCell ref="A30:A62"/>
     <mergeCell ref="C53:C58"/>
     <mergeCell ref="D125:D129"/>
     <mergeCell ref="D40:D52"/>
-    <mergeCell ref="C152:C158"/>
+    <mergeCell ref="B181:B187"/>
+    <mergeCell ref="B233:B236"/>
     <mergeCell ref="B100:B105"/>
-    <mergeCell ref="B190:B193"/>
-    <mergeCell ref="B165:B168"/>
-    <mergeCell ref="D190:D193"/>
+    <mergeCell ref="I170:I174"/>
     <mergeCell ref="I82:I84"/>
     <mergeCell ref="I2:I5"/>
     <mergeCell ref="C63:C66"/>
-    <mergeCell ref="A131:A133"/>
-    <mergeCell ref="B198:B200"/>
     <mergeCell ref="A113:A130"/>
-    <mergeCell ref="A146:A151"/>
+    <mergeCell ref="B194:B207"/>
     <mergeCell ref="D92:D96"/>
     <mergeCell ref="D113:D124"/>
-    <mergeCell ref="C146:C151"/>
     <mergeCell ref="C90:C91"/>
+    <mergeCell ref="A181:A187"/>
+    <mergeCell ref="C181:C187"/>
     <mergeCell ref="D194:D197"/>
-    <mergeCell ref="C169:C181"/>
     <mergeCell ref="D10:D14"/>
     <mergeCell ref="B106:B108"/>
-    <mergeCell ref="I146:I151"/>
     <mergeCell ref="B30:B62"/>
     <mergeCell ref="D72:D77"/>
-    <mergeCell ref="B134:B140"/>
+    <mergeCell ref="D152:D157"/>
+    <mergeCell ref="C103:C105"/>
+    <mergeCell ref="I229:I232"/>
+    <mergeCell ref="C208:C220"/>
     <mergeCell ref="A100:A105"/>
-    <mergeCell ref="I169:I181"/>
-    <mergeCell ref="C103:C105"/>
-    <mergeCell ref="A190:A193"/>
-    <mergeCell ref="C190:C193"/>
+    <mergeCell ref="A188:A193"/>
+    <mergeCell ref="C188:C193"/>
     <mergeCell ref="I125:I129"/>
+    <mergeCell ref="I40:I52"/>
+    <mergeCell ref="C100:C102"/>
     <mergeCell ref="A109:A112"/>
-    <mergeCell ref="C100:C102"/>
-    <mergeCell ref="I40:I52"/>
     <mergeCell ref="I78:I81"/>
-    <mergeCell ref="B152:B158"/>
+    <mergeCell ref="B170:B174"/>
+    <mergeCell ref="D145:D151"/>
+    <mergeCell ref="D170:D174"/>
     <mergeCell ref="C85:C89"/>
     <mergeCell ref="I103:I105"/>
     <mergeCell ref="C72:C77"/>
+    <mergeCell ref="C142:C144"/>
     <mergeCell ref="B82:B99"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6954,14 +8118,14 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>・「公開API」は routes/api.php に定義されている GET /api/user (auth:sanctum) のみを対象としています。認証不要で叩ける真の公開エンドポイントは現状実装されていないため、カテゴリの意図の再確認をおすすめします。</t>
+          <t>・「公開API」は、認証不要の書籍一覧・詳細取得API(GET /api/v1/books, /api/v1/books/{book})、Sanctumトークン認証が必要な書籍の登録・更新・削除API(POST/PUT/DELETE)、およびユーザー情報取得API(GET /api/user)を対象としています。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>・「Sanctum認証」はAPIトークンを発行する専用エンドポイントが実装されていないため、テスト内では $user-&gt;createToken() を直接呼び出してトークンを用意する想定にしています。</t>
+          <t>・「Sanctum認証」は、アクセストークン発行API(POST /api/v1/auth/token)と、発行したトークンによる認証(GET /api/user)を対象としています。トークンによる認証の確認では $user-&gt;createToken() で直接トークンを用意し、発行APIの確認ではAPIそのものを呼び出す想定です。</t>
         </is>
       </c>
     </row>
@@ -6982,7 +8146,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>・17-1-13「読書計画削除時に関連するリマインダー通知も同時に削除される」はレビュー指摘により追加した項目ですが、2026-09-18時点のコード(ReadingPlanController::destroy)では読書計画の削除時に関連通知を削除する処理が実装されていません。このテストを実装するには、先にアプリ側へ削除処理(例: モデルのdeletingイベントやコントローラでの明示的な削除)を追加する必要があります。</t>
+          <t>・17-1-13「読書計画削除時に関連するリマインダー通知も同時に削除される」はレビュー指摘により追加した項目です。ReadingPlanモデルのdeletingイベントで、削除される計画に紐づく通知(dataのplan_idが一致するReadingPlanReminder)を削除する実装を追加済みです。モデル経由の削除($readingPlan-&gt;delete())でのみ動作します。</t>
         </is>
       </c>
     </row>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I239"/>
+  <dimension ref="A1:I229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6590,8 +6590,8 @@
       <c r="I196" s="4" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="4" t="n"/>
-      <c r="B197" s="4" t="n"/>
+      <c r="A197" s="5" t="n"/>
+      <c r="B197" s="5" t="n"/>
       <c r="C197" s="5" t="n"/>
       <c r="D197" s="5" t="n"/>
       <c r="E197" s="6" t="inlineStr">
@@ -6618,42 +6618,49 @@
       <c r="I197" s="5" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="4" t="n"/>
-      <c r="B198" s="4" t="n"/>
-      <c r="C198" s="2" t="inlineStr">
-        <is>
-          <t>16-2</t>
-        </is>
-      </c>
-      <c r="D198" s="2" t="inlineStr">
-        <is>
-          <t>アクセストークン発行API(POST /api/v1/auth/token)</t>
-        </is>
-      </c>
-      <c r="E198" s="2" t="inlineStr">
-        <is>
-          <t>16-2-1</t>
-        </is>
-      </c>
-      <c r="F198" s="3" t="inlineStr">
-        <is>
-          <t>正しいメールアドレス・パスワードでトークンが発行される</t>
-        </is>
-      </c>
-      <c r="G198" s="3" t="inlineStr">
-        <is>
-          <t>1.ユーザーを用意する
-2.そのユーザーのメールアドレス・パスワードでPOST /api/v1/auth/tokenにアクセスする(Accept: application/json)</t>
-        </is>
-      </c>
-      <c r="H198" s="3" t="inlineStr">
-        <is>
-          <t>201が返り、token(文字列)とtoken_type(Bearer)を含むJSONが返る</t>
-        </is>
-      </c>
-      <c r="I198" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/SanctumAuth/TokenIssueTest.php</t>
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>読書計画</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>17-1</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>読書計画の作成・一覧・読了・削除</t>
+        </is>
+      </c>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
+          <t>17-1-1</t>
+        </is>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
+        </is>
+      </c>
+      <c r="H198" s="7" t="inlineStr">
+        <is>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I198" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
         </is>
       </c>
     </row>
@@ -6662,25 +6669,25 @@
       <c r="B199" s="4" t="n"/>
       <c r="C199" s="4" t="n"/>
       <c r="D199" s="4" t="n"/>
-      <c r="E199" s="2" t="inlineStr">
-        <is>
-          <t>16-2-2</t>
-        </is>
-      </c>
-      <c r="F199" s="3" t="inlineStr">
-        <is>
-          <t>発行されたトークンで、認証が必要なAPIにアクセスできる</t>
-        </is>
-      </c>
-      <c r="G199" s="3" t="inlineStr">
-        <is>
-          <t>1.POST /api/v1/auth/tokenでトークンを発行する
-2.そのトークンをBearerヘッダーに付与してGET /api/userにアクセスする</t>
-        </is>
-      </c>
-      <c r="H199" s="3" t="inlineStr">
-        <is>
-          <t>200が返り、トークンを発行したユーザーの情報が返る</t>
+      <c r="E199" s="6" t="inlineStr">
+        <is>
+          <t>17-1-2</t>
+        </is>
+      </c>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>1.自分と他人の読書計画をそれぞれ用意する
+2.読書計画一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H199" s="7" t="inlineStr">
+        <is>
+          <t>自分の計画のみが、target_dateの昇順で表示される</t>
         </is>
       </c>
       <c r="I199" s="4" t="n"/>
@@ -6690,25 +6697,25 @@
       <c r="B200" s="4" t="n"/>
       <c r="C200" s="4" t="n"/>
       <c r="D200" s="4" t="n"/>
-      <c r="E200" s="2" t="inlineStr">
-        <is>
-          <t>16-2-3</t>
-        </is>
-      </c>
-      <c r="F200" s="3" t="inlineStr">
-        <is>
-          <t>発行したトークンが保存され、device_nameを指定するとトークン名になる(省略時は「api-token」)</t>
-        </is>
-      </c>
-      <c r="G200" s="3" t="inlineStr">
-        <is>
-          <t>1.device_nameを指定して、または省略してPOST /api/v1/auth/tokenにアクセスする
-2.personal_access_tokensテーブルを確認する</t>
-        </is>
-      </c>
-      <c r="H200" s="3" t="inlineStr">
-        <is>
-          <t>対象ユーザーのトークンが保存され、nameが指定したdevice_name(省略時はapi-token)になっている。平文のトークンは保存されない</t>
+      <c r="E200" s="6" t="inlineStr">
+        <is>
+          <t>17-1-3</t>
+        </is>
+      </c>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>ステータスで絞り込んで表示できる</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t>1.進行中・完了・期限超過の計画をそれぞれ用意する
+2.statusパラメータを指定して一覧を開く</t>
+        </is>
+      </c>
+      <c r="H200" s="7" t="inlineStr">
+        <is>
+          <t>指定したステータスの計画のみ表示される</t>
         </is>
       </c>
       <c r="I200" s="4" t="n"/>
@@ -6718,25 +6725,25 @@
       <c r="B201" s="4" t="n"/>
       <c r="C201" s="4" t="n"/>
       <c r="D201" s="4" t="n"/>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t>16-2-4</t>
-        </is>
-      </c>
-      <c r="F201" s="3" t="inlineStr">
-        <is>
-          <t>同じユーザーが複数回発行でき、それぞれのトークンが有効</t>
-        </is>
-      </c>
-      <c r="G201" s="3" t="inlineStr">
-        <is>
-          <t>1.同じユーザーでPOST /api/v1/auth/tokenに2回アクセスする
-2.それぞれのトークンでGET /api/userにアクセスする</t>
-        </is>
-      </c>
-      <c r="H201" s="3" t="inlineStr">
-        <is>
-          <t>2つのトークンが発行され、どちらでも200が返る</t>
+      <c r="E201" s="6" t="inlineStr">
+        <is>
+          <t>17-1-4</t>
+        </is>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>1.ある書籍について進行中の計画を作成する
+2.計画作成ページを開く</t>
+        </is>
+      </c>
+      <c r="H201" s="7" t="inlineStr">
+        <is>
+          <t>書籍選択肢にその書籍が表示されない</t>
         </is>
       </c>
       <c r="I201" s="4" t="n"/>
@@ -6746,24 +6753,24 @@
       <c r="B202" s="4" t="n"/>
       <c r="C202" s="4" t="n"/>
       <c r="D202" s="4" t="n"/>
-      <c r="E202" s="2" t="inlineStr">
-        <is>
-          <t>16-2-5</t>
-        </is>
-      </c>
-      <c r="F202" s="3" t="inlineStr">
-        <is>
-          <t>パスワードが誤っている場合、422が返りトークンは発行されない</t>
-        </is>
-      </c>
-      <c r="G202" s="3" t="inlineStr">
-        <is>
-          <t>1.登録済みのメールアドレスと誤ったパスワードでPOST /api/v1/auth/tokenにアクセスする</t>
-        </is>
-      </c>
-      <c r="H202" s="3" t="inlineStr">
-        <is>
-          <t>422が返り、「会員情報が登録されていません」が返る。トークンは作成されない</t>
+      <c r="E202" s="6" t="inlineStr">
+        <is>
+          <t>17-1-5</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H202" s="7" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、計画は作成されない</t>
         </is>
       </c>
       <c r="I202" s="4" t="n"/>
@@ -6773,24 +6780,25 @@
       <c r="B203" s="4" t="n"/>
       <c r="C203" s="4" t="n"/>
       <c r="D203" s="4" t="n"/>
-      <c r="E203" s="2" t="inlineStr">
-        <is>
-          <t>16-2-6</t>
-        </is>
-      </c>
-      <c r="F203" s="3" t="inlineStr">
-        <is>
-          <t>登録されていないメールアドレスの場合、422が返る</t>
-        </is>
-      </c>
-      <c r="G203" s="3" t="inlineStr">
-        <is>
-          <t>1.未登録のメールアドレスでPOST /api/v1/auth/tokenにアクセスする</t>
-        </is>
-      </c>
-      <c r="H203" s="3" t="inlineStr">
-        <is>
-          <t>422が返り、「会員情報が登録されていません」が返る(パスワード誤りの場合と同じメッセージ)</t>
+      <c r="E203" s="6" t="inlineStr">
+        <is>
+          <t>17-1-6</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>1.ある書籍の計画を読了(完了)状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H203" s="7" t="inlineStr">
+        <is>
+          <t>新しい計画が作成される</t>
         </is>
       </c>
       <c r="I203" s="4" t="n"/>
@@ -6800,24 +6808,25 @@
       <c r="B204" s="4" t="n"/>
       <c r="C204" s="4" t="n"/>
       <c r="D204" s="4" t="n"/>
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t>16-2-7</t>
-        </is>
-      </c>
-      <c r="F204" s="3" t="inlineStr">
-        <is>
-          <t>メールアドレスが未入力の場合、422が返る</t>
-        </is>
-      </c>
-      <c r="G204" s="3" t="inlineStr">
-        <is>
-          <t>1.メールアドレスを指定せずPOST /api/v1/auth/tokenにアクセスする</t>
-        </is>
-      </c>
-      <c r="H204" s="3" t="inlineStr">
-        <is>
-          <t>422が返り、「メールアドレスを入力してください」が返る</t>
+      <c r="E204" s="6" t="inlineStr">
+        <is>
+          <t>17-1-7</t>
+        </is>
+      </c>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="inlineStr">
+        <is>
+          <t>1.計画作成ページを開く
+2.期日を入力せずに登録する</t>
+        </is>
+      </c>
+      <c r="H204" s="7" t="inlineStr">
+        <is>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I204" s="4" t="n"/>
@@ -6827,24 +6836,25 @@
       <c r="B205" s="4" t="n"/>
       <c r="C205" s="4" t="n"/>
       <c r="D205" s="4" t="n"/>
-      <c r="E205" s="2" t="inlineStr">
-        <is>
-          <t>16-2-8</t>
-        </is>
-      </c>
-      <c r="F205" s="3" t="inlineStr">
-        <is>
-          <t>メールアドレスがメール形式でない場合、422が返る</t>
-        </is>
-      </c>
-      <c r="G205" s="3" t="inlineStr">
-        <is>
-          <t>1.「abc」のようなメール形式でない値を指定してPOST /api/v1/auth/tokenにアクセスする</t>
-        </is>
-      </c>
-      <c r="H205" s="3" t="inlineStr">
-        <is>
-          <t>422が返り、「メールアドレスはメール形式で入力してください」が返る</t>
+      <c r="E205" s="6" t="inlineStr">
+        <is>
+          <t>17-1-8</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>1.計画作成ページを開く
+2.過去の日付を期日に指定して登録する</t>
+        </is>
+      </c>
+      <c r="H205" s="7" t="inlineStr">
+        <is>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I205" s="4" t="n"/>
@@ -6854,101 +6864,82 @@
       <c r="B206" s="4" t="n"/>
       <c r="C206" s="4" t="n"/>
       <c r="D206" s="4" t="n"/>
-      <c r="E206" s="2" t="inlineStr">
-        <is>
-          <t>16-2-9</t>
-        </is>
-      </c>
-      <c r="F206" s="3" t="inlineStr">
-        <is>
-          <t>パスワードが未入力の場合、422が返る</t>
-        </is>
-      </c>
-      <c r="G206" s="3" t="inlineStr">
-        <is>
-          <t>1.パスワードを指定せずPOST /api/v1/auth/tokenにアクセスする</t>
-        </is>
-      </c>
-      <c r="H206" s="3" t="inlineStr">
-        <is>
-          <t>422が返り、「パスワードを入力してください」が返る</t>
+      <c r="E206" s="6" t="inlineStr">
+        <is>
+          <t>17-1-9</t>
+        </is>
+      </c>
+      <c r="F206" s="7" t="inlineStr">
+        <is>
+          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="inlineStr">
+        <is>
+          <t>1.計画作成ページを開く
+2.書籍・期日を正しく入力して登録する</t>
+        </is>
+      </c>
+      <c r="H206" s="7" t="inlineStr">
+        <is>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
         </is>
       </c>
       <c r="I206" s="4" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="5" t="n"/>
-      <c r="B207" s="5" t="n"/>
-      <c r="C207" s="5" t="n"/>
-      <c r="D207" s="5" t="n"/>
-      <c r="E207" s="2" t="inlineStr">
-        <is>
-          <t>16-2-10</t>
-        </is>
-      </c>
-      <c r="F207" s="3" t="inlineStr">
-        <is>
-          <t>device_nameが256文字以上の場合、422が返る</t>
-        </is>
-      </c>
-      <c r="G207" s="3" t="inlineStr">
-        <is>
-          <t>1.256文字のdevice_nameを指定してPOST /api/v1/auth/tokenにアクセスする</t>
-        </is>
-      </c>
-      <c r="H207" s="3" t="inlineStr">
-        <is>
-          <t>422が返り、「トークン名は255文字以内で入力してください」が返る</t>
-        </is>
-      </c>
-      <c r="I207" s="5" t="n"/>
+      <c r="A207" s="4" t="n"/>
+      <c r="B207" s="4" t="n"/>
+      <c r="C207" s="4" t="n"/>
+      <c r="D207" s="4" t="n"/>
+      <c r="E207" s="6" t="inlineStr">
+        <is>
+          <t>17-1-10</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>1.進行中の計画に対して読了操作を行う</t>
+        </is>
+      </c>
+      <c r="H207" s="7" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B208" s="6" t="inlineStr">
-        <is>
-          <t>読書計画</t>
-        </is>
-      </c>
-      <c r="C208" s="6" t="inlineStr">
-        <is>
-          <t>17-1</t>
-        </is>
-      </c>
-      <c r="D208" s="6" t="inlineStr">
-        <is>
-          <t>読書計画の作成・一覧・読了・削除</t>
-        </is>
-      </c>
+      <c r="A208" s="4" t="n"/>
+      <c r="B208" s="4" t="n"/>
+      <c r="C208" s="4" t="n"/>
+      <c r="D208" s="4" t="n"/>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>17-1-1</t>
+          <t>17-1-11</t>
         </is>
       </c>
       <c r="F208" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
+          <t>他人が作成した読書計画は読了・削除できない</t>
         </is>
       </c>
       <c r="G208" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
+          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
         </is>
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I208" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
-        </is>
-      </c>
+          <t>いずれも403Forbiddenになる</t>
+        </is>
+      </c>
+      <c r="I208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="n"/>
@@ -6957,82 +6948,100 @@
       <c r="D209" s="4" t="n"/>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>17-1-2</t>
+          <t>17-1-12</t>
         </is>
       </c>
       <c r="F209" s="7" t="inlineStr">
         <is>
-          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
+          <t>自分が作成した読書計画は削除できる</t>
         </is>
       </c>
       <c r="G209" s="7" t="inlineStr">
         <is>
-          <t>1.自分と他人の読書計画をそれぞれ用意する
-2.読書計画一覧ページを開く</t>
+          <t>1.自分が作成した計画の削除ボタンを押す</t>
         </is>
       </c>
       <c r="H209" s="7" t="inlineStr">
         <is>
-          <t>自分の計画のみが、target_dateの昇順で表示される</t>
+          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
         </is>
       </c>
       <c r="I209" s="4" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="4" t="n"/>
-      <c r="B210" s="4" t="n"/>
-      <c r="C210" s="4" t="n"/>
-      <c r="D210" s="4" t="n"/>
-      <c r="E210" s="6" t="inlineStr">
-        <is>
-          <t>17-1-3</t>
-        </is>
-      </c>
-      <c r="F210" s="7" t="inlineStr">
-        <is>
-          <t>ステータスで絞り込んで表示できる</t>
-        </is>
-      </c>
-      <c r="G210" s="7" t="inlineStr">
-        <is>
-          <t>1.進行中・完了・期限超過の計画をそれぞれ用意する
-2.statusパラメータを指定して一覧を開く</t>
-        </is>
-      </c>
-      <c r="H210" s="7" t="inlineStr">
-        <is>
-          <t>指定したステータスの計画のみ表示される</t>
-        </is>
-      </c>
-      <c r="I210" s="4" t="n"/>
+      <c r="A210" s="5" t="n"/>
+      <c r="B210" s="5" t="n"/>
+      <c r="C210" s="5" t="n"/>
+      <c r="D210" s="5" t="n"/>
+      <c r="E210" s="8" t="inlineStr">
+        <is>
+          <t>17-1-13</t>
+        </is>
+      </c>
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
+        </is>
+      </c>
+      <c r="G210" s="9" t="inlineStr">
+        <is>
+          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
+2.その読書計画を削除する</t>
+        </is>
+      </c>
+      <c r="H210" s="9" t="inlineStr">
+        <is>
+          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
+        </is>
+      </c>
+      <c r="I210" s="5" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="4" t="n"/>
-      <c r="B211" s="4" t="n"/>
-      <c r="C211" s="4" t="n"/>
-      <c r="D211" s="4" t="n"/>
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>読書計画（期限変更）</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>18-1</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="inlineStr">
+        <is>
+          <t>読書計画の期日変更</t>
+        </is>
+      </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>17-1-4</t>
+          <t>18-1-1</t>
         </is>
       </c>
       <c r="F211" s="7" t="inlineStr">
         <is>
-          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
+          <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
         </is>
       </c>
       <c r="G211" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍について進行中の計画を作成する
-2.計画作成ページを開く</t>
+          <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H211" s="7" t="inlineStr">
         <is>
-          <t>書籍選択肢にその書籍が表示されない</t>
-        </is>
-      </c>
-      <c r="I211" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I211" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="n"/>
@@ -7041,22 +7050,22 @@
       <c r="D212" s="4" t="n"/>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>17-1-5</t>
+          <t>18-1-2</t>
         </is>
       </c>
       <c r="F212" s="7" t="inlineStr">
         <is>
-          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
+          <t>他人が作成した読書計画の期日は変更できない</t>
         </is>
       </c>
       <c r="G212" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
+          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H212" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、計画は作成されない</t>
+          <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
       <c r="I212" s="4" t="n"/>
@@ -7068,23 +7077,22 @@
       <c r="D213" s="4" t="n"/>
       <c r="E213" s="6" t="inlineStr">
         <is>
-          <t>17-1-6</t>
+          <t>18-1-3</t>
         </is>
       </c>
       <c r="F213" s="7" t="inlineStr">
         <is>
-          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
+          <t>編集画面を開くと現在の期日が初期表示される</t>
         </is>
       </c>
       <c r="G213" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を読了(完了)状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.自分が作成した計画の編集ページを開く</t>
         </is>
       </c>
       <c r="H213" s="7" t="inlineStr">
         <is>
-          <t>新しい計画が作成される</t>
+          <t>現在登録されている期日が入力欄に表示される</t>
         </is>
       </c>
       <c r="I213" s="4" t="n"/>
@@ -7096,7 +7104,7 @@
       <c r="D214" s="4" t="n"/>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>17-1-7</t>
+          <t>18-1-4</t>
         </is>
       </c>
       <c r="F214" s="7" t="inlineStr">
@@ -7106,8 +7114,8 @@
       </c>
       <c r="G214" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.期日を入力せずに登録する</t>
+          <t>1.編集ページを開く
+2.期日を空にして更新する</t>
         </is>
       </c>
       <c r="H214" s="7" t="inlineStr">
@@ -7124,7 +7132,7 @@
       <c r="D215" s="4" t="n"/>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>17-1-8</t>
+          <t>18-1-5</t>
         </is>
       </c>
       <c r="F215" s="7" t="inlineStr">
@@ -7134,8 +7142,8 @@
       </c>
       <c r="G215" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.過去の日付を期日に指定して登録する</t>
+          <t>1.編集ページを開く
+2.過去の日付に変更して更新する</t>
         </is>
       </c>
       <c r="H215" s="7" t="inlineStr">
@@ -7152,23 +7160,23 @@
       <c r="D216" s="4" t="n"/>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>17-1-9</t>
+          <t>18-1-6</t>
         </is>
       </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
-          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
+          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
         </is>
       </c>
       <c r="G216" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍・期日を正しく入力して登録する</t>
+          <t>1.編集ページを開く
+2.未来の日付に正しく変更して更新する</t>
         </is>
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
+          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
         </is>
       </c>
       <c r="I216" s="4" t="n"/>
@@ -7180,208 +7188,233 @@
       <c r="D217" s="4" t="n"/>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>17-1-10</t>
+          <t>18-1-7</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
+          <t>一覧・編集画面表示時に、期日を過ぎた「進行中」の計画は自動的に「期限超過」に更新される</t>
         </is>
       </c>
       <c r="G217" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画に対して読了操作を行う</t>
+          <t>1.期日が過去で「進行中」の計画を用意する
+2.読書計画一覧または編集ページを開く</t>
         </is>
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
+          <t>表示前に計画のステータスが「期限超過」に更新される</t>
         </is>
       </c>
       <c r="I217" s="4" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="4" t="n"/>
-      <c r="B218" s="4" t="n"/>
-      <c r="C218" s="4" t="n"/>
-      <c r="D218" s="4" t="n"/>
+      <c r="A218" s="5" t="n"/>
+      <c r="B218" s="5" t="n"/>
+      <c r="C218" s="5" t="n"/>
+      <c r="D218" s="5" t="n"/>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>17-1-11</t>
+          <t>18-1-8</t>
         </is>
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画は読了・削除できない</t>
+          <t>ステータスが「完了」の計画は期日を変更できない</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>いずれも403Forbiddenになる</t>
-        </is>
-      </c>
-      <c r="I218" s="4" t="n"/>
+          <t>403Forbiddenになり、期日は変更されない</t>
+        </is>
+      </c>
+      <c r="I218" s="5" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="4" t="n"/>
-      <c r="B219" s="4" t="n"/>
-      <c r="C219" s="4" t="n"/>
-      <c r="D219" s="4" t="n"/>
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t>リマインダーバッチ</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>19-1</t>
+        </is>
+      </c>
+      <c r="D219" s="6" t="inlineStr">
+        <is>
+          <t>reading-plans:remindコマンドによるリマインダー通知</t>
+        </is>
+      </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>17-1-12</t>
+          <t>19-1-1</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>自分が作成した読書計画は削除できる</t>
+          <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
         </is>
       </c>
       <c r="G219" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の削除ボタンを押す</t>
+          <t>1.target_dateが3日後・ステータス進行中の計画を用意する
+2.Notification::fake()を設定し reading-plans:remind を実行する</t>
         </is>
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
-        </is>
-      </c>
-      <c r="I219" s="4" t="n"/>
+          <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I219" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="5" t="n"/>
-      <c r="B220" s="5" t="n"/>
-      <c r="C220" s="5" t="n"/>
-      <c r="D220" s="5" t="n"/>
-      <c r="E220" s="8" t="inlineStr">
-        <is>
-          <t>17-1-13</t>
-        </is>
-      </c>
-      <c r="F220" s="9" t="inlineStr">
-        <is>
-          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
-        </is>
-      </c>
-      <c r="G220" s="9" t="inlineStr">
-        <is>
-          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
-2.その読書計画を削除する</t>
-        </is>
-      </c>
-      <c r="H220" s="9" t="inlineStr">
-        <is>
-          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
-        </is>
-      </c>
-      <c r="I220" s="5" t="n"/>
+      <c r="A220" s="4" t="n"/>
+      <c r="B220" s="4" t="n"/>
+      <c r="C220" s="4" t="n"/>
+      <c r="D220" s="4" t="n"/>
+      <c r="E220" s="6" t="inlineStr">
+        <is>
+          <t>19-1-2</t>
+        </is>
+      </c>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが本日・ステータス進行中の計画を用意する
+2.reading-plans:remindを実行する</t>
+        </is>
+      </c>
+      <c r="H220" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I220" s="4" t="n"/>
     </row>
     <row r="221">
-      <c r="A221" s="6" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B221" s="6" t="inlineStr">
-        <is>
-          <t>読書計画（期限変更）</t>
-        </is>
-      </c>
-      <c r="C221" s="6" t="inlineStr">
-        <is>
-          <t>18-1</t>
-        </is>
-      </c>
-      <c r="D221" s="6" t="inlineStr">
-        <is>
-          <t>読書計画の期日変更</t>
-        </is>
-      </c>
+      <c r="A221" s="4" t="n"/>
+      <c r="B221" s="4" t="n"/>
+      <c r="C221" s="4" t="n"/>
+      <c r="D221" s="4" t="n"/>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>18-1-1</t>
+          <t>19-1-3</t>
         </is>
       </c>
       <c r="F221" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
+          <t>期限超過から3日後の計画に再エンゲージメント通知が送信される</t>
         </is>
       </c>
       <c r="G221" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
+          <t>1.target_dateが3日前・ステータス期限超過の計画を用意する
+2.reading-plans:remindを実行する</t>
         </is>
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I221" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
-        </is>
-      </c>
+          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I221" s="4" t="n"/>
     </row>
     <row r="222">
-      <c r="A222" s="4" t="n"/>
-      <c r="B222" s="4" t="n"/>
-      <c r="C222" s="4" t="n"/>
-      <c r="D222" s="4" t="n"/>
+      <c r="A222" s="5" t="n"/>
+      <c r="B222" s="5" t="n"/>
+      <c r="C222" s="5" t="n"/>
+      <c r="D222" s="5" t="n"/>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>18-1-2</t>
+          <t>19-1-4</t>
         </is>
       </c>
       <c r="F222" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画の期日は変更できない</t>
+          <t>いずれの条件にも該当しない計画には通知が送信されない</t>
         </is>
       </c>
       <c r="G222" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
+          <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
+2.reading-plans:remindを実行する</t>
         </is>
       </c>
       <c r="H222" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
-        </is>
-      </c>
-      <c r="I222" s="4" t="n"/>
+          <t>その計画のユーザーに通知が送信されない</t>
+        </is>
+      </c>
+      <c r="I222" s="5" t="n"/>
     </row>
     <row r="223">
-      <c r="A223" s="4" t="n"/>
-      <c r="B223" s="4" t="n"/>
-      <c r="C223" s="4" t="n"/>
-      <c r="D223" s="4" t="n"/>
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B223" s="6" t="inlineStr">
+        <is>
+          <t>自動失効バッチ</t>
+        </is>
+      </c>
+      <c r="C223" s="6" t="inlineStr">
+        <is>
+          <t>20-1</t>
+        </is>
+      </c>
+      <c r="D223" s="6" t="inlineStr">
+        <is>
+          <t>reading-plans:expireコマンドによる自動失効処理</t>
+        </is>
+      </c>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>18-1-3</t>
+          <t>20-1-1</t>
         </is>
       </c>
       <c r="F223" s="7" t="inlineStr">
         <is>
-          <t>編集画面を開くと現在の期日が初期表示される</t>
+          <t>期日を過ぎた「進行中」の計画が「期限超過」に更新される</t>
         </is>
       </c>
       <c r="G223" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の編集ページを開く</t>
+          <t>1.target_dateが過去・ステータス進行中の計画を用意する
+2.reading-plans:expireを実行する</t>
         </is>
       </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
-          <t>現在登録されている期日が入力欄に表示される</t>
-        </is>
-      </c>
-      <c r="I223" s="4" t="n"/>
+          <t>対象の計画のstatusが「期限超過」に更新される</t>
+        </is>
+      </c>
+      <c r="I223" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="4" t="n"/>
@@ -7390,23 +7423,23 @@
       <c r="D224" s="4" t="n"/>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>18-1-4</t>
+          <t>20-1-2</t>
         </is>
       </c>
       <c r="F224" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>期日が今日以降の「進行中」の計画は失効しない</t>
         </is>
       </c>
       <c r="G224" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.期日を空にして更新する</t>
+          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
+2.reading-plans:expireを実行する</t>
         </is>
       </c>
       <c r="H224" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>その計画のstatusは「進行中」のまま変化しない</t>
         </is>
       </c>
       <c r="I224" s="4" t="n"/>
@@ -7418,570 +7451,243 @@
       <c r="D225" s="4" t="n"/>
       <c r="E225" s="6" t="inlineStr">
         <is>
-          <t>18-1-5</t>
+          <t>20-1-3</t>
         </is>
       </c>
       <c r="F225" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>既に「完了」または「期限超過」の計画は対象外(重複更新されない)</t>
         </is>
       </c>
       <c r="G225" s="7" t="inlineStr">
-        <is>
-          <t>1.編集ページを開く
-2.過去の日付に変更して更新する</t>
-        </is>
-      </c>
-      <c r="H225" s="7" t="inlineStr">
-        <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I225" s="4" t="n"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="4" t="n"/>
-      <c r="B226" s="4" t="n"/>
-      <c r="C226" s="4" t="n"/>
-      <c r="D226" s="4" t="n"/>
-      <c r="E226" s="6" t="inlineStr">
-        <is>
-          <t>18-1-6</t>
-        </is>
-      </c>
-      <c r="F226" s="7" t="inlineStr">
-        <is>
-          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
-        </is>
-      </c>
-      <c r="G226" s="7" t="inlineStr">
-        <is>
-          <t>1.編集ページを開く
-2.未来の日付に正しく変更して更新する</t>
-        </is>
-      </c>
-      <c r="H226" s="7" t="inlineStr">
-        <is>
-          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
-        </is>
-      </c>
-      <c r="I226" s="4" t="n"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="4" t="n"/>
-      <c r="B227" s="4" t="n"/>
-      <c r="C227" s="4" t="n"/>
-      <c r="D227" s="4" t="n"/>
-      <c r="E227" s="6" t="inlineStr">
-        <is>
-          <t>18-1-7</t>
-        </is>
-      </c>
-      <c r="F227" s="7" t="inlineStr">
-        <is>
-          <t>一覧・編集画面表示時に、期日を過ぎた「進行中」の計画は自動的に「期限超過」に更新される</t>
-        </is>
-      </c>
-      <c r="G227" s="7" t="inlineStr">
-        <is>
-          <t>1.期日が過去で「進行中」の計画を用意する
-2.読書計画一覧または編集ページを開く</t>
-        </is>
-      </c>
-      <c r="H227" s="7" t="inlineStr">
-        <is>
-          <t>表示前に計画のステータスが「期限超過」に更新される</t>
-        </is>
-      </c>
-      <c r="I227" s="4" t="n"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="5" t="n"/>
-      <c r="B228" s="5" t="n"/>
-      <c r="C228" s="5" t="n"/>
-      <c r="D228" s="5" t="n"/>
-      <c r="E228" s="6" t="inlineStr">
-        <is>
-          <t>18-1-8</t>
-        </is>
-      </c>
-      <c r="F228" s="7" t="inlineStr">
-        <is>
-          <t>ステータスが「完了」の計画は期日を変更できない</t>
-        </is>
-      </c>
-      <c r="G228" s="7" t="inlineStr">
-        <is>
-          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H228" s="7" t="inlineStr">
-        <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
-        </is>
-      </c>
-      <c r="I228" s="5" t="n"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B229" s="6" t="inlineStr">
-        <is>
-          <t>リマインダーバッチ</t>
-        </is>
-      </c>
-      <c r="C229" s="6" t="inlineStr">
-        <is>
-          <t>19-1</t>
-        </is>
-      </c>
-      <c r="D229" s="6" t="inlineStr">
-        <is>
-          <t>reading-plans:remindコマンドによるリマインダー通知</t>
-        </is>
-      </c>
-      <c r="E229" s="6" t="inlineStr">
-        <is>
-          <t>19-1-1</t>
-        </is>
-      </c>
-      <c r="F229" s="7" t="inlineStr">
-        <is>
-          <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
-        </is>
-      </c>
-      <c r="G229" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが3日後・ステータス進行中の計画を用意する
-2.Notification::fake()を設定し reading-plans:remind を実行する</t>
-        </is>
-      </c>
-      <c r="H229" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I229" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="4" t="n"/>
-      <c r="B230" s="4" t="n"/>
-      <c r="C230" s="4" t="n"/>
-      <c r="D230" s="4" t="n"/>
-      <c r="E230" s="6" t="inlineStr">
-        <is>
-          <t>19-1-2</t>
-        </is>
-      </c>
-      <c r="F230" s="7" t="inlineStr">
-        <is>
-          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
-        </is>
-      </c>
-      <c r="G230" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが本日・ステータス進行中の計画を用意する
-2.reading-plans:remindを実行する</t>
-        </is>
-      </c>
-      <c r="H230" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I230" s="4" t="n"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="4" t="n"/>
-      <c r="B231" s="4" t="n"/>
-      <c r="C231" s="4" t="n"/>
-      <c r="D231" s="4" t="n"/>
-      <c r="E231" s="6" t="inlineStr">
-        <is>
-          <t>19-1-3</t>
-        </is>
-      </c>
-      <c r="F231" s="7" t="inlineStr">
-        <is>
-          <t>期限超過から3日後の計画に再エンゲージメント通知が送信される</t>
-        </is>
-      </c>
-      <c r="G231" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが3日前・ステータス期限超過の計画を用意する
-2.reading-plans:remindを実行する</t>
-        </is>
-      </c>
-      <c r="H231" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I231" s="4" t="n"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="5" t="n"/>
-      <c r="B232" s="5" t="n"/>
-      <c r="C232" s="5" t="n"/>
-      <c r="D232" s="5" t="n"/>
-      <c r="E232" s="6" t="inlineStr">
-        <is>
-          <t>19-1-4</t>
-        </is>
-      </c>
-      <c r="F232" s="7" t="inlineStr">
-        <is>
-          <t>いずれの条件にも該当しない計画には通知が送信されない</t>
-        </is>
-      </c>
-      <c r="G232" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
-2.reading-plans:remindを実行する</t>
-        </is>
-      </c>
-      <c r="H232" s="7" t="inlineStr">
-        <is>
-          <t>その計画のユーザーに通知が送信されない</t>
-        </is>
-      </c>
-      <c r="I232" s="5" t="n"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B233" s="6" t="inlineStr">
-        <is>
-          <t>自動失効バッチ</t>
-        </is>
-      </c>
-      <c r="C233" s="6" t="inlineStr">
-        <is>
-          <t>20-1</t>
-        </is>
-      </c>
-      <c r="D233" s="6" t="inlineStr">
-        <is>
-          <t>reading-plans:expireコマンドによる自動失効処理</t>
-        </is>
-      </c>
-      <c r="E233" s="6" t="inlineStr">
-        <is>
-          <t>20-1-1</t>
-        </is>
-      </c>
-      <c r="F233" s="7" t="inlineStr">
-        <is>
-          <t>期日を過ぎた「進行中」の計画が「期限超過」に更新される</t>
-        </is>
-      </c>
-      <c r="G233" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが過去・ステータス進行中の計画を用意する
-2.reading-plans:expireを実行する</t>
-        </is>
-      </c>
-      <c r="H233" s="7" t="inlineStr">
-        <is>
-          <t>対象の計画のstatusが「期限超過」に更新される</t>
-        </is>
-      </c>
-      <c r="I233" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" s="4" t="n"/>
-      <c r="B234" s="4" t="n"/>
-      <c r="C234" s="4" t="n"/>
-      <c r="D234" s="4" t="n"/>
-      <c r="E234" s="6" t="inlineStr">
-        <is>
-          <t>20-1-2</t>
-        </is>
-      </c>
-      <c r="F234" s="7" t="inlineStr">
-        <is>
-          <t>期日が今日以降の「進行中」の計画は失効しない</t>
-        </is>
-      </c>
-      <c r="G234" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
-2.reading-plans:expireを実行する</t>
-        </is>
-      </c>
-      <c r="H234" s="7" t="inlineStr">
-        <is>
-          <t>その計画のstatusは「進行中」のまま変化しない</t>
-        </is>
-      </c>
-      <c r="I234" s="4" t="n"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="4" t="n"/>
-      <c r="B235" s="4" t="n"/>
-      <c r="C235" s="4" t="n"/>
-      <c r="D235" s="4" t="n"/>
-      <c r="E235" s="6" t="inlineStr">
-        <is>
-          <t>20-1-3</t>
-        </is>
-      </c>
-      <c r="F235" s="7" t="inlineStr">
-        <is>
-          <t>既に「完了」または「期限超過」の計画は対象外(重複更新されない)</t>
-        </is>
-      </c>
-      <c r="G235" s="7" t="inlineStr">
         <is>
           <t>1.完了済み・期限超過済みの計画をそれぞれ用意する
 2.reading-plans:expireを実行する</t>
         </is>
       </c>
-      <c r="H235" s="7" t="inlineStr">
+      <c r="H225" s="7" t="inlineStr">
         <is>
           <t>いずれの計画もstatusが変化しない</t>
         </is>
       </c>
-      <c r="I235" s="4" t="n"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="5" t="n"/>
-      <c r="B236" s="5" t="n"/>
-      <c r="C236" s="5" t="n"/>
-      <c r="D236" s="5" t="n"/>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="I225" s="4" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="n"/>
+      <c r="B226" s="5" t="n"/>
+      <c r="C226" s="5" t="n"/>
+      <c r="D226" s="5" t="n"/>
+      <c r="E226" s="6" t="inlineStr">
         <is>
           <t>20-1-4</t>
         </is>
       </c>
-      <c r="F236" s="7" t="inlineStr">
+      <c r="F226" s="7" t="inlineStr">
         <is>
           <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
         </is>
       </c>
-      <c r="G236" s="7" t="inlineStr">
+      <c r="G226" s="7" t="inlineStr">
         <is>
           <t>1.失効対象の計画を用意し reading-plans:expire を実行する
 2.DBを直接確認する</t>
         </is>
       </c>
-      <c r="H236" s="7" t="inlineStr">
+      <c r="H226" s="7" t="inlineStr">
         <is>
           <t>assertDatabaseHasでstatus=expiredが確認できる</t>
         </is>
       </c>
-      <c r="I236" s="5" t="n"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="8" t="inlineStr">
+      <c r="I226" s="5" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="8" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B237" s="8" t="inlineStr">
+      <c r="B227" s="8" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="C237" s="8" t="inlineStr">
+      <c r="C227" s="8" t="inlineStr">
         <is>
           <t>21-1</t>
         </is>
       </c>
-      <c r="D237" s="8" t="inlineStr">
+      <c r="D227" s="8" t="inlineStr">
         <is>
           <t>通知の既読化</t>
         </is>
       </c>
-      <c r="E237" s="8" t="inlineStr">
+      <c r="E227" s="8" t="inlineStr">
         <is>
           <t>21-1-1</t>
         </is>
       </c>
-      <c r="F237" s="9" t="inlineStr">
+      <c r="F227" s="9" t="inlineStr">
         <is>
           <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
         </is>
       </c>
-      <c r="G237" s="9" t="inlineStr">
+      <c r="G227" s="9" t="inlineStr">
         <is>
           <t>1.未ログイン状態でPATCH /notifications/{id} に直接リクエストを送信する</t>
         </is>
       </c>
-      <c r="H237" s="9" t="inlineStr">
+      <c r="H227" s="9" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
         </is>
       </c>
-      <c r="I237" s="9" t="inlineStr">
+      <c r="I227" s="9" t="inlineStr">
         <is>
           <t>tests/Feature/Notification/NotificationTest.php</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="4" t="n"/>
-      <c r="B238" s="4" t="n"/>
-      <c r="C238" s="4" t="n"/>
-      <c r="D238" s="4" t="n"/>
-      <c r="E238" s="8" t="inlineStr">
+    <row r="228">
+      <c r="A228" s="4" t="n"/>
+      <c r="B228" s="4" t="n"/>
+      <c r="C228" s="4" t="n"/>
+      <c r="D228" s="4" t="n"/>
+      <c r="E228" s="8" t="inlineStr">
         <is>
           <t>21-1-2</t>
         </is>
       </c>
-      <c r="F238" s="9" t="inlineStr">
+      <c r="F228" s="9" t="inlineStr">
         <is>
           <t>自分の通知を既読にできる</t>
         </is>
       </c>
-      <c r="G238" s="9" t="inlineStr">
+      <c r="G228" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知を用意する
 2.その通知に対してPATCH /notifications/{id} を送信する</t>
         </is>
       </c>
-      <c r="H238" s="9" t="inlineStr">
+      <c r="H228" s="9" t="inlineStr">
         <is>
           <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）</t>
         </is>
       </c>
-      <c r="I238" s="4" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="5" t="n"/>
-      <c r="B239" s="5" t="n"/>
-      <c r="C239" s="5" t="n"/>
-      <c r="D239" s="5" t="n"/>
-      <c r="E239" s="8" t="inlineStr">
+      <c r="I228" s="4" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="5" t="n"/>
+      <c r="B229" s="5" t="n"/>
+      <c r="C229" s="5" t="n"/>
+      <c r="D229" s="5" t="n"/>
+      <c r="E229" s="8" t="inlineStr">
         <is>
           <t>21-1-3</t>
         </is>
       </c>
-      <c r="F239" s="9" t="inlineStr">
+      <c r="F229" s="9" t="inlineStr">
         <is>
           <t>他ユーザーの通知は既読にできない</t>
         </is>
       </c>
-      <c r="G239" s="9" t="inlineStr">
+      <c r="G229" s="9" t="inlineStr">
         <is>
           <t>1.他ユーザー宛ての通知を用意する
 2.そのIDに対してPATCH /notifications/{id} を送信する</t>
         </is>
       </c>
-      <c r="H239" s="9" t="inlineStr">
+      <c r="H229" s="9" t="inlineStr">
         <is>
           <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
         </is>
       </c>
-      <c r="I239" s="5" t="n"/>
+      <c r="I229" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="168">
+  <mergeCells count="165">
     <mergeCell ref="I30:I33"/>
     <mergeCell ref="I92:I96"/>
     <mergeCell ref="C131:C133"/>
     <mergeCell ref="D34:D39"/>
     <mergeCell ref="D59:D62"/>
+    <mergeCell ref="D181:D187"/>
     <mergeCell ref="C30:C33"/>
-    <mergeCell ref="D181:D187"/>
-    <mergeCell ref="B221:B228"/>
+    <mergeCell ref="D67:D71"/>
     <mergeCell ref="I194:I197"/>
-    <mergeCell ref="D67:D71"/>
+    <mergeCell ref="B131:B162"/>
+    <mergeCell ref="C7:C9"/>
     <mergeCell ref="I10:I14"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="B131:B162"/>
     <mergeCell ref="C175:C180"/>
     <mergeCell ref="C125:C129"/>
     <mergeCell ref="I72:I77"/>
-    <mergeCell ref="B229:B232"/>
-    <mergeCell ref="A233:A236"/>
+    <mergeCell ref="C170:C174"/>
+    <mergeCell ref="B16:B29"/>
     <mergeCell ref="A170:A174"/>
-    <mergeCell ref="B16:B29"/>
-    <mergeCell ref="C170:C174"/>
-    <mergeCell ref="D229:D232"/>
-    <mergeCell ref="I198:I207"/>
+    <mergeCell ref="C198:C210"/>
     <mergeCell ref="D85:D89"/>
     <mergeCell ref="I175:I180"/>
     <mergeCell ref="B163:B169"/>
     <mergeCell ref="D78:D81"/>
-    <mergeCell ref="I237:I239"/>
     <mergeCell ref="I134:I141"/>
-    <mergeCell ref="A237:A239"/>
+    <mergeCell ref="I145:I151"/>
     <mergeCell ref="C2:C5"/>
-    <mergeCell ref="I145:I151"/>
     <mergeCell ref="C134:C141"/>
     <mergeCell ref="B2:B15"/>
-    <mergeCell ref="D221:D228"/>
     <mergeCell ref="D158:D162"/>
     <mergeCell ref="I131:I133"/>
     <mergeCell ref="I100:I102"/>
+    <mergeCell ref="I85:I89"/>
     <mergeCell ref="I109:I112"/>
-    <mergeCell ref="I85:I89"/>
     <mergeCell ref="C10:C14"/>
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="I34:I39"/>
-    <mergeCell ref="I208:I220"/>
+    <mergeCell ref="D63:D66"/>
     <mergeCell ref="I59:I62"/>
-    <mergeCell ref="D63:D66"/>
+    <mergeCell ref="B194:B197"/>
     <mergeCell ref="I181:I187"/>
-    <mergeCell ref="A229:A232"/>
-    <mergeCell ref="C229:C232"/>
+    <mergeCell ref="A211:A218"/>
+    <mergeCell ref="I67:I71"/>
     <mergeCell ref="B63:B81"/>
-    <mergeCell ref="A194:A207"/>
-    <mergeCell ref="I67:I71"/>
     <mergeCell ref="C34:C39"/>
+    <mergeCell ref="D227:D229"/>
+    <mergeCell ref="B223:B226"/>
     <mergeCell ref="I142:I144"/>
-    <mergeCell ref="D233:D236"/>
-    <mergeCell ref="A208:A220"/>
+    <mergeCell ref="D198:D210"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="A106:A108"/>
     <mergeCell ref="C106:C108"/>
     <mergeCell ref="I188:I193"/>
-    <mergeCell ref="B237:B239"/>
     <mergeCell ref="C158:C162"/>
     <mergeCell ref="C152:C157"/>
     <mergeCell ref="C40:C52"/>
     <mergeCell ref="C109:C112"/>
+    <mergeCell ref="A219:A222"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="C145:C151"/>
+    <mergeCell ref="B113:B130"/>
+    <mergeCell ref="C92:C96"/>
+    <mergeCell ref="D100:D102"/>
     <mergeCell ref="I158:I162"/>
-    <mergeCell ref="C92:C96"/>
-    <mergeCell ref="B113:B130"/>
-    <mergeCell ref="D100:D102"/>
+    <mergeCell ref="C219:C222"/>
     <mergeCell ref="C113:C124"/>
-    <mergeCell ref="C145:C151"/>
     <mergeCell ref="I152:I157"/>
     <mergeCell ref="D53:D58"/>
+    <mergeCell ref="A227:A229"/>
     <mergeCell ref="D30:D33"/>
     <mergeCell ref="A82:A99"/>
+    <mergeCell ref="I63:I66"/>
     <mergeCell ref="I106:I108"/>
-    <mergeCell ref="I63:I66"/>
-    <mergeCell ref="C198:C207"/>
     <mergeCell ref="D16:D29"/>
     <mergeCell ref="A63:A81"/>
-    <mergeCell ref="B208:B220"/>
     <mergeCell ref="D103:D105"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="D97:D99"/>
     <mergeCell ref="D163:D169"/>
-    <mergeCell ref="D208:D220"/>
-    <mergeCell ref="D97:D99"/>
+    <mergeCell ref="I198:I210"/>
     <mergeCell ref="B188:B193"/>
-    <mergeCell ref="D90:D91"/>
     <mergeCell ref="D106:D108"/>
+    <mergeCell ref="A131:A162"/>
     <mergeCell ref="D188:D193"/>
-    <mergeCell ref="A131:A162"/>
-    <mergeCell ref="C237:C239"/>
     <mergeCell ref="B109:B112"/>
     <mergeCell ref="D109:D112"/>
     <mergeCell ref="C82:C84"/>
@@ -7989,75 +7695,80 @@
     <mergeCell ref="C67:C71"/>
     <mergeCell ref="A163:A169"/>
     <mergeCell ref="C163:C169"/>
-    <mergeCell ref="I233:I236"/>
     <mergeCell ref="D82:D84"/>
+    <mergeCell ref="I53:I58"/>
     <mergeCell ref="D131:D133"/>
-    <mergeCell ref="I53:I58"/>
     <mergeCell ref="C59:C62"/>
-    <mergeCell ref="A221:A228"/>
-    <mergeCell ref="C221:C228"/>
-    <mergeCell ref="D198:D207"/>
-    <mergeCell ref="D237:D239"/>
+    <mergeCell ref="A223:A226"/>
     <mergeCell ref="B175:B180"/>
+    <mergeCell ref="D175:D180"/>
     <mergeCell ref="C97:C99"/>
-    <mergeCell ref="D175:D180"/>
     <mergeCell ref="I113:I124"/>
+    <mergeCell ref="I219:I222"/>
+    <mergeCell ref="A175:A180"/>
+    <mergeCell ref="I16:I29"/>
     <mergeCell ref="D134:D141"/>
-    <mergeCell ref="I16:I29"/>
-    <mergeCell ref="I221:I228"/>
-    <mergeCell ref="A175:A180"/>
+    <mergeCell ref="I227:I229"/>
     <mergeCell ref="A16:A29"/>
     <mergeCell ref="C16:C29"/>
+    <mergeCell ref="B198:B210"/>
     <mergeCell ref="C194:C197"/>
     <mergeCell ref="I163:I169"/>
+    <mergeCell ref="B211:B218"/>
     <mergeCell ref="I97:I99"/>
     <mergeCell ref="I90:I91"/>
+    <mergeCell ref="C227:C229"/>
     <mergeCell ref="I7:I9"/>
+    <mergeCell ref="D223:D226"/>
     <mergeCell ref="C78:C81"/>
-    <mergeCell ref="C233:C236"/>
+    <mergeCell ref="D211:D218"/>
     <mergeCell ref="A2:A15"/>
     <mergeCell ref="A30:A62"/>
+    <mergeCell ref="B181:B187"/>
+    <mergeCell ref="D125:D129"/>
     <mergeCell ref="C53:C58"/>
-    <mergeCell ref="D125:D129"/>
     <mergeCell ref="D40:D52"/>
-    <mergeCell ref="B181:B187"/>
-    <mergeCell ref="B233:B236"/>
     <mergeCell ref="B100:B105"/>
     <mergeCell ref="I170:I174"/>
     <mergeCell ref="I82:I84"/>
     <mergeCell ref="I2:I5"/>
     <mergeCell ref="C63:C66"/>
+    <mergeCell ref="B219:B222"/>
+    <mergeCell ref="A198:A210"/>
+    <mergeCell ref="D92:D96"/>
     <mergeCell ref="A113:A130"/>
-    <mergeCell ref="B194:B207"/>
-    <mergeCell ref="D92:D96"/>
+    <mergeCell ref="D219:D222"/>
     <mergeCell ref="D113:D124"/>
+    <mergeCell ref="I223:I226"/>
     <mergeCell ref="C90:C91"/>
+    <mergeCell ref="B227:B229"/>
+    <mergeCell ref="C223:C226"/>
     <mergeCell ref="A181:A187"/>
+    <mergeCell ref="D194:D197"/>
     <mergeCell ref="C181:C187"/>
-    <mergeCell ref="D194:D197"/>
     <mergeCell ref="D10:D14"/>
+    <mergeCell ref="C211:C218"/>
     <mergeCell ref="B106:B108"/>
     <mergeCell ref="B30:B62"/>
     <mergeCell ref="D72:D77"/>
     <mergeCell ref="D152:D157"/>
+    <mergeCell ref="A100:A105"/>
     <mergeCell ref="C103:C105"/>
-    <mergeCell ref="I229:I232"/>
-    <mergeCell ref="C208:C220"/>
-    <mergeCell ref="A100:A105"/>
+    <mergeCell ref="I211:I218"/>
     <mergeCell ref="A188:A193"/>
     <mergeCell ref="C188:C193"/>
     <mergeCell ref="I125:I129"/>
+    <mergeCell ref="A109:A112"/>
+    <mergeCell ref="C100:C102"/>
     <mergeCell ref="I40:I52"/>
-    <mergeCell ref="C100:C102"/>
-    <mergeCell ref="A109:A112"/>
+    <mergeCell ref="D145:D151"/>
+    <mergeCell ref="B170:B174"/>
     <mergeCell ref="I78:I81"/>
-    <mergeCell ref="B170:B174"/>
-    <mergeCell ref="D145:D151"/>
     <mergeCell ref="D170:D174"/>
     <mergeCell ref="C85:C89"/>
     <mergeCell ref="I103:I105"/>
+    <mergeCell ref="C142:C144"/>
     <mergeCell ref="C72:C77"/>
-    <mergeCell ref="C142:C144"/>
     <mergeCell ref="B82:B99"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8125,7 +7836,7 @@
     <row r="8" ht="40" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>・「Sanctum認証」は、アクセストークン発行API(POST /api/v1/auth/token)と、発行したトークンによる認証(GET /api/user)を対象としています。トークンによる認証の確認では $user-&gt;createToken() で直接トークンを用意し、発行APIの確認ではAPIそのものを呼び出す想定です。</t>
+          <t>・「Sanctum認証」はAPIトークンを発行する専用エンドポイントを設けないため、テスト内では $user-&gt;createToken() を直接呼び出してトークンを用意する想定にしています。</t>
         </is>
       </c>
     </row>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I229"/>
+  <dimension ref="A1:I232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5512,8 +5512,8 @@
       <c r="I161" s="4" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="5" t="n"/>
-      <c r="B162" s="5" t="n"/>
+      <c r="A162" s="4" t="n"/>
+      <c r="B162" s="4" t="n"/>
       <c r="C162" s="5" t="n"/>
       <c r="D162" s="5" t="n"/>
       <c r="E162" s="2" t="inlineStr">
@@ -5539,50 +5539,41 @@
       <c r="I162" s="5" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>検索・フィルタ</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>11-1</t>
-        </is>
-      </c>
-      <c r="D163" s="6" t="inlineStr">
-        <is>
-          <t>書籍のキーワード検索・ジャンル絞り込み</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
-        <is>
-          <t>11-1-1</t>
-        </is>
-      </c>
-      <c r="F163" s="7" t="inlineStr">
-        <is>
-          <t>タイトルにキーワードを含む書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="G163" s="7" t="inlineStr">
-        <is>
-          <t>1.タイトルにキーワードを含む書籍を用意する
-2.書籍一覧ページでkeywordにそのキーワードを指定して検索する</t>
-        </is>
-      </c>
-      <c r="H163" s="7" t="inlineStr">
-        <is>
-          <t>該当する書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="I163" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Search/SearchTest.php</t>
+      <c r="A163" s="4" t="n"/>
+      <c r="B163" s="4" t="n"/>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>10-7</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>APIのレスポンス形式(Acceptヘッダーなし)</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>10-7-1</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="inlineStr">
+        <is>
+          <t>Acceptヘッダーを付けなくても、未認証の書き込みAPIは401のJSONが返る</t>
+        </is>
+      </c>
+      <c r="G163" s="3" t="inlineStr">
+        <is>
+          <t>1.Acceptヘッダーも認証情報も付与せずPOST /api/v1/booksにアクセスする</t>
+        </is>
+      </c>
+      <c r="H163" s="3" t="inlineStr">
+        <is>
+          <t>401が返り、JSON(「Unauthenticated.」)になる。ログイン画面へのリダイレクト(302)にならない</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/ApiJsonResponseTest.php</t>
         </is>
       </c>
     </row>
@@ -5591,83 +5582,102 @@
       <c r="B164" s="4" t="n"/>
       <c r="C164" s="4" t="n"/>
       <c r="D164" s="4" t="n"/>
-      <c r="E164" s="6" t="inlineStr">
-        <is>
-          <t>11-1-2</t>
-        </is>
-      </c>
-      <c r="F164" s="7" t="inlineStr">
-        <is>
-          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="G164" s="7" t="inlineStr">
-        <is>
-          <t>1.著者名にキーワードを含む書籍を用意する
-2.同キーワードで検索する</t>
-        </is>
-      </c>
-      <c r="H164" s="7" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>10-7-2</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="inlineStr">
+        <is>
+          <t>Acceptヘッダーを付けなくても、バリデーションエラーは422のJSONが返る</t>
+        </is>
+      </c>
+      <c r="G164" s="3" t="inlineStr">
+        <is>
+          <t>1.トークンを付与し、Acceptヘッダーは付与せず、title・author・genresを指定せずにPOST /api/v1/booksにアクセスする</t>
+        </is>
+      </c>
+      <c r="H164" s="3" t="inlineStr">
+        <is>
+          <t>422が返り、JSONでエラーメッセージが返る。元の画面へのリダイレクト(302)にならない</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="5" t="n"/>
+      <c r="B165" s="5" t="n"/>
+      <c r="C165" s="5" t="n"/>
+      <c r="D165" s="5" t="n"/>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>10-7-3</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="inlineStr">
+        <is>
+          <t>Acceptヘッダーを付けなくても、存在しないIDは404のJSON(日本語メッセージ)が返る</t>
+        </is>
+      </c>
+      <c r="G165" s="3" t="inlineStr">
+        <is>
+          <t>1.Acceptヘッダーを付与せず、存在しない書籍IDでGET /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H165" s="3" t="inlineStr">
+        <is>
+          <t>404が返り、「指定された書籍が見つかりません」を含むJSONが返る(HTMLの404画面にならない)</t>
+        </is>
+      </c>
+      <c r="I165" s="5" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>検索・フィルタ</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>11-1</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>書籍のキーワード検索・ジャンル絞り込み</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>11-1-1</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>タイトルにキーワードを含む書籍が検索結果に表示される</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>1.タイトルにキーワードを含む書籍を用意する
+2.書籍一覧ページでkeywordにそのキーワードを指定して検索する</t>
+        </is>
+      </c>
+      <c r="H166" s="7" t="inlineStr">
         <is>
           <t>該当する書籍が検索結果に表示される</t>
         </is>
       </c>
-      <c r="I164" s="4" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="4" t="n"/>
-      <c r="B165" s="4" t="n"/>
-      <c r="C165" s="4" t="n"/>
-      <c r="D165" s="4" t="n"/>
-      <c r="E165" s="6" t="inlineStr">
-        <is>
-          <t>11-1-3</t>
-        </is>
-      </c>
-      <c r="F165" s="7" t="inlineStr">
-        <is>
-          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
-        </is>
-      </c>
-      <c r="G165" s="7" t="inlineStr">
-        <is>
-          <t>1.キーワードに一致しない書籍を用意する
-2.検索する</t>
-        </is>
-      </c>
-      <c r="H165" s="7" t="inlineStr">
-        <is>
-          <t>その書籍は検索結果に表示されない</t>
-        </is>
-      </c>
-      <c r="I165" s="4" t="n"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="4" t="n"/>
-      <c r="B166" s="4" t="n"/>
-      <c r="C166" s="4" t="n"/>
-      <c r="D166" s="4" t="n"/>
-      <c r="E166" s="6" t="inlineStr">
-        <is>
-          <t>11-1-4</t>
-        </is>
-      </c>
-      <c r="F166" s="7" t="inlineStr">
-        <is>
-          <t>キーワード未入力の場合は全件が表示される</t>
-        </is>
-      </c>
-      <c r="G166" s="7" t="inlineStr">
-        <is>
-          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H166" s="7" t="inlineStr">
-        <is>
-          <t>登録されている全ての書籍が表示される</t>
-        </is>
-      </c>
-      <c r="I166" s="4" t="n"/>
+      <c r="I166" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Search/SearchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n"/>
@@ -5676,23 +5686,23 @@
       <c r="D167" s="4" t="n"/>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>11-1-5</t>
+          <t>11-1-2</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
+          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>1.複数ジャンルの書籍を用意する
-2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
+          <t>1.著者名にキーワードを含む書籍を用意する
+2.同キーワードで検索する</t>
         </is>
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
-          <t>指定したジャンルに紐づく書籍のみ表示される</t>
+          <t>該当する書籍が検索結果に表示される</t>
         </is>
       </c>
       <c r="I167" s="4" t="n"/>
@@ -5704,100 +5714,81 @@
       <c r="D168" s="4" t="n"/>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>11-1-6</t>
+          <t>11-1-3</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>キーワード検索とジャンル絞り込みを組み合わせて使用できる</t>
+          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>1.keywordとgenreの両方を指定して一覧を開く</t>
+          <t>1.キーワードに一致しない書籍を用意する
+2.検索する</t>
         </is>
       </c>
       <c r="H168" s="7" t="inlineStr">
         <is>
-          <t>キーワードとジャンルの両方の条件に一致する書籍のみ表示される</t>
+          <t>その書籍は検索結果に表示されない</t>
         </is>
       </c>
       <c r="I168" s="4" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="n"/>
-      <c r="B169" s="5" t="n"/>
-      <c r="C169" s="5" t="n"/>
-      <c r="D169" s="5" t="n"/>
+      <c r="A169" s="4" t="n"/>
+      <c r="B169" s="4" t="n"/>
+      <c r="C169" s="4" t="n"/>
+      <c r="D169" s="4" t="n"/>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>11-1-7</t>
+          <t>11-1-4</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>検索結果が0件の場合の表示を確認する</t>
+          <t>キーワード未入力の場合は全件が表示される</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>1.どの書籍にも一致しないキーワードで検索する</t>
+          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
         </is>
       </c>
       <c r="H169" s="7" t="inlineStr">
         <is>
-          <t>「書籍が登録されていません。」など0件である旨が表示される</t>
-        </is>
-      </c>
-      <c r="I169" s="5" t="n"/>
+          <t>登録されている全ての書籍が表示される</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B170" s="6" t="inlineStr">
-        <is>
-          <t>ソート</t>
-        </is>
-      </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>12-1</t>
-        </is>
-      </c>
-      <c r="D170" s="6" t="inlineStr">
-        <is>
-          <t>書籍一覧の並び替え</t>
-        </is>
-      </c>
+      <c r="A170" s="4" t="n"/>
+      <c r="B170" s="4" t="n"/>
+      <c r="C170" s="4" t="n"/>
+      <c r="D170" s="4" t="n"/>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>12-1-1</t>
+          <t>11-1-5</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>並び替え未指定時は新着順(登録が新しい順)で表示される</t>
+          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>1.複数の書籍を異なる日時で登録する
-2.sortを指定せずに書籍一覧を開く</t>
+          <t>1.複数ジャンルの書籍を用意する
+2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
         </is>
       </c>
       <c r="H170" s="7" t="inlineStr">
         <is>
-          <t>登録日時が新しい順に表示される</t>
-        </is>
-      </c>
-      <c r="I170" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Sort/SortTest.php</t>
-        </is>
-      </c>
+          <t>指定したジャンルに紐づく書籍のみ表示される</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
@@ -5806,157 +5797,156 @@
       <c r="D171" s="4" t="n"/>
       <c r="E171" s="6" t="inlineStr">
         <is>
+          <t>11-1-6</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>キーワード検索とジャンル絞り込みを組み合わせて使用できる</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>1.keywordとgenreの両方を指定して一覧を開く</t>
+        </is>
+      </c>
+      <c r="H171" s="7" t="inlineStr">
+        <is>
+          <t>キーワードとジャンルの両方の条件に一致する書籍のみ表示される</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="n"/>
+      <c r="B172" s="5" t="n"/>
+      <c r="C172" s="5" t="n"/>
+      <c r="D172" s="5" t="n"/>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>11-1-7</t>
+        </is>
+      </c>
+      <c r="F172" s="7" t="inlineStr">
+        <is>
+          <t>検索結果が0件の場合の表示を確認する</t>
+        </is>
+      </c>
+      <c r="G172" s="7" t="inlineStr">
+        <is>
+          <t>1.どの書籍にも一致しないキーワードで検索する</t>
+        </is>
+      </c>
+      <c r="H172" s="7" t="inlineStr">
+        <is>
+          <t>「書籍が登録されていません。」など0件である旨が表示される</t>
+        </is>
+      </c>
+      <c r="I172" s="5" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t>ソート</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>書籍一覧の並び替え</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>12-1-1</t>
+        </is>
+      </c>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>並び替え未指定時は新着順(登録が新しい順)で表示される</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>1.複数の書籍を異なる日時で登録する
+2.sortを指定せずに書籍一覧を開く</t>
+        </is>
+      </c>
+      <c r="H173" s="7" t="inlineStr">
+        <is>
+          <t>登録日時が新しい順に表示される</t>
+        </is>
+      </c>
+      <c r="I173" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Sort/SortTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="n"/>
+      <c r="B174" s="4" t="n"/>
+      <c r="C174" s="4" t="n"/>
+      <c r="D174" s="4" t="n"/>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
           <t>12-1-2</t>
         </is>
       </c>
-      <c r="F171" s="7" t="inlineStr">
+      <c r="F174" s="7" t="inlineStr">
         <is>
           <t>sort=oldestを指定すると登録が古い順に表示される</t>
         </is>
       </c>
-      <c r="G171" s="7" t="inlineStr">
+      <c r="G174" s="7" t="inlineStr">
         <is>
           <t>1.複数の書籍を異なる日時で登録する
 2.sort=oldestを指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H171" s="7" t="inlineStr">
+      <c r="H174" s="7" t="inlineStr">
         <is>
           <t>登録日時が古い順に表示される</t>
         </is>
       </c>
-      <c r="I171" s="4" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="4" t="n"/>
-      <c r="B172" s="4" t="n"/>
-      <c r="C172" s="4" t="n"/>
-      <c r="D172" s="4" t="n"/>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="I174" s="4" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="n"/>
+      <c r="B175" s="4" t="n"/>
+      <c r="C175" s="4" t="n"/>
+      <c r="D175" s="4" t="n"/>
+      <c r="E175" s="6" t="inlineStr">
         <is>
           <t>12-1-3</t>
         </is>
       </c>
-      <c r="F172" s="7" t="inlineStr">
+      <c r="F175" s="7" t="inlineStr">
         <is>
           <t>sort=titleを指定するとタイトルの昇順で表示される</t>
         </is>
       </c>
-      <c r="G172" s="7" t="inlineStr">
+      <c r="G175" s="7" t="inlineStr">
         <is>
           <t>1.複数の書籍を用意する
 2.sort=titleを指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H172" s="7" t="inlineStr">
+      <c r="H175" s="7" t="inlineStr">
         <is>
           <t>タイトルの昇順で表示される</t>
         </is>
       </c>
-      <c r="I172" s="4" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="4" t="n"/>
-      <c r="B173" s="4" t="n"/>
-      <c r="C173" s="4" t="n"/>
-      <c r="D173" s="4" t="n"/>
-      <c r="E173" s="6" t="inlineStr">
-        <is>
-          <t>12-1-4</t>
-        </is>
-      </c>
-      <c r="F173" s="7" t="inlineStr">
-        <is>
-          <t>sort=ratingを指定すると平均評価が高い順に表示される</t>
-        </is>
-      </c>
-      <c r="G173" s="7" t="inlineStr">
-        <is>
-          <t>1.平均評価が異なる複数の書籍を用意する
-2.sort=ratingを指定して書籍一覧を開く</t>
-        </is>
-      </c>
-      <c r="H173" s="7" t="inlineStr">
-        <is>
-          <t>平均評価が高い順に表示される</t>
-        </is>
-      </c>
-      <c r="I173" s="4" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="5" t="n"/>
-      <c r="B174" s="5" t="n"/>
-      <c r="C174" s="5" t="n"/>
-      <c r="D174" s="5" t="n"/>
-      <c r="E174" s="6" t="inlineStr">
-        <is>
-          <t>12-1-5</t>
-        </is>
-      </c>
-      <c r="F174" s="7" t="inlineStr">
-        <is>
-          <t>sort=rating指定時、平均評価が同じ書籍は新着順で表示される</t>
-        </is>
-      </c>
-      <c r="G174" s="7" t="inlineStr">
-        <is>
-          <t>1.平均評価が同じ複数の書籍を、異なる登録日時で用意する
-2.sort=ratingを指定して書籍一覧を開く</t>
-        </is>
-      </c>
-      <c r="H174" s="7" t="inlineStr">
-        <is>
-          <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
-        </is>
-      </c>
-      <c r="I174" s="5" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B175" s="6" t="inlineStr">
-        <is>
-          <t>書籍CRUD（認可の詳細テスト）</t>
-        </is>
-      </c>
-      <c r="C175" s="6" t="inlineStr">
-        <is>
-          <t>13-1</t>
-        </is>
-      </c>
-      <c r="D175" s="6" t="inlineStr">
-        <is>
-          <t>BookPolicyの認可ロジック</t>
-        </is>
-      </c>
-      <c r="E175" s="6" t="inlineStr">
-        <is>
-          <t>13-1-1</t>
-        </is>
-      </c>
-      <c r="F175" s="7" t="inlineStr">
-        <is>
-          <t>ログインユーザーは誰でも書籍を作成できる</t>
-        </is>
-      </c>
-      <c r="G175" s="7" t="inlineStr">
-        <is>
-          <t>1.任意のログインユーザーで BookPolicy::create() を確認する</t>
-        </is>
-      </c>
-      <c r="H175" s="7" t="inlineStr">
-        <is>
-          <t>trueが返り、作成が許可される</t>
-        </is>
-      </c>
-      <c r="I175" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/BookAuthorization/BookAuthorizationTest.php</t>
-        </is>
-      </c>
+      <c r="I175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n"/>
@@ -5965,79 +5955,101 @@
       <c r="D176" s="4" t="n"/>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>13-1-2</t>
+          <t>12-1-4</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者本人は更新が許可される</t>
+          <t>sort=ratingを指定すると平均評価が高い順に表示される</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
+          <t>1.平均評価が異なる複数の書籍を用意する
+2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
-          <t>trueが返る</t>
+          <t>平均評価が高い順に表示される</t>
         </is>
       </c>
       <c r="I176" s="4" t="n"/>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="n"/>
-      <c r="B177" s="4" t="n"/>
-      <c r="C177" s="4" t="n"/>
-      <c r="D177" s="4" t="n"/>
+      <c r="A177" s="5" t="n"/>
+      <c r="B177" s="5" t="n"/>
+      <c r="C177" s="5" t="n"/>
+      <c r="D177" s="5" t="n"/>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>13-1-3</t>
+          <t>12-1-5</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者以外は更新が許可されない</t>
+          <t>sort=rating指定時、平均評価が同じ書籍は新着順で表示される</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
+          <t>1.平均評価が同じ複数の書籍を、異なる登録日時で用意する
+2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H177" s="7" t="inlineStr">
         <is>
-          <t>falseが返る</t>
-        </is>
-      </c>
-      <c r="I177" s="4" t="n"/>
+          <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
+        </is>
+      </c>
+      <c r="I177" s="5" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="4" t="n"/>
-      <c r="B178" s="4" t="n"/>
-      <c r="C178" s="4" t="n"/>
-      <c r="D178" s="4" t="n"/>
+      <c r="A178" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B178" s="6" t="inlineStr">
+        <is>
+          <t>書籍CRUD（認可の詳細テスト）</t>
+        </is>
+      </c>
+      <c r="C178" s="6" t="inlineStr">
+        <is>
+          <t>13-1</t>
+        </is>
+      </c>
+      <c r="D178" s="6" t="inlineStr">
+        <is>
+          <t>BookPolicyの認可ロジック</t>
+        </is>
+      </c>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>13-1-4</t>
+          <t>13-1-1</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者本人は削除が許可される</t>
+          <t>ログインユーザーは誰でも書籍を作成できる</t>
         </is>
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
+          <t>1.任意のログインユーザーで BookPolicy::create() を確認する</t>
         </is>
       </c>
       <c r="H178" s="7" t="inlineStr">
         <is>
-          <t>trueが返る</t>
-        </is>
-      </c>
-      <c r="I178" s="4" t="n"/>
+          <t>trueが返り、作成が許可される</t>
+        </is>
+      </c>
+      <c r="I178" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/BookAuthorization/BookAuthorizationTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n"/>
@@ -6046,99 +6058,79 @@
       <c r="D179" s="4" t="n"/>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>13-1-5</t>
+          <t>13-1-2</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者以外は削除が許可されない</t>
+          <t>書籍の登録者本人は更新が許可される</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
+          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H179" s="7" t="inlineStr">
         <is>
+          <t>trueが返る</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="n"/>
+      <c r="B180" s="4" t="n"/>
+      <c r="C180" s="4" t="n"/>
+      <c r="D180" s="4" t="n"/>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>13-1-3</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>書籍の登録者以外は更新が許可されない</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
+        </is>
+      </c>
+      <c r="H180" s="7" t="inlineStr">
+        <is>
           <t>falseが返る</t>
         </is>
       </c>
-      <c r="I179" s="4" t="n"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="5" t="n"/>
-      <c r="B180" s="5" t="n"/>
-      <c r="C180" s="5" t="n"/>
-      <c r="D180" s="5" t="n"/>
-      <c r="E180" s="6" t="inlineStr">
-        <is>
-          <t>13-1-6</t>
-        </is>
-      </c>
-      <c r="F180" s="7" t="inlineStr">
-        <is>
-          <t>フォームを介さない直接のPUT/DELETEリクエストでも他人の書籍は操作できない</t>
-        </is>
-      </c>
-      <c r="G180" s="7" t="inlineStr">
-        <is>
-          <t>1.他人が登録した書籍に対して、直接PUT・DELETEリクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H180" s="7" t="inlineStr">
-        <is>
-          <t>いずれも403Forbiddenになり、データは変更されない</t>
-        </is>
-      </c>
-      <c r="I180" s="5" t="n"/>
+      <c r="I180" s="4" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B181" s="6" t="inlineStr">
-        <is>
-          <t>ISBN検索</t>
-        </is>
-      </c>
-      <c r="C181" s="6" t="inlineStr">
-        <is>
-          <t>14-1</t>
-        </is>
-      </c>
-      <c r="D181" s="6" t="inlineStr">
-        <is>
-          <t>ISBNからの書籍情報取得(外部API連携)</t>
-        </is>
-      </c>
+      <c r="A181" s="4" t="n"/>
+      <c r="B181" s="4" t="n"/>
+      <c r="C181" s="4" t="n"/>
+      <c r="D181" s="4" t="n"/>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>14-1-1</t>
+          <t>13-1-4</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、ISBN検索エンドポイントにアクセスできない</t>
+          <t>書籍の登録者本人は削除が許可される</t>
         </is>
       </c>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態でGET /books/isbn/{isbn} にアクセスする</t>
+          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
         </is>
       </c>
       <c r="H181" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I181" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Isbn/IsbnSearchTest.php</t>
-        </is>
-      </c>
+          <t>trueが返る</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="n"/>
@@ -6147,79 +6139,99 @@
       <c r="D182" s="4" t="n"/>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>14-1-2</t>
+          <t>13-1-5</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>ISBNが未入力(空文字)の場合、バリデーションエラーが返る</t>
+          <t>書籍の登録者以外は削除が許可されない</t>
         </is>
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>1.ログイン状態でISBN部分を空にしてリクエストする</t>
+          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
         </is>
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「ISBNを入力してください」が返る</t>
+          <t>falseが返る</t>
         </is>
       </c>
       <c r="I182" s="4" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="4" t="n"/>
-      <c r="B183" s="4" t="n"/>
-      <c r="C183" s="4" t="n"/>
-      <c r="D183" s="4" t="n"/>
+      <c r="A183" s="5" t="n"/>
+      <c r="B183" s="5" t="n"/>
+      <c r="C183" s="5" t="n"/>
+      <c r="D183" s="5" t="n"/>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>14-1-3</t>
+          <t>13-1-6</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
+          <t>フォームを介さない直接のPUT/DELETEリクエストでも他人の書籍は操作できない</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>1.13桁でないISBNでリクエストする</t>
+          <t>1.他人が登録した書籍に対して、直接PUT・DELETEリクエストを送信する</t>
         </is>
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
-        </is>
-      </c>
-      <c r="I183" s="4" t="n"/>
+          <t>いずれも403Forbiddenになり、データは変更されない</t>
+        </is>
+      </c>
+      <c r="I183" s="5" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="4" t="n"/>
-      <c r="B184" s="4" t="n"/>
-      <c r="C184" s="4" t="n"/>
-      <c r="D184" s="4" t="n"/>
+      <c r="A184" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B184" s="6" t="inlineStr">
+        <is>
+          <t>ISBN検索</t>
+        </is>
+      </c>
+      <c r="C184" s="6" t="inlineStr">
+        <is>
+          <t>14-1</t>
+        </is>
+      </c>
+      <c r="D184" s="6" t="inlineStr">
+        <is>
+          <t>ISBNからの書籍情報取得(外部API連携)</t>
+        </is>
+      </c>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>14-1-4</t>
+          <t>14-1-1</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
+          <t>未ログインの場合、ISBN検索エンドポイントにアクセスできない</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
-          <t>1.登録済みのISBNでリクエストする</t>
+          <t>1.未ログイン状態でGET /books/isbn/{isbn} にアクセスする</t>
         </is>
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
-        </is>
-      </c>
-      <c r="I184" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I184" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Isbn/IsbnSearchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n"/>
@@ -6228,23 +6240,22 @@
       <c r="D185" s="4" t="n"/>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>14-1-5</t>
+          <t>14-1-2</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
+          <t>ISBNが未入力(空文字)の場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
-2.未登録ISBNでリクエストする</t>
+          <t>1.ログイン状態でISBN部分を空にしてリクエストする</t>
         </is>
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
+          <t>422が返り、「ISBNを入力してください」が返る</t>
         </is>
       </c>
       <c r="I185" s="4" t="n"/>
@@ -6256,101 +6267,80 @@
       <c r="D186" s="4" t="n"/>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>14-1-6</t>
+          <t>14-1-3</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
+          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でitemsが空のレスポンスをモックする
+          <t>1.13桁でないISBNでリクエストする</t>
+        </is>
+      </c>
+      <c r="H186" s="7" t="inlineStr">
+        <is>
+          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
+        </is>
+      </c>
+      <c r="I186" s="4" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n"/>
+      <c r="B187" s="4" t="n"/>
+      <c r="C187" s="4" t="n"/>
+      <c r="D187" s="4" t="n"/>
+      <c r="E187" s="6" t="inlineStr">
+        <is>
+          <t>14-1-4</t>
+        </is>
+      </c>
+      <c r="F187" s="7" t="inlineStr">
+        <is>
+          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>1.登録済みのISBNでリクエストする</t>
+        </is>
+      </c>
+      <c r="H187" s="7" t="inlineStr">
+        <is>
+          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
+        </is>
+      </c>
+      <c r="I187" s="4" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n"/>
+      <c r="B188" s="4" t="n"/>
+      <c r="C188" s="4" t="n"/>
+      <c r="D188" s="4" t="n"/>
+      <c r="E188" s="6" t="inlineStr">
+        <is>
+          <t>14-1-5</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H186" s="7" t="inlineStr">
-        <is>
-          <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
-        </is>
-      </c>
-      <c r="I186" s="4" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="5" t="n"/>
-      <c r="B187" s="5" t="n"/>
-      <c r="C187" s="5" t="n"/>
-      <c r="D187" s="5" t="n"/>
-      <c r="E187" s="6" t="inlineStr">
-        <is>
-          <t>14-1-7</t>
-        </is>
-      </c>
-      <c r="F187" s="7" t="inlineStr">
-        <is>
-          <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
-        </is>
-      </c>
-      <c r="G187" s="7" t="inlineStr">
-        <is>
-          <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
-2.未登録ISBNでリクエストする</t>
-        </is>
-      </c>
-      <c r="H187" s="7" t="inlineStr">
-        <is>
-          <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
-        </is>
-      </c>
-      <c r="I187" s="5" t="n"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B188" s="6" t="inlineStr">
-        <is>
-          <t>マイ読書レポート</t>
-        </is>
-      </c>
-      <c r="C188" s="6" t="inlineStr">
-        <is>
-          <t>15-1</t>
-        </is>
-      </c>
-      <c r="D188" s="6" t="inlineStr">
-        <is>
-          <t>読書統計の表示</t>
-        </is>
-      </c>
-      <c r="E188" s="6" t="inlineStr">
-        <is>
-          <t>15-1-1</t>
-        </is>
-      </c>
-      <c r="F188" s="7" t="inlineStr">
-        <is>
-          <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
-        </is>
-      </c>
-      <c r="G188" s="7" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態で/reportsを開く</t>
-        </is>
-      </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I188" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Report/ReportTest.php</t>
-        </is>
-      </c>
+          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
+        </is>
+      </c>
+      <c r="I188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n"/>
@@ -6359,79 +6349,101 @@
       <c r="D189" s="4" t="n"/>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>15-1-2</t>
+          <t>14-1-6</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
+          <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
+          <t>1.Http::fake()でitemsが空のレスポンスをモックする
+2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
+          <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
         </is>
       </c>
       <c r="I189" s="4" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="4" t="n"/>
-      <c r="B190" s="4" t="n"/>
-      <c r="C190" s="4" t="n"/>
-      <c r="D190" s="4" t="n"/>
+      <c r="A190" s="5" t="n"/>
+      <c r="B190" s="5" t="n"/>
+      <c r="C190" s="5" t="n"/>
+      <c r="D190" s="5" t="n"/>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>15-1-3</t>
+          <t>14-1-7</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>評価分布(★1〜★5)が正しく表示される</t>
+          <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
+          <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
+2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
-          <t>各評価の件数が実データと一致して表示される</t>
-        </is>
-      </c>
-      <c r="I190" s="4" t="n"/>
+          <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
+        </is>
+      </c>
+      <c r="I190" s="5" t="n"/>
     </row>
     <row r="191">
-      <c r="A191" s="4" t="n"/>
-      <c r="B191" s="4" t="n"/>
-      <c r="C191" s="4" t="n"/>
-      <c r="D191" s="4" t="n"/>
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B191" s="6" t="inlineStr">
+        <is>
+          <t>マイ読書レポート</t>
+        </is>
+      </c>
+      <c r="C191" s="6" t="inlineStr">
+        <is>
+          <t>15-1</t>
+        </is>
+      </c>
+      <c r="D191" s="6" t="inlineStr">
+        <is>
+          <t>読書統計の表示</t>
+        </is>
+      </c>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>15-1-4</t>
+          <t>15-1-1</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
+          <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
+          <t>1.未ログイン状態で/reportsを開く</t>
         </is>
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
-          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
-        </is>
-      </c>
-      <c r="I191" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I191" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Report/ReportTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="n"/>
@@ -6440,100 +6452,79 @@
       <c r="D192" s="4" t="n"/>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>15-1-5</t>
+          <t>15-1-2</t>
         </is>
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
-          <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
+          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
         </is>
       </c>
       <c r="G192" s="7" t="inlineStr">
         <is>
-          <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
+          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H192" s="7" t="inlineStr">
         <is>
-          <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
+          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
         </is>
       </c>
       <c r="I192" s="4" t="n"/>
     </row>
     <row r="193">
-      <c r="A193" s="5" t="n"/>
-      <c r="B193" s="5" t="n"/>
-      <c r="C193" s="5" t="n"/>
-      <c r="D193" s="5" t="n"/>
+      <c r="A193" s="4" t="n"/>
+      <c r="B193" s="4" t="n"/>
+      <c r="C193" s="4" t="n"/>
+      <c r="D193" s="4" t="n"/>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>15-1-6</t>
+          <t>15-1-3</t>
         </is>
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>レビューを1件も投稿していない場合の表示を確認する</t>
+          <t>評価分布(★1〜★5)が正しく表示される</t>
         </is>
       </c>
       <c r="G193" s="7" t="inlineStr">
         <is>
-          <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
+          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H193" s="7" t="inlineStr">
         <is>
-          <t>総レビュー数・読了冊数が0、平均評価が0として表示され、TOP5一覧は空になる</t>
-        </is>
-      </c>
-      <c r="I193" s="5" t="n"/>
+          <t>各評価の件数が実データと一致して表示される</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" s="6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B194" s="6" t="inlineStr">
-        <is>
-          <t>Sanctum認証</t>
-        </is>
-      </c>
-      <c r="C194" s="6" t="inlineStr">
-        <is>
-          <t>16-1</t>
-        </is>
-      </c>
-      <c r="D194" s="6" t="inlineStr">
-        <is>
-          <t>APIトークン認証</t>
-        </is>
-      </c>
+      <c r="A194" s="4" t="n"/>
+      <c r="B194" s="4" t="n"/>
+      <c r="C194" s="4" t="n"/>
+      <c r="D194" s="4" t="n"/>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>16-1-1</t>
+          <t>15-1-4</t>
         </is>
       </c>
       <c r="F194" s="7" t="inlineStr">
         <is>
-          <t>有効なpersonal access tokenを付与すると/api/userにアクセスできる</t>
+          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
         </is>
       </c>
       <c r="G194" s="7" t="inlineStr">
         <is>
-          <t>1.$user-&gt;createToken()でトークンを発行する
-2.Authorization: Bearer {token}を付与してGET /api/userにアクセスする</t>
+          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
-          <t>200が返り、対象ユーザーの情報が返る</t>
-        </is>
-      </c>
-      <c r="I194" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
-        </is>
-      </c>
+          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
+        </is>
+      </c>
+      <c r="I194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n"/>
@@ -6542,127 +6533,127 @@
       <c r="D195" s="4" t="n"/>
       <c r="E195" s="6" t="inlineStr">
         <is>
+          <t>15-1-5</t>
+        </is>
+      </c>
+      <c r="F195" s="7" t="inlineStr">
+        <is>
+          <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="inlineStr">
+        <is>
+          <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
+        </is>
+      </c>
+      <c r="H195" s="7" t="inlineStr">
+        <is>
+          <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
+        </is>
+      </c>
+      <c r="I195" s="4" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="n"/>
+      <c r="B196" s="5" t="n"/>
+      <c r="C196" s="5" t="n"/>
+      <c r="D196" s="5" t="n"/>
+      <c r="E196" s="6" t="inlineStr">
+        <is>
+          <t>15-1-6</t>
+        </is>
+      </c>
+      <c r="F196" s="7" t="inlineStr">
+        <is>
+          <t>レビューを1件も投稿していない場合の表示を確認する</t>
+        </is>
+      </c>
+      <c r="G196" s="7" t="inlineStr">
+        <is>
+          <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
+        </is>
+      </c>
+      <c r="H196" s="7" t="inlineStr">
+        <is>
+          <t>総レビュー数・読了冊数が0、平均評価が0として表示され、TOP5一覧は空になる</t>
+        </is>
+      </c>
+      <c r="I196" s="5" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>Sanctum認証</t>
+        </is>
+      </c>
+      <c r="C197" s="6" t="inlineStr">
+        <is>
+          <t>16-1</t>
+        </is>
+      </c>
+      <c r="D197" s="6" t="inlineStr">
+        <is>
+          <t>APIトークン認証</t>
+        </is>
+      </c>
+      <c r="E197" s="6" t="inlineStr">
+        <is>
+          <t>16-1-1</t>
+        </is>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>有効なpersonal access tokenを付与すると/api/userにアクセスできる</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>1.$user-&gt;createToken()でトークンを発行する
+2.Authorization: Bearer {token}を付与してGET /api/userにアクセスする</t>
+        </is>
+      </c>
+      <c r="H197" s="7" t="inlineStr">
+        <is>
+          <t>200が返り、対象ユーザーの情報が返る</t>
+        </is>
+      </c>
+      <c r="I197" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="n"/>
+      <c r="B198" s="4" t="n"/>
+      <c r="C198" s="4" t="n"/>
+      <c r="D198" s="4" t="n"/>
+      <c r="E198" s="6" t="inlineStr">
+        <is>
           <t>16-1-2</t>
         </is>
       </c>
-      <c r="F195" s="7" t="inlineStr">
+      <c r="F198" s="7" t="inlineStr">
         <is>
           <t>トークンなしでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G195" s="7" t="inlineStr">
+      <c r="G198" s="7" t="inlineStr">
         <is>
           <t>1.Authorizationヘッダーを付与せずにGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H195" s="7" t="inlineStr">
+      <c r="H198" s="7" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返る</t>
         </is>
       </c>
-      <c r="I195" s="4" t="n"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="4" t="n"/>
-      <c r="B196" s="4" t="n"/>
-      <c r="C196" s="4" t="n"/>
-      <c r="D196" s="4" t="n"/>
-      <c r="E196" s="6" t="inlineStr">
-        <is>
-          <t>16-1-3</t>
-        </is>
-      </c>
-      <c r="F196" s="7" t="inlineStr">
-        <is>
-          <t>不正な(存在しない)トークンでアクセスすると401が返る</t>
-        </is>
-      </c>
-      <c r="G196" s="7" t="inlineStr">
-        <is>
-          <t>1.ランダムな文字列をBearerトークンとして付与しGET /api/userにアクセスする</t>
-        </is>
-      </c>
-      <c r="H196" s="7" t="inlineStr">
-        <is>
-          <t>401 Unauthorizedが返る</t>
-        </is>
-      </c>
-      <c r="I196" s="4" t="n"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="5" t="n"/>
-      <c r="B197" s="5" t="n"/>
-      <c r="C197" s="5" t="n"/>
-      <c r="D197" s="5" t="n"/>
-      <c r="E197" s="6" t="inlineStr">
-        <is>
-          <t>16-1-4</t>
-        </is>
-      </c>
-      <c r="F197" s="7" t="inlineStr">
-        <is>
-          <t>削除済み(失効済み)のトークンでアクセスすると401が返る</t>
-        </is>
-      </c>
-      <c r="G197" s="7" t="inlineStr">
-        <is>
-          <t>1.発行済みトークンを削除する
-2.そのトークンでGET /api/userにアクセスする</t>
-        </is>
-      </c>
-      <c r="H197" s="7" t="inlineStr">
-        <is>
-          <t>401 Unauthorizedが返る</t>
-        </is>
-      </c>
-      <c r="I197" s="5" t="n"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B198" s="6" t="inlineStr">
-        <is>
-          <t>読書計画</t>
-        </is>
-      </c>
-      <c r="C198" s="6" t="inlineStr">
-        <is>
-          <t>17-1</t>
-        </is>
-      </c>
-      <c r="D198" s="6" t="inlineStr">
-        <is>
-          <t>読書計画の作成・一覧・読了・削除</t>
-        </is>
-      </c>
-      <c r="E198" s="6" t="inlineStr">
-        <is>
-          <t>17-1-1</t>
-        </is>
-      </c>
-      <c r="F198" s="7" t="inlineStr">
-        <is>
-          <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
-        </is>
-      </c>
-      <c r="G198" s="7" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
-        </is>
-      </c>
-      <c r="H198" s="7" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I198" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
-        </is>
-      </c>
+      <c r="I198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n"/>
@@ -6671,82 +6662,100 @@
       <c r="D199" s="4" t="n"/>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>17-1-2</t>
+          <t>16-1-3</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
+          <t>不正な(存在しない)トークンでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G199" s="7" t="inlineStr">
         <is>
-          <t>1.自分と他人の読書計画をそれぞれ用意する
-2.読書計画一覧ページを開く</t>
+          <t>1.ランダムな文字列をBearerトークンとして付与しGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>自分の計画のみが、target_dateの昇順で表示される</t>
+          <t>401 Unauthorizedが返る</t>
         </is>
       </c>
       <c r="I199" s="4" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="4" t="n"/>
-      <c r="B200" s="4" t="n"/>
-      <c r="C200" s="4" t="n"/>
-      <c r="D200" s="4" t="n"/>
+      <c r="A200" s="5" t="n"/>
+      <c r="B200" s="5" t="n"/>
+      <c r="C200" s="5" t="n"/>
+      <c r="D200" s="5" t="n"/>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>17-1-3</t>
+          <t>16-1-4</t>
         </is>
       </c>
       <c r="F200" s="7" t="inlineStr">
         <is>
-          <t>ステータスで絞り込んで表示できる</t>
+          <t>削除済み(失効済み)のトークンでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G200" s="7" t="inlineStr">
         <is>
-          <t>1.進行中・完了・期限超過の計画をそれぞれ用意する
-2.statusパラメータを指定して一覧を開く</t>
+          <t>1.発行済みトークンを削除する
+2.そのトークンでGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
-          <t>指定したステータスの計画のみ表示される</t>
-        </is>
-      </c>
-      <c r="I200" s="4" t="n"/>
+          <t>401 Unauthorizedが返る</t>
+        </is>
+      </c>
+      <c r="I200" s="5" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="4" t="n"/>
-      <c r="B201" s="4" t="n"/>
-      <c r="C201" s="4" t="n"/>
-      <c r="D201" s="4" t="n"/>
+      <c r="A201" s="6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B201" s="6" t="inlineStr">
+        <is>
+          <t>読書計画</t>
+        </is>
+      </c>
+      <c r="C201" s="6" t="inlineStr">
+        <is>
+          <t>17-1</t>
+        </is>
+      </c>
+      <c r="D201" s="6" t="inlineStr">
+        <is>
+          <t>読書計画の作成・一覧・読了・削除</t>
+        </is>
+      </c>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>17-1-4</t>
+          <t>17-1-1</t>
         </is>
       </c>
       <c r="F201" s="7" t="inlineStr">
         <is>
-          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
+          <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
         </is>
       </c>
       <c r="G201" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍について進行中の計画を作成する
-2.計画作成ページを開く</t>
+          <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
-          <t>書籍選択肢にその書籍が表示されない</t>
-        </is>
-      </c>
-      <c r="I201" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I201" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="n"/>
@@ -6755,22 +6764,23 @@
       <c r="D202" s="4" t="n"/>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>17-1-5</t>
+          <t>17-1-2</t>
         </is>
       </c>
       <c r="F202" s="7" t="inlineStr">
         <is>
-          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
+          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
         </is>
       </c>
       <c r="G202" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
+          <t>1.自分と他人の読書計画をそれぞれ用意する
+2.読書計画一覧ページを開く</t>
         </is>
       </c>
       <c r="H202" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、計画は作成されない</t>
+          <t>自分の計画のみが、target_dateの昇順で表示される</t>
         </is>
       </c>
       <c r="I202" s="4" t="n"/>
@@ -6782,23 +6792,23 @@
       <c r="D203" s="4" t="n"/>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>17-1-6</t>
+          <t>17-1-3</t>
         </is>
       </c>
       <c r="F203" s="7" t="inlineStr">
         <is>
-          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
+          <t>ステータスで絞り込んで表示できる</t>
         </is>
       </c>
       <c r="G203" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を読了(完了)状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.進行中・完了・期限超過の計画をそれぞれ用意する
+2.statusパラメータを指定して一覧を開く</t>
         </is>
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
-          <t>新しい計画が作成される</t>
+          <t>指定したステータスの計画のみ表示される</t>
         </is>
       </c>
       <c r="I203" s="4" t="n"/>
@@ -6810,23 +6820,23 @@
       <c r="D204" s="4" t="n"/>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>17-1-7</t>
+          <t>17-1-4</t>
         </is>
       </c>
       <c r="F204" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
         </is>
       </c>
       <c r="G204" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.期日を入力せずに登録する</t>
+          <t>1.ある書籍について進行中の計画を作成する
+2.計画作成ページを開く</t>
         </is>
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>書籍選択肢にその書籍が表示されない</t>
         </is>
       </c>
       <c r="I204" s="4" t="n"/>
@@ -6838,23 +6848,22 @@
       <c r="D205" s="4" t="n"/>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>17-1-8</t>
+          <t>17-1-5</t>
         </is>
       </c>
       <c r="F205" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
         </is>
       </c>
       <c r="G205" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.過去の日付を期日に指定して登録する</t>
+          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>403Forbiddenになり、計画は作成されない</t>
         </is>
       </c>
       <c r="I205" s="4" t="n"/>
@@ -6866,23 +6875,23 @@
       <c r="D206" s="4" t="n"/>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>17-1-9</t>
+          <t>17-1-6</t>
         </is>
       </c>
       <c r="F206" s="7" t="inlineStr">
         <is>
-          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
+          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
         </is>
       </c>
       <c r="G206" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍・期日を正しく入力して登録する</t>
+          <t>1.ある書籍の計画を読了(完了)状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
+          <t>新しい計画が作成される</t>
         </is>
       </c>
       <c r="I206" s="4" t="n"/>
@@ -6894,22 +6903,23 @@
       <c r="D207" s="4" t="n"/>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>17-1-10</t>
+          <t>17-1-7</t>
         </is>
       </c>
       <c r="F207" s="7" t="inlineStr">
         <is>
-          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G207" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画に対して読了操作を行う</t>
+          <t>1.計画作成ページを開く
+2.期日を入力せずに登録する</t>
         </is>
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I207" s="4" t="n"/>
@@ -6921,22 +6931,23 @@
       <c r="D208" s="4" t="n"/>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>17-1-11</t>
+          <t>17-1-8</t>
         </is>
       </c>
       <c r="F208" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画は読了・削除できない</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G208" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+          <t>1.計画作成ページを開く
+2.過去の日付を期日に指定して登録する</t>
         </is>
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
-          <t>いずれも403Forbiddenになる</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I208" s="4" t="n"/>
@@ -6948,100 +6959,80 @@
       <c r="D209" s="4" t="n"/>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>17-1-12</t>
+          <t>17-1-9</t>
         </is>
       </c>
       <c r="F209" s="7" t="inlineStr">
         <is>
-          <t>自分が作成した読書計画は削除できる</t>
+          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
         </is>
       </c>
       <c r="G209" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の削除ボタンを押す</t>
+          <t>1.計画作成ページを開く
+2.書籍・期日を正しく入力して登録する</t>
         </is>
       </c>
       <c r="H209" s="7" t="inlineStr">
         <is>
-          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
         </is>
       </c>
       <c r="I209" s="4" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="5" t="n"/>
-      <c r="B210" s="5" t="n"/>
-      <c r="C210" s="5" t="n"/>
-      <c r="D210" s="5" t="n"/>
-      <c r="E210" s="8" t="inlineStr">
-        <is>
-          <t>17-1-13</t>
-        </is>
-      </c>
-      <c r="F210" s="9" t="inlineStr">
-        <is>
-          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
-        </is>
-      </c>
-      <c r="G210" s="9" t="inlineStr">
-        <is>
-          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
-2.その読書計画を削除する</t>
-        </is>
-      </c>
-      <c r="H210" s="9" t="inlineStr">
-        <is>
-          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
-        </is>
-      </c>
-      <c r="I210" s="5" t="n"/>
+      <c r="A210" s="4" t="n"/>
+      <c r="B210" s="4" t="n"/>
+      <c r="C210" s="4" t="n"/>
+      <c r="D210" s="4" t="n"/>
+      <c r="E210" s="6" t="inlineStr">
+        <is>
+          <t>17-1-10</t>
+        </is>
+      </c>
+      <c r="F210" s="7" t="inlineStr">
+        <is>
+          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="inlineStr">
+        <is>
+          <t>1.進行中の計画に対して読了操作を行う</t>
+        </is>
+      </c>
+      <c r="H210" s="7" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
+        </is>
+      </c>
+      <c r="I210" s="4" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="6" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B211" s="6" t="inlineStr">
-        <is>
-          <t>読書計画（期限変更）</t>
-        </is>
-      </c>
-      <c r="C211" s="6" t="inlineStr">
-        <is>
-          <t>18-1</t>
-        </is>
-      </c>
-      <c r="D211" s="6" t="inlineStr">
-        <is>
-          <t>読書計画の期日変更</t>
-        </is>
-      </c>
+      <c r="A211" s="4" t="n"/>
+      <c r="B211" s="4" t="n"/>
+      <c r="C211" s="4" t="n"/>
+      <c r="D211" s="4" t="n"/>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>18-1-1</t>
+          <t>17-1-11</t>
         </is>
       </c>
       <c r="F211" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
+          <t>他人が作成した読書計画は読了・削除できない</t>
         </is>
       </c>
       <c r="G211" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
+          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
         </is>
       </c>
       <c r="H211" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I211" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
-        </is>
-      </c>
+          <t>いずれも403Forbiddenになる</t>
+        </is>
+      </c>
+      <c r="I211" s="4" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="4" t="n"/>
@@ -7050,80 +7041,100 @@
       <c r="D212" s="4" t="n"/>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>18-1-2</t>
+          <t>17-1-12</t>
         </is>
       </c>
       <c r="F212" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画の期日は変更できない</t>
+          <t>自分が作成した読書計画は削除できる</t>
         </is>
       </c>
       <c r="G212" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
+          <t>1.自分が作成した計画の削除ボタンを押す</t>
         </is>
       </c>
       <c r="H212" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
+          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
         </is>
       </c>
       <c r="I212" s="4" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="4" t="n"/>
-      <c r="B213" s="4" t="n"/>
-      <c r="C213" s="4" t="n"/>
-      <c r="D213" s="4" t="n"/>
-      <c r="E213" s="6" t="inlineStr">
-        <is>
-          <t>18-1-3</t>
-        </is>
-      </c>
-      <c r="F213" s="7" t="inlineStr">
-        <is>
-          <t>編集画面を開くと現在の期日が初期表示される</t>
-        </is>
-      </c>
-      <c r="G213" s="7" t="inlineStr">
-        <is>
-          <t>1.自分が作成した計画の編集ページを開く</t>
-        </is>
-      </c>
-      <c r="H213" s="7" t="inlineStr">
-        <is>
-          <t>現在登録されている期日が入力欄に表示される</t>
-        </is>
-      </c>
-      <c r="I213" s="4" t="n"/>
+      <c r="A213" s="5" t="n"/>
+      <c r="B213" s="5" t="n"/>
+      <c r="C213" s="5" t="n"/>
+      <c r="D213" s="5" t="n"/>
+      <c r="E213" s="8" t="inlineStr">
+        <is>
+          <t>17-1-13</t>
+        </is>
+      </c>
+      <c r="F213" s="9" t="inlineStr">
+        <is>
+          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
+        </is>
+      </c>
+      <c r="G213" s="9" t="inlineStr">
+        <is>
+          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
+2.その読書計画を削除する</t>
+        </is>
+      </c>
+      <c r="H213" s="9" t="inlineStr">
+        <is>
+          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
+        </is>
+      </c>
+      <c r="I213" s="5" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="4" t="n"/>
-      <c r="B214" s="4" t="n"/>
-      <c r="C214" s="4" t="n"/>
-      <c r="D214" s="4" t="n"/>
+      <c r="A214" s="6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B214" s="6" t="inlineStr">
+        <is>
+          <t>読書計画（期限変更）</t>
+        </is>
+      </c>
+      <c r="C214" s="6" t="inlineStr">
+        <is>
+          <t>18-1</t>
+        </is>
+      </c>
+      <c r="D214" s="6" t="inlineStr">
+        <is>
+          <t>読書計画の期日変更</t>
+        </is>
+      </c>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>18-1-4</t>
+          <t>18-1-1</t>
         </is>
       </c>
       <c r="F214" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
         </is>
       </c>
       <c r="G214" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.期日を空にして更新する</t>
+          <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H214" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I214" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I214" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="n"/>
@@ -7132,23 +7143,22 @@
       <c r="D215" s="4" t="n"/>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>18-1-5</t>
+          <t>18-1-2</t>
         </is>
       </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>他人が作成した読書計画の期日は変更できない</t>
         </is>
       </c>
       <c r="G215" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.過去の日付に変更して更新する</t>
+          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
       <c r="I215" s="4" t="n"/>
@@ -7160,23 +7170,22 @@
       <c r="D216" s="4" t="n"/>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>18-1-6</t>
+          <t>18-1-3</t>
         </is>
       </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
-          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
+          <t>編集画面を開くと現在の期日が初期表示される</t>
         </is>
       </c>
       <c r="G216" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.未来の日付に正しく変更して更新する</t>
+          <t>1.自分が作成した計画の編集ページを開く</t>
         </is>
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
-          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
+          <t>現在登録されている期日が入力欄に表示される</t>
         </is>
       </c>
       <c r="I216" s="4" t="n"/>
@@ -7188,101 +7197,82 @@
       <c r="D217" s="4" t="n"/>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>18-1-7</t>
+          <t>18-1-4</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>一覧・編集画面表示時に、期日を過ぎた「進行中」の計画は自動的に「期限超過」に更新される</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G217" s="7" t="inlineStr">
         <is>
-          <t>1.期日が過去で「進行中」の計画を用意する
-2.読書計画一覧または編集ページを開く</t>
+          <t>1.編集ページを開く
+2.期日を空にして更新する</t>
         </is>
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
-          <t>表示前に計画のステータスが「期限超過」に更新される</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I217" s="4" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="5" t="n"/>
-      <c r="B218" s="5" t="n"/>
-      <c r="C218" s="5" t="n"/>
-      <c r="D218" s="5" t="n"/>
+      <c r="A218" s="4" t="n"/>
+      <c r="B218" s="4" t="n"/>
+      <c r="C218" s="4" t="n"/>
+      <c r="D218" s="4" t="n"/>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>18-1-8</t>
+          <t>18-1-5</t>
         </is>
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は期日を変更できない</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
+          <t>1.編集ページを開く
+2.過去の日付に変更して更新する</t>
         </is>
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
-        </is>
-      </c>
-      <c r="I218" s="5" t="n"/>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I218" s="4" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B219" s="6" t="inlineStr">
-        <is>
-          <t>リマインダーバッチ</t>
-        </is>
-      </c>
-      <c r="C219" s="6" t="inlineStr">
-        <is>
-          <t>19-1</t>
-        </is>
-      </c>
-      <c r="D219" s="6" t="inlineStr">
-        <is>
-          <t>reading-plans:remindコマンドによるリマインダー通知</t>
-        </is>
-      </c>
+      <c r="A219" s="4" t="n"/>
+      <c r="B219" s="4" t="n"/>
+      <c r="C219" s="4" t="n"/>
+      <c r="D219" s="4" t="n"/>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>19-1-1</t>
+          <t>18-1-6</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
+          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
         </is>
       </c>
       <c r="G219" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが3日後・ステータス進行中の計画を用意する
-2.Notification::fake()を設定し reading-plans:remind を実行する</t>
+          <t>1.編集ページを開く
+2.未来の日付に正しく変更して更新する</t>
         </is>
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I219" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
-        </is>
-      </c>
+          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
+        </is>
+      </c>
+      <c r="I219" s="4" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="4" t="n"/>
@@ -7291,130 +7281,129 @@
       <c r="D220" s="4" t="n"/>
       <c r="E220" s="6" t="inlineStr">
         <is>
+          <t>18-1-7</t>
+        </is>
+      </c>
+      <c r="F220" s="7" t="inlineStr">
+        <is>
+          <t>一覧・編集画面表示時に、期日を過ぎた「進行中」の計画は自動的に「期限超過」に更新される</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="inlineStr">
+        <is>
+          <t>1.期日が過去で「進行中」の計画を用意する
+2.読書計画一覧または編集ページを開く</t>
+        </is>
+      </c>
+      <c r="H220" s="7" t="inlineStr">
+        <is>
+          <t>表示前に計画のステータスが「期限超過」に更新される</t>
+        </is>
+      </c>
+      <c r="I220" s="4" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="5" t="n"/>
+      <c r="B221" s="5" t="n"/>
+      <c r="C221" s="5" t="n"/>
+      <c r="D221" s="5" t="n"/>
+      <c r="E221" s="6" t="inlineStr">
+        <is>
+          <t>18-1-8</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」の計画は期日を変更できない</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="inlineStr">
+        <is>
+          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H221" s="7" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、期日は変更されない</t>
+        </is>
+      </c>
+      <c r="I221" s="5" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B222" s="6" t="inlineStr">
+        <is>
+          <t>リマインダーバッチ</t>
+        </is>
+      </c>
+      <c r="C222" s="6" t="inlineStr">
+        <is>
+          <t>19-1</t>
+        </is>
+      </c>
+      <c r="D222" s="6" t="inlineStr">
+        <is>
+          <t>reading-plans:remindコマンドによるリマインダー通知</t>
+        </is>
+      </c>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>19-1-1</t>
+        </is>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日後・ステータス進行中の計画を用意する
+2.Notification::fake()を設定し reading-plans:remind を実行する</t>
+        </is>
+      </c>
+      <c r="H222" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I222" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="n"/>
+      <c r="B223" s="4" t="n"/>
+      <c r="C223" s="4" t="n"/>
+      <c r="D223" s="4" t="n"/>
+      <c r="E223" s="6" t="inlineStr">
+        <is>
           <t>19-1-2</t>
         </is>
       </c>
-      <c r="F220" s="7" t="inlineStr">
+      <c r="F223" s="7" t="inlineStr">
         <is>
           <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
         </is>
       </c>
-      <c r="G220" s="7" t="inlineStr">
+      <c r="G223" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが本日・ステータス進行中の計画を用意する
 2.reading-plans:remindを実行する</t>
         </is>
       </c>
-      <c r="H220" s="7" t="inlineStr">
+      <c r="H223" s="7" t="inlineStr">
         <is>
           <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される</t>
         </is>
       </c>
-      <c r="I220" s="4" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="4" t="n"/>
-      <c r="B221" s="4" t="n"/>
-      <c r="C221" s="4" t="n"/>
-      <c r="D221" s="4" t="n"/>
-      <c r="E221" s="6" t="inlineStr">
-        <is>
-          <t>19-1-3</t>
-        </is>
-      </c>
-      <c r="F221" s="7" t="inlineStr">
-        <is>
-          <t>期限超過から3日後の計画に再エンゲージメント通知が送信される</t>
-        </is>
-      </c>
-      <c r="G221" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが3日前・ステータス期限超過の計画を用意する
-2.reading-plans:remindを実行する</t>
-        </is>
-      </c>
-      <c r="H221" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I221" s="4" t="n"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="5" t="n"/>
-      <c r="B222" s="5" t="n"/>
-      <c r="C222" s="5" t="n"/>
-      <c r="D222" s="5" t="n"/>
-      <c r="E222" s="6" t="inlineStr">
-        <is>
-          <t>19-1-4</t>
-        </is>
-      </c>
-      <c r="F222" s="7" t="inlineStr">
-        <is>
-          <t>いずれの条件にも該当しない計画には通知が送信されない</t>
-        </is>
-      </c>
-      <c r="G222" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
-2.reading-plans:remindを実行する</t>
-        </is>
-      </c>
-      <c r="H222" s="7" t="inlineStr">
-        <is>
-          <t>その計画のユーザーに通知が送信されない</t>
-        </is>
-      </c>
-      <c r="I222" s="5" t="n"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B223" s="6" t="inlineStr">
-        <is>
-          <t>自動失効バッチ</t>
-        </is>
-      </c>
-      <c r="C223" s="6" t="inlineStr">
-        <is>
-          <t>20-1</t>
-        </is>
-      </c>
-      <c r="D223" s="6" t="inlineStr">
-        <is>
-          <t>reading-plans:expireコマンドによる自動失効処理</t>
-        </is>
-      </c>
-      <c r="E223" s="6" t="inlineStr">
-        <is>
-          <t>20-1-1</t>
-        </is>
-      </c>
-      <c r="F223" s="7" t="inlineStr">
-        <is>
-          <t>期日を過ぎた「進行中」の計画が「期限超過」に更新される</t>
-        </is>
-      </c>
-      <c r="G223" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが過去・ステータス進行中の計画を用意する
-2.reading-plans:expireを実行する</t>
-        </is>
-      </c>
-      <c r="H223" s="7" t="inlineStr">
-        <is>
-          <t>対象の計画のstatusが「期限超過」に更新される</t>
-        </is>
-      </c>
-      <c r="I223" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
-        </is>
-      </c>
+      <c r="I223" s="4" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="4" t="n"/>
@@ -7423,154 +7412,155 @@
       <c r="D224" s="4" t="n"/>
       <c r="E224" s="6" t="inlineStr">
         <is>
+          <t>19-1-3</t>
+        </is>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>期限超過から3日後の計画に再エンゲージメント通知が送信される</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日前・ステータス期限超過の計画を用意する
+2.reading-plans:remindを実行する</t>
+        </is>
+      </c>
+      <c r="H224" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I224" s="4" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="5" t="n"/>
+      <c r="B225" s="5" t="n"/>
+      <c r="C225" s="5" t="n"/>
+      <c r="D225" s="5" t="n"/>
+      <c r="E225" s="6" t="inlineStr">
+        <is>
+          <t>19-1-4</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>いずれの条件にも該当しない計画には通知が送信されない</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
+2.reading-plans:remindを実行する</t>
+        </is>
+      </c>
+      <c r="H225" s="7" t="inlineStr">
+        <is>
+          <t>その計画のユーザーに通知が送信されない</t>
+        </is>
+      </c>
+      <c r="I225" s="5" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B226" s="6" t="inlineStr">
+        <is>
+          <t>自動失効バッチ</t>
+        </is>
+      </c>
+      <c r="C226" s="6" t="inlineStr">
+        <is>
+          <t>20-1</t>
+        </is>
+      </c>
+      <c r="D226" s="6" t="inlineStr">
+        <is>
+          <t>reading-plans:expireコマンドによる自動失効処理</t>
+        </is>
+      </c>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>20-1-1</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>期日を過ぎた「進行中」の計画が「期限超過」に更新される</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが過去・ステータス進行中の計画を用意する
+2.reading-plans:expireを実行する</t>
+        </is>
+      </c>
+      <c r="H226" s="7" t="inlineStr">
+        <is>
+          <t>対象の計画のstatusが「期限超過」に更新される</t>
+        </is>
+      </c>
+      <c r="I226" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="n"/>
+      <c r="B227" s="4" t="n"/>
+      <c r="C227" s="4" t="n"/>
+      <c r="D227" s="4" t="n"/>
+      <c r="E227" s="6" t="inlineStr">
+        <is>
           <t>20-1-2</t>
         </is>
       </c>
-      <c r="F224" s="7" t="inlineStr">
+      <c r="F227" s="7" t="inlineStr">
         <is>
           <t>期日が今日以降の「進行中」の計画は失効しない</t>
         </is>
       </c>
-      <c r="G224" s="7" t="inlineStr">
+      <c r="G227" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
 2.reading-plans:expireを実行する</t>
         </is>
       </c>
-      <c r="H224" s="7" t="inlineStr">
+      <c r="H227" s="7" t="inlineStr">
         <is>
           <t>その計画のstatusは「進行中」のまま変化しない</t>
         </is>
       </c>
-      <c r="I224" s="4" t="n"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="4" t="n"/>
-      <c r="B225" s="4" t="n"/>
-      <c r="C225" s="4" t="n"/>
-      <c r="D225" s="4" t="n"/>
-      <c r="E225" s="6" t="inlineStr">
-        <is>
-          <t>20-1-3</t>
-        </is>
-      </c>
-      <c r="F225" s="7" t="inlineStr">
-        <is>
-          <t>既に「完了」または「期限超過」の計画は対象外(重複更新されない)</t>
-        </is>
-      </c>
-      <c r="G225" s="7" t="inlineStr">
-        <is>
-          <t>1.完了済み・期限超過済みの計画をそれぞれ用意する
-2.reading-plans:expireを実行する</t>
-        </is>
-      </c>
-      <c r="H225" s="7" t="inlineStr">
-        <is>
-          <t>いずれの計画もstatusが変化しない</t>
-        </is>
-      </c>
-      <c r="I225" s="4" t="n"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="5" t="n"/>
-      <c r="B226" s="5" t="n"/>
-      <c r="C226" s="5" t="n"/>
-      <c r="D226" s="5" t="n"/>
-      <c r="E226" s="6" t="inlineStr">
-        <is>
-          <t>20-1-4</t>
-        </is>
-      </c>
-      <c r="F226" s="7" t="inlineStr">
-        <is>
-          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
-        </is>
-      </c>
-      <c r="G226" s="7" t="inlineStr">
-        <is>
-          <t>1.失効対象の計画を用意し reading-plans:expire を実行する
-2.DBを直接確認する</t>
-        </is>
-      </c>
-      <c r="H226" s="7" t="inlineStr">
-        <is>
-          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
-        </is>
-      </c>
-      <c r="I226" s="5" t="n"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B227" s="8" t="inlineStr">
-        <is>
-          <t>通知</t>
-        </is>
-      </c>
-      <c r="C227" s="8" t="inlineStr">
-        <is>
-          <t>21-1</t>
-        </is>
-      </c>
-      <c r="D227" s="8" t="inlineStr">
-        <is>
-          <t>通知の既読化</t>
-        </is>
-      </c>
-      <c r="E227" s="8" t="inlineStr">
-        <is>
-          <t>21-1-1</t>
-        </is>
-      </c>
-      <c r="F227" s="9" t="inlineStr">
-        <is>
-          <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
-        </is>
-      </c>
-      <c r="G227" s="9" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態でPATCH /notifications/{id} に直接リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H227" s="9" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
-        </is>
-      </c>
-      <c r="I227" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationTest.php</t>
-        </is>
-      </c>
+      <c r="I227" s="4" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="4" t="n"/>
       <c r="B228" s="4" t="n"/>
       <c r="C228" s="4" t="n"/>
       <c r="D228" s="4" t="n"/>
-      <c r="E228" s="8" t="inlineStr">
-        <is>
-          <t>21-1-2</t>
-        </is>
-      </c>
-      <c r="F228" s="9" t="inlineStr">
-        <is>
-          <t>自分の通知を既読にできる</t>
-        </is>
-      </c>
-      <c r="G228" s="9" t="inlineStr">
-        <is>
-          <t>1.自分宛ての未読通知を用意する
-2.その通知に対してPATCH /notifications/{id} を送信する</t>
-        </is>
-      </c>
-      <c r="H228" s="9" t="inlineStr">
-        <is>
-          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）</t>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>20-1-3</t>
+        </is>
+      </c>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>既に「完了」または「期限超過」の計画は対象外(重複更新されない)</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="inlineStr">
+        <is>
+          <t>1.完了済み・期限超過済みの計画をそれぞれ用意する
+2.reading-plans:expireを実行する</t>
+        </is>
+      </c>
+      <c r="H228" s="7" t="inlineStr">
+        <is>
+          <t>いずれの計画もstatusが変化しない</t>
         </is>
       </c>
       <c r="I228" s="4" t="n"/>
@@ -7580,195 +7570,301 @@
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="5" t="n"/>
       <c r="D229" s="5" t="n"/>
-      <c r="E229" s="8" t="inlineStr">
+      <c r="E229" s="6" t="inlineStr">
+        <is>
+          <t>20-1-4</t>
+        </is>
+      </c>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="inlineStr">
+        <is>
+          <t>1.失効対象の計画を用意し reading-plans:expire を実行する
+2.DBを直接確認する</t>
+        </is>
+      </c>
+      <c r="H229" s="7" t="inlineStr">
+        <is>
+          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
+        </is>
+      </c>
+      <c r="I229" s="5" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B230" s="8" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="C230" s="8" t="inlineStr">
+        <is>
+          <t>21-1</t>
+        </is>
+      </c>
+      <c r="D230" s="8" t="inlineStr">
+        <is>
+          <t>通知の既読化</t>
+        </is>
+      </c>
+      <c r="E230" s="8" t="inlineStr">
+        <is>
+          <t>21-1-1</t>
+        </is>
+      </c>
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
+        </is>
+      </c>
+      <c r="G230" s="9" t="inlineStr">
+        <is>
+          <t>1.未ログイン状態でPATCH /notifications/{id} に直接リクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H230" s="9" t="inlineStr">
+        <is>
+          <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
+        </is>
+      </c>
+      <c r="I230" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="n"/>
+      <c r="B231" s="4" t="n"/>
+      <c r="C231" s="4" t="n"/>
+      <c r="D231" s="4" t="n"/>
+      <c r="E231" s="8" t="inlineStr">
+        <is>
+          <t>21-1-2</t>
+        </is>
+      </c>
+      <c r="F231" s="9" t="inlineStr">
+        <is>
+          <t>自分の通知を既読にできる</t>
+        </is>
+      </c>
+      <c r="G231" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての未読通知を用意する
+2.その通知に対してPATCH /notifications/{id} を送信する</t>
+        </is>
+      </c>
+      <c r="H231" s="9" t="inlineStr">
+        <is>
+          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）</t>
+        </is>
+      </c>
+      <c r="I231" s="4" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="n"/>
+      <c r="B232" s="5" t="n"/>
+      <c r="C232" s="5" t="n"/>
+      <c r="D232" s="5" t="n"/>
+      <c r="E232" s="8" t="inlineStr">
         <is>
           <t>21-1-3</t>
         </is>
       </c>
-      <c r="F229" s="9" t="inlineStr">
+      <c r="F232" s="9" t="inlineStr">
         <is>
           <t>他ユーザーの通知は既読にできない</t>
         </is>
       </c>
-      <c r="G229" s="9" t="inlineStr">
+      <c r="G232" s="9" t="inlineStr">
         <is>
           <t>1.他ユーザー宛ての通知を用意する
 2.そのIDに対してPATCH /notifications/{id} を送信する</t>
         </is>
       </c>
-      <c r="H229" s="9" t="inlineStr">
+      <c r="H232" s="9" t="inlineStr">
         <is>
           <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
         </is>
       </c>
-      <c r="I229" s="5" t="n"/>
+      <c r="I232" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="165">
+  <mergeCells count="168">
     <mergeCell ref="I30:I33"/>
     <mergeCell ref="I92:I96"/>
     <mergeCell ref="C131:C133"/>
+    <mergeCell ref="D178:D183"/>
     <mergeCell ref="D34:D39"/>
     <mergeCell ref="D59:D62"/>
-    <mergeCell ref="D181:D187"/>
+    <mergeCell ref="A191:A196"/>
     <mergeCell ref="C30:C33"/>
+    <mergeCell ref="C191:C196"/>
     <mergeCell ref="D67:D71"/>
-    <mergeCell ref="I194:I197"/>
-    <mergeCell ref="B131:B162"/>
+    <mergeCell ref="I10:I14"/>
     <mergeCell ref="C7:C9"/>
-    <mergeCell ref="I10:I14"/>
-    <mergeCell ref="C175:C180"/>
+    <mergeCell ref="I166:I172"/>
+    <mergeCell ref="B214:B221"/>
+    <mergeCell ref="A184:A190"/>
     <mergeCell ref="C125:C129"/>
     <mergeCell ref="I72:I77"/>
-    <mergeCell ref="C170:C174"/>
     <mergeCell ref="B16:B29"/>
-    <mergeCell ref="A170:A174"/>
-    <mergeCell ref="C198:C210"/>
     <mergeCell ref="D85:D89"/>
-    <mergeCell ref="I175:I180"/>
-    <mergeCell ref="B163:B169"/>
+    <mergeCell ref="I226:I229"/>
     <mergeCell ref="D78:D81"/>
     <mergeCell ref="I134:I141"/>
+    <mergeCell ref="C2:C5"/>
     <mergeCell ref="I145:I151"/>
-    <mergeCell ref="C2:C5"/>
     <mergeCell ref="C134:C141"/>
     <mergeCell ref="B2:B15"/>
+    <mergeCell ref="B226:B229"/>
     <mergeCell ref="D158:D162"/>
     <mergeCell ref="I131:I133"/>
     <mergeCell ref="I100:I102"/>
+    <mergeCell ref="I184:I190"/>
+    <mergeCell ref="I109:I112"/>
     <mergeCell ref="I85:I89"/>
-    <mergeCell ref="I109:I112"/>
     <mergeCell ref="C10:C14"/>
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="I34:I39"/>
+    <mergeCell ref="D191:D196"/>
+    <mergeCell ref="C173:C177"/>
+    <mergeCell ref="I59:I62"/>
     <mergeCell ref="D63:D66"/>
-    <mergeCell ref="I59:I62"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="I181:I187"/>
-    <mergeCell ref="A211:A218"/>
+    <mergeCell ref="B63:B81"/>
     <mergeCell ref="I67:I71"/>
-    <mergeCell ref="B63:B81"/>
+    <mergeCell ref="B166:B172"/>
     <mergeCell ref="C34:C39"/>
-    <mergeCell ref="D227:D229"/>
-    <mergeCell ref="B223:B226"/>
+    <mergeCell ref="D166:D172"/>
+    <mergeCell ref="D184:D190"/>
+    <mergeCell ref="A222:A225"/>
     <mergeCell ref="I142:I144"/>
-    <mergeCell ref="D198:D210"/>
+    <mergeCell ref="A230:A232"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="A106:A108"/>
     <mergeCell ref="C106:C108"/>
-    <mergeCell ref="I188:I193"/>
     <mergeCell ref="C158:C162"/>
+    <mergeCell ref="C201:C213"/>
     <mergeCell ref="C152:C157"/>
+    <mergeCell ref="B173:B177"/>
+    <mergeCell ref="D173:D177"/>
     <mergeCell ref="C40:C52"/>
+    <mergeCell ref="C226:C229"/>
     <mergeCell ref="C109:C112"/>
-    <mergeCell ref="A219:A222"/>
-    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="I201:I213"/>
+    <mergeCell ref="C113:C124"/>
+    <mergeCell ref="D100:D102"/>
+    <mergeCell ref="C92:C96"/>
+    <mergeCell ref="B113:B130"/>
+    <mergeCell ref="I158:I162"/>
     <mergeCell ref="C145:C151"/>
-    <mergeCell ref="B113:B130"/>
-    <mergeCell ref="C92:C96"/>
-    <mergeCell ref="D100:D102"/>
-    <mergeCell ref="I158:I162"/>
-    <mergeCell ref="C219:C222"/>
-    <mergeCell ref="C113:C124"/>
     <mergeCell ref="I152:I157"/>
     <mergeCell ref="D53:D58"/>
-    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="B178:B183"/>
     <mergeCell ref="D30:D33"/>
     <mergeCell ref="A82:A99"/>
+    <mergeCell ref="I106:I108"/>
     <mergeCell ref="I63:I66"/>
-    <mergeCell ref="I106:I108"/>
+    <mergeCell ref="C184:C190"/>
+    <mergeCell ref="C178:C183"/>
     <mergeCell ref="D16:D29"/>
     <mergeCell ref="A63:A81"/>
     <mergeCell ref="D103:D105"/>
+    <mergeCell ref="B230:B232"/>
     <mergeCell ref="D90:D91"/>
     <mergeCell ref="D97:D99"/>
-    <mergeCell ref="D163:D169"/>
-    <mergeCell ref="I198:I210"/>
-    <mergeCell ref="B188:B193"/>
+    <mergeCell ref="D230:D232"/>
     <mergeCell ref="D106:D108"/>
-    <mergeCell ref="A131:A162"/>
-    <mergeCell ref="D188:D193"/>
+    <mergeCell ref="C163:C165"/>
+    <mergeCell ref="I178:I183"/>
+    <mergeCell ref="A197:A200"/>
     <mergeCell ref="B109:B112"/>
+    <mergeCell ref="C197:C200"/>
     <mergeCell ref="D109:D112"/>
     <mergeCell ref="C82:C84"/>
+    <mergeCell ref="I222:I225"/>
     <mergeCell ref="D142:D144"/>
+    <mergeCell ref="I173:I177"/>
     <mergeCell ref="C67:C71"/>
-    <mergeCell ref="A163:A169"/>
-    <mergeCell ref="C163:C169"/>
     <mergeCell ref="D82:D84"/>
     <mergeCell ref="I53:I58"/>
     <mergeCell ref="D131:D133"/>
     <mergeCell ref="C59:C62"/>
-    <mergeCell ref="A223:A226"/>
-    <mergeCell ref="B175:B180"/>
-    <mergeCell ref="D175:D180"/>
+    <mergeCell ref="B191:B196"/>
+    <mergeCell ref="A173:A177"/>
+    <mergeCell ref="D197:D200"/>
     <mergeCell ref="C97:C99"/>
+    <mergeCell ref="A214:A221"/>
     <mergeCell ref="I113:I124"/>
-    <mergeCell ref="I219:I222"/>
-    <mergeCell ref="A175:A180"/>
+    <mergeCell ref="C214:C221"/>
+    <mergeCell ref="B184:B190"/>
     <mergeCell ref="I16:I29"/>
     <mergeCell ref="D134:D141"/>
-    <mergeCell ref="I227:I229"/>
     <mergeCell ref="A16:A29"/>
     <mergeCell ref="C16:C29"/>
-    <mergeCell ref="B198:B210"/>
-    <mergeCell ref="C194:C197"/>
-    <mergeCell ref="I163:I169"/>
-    <mergeCell ref="B211:B218"/>
+    <mergeCell ref="D163:D165"/>
+    <mergeCell ref="I90:I91"/>
     <mergeCell ref="I97:I99"/>
-    <mergeCell ref="I90:I91"/>
-    <mergeCell ref="C227:C229"/>
+    <mergeCell ref="A166:A172"/>
+    <mergeCell ref="C166:C172"/>
+    <mergeCell ref="D214:D221"/>
+    <mergeCell ref="C78:C81"/>
     <mergeCell ref="I7:I9"/>
-    <mergeCell ref="D223:D226"/>
-    <mergeCell ref="C78:C81"/>
-    <mergeCell ref="D211:D218"/>
+    <mergeCell ref="A201:A213"/>
+    <mergeCell ref="I191:I196"/>
+    <mergeCell ref="A226:A229"/>
     <mergeCell ref="A2:A15"/>
     <mergeCell ref="A30:A62"/>
-    <mergeCell ref="B181:B187"/>
     <mergeCell ref="D125:D129"/>
     <mergeCell ref="C53:C58"/>
+    <mergeCell ref="B131:B165"/>
     <mergeCell ref="D40:D52"/>
+    <mergeCell ref="D222:D225"/>
+    <mergeCell ref="I197:I200"/>
     <mergeCell ref="B100:B105"/>
-    <mergeCell ref="I170:I174"/>
     <mergeCell ref="I82:I84"/>
     <mergeCell ref="I2:I5"/>
     <mergeCell ref="C63:C66"/>
-    <mergeCell ref="B219:B222"/>
-    <mergeCell ref="A198:A210"/>
     <mergeCell ref="D92:D96"/>
     <mergeCell ref="A113:A130"/>
-    <mergeCell ref="D219:D222"/>
     <mergeCell ref="D113:D124"/>
-    <mergeCell ref="I223:I226"/>
+    <mergeCell ref="A178:A183"/>
     <mergeCell ref="C90:C91"/>
-    <mergeCell ref="B227:B229"/>
-    <mergeCell ref="C223:C226"/>
-    <mergeCell ref="A181:A187"/>
-    <mergeCell ref="D194:D197"/>
-    <mergeCell ref="C181:C187"/>
     <mergeCell ref="D10:D14"/>
-    <mergeCell ref="C211:C218"/>
     <mergeCell ref="B106:B108"/>
+    <mergeCell ref="I163:I165"/>
     <mergeCell ref="B30:B62"/>
+    <mergeCell ref="A131:A165"/>
+    <mergeCell ref="B201:B213"/>
+    <mergeCell ref="C222:C225"/>
     <mergeCell ref="D72:D77"/>
+    <mergeCell ref="D201:D213"/>
+    <mergeCell ref="I214:I221"/>
     <mergeCell ref="D152:D157"/>
     <mergeCell ref="A100:A105"/>
     <mergeCell ref="C103:C105"/>
-    <mergeCell ref="I211:I218"/>
-    <mergeCell ref="A188:A193"/>
-    <mergeCell ref="C188:C193"/>
+    <mergeCell ref="C230:C232"/>
+    <mergeCell ref="D226:D229"/>
+    <mergeCell ref="B222:B225"/>
     <mergeCell ref="I125:I129"/>
+    <mergeCell ref="C100:C102"/>
     <mergeCell ref="A109:A112"/>
-    <mergeCell ref="C100:C102"/>
+    <mergeCell ref="B197:B200"/>
     <mergeCell ref="I40:I52"/>
+    <mergeCell ref="I78:I81"/>
     <mergeCell ref="D145:D151"/>
-    <mergeCell ref="B170:B174"/>
-    <mergeCell ref="I78:I81"/>
-    <mergeCell ref="D170:D174"/>
     <mergeCell ref="C85:C89"/>
     <mergeCell ref="I103:I105"/>
+    <mergeCell ref="I230:I232"/>
+    <mergeCell ref="C72:C77"/>
     <mergeCell ref="C142:C144"/>
-    <mergeCell ref="C72:C77"/>
     <mergeCell ref="B82:B99"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I232"/>
+  <dimension ref="A1:I229"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5512,8 +5512,8 @@
       <c r="I161" s="4" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="4" t="n"/>
-      <c r="B162" s="4" t="n"/>
+      <c r="A162" s="5" t="n"/>
+      <c r="B162" s="5" t="n"/>
       <c r="C162" s="5" t="n"/>
       <c r="D162" s="5" t="n"/>
       <c r="E162" s="2" t="inlineStr">
@@ -5539,41 +5539,50 @@
       <c r="I162" s="5" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="4" t="n"/>
-      <c r="B163" s="4" t="n"/>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>10-7</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
-        <is>
-          <t>APIのレスポンス形式(Acceptヘッダーなし)</t>
-        </is>
-      </c>
-      <c r="E163" s="2" t="inlineStr">
-        <is>
-          <t>10-7-1</t>
-        </is>
-      </c>
-      <c r="F163" s="3" t="inlineStr">
-        <is>
-          <t>Acceptヘッダーを付けなくても、未認証の書き込みAPIは401のJSONが返る</t>
-        </is>
-      </c>
-      <c r="G163" s="3" t="inlineStr">
-        <is>
-          <t>1.Acceptヘッダーも認証情報も付与せずPOST /api/v1/booksにアクセスする</t>
-        </is>
-      </c>
-      <c r="H163" s="3" t="inlineStr">
-        <is>
-          <t>401が返り、JSON(「Unauthenticated.」)になる。ログイン画面へのリダイレクト(302)にならない</t>
-        </is>
-      </c>
-      <c r="I163" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/ApiJsonResponseTest.php</t>
+      <c r="A163" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>検索・フィルタ</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>11-1</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>書籍のキーワード検索・ジャンル絞り込み</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>11-1-1</t>
+        </is>
+      </c>
+      <c r="F163" s="7" t="inlineStr">
+        <is>
+          <t>タイトルにキーワードを含む書籍が検索結果に表示される</t>
+        </is>
+      </c>
+      <c r="G163" s="7" t="inlineStr">
+        <is>
+          <t>1.タイトルにキーワードを含む書籍を用意する
+2.書籍一覧ページでkeywordにそのキーワードを指定して検索する</t>
+        </is>
+      </c>
+      <c r="H163" s="7" t="inlineStr">
+        <is>
+          <t>該当する書籍が検索結果に表示される</t>
+        </is>
+      </c>
+      <c r="I163" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Search/SearchTest.php</t>
         </is>
       </c>
     </row>
@@ -5582,102 +5591,83 @@
       <c r="B164" s="4" t="n"/>
       <c r="C164" s="4" t="n"/>
       <c r="D164" s="4" t="n"/>
-      <c r="E164" s="2" t="inlineStr">
-        <is>
-          <t>10-7-2</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="inlineStr">
-        <is>
-          <t>Acceptヘッダーを付けなくても、バリデーションエラーは422のJSONが返る</t>
-        </is>
-      </c>
-      <c r="G164" s="3" t="inlineStr">
-        <is>
-          <t>1.トークンを付与し、Acceptヘッダーは付与せず、title・author・genresを指定せずにPOST /api/v1/booksにアクセスする</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>422が返り、JSONでエラーメッセージが返る。元の画面へのリダイレクト(302)にならない</t>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>11-1-2</t>
+        </is>
+      </c>
+      <c r="F164" s="7" t="inlineStr">
+        <is>
+          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
+        </is>
+      </c>
+      <c r="G164" s="7" t="inlineStr">
+        <is>
+          <t>1.著者名にキーワードを含む書籍を用意する
+2.同キーワードで検索する</t>
+        </is>
+      </c>
+      <c r="H164" s="7" t="inlineStr">
+        <is>
+          <t>該当する書籍が検索結果に表示される</t>
         </is>
       </c>
       <c r="I164" s="4" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="5" t="n"/>
-      <c r="B165" s="5" t="n"/>
-      <c r="C165" s="5" t="n"/>
-      <c r="D165" s="5" t="n"/>
-      <c r="E165" s="2" t="inlineStr">
-        <is>
-          <t>10-7-3</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="inlineStr">
-        <is>
-          <t>Acceptヘッダーを付けなくても、存在しないIDは404のJSON(日本語メッセージ)が返る</t>
-        </is>
-      </c>
-      <c r="G165" s="3" t="inlineStr">
-        <is>
-          <t>1.Acceptヘッダーを付与せず、存在しない書籍IDでGET /api/v1/books/{book}にアクセスする</t>
-        </is>
-      </c>
-      <c r="H165" s="3" t="inlineStr">
-        <is>
-          <t>404が返り、「指定された書籍が見つかりません」を含むJSONが返る(HTMLの404画面にならない)</t>
-        </is>
-      </c>
-      <c r="I165" s="5" t="n"/>
+      <c r="A165" s="4" t="n"/>
+      <c r="B165" s="4" t="n"/>
+      <c r="C165" s="4" t="n"/>
+      <c r="D165" s="4" t="n"/>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>11-1-3</t>
+        </is>
+      </c>
+      <c r="F165" s="7" t="inlineStr">
+        <is>
+          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
+        </is>
+      </c>
+      <c r="G165" s="7" t="inlineStr">
+        <is>
+          <t>1.キーワードに一致しない書籍を用意する
+2.検索する</t>
+        </is>
+      </c>
+      <c r="H165" s="7" t="inlineStr">
+        <is>
+          <t>その書籍は検索結果に表示されない</t>
+        </is>
+      </c>
+      <c r="I165" s="4" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B166" s="6" t="inlineStr">
-        <is>
-          <t>検索・フィルタ</t>
-        </is>
-      </c>
-      <c r="C166" s="6" t="inlineStr">
-        <is>
-          <t>11-1</t>
-        </is>
-      </c>
-      <c r="D166" s="6" t="inlineStr">
-        <is>
-          <t>書籍のキーワード検索・ジャンル絞り込み</t>
-        </is>
-      </c>
+      <c r="A166" s="4" t="n"/>
+      <c r="B166" s="4" t="n"/>
+      <c r="C166" s="4" t="n"/>
+      <c r="D166" s="4" t="n"/>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>11-1-1</t>
+          <t>11-1-4</t>
         </is>
       </c>
       <c r="F166" s="7" t="inlineStr">
         <is>
-          <t>タイトルにキーワードを含む書籍が検索結果に表示される</t>
+          <t>キーワード未入力の場合は全件が表示される</t>
         </is>
       </c>
       <c r="G166" s="7" t="inlineStr">
         <is>
-          <t>1.タイトルにキーワードを含む書籍を用意する
-2.書籍一覧ページでkeywordにそのキーワードを指定して検索する</t>
+          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
         </is>
       </c>
       <c r="H166" s="7" t="inlineStr">
         <is>
-          <t>該当する書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="I166" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Search/SearchTest.php</t>
-        </is>
-      </c>
+          <t>登録されている全ての書籍が表示される</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="n"/>
@@ -5686,23 +5676,23 @@
       <c r="D167" s="4" t="n"/>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>11-1-2</t>
+          <t>11-1-5</t>
         </is>
       </c>
       <c r="F167" s="7" t="inlineStr">
         <is>
-          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
+          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
         </is>
       </c>
       <c r="G167" s="7" t="inlineStr">
         <is>
-          <t>1.著者名にキーワードを含む書籍を用意する
-2.同キーワードで検索する</t>
+          <t>1.複数ジャンルの書籍を用意する
+2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
         </is>
       </c>
       <c r="H167" s="7" t="inlineStr">
         <is>
-          <t>該当する書籍が検索結果に表示される</t>
+          <t>指定したジャンルに紐づく書籍のみ表示される</t>
         </is>
       </c>
       <c r="I167" s="4" t="n"/>
@@ -5714,81 +5704,100 @@
       <c r="D168" s="4" t="n"/>
       <c r="E168" s="6" t="inlineStr">
         <is>
-          <t>11-1-3</t>
+          <t>11-1-6</t>
         </is>
       </c>
       <c r="F168" s="7" t="inlineStr">
         <is>
-          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
+          <t>キーワード検索とジャンル絞り込みを組み合わせて使用できる</t>
         </is>
       </c>
       <c r="G168" s="7" t="inlineStr">
         <is>
-          <t>1.キーワードに一致しない書籍を用意する
-2.検索する</t>
+          <t>1.keywordとgenreの両方を指定して一覧を開く</t>
         </is>
       </c>
       <c r="H168" s="7" t="inlineStr">
         <is>
-          <t>その書籍は検索結果に表示されない</t>
+          <t>キーワードとジャンルの両方の条件に一致する書籍のみ表示される</t>
         </is>
       </c>
       <c r="I168" s="4" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="4" t="n"/>
-      <c r="B169" s="4" t="n"/>
-      <c r="C169" s="4" t="n"/>
-      <c r="D169" s="4" t="n"/>
+      <c r="A169" s="5" t="n"/>
+      <c r="B169" s="5" t="n"/>
+      <c r="C169" s="5" t="n"/>
+      <c r="D169" s="5" t="n"/>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>11-1-4</t>
+          <t>11-1-7</t>
         </is>
       </c>
       <c r="F169" s="7" t="inlineStr">
         <is>
-          <t>キーワード未入力の場合は全件が表示される</t>
+          <t>検索結果が0件の場合の表示を確認する</t>
         </is>
       </c>
       <c r="G169" s="7" t="inlineStr">
         <is>
-          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
+          <t>1.どの書籍にも一致しないキーワードで検索する</t>
         </is>
       </c>
       <c r="H169" s="7" t="inlineStr">
         <is>
-          <t>登録されている全ての書籍が表示される</t>
-        </is>
-      </c>
-      <c r="I169" s="4" t="n"/>
+          <t>「書籍が登録されていません。」など0件である旨が表示される</t>
+        </is>
+      </c>
+      <c r="I169" s="5" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="4" t="n"/>
-      <c r="B170" s="4" t="n"/>
-      <c r="C170" s="4" t="n"/>
-      <c r="D170" s="4" t="n"/>
+      <c r="A170" s="6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>ソート</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>書籍一覧の並び替え</t>
+        </is>
+      </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>11-1-5</t>
+          <t>12-1-1</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
+          <t>並び替え未指定時は新着順(登録が新しい順)で表示される</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>1.複数ジャンルの書籍を用意する
-2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
+          <t>1.複数の書籍を異なる日時で登録する
+2.sortを指定せずに書籍一覧を開く</t>
         </is>
       </c>
       <c r="H170" s="7" t="inlineStr">
         <is>
-          <t>指定したジャンルに紐づく書籍のみ表示される</t>
-        </is>
-      </c>
-      <c r="I170" s="4" t="n"/>
+          <t>登録日時が新しい順に表示される</t>
+        </is>
+      </c>
+      <c r="I170" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Sort/SortTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
@@ -5797,156 +5806,157 @@
       <c r="D171" s="4" t="n"/>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>11-1-6</t>
+          <t>12-1-2</t>
         </is>
       </c>
       <c r="F171" s="7" t="inlineStr">
         <is>
-          <t>キーワード検索とジャンル絞り込みを組み合わせて使用できる</t>
+          <t>sort=oldestを指定すると登録が古い順に表示される</t>
         </is>
       </c>
       <c r="G171" s="7" t="inlineStr">
-        <is>
-          <t>1.keywordとgenreの両方を指定して一覧を開く</t>
-        </is>
-      </c>
-      <c r="H171" s="7" t="inlineStr">
-        <is>
-          <t>キーワードとジャンルの両方の条件に一致する書籍のみ表示される</t>
-        </is>
-      </c>
-      <c r="I171" s="4" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="5" t="n"/>
-      <c r="B172" s="5" t="n"/>
-      <c r="C172" s="5" t="n"/>
-      <c r="D172" s="5" t="n"/>
-      <c r="E172" s="6" t="inlineStr">
-        <is>
-          <t>11-1-7</t>
-        </is>
-      </c>
-      <c r="F172" s="7" t="inlineStr">
-        <is>
-          <t>検索結果が0件の場合の表示を確認する</t>
-        </is>
-      </c>
-      <c r="G172" s="7" t="inlineStr">
-        <is>
-          <t>1.どの書籍にも一致しないキーワードで検索する</t>
-        </is>
-      </c>
-      <c r="H172" s="7" t="inlineStr">
-        <is>
-          <t>「書籍が登録されていません。」など0件である旨が表示される</t>
-        </is>
-      </c>
-      <c r="I172" s="5" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B173" s="6" t="inlineStr">
-        <is>
-          <t>ソート</t>
-        </is>
-      </c>
-      <c r="C173" s="6" t="inlineStr">
-        <is>
-          <t>12-1</t>
-        </is>
-      </c>
-      <c r="D173" s="6" t="inlineStr">
-        <is>
-          <t>書籍一覧の並び替え</t>
-        </is>
-      </c>
-      <c r="E173" s="6" t="inlineStr">
-        <is>
-          <t>12-1-1</t>
-        </is>
-      </c>
-      <c r="F173" s="7" t="inlineStr">
-        <is>
-          <t>並び替え未指定時は新着順(登録が新しい順)で表示される</t>
-        </is>
-      </c>
-      <c r="G173" s="7" t="inlineStr">
-        <is>
-          <t>1.複数の書籍を異なる日時で登録する
-2.sortを指定せずに書籍一覧を開く</t>
-        </is>
-      </c>
-      <c r="H173" s="7" t="inlineStr">
-        <is>
-          <t>登録日時が新しい順に表示される</t>
-        </is>
-      </c>
-      <c r="I173" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Sort/SortTest.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="4" t="n"/>
-      <c r="B174" s="4" t="n"/>
-      <c r="C174" s="4" t="n"/>
-      <c r="D174" s="4" t="n"/>
-      <c r="E174" s="6" t="inlineStr">
-        <is>
-          <t>12-1-2</t>
-        </is>
-      </c>
-      <c r="F174" s="7" t="inlineStr">
-        <is>
-          <t>sort=oldestを指定すると登録が古い順に表示される</t>
-        </is>
-      </c>
-      <c r="G174" s="7" t="inlineStr">
         <is>
           <t>1.複数の書籍を異なる日時で登録する
 2.sort=oldestを指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H174" s="7" t="inlineStr">
+      <c r="H171" s="7" t="inlineStr">
         <is>
           <t>登録日時が古い順に表示される</t>
         </is>
       </c>
-      <c r="I174" s="4" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="4" t="n"/>
-      <c r="B175" s="4" t="n"/>
-      <c r="C175" s="4" t="n"/>
-      <c r="D175" s="4" t="n"/>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="I171" s="4" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="n"/>
+      <c r="B172" s="4" t="n"/>
+      <c r="C172" s="4" t="n"/>
+      <c r="D172" s="4" t="n"/>
+      <c r="E172" s="6" t="inlineStr">
         <is>
           <t>12-1-3</t>
         </is>
       </c>
-      <c r="F175" s="7" t="inlineStr">
+      <c r="F172" s="7" t="inlineStr">
         <is>
           <t>sort=titleを指定するとタイトルの昇順で表示される</t>
         </is>
       </c>
-      <c r="G175" s="7" t="inlineStr">
+      <c r="G172" s="7" t="inlineStr">
         <is>
           <t>1.複数の書籍を用意する
 2.sort=titleを指定して書籍一覧を開く</t>
         </is>
       </c>
+      <c r="H172" s="7" t="inlineStr">
+        <is>
+          <t>タイトルの昇順で表示される</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="n"/>
+      <c r="B173" s="4" t="n"/>
+      <c r="C173" s="4" t="n"/>
+      <c r="D173" s="4" t="n"/>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>12-1-4</t>
+        </is>
+      </c>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>sort=ratingを指定すると平均評価が高い順に表示される</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>1.平均評価が異なる複数の書籍を用意する
+2.sort=ratingを指定して書籍一覧を開く</t>
+        </is>
+      </c>
+      <c r="H173" s="7" t="inlineStr">
+        <is>
+          <t>平均評価が高い順に表示される</t>
+        </is>
+      </c>
+      <c r="I173" s="4" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="n"/>
+      <c r="B174" s="5" t="n"/>
+      <c r="C174" s="5" t="n"/>
+      <c r="D174" s="5" t="n"/>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>12-1-5</t>
+        </is>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>sort=rating指定時、平均評価が同じ書籍は新着順で表示される</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t>1.平均評価が同じ複数の書籍を、異なる登録日時で用意する
+2.sort=ratingを指定して書籍一覧を開く</t>
+        </is>
+      </c>
+      <c r="H174" s="7" t="inlineStr">
+        <is>
+          <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
+        </is>
+      </c>
+      <c r="I174" s="5" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>書籍CRUD（認可の詳細テスト）</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>13-1</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>BookPolicyの認可ロジック</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>13-1-1</t>
+        </is>
+      </c>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>ログインユーザーは誰でも書籍を作成できる</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>1.任意のログインユーザーで BookPolicy::create() を確認する</t>
+        </is>
+      </c>
       <c r="H175" s="7" t="inlineStr">
         <is>
-          <t>タイトルの昇順で表示される</t>
-        </is>
-      </c>
-      <c r="I175" s="4" t="n"/>
+          <t>trueが返り、作成が許可される</t>
+        </is>
+      </c>
+      <c r="I175" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/BookAuthorization/BookAuthorizationTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n"/>
@@ -5955,101 +5965,79 @@
       <c r="D176" s="4" t="n"/>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>12-1-4</t>
+          <t>13-1-2</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>sort=ratingを指定すると平均評価が高い順に表示される</t>
+          <t>書籍の登録者本人は更新が許可される</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>1.平均評価が異なる複数の書籍を用意する
-2.sort=ratingを指定して書籍一覧を開く</t>
+          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
-          <t>平均評価が高い順に表示される</t>
+          <t>trueが返る</t>
         </is>
       </c>
       <c r="I176" s="4" t="n"/>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="n"/>
-      <c r="B177" s="5" t="n"/>
-      <c r="C177" s="5" t="n"/>
-      <c r="D177" s="5" t="n"/>
+      <c r="A177" s="4" t="n"/>
+      <c r="B177" s="4" t="n"/>
+      <c r="C177" s="4" t="n"/>
+      <c r="D177" s="4" t="n"/>
       <c r="E177" s="6" t="inlineStr">
         <is>
-          <t>12-1-5</t>
+          <t>13-1-3</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>sort=rating指定時、平均評価が同じ書籍は新着順で表示される</t>
+          <t>書籍の登録者以外は更新が許可されない</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>1.平均評価が同じ複数の書籍を、異なる登録日時で用意する
-2.sort=ratingを指定して書籍一覧を開く</t>
+          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H177" s="7" t="inlineStr">
         <is>
-          <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
-        </is>
-      </c>
-      <c r="I177" s="5" t="n"/>
+          <t>falseが返る</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B178" s="6" t="inlineStr">
-        <is>
-          <t>書籍CRUD（認可の詳細テスト）</t>
-        </is>
-      </c>
-      <c r="C178" s="6" t="inlineStr">
-        <is>
-          <t>13-1</t>
-        </is>
-      </c>
-      <c r="D178" s="6" t="inlineStr">
-        <is>
-          <t>BookPolicyの認可ロジック</t>
-        </is>
-      </c>
+      <c r="A178" s="4" t="n"/>
+      <c r="B178" s="4" t="n"/>
+      <c r="C178" s="4" t="n"/>
+      <c r="D178" s="4" t="n"/>
       <c r="E178" s="6" t="inlineStr">
         <is>
-          <t>13-1-1</t>
+          <t>13-1-4</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>ログインユーザーは誰でも書籍を作成できる</t>
+          <t>書籍の登録者本人は削除が許可される</t>
         </is>
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>1.任意のログインユーザーで BookPolicy::create() を確認する</t>
+          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
         </is>
       </c>
       <c r="H178" s="7" t="inlineStr">
         <is>
-          <t>trueが返り、作成が許可される</t>
-        </is>
-      </c>
-      <c r="I178" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/BookAuthorization/BookAuthorizationTest.php</t>
-        </is>
-      </c>
+          <t>trueが返る</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n"/>
@@ -6058,79 +6046,99 @@
       <c r="D179" s="4" t="n"/>
       <c r="E179" s="6" t="inlineStr">
         <is>
-          <t>13-1-2</t>
+          <t>13-1-5</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者本人は更新が許可される</t>
+          <t>書籍の登録者以外は削除が許可されない</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
+          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
         </is>
       </c>
       <c r="H179" s="7" t="inlineStr">
         <is>
-          <t>trueが返る</t>
+          <t>falseが返る</t>
         </is>
       </c>
       <c r="I179" s="4" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="4" t="n"/>
-      <c r="B180" s="4" t="n"/>
-      <c r="C180" s="4" t="n"/>
-      <c r="D180" s="4" t="n"/>
+      <c r="A180" s="5" t="n"/>
+      <c r="B180" s="5" t="n"/>
+      <c r="C180" s="5" t="n"/>
+      <c r="D180" s="5" t="n"/>
       <c r="E180" s="6" t="inlineStr">
         <is>
-          <t>13-1-3</t>
+          <t>13-1-6</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者以外は更新が許可されない</t>
+          <t>フォームを介さない直接のPUT/DELETEリクエストでも他人の書籍は操作できない</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
+          <t>1.他人が登録した書籍に対して、直接PUT・DELETEリクエストを送信する</t>
         </is>
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
-          <t>falseが返る</t>
-        </is>
-      </c>
-      <c r="I180" s="4" t="n"/>
+          <t>いずれも403Forbiddenになり、データは変更されない</t>
+        </is>
+      </c>
+      <c r="I180" s="5" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="4" t="n"/>
-      <c r="B181" s="4" t="n"/>
-      <c r="C181" s="4" t="n"/>
-      <c r="D181" s="4" t="n"/>
+      <c r="A181" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B181" s="6" t="inlineStr">
+        <is>
+          <t>ISBN検索</t>
+        </is>
+      </c>
+      <c r="C181" s="6" t="inlineStr">
+        <is>
+          <t>14-1</t>
+        </is>
+      </c>
+      <c r="D181" s="6" t="inlineStr">
+        <is>
+          <t>ISBNからの書籍情報取得(外部API連携)</t>
+        </is>
+      </c>
       <c r="E181" s="6" t="inlineStr">
         <is>
-          <t>13-1-4</t>
+          <t>14-1-1</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者本人は削除が許可される</t>
+          <t>未ログインの場合、ISBN検索エンドポイントにアクセスできない</t>
         </is>
       </c>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
+          <t>1.未ログイン状態でGET /books/isbn/{isbn} にアクセスする</t>
         </is>
       </c>
       <c r="H181" s="7" t="inlineStr">
         <is>
-          <t>trueが返る</t>
-        </is>
-      </c>
-      <c r="I181" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I181" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Isbn/IsbnSearchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="n"/>
@@ -6139,99 +6147,79 @@
       <c r="D182" s="4" t="n"/>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>13-1-5</t>
+          <t>14-1-2</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者以外は削除が許可されない</t>
+          <t>ISBNが未入力(空文字)の場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
+          <t>1.ログイン状態でISBN部分を空にしてリクエストする</t>
         </is>
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
-          <t>falseが返る</t>
+          <t>422が返り、「ISBNを入力してください」が返る</t>
         </is>
       </c>
       <c r="I182" s="4" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="n"/>
-      <c r="B183" s="5" t="n"/>
-      <c r="C183" s="5" t="n"/>
-      <c r="D183" s="5" t="n"/>
+      <c r="A183" s="4" t="n"/>
+      <c r="B183" s="4" t="n"/>
+      <c r="C183" s="4" t="n"/>
+      <c r="D183" s="4" t="n"/>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>13-1-6</t>
+          <t>14-1-3</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>フォームを介さない直接のPUT/DELETEリクエストでも他人の書籍は操作できない</t>
+          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>1.他人が登録した書籍に対して、直接PUT・DELETEリクエストを送信する</t>
+          <t>1.13桁でないISBNでリクエストする</t>
         </is>
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>いずれも403Forbiddenになり、データは変更されない</t>
-        </is>
-      </c>
-      <c r="I183" s="5" t="n"/>
+          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B184" s="6" t="inlineStr">
-        <is>
-          <t>ISBN検索</t>
-        </is>
-      </c>
-      <c r="C184" s="6" t="inlineStr">
-        <is>
-          <t>14-1</t>
-        </is>
-      </c>
-      <c r="D184" s="6" t="inlineStr">
-        <is>
-          <t>ISBNからの書籍情報取得(外部API連携)</t>
-        </is>
-      </c>
+      <c r="A184" s="4" t="n"/>
+      <c r="B184" s="4" t="n"/>
+      <c r="C184" s="4" t="n"/>
+      <c r="D184" s="4" t="n"/>
       <c r="E184" s="6" t="inlineStr">
         <is>
-          <t>14-1-1</t>
+          <t>14-1-4</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、ISBN検索エンドポイントにアクセスできない</t>
+          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態でGET /books/isbn/{isbn} にアクセスする</t>
+          <t>1.登録済みのISBNでリクエストする</t>
         </is>
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I184" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Isbn/IsbnSearchTest.php</t>
-        </is>
-      </c>
+          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
+        </is>
+      </c>
+      <c r="I184" s="4" t="n"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="n"/>
@@ -6240,22 +6228,23 @@
       <c r="D185" s="4" t="n"/>
       <c r="E185" s="6" t="inlineStr">
         <is>
-          <t>14-1-2</t>
+          <t>14-1-5</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>ISBNが未入力(空文字)の場合、バリデーションエラーが返る</t>
+          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
         </is>
       </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>1.ログイン状態でISBN部分を空にしてリクエストする</t>
+          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
+2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「ISBNを入力してください」が返る</t>
+          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
         </is>
       </c>
       <c r="I185" s="4" t="n"/>
@@ -6267,80 +6256,101 @@
       <c r="D186" s="4" t="n"/>
       <c r="E186" s="6" t="inlineStr">
         <is>
-          <t>14-1-3</t>
+          <t>14-1-6</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
+          <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>1.13桁でないISBNでリクエストする</t>
+          <t>1.Http::fake()でitemsが空のレスポンスをモックする
+2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
+          <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
         </is>
       </c>
       <c r="I186" s="4" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="4" t="n"/>
-      <c r="B187" s="4" t="n"/>
-      <c r="C187" s="4" t="n"/>
-      <c r="D187" s="4" t="n"/>
+      <c r="A187" s="5" t="n"/>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="5" t="n"/>
+      <c r="D187" s="5" t="n"/>
       <c r="E187" s="6" t="inlineStr">
         <is>
-          <t>14-1-4</t>
+          <t>14-1-7</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
+          <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
         </is>
       </c>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>1.登録済みのISBNでリクエストする</t>
+          <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
+2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H187" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
-        </is>
-      </c>
-      <c r="I187" s="4" t="n"/>
+          <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="4" t="n"/>
-      <c r="B188" s="4" t="n"/>
-      <c r="C188" s="4" t="n"/>
-      <c r="D188" s="4" t="n"/>
+      <c r="A188" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B188" s="6" t="inlineStr">
+        <is>
+          <t>マイ読書レポート</t>
+        </is>
+      </c>
+      <c r="C188" s="6" t="inlineStr">
+        <is>
+          <t>15-1</t>
+        </is>
+      </c>
+      <c r="D188" s="6" t="inlineStr">
+        <is>
+          <t>読書統計の表示</t>
+        </is>
+      </c>
       <c r="E188" s="6" t="inlineStr">
         <is>
-          <t>14-1-5</t>
+          <t>15-1-1</t>
         </is>
       </c>
       <c r="F188" s="7" t="inlineStr">
         <is>
-          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
+          <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
         </is>
       </c>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
-2.未登録ISBNでリクエストする</t>
+          <t>1.未ログイン状態で/reportsを開く</t>
         </is>
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
-          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
-        </is>
-      </c>
-      <c r="I188" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I188" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Report/ReportTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n"/>
@@ -6349,101 +6359,79 @@
       <c r="D189" s="4" t="n"/>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>14-1-6</t>
+          <t>15-1-2</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
+          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でitemsが空のレスポンスをモックする
-2.未登録ISBNでリクエストする</t>
+          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
+          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
         </is>
       </c>
       <c r="I189" s="4" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="n"/>
-      <c r="B190" s="5" t="n"/>
-      <c r="C190" s="5" t="n"/>
-      <c r="D190" s="5" t="n"/>
+      <c r="A190" s="4" t="n"/>
+      <c r="B190" s="4" t="n"/>
+      <c r="C190" s="4" t="n"/>
+      <c r="D190" s="4" t="n"/>
       <c r="E190" s="6" t="inlineStr">
         <is>
-          <t>14-1-7</t>
+          <t>15-1-3</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
+          <t>評価分布(★1〜★5)が正しく表示される</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
-2.未登録ISBNでリクエストする</t>
+          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
-          <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
-        </is>
-      </c>
-      <c r="I190" s="5" t="n"/>
+          <t>各評価の件数が実データと一致して表示される</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="n"/>
     </row>
     <row r="191">
-      <c r="A191" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B191" s="6" t="inlineStr">
-        <is>
-          <t>マイ読書レポート</t>
-        </is>
-      </c>
-      <c r="C191" s="6" t="inlineStr">
-        <is>
-          <t>15-1</t>
-        </is>
-      </c>
-      <c r="D191" s="6" t="inlineStr">
-        <is>
-          <t>読書統計の表示</t>
-        </is>
-      </c>
+      <c r="A191" s="4" t="n"/>
+      <c r="B191" s="4" t="n"/>
+      <c r="C191" s="4" t="n"/>
+      <c r="D191" s="4" t="n"/>
       <c r="E191" s="6" t="inlineStr">
         <is>
-          <t>15-1-1</t>
+          <t>15-1-4</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
+          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で/reportsを開く</t>
+          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I191" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Report/ReportTest.php</t>
-        </is>
-      </c>
+          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
+        </is>
+      </c>
+      <c r="I191" s="4" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="n"/>
@@ -6452,79 +6440,100 @@
       <c r="D192" s="4" t="n"/>
       <c r="E192" s="6" t="inlineStr">
         <is>
-          <t>15-1-2</t>
+          <t>15-1-5</t>
         </is>
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
-          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
+          <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
         </is>
       </c>
       <c r="G192" s="7" t="inlineStr">
         <is>
-          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
+          <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H192" s="7" t="inlineStr">
         <is>
-          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
+          <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
         </is>
       </c>
       <c r="I192" s="4" t="n"/>
     </row>
     <row r="193">
-      <c r="A193" s="4" t="n"/>
-      <c r="B193" s="4" t="n"/>
-      <c r="C193" s="4" t="n"/>
-      <c r="D193" s="4" t="n"/>
+      <c r="A193" s="5" t="n"/>
+      <c r="B193" s="5" t="n"/>
+      <c r="C193" s="5" t="n"/>
+      <c r="D193" s="5" t="n"/>
       <c r="E193" s="6" t="inlineStr">
         <is>
-          <t>15-1-3</t>
+          <t>15-1-6</t>
         </is>
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>評価分布(★1〜★5)が正しく表示される</t>
+          <t>レビューを1件も投稿していない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G193" s="7" t="inlineStr">
         <is>
-          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
+          <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H193" s="7" t="inlineStr">
         <is>
-          <t>各評価の件数が実データと一致して表示される</t>
-        </is>
-      </c>
-      <c r="I193" s="4" t="n"/>
+          <t>総レビュー数・読了冊数が0、平均評価が0として表示され、TOP5一覧は空になる</t>
+        </is>
+      </c>
+      <c r="I193" s="5" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" s="4" t="n"/>
-      <c r="B194" s="4" t="n"/>
-      <c r="C194" s="4" t="n"/>
-      <c r="D194" s="4" t="n"/>
+      <c r="A194" s="6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>Sanctum認証</t>
+        </is>
+      </c>
+      <c r="C194" s="6" t="inlineStr">
+        <is>
+          <t>16-1</t>
+        </is>
+      </c>
+      <c r="D194" s="6" t="inlineStr">
+        <is>
+          <t>APIトークン認証</t>
+        </is>
+      </c>
       <c r="E194" s="6" t="inlineStr">
         <is>
-          <t>15-1-4</t>
+          <t>16-1-1</t>
         </is>
       </c>
       <c r="F194" s="7" t="inlineStr">
         <is>
-          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
+          <t>有効なpersonal access tokenを付与すると/api/userにアクセスできる</t>
         </is>
       </c>
       <c r="G194" s="7" t="inlineStr">
         <is>
-          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
+          <t>1.$user-&gt;createToken()でトークンを発行する
+2.Authorization: Bearer {token}を付与してGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
-          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
-        </is>
-      </c>
-      <c r="I194" s="4" t="n"/>
+          <t>200が返り、対象ユーザーの情報が返る</t>
+        </is>
+      </c>
+      <c r="I194" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n"/>
@@ -6533,127 +6542,127 @@
       <c r="D195" s="4" t="n"/>
       <c r="E195" s="6" t="inlineStr">
         <is>
-          <t>15-1-5</t>
+          <t>16-1-2</t>
         </is>
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
-          <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
+          <t>トークンなしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G195" s="7" t="inlineStr">
         <is>
-          <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
+          <t>1.Authorizationヘッダーを付与せずにGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
-          <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
+          <t>401 Unauthorizedが返る</t>
         </is>
       </c>
       <c r="I195" s="4" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="n"/>
-      <c r="B196" s="5" t="n"/>
-      <c r="C196" s="5" t="n"/>
-      <c r="D196" s="5" t="n"/>
+      <c r="A196" s="4" t="n"/>
+      <c r="B196" s="4" t="n"/>
+      <c r="C196" s="4" t="n"/>
+      <c r="D196" s="4" t="n"/>
       <c r="E196" s="6" t="inlineStr">
         <is>
-          <t>15-1-6</t>
+          <t>16-1-3</t>
         </is>
       </c>
       <c r="F196" s="7" t="inlineStr">
         <is>
-          <t>レビューを1件も投稿していない場合の表示を確認する</t>
+          <t>不正な(存在しない)トークンでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
+          <t>1.ランダムな文字列をBearerトークンとして付与しGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
-          <t>総レビュー数・読了冊数が0、平均評価が0として表示され、TOP5一覧は空になる</t>
-        </is>
-      </c>
-      <c r="I196" s="5" t="n"/>
+          <t>401 Unauthorizedが返る</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B197" s="6" t="inlineStr">
-        <is>
-          <t>Sanctum認証</t>
-        </is>
-      </c>
-      <c r="C197" s="6" t="inlineStr">
-        <is>
-          <t>16-1</t>
-        </is>
-      </c>
-      <c r="D197" s="6" t="inlineStr">
-        <is>
-          <t>APIトークン認証</t>
-        </is>
-      </c>
+      <c r="A197" s="5" t="n"/>
+      <c r="B197" s="5" t="n"/>
+      <c r="C197" s="5" t="n"/>
+      <c r="D197" s="5" t="n"/>
       <c r="E197" s="6" t="inlineStr">
         <is>
-          <t>16-1-1</t>
+          <t>16-1-4</t>
         </is>
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
-          <t>有効なpersonal access tokenを付与すると/api/userにアクセスできる</t>
+          <t>削除済み(失効済み)のトークンでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>1.$user-&gt;createToken()でトークンを発行する
-2.Authorization: Bearer {token}を付与してGET /api/userにアクセスする</t>
+          <t>1.発行済みトークンを削除する
+2.そのトークンでGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>200が返り、対象ユーザーの情報が返る</t>
-        </is>
-      </c>
-      <c r="I197" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
-        </is>
-      </c>
+          <t>401 Unauthorizedが返る</t>
+        </is>
+      </c>
+      <c r="I197" s="5" t="n"/>
     </row>
     <row r="198">
-      <c r="A198" s="4" t="n"/>
-      <c r="B198" s="4" t="n"/>
-      <c r="C198" s="4" t="n"/>
-      <c r="D198" s="4" t="n"/>
+      <c r="A198" s="6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>読書計画</t>
+        </is>
+      </c>
+      <c r="C198" s="6" t="inlineStr">
+        <is>
+          <t>17-1</t>
+        </is>
+      </c>
+      <c r="D198" s="6" t="inlineStr">
+        <is>
+          <t>読書計画の作成・一覧・読了・削除</t>
+        </is>
+      </c>
       <c r="E198" s="6" t="inlineStr">
         <is>
-          <t>16-1-2</t>
+          <t>17-1-1</t>
         </is>
       </c>
       <c r="F198" s="7" t="inlineStr">
         <is>
-          <t>トークンなしでアクセスすると401が返る</t>
+          <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
         </is>
       </c>
       <c r="G198" s="7" t="inlineStr">
         <is>
-          <t>1.Authorizationヘッダーを付与せずにGET /api/userにアクセスする</t>
+          <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H198" s="7" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返る</t>
-        </is>
-      </c>
-      <c r="I198" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I198" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n"/>
@@ -6662,100 +6671,82 @@
       <c r="D199" s="4" t="n"/>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>16-1-3</t>
+          <t>17-1-2</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>不正な(存在しない)トークンでアクセスすると401が返る</t>
+          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
         </is>
       </c>
       <c r="G199" s="7" t="inlineStr">
         <is>
-          <t>1.ランダムな文字列をBearerトークンとして付与しGET /api/userにアクセスする</t>
+          <t>1.自分と他人の読書計画をそれぞれ用意する
+2.読書計画一覧ページを開く</t>
         </is>
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返る</t>
+          <t>自分の計画のみが、target_dateの昇順で表示される</t>
         </is>
       </c>
       <c r="I199" s="4" t="n"/>
     </row>
     <row r="200">
-      <c r="A200" s="5" t="n"/>
-      <c r="B200" s="5" t="n"/>
-      <c r="C200" s="5" t="n"/>
-      <c r="D200" s="5" t="n"/>
+      <c r="A200" s="4" t="n"/>
+      <c r="B200" s="4" t="n"/>
+      <c r="C200" s="4" t="n"/>
+      <c r="D200" s="4" t="n"/>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>16-1-4</t>
+          <t>17-1-3</t>
         </is>
       </c>
       <c r="F200" s="7" t="inlineStr">
         <is>
-          <t>削除済み(失効済み)のトークンでアクセスすると401が返る</t>
+          <t>ステータスで絞り込んで表示できる</t>
         </is>
       </c>
       <c r="G200" s="7" t="inlineStr">
         <is>
-          <t>1.発行済みトークンを削除する
-2.そのトークンでGET /api/userにアクセスする</t>
+          <t>1.進行中・完了・期限超過の計画をそれぞれ用意する
+2.statusパラメータを指定して一覧を開く</t>
         </is>
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返る</t>
-        </is>
-      </c>
-      <c r="I200" s="5" t="n"/>
+          <t>指定したステータスの計画のみ表示される</t>
+        </is>
+      </c>
+      <c r="I200" s="4" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B201" s="6" t="inlineStr">
-        <is>
-          <t>読書計画</t>
-        </is>
-      </c>
-      <c r="C201" s="6" t="inlineStr">
-        <is>
-          <t>17-1</t>
-        </is>
-      </c>
-      <c r="D201" s="6" t="inlineStr">
-        <is>
-          <t>読書計画の作成・一覧・読了・削除</t>
-        </is>
-      </c>
+      <c r="A201" s="4" t="n"/>
+      <c r="B201" s="4" t="n"/>
+      <c r="C201" s="4" t="n"/>
+      <c r="D201" s="4" t="n"/>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>17-1-1</t>
+          <t>17-1-4</t>
         </is>
       </c>
       <c r="F201" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
+          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
         </is>
       </c>
       <c r="G201" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
+          <t>1.ある書籍について進行中の計画を作成する
+2.計画作成ページを開く</t>
         </is>
       </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I201" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
-        </is>
-      </c>
+          <t>書籍選択肢にその書籍が表示されない</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="4" t="n"/>
@@ -6764,23 +6755,22 @@
       <c r="D202" s="4" t="n"/>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>17-1-2</t>
+          <t>17-1-5</t>
         </is>
       </c>
       <c r="F202" s="7" t="inlineStr">
         <is>
-          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
+          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
         </is>
       </c>
       <c r="G202" s="7" t="inlineStr">
         <is>
-          <t>1.自分と他人の読書計画をそれぞれ用意する
-2.読書計画一覧ページを開く</t>
+          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H202" s="7" t="inlineStr">
         <is>
-          <t>自分の計画のみが、target_dateの昇順で表示される</t>
+          <t>403Forbiddenになり、計画は作成されない</t>
         </is>
       </c>
       <c r="I202" s="4" t="n"/>
@@ -6792,23 +6782,23 @@
       <c r="D203" s="4" t="n"/>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>17-1-3</t>
+          <t>17-1-6</t>
         </is>
       </c>
       <c r="F203" s="7" t="inlineStr">
         <is>
-          <t>ステータスで絞り込んで表示できる</t>
+          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
         </is>
       </c>
       <c r="G203" s="7" t="inlineStr">
         <is>
-          <t>1.進行中・完了・期限超過の計画をそれぞれ用意する
-2.statusパラメータを指定して一覧を開く</t>
+          <t>1.ある書籍の計画を読了(完了)状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
-          <t>指定したステータスの計画のみ表示される</t>
+          <t>新しい計画が作成される</t>
         </is>
       </c>
       <c r="I203" s="4" t="n"/>
@@ -6820,23 +6810,23 @@
       <c r="D204" s="4" t="n"/>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>17-1-4</t>
+          <t>17-1-7</t>
         </is>
       </c>
       <c r="F204" s="7" t="inlineStr">
         <is>
-          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G204" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍について進行中の計画を作成する
-2.計画作成ページを開く</t>
+          <t>1.計画作成ページを開く
+2.期日を入力せずに登録する</t>
         </is>
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
-          <t>書籍選択肢にその書籍が表示されない</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I204" s="4" t="n"/>
@@ -6848,22 +6838,23 @@
       <c r="D205" s="4" t="n"/>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>17-1-5</t>
+          <t>17-1-8</t>
         </is>
       </c>
       <c r="F205" s="7" t="inlineStr">
         <is>
-          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G205" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
+          <t>1.計画作成ページを開く
+2.過去の日付を期日に指定して登録する</t>
         </is>
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、計画は作成されない</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I205" s="4" t="n"/>
@@ -6875,23 +6866,23 @@
       <c r="D206" s="4" t="n"/>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>17-1-6</t>
+          <t>17-1-9</t>
         </is>
       </c>
       <c r="F206" s="7" t="inlineStr">
         <is>
-          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
+          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
         </is>
       </c>
       <c r="G206" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を読了(完了)状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.計画作成ページを開く
+2.書籍・期日を正しく入力して登録する</t>
         </is>
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>新しい計画が作成される</t>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
         </is>
       </c>
       <c r="I206" s="4" t="n"/>
@@ -6903,23 +6894,22 @@
       <c r="D207" s="4" t="n"/>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>17-1-7</t>
+          <t>17-1-10</t>
         </is>
       </c>
       <c r="F207" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
         </is>
       </c>
       <c r="G207" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.期日を入力せずに登録する</t>
+          <t>1.進行中の計画に対して読了操作を行う</t>
         </is>
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
         </is>
       </c>
       <c r="I207" s="4" t="n"/>
@@ -6931,23 +6921,22 @@
       <c r="D208" s="4" t="n"/>
       <c r="E208" s="6" t="inlineStr">
         <is>
-          <t>17-1-8</t>
+          <t>17-1-11</t>
         </is>
       </c>
       <c r="F208" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>他人が作成した読書計画は読了・削除できない</t>
         </is>
       </c>
       <c r="G208" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.過去の日付を期日に指定して登録する</t>
+          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
         </is>
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>いずれも403Forbiddenになる</t>
         </is>
       </c>
       <c r="I208" s="4" t="n"/>
@@ -6959,80 +6948,100 @@
       <c r="D209" s="4" t="n"/>
       <c r="E209" s="6" t="inlineStr">
         <is>
-          <t>17-1-9</t>
+          <t>17-1-12</t>
         </is>
       </c>
       <c r="F209" s="7" t="inlineStr">
         <is>
-          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
+          <t>自分が作成した読書計画は削除できる</t>
         </is>
       </c>
       <c r="G209" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍・期日を正しく入力して登録する</t>
+          <t>1.自分が作成した計画の削除ボタンを押す</t>
         </is>
       </c>
       <c r="H209" s="7" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
+          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
         </is>
       </c>
       <c r="I209" s="4" t="n"/>
     </row>
     <row r="210">
-      <c r="A210" s="4" t="n"/>
-      <c r="B210" s="4" t="n"/>
-      <c r="C210" s="4" t="n"/>
-      <c r="D210" s="4" t="n"/>
-      <c r="E210" s="6" t="inlineStr">
-        <is>
-          <t>17-1-10</t>
-        </is>
-      </c>
-      <c r="F210" s="7" t="inlineStr">
-        <is>
-          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
-        </is>
-      </c>
-      <c r="G210" s="7" t="inlineStr">
-        <is>
-          <t>1.進行中の計画に対して読了操作を行う</t>
-        </is>
-      </c>
-      <c r="H210" s="7" t="inlineStr">
-        <is>
-          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
-        </is>
-      </c>
-      <c r="I210" s="4" t="n"/>
+      <c r="A210" s="5" t="n"/>
+      <c r="B210" s="5" t="n"/>
+      <c r="C210" s="5" t="n"/>
+      <c r="D210" s="5" t="n"/>
+      <c r="E210" s="8" t="inlineStr">
+        <is>
+          <t>17-1-13</t>
+        </is>
+      </c>
+      <c r="F210" s="9" t="inlineStr">
+        <is>
+          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
+        </is>
+      </c>
+      <c r="G210" s="9" t="inlineStr">
+        <is>
+          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
+2.その読書計画を削除する</t>
+        </is>
+      </c>
+      <c r="H210" s="9" t="inlineStr">
+        <is>
+          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
+        </is>
+      </c>
+      <c r="I210" s="5" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="4" t="n"/>
-      <c r="B211" s="4" t="n"/>
-      <c r="C211" s="4" t="n"/>
-      <c r="D211" s="4" t="n"/>
+      <c r="A211" s="6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B211" s="6" t="inlineStr">
+        <is>
+          <t>読書計画（期限変更）</t>
+        </is>
+      </c>
+      <c r="C211" s="6" t="inlineStr">
+        <is>
+          <t>18-1</t>
+        </is>
+      </c>
+      <c r="D211" s="6" t="inlineStr">
+        <is>
+          <t>読書計画の期日変更</t>
+        </is>
+      </c>
       <c r="E211" s="6" t="inlineStr">
         <is>
-          <t>17-1-11</t>
+          <t>18-1-1</t>
         </is>
       </c>
       <c r="F211" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画は読了・削除できない</t>
+          <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
         </is>
       </c>
       <c r="G211" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+          <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H211" s="7" t="inlineStr">
         <is>
-          <t>いずれも403Forbiddenになる</t>
-        </is>
-      </c>
-      <c r="I211" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I211" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="n"/>
@@ -7041,100 +7050,80 @@
       <c r="D212" s="4" t="n"/>
       <c r="E212" s="6" t="inlineStr">
         <is>
-          <t>17-1-12</t>
+          <t>18-1-2</t>
         </is>
       </c>
       <c r="F212" s="7" t="inlineStr">
         <is>
-          <t>自分が作成した読書計画は削除できる</t>
+          <t>他人が作成した読書計画の期日は変更できない</t>
         </is>
       </c>
       <c r="G212" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の削除ボタンを押す</t>
+          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H212" s="7" t="inlineStr">
         <is>
-          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
+          <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
       <c r="I212" s="4" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="n"/>
-      <c r="B213" s="5" t="n"/>
-      <c r="C213" s="5" t="n"/>
-      <c r="D213" s="5" t="n"/>
-      <c r="E213" s="8" t="inlineStr">
-        <is>
-          <t>17-1-13</t>
-        </is>
-      </c>
-      <c r="F213" s="9" t="inlineStr">
-        <is>
-          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
-        </is>
-      </c>
-      <c r="G213" s="9" t="inlineStr">
-        <is>
-          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
-2.その読書計画を削除する</t>
-        </is>
-      </c>
-      <c r="H213" s="9" t="inlineStr">
-        <is>
-          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
-        </is>
-      </c>
-      <c r="I213" s="5" t="n"/>
+      <c r="A213" s="4" t="n"/>
+      <c r="B213" s="4" t="n"/>
+      <c r="C213" s="4" t="n"/>
+      <c r="D213" s="4" t="n"/>
+      <c r="E213" s="6" t="inlineStr">
+        <is>
+          <t>18-1-3</t>
+        </is>
+      </c>
+      <c r="F213" s="7" t="inlineStr">
+        <is>
+          <t>編集画面を開くと現在の期日が初期表示される</t>
+        </is>
+      </c>
+      <c r="G213" s="7" t="inlineStr">
+        <is>
+          <t>1.自分が作成した計画の編集ページを開く</t>
+        </is>
+      </c>
+      <c r="H213" s="7" t="inlineStr">
+        <is>
+          <t>現在登録されている期日が入力欄に表示される</t>
+        </is>
+      </c>
+      <c r="I213" s="4" t="n"/>
     </row>
     <row r="214">
-      <c r="A214" s="6" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B214" s="6" t="inlineStr">
-        <is>
-          <t>読書計画（期限変更）</t>
-        </is>
-      </c>
-      <c r="C214" s="6" t="inlineStr">
-        <is>
-          <t>18-1</t>
-        </is>
-      </c>
-      <c r="D214" s="6" t="inlineStr">
-        <is>
-          <t>読書計画の期日変更</t>
-        </is>
-      </c>
+      <c r="A214" s="4" t="n"/>
+      <c r="B214" s="4" t="n"/>
+      <c r="C214" s="4" t="n"/>
+      <c r="D214" s="4" t="n"/>
       <c r="E214" s="6" t="inlineStr">
         <is>
-          <t>18-1-1</t>
+          <t>18-1-4</t>
         </is>
       </c>
       <c r="F214" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G214" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
+          <t>1.編集ページを開く
+2.期日を空にして更新する</t>
         </is>
       </c>
       <c r="H214" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I214" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
-        </is>
-      </c>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="n"/>
@@ -7143,22 +7132,23 @@
       <c r="D215" s="4" t="n"/>
       <c r="E215" s="6" t="inlineStr">
         <is>
-          <t>18-1-2</t>
+          <t>18-1-5</t>
         </is>
       </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画の期日は変更できない</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G215" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
+          <t>1.編集ページを開く
+2.過去の日付に変更して更新する</t>
         </is>
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I215" s="4" t="n"/>
@@ -7170,22 +7160,23 @@
       <c r="D216" s="4" t="n"/>
       <c r="E216" s="6" t="inlineStr">
         <is>
-          <t>18-1-3</t>
+          <t>18-1-6</t>
         </is>
       </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
-          <t>編集画面を開くと現在の期日が初期表示される</t>
+          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
         </is>
       </c>
       <c r="G216" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の編集ページを開く</t>
+          <t>1.編集ページを開く
+2.未来の日付に正しく変更して更新する</t>
         </is>
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
-          <t>現在登録されている期日が入力欄に表示される</t>
+          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
         </is>
       </c>
       <c r="I216" s="4" t="n"/>
@@ -7197,82 +7188,101 @@
       <c r="D217" s="4" t="n"/>
       <c r="E217" s="6" t="inlineStr">
         <is>
-          <t>18-1-4</t>
+          <t>18-1-7</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>一覧・編集画面表示時に、期日を過ぎた「進行中」の計画は自動的に「期限超過」に更新される</t>
         </is>
       </c>
       <c r="G217" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.期日を空にして更新する</t>
+          <t>1.期日が過去で「進行中」の計画を用意する
+2.読書計画一覧または編集ページを開く</t>
         </is>
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>表示前に計画のステータスが「期限超過」に更新される</t>
         </is>
       </c>
       <c r="I217" s="4" t="n"/>
     </row>
     <row r="218">
-      <c r="A218" s="4" t="n"/>
-      <c r="B218" s="4" t="n"/>
-      <c r="C218" s="4" t="n"/>
-      <c r="D218" s="4" t="n"/>
+      <c r="A218" s="5" t="n"/>
+      <c r="B218" s="5" t="n"/>
+      <c r="C218" s="5" t="n"/>
+      <c r="D218" s="5" t="n"/>
       <c r="E218" s="6" t="inlineStr">
         <is>
-          <t>18-1-5</t>
+          <t>18-1-8</t>
         </is>
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>ステータスが「完了」の計画は期日を変更できない</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.過去の日付に変更して更新する</t>
+          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I218" s="4" t="n"/>
+          <t>403Forbiddenになり、期日は変更されない</t>
+        </is>
+      </c>
+      <c r="I218" s="5" t="n"/>
     </row>
     <row r="219">
-      <c r="A219" s="4" t="n"/>
-      <c r="B219" s="4" t="n"/>
-      <c r="C219" s="4" t="n"/>
-      <c r="D219" s="4" t="n"/>
+      <c r="A219" s="6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B219" s="6" t="inlineStr">
+        <is>
+          <t>リマインダーバッチ</t>
+        </is>
+      </c>
+      <c r="C219" s="6" t="inlineStr">
+        <is>
+          <t>19-1</t>
+        </is>
+      </c>
+      <c r="D219" s="6" t="inlineStr">
+        <is>
+          <t>reading-plans:remindコマンドによるリマインダー通知</t>
+        </is>
+      </c>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>18-1-6</t>
+          <t>19-1-1</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
+          <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
         </is>
       </c>
       <c r="G219" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.未来の日付に正しく変更して更新する</t>
+          <t>1.target_dateが3日後・ステータス進行中の計画を用意する
+2.Notification::fake()を設定し reading-plans:remind を実行する</t>
         </is>
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
-        </is>
-      </c>
-      <c r="I219" s="4" t="n"/>
+          <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I219" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="4" t="n"/>
@@ -7281,129 +7291,130 @@
       <c r="D220" s="4" t="n"/>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>18-1-7</t>
+          <t>19-1-2</t>
         </is>
       </c>
       <c r="F220" s="7" t="inlineStr">
         <is>
-          <t>一覧・編集画面表示時に、期日を過ぎた「進行中」の計画は自動的に「期限超過」に更新される</t>
+          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
         </is>
       </c>
       <c r="G220" s="7" t="inlineStr">
-        <is>
-          <t>1.期日が過去で「進行中」の計画を用意する
-2.読書計画一覧または編集ページを開く</t>
-        </is>
-      </c>
-      <c r="H220" s="7" t="inlineStr">
-        <is>
-          <t>表示前に計画のステータスが「期限超過」に更新される</t>
-        </is>
-      </c>
-      <c r="I220" s="4" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="5" t="n"/>
-      <c r="B221" s="5" t="n"/>
-      <c r="C221" s="5" t="n"/>
-      <c r="D221" s="5" t="n"/>
-      <c r="E221" s="6" t="inlineStr">
-        <is>
-          <t>18-1-8</t>
-        </is>
-      </c>
-      <c r="F221" s="7" t="inlineStr">
-        <is>
-          <t>ステータスが「完了」の計画は期日を変更できない</t>
-        </is>
-      </c>
-      <c r="G221" s="7" t="inlineStr">
-        <is>
-          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H221" s="7" t="inlineStr">
-        <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
-        </is>
-      </c>
-      <c r="I221" s="5" t="n"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B222" s="6" t="inlineStr">
-        <is>
-          <t>リマインダーバッチ</t>
-        </is>
-      </c>
-      <c r="C222" s="6" t="inlineStr">
-        <is>
-          <t>19-1</t>
-        </is>
-      </c>
-      <c r="D222" s="6" t="inlineStr">
-        <is>
-          <t>reading-plans:remindコマンドによるリマインダー通知</t>
-        </is>
-      </c>
-      <c r="E222" s="6" t="inlineStr">
-        <is>
-          <t>19-1-1</t>
-        </is>
-      </c>
-      <c r="F222" s="7" t="inlineStr">
-        <is>
-          <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
-        </is>
-      </c>
-      <c r="G222" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが3日後・ステータス進行中の計画を用意する
-2.Notification::fake()を設定し reading-plans:remind を実行する</t>
-        </is>
-      </c>
-      <c r="H222" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I222" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="4" t="n"/>
-      <c r="B223" s="4" t="n"/>
-      <c r="C223" s="4" t="n"/>
-      <c r="D223" s="4" t="n"/>
-      <c r="E223" s="6" t="inlineStr">
-        <is>
-          <t>19-1-2</t>
-        </is>
-      </c>
-      <c r="F223" s="7" t="inlineStr">
-        <is>
-          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
-        </is>
-      </c>
-      <c r="G223" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが本日・ステータス進行中の計画を用意する
 2.reading-plans:remindを実行する</t>
         </is>
       </c>
+      <c r="H220" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I220" s="4" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="n"/>
+      <c r="B221" s="4" t="n"/>
+      <c r="C221" s="4" t="n"/>
+      <c r="D221" s="4" t="n"/>
+      <c r="E221" s="6" t="inlineStr">
+        <is>
+          <t>19-1-3</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>期限超過から3日後の計画に再エンゲージメント通知が送信される</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日前・ステータス期限超過の計画を用意する
+2.reading-plans:remindを実行する</t>
+        </is>
+      </c>
+      <c r="H221" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I221" s="4" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="5" t="n"/>
+      <c r="B222" s="5" t="n"/>
+      <c r="C222" s="5" t="n"/>
+      <c r="D222" s="5" t="n"/>
+      <c r="E222" s="6" t="inlineStr">
+        <is>
+          <t>19-1-4</t>
+        </is>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>いずれの条件にも該当しない計画には通知が送信されない</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
+2.reading-plans:remindを実行する</t>
+        </is>
+      </c>
+      <c r="H222" s="7" t="inlineStr">
+        <is>
+          <t>その計画のユーザーに通知が送信されない</t>
+        </is>
+      </c>
+      <c r="I222" s="5" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B223" s="6" t="inlineStr">
+        <is>
+          <t>自動失効バッチ</t>
+        </is>
+      </c>
+      <c r="C223" s="6" t="inlineStr">
+        <is>
+          <t>20-1</t>
+        </is>
+      </c>
+      <c r="D223" s="6" t="inlineStr">
+        <is>
+          <t>reading-plans:expireコマンドによる自動失効処理</t>
+        </is>
+      </c>
+      <c r="E223" s="6" t="inlineStr">
+        <is>
+          <t>20-1-1</t>
+        </is>
+      </c>
+      <c r="F223" s="7" t="inlineStr">
+        <is>
+          <t>期日を過ぎた「進行中」の計画が「期限超過」に更新される</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが過去・ステータス進行中の計画を用意する
+2.reading-plans:expireを実行する</t>
+        </is>
+      </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I223" s="4" t="n"/>
+          <t>対象の計画のstatusが「期限超過」に更新される</t>
+        </is>
+      </c>
+      <c r="I223" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="4" t="n"/>
@@ -7412,155 +7423,154 @@
       <c r="D224" s="4" t="n"/>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>19-1-3</t>
+          <t>20-1-2</t>
         </is>
       </c>
       <c r="F224" s="7" t="inlineStr">
         <is>
-          <t>期限超過から3日後の計画に再エンゲージメント通知が送信される</t>
+          <t>期日が今日以降の「進行中」の計画は失効しない</t>
         </is>
       </c>
       <c r="G224" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが3日前・ステータス期限超過の計画を用意する
-2.reading-plans:remindを実行する</t>
-        </is>
-      </c>
-      <c r="H224" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I224" s="4" t="n"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="5" t="n"/>
-      <c r="B225" s="5" t="n"/>
-      <c r="C225" s="5" t="n"/>
-      <c r="D225" s="5" t="n"/>
-      <c r="E225" s="6" t="inlineStr">
-        <is>
-          <t>19-1-4</t>
-        </is>
-      </c>
-      <c r="F225" s="7" t="inlineStr">
-        <is>
-          <t>いずれの条件にも該当しない計画には通知が送信されない</t>
-        </is>
-      </c>
-      <c r="G225" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
-2.reading-plans:remindを実行する</t>
-        </is>
-      </c>
-      <c r="H225" s="7" t="inlineStr">
-        <is>
-          <t>その計画のユーザーに通知が送信されない</t>
-        </is>
-      </c>
-      <c r="I225" s="5" t="n"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B226" s="6" t="inlineStr">
-        <is>
-          <t>自動失効バッチ</t>
-        </is>
-      </c>
-      <c r="C226" s="6" t="inlineStr">
-        <is>
-          <t>20-1</t>
-        </is>
-      </c>
-      <c r="D226" s="6" t="inlineStr">
-        <is>
-          <t>reading-plans:expireコマンドによる自動失効処理</t>
-        </is>
-      </c>
-      <c r="E226" s="6" t="inlineStr">
-        <is>
-          <t>20-1-1</t>
-        </is>
-      </c>
-      <c r="F226" s="7" t="inlineStr">
-        <is>
-          <t>期日を過ぎた「進行中」の計画が「期限超過」に更新される</t>
-        </is>
-      </c>
-      <c r="G226" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが過去・ステータス進行中の計画を用意する
-2.reading-plans:expireを実行する</t>
-        </is>
-      </c>
-      <c r="H226" s="7" t="inlineStr">
-        <is>
-          <t>対象の計画のstatusが「期限超過」に更新される</t>
-        </is>
-      </c>
-      <c r="I226" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" s="4" t="n"/>
-      <c r="B227" s="4" t="n"/>
-      <c r="C227" s="4" t="n"/>
-      <c r="D227" s="4" t="n"/>
-      <c r="E227" s="6" t="inlineStr">
-        <is>
-          <t>20-1-2</t>
-        </is>
-      </c>
-      <c r="F227" s="7" t="inlineStr">
-        <is>
-          <t>期日が今日以降の「進行中」の計画は失効しない</t>
-        </is>
-      </c>
-      <c r="G227" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
 2.reading-plans:expireを実行する</t>
         </is>
       </c>
-      <c r="H227" s="7" t="inlineStr">
+      <c r="H224" s="7" t="inlineStr">
         <is>
           <t>その計画のstatusは「進行中」のまま変化しない</t>
         </is>
       </c>
-      <c r="I227" s="4" t="n"/>
+      <c r="I224" s="4" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="n"/>
+      <c r="B225" s="4" t="n"/>
+      <c r="C225" s="4" t="n"/>
+      <c r="D225" s="4" t="n"/>
+      <c r="E225" s="6" t="inlineStr">
+        <is>
+          <t>20-1-3</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>既に「完了」または「期限超過」の計画は対象外(重複更新されない)</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>1.完了済み・期限超過済みの計画をそれぞれ用意する
+2.reading-plans:expireを実行する</t>
+        </is>
+      </c>
+      <c r="H225" s="7" t="inlineStr">
+        <is>
+          <t>いずれの計画もstatusが変化しない</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="5" t="n"/>
+      <c r="B226" s="5" t="n"/>
+      <c r="C226" s="5" t="n"/>
+      <c r="D226" s="5" t="n"/>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>20-1-4</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr">
+        <is>
+          <t>1.失効対象の計画を用意し reading-plans:expire を実行する
+2.DBを直接確認する</t>
+        </is>
+      </c>
+      <c r="H226" s="7" t="inlineStr">
+        <is>
+          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
+        </is>
+      </c>
+      <c r="I226" s="5" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="C227" s="8" t="inlineStr">
+        <is>
+          <t>21-1</t>
+        </is>
+      </c>
+      <c r="D227" s="8" t="inlineStr">
+        <is>
+          <t>通知の既読化</t>
+        </is>
+      </c>
+      <c r="E227" s="8" t="inlineStr">
+        <is>
+          <t>21-1-1</t>
+        </is>
+      </c>
+      <c r="F227" s="9" t="inlineStr">
+        <is>
+          <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
+        </is>
+      </c>
+      <c r="G227" s="9" t="inlineStr">
+        <is>
+          <t>1.未ログイン状態でPATCH /notifications/{id} に直接リクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H227" s="9" t="inlineStr">
+        <is>
+          <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
+        </is>
+      </c>
+      <c r="I227" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="4" t="n"/>
       <c r="B228" s="4" t="n"/>
       <c r="C228" s="4" t="n"/>
       <c r="D228" s="4" t="n"/>
-      <c r="E228" s="6" t="inlineStr">
-        <is>
-          <t>20-1-3</t>
-        </is>
-      </c>
-      <c r="F228" s="7" t="inlineStr">
-        <is>
-          <t>既に「完了」または「期限超過」の計画は対象外(重複更新されない)</t>
-        </is>
-      </c>
-      <c r="G228" s="7" t="inlineStr">
-        <is>
-          <t>1.完了済み・期限超過済みの計画をそれぞれ用意する
-2.reading-plans:expireを実行する</t>
-        </is>
-      </c>
-      <c r="H228" s="7" t="inlineStr">
-        <is>
-          <t>いずれの計画もstatusが変化しない</t>
+      <c r="E228" s="8" t="inlineStr">
+        <is>
+          <t>21-1-2</t>
+        </is>
+      </c>
+      <c r="F228" s="9" t="inlineStr">
+        <is>
+          <t>自分の通知を既読にできる</t>
+        </is>
+      </c>
+      <c r="G228" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての未読通知を用意する
+2.その通知に対してPATCH /notifications/{id} を送信する</t>
+        </is>
+      </c>
+      <c r="H228" s="9" t="inlineStr">
+        <is>
+          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）</t>
         </is>
       </c>
       <c r="I228" s="4" t="n"/>
@@ -7570,301 +7580,195 @@
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="5" t="n"/>
       <c r="D229" s="5" t="n"/>
-      <c r="E229" s="6" t="inlineStr">
-        <is>
-          <t>20-1-4</t>
-        </is>
-      </c>
-      <c r="F229" s="7" t="inlineStr">
-        <is>
-          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
-        </is>
-      </c>
-      <c r="G229" s="7" t="inlineStr">
-        <is>
-          <t>1.失効対象の計画を用意し reading-plans:expire を実行する
-2.DBを直接確認する</t>
-        </is>
-      </c>
-      <c r="H229" s="7" t="inlineStr">
-        <is>
-          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
-        </is>
-      </c>
-      <c r="I229" s="5" t="n"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B230" s="8" t="inlineStr">
-        <is>
-          <t>通知</t>
-        </is>
-      </c>
-      <c r="C230" s="8" t="inlineStr">
-        <is>
-          <t>21-1</t>
-        </is>
-      </c>
-      <c r="D230" s="8" t="inlineStr">
-        <is>
-          <t>通知の既読化</t>
-        </is>
-      </c>
-      <c r="E230" s="8" t="inlineStr">
-        <is>
-          <t>21-1-1</t>
-        </is>
-      </c>
-      <c r="F230" s="9" t="inlineStr">
-        <is>
-          <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
-        </is>
-      </c>
-      <c r="G230" s="9" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態でPATCH /notifications/{id} に直接リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H230" s="9" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
-        </is>
-      </c>
-      <c r="I230" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationTest.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="4" t="n"/>
-      <c r="B231" s="4" t="n"/>
-      <c r="C231" s="4" t="n"/>
-      <c r="D231" s="4" t="n"/>
-      <c r="E231" s="8" t="inlineStr">
-        <is>
-          <t>21-1-2</t>
-        </is>
-      </c>
-      <c r="F231" s="9" t="inlineStr">
-        <is>
-          <t>自分の通知を既読にできる</t>
-        </is>
-      </c>
-      <c r="G231" s="9" t="inlineStr">
-        <is>
-          <t>1.自分宛ての未読通知を用意する
-2.その通知に対してPATCH /notifications/{id} を送信する</t>
-        </is>
-      </c>
-      <c r="H231" s="9" t="inlineStr">
-        <is>
-          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）</t>
-        </is>
-      </c>
-      <c r="I231" s="4" t="n"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="5" t="n"/>
-      <c r="B232" s="5" t="n"/>
-      <c r="C232" s="5" t="n"/>
-      <c r="D232" s="5" t="n"/>
-      <c r="E232" s="8" t="inlineStr">
+      <c r="E229" s="8" t="inlineStr">
         <is>
           <t>21-1-3</t>
         </is>
       </c>
-      <c r="F232" s="9" t="inlineStr">
+      <c r="F229" s="9" t="inlineStr">
         <is>
           <t>他ユーザーの通知は既読にできない</t>
         </is>
       </c>
-      <c r="G232" s="9" t="inlineStr">
+      <c r="G229" s="9" t="inlineStr">
         <is>
           <t>1.他ユーザー宛ての通知を用意する
 2.そのIDに対してPATCH /notifications/{id} を送信する</t>
         </is>
       </c>
-      <c r="H232" s="9" t="inlineStr">
+      <c r="H229" s="9" t="inlineStr">
         <is>
           <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
         </is>
       </c>
-      <c r="I232" s="5" t="n"/>
+      <c r="I229" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="168">
+  <mergeCells count="165">
     <mergeCell ref="I30:I33"/>
     <mergeCell ref="I92:I96"/>
     <mergeCell ref="C131:C133"/>
-    <mergeCell ref="D178:D183"/>
     <mergeCell ref="D34:D39"/>
     <mergeCell ref="D59:D62"/>
-    <mergeCell ref="A191:A196"/>
+    <mergeCell ref="D181:D187"/>
     <mergeCell ref="C30:C33"/>
-    <mergeCell ref="C191:C196"/>
     <mergeCell ref="D67:D71"/>
+    <mergeCell ref="I194:I197"/>
+    <mergeCell ref="B131:B162"/>
+    <mergeCell ref="C7:C9"/>
     <mergeCell ref="I10:I14"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="I166:I172"/>
-    <mergeCell ref="B214:B221"/>
-    <mergeCell ref="A184:A190"/>
+    <mergeCell ref="C175:C180"/>
     <mergeCell ref="C125:C129"/>
     <mergeCell ref="I72:I77"/>
+    <mergeCell ref="C170:C174"/>
     <mergeCell ref="B16:B29"/>
+    <mergeCell ref="A170:A174"/>
+    <mergeCell ref="C198:C210"/>
     <mergeCell ref="D85:D89"/>
-    <mergeCell ref="I226:I229"/>
+    <mergeCell ref="I175:I180"/>
+    <mergeCell ref="B163:B169"/>
     <mergeCell ref="D78:D81"/>
     <mergeCell ref="I134:I141"/>
+    <mergeCell ref="I145:I151"/>
     <mergeCell ref="C2:C5"/>
-    <mergeCell ref="I145:I151"/>
     <mergeCell ref="C134:C141"/>
     <mergeCell ref="B2:B15"/>
-    <mergeCell ref="B226:B229"/>
     <mergeCell ref="D158:D162"/>
     <mergeCell ref="I131:I133"/>
     <mergeCell ref="I100:I102"/>
-    <mergeCell ref="I184:I190"/>
+    <mergeCell ref="I85:I89"/>
     <mergeCell ref="I109:I112"/>
-    <mergeCell ref="I85:I89"/>
     <mergeCell ref="C10:C14"/>
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="I34:I39"/>
-    <mergeCell ref="D191:D196"/>
-    <mergeCell ref="C173:C177"/>
+    <mergeCell ref="D63:D66"/>
     <mergeCell ref="I59:I62"/>
-    <mergeCell ref="D63:D66"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="I181:I187"/>
+    <mergeCell ref="A211:A218"/>
+    <mergeCell ref="I67:I71"/>
     <mergeCell ref="B63:B81"/>
-    <mergeCell ref="I67:I71"/>
-    <mergeCell ref="B166:B172"/>
     <mergeCell ref="C34:C39"/>
-    <mergeCell ref="D166:D172"/>
-    <mergeCell ref="D184:D190"/>
-    <mergeCell ref="A222:A225"/>
+    <mergeCell ref="D227:D229"/>
+    <mergeCell ref="B223:B226"/>
     <mergeCell ref="I142:I144"/>
-    <mergeCell ref="A230:A232"/>
+    <mergeCell ref="D198:D210"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="A106:A108"/>
     <mergeCell ref="C106:C108"/>
+    <mergeCell ref="I188:I193"/>
     <mergeCell ref="C158:C162"/>
-    <mergeCell ref="C201:C213"/>
     <mergeCell ref="C152:C157"/>
-    <mergeCell ref="B173:B177"/>
-    <mergeCell ref="D173:D177"/>
     <mergeCell ref="C40:C52"/>
-    <mergeCell ref="C226:C229"/>
     <mergeCell ref="C109:C112"/>
-    <mergeCell ref="I201:I213"/>
+    <mergeCell ref="A219:A222"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="C145:C151"/>
+    <mergeCell ref="B113:B130"/>
+    <mergeCell ref="C92:C96"/>
+    <mergeCell ref="D100:D102"/>
+    <mergeCell ref="I158:I162"/>
+    <mergeCell ref="C219:C222"/>
     <mergeCell ref="C113:C124"/>
-    <mergeCell ref="D100:D102"/>
-    <mergeCell ref="C92:C96"/>
-    <mergeCell ref="B113:B130"/>
-    <mergeCell ref="I158:I162"/>
-    <mergeCell ref="C145:C151"/>
     <mergeCell ref="I152:I157"/>
     <mergeCell ref="D53:D58"/>
-    <mergeCell ref="B178:B183"/>
+    <mergeCell ref="A227:A229"/>
     <mergeCell ref="D30:D33"/>
     <mergeCell ref="A82:A99"/>
+    <mergeCell ref="I63:I66"/>
     <mergeCell ref="I106:I108"/>
-    <mergeCell ref="I63:I66"/>
-    <mergeCell ref="C184:C190"/>
-    <mergeCell ref="C178:C183"/>
     <mergeCell ref="D16:D29"/>
     <mergeCell ref="A63:A81"/>
     <mergeCell ref="D103:D105"/>
-    <mergeCell ref="B230:B232"/>
     <mergeCell ref="D90:D91"/>
     <mergeCell ref="D97:D99"/>
-    <mergeCell ref="D230:D232"/>
+    <mergeCell ref="D163:D169"/>
+    <mergeCell ref="I198:I210"/>
+    <mergeCell ref="B188:B193"/>
     <mergeCell ref="D106:D108"/>
-    <mergeCell ref="C163:C165"/>
-    <mergeCell ref="I178:I183"/>
-    <mergeCell ref="A197:A200"/>
+    <mergeCell ref="A131:A162"/>
+    <mergeCell ref="D188:D193"/>
     <mergeCell ref="B109:B112"/>
-    <mergeCell ref="C197:C200"/>
     <mergeCell ref="D109:D112"/>
     <mergeCell ref="C82:C84"/>
-    <mergeCell ref="I222:I225"/>
     <mergeCell ref="D142:D144"/>
-    <mergeCell ref="I173:I177"/>
     <mergeCell ref="C67:C71"/>
+    <mergeCell ref="A163:A169"/>
+    <mergeCell ref="C163:C169"/>
     <mergeCell ref="D82:D84"/>
     <mergeCell ref="I53:I58"/>
     <mergeCell ref="D131:D133"/>
     <mergeCell ref="C59:C62"/>
-    <mergeCell ref="B191:B196"/>
-    <mergeCell ref="A173:A177"/>
-    <mergeCell ref="D197:D200"/>
+    <mergeCell ref="A223:A226"/>
+    <mergeCell ref="B175:B180"/>
+    <mergeCell ref="D175:D180"/>
     <mergeCell ref="C97:C99"/>
-    <mergeCell ref="A214:A221"/>
     <mergeCell ref="I113:I124"/>
-    <mergeCell ref="C214:C221"/>
-    <mergeCell ref="B184:B190"/>
+    <mergeCell ref="I219:I222"/>
+    <mergeCell ref="A175:A180"/>
     <mergeCell ref="I16:I29"/>
     <mergeCell ref="D134:D141"/>
+    <mergeCell ref="I227:I229"/>
     <mergeCell ref="A16:A29"/>
     <mergeCell ref="C16:C29"/>
-    <mergeCell ref="D163:D165"/>
+    <mergeCell ref="B198:B210"/>
+    <mergeCell ref="C194:C197"/>
+    <mergeCell ref="I163:I169"/>
+    <mergeCell ref="B211:B218"/>
+    <mergeCell ref="I97:I99"/>
     <mergeCell ref="I90:I91"/>
-    <mergeCell ref="I97:I99"/>
-    <mergeCell ref="A166:A172"/>
-    <mergeCell ref="C166:C172"/>
-    <mergeCell ref="D214:D221"/>
+    <mergeCell ref="C227:C229"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="D223:D226"/>
     <mergeCell ref="C78:C81"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="A201:A213"/>
-    <mergeCell ref="I191:I196"/>
-    <mergeCell ref="A226:A229"/>
+    <mergeCell ref="D211:D218"/>
     <mergeCell ref="A2:A15"/>
     <mergeCell ref="A30:A62"/>
+    <mergeCell ref="B181:B187"/>
     <mergeCell ref="D125:D129"/>
     <mergeCell ref="C53:C58"/>
-    <mergeCell ref="B131:B165"/>
     <mergeCell ref="D40:D52"/>
-    <mergeCell ref="D222:D225"/>
-    <mergeCell ref="I197:I200"/>
     <mergeCell ref="B100:B105"/>
+    <mergeCell ref="I170:I174"/>
     <mergeCell ref="I82:I84"/>
     <mergeCell ref="I2:I5"/>
     <mergeCell ref="C63:C66"/>
+    <mergeCell ref="B219:B222"/>
+    <mergeCell ref="A198:A210"/>
     <mergeCell ref="D92:D96"/>
     <mergeCell ref="A113:A130"/>
+    <mergeCell ref="D219:D222"/>
     <mergeCell ref="D113:D124"/>
-    <mergeCell ref="A178:A183"/>
+    <mergeCell ref="I223:I226"/>
     <mergeCell ref="C90:C91"/>
+    <mergeCell ref="B227:B229"/>
+    <mergeCell ref="C223:C226"/>
+    <mergeCell ref="A181:A187"/>
+    <mergeCell ref="D194:D197"/>
+    <mergeCell ref="C181:C187"/>
     <mergeCell ref="D10:D14"/>
+    <mergeCell ref="C211:C218"/>
     <mergeCell ref="B106:B108"/>
-    <mergeCell ref="I163:I165"/>
     <mergeCell ref="B30:B62"/>
-    <mergeCell ref="A131:A165"/>
-    <mergeCell ref="B201:B213"/>
-    <mergeCell ref="C222:C225"/>
     <mergeCell ref="D72:D77"/>
-    <mergeCell ref="D201:D213"/>
-    <mergeCell ref="I214:I221"/>
     <mergeCell ref="D152:D157"/>
     <mergeCell ref="A100:A105"/>
     <mergeCell ref="C103:C105"/>
-    <mergeCell ref="C230:C232"/>
-    <mergeCell ref="D226:D229"/>
-    <mergeCell ref="B222:B225"/>
+    <mergeCell ref="I211:I218"/>
+    <mergeCell ref="A188:A193"/>
+    <mergeCell ref="C188:C193"/>
     <mergeCell ref="I125:I129"/>
+    <mergeCell ref="A109:A112"/>
     <mergeCell ref="C100:C102"/>
-    <mergeCell ref="A109:A112"/>
-    <mergeCell ref="B197:B200"/>
     <mergeCell ref="I40:I52"/>
+    <mergeCell ref="D145:D151"/>
+    <mergeCell ref="B170:B174"/>
     <mergeCell ref="I78:I81"/>
-    <mergeCell ref="D145:D151"/>
+    <mergeCell ref="D170:D174"/>
     <mergeCell ref="C85:C89"/>
     <mergeCell ref="I103:I105"/>
-    <mergeCell ref="I230:I232"/>
+    <mergeCell ref="C142:C144"/>
     <mergeCell ref="C72:C77"/>
-    <mergeCell ref="C142:C144"/>
     <mergeCell ref="B82:B99"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I229"/>
+  <dimension ref="A1:I232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="D219" s="6" t="inlineStr">
         <is>
-          <t>reading-plans:remindコマンドによるリマインダー通知</t>
+          <t>日次バッチ(reading-plans:daily)によるリマインダー通知</t>
         </is>
       </c>
       <c r="E219" s="6" t="inlineStr">
@@ -7270,7 +7270,7 @@
       <c r="G219" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日後・ステータス進行中の計画を用意する
-2.Notification::fake()を設定し reading-plans:remind を実行する</t>
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
       <c r="H219" s="7" t="inlineStr">
@@ -7302,7 +7302,7 @@
       <c r="G220" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが本日・ステータス進行中の計画を用意する
-2.reading-plans:remindを実行する</t>
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H220" s="7" t="inlineStr">
@@ -7330,7 +7330,7 @@
       <c r="G221" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日前・ステータス期限超過の計画を用意する
-2.reading-plans:remindを実行する</t>
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H221" s="7" t="inlineStr">
@@ -7358,7 +7358,7 @@
       <c r="G222" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
-2.reading-plans:remindを実行する</t>
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H222" s="7" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="D223" s="6" t="inlineStr">
         <is>
-          <t>reading-plans:expireコマンドによる自動失効処理</t>
+          <t>日次バッチ(reading-plans:daily)による自動失効処理</t>
         </is>
       </c>
       <c r="E223" s="6" t="inlineStr">
@@ -7402,7 +7402,7 @@
       <c r="G223" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが過去・ステータス進行中の計画を用意する
-2.reading-plans:expireを実行する</t>
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H223" s="7" t="inlineStr">
@@ -7434,7 +7434,7 @@
       <c r="G224" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
-2.reading-plans:expireを実行する</t>
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H224" s="7" t="inlineStr">
@@ -7462,7 +7462,7 @@
       <c r="G225" s="7" t="inlineStr">
         <is>
           <t>1.完了済み・期限超過済みの計画をそれぞれ用意する
-2.reading-plans:expireを実行する</t>
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H225" s="7" t="inlineStr">
@@ -7473,8 +7473,8 @@
       <c r="I225" s="4" t="n"/>
     </row>
     <row r="226">
-      <c r="A226" s="5" t="n"/>
-      <c r="B226" s="5" t="n"/>
+      <c r="A226" s="4" t="n"/>
+      <c r="B226" s="4" t="n"/>
       <c r="C226" s="5" t="n"/>
       <c r="D226" s="5" t="n"/>
       <c r="E226" s="6" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="G226" s="7" t="inlineStr">
         <is>
-          <t>1.失効対象の計画を用意し reading-plans:expire を実行する
+          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
 2.DBを直接確認する</t>
         </is>
       </c>
@@ -7501,49 +7501,42 @@
       <c r="I226" s="5" t="n"/>
     </row>
     <row r="227">
-      <c r="A227" s="8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B227" s="8" t="inlineStr">
-        <is>
-          <t>通知</t>
-        </is>
-      </c>
-      <c r="C227" s="8" t="inlineStr">
-        <is>
-          <t>21-1</t>
-        </is>
-      </c>
-      <c r="D227" s="8" t="inlineStr">
-        <is>
-          <t>通知の既読化</t>
-        </is>
-      </c>
-      <c r="E227" s="8" t="inlineStr">
-        <is>
-          <t>21-1-1</t>
-        </is>
-      </c>
-      <c r="F227" s="9" t="inlineStr">
-        <is>
-          <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
-        </is>
-      </c>
-      <c r="G227" s="9" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態でPATCH /notifications/{id} に直接リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H227" s="9" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
-        </is>
-      </c>
-      <c r="I227" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationTest.php</t>
+      <c r="A227" s="4" t="n"/>
+      <c r="B227" s="4" t="n"/>
+      <c r="C227" s="6" t="inlineStr">
+        <is>
+          <t>20-2</t>
+        </is>
+      </c>
+      <c r="D227" s="6" t="inlineStr">
+        <is>
+          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
+        </is>
+      </c>
+      <c r="E227" s="6" t="inlineStr">
+        <is>
+          <t>20-2-1</t>
+        </is>
+      </c>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>reading-plans:dailyを実行すると、期限超過への更新と通知の送信の両方が行われる</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="inlineStr">
+        <is>
+          <t>1.期日を過ぎた進行中の計画と、期日3日後の進行中の計画をそれぞれ用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+        </is>
+      </c>
+      <c r="H227" s="7" t="inlineStr">
+        <is>
+          <t>期日を過ぎた計画のstatusが「期限超過」に更新され、期日3日後の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I227" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
         </is>
       </c>
     </row>
@@ -7552,25 +7545,25 @@
       <c r="B228" s="4" t="n"/>
       <c r="C228" s="4" t="n"/>
       <c r="D228" s="4" t="n"/>
-      <c r="E228" s="8" t="inlineStr">
-        <is>
-          <t>21-1-2</t>
-        </is>
-      </c>
-      <c r="F228" s="9" t="inlineStr">
-        <is>
-          <t>自分の通知を既読にできる</t>
-        </is>
-      </c>
-      <c r="G228" s="9" t="inlineStr">
-        <is>
-          <t>1.自分宛ての未読通知を用意する
-2.その通知に対してPATCH /notifications/{id} を送信する</t>
-        </is>
-      </c>
-      <c r="H228" s="9" t="inlineStr">
-        <is>
-          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）</t>
+      <c r="E228" s="6" t="inlineStr">
+        <is>
+          <t>20-2-2</t>
+        </is>
+      </c>
+      <c r="F228" s="7" t="inlineStr">
+        <is>
+          <t>期限超過への更新が、通知対象の抽出より先に行われる</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日前で、ステータスが「進行中」のまま(未更新)の計画を用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+        </is>
+      </c>
+      <c r="H228" s="7" t="inlineStr">
+        <is>
+          <t>計画のstatusが「期限超過」に更新され、そのユーザーに再エンゲージメント(re_engagement)通知が送信される</t>
         </is>
       </c>
       <c r="I228" s="4" t="n"/>
@@ -7580,79 +7573,182 @@
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="5" t="n"/>
       <c r="D229" s="5" t="n"/>
-      <c r="E229" s="8" t="inlineStr">
+      <c r="E229" s="6" t="inlineStr">
+        <is>
+          <t>20-2-3</t>
+        </is>
+      </c>
+      <c r="F229" s="7" t="inlineStr">
+        <is>
+          <t>reading-plans:dailyが毎日20:00に実行されるようスケジュールされている</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="inlineStr">
+        <is>
+          <t>1.アプリケーションのスケジュール(Illuminate\Console\Scheduling\Schedule)から、登録済みのイベントを取得する</t>
+        </is>
+      </c>
+      <c r="H229" s="7" t="inlineStr">
+        <is>
+          <t>reading-plans:dailyのイベントが登録されており、cron式が毎日20:00(0 20 * * *)になっている</t>
+        </is>
+      </c>
+      <c r="I229" s="5" t="n"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B230" s="8" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="C230" s="8" t="inlineStr">
+        <is>
+          <t>21-1</t>
+        </is>
+      </c>
+      <c r="D230" s="8" t="inlineStr">
+        <is>
+          <t>通知の既読化</t>
+        </is>
+      </c>
+      <c r="E230" s="8" t="inlineStr">
+        <is>
+          <t>21-1-1</t>
+        </is>
+      </c>
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
+        </is>
+      </c>
+      <c r="G230" s="9" t="inlineStr">
+        <is>
+          <t>1.未ログイン状態でPATCH /notifications/{id} に直接リクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H230" s="9" t="inlineStr">
+        <is>
+          <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
+        </is>
+      </c>
+      <c r="I230" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="n"/>
+      <c r="B231" s="4" t="n"/>
+      <c r="C231" s="4" t="n"/>
+      <c r="D231" s="4" t="n"/>
+      <c r="E231" s="8" t="inlineStr">
+        <is>
+          <t>21-1-2</t>
+        </is>
+      </c>
+      <c r="F231" s="9" t="inlineStr">
+        <is>
+          <t>自分の通知を既読にできる</t>
+        </is>
+      </c>
+      <c r="G231" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての未読通知を用意する
+2.その通知に対してPATCH /notifications/{id} を送信する</t>
+        </is>
+      </c>
+      <c r="H231" s="9" t="inlineStr">
+        <is>
+          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）</t>
+        </is>
+      </c>
+      <c r="I231" s="4" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="5" t="n"/>
+      <c r="B232" s="5" t="n"/>
+      <c r="C232" s="5" t="n"/>
+      <c r="D232" s="5" t="n"/>
+      <c r="E232" s="8" t="inlineStr">
         <is>
           <t>21-1-3</t>
         </is>
       </c>
-      <c r="F229" s="9" t="inlineStr">
+      <c r="F232" s="9" t="inlineStr">
         <is>
           <t>他ユーザーの通知は既読にできない</t>
         </is>
       </c>
-      <c r="G229" s="9" t="inlineStr">
+      <c r="G232" s="9" t="inlineStr">
         <is>
           <t>1.他ユーザー宛ての通知を用意する
 2.そのIDに対してPATCH /notifications/{id} を送信する</t>
         </is>
       </c>
-      <c r="H229" s="9" t="inlineStr">
+      <c r="H232" s="9" t="inlineStr">
         <is>
           <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
         </is>
       </c>
-      <c r="I229" s="5" t="n"/>
+      <c r="I232" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="165">
+  <mergeCells count="168">
     <mergeCell ref="I30:I33"/>
+    <mergeCell ref="A223:A229"/>
     <mergeCell ref="I92:I96"/>
     <mergeCell ref="C131:C133"/>
     <mergeCell ref="D34:D39"/>
     <mergeCell ref="D59:D62"/>
+    <mergeCell ref="C30:C33"/>
     <mergeCell ref="D181:D187"/>
-    <mergeCell ref="C30:C33"/>
     <mergeCell ref="D67:D71"/>
     <mergeCell ref="I194:I197"/>
+    <mergeCell ref="I10:I14"/>
     <mergeCell ref="B131:B162"/>
     <mergeCell ref="C7:C9"/>
-    <mergeCell ref="I10:I14"/>
     <mergeCell ref="C175:C180"/>
     <mergeCell ref="C125:C129"/>
     <mergeCell ref="I72:I77"/>
+    <mergeCell ref="A170:A174"/>
+    <mergeCell ref="B16:B29"/>
     <mergeCell ref="C170:C174"/>
-    <mergeCell ref="B16:B29"/>
-    <mergeCell ref="A170:A174"/>
     <mergeCell ref="C198:C210"/>
     <mergeCell ref="D85:D89"/>
     <mergeCell ref="I175:I180"/>
     <mergeCell ref="B163:B169"/>
     <mergeCell ref="D78:D81"/>
     <mergeCell ref="I134:I141"/>
+    <mergeCell ref="C2:C5"/>
     <mergeCell ref="I145:I151"/>
-    <mergeCell ref="C2:C5"/>
     <mergeCell ref="C134:C141"/>
     <mergeCell ref="B2:B15"/>
     <mergeCell ref="D158:D162"/>
     <mergeCell ref="I131:I133"/>
     <mergeCell ref="I100:I102"/>
+    <mergeCell ref="I109:I112"/>
     <mergeCell ref="I85:I89"/>
-    <mergeCell ref="I109:I112"/>
     <mergeCell ref="C10:C14"/>
     <mergeCell ref="D7:D9"/>
     <mergeCell ref="I34:I39"/>
+    <mergeCell ref="I59:I62"/>
     <mergeCell ref="D63:D66"/>
-    <mergeCell ref="I59:I62"/>
     <mergeCell ref="B194:B197"/>
     <mergeCell ref="I181:I187"/>
+    <mergeCell ref="B63:B81"/>
+    <mergeCell ref="I67:I71"/>
     <mergeCell ref="A211:A218"/>
-    <mergeCell ref="I67:I71"/>
-    <mergeCell ref="B63:B81"/>
     <mergeCell ref="C34:C39"/>
     <mergeCell ref="D227:D229"/>
-    <mergeCell ref="B223:B226"/>
     <mergeCell ref="I142:I144"/>
     <mergeCell ref="D198:D210"/>
+    <mergeCell ref="A230:A232"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="A106:A108"/>
     <mergeCell ref="C106:C108"/>
@@ -7661,29 +7757,31 @@
     <mergeCell ref="C152:C157"/>
     <mergeCell ref="C40:C52"/>
     <mergeCell ref="C109:C112"/>
+    <mergeCell ref="D100:D102"/>
+    <mergeCell ref="C92:C96"/>
+    <mergeCell ref="B113:B130"/>
+    <mergeCell ref="C145:C151"/>
+    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="I158:I162"/>
     <mergeCell ref="A219:A222"/>
-    <mergeCell ref="A194:A197"/>
-    <mergeCell ref="C145:C151"/>
-    <mergeCell ref="B113:B130"/>
-    <mergeCell ref="C92:C96"/>
-    <mergeCell ref="D100:D102"/>
-    <mergeCell ref="I158:I162"/>
     <mergeCell ref="C219:C222"/>
     <mergeCell ref="C113:C124"/>
     <mergeCell ref="I152:I157"/>
     <mergeCell ref="D53:D58"/>
-    <mergeCell ref="A227:A229"/>
     <mergeCell ref="D30:D33"/>
     <mergeCell ref="A82:A99"/>
+    <mergeCell ref="I106:I108"/>
     <mergeCell ref="I63:I66"/>
-    <mergeCell ref="I106:I108"/>
+    <mergeCell ref="B223:B229"/>
     <mergeCell ref="D16:D29"/>
     <mergeCell ref="A63:A81"/>
     <mergeCell ref="D103:D105"/>
+    <mergeCell ref="B230:B232"/>
+    <mergeCell ref="I198:I210"/>
     <mergeCell ref="D90:D91"/>
     <mergeCell ref="D97:D99"/>
     <mergeCell ref="D163:D169"/>
-    <mergeCell ref="I198:I210"/>
+    <mergeCell ref="D230:D232"/>
     <mergeCell ref="B188:B193"/>
     <mergeCell ref="D106:D108"/>
     <mergeCell ref="A131:A162"/>
@@ -7699,33 +7797,32 @@
     <mergeCell ref="I53:I58"/>
     <mergeCell ref="D131:D133"/>
     <mergeCell ref="C59:C62"/>
-    <mergeCell ref="A223:A226"/>
     <mergeCell ref="B175:B180"/>
+    <mergeCell ref="I219:I222"/>
+    <mergeCell ref="C97:C99"/>
     <mergeCell ref="D175:D180"/>
-    <mergeCell ref="C97:C99"/>
     <mergeCell ref="I113:I124"/>
-    <mergeCell ref="I219:I222"/>
+    <mergeCell ref="I16:I29"/>
     <mergeCell ref="A175:A180"/>
-    <mergeCell ref="I16:I29"/>
     <mergeCell ref="D134:D141"/>
+    <mergeCell ref="A16:A29"/>
     <mergeCell ref="I227:I229"/>
-    <mergeCell ref="A16:A29"/>
+    <mergeCell ref="C194:C197"/>
+    <mergeCell ref="B198:B210"/>
     <mergeCell ref="C16:C29"/>
-    <mergeCell ref="B198:B210"/>
-    <mergeCell ref="C194:C197"/>
+    <mergeCell ref="I97:I99"/>
+    <mergeCell ref="B211:B218"/>
     <mergeCell ref="I163:I169"/>
-    <mergeCell ref="B211:B218"/>
-    <mergeCell ref="I97:I99"/>
     <mergeCell ref="I90:I91"/>
     <mergeCell ref="C227:C229"/>
+    <mergeCell ref="C78:C81"/>
+    <mergeCell ref="D223:D226"/>
     <mergeCell ref="I7:I9"/>
-    <mergeCell ref="D223:D226"/>
-    <mergeCell ref="C78:C81"/>
     <mergeCell ref="D211:D218"/>
     <mergeCell ref="A2:A15"/>
     <mergeCell ref="A30:A62"/>
+    <mergeCell ref="D125:D129"/>
     <mergeCell ref="B181:B187"/>
-    <mergeCell ref="D125:D129"/>
     <mergeCell ref="C53:C58"/>
     <mergeCell ref="D40:D52"/>
     <mergeCell ref="B100:B105"/>
@@ -7733,19 +7830,18 @@
     <mergeCell ref="I82:I84"/>
     <mergeCell ref="I2:I5"/>
     <mergeCell ref="C63:C66"/>
+    <mergeCell ref="A198:A210"/>
     <mergeCell ref="B219:B222"/>
-    <mergeCell ref="A198:A210"/>
+    <mergeCell ref="A113:A130"/>
     <mergeCell ref="D92:D96"/>
-    <mergeCell ref="A113:A130"/>
     <mergeCell ref="D219:D222"/>
     <mergeCell ref="D113:D124"/>
+    <mergeCell ref="C90:C91"/>
     <mergeCell ref="I223:I226"/>
-    <mergeCell ref="C90:C91"/>
-    <mergeCell ref="B227:B229"/>
     <mergeCell ref="C223:C226"/>
     <mergeCell ref="A181:A187"/>
+    <mergeCell ref="C181:C187"/>
     <mergeCell ref="D194:D197"/>
-    <mergeCell ref="C181:C187"/>
     <mergeCell ref="D10:D14"/>
     <mergeCell ref="C211:C218"/>
     <mergeCell ref="B106:B108"/>
@@ -7754,21 +7850,23 @@
     <mergeCell ref="D152:D157"/>
     <mergeCell ref="A100:A105"/>
     <mergeCell ref="C103:C105"/>
+    <mergeCell ref="C230:C232"/>
     <mergeCell ref="I211:I218"/>
     <mergeCell ref="A188:A193"/>
     <mergeCell ref="C188:C193"/>
     <mergeCell ref="I125:I129"/>
+    <mergeCell ref="I40:I52"/>
+    <mergeCell ref="C100:C102"/>
     <mergeCell ref="A109:A112"/>
-    <mergeCell ref="C100:C102"/>
-    <mergeCell ref="I40:I52"/>
+    <mergeCell ref="I78:I81"/>
+    <mergeCell ref="B170:B174"/>
     <mergeCell ref="D145:D151"/>
-    <mergeCell ref="B170:B174"/>
-    <mergeCell ref="I78:I81"/>
     <mergeCell ref="D170:D174"/>
     <mergeCell ref="C85:C89"/>
     <mergeCell ref="I103:I105"/>
+    <mergeCell ref="I230:I232"/>
+    <mergeCell ref="C72:C77"/>
     <mergeCell ref="C142:C144"/>
-    <mergeCell ref="C72:C77"/>
     <mergeCell ref="B82:B99"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7843,7 +7941,7 @@
     <row r="9" ht="40" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>・「リマインダーバッチ」は reading-plans:remind コマンド、「自動失効バッチ」は reading-plans:expire コマンドがそれぞれ担っており(旧 reading-plans:check を分割)、検証観点(通知送信/ステータス更新)ごとにテストファイルを分けています。</t>
+          <t>・「リマインダーバッチ」「自動失効バッチ」は、どちらも日次バッチ reading-plans:daily(毎日20:00に実行)が担っています。daily は内部で reading-plans:expire(期限超過への更新)→ reading-plans:remind(通知の送信)の順に実行するため、テストでは実際の入口である reading-plans:daily を実行し、検証観点(通知送信/ステータス更新)ごとにテストファイルを分けています。実行順・スケジュール登録に関するケースは 20-2 にまとめています。</t>
         </is>
       </c>
     </row>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I249"/>
+  <dimension ref="A1:I251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返る</t>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
         </is>
       </c>
       <c r="I129" s="3" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、書籍は登録されない</t>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録されない</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、書籍は更新されない</t>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は更新されない</t>
         </is>
       </c>
       <c r="I150" s="3" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>403 Forbiddenが返り、書籍は更新されない</t>
+          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は更新されない</t>
         </is>
       </c>
       <c r="I153" s="4" t="n"/>
@@ -5336,69 +5336,69 @@
     <row r="156">
       <c r="A156" s="4" t="n"/>
       <c r="B156" s="4" t="n"/>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>10-6</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
-        <is>
-          <t>書籍削除API(DELETE /api/v1/books/{book})</t>
-        </is>
-      </c>
+      <c r="C156" s="5" t="n"/>
+      <c r="D156" s="5" t="n"/>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>10-6-1</t>
+          <t>10-5-7</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>認証なしでアクセスすると401が返る</t>
+          <t>他のユーザーが登録した書籍に対して不正な入力で更新しようとしても、422ではなく403が返る</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>1.認証情報を付与せずDELETE /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
+          <t>1.他のユーザーが登録した書籍を用意する
+2.別のユーザーのトークンを付与し、タイトルを空にするなど不正な内容でPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、書籍は削除されない</t>
-        </is>
-      </c>
-      <c r="I156" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiDestroyTest.php</t>
-        </is>
-      </c>
+          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る（入力チェックより先に権限が判定される）。書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I156" s="5" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n"/>
       <c r="B157" s="4" t="n"/>
-      <c r="C157" s="4" t="n"/>
-      <c r="D157" s="4" t="n"/>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>10-6</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>書籍削除API(DELETE /api/v1/books/{book})</t>
+        </is>
+      </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>10-6-2</t>
+          <t>10-6-1</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>自分が登録した書籍を削除できる</t>
+          <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーが登録した書籍を用意する
-2.そのユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
+          <t>1.認証情報を付与せずDELETE /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>204が返り(レスポンスボディなし)、書籍がDBから削除される</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="n"/>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は削除されない</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiDestroyTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n"/>
@@ -5407,23 +5407,23 @@
       <c r="D158" s="4" t="n"/>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>10-6-3</t>
+          <t>10-6-2</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>書籍を削除すると、関連するデータも一緒に削除される</t>
+          <t>自分が登録した書籍を削除できる</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンルの紐づけ・レビュー・お気に入り・レビューへのいいねを持つ書籍を用意する
-2.所有者のトークンでDELETE /api/v1/books/{book}にアクセスする</t>
+          <t>1.ユーザーが登録した書籍を用意する
+2.そのユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>book_genres・reviews・favorites・review_likesの該当データも削除される</t>
+          <t>204が返り(レスポンスボディなし)、書籍がDBから削除される</t>
         </is>
       </c>
       <c r="I158" s="4" t="n"/>
@@ -5435,129 +5435,129 @@
       <c r="D159" s="4" t="n"/>
       <c r="E159" s="2" t="inlineStr">
         <is>
+          <t>10-6-3</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="inlineStr">
+        <is>
+          <t>書籍を削除すると、関連するデータも一緒に削除される</t>
+        </is>
+      </c>
+      <c r="G159" s="3" t="inlineStr">
+        <is>
+          <t>1.ジャンルの紐づけ・レビュー・お気に入り・レビューへのいいねを持つ書籍を用意する
+2.所有者のトークンでDELETE /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H159" s="3" t="inlineStr">
+        <is>
+          <t>book_genres・reviews・favorites・review_likesの該当データも削除される</t>
+        </is>
+      </c>
+      <c r="I159" s="4" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="n"/>
+      <c r="B160" s="4" t="n"/>
+      <c r="C160" s="4" t="n"/>
+      <c r="D160" s="4" t="n"/>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
           <t>10-6-4</t>
         </is>
       </c>
-      <c r="F159" s="3" t="inlineStr">
+      <c r="F160" s="3" t="inlineStr">
         <is>
           <t>他のユーザーが登録した書籍は削除できない</t>
         </is>
       </c>
-      <c r="G159" s="3" t="inlineStr">
+      <c r="G160" s="3" t="inlineStr">
         <is>
           <t>1.他のユーザーが登録した書籍を用意する
 2.別のユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr">
-        <is>
-          <t>403 Forbiddenが返り、書籍は削除されない</t>
-        </is>
-      </c>
-      <c r="I159" s="4" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="5" t="n"/>
-      <c r="B160" s="5" t="n"/>
-      <c r="C160" s="5" t="n"/>
-      <c r="D160" s="5" t="n"/>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="H160" s="3" t="inlineStr">
+        <is>
+          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は削除されない</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="5" t="n"/>
+      <c r="B161" s="5" t="n"/>
+      <c r="C161" s="5" t="n"/>
+      <c r="D161" s="5" t="n"/>
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>10-6-5</t>
         </is>
       </c>
-      <c r="F160" s="3" t="inlineStr">
+      <c r="F161" s="3" t="inlineStr">
         <is>
           <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
-      <c r="G160" s="3" t="inlineStr">
+      <c r="G161" s="3" t="inlineStr">
         <is>
           <t>1.トークンを付与し、存在しない書籍IDでDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
+      <c r="H161" s="3" t="inlineStr">
         <is>
           <t>404が返り、「指定された書籍が見つかりません」が返る</t>
         </is>
       </c>
-      <c r="I160" s="5" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="6" t="inlineStr">
+      <c r="I161" s="5" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B161" s="6" t="inlineStr">
+      <c r="B162" s="6" t="inlineStr">
         <is>
           <t>検索・フィルタ</t>
         </is>
       </c>
-      <c r="C161" s="6" t="inlineStr">
+      <c r="C162" s="6" t="inlineStr">
         <is>
           <t>11-1</t>
         </is>
       </c>
-      <c r="D161" s="6" t="inlineStr">
+      <c r="D162" s="6" t="inlineStr">
         <is>
           <t>書籍のキーワード検索・ジャンル絞り込み</t>
         </is>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="E162" s="6" t="inlineStr">
         <is>
           <t>11-1-1</t>
         </is>
       </c>
-      <c r="F161" s="7" t="inlineStr">
+      <c r="F162" s="7" t="inlineStr">
         <is>
           <t>タイトルにキーワードを含む書籍が検索結果に表示される</t>
         </is>
       </c>
-      <c r="G161" s="7" t="inlineStr">
+      <c r="G162" s="7" t="inlineStr">
         <is>
           <t>1.タイトルにキーワードを含む書籍を用意する
 2.書籍一覧ページでkeywordにそのキーワードを指定して検索する</t>
         </is>
       </c>
-      <c r="H161" s="7" t="inlineStr">
+      <c r="H162" s="7" t="inlineStr">
         <is>
           <t>該当する書籍が検索結果に表示される</t>
         </is>
       </c>
-      <c r="I161" s="7" t="inlineStr">
+      <c r="I162" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Search/SearchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="4" t="n"/>
-      <c r="B162" s="4" t="n"/>
-      <c r="C162" s="4" t="n"/>
-      <c r="D162" s="4" t="n"/>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>11-1-2</t>
-        </is>
-      </c>
-      <c r="F162" s="7" t="inlineStr">
-        <is>
-          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>1.著者名にキーワードを含む書籍を用意する
-2.同キーワードで検索する</t>
-        </is>
-      </c>
-      <c r="H162" s="7" t="inlineStr">
-        <is>
-          <t>該当する書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="I162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n"/>
@@ -5566,23 +5566,23 @@
       <c r="D163" s="4" t="n"/>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>11-1-3</t>
+          <t>11-1-2</t>
         </is>
       </c>
       <c r="F163" s="7" t="inlineStr">
         <is>
-          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
+          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
         </is>
       </c>
       <c r="G163" s="7" t="inlineStr">
         <is>
-          <t>1.キーワードに一致しない書籍を用意する
-2.検索する</t>
+          <t>1.著者名にキーワードを含む書籍を用意する
+2.同キーワードで検索する</t>
         </is>
       </c>
       <c r="H163" s="7" t="inlineStr">
         <is>
-          <t>その書籍は検索結果に表示されない</t>
+          <t>該当する書籍が検索結果に表示される</t>
         </is>
       </c>
       <c r="I163" s="4" t="n"/>
@@ -5594,22 +5594,23 @@
       <c r="D164" s="4" t="n"/>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>11-1-4</t>
+          <t>11-1-3</t>
         </is>
       </c>
       <c r="F164" s="7" t="inlineStr">
         <is>
-          <t>キーワード未入力の場合は全件が表示される</t>
+          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
         </is>
       </c>
       <c r="G164" s="7" t="inlineStr">
         <is>
-          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
+          <t>1.キーワードに一致しない書籍を用意する
+2.検索する</t>
         </is>
       </c>
       <c r="H164" s="7" t="inlineStr">
         <is>
-          <t>登録されている全ての書籍が表示される</t>
+          <t>その書籍は検索結果に表示されない</t>
         </is>
       </c>
       <c r="I164" s="4" t="n"/>
@@ -5621,23 +5622,22 @@
       <c r="D165" s="4" t="n"/>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>11-1-5</t>
+          <t>11-1-4</t>
         </is>
       </c>
       <c r="F165" s="7" t="inlineStr">
         <is>
-          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
+          <t>キーワード未入力の場合は全件が表示される</t>
         </is>
       </c>
       <c r="G165" s="7" t="inlineStr">
         <is>
-          <t>1.複数ジャンルの書籍を用意する
-2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
+          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
         </is>
       </c>
       <c r="H165" s="7" t="inlineStr">
         <is>
-          <t>指定したジャンルに紐づく書籍のみ表示される</t>
+          <t>登録されている全ての書籍が表示される</t>
         </is>
       </c>
       <c r="I165" s="4" t="n"/>
@@ -5649,128 +5649,128 @@
       <c r="D166" s="4" t="n"/>
       <c r="E166" s="6" t="inlineStr">
         <is>
+          <t>11-1-5</t>
+        </is>
+      </c>
+      <c r="F166" s="7" t="inlineStr">
+        <is>
+          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
+        </is>
+      </c>
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>1.複数ジャンルの書籍を用意する
+2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
+        </is>
+      </c>
+      <c r="H166" s="7" t="inlineStr">
+        <is>
+          <t>指定したジャンルに紐づく書籍のみ表示される</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="n"/>
+      <c r="B167" s="4" t="n"/>
+      <c r="C167" s="4" t="n"/>
+      <c r="D167" s="4" t="n"/>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
           <t>11-1-6</t>
         </is>
       </c>
-      <c r="F166" s="7" t="inlineStr">
+      <c r="F167" s="7" t="inlineStr">
         <is>
           <t>キーワード検索とジャンル絞り込みを組み合わせて使用できる</t>
         </is>
       </c>
-      <c r="G166" s="7" t="inlineStr">
+      <c r="G167" s="7" t="inlineStr">
         <is>
           <t>1.keywordとgenreの両方を指定して一覧を開く</t>
         </is>
       </c>
-      <c r="H166" s="7" t="inlineStr">
+      <c r="H167" s="7" t="inlineStr">
         <is>
           <t>キーワードとジャンルの両方の条件に一致する書籍のみ表示される</t>
         </is>
       </c>
-      <c r="I166" s="4" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="5" t="n"/>
-      <c r="B167" s="5" t="n"/>
-      <c r="C167" s="5" t="n"/>
-      <c r="D167" s="5" t="n"/>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="I167" s="4" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="5" t="n"/>
+      <c r="B168" s="5" t="n"/>
+      <c r="C168" s="5" t="n"/>
+      <c r="D168" s="5" t="n"/>
+      <c r="E168" s="6" t="inlineStr">
         <is>
           <t>11-1-7</t>
         </is>
       </c>
-      <c r="F167" s="7" t="inlineStr">
+      <c r="F168" s="7" t="inlineStr">
         <is>
           <t>検索結果が0件の場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G167" s="7" t="inlineStr">
+      <c r="G168" s="7" t="inlineStr">
         <is>
           <t>1.どの書籍にも一致しないキーワードで検索する</t>
         </is>
       </c>
-      <c r="H167" s="7" t="inlineStr">
+      <c r="H168" s="7" t="inlineStr">
         <is>
           <t>「書籍が登録されていません。」など0件である旨が表示される</t>
         </is>
       </c>
-      <c r="I167" s="5" t="n"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="6" t="inlineStr">
+      <c r="I168" s="5" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B168" s="6" t="inlineStr">
+      <c r="B169" s="6" t="inlineStr">
         <is>
           <t>ソート</t>
         </is>
       </c>
-      <c r="C168" s="6" t="inlineStr">
+      <c r="C169" s="6" t="inlineStr">
         <is>
           <t>12-1</t>
         </is>
       </c>
-      <c r="D168" s="6" t="inlineStr">
+      <c r="D169" s="6" t="inlineStr">
         <is>
           <t>書籍一覧の並び替え</t>
         </is>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="E169" s="6" t="inlineStr">
         <is>
           <t>12-1-1</t>
         </is>
       </c>
-      <c r="F168" s="7" t="inlineStr">
+      <c r="F169" s="7" t="inlineStr">
         <is>
           <t>並び替え未指定時は新着順(登録が新しい順)で表示される</t>
         </is>
       </c>
-      <c r="G168" s="7" t="inlineStr">
+      <c r="G169" s="7" t="inlineStr">
         <is>
           <t>1.複数の書籍を異なる日時で登録する
 2.sortを指定せずに書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H168" s="7" t="inlineStr">
+      <c r="H169" s="7" t="inlineStr">
         <is>
           <t>登録日時が新しい順に表示される</t>
         </is>
       </c>
-      <c r="I168" s="7" t="inlineStr">
+      <c r="I169" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Sort/SortTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="4" t="n"/>
-      <c r="B169" s="4" t="n"/>
-      <c r="C169" s="4" t="n"/>
-      <c r="D169" s="4" t="n"/>
-      <c r="E169" s="6" t="inlineStr">
-        <is>
-          <t>12-1-2</t>
-        </is>
-      </c>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>sort=oldestを指定すると登録が古い順に表示される</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="inlineStr">
-        <is>
-          <t>1.複数の書籍を異なる日時で登録する
-2.sort=oldestを指定して書籍一覧を開く</t>
-        </is>
-      </c>
-      <c r="H169" s="7" t="inlineStr">
-        <is>
-          <t>登録日時が古い順に表示される</t>
-        </is>
-      </c>
-      <c r="I169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n"/>
@@ -5779,23 +5779,23 @@
       <c r="D170" s="4" t="n"/>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>12-1-3</t>
+          <t>12-1-2</t>
         </is>
       </c>
       <c r="F170" s="7" t="inlineStr">
         <is>
-          <t>sort=titleを指定するとタイトルの昇順で表示される</t>
+          <t>sort=oldestを指定すると登録が古い順に表示される</t>
         </is>
       </c>
       <c r="G170" s="7" t="inlineStr">
         <is>
-          <t>1.複数の書籍を用意する
-2.sort=titleを指定して書籍一覧を開く</t>
+          <t>1.複数の書籍を異なる日時で登録する
+2.sort=oldestを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H170" s="7" t="inlineStr">
         <is>
-          <t>タイトルの昇順で表示される</t>
+          <t>登録日時が古い順に表示される</t>
         </is>
       </c>
       <c r="I170" s="4" t="n"/>
@@ -5807,128 +5807,129 @@
       <c r="D171" s="4" t="n"/>
       <c r="E171" s="6" t="inlineStr">
         <is>
+          <t>12-1-3</t>
+        </is>
+      </c>
+      <c r="F171" s="7" t="inlineStr">
+        <is>
+          <t>sort=titleを指定するとタイトルの昇順で表示される</t>
+        </is>
+      </c>
+      <c r="G171" s="7" t="inlineStr">
+        <is>
+          <t>1.複数の書籍を用意する
+2.sort=titleを指定して書籍一覧を開く</t>
+        </is>
+      </c>
+      <c r="H171" s="7" t="inlineStr">
+        <is>
+          <t>タイトルの昇順で表示される</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="n"/>
+      <c r="B172" s="4" t="n"/>
+      <c r="C172" s="4" t="n"/>
+      <c r="D172" s="4" t="n"/>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
           <t>12-1-4</t>
         </is>
       </c>
-      <c r="F171" s="7" t="inlineStr">
+      <c r="F172" s="7" t="inlineStr">
         <is>
           <t>sort=ratingを指定すると平均評価が高い順に表示される</t>
         </is>
       </c>
-      <c r="G171" s="7" t="inlineStr">
+      <c r="G172" s="7" t="inlineStr">
         <is>
           <t>1.平均評価が異なる複数の書籍を用意する
 2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H171" s="7" t="inlineStr">
+      <c r="H172" s="7" t="inlineStr">
         <is>
           <t>平均評価が高い順に表示される</t>
         </is>
       </c>
-      <c r="I171" s="4" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="5" t="n"/>
-      <c r="B172" s="5" t="n"/>
-      <c r="C172" s="5" t="n"/>
-      <c r="D172" s="5" t="n"/>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="I172" s="4" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="5" t="n"/>
+      <c r="B173" s="5" t="n"/>
+      <c r="C173" s="5" t="n"/>
+      <c r="D173" s="5" t="n"/>
+      <c r="E173" s="6" t="inlineStr">
         <is>
           <t>12-1-5</t>
         </is>
       </c>
-      <c r="F172" s="7" t="inlineStr">
+      <c r="F173" s="7" t="inlineStr">
         <is>
           <t>sort=rating指定時、平均評価が同じ書籍は新着順で表示される</t>
         </is>
       </c>
-      <c r="G172" s="7" t="inlineStr">
+      <c r="G173" s="7" t="inlineStr">
         <is>
           <t>1.平均評価が同じ複数の書籍を、異なる登録日時で用意する
 2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H172" s="7" t="inlineStr">
+      <c r="H173" s="7" t="inlineStr">
         <is>
           <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
         </is>
       </c>
-      <c r="I172" s="5" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="6" t="inlineStr">
+      <c r="I173" s="5" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="6" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B173" s="6" t="inlineStr">
+      <c r="B174" s="6" t="inlineStr">
         <is>
           <t>書籍CRUD（認可の詳細テスト）</t>
         </is>
       </c>
-      <c r="C173" s="6" t="inlineStr">
+      <c r="C174" s="6" t="inlineStr">
         <is>
           <t>13-1</t>
         </is>
       </c>
-      <c r="D173" s="6" t="inlineStr">
+      <c r="D174" s="6" t="inlineStr">
         <is>
           <t>BookPolicyの認可ロジック</t>
         </is>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="E174" s="6" t="inlineStr">
         <is>
           <t>13-1-1</t>
         </is>
       </c>
-      <c r="F173" s="7" t="inlineStr">
+      <c r="F174" s="7" t="inlineStr">
         <is>
           <t>ログインユーザーは誰でも書籍を作成できる</t>
         </is>
       </c>
-      <c r="G173" s="7" t="inlineStr">
+      <c r="G174" s="7" t="inlineStr">
         <is>
           <t>1.任意のログインユーザーで BookPolicy::create() を確認する</t>
         </is>
       </c>
-      <c r="H173" s="7" t="inlineStr">
+      <c r="H174" s="7" t="inlineStr">
         <is>
           <t>trueが返り、作成が許可される</t>
         </is>
       </c>
-      <c r="I173" s="7" t="inlineStr">
+      <c r="I174" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/BookAuthorization/BookAuthorizationTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="4" t="n"/>
-      <c r="B174" s="4" t="n"/>
-      <c r="C174" s="4" t="n"/>
-      <c r="D174" s="4" t="n"/>
-      <c r="E174" s="6" t="inlineStr">
-        <is>
-          <t>13-1-2</t>
-        </is>
-      </c>
-      <c r="F174" s="7" t="inlineStr">
-        <is>
-          <t>書籍の登録者本人は更新が許可される</t>
-        </is>
-      </c>
-      <c r="G174" s="7" t="inlineStr">
-        <is>
-          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
-        </is>
-      </c>
-      <c r="H174" s="7" t="inlineStr">
-        <is>
-          <t>trueが返る</t>
-        </is>
-      </c>
-      <c r="I174" s="4" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n"/>
@@ -5937,22 +5938,22 @@
       <c r="D175" s="4" t="n"/>
       <c r="E175" s="6" t="inlineStr">
         <is>
-          <t>13-1-3</t>
+          <t>13-1-2</t>
         </is>
       </c>
       <c r="F175" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者以外は更新が許可されない</t>
+          <t>書籍の登録者本人は更新が許可される</t>
         </is>
       </c>
       <c r="G175" s="7" t="inlineStr">
         <is>
-          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
+          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H175" s="7" t="inlineStr">
         <is>
-          <t>falseが返る</t>
+          <t>trueが返る</t>
         </is>
       </c>
       <c r="I175" s="4" t="n"/>
@@ -5964,22 +5965,22 @@
       <c r="D176" s="4" t="n"/>
       <c r="E176" s="6" t="inlineStr">
         <is>
-          <t>13-1-4</t>
+          <t>13-1-3</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者本人は削除が許可される</t>
+          <t>書籍の登録者以外は更新が許可されない</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
+          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
-          <t>trueが返る</t>
+          <t>falseが返る</t>
         </is>
       </c>
       <c r="I176" s="4" t="n"/>
@@ -5991,153 +5992,153 @@
       <c r="D177" s="4" t="n"/>
       <c r="E177" s="6" t="inlineStr">
         <is>
+          <t>13-1-4</t>
+        </is>
+      </c>
+      <c r="F177" s="7" t="inlineStr">
+        <is>
+          <t>書籍の登録者本人は削除が許可される</t>
+        </is>
+      </c>
+      <c r="G177" s="7" t="inlineStr">
+        <is>
+          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
+        </is>
+      </c>
+      <c r="H177" s="7" t="inlineStr">
+        <is>
+          <t>trueが返る</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="n"/>
+      <c r="B178" s="4" t="n"/>
+      <c r="C178" s="4" t="n"/>
+      <c r="D178" s="4" t="n"/>
+      <c r="E178" s="6" t="inlineStr">
+        <is>
           <t>13-1-5</t>
         </is>
       </c>
-      <c r="F177" s="7" t="inlineStr">
+      <c r="F178" s="7" t="inlineStr">
         <is>
           <t>書籍の登録者以外は削除が許可されない</t>
         </is>
       </c>
-      <c r="G177" s="7" t="inlineStr">
+      <c r="G178" s="7" t="inlineStr">
         <is>
           <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
         </is>
       </c>
-      <c r="H177" s="7" t="inlineStr">
+      <c r="H178" s="7" t="inlineStr">
         <is>
           <t>falseが返る</t>
         </is>
       </c>
-      <c r="I177" s="4" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="5" t="n"/>
-      <c r="B178" s="5" t="n"/>
-      <c r="C178" s="5" t="n"/>
-      <c r="D178" s="5" t="n"/>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="I178" s="4" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="n"/>
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="5" t="n"/>
+      <c r="D179" s="5" t="n"/>
+      <c r="E179" s="6" t="inlineStr">
         <is>
           <t>13-1-6</t>
         </is>
       </c>
-      <c r="F178" s="7" t="inlineStr">
+      <c r="F179" s="7" t="inlineStr">
         <is>
           <t>フォームを介さない直接のPUT/DELETEリクエストでも他人の書籍は操作できない</t>
         </is>
       </c>
-      <c r="G178" s="7" t="inlineStr">
+      <c r="G179" s="7" t="inlineStr">
         <is>
           <t>1.他人が登録した書籍に対して、直接PUT・DELETEリクエストを送信する</t>
         </is>
       </c>
-      <c r="H178" s="7" t="inlineStr">
+      <c r="H179" s="7" t="inlineStr">
         <is>
           <t>いずれも403Forbiddenになり、データは変更されない</t>
         </is>
       </c>
-      <c r="I178" s="5" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="6" t="inlineStr">
+      <c r="I179" s="5" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="5" t="n"/>
+      <c r="B180" s="5" t="n"/>
+      <c r="C180" s="5" t="n"/>
+      <c r="D180" s="5" t="n"/>
+      <c r="E180" s="6" t="inlineStr">
+        <is>
+          <t>13-1-7</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>他人の書籍に対して不正な入力を直接PUTしても、入力エラーではなく403になる</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>1.他人が登録した書籍に対して、タイトルを空にするなど不正な内容で、直接PUTリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H180" s="7" t="inlineStr">
+        <is>
+          <t>バリデーションエラーにはならず、403Forbiddenになる（入力チェックより先に権限が判定される）。データは変更されない</t>
+        </is>
+      </c>
+      <c r="I180" s="5" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B179" s="6" t="inlineStr">
+      <c r="B181" s="6" t="inlineStr">
         <is>
           <t>ISBN検索</t>
         </is>
       </c>
-      <c r="C179" s="6" t="inlineStr">
+      <c r="C181" s="6" t="inlineStr">
         <is>
           <t>14-1</t>
         </is>
       </c>
-      <c r="D179" s="6" t="inlineStr">
+      <c r="D181" s="6" t="inlineStr">
         <is>
           <t>ISBNからの書籍情報取得(外部API連携)</t>
         </is>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="E181" s="6" t="inlineStr">
         <is>
           <t>14-1-1</t>
         </is>
       </c>
-      <c r="F179" s="7" t="inlineStr">
+      <c r="F181" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、ISBN検索エンドポイントにアクセスできない</t>
         </is>
       </c>
-      <c r="G179" s="7" t="inlineStr">
+      <c r="G181" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態でGET /books/isbn/{isbn} にアクセスする</t>
         </is>
       </c>
-      <c r="H179" s="7" t="inlineStr">
+      <c r="H181" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I179" s="7" t="inlineStr">
+      <c r="I181" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Isbn/IsbnSearchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="4" t="n"/>
-      <c r="B180" s="4" t="n"/>
-      <c r="C180" s="4" t="n"/>
-      <c r="D180" s="4" t="n"/>
-      <c r="E180" s="6" t="inlineStr">
-        <is>
-          <t>14-1-2</t>
-        </is>
-      </c>
-      <c r="F180" s="7" t="inlineStr">
-        <is>
-          <t>ISBNが未入力(空文字)の場合、バリデーションエラーが返る</t>
-        </is>
-      </c>
-      <c r="G180" s="7" t="inlineStr">
-        <is>
-          <t>1.ログイン状態でISBN部分を空にしてリクエストする</t>
-        </is>
-      </c>
-      <c r="H180" s="7" t="inlineStr">
-        <is>
-          <t>422が返り、「ISBNを入力してください」が返る</t>
-        </is>
-      </c>
-      <c r="I180" s="4" t="n"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="4" t="n"/>
-      <c r="B181" s="4" t="n"/>
-      <c r="C181" s="4" t="n"/>
-      <c r="D181" s="4" t="n"/>
-      <c r="E181" s="6" t="inlineStr">
-        <is>
-          <t>14-1-3</t>
-        </is>
-      </c>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
-          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
-        </is>
-      </c>
-      <c r="G181" s="7" t="inlineStr">
-        <is>
-          <t>1.13桁でないISBNでリクエストする</t>
-        </is>
-      </c>
-      <c r="H181" s="7" t="inlineStr">
-        <is>
-          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
-        </is>
-      </c>
-      <c r="I181" s="4" t="n"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="n"/>
@@ -6146,22 +6147,22 @@
       <c r="D182" s="4" t="n"/>
       <c r="E182" s="6" t="inlineStr">
         <is>
-          <t>14-1-4</t>
+          <t>14-1-2</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
+          <t>ISBNが未入力(空文字)の場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>1.登録済みのISBNでリクエストする</t>
+          <t>1.ログイン状態でISBN部分を空にしてリクエストする</t>
         </is>
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
+          <t>422が返り、「ISBNを入力してください」が返る</t>
         </is>
       </c>
       <c r="I182" s="4" t="n"/>
@@ -6173,23 +6174,22 @@
       <c r="D183" s="4" t="n"/>
       <c r="E183" s="6" t="inlineStr">
         <is>
-          <t>14-1-5</t>
+          <t>14-1-3</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
+          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
-2.未登録ISBNでリクエストする</t>
+          <t>1.13桁でないISBNでリクエストする</t>
         </is>
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
+          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
         </is>
       </c>
       <c r="I183" s="4" t="n"/>
@@ -6201,155 +6201,156 @@
       <c r="D184" s="4" t="n"/>
       <c r="E184" s="6" t="inlineStr">
         <is>
+          <t>14-1-4</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>1.登録済みのISBNでリクエストする</t>
+        </is>
+      </c>
+      <c r="H184" s="7" t="inlineStr">
+        <is>
+          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
+        </is>
+      </c>
+      <c r="I184" s="4" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="n"/>
+      <c r="B185" s="4" t="n"/>
+      <c r="C185" s="4" t="n"/>
+      <c r="D185" s="4" t="n"/>
+      <c r="E185" s="6" t="inlineStr">
+        <is>
+          <t>14-1-5</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
+2.未登録ISBNでリクエストする</t>
+        </is>
+      </c>
+      <c r="H185" s="7" t="inlineStr">
+        <is>
+          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n"/>
+      <c r="B186" s="4" t="n"/>
+      <c r="C186" s="4" t="n"/>
+      <c r="D186" s="4" t="n"/>
+      <c r="E186" s="6" t="inlineStr">
+        <is>
           <t>14-1-6</t>
         </is>
       </c>
-      <c r="F184" s="7" t="inlineStr">
+      <c r="F186" s="7" t="inlineStr">
         <is>
           <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
         </is>
       </c>
-      <c r="G184" s="7" t="inlineStr">
+      <c r="G186" s="7" t="inlineStr">
         <is>
           <t>1.Http::fake()でitemsが空のレスポンスをモックする
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H184" s="7" t="inlineStr">
+      <c r="H186" s="7" t="inlineStr">
         <is>
           <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
         </is>
       </c>
-      <c r="I184" s="4" t="n"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="5" t="n"/>
-      <c r="B185" s="5" t="n"/>
-      <c r="C185" s="5" t="n"/>
-      <c r="D185" s="5" t="n"/>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="I186" s="4" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="n"/>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="5" t="n"/>
+      <c r="D187" s="5" t="n"/>
+      <c r="E187" s="6" t="inlineStr">
         <is>
           <t>14-1-7</t>
         </is>
       </c>
-      <c r="F185" s="7" t="inlineStr">
+      <c r="F187" s="7" t="inlineStr">
         <is>
           <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
         </is>
       </c>
-      <c r="G185" s="7" t="inlineStr">
+      <c r="G187" s="7" t="inlineStr">
         <is>
           <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H185" s="7" t="inlineStr">
+      <c r="H187" s="7" t="inlineStr">
         <is>
           <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
         </is>
       </c>
-      <c r="I185" s="5" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="6" t="inlineStr">
+      <c r="I187" s="5" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B186" s="6" t="inlineStr">
+      <c r="B188" s="6" t="inlineStr">
         <is>
           <t>マイ読書レポート</t>
         </is>
       </c>
-      <c r="C186" s="6" t="inlineStr">
+      <c r="C188" s="6" t="inlineStr">
         <is>
           <t>15-1</t>
         </is>
       </c>
-      <c r="D186" s="6" t="inlineStr">
+      <c r="D188" s="6" t="inlineStr">
         <is>
           <t>読書統計の表示</t>
         </is>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E188" s="6" t="inlineStr">
         <is>
           <t>15-1-1</t>
         </is>
       </c>
-      <c r="F186" s="7" t="inlineStr">
+      <c r="F188" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
         </is>
       </c>
-      <c r="G186" s="7" t="inlineStr">
+      <c r="G188" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で/reportsを開く</t>
         </is>
       </c>
-      <c r="H186" s="7" t="inlineStr">
+      <c r="H188" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I186" s="7" t="inlineStr">
+      <c r="I188" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Report/ReportTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="4" t="n"/>
-      <c r="B187" s="4" t="n"/>
-      <c r="C187" s="4" t="n"/>
-      <c r="D187" s="4" t="n"/>
-      <c r="E187" s="6" t="inlineStr">
-        <is>
-          <t>15-1-2</t>
-        </is>
-      </c>
-      <c r="F187" s="7" t="inlineStr">
-        <is>
-          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
-        </is>
-      </c>
-      <c r="G187" s="7" t="inlineStr">
-        <is>
-          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
-        </is>
-      </c>
-      <c r="H187" s="7" t="inlineStr">
-        <is>
-          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
-        </is>
-      </c>
-      <c r="I187" s="4" t="n"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="4" t="n"/>
-      <c r="B188" s="4" t="n"/>
-      <c r="C188" s="4" t="n"/>
-      <c r="D188" s="4" t="n"/>
-      <c r="E188" s="6" t="inlineStr">
-        <is>
-          <t>15-1-3</t>
-        </is>
-      </c>
-      <c r="F188" s="7" t="inlineStr">
-        <is>
-          <t>評価分布(★1〜★5)が正しく表示される</t>
-        </is>
-      </c>
-      <c r="G188" s="7" t="inlineStr">
-        <is>
-          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
-        </is>
-      </c>
-      <c r="H188" s="7" t="inlineStr">
-        <is>
-          <t>各評価の件数が実データと一致して表示される</t>
-        </is>
-      </c>
-      <c r="I188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n"/>
@@ -6358,22 +6359,22 @@
       <c r="D189" s="4" t="n"/>
       <c r="E189" s="6" t="inlineStr">
         <is>
-          <t>15-1-4</t>
+          <t>15-1-2</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
+          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
+          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
+          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
         </is>
       </c>
       <c r="I189" s="4" t="n"/>
@@ -6385,285 +6386,283 @@
       <c r="D190" s="4" t="n"/>
       <c r="E190" s="6" t="inlineStr">
         <is>
+          <t>15-1-3</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>評価分布(★1〜★5)が正しく表示される</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
+        </is>
+      </c>
+      <c r="H190" s="7" t="inlineStr">
+        <is>
+          <t>各評価の件数が実データと一致して表示される</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n"/>
+      <c r="B191" s="4" t="n"/>
+      <c r="C191" s="4" t="n"/>
+      <c r="D191" s="4" t="n"/>
+      <c r="E191" s="6" t="inlineStr">
+        <is>
+          <t>15-1-4</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
+        </is>
+      </c>
+      <c r="H191" s="7" t="inlineStr">
+        <is>
+          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
+        </is>
+      </c>
+      <c r="I191" s="4" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="n"/>
+      <c r="B192" s="4" t="n"/>
+      <c r="C192" s="4" t="n"/>
+      <c r="D192" s="4" t="n"/>
+      <c r="E192" s="6" t="inlineStr">
+        <is>
           <t>15-1-5</t>
         </is>
       </c>
-      <c r="F190" s="7" t="inlineStr">
+      <c r="F192" s="7" t="inlineStr">
         <is>
           <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
         </is>
       </c>
-      <c r="G190" s="7" t="inlineStr">
+      <c r="G192" s="7" t="inlineStr">
         <is>
           <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H190" s="7" t="inlineStr">
+      <c r="H192" s="7" t="inlineStr">
         <is>
           <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
         </is>
       </c>
-      <c r="I190" s="4" t="n"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="5" t="n"/>
-      <c r="B191" s="5" t="n"/>
-      <c r="C191" s="5" t="n"/>
-      <c r="D191" s="5" t="n"/>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="I192" s="4" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="n"/>
+      <c r="B193" s="5" t="n"/>
+      <c r="C193" s="5" t="n"/>
+      <c r="D193" s="5" t="n"/>
+      <c r="E193" s="6" t="inlineStr">
         <is>
           <t>15-1-6</t>
         </is>
       </c>
-      <c r="F191" s="7" t="inlineStr">
+      <c r="F193" s="7" t="inlineStr">
         <is>
           <t>レビューを1件も投稿していない場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G191" s="7" t="inlineStr">
+      <c r="G193" s="7" t="inlineStr">
         <is>
           <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H191" s="7" t="inlineStr">
+      <c r="H193" s="7" t="inlineStr">
         <is>
           <t>総レビュー数・読了冊数が0、平均評価が0として表示され、TOP5一覧は空になる</t>
         </is>
       </c>
-      <c r="I191" s="5" t="n"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="6" t="inlineStr">
+      <c r="I193" s="5" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B192" s="6" t="inlineStr">
+      <c r="B194" s="6" t="inlineStr">
         <is>
           <t>Sanctum認証</t>
         </is>
       </c>
-      <c r="C192" s="6" t="inlineStr">
+      <c r="C194" s="6" t="inlineStr">
         <is>
           <t>16-1</t>
         </is>
       </c>
-      <c r="D192" s="6" t="inlineStr">
+      <c r="D194" s="6" t="inlineStr">
         <is>
           <t>APIトークン認証</t>
         </is>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="E194" s="6" t="inlineStr">
         <is>
           <t>16-1-1</t>
         </is>
       </c>
-      <c r="F192" s="7" t="inlineStr">
+      <c r="F194" s="7" t="inlineStr">
         <is>
           <t>有効なpersonal access tokenを付与すると/api/userにアクセスできる</t>
         </is>
       </c>
-      <c r="G192" s="7" t="inlineStr">
+      <c r="G194" s="7" t="inlineStr">
         <is>
           <t>1.$user-&gt;createToken()でトークンを発行する
 2.Authorization: Bearer {token}を付与してGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H192" s="7" t="inlineStr">
+      <c r="H194" s="7" t="inlineStr">
         <is>
           <t>200が返り、対象ユーザーの情報が返る</t>
         </is>
       </c>
-      <c r="I192" s="7" t="inlineStr">
+      <c r="I194" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
         </is>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="4" t="n"/>
-      <c r="B193" s="4" t="n"/>
-      <c r="C193" s="4" t="n"/>
-      <c r="D193" s="4" t="n"/>
-      <c r="E193" s="6" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="4" t="n"/>
+      <c r="B195" s="4" t="n"/>
+      <c r="C195" s="4" t="n"/>
+      <c r="D195" s="4" t="n"/>
+      <c r="E195" s="6" t="inlineStr">
         <is>
           <t>16-1-2</t>
         </is>
       </c>
-      <c r="F193" s="7" t="inlineStr">
+      <c r="F195" s="7" t="inlineStr">
         <is>
           <t>トークンなしでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G193" s="7" t="inlineStr">
+      <c r="G195" s="7" t="inlineStr">
         <is>
           <t>1.Authorizationヘッダーを付与せずにGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H193" s="7" t="inlineStr">
-        <is>
-          <t>401 Unauthorizedが返る</t>
-        </is>
-      </c>
-      <c r="I193" s="4" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="4" t="n"/>
-      <c r="B194" s="4" t="n"/>
-      <c r="C194" s="4" t="n"/>
-      <c r="D194" s="4" t="n"/>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="H195" s="7" t="inlineStr">
+        <is>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
+        </is>
+      </c>
+      <c r="I195" s="4" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="n"/>
+      <c r="B196" s="4" t="n"/>
+      <c r="C196" s="4" t="n"/>
+      <c r="D196" s="4" t="n"/>
+      <c r="E196" s="6" t="inlineStr">
         <is>
           <t>16-1-3</t>
         </is>
       </c>
-      <c r="F194" s="7" t="inlineStr">
+      <c r="F196" s="7" t="inlineStr">
         <is>
           <t>不正な(存在しない)トークンでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G194" s="7" t="inlineStr">
+      <c r="G196" s="7" t="inlineStr">
         <is>
           <t>1.ランダムな文字列をBearerトークンとして付与しGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H194" s="7" t="inlineStr">
-        <is>
-          <t>401 Unauthorizedが返る</t>
-        </is>
-      </c>
-      <c r="I194" s="4" t="n"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="5" t="n"/>
-      <c r="B195" s="5" t="n"/>
-      <c r="C195" s="5" t="n"/>
-      <c r="D195" s="5" t="n"/>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="H196" s="7" t="inlineStr">
+        <is>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="n"/>
+      <c r="B197" s="5" t="n"/>
+      <c r="C197" s="5" t="n"/>
+      <c r="D197" s="5" t="n"/>
+      <c r="E197" s="6" t="inlineStr">
         <is>
           <t>16-1-4</t>
         </is>
       </c>
-      <c r="F195" s="7" t="inlineStr">
+      <c r="F197" s="7" t="inlineStr">
         <is>
           <t>削除済み(失効済み)のトークンでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G195" s="7" t="inlineStr">
+      <c r="G197" s="7" t="inlineStr">
         <is>
           <t>1.発行済みトークンを削除する
 2.そのトークンでGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H195" s="7" t="inlineStr">
-        <is>
-          <t>401 Unauthorizedが返る</t>
-        </is>
-      </c>
-      <c r="I195" s="5" t="n"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="6" t="inlineStr">
+      <c r="H197" s="7" t="inlineStr">
+        <is>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
+        </is>
+      </c>
+      <c r="I197" s="5" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="6" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B196" s="6" t="inlineStr">
+      <c r="B198" s="6" t="inlineStr">
         <is>
           <t>読書計画</t>
         </is>
       </c>
-      <c r="C196" s="6" t="inlineStr">
+      <c r="C198" s="6" t="inlineStr">
         <is>
           <t>17-1</t>
         </is>
       </c>
-      <c r="D196" s="6" t="inlineStr">
+      <c r="D198" s="6" t="inlineStr">
         <is>
           <t>読書計画の作成・一覧・読了・削除</t>
         </is>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="E198" s="6" t="inlineStr">
         <is>
           <t>17-1-1</t>
         </is>
       </c>
-      <c r="F196" s="7" t="inlineStr">
+      <c r="F198" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
         </is>
       </c>
-      <c r="G196" s="7" t="inlineStr">
+      <c r="G198" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H196" s="7" t="inlineStr">
+      <c r="H198" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I196" s="7" t="inlineStr">
+      <c r="I198" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="4" t="n"/>
-      <c r="B197" s="4" t="n"/>
-      <c r="C197" s="4" t="n"/>
-      <c r="D197" s="4" t="n"/>
-      <c r="E197" s="6" t="inlineStr">
-        <is>
-          <t>17-1-2</t>
-        </is>
-      </c>
-      <c r="F197" s="7" t="inlineStr">
-        <is>
-          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
-        </is>
-      </c>
-      <c r="G197" s="7" t="inlineStr">
-        <is>
-          <t>1.自分と他人の読書計画をそれぞれ用意する
-2.読書計画一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H197" s="7" t="inlineStr">
-        <is>
-          <t>自分の計画のみが、target_dateの昇順で表示される</t>
-        </is>
-      </c>
-      <c r="I197" s="4" t="n"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="4" t="n"/>
-      <c r="B198" s="4" t="n"/>
-      <c r="C198" s="4" t="n"/>
-      <c r="D198" s="4" t="n"/>
-      <c r="E198" s="6" t="inlineStr">
-        <is>
-          <t>17-1-3</t>
-        </is>
-      </c>
-      <c r="F198" s="7" t="inlineStr">
-        <is>
-          <t>ステータスで絞り込んで表示できる</t>
-        </is>
-      </c>
-      <c r="G198" s="7" t="inlineStr">
-        <is>
-          <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
-2.statusパラメータを指定して一覧を開く</t>
-        </is>
-      </c>
-      <c r="H198" s="7" t="inlineStr">
-        <is>
-          <t>指定したステータスの計画のみ表示される</t>
-        </is>
-      </c>
-      <c r="I198" s="4" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="4" t="n"/>
@@ -6672,23 +6671,23 @@
       <c r="D199" s="4" t="n"/>
       <c r="E199" s="6" t="inlineStr">
         <is>
-          <t>17-1-4</t>
+          <t>17-1-2</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
+          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
         </is>
       </c>
       <c r="G199" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍について進行中の計画を作成する
-2.計画作成ページを開く</t>
+          <t>1.自分と他人の読書計画をそれぞれ用意する
+2.読書計画一覧ページを開く</t>
         </is>
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>書籍選択肢にその書籍が表示されない</t>
+          <t>自分の計画のみが、target_dateの昇順で表示される</t>
         </is>
       </c>
       <c r="I199" s="4" t="n"/>
@@ -6700,22 +6699,23 @@
       <c r="D200" s="4" t="n"/>
       <c r="E200" s="6" t="inlineStr">
         <is>
-          <t>17-1-5</t>
+          <t>17-1-3</t>
         </is>
       </c>
       <c r="F200" s="7" t="inlineStr">
         <is>
-          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
+          <t>ステータスで絞り込んで表示できる</t>
         </is>
       </c>
       <c r="G200" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
+          <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
+2.statusパラメータを指定して一覧を開く</t>
         </is>
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、計画は作成されない</t>
+          <t>指定したステータスの計画のみ表示される</t>
         </is>
       </c>
       <c r="I200" s="4" t="n"/>
@@ -6727,23 +6727,23 @@
       <c r="D201" s="4" t="n"/>
       <c r="E201" s="6" t="inlineStr">
         <is>
-          <t>17-1-6</t>
+          <t>17-1-4</t>
         </is>
       </c>
       <c r="F201" s="7" t="inlineStr">
         <is>
-          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
+          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
         </is>
       </c>
       <c r="G201" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を読了(完了)状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.ある書籍について進行中の計画を作成する
+2.計画作成ページを開く</t>
         </is>
       </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
-          <t>新しい計画が作成される</t>
+          <t>書籍選択肢にその書籍が表示されない</t>
         </is>
       </c>
       <c r="I201" s="4" t="n"/>
@@ -6755,23 +6755,22 @@
       <c r="D202" s="4" t="n"/>
       <c r="E202" s="6" t="inlineStr">
         <is>
-          <t>17-1-7</t>
+          <t>17-1-5</t>
         </is>
       </c>
       <c r="F202" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
         </is>
       </c>
       <c r="G202" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.期日を入力せずに登録する</t>
+          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H202" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>403Forbiddenになり、計画は作成されない</t>
         </is>
       </c>
       <c r="I202" s="4" t="n"/>
@@ -6783,23 +6782,23 @@
       <c r="D203" s="4" t="n"/>
       <c r="E203" s="6" t="inlineStr">
         <is>
-          <t>17-1-8</t>
+          <t>17-1-6</t>
         </is>
       </c>
       <c r="F203" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
         </is>
       </c>
       <c r="G203" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.過去の日付を期日に指定して登録する</t>
+          <t>1.ある書籍の計画を読了(完了)状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>新しい計画が作成される</t>
         </is>
       </c>
       <c r="I203" s="4" t="n"/>
@@ -6811,23 +6810,23 @@
       <c r="D204" s="4" t="n"/>
       <c r="E204" s="6" t="inlineStr">
         <is>
-          <t>17-1-9</t>
+          <t>17-1-7</t>
         </is>
       </c>
       <c r="F204" s="7" t="inlineStr">
         <is>
-          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G204" s="7" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
-2.書籍・期日を正しく入力して登録する</t>
+2.期日を入力せずに登録する</t>
         </is>
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I204" s="4" t="n"/>
@@ -6839,22 +6838,23 @@
       <c r="D205" s="4" t="n"/>
       <c r="E205" s="6" t="inlineStr">
         <is>
-          <t>17-1-10</t>
+          <t>17-1-8</t>
         </is>
       </c>
       <c r="F205" s="7" t="inlineStr">
         <is>
-          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G205" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画に対して読了操作を行う</t>
+          <t>1.計画作成ページを開く
+2.過去の日付を期日に指定して登録する</t>
         </is>
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I205" s="4" t="n"/>
@@ -6866,22 +6866,23 @@
       <c r="D206" s="4" t="n"/>
       <c r="E206" s="6" t="inlineStr">
         <is>
-          <t>17-1-11</t>
+          <t>17-1-9</t>
         </is>
       </c>
       <c r="F206" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画は読了・削除できない</t>
+          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
         </is>
       </c>
       <c r="G206" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+          <t>1.計画作成ページを開く
+2.書籍・期日を正しく入力して登録する</t>
         </is>
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>いずれも403Forbiddenになる</t>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
         </is>
       </c>
       <c r="I206" s="4" t="n"/>
@@ -6893,22 +6894,22 @@
       <c r="D207" s="4" t="n"/>
       <c r="E207" s="6" t="inlineStr">
         <is>
-          <t>17-1-12</t>
+          <t>17-1-10</t>
         </is>
       </c>
       <c r="F207" s="7" t="inlineStr">
         <is>
-          <t>自分が作成した読書計画は削除できる</t>
+          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
         </is>
       </c>
       <c r="G207" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の削除ボタンを押す</t>
+          <t>1.進行中の計画に対して読了操作を行う</t>
         </is>
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
-          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
+          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
         </is>
       </c>
       <c r="I207" s="4" t="n"/>
@@ -6918,25 +6919,24 @@
       <c r="B208" s="4" t="n"/>
       <c r="C208" s="4" t="n"/>
       <c r="D208" s="4" t="n"/>
-      <c r="E208" s="8" t="inlineStr">
-        <is>
-          <t>17-1-13</t>
-        </is>
-      </c>
-      <c r="F208" s="9" t="inlineStr">
-        <is>
-          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
-        </is>
-      </c>
-      <c r="G208" s="9" t="inlineStr">
-        <is>
-          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
-2.その読書計画を削除する</t>
-        </is>
-      </c>
-      <c r="H208" s="9" t="inlineStr">
-        <is>
-          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
+      <c r="E208" s="6" t="inlineStr">
+        <is>
+          <t>17-1-11</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>他人が作成した読書計画は読了・削除できない</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+        </is>
+      </c>
+      <c r="H208" s="7" t="inlineStr">
+        <is>
+          <t>いずれも403Forbiddenになる</t>
         </is>
       </c>
       <c r="I208" s="4" t="n"/>
@@ -6946,24 +6946,24 @@
       <c r="B209" s="4" t="n"/>
       <c r="C209" s="4" t="n"/>
       <c r="D209" s="4" t="n"/>
-      <c r="E209" s="8" t="inlineStr">
-        <is>
-          <t>17-1-14</t>
-        </is>
-      </c>
-      <c r="F209" s="9" t="inlineStr">
-        <is>
-          <t>ステータスが「完了」の計画は、読了操作を行えない</t>
-        </is>
-      </c>
-      <c r="G209" s="9" t="inlineStr">
-        <is>
-          <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H209" s="9" t="inlineStr">
-        <is>
-          <t>403Forbiddenになり、completed_atは変更されない</t>
+      <c r="E209" s="6" t="inlineStr">
+        <is>
+          <t>17-1-12</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>自分が作成した読書計画は削除できる</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>1.自分が作成した計画の削除ボタンを押す</t>
+        </is>
+      </c>
+      <c r="H209" s="7" t="inlineStr">
+        <is>
+          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
         </is>
       </c>
       <c r="I209" s="4" t="n"/>
@@ -6975,23 +6975,23 @@
       <c r="D210" s="4" t="n"/>
       <c r="E210" s="8" t="inlineStr">
         <is>
-          <t>17-1-15</t>
+          <t>17-1-13</t>
         </is>
       </c>
       <c r="F210" s="9" t="inlineStr">
         <is>
-          <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
+          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
         </is>
       </c>
       <c r="G210" s="9" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を「期限切れ」の状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
+2.その読書計画を削除する</t>
         </is>
       </c>
       <c r="H210" s="9" t="inlineStr">
         <is>
-          <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
+          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
         </is>
       </c>
       <c r="I210" s="4" t="n"/>
@@ -7003,23 +7003,22 @@
       <c r="D211" s="4" t="n"/>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>17-1-16</t>
+          <t>17-1-14</t>
         </is>
       </c>
       <c r="F211" s="9" t="inlineStr">
         <is>
-          <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
+          <t>ステータスが「完了」の計画は、読了操作を行えない</t>
         </is>
       </c>
       <c r="G211" s="9" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍を選択せずに期日を入力して登録する</t>
+          <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
         </is>
       </c>
       <c r="H211" s="9" t="inlineStr">
         <is>
-          <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
+          <t>403Forbiddenになり、completed_atは変更されない</t>
         </is>
       </c>
       <c r="I211" s="4" t="n"/>
@@ -7031,22 +7030,23 @@
       <c r="D212" s="4" t="n"/>
       <c r="E212" s="8" t="inlineStr">
         <is>
-          <t>17-1-17</t>
+          <t>17-1-15</t>
         </is>
       </c>
       <c r="F212" s="9" t="inlineStr">
         <is>
-          <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
+          <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
         </is>
       </c>
       <c r="G212" s="9" t="inlineStr">
         <is>
-          <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.ある書籍の計画を「期限切れ」の状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H212" s="9" t="inlineStr">
         <is>
-          <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
+          <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
         </is>
       </c>
       <c r="I212" s="4" t="n"/>
@@ -7058,22 +7058,23 @@
       <c r="D213" s="4" t="n"/>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>17-1-18</t>
+          <t>17-1-16</t>
         </is>
       </c>
       <c r="F213" s="9" t="inlineStr">
         <is>
-          <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
+          <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G213" s="9" t="inlineStr">
         <is>
-          <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.計画作成ページを開く
+2.書籍を選択せずに期日を入力して登録する</t>
         </is>
       </c>
       <c r="H213" s="9" t="inlineStr">
         <is>
-          <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
+          <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I213" s="4" t="n"/>
@@ -7085,154 +7086,154 @@
       <c r="D214" s="4" t="n"/>
       <c r="E214" s="8" t="inlineStr">
         <is>
+          <t>17-1-17</t>
+        </is>
+      </c>
+      <c r="F214" s="9" t="inlineStr">
+        <is>
+          <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="G214" s="9" t="inlineStr">
+        <is>
+          <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H214" s="9" t="inlineStr">
+        <is>
+          <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I214" s="4" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="n"/>
+      <c r="B215" s="4" t="n"/>
+      <c r="C215" s="4" t="n"/>
+      <c r="D215" s="4" t="n"/>
+      <c r="E215" s="8" t="inlineStr">
+        <is>
+          <t>17-1-18</t>
+        </is>
+      </c>
+      <c r="F215" s="9" t="inlineStr">
+        <is>
+          <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="G215" s="9" t="inlineStr">
+        <is>
+          <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H215" s="9" t="inlineStr">
+        <is>
+          <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I215" s="4" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="n"/>
+      <c r="B216" s="4" t="n"/>
+      <c r="C216" s="4" t="n"/>
+      <c r="D216" s="4" t="n"/>
+      <c r="E216" s="8" t="inlineStr">
+        <is>
           <t>17-1-19</t>
         </is>
       </c>
-      <c r="F214" s="9" t="inlineStr">
+      <c r="F216" s="9" t="inlineStr">
         <is>
           <t>期日が日付形式でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G214" s="9" t="inlineStr">
+      <c r="G216" s="9" t="inlineStr">
         <is>
           <t>1.書籍と、日付として不正な期日(例:abc)を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H214" s="9" t="inlineStr">
+      <c r="H216" s="9" t="inlineStr">
         <is>
           <t>「正しい日付を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I214" s="4" t="n"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="5" t="n"/>
-      <c r="B215" s="5" t="n"/>
-      <c r="C215" s="5" t="n"/>
-      <c r="D215" s="5" t="n"/>
-      <c r="E215" s="8" t="inlineStr">
+      <c r="I216" s="4" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="5" t="n"/>
+      <c r="B217" s="5" t="n"/>
+      <c r="C217" s="5" t="n"/>
+      <c r="D217" s="5" t="n"/>
+      <c r="E217" s="8" t="inlineStr">
         <is>
           <t>17-1-20</t>
         </is>
       </c>
-      <c r="F215" s="9" t="inlineStr">
+      <c r="F217" s="9" t="inlineStr">
         <is>
           <t>期日に今日の日付を指定した場合、計画を作成できる</t>
         </is>
       </c>
-      <c r="G215" s="9" t="inlineStr">
+      <c r="G217" s="9" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
 2.書籍を選択し、期日に今日の日付を指定して登録する</t>
         </is>
       </c>
-      <c r="H215" s="9" t="inlineStr">
+      <c r="H217" s="9" t="inlineStr">
         <is>
           <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される（今日の日付は指定可能）</t>
         </is>
       </c>
-      <c r="I215" s="5" t="n"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="6" t="inlineStr">
+      <c r="I217" s="5" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="6" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B216" s="6" t="inlineStr">
+      <c r="B218" s="6" t="inlineStr">
         <is>
           <t>読書計画（期限変更）</t>
         </is>
       </c>
-      <c r="C216" s="6" t="inlineStr">
+      <c r="C218" s="6" t="inlineStr">
         <is>
           <t>18-1</t>
         </is>
       </c>
-      <c r="D216" s="6" t="inlineStr">
+      <c r="D218" s="6" t="inlineStr">
         <is>
           <t>読書計画の期日変更</t>
         </is>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="E218" s="6" t="inlineStr">
         <is>
           <t>18-1-1</t>
         </is>
       </c>
-      <c r="F216" s="7" t="inlineStr">
+      <c r="F218" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
         </is>
       </c>
-      <c r="G216" s="7" t="inlineStr">
+      <c r="G218" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H216" s="7" t="inlineStr">
+      <c r="H218" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I216" s="7" t="inlineStr">
+      <c r="I218" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="4" t="n"/>
-      <c r="B217" s="4" t="n"/>
-      <c r="C217" s="4" t="n"/>
-      <c r="D217" s="4" t="n"/>
-      <c r="E217" s="6" t="inlineStr">
-        <is>
-          <t>18-1-2</t>
-        </is>
-      </c>
-      <c r="F217" s="7" t="inlineStr">
-        <is>
-          <t>他人が作成した読書計画の期日は変更できない</t>
-        </is>
-      </c>
-      <c r="G217" s="7" t="inlineStr">
-        <is>
-          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H217" s="7" t="inlineStr">
-        <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
-        </is>
-      </c>
-      <c r="I217" s="4" t="n"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="4" t="n"/>
-      <c r="B218" s="4" t="n"/>
-      <c r="C218" s="4" t="n"/>
-      <c r="D218" s="4" t="n"/>
-      <c r="E218" s="6" t="inlineStr">
-        <is>
-          <t>18-1-3</t>
-        </is>
-      </c>
-      <c r="F218" s="7" t="inlineStr">
-        <is>
-          <t>編集画面を開くと現在の期日が初期表示される</t>
-        </is>
-      </c>
-      <c r="G218" s="7" t="inlineStr">
-        <is>
-          <t>1.自分が作成した計画の編集ページを開く</t>
-        </is>
-      </c>
-      <c r="H218" s="7" t="inlineStr">
-        <is>
-          <t>現在登録されている期日が入力欄に表示される</t>
-        </is>
-      </c>
-      <c r="I218" s="4" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="4" t="n"/>
@@ -7241,23 +7242,22 @@
       <c r="D219" s="4" t="n"/>
       <c r="E219" s="6" t="inlineStr">
         <is>
-          <t>18-1-4</t>
+          <t>18-1-2</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>他人が作成した読書計画の期日は変更できない</t>
         </is>
       </c>
       <c r="G219" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.期日を空にして更新する</t>
+          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
       <c r="I219" s="4" t="n"/>
@@ -7269,23 +7269,22 @@
       <c r="D220" s="4" t="n"/>
       <c r="E220" s="6" t="inlineStr">
         <is>
-          <t>18-1-5</t>
+          <t>18-1-3</t>
         </is>
       </c>
       <c r="F220" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>編集画面を開くと現在の期日が初期表示される</t>
         </is>
       </c>
       <c r="G220" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.過去の日付に変更して更新する</t>
+          <t>1.自分が作成した計画の編集ページを開く</t>
         </is>
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>現在登録されている期日が入力欄に表示される</t>
         </is>
       </c>
       <c r="I220" s="4" t="n"/>
@@ -7297,23 +7296,23 @@
       <c r="D221" s="4" t="n"/>
       <c r="E221" s="6" t="inlineStr">
         <is>
-          <t>18-1-6</t>
+          <t>18-1-4</t>
         </is>
       </c>
       <c r="F221" s="7" t="inlineStr">
         <is>
-          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G221" s="7" t="inlineStr">
         <is>
           <t>1.編集ページを開く
-2.未来の日付に正しく変更して更新する</t>
+2.期日を空にして更新する</t>
         </is>
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
-          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I221" s="4" t="n"/>
@@ -7325,23 +7324,23 @@
       <c r="D222" s="4" t="n"/>
       <c r="E222" s="6" t="inlineStr">
         <is>
-          <t>18-1-7</t>
+          <t>18-1-5</t>
         </is>
       </c>
       <c r="F222" s="7" t="inlineStr">
         <is>
-          <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G222" s="7" t="inlineStr">
         <is>
-          <t>1.期日が過去で「進行中」の計画を用意する
-2.読書計画一覧または編集ページを開く</t>
+          <t>1.編集ページを開く
+2.過去の日付に変更して更新する</t>
         </is>
       </c>
       <c r="H222" s="7" t="inlineStr">
         <is>
-          <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I222" s="4" t="n"/>
@@ -7353,22 +7352,23 @@
       <c r="D223" s="4" t="n"/>
       <c r="E223" s="6" t="inlineStr">
         <is>
-          <t>18-1-8</t>
+          <t>18-1-6</t>
         </is>
       </c>
       <c r="F223" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は期日を変更できない</t>
+          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
         </is>
       </c>
       <c r="G223" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
+          <t>1.編集ページを開く
+2.未来の日付に正しく変更して更新する</t>
         </is>
       </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
+          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
         </is>
       </c>
       <c r="I223" s="4" t="n"/>
@@ -7380,22 +7380,23 @@
       <c r="D224" s="4" t="n"/>
       <c r="E224" s="6" t="inlineStr">
         <is>
-          <t>18-1-9</t>
+          <t>18-1-7</t>
         </is>
       </c>
       <c r="F224" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
+          <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
         </is>
       </c>
       <c r="G224" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
+          <t>1.期日が過去で「進行中」の計画を用意する
+2.読書計画一覧または編集ページを開く</t>
         </is>
       </c>
       <c r="H224" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、編集ページは表示されない</t>
+          <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
         </is>
       </c>
       <c r="I224" s="4" t="n"/>
@@ -7407,158 +7408,156 @@
       <c r="D225" s="4" t="n"/>
       <c r="E225" s="6" t="inlineStr">
         <is>
+          <t>18-1-8</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」の計画は期日を変更できない</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H225" s="7" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、期日は変更されない</t>
+        </is>
+      </c>
+      <c r="I225" s="4" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="n"/>
+      <c r="B226" s="4" t="n"/>
+      <c r="C226" s="4" t="n"/>
+      <c r="D226" s="4" t="n"/>
+      <c r="E226" s="6" t="inlineStr">
+        <is>
+          <t>18-1-9</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr">
+        <is>
+          <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
+        </is>
+      </c>
+      <c r="H226" s="7" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、編集ページは表示されない</t>
+        </is>
+      </c>
+      <c r="I226" s="4" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="n"/>
+      <c r="B227" s="4" t="n"/>
+      <c r="C227" s="4" t="n"/>
+      <c r="D227" s="4" t="n"/>
+      <c r="E227" s="6" t="inlineStr">
+        <is>
           <t>18-1-10</t>
         </is>
       </c>
-      <c r="F225" s="7" t="inlineStr">
+      <c r="F227" s="7" t="inlineStr">
         <is>
           <t>他人が作成した読書計画の編集ページにはアクセスできない</t>
         </is>
       </c>
-      <c r="G225" s="7" t="inlineStr">
+      <c r="G227" s="7" t="inlineStr">
         <is>
           <t>1.他人が作成した計画の編集ページのURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H225" s="7" t="inlineStr">
+      <c r="H227" s="7" t="inlineStr">
         <is>
           <t>403Forbiddenになり、編集ページは表示されない</t>
         </is>
       </c>
-      <c r="I225" s="4" t="n"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="5" t="n"/>
-      <c r="B226" s="5" t="n"/>
-      <c r="C226" s="5" t="n"/>
-      <c r="D226" s="5" t="n"/>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="I227" s="4" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="n"/>
+      <c r="B228" s="5" t="n"/>
+      <c r="C228" s="5" t="n"/>
+      <c r="D228" s="5" t="n"/>
+      <c r="E228" s="6" t="inlineStr">
         <is>
           <t>18-1-11</t>
         </is>
       </c>
-      <c r="F226" s="7" t="inlineStr">
+      <c r="F228" s="7" t="inlineStr">
         <is>
           <t>同じ書籍に「進行中」の計画がある場合、「期限切れ」の計画は編集・更新できない</t>
         </is>
       </c>
-      <c r="G226" s="7" t="inlineStr">
+      <c r="G228" s="7" t="inlineStr">
         <is>
           <t>1.同じ書籍について、「期限切れ」の計画と「進行中」の計画をそれぞれ用意する
 2.「期限切れ」の計画の編集ページのURLに直接アクセスする
 3.「期限切れ」の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
-      <c r="H226" s="7" t="inlineStr">
+      <c r="H228" s="7" t="inlineStr">
         <is>
           <t>いずれも403Forbiddenになり、「期限切れ」の計画のステータス・期日は変更されない（同じ書籍の「進行中」の計画が2件になることを防ぐ）</t>
         </is>
       </c>
-      <c r="I226" s="5" t="n"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="6" t="inlineStr">
+      <c r="I228" s="5" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B227" s="6" t="inlineStr">
+      <c r="B229" s="6" t="inlineStr">
         <is>
           <t>リマインダーバッチ</t>
         </is>
       </c>
-      <c r="C227" s="6" t="inlineStr">
+      <c r="C229" s="6" t="inlineStr">
         <is>
           <t>19-1</t>
         </is>
       </c>
-      <c r="D227" s="6" t="inlineStr">
+      <c r="D229" s="6" t="inlineStr">
         <is>
           <t>日次バッチ(reading-plans:daily)によるリマインダー通知</t>
         </is>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="E229" s="6" t="inlineStr">
         <is>
           <t>19-1-1</t>
         </is>
       </c>
-      <c r="F227" s="7" t="inlineStr">
+      <c r="F229" s="7" t="inlineStr">
         <is>
           <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
         </is>
       </c>
-      <c r="G227" s="7" t="inlineStr">
+      <c r="G229" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日後・ステータス進行中の計画を用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
-      <c r="H227" s="7" t="inlineStr">
+      <c r="H229" s="7" t="inlineStr">
         <is>
           <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_before)・title(「読書期限のお知らせ」)・body(「「(書籍名)」の読書期限まであと3日です。」)が含まれる</t>
         </is>
       </c>
-      <c r="I227" s="7" t="inlineStr">
+      <c r="I229" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="4" t="n"/>
-      <c r="B228" s="4" t="n"/>
-      <c r="C228" s="4" t="n"/>
-      <c r="D228" s="4" t="n"/>
-      <c r="E228" s="6" t="inlineStr">
-        <is>
-          <t>19-1-2</t>
-        </is>
-      </c>
-      <c r="F228" s="7" t="inlineStr">
-        <is>
-          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
-        </is>
-      </c>
-      <c r="G228" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが本日・ステータス進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H228" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される。通知のdataには、plan_id・book_title・timing(on_due_date)・title(「読書期限当日のお知らせ」)・body(「「(書籍名)」の読書期限は本日までです。」)が含まれる</t>
-        </is>
-      </c>
-      <c r="I228" s="4" t="n"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="4" t="n"/>
-      <c r="B229" s="4" t="n"/>
-      <c r="C229" s="4" t="n"/>
-      <c r="D229" s="4" t="n"/>
-      <c r="E229" s="6" t="inlineStr">
-        <is>
-          <t>19-1-3</t>
-        </is>
-      </c>
-      <c r="F229" s="7" t="inlineStr">
-        <is>
-          <t>期限切れから3日後の計画に再エンゲージメント通知が送信される</t>
-        </is>
-      </c>
-      <c r="G229" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが3日前・ステータス期限切れの計画を用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H229" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
-        </is>
-      </c>
-      <c r="I229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="4" t="n"/>
@@ -7567,479 +7566,479 @@
       <c r="D230" s="4" t="n"/>
       <c r="E230" s="6" t="inlineStr">
         <is>
+          <t>19-1-2</t>
+        </is>
+      </c>
+      <c r="F230" s="7" t="inlineStr">
+        <is>
+          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが本日・ステータス進行中の計画を用意する
+2.reading-plans:dailyを実行する</t>
+        </is>
+      </c>
+      <c r="H230" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される。通知のdataには、plan_id・book_title・timing(on_due_date)・title(「読書期限当日のお知らせ」)・body(「「(書籍名)」の読書期限は本日までです。」)が含まれる</t>
+        </is>
+      </c>
+      <c r="I230" s="4" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="n"/>
+      <c r="B231" s="4" t="n"/>
+      <c r="C231" s="4" t="n"/>
+      <c r="D231" s="4" t="n"/>
+      <c r="E231" s="6" t="inlineStr">
+        <is>
+          <t>19-1-3</t>
+        </is>
+      </c>
+      <c r="F231" s="7" t="inlineStr">
+        <is>
+          <t>期限切れから3日後の計画に再エンゲージメント通知が送信される</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日前・ステータス期限切れの計画を用意する
+2.reading-plans:dailyを実行する</t>
+        </is>
+      </c>
+      <c r="H231" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
+        </is>
+      </c>
+      <c r="I231" s="4" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="n"/>
+      <c r="B232" s="4" t="n"/>
+      <c r="C232" s="4" t="n"/>
+      <c r="D232" s="4" t="n"/>
+      <c r="E232" s="6" t="inlineStr">
+        <is>
           <t>19-1-4</t>
         </is>
       </c>
-      <c r="F230" s="7" t="inlineStr">
+      <c r="F232" s="7" t="inlineStr">
         <is>
           <t>いずれの条件にも該当しない計画には通知が送信されない</t>
         </is>
       </c>
-      <c r="G230" s="7" t="inlineStr">
+      <c r="G232" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H230" s="7" t="inlineStr">
+      <c r="H232" s="7" t="inlineStr">
         <is>
           <t>その計画のユーザーに通知が送信されない</t>
         </is>
       </c>
-      <c r="I230" s="4" t="n"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="5" t="n"/>
-      <c r="B231" s="5" t="n"/>
-      <c r="C231" s="5" t="n"/>
-      <c r="D231" s="5" t="n"/>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="I232" s="4" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="n"/>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="5" t="n"/>
+      <c r="D233" s="5" t="n"/>
+      <c r="E233" s="6" t="inlineStr">
         <is>
           <t>19-1-5</t>
         </is>
       </c>
-      <c r="F231" s="7" t="inlineStr">
+      <c r="F233" s="7" t="inlineStr">
         <is>
           <t>ステータスが「完了」の計画には、期日の条件に合っていても通知が送信されない</t>
         </is>
       </c>
-      <c r="G231" s="7" t="inlineStr">
+      <c r="G233" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日後・本日・3日前で、ステータスが完了の計画をそれぞれ用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
-      <c r="H231" s="7" t="inlineStr">
+      <c r="H233" s="7" t="inlineStr">
         <is>
           <t>いずれの計画のユーザーにも通知が送信されない</t>
         </is>
       </c>
-      <c r="I231" s="5" t="n"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="6" t="inlineStr">
+      <c r="I233" s="5" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B232" s="6" t="inlineStr">
+      <c r="B234" s="6" t="inlineStr">
         <is>
           <t>自動失効バッチ</t>
         </is>
       </c>
-      <c r="C232" s="6" t="inlineStr">
+      <c r="C234" s="6" t="inlineStr">
         <is>
           <t>20-1</t>
         </is>
       </c>
-      <c r="D232" s="6" t="inlineStr">
+      <c r="D234" s="6" t="inlineStr">
         <is>
           <t>日次バッチ(reading-plans:daily)による自動失効処理</t>
         </is>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="E234" s="6" t="inlineStr">
         <is>
           <t>20-1-1</t>
         </is>
       </c>
-      <c r="F232" s="7" t="inlineStr">
+      <c r="F234" s="7" t="inlineStr">
         <is>
           <t>期日を過ぎた「進行中」の計画が「期限切れ」に更新される</t>
         </is>
       </c>
-      <c r="G232" s="7" t="inlineStr">
+      <c r="G234" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが過去・ステータス進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H232" s="7" t="inlineStr">
+      <c r="H234" s="7" t="inlineStr">
         <is>
           <t>対象の計画のstatusが「期限切れ」に更新される</t>
         </is>
       </c>
-      <c r="I232" s="7" t="inlineStr">
+      <c r="I234" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="4" t="n"/>
-      <c r="B233" s="4" t="n"/>
-      <c r="C233" s="4" t="n"/>
-      <c r="D233" s="4" t="n"/>
-      <c r="E233" s="6" t="inlineStr">
-        <is>
-          <t>20-1-2</t>
-        </is>
-      </c>
-      <c r="F233" s="7" t="inlineStr">
-        <is>
-          <t>期日が今日以降の「進行中」の計画は失効しない</t>
-        </is>
-      </c>
-      <c r="G233" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H233" s="7" t="inlineStr">
-        <is>
-          <t>その計画のstatusは「進行中」のまま変化しない</t>
-        </is>
-      </c>
-      <c r="I233" s="4" t="n"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="4" t="n"/>
-      <c r="B234" s="4" t="n"/>
-      <c r="C234" s="4" t="n"/>
-      <c r="D234" s="4" t="n"/>
-      <c r="E234" s="6" t="inlineStr">
-        <is>
-          <t>20-1-3</t>
-        </is>
-      </c>
-      <c r="F234" s="7" t="inlineStr">
-        <is>
-          <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
-        </is>
-      </c>
-      <c r="G234" s="7" t="inlineStr">
-        <is>
-          <t>1.完了済み・期限切れの計画をそれぞれ用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H234" s="7" t="inlineStr">
-        <is>
-          <t>いずれの計画もstatusが変化しない</t>
-        </is>
-      </c>
-      <c r="I234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="n"/>
       <c r="B235" s="4" t="n"/>
-      <c r="C235" s="5" t="n"/>
-      <c r="D235" s="5" t="n"/>
+      <c r="C235" s="4" t="n"/>
+      <c r="D235" s="4" t="n"/>
       <c r="E235" s="6" t="inlineStr">
         <is>
-          <t>20-1-4</t>
+          <t>20-1-2</t>
         </is>
       </c>
       <c r="F235" s="7" t="inlineStr">
         <is>
-          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+          <t>期日が今日以降の「進行中」の計画は失効しない</t>
         </is>
       </c>
       <c r="G235" s="7" t="inlineStr">
         <is>
-          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
-2.DBを直接確認する</t>
+          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H235" s="7" t="inlineStr">
         <is>
-          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
-        </is>
-      </c>
-      <c r="I235" s="5" t="n"/>
+          <t>その計画のstatusは「進行中」のまま変化しない</t>
+        </is>
+      </c>
+      <c r="I235" s="4" t="n"/>
     </row>
     <row r="236">
       <c r="A236" s="4" t="n"/>
       <c r="B236" s="4" t="n"/>
-      <c r="C236" s="6" t="inlineStr">
-        <is>
-          <t>20-2</t>
-        </is>
-      </c>
-      <c r="D236" s="6" t="inlineStr">
-        <is>
-          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
-        </is>
-      </c>
+      <c r="C236" s="4" t="n"/>
+      <c r="D236" s="4" t="n"/>
       <c r="E236" s="6" t="inlineStr">
         <is>
-          <t>20-2-1</t>
+          <t>20-1-3</t>
         </is>
       </c>
       <c r="F236" s="7" t="inlineStr">
         <is>
-          <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
+          <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
         </is>
       </c>
       <c r="G236" s="7" t="inlineStr">
         <is>
-          <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+          <t>1.完了済み・期限切れの計画をそれぞれ用意する
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H236" s="7" t="inlineStr">
         <is>
-          <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I236" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
-        </is>
-      </c>
+          <t>いずれの計画もstatusが変化しない</t>
+        </is>
+      </c>
+      <c r="I236" s="4" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="4" t="n"/>
       <c r="B237" s="4" t="n"/>
-      <c r="C237" s="4" t="n"/>
-      <c r="D237" s="4" t="n"/>
+      <c r="C237" s="5" t="n"/>
+      <c r="D237" s="5" t="n"/>
       <c r="E237" s="6" t="inlineStr">
         <is>
+          <t>20-1-4</t>
+        </is>
+      </c>
+      <c r="F237" s="7" t="inlineStr">
+        <is>
+          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+        </is>
+      </c>
+      <c r="G237" s="7" t="inlineStr">
+        <is>
+          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
+2.DBを直接確認する</t>
+        </is>
+      </c>
+      <c r="H237" s="7" t="inlineStr">
+        <is>
+          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
+        </is>
+      </c>
+      <c r="I237" s="5" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="n"/>
+      <c r="B238" s="4" t="n"/>
+      <c r="C238" s="6" t="inlineStr">
+        <is>
+          <t>20-2</t>
+        </is>
+      </c>
+      <c r="D238" s="6" t="inlineStr">
+        <is>
+          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
+        </is>
+      </c>
+      <c r="E238" s="6" t="inlineStr">
+        <is>
+          <t>20-2-1</t>
+        </is>
+      </c>
+      <c r="F238" s="7" t="inlineStr">
+        <is>
+          <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="inlineStr">
+        <is>
+          <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+        </is>
+      </c>
+      <c r="H238" s="7" t="inlineStr">
+        <is>
+          <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I238" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="n"/>
+      <c r="B239" s="4" t="n"/>
+      <c r="C239" s="4" t="n"/>
+      <c r="D239" s="4" t="n"/>
+      <c r="E239" s="6" t="inlineStr">
+        <is>
           <t>20-2-2</t>
         </is>
       </c>
-      <c r="F237" s="7" t="inlineStr">
+      <c r="F239" s="7" t="inlineStr">
         <is>
           <t>期限切れへの更新が、通知対象の抽出より先に行われる</t>
         </is>
       </c>
-      <c r="G237" s="7" t="inlineStr">
+      <c r="G239" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日前で、ステータスが「進行中」のまま(未更新)の計画を用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
-      <c r="H237" s="7" t="inlineStr">
+      <c r="H239" s="7" t="inlineStr">
         <is>
           <t>計画のstatusが「期限切れ」に更新され、そのユーザーに再エンゲージメント(re_engagement)通知が送信される</t>
         </is>
       </c>
-      <c r="I237" s="4" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="5" t="n"/>
-      <c r="B238" s="5" t="n"/>
-      <c r="C238" s="5" t="n"/>
-      <c r="D238" s="5" t="n"/>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="I239" s="4" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="n"/>
+      <c r="B240" s="5" t="n"/>
+      <c r="C240" s="5" t="n"/>
+      <c r="D240" s="5" t="n"/>
+      <c r="E240" s="6" t="inlineStr">
         <is>
           <t>20-2-3</t>
         </is>
       </c>
-      <c r="F238" s="7" t="inlineStr">
+      <c r="F240" s="7" t="inlineStr">
         <is>
           <t>reading-plans:dailyが毎日20:00に実行されるようスケジュールされている</t>
         </is>
       </c>
-      <c r="G238" s="7" t="inlineStr">
+      <c r="G240" s="7" t="inlineStr">
         <is>
           <t>1.アプリケーションのスケジュール(Illuminate\Console\Scheduling\Schedule)から、登録済みのイベントを取得する</t>
         </is>
       </c>
-      <c r="H238" s="7" t="inlineStr">
+      <c r="H240" s="7" t="inlineStr">
         <is>
           <t>reading-plans:dailyのイベントが登録されており、cron式が毎日20:00(0 20 * * *)になっている</t>
         </is>
       </c>
-      <c r="I238" s="5" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="8" t="inlineStr">
+      <c r="I240" s="5" t="n"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="8" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B239" s="8" t="inlineStr">
+      <c r="B241" s="8" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="C239" s="8" t="inlineStr">
+      <c r="C241" s="8" t="inlineStr">
         <is>
           <t>21-1</t>
         </is>
       </c>
-      <c r="D239" s="8" t="inlineStr">
+      <c r="D241" s="8" t="inlineStr">
         <is>
           <t>通知の既読化</t>
         </is>
       </c>
-      <c r="E239" s="8" t="inlineStr">
+      <c r="E241" s="8" t="inlineStr">
         <is>
           <t>21-1-1</t>
         </is>
       </c>
-      <c r="F239" s="9" t="inlineStr">
+      <c r="F241" s="9" t="inlineStr">
         <is>
           <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
         </is>
       </c>
-      <c r="G239" s="9" t="inlineStr">
+      <c r="G241" s="9" t="inlineStr">
         <is>
           <t>1.未ログイン状態でPATCH /notifications/{id} に直接リクエストを送信する</t>
         </is>
       </c>
-      <c r="H239" s="9" t="inlineStr">
+      <c r="H241" s="9" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
         </is>
       </c>
-      <c r="I239" s="9" t="inlineStr">
+      <c r="I241" s="9" t="inlineStr">
         <is>
           <t>tests/Feature/Notification/NotificationTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="4" t="n"/>
-      <c r="B240" s="4" t="n"/>
-      <c r="C240" s="4" t="n"/>
-      <c r="D240" s="4" t="n"/>
-      <c r="E240" s="8" t="inlineStr">
-        <is>
-          <t>21-1-2</t>
-        </is>
-      </c>
-      <c r="F240" s="9" t="inlineStr">
-        <is>
-          <t>自分の通知を既読にできる</t>
-        </is>
-      </c>
-      <c r="G240" s="9" t="inlineStr">
-        <is>
-          <t>1.自分宛ての未読通知を用意する
-2.その通知に対してPATCH /notifications/{id} を送信する</t>
-        </is>
-      </c>
-      <c r="H240" s="9" t="inlineStr">
-        <is>
-          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
-        </is>
-      </c>
-      <c r="I240" s="4" t="n"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="4" t="n"/>
-      <c r="B241" s="4" t="n"/>
-      <c r="C241" s="5" t="n"/>
-      <c r="D241" s="5" t="n"/>
-      <c r="E241" s="8" t="inlineStr">
-        <is>
-          <t>21-1-3</t>
-        </is>
-      </c>
-      <c r="F241" s="9" t="inlineStr">
-        <is>
-          <t>他ユーザーの通知は既読にできない</t>
-        </is>
-      </c>
-      <c r="G241" s="9" t="inlineStr">
-        <is>
-          <t>1.他ユーザー宛ての通知を用意する
-2.そのIDに対してPATCH /notifications/{id} を送信する</t>
-        </is>
-      </c>
-      <c r="H241" s="9" t="inlineStr">
-        <is>
-          <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
-        </is>
-      </c>
-      <c r="I241" s="5" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="4" t="n"/>
       <c r="B242" s="4" t="n"/>
-      <c r="C242" s="8" t="inlineStr">
-        <is>
-          <t>21-2</t>
-        </is>
-      </c>
-      <c r="D242" s="8" t="inlineStr">
-        <is>
-          <t>通知一覧</t>
-        </is>
-      </c>
+      <c r="C242" s="4" t="n"/>
+      <c r="D242" s="4" t="n"/>
       <c r="E242" s="8" t="inlineStr">
         <is>
-          <t>21-2-1</t>
+          <t>21-1-2</t>
         </is>
       </c>
       <c r="F242" s="9" t="inlineStr">
         <is>
-          <t>未ログインの場合、通知一覧にアクセスできない</t>
+          <t>自分の通知を既読にできる</t>
         </is>
       </c>
       <c r="G242" s="9" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
+          <t>1.自分宛ての未読通知を用意する
+2.その通知に対してPATCH /notifications/{id} を送信する</t>
         </is>
       </c>
       <c r="H242" s="9" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I242" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationIndexTest.php</t>
-        </is>
-      </c>
+          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
+        </is>
+      </c>
+      <c r="I242" s="4" t="n"/>
     </row>
     <row r="243">
       <c r="A243" s="4" t="n"/>
       <c r="B243" s="4" t="n"/>
-      <c r="C243" s="4" t="n"/>
-      <c r="D243" s="4" t="n"/>
+      <c r="C243" s="5" t="n"/>
+      <c r="D243" s="5" t="n"/>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>21-2-2</t>
+          <t>21-1-3</t>
         </is>
       </c>
       <c r="F243" s="9" t="inlineStr">
         <is>
-          <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
+          <t>他ユーザーの通知は既読にできない</t>
         </is>
       </c>
       <c r="G243" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
-2.通知一覧ページを開く</t>
+          <t>1.他ユーザー宛ての通知を用意する
+2.そのIDに対してPATCH /notifications/{id} を送信する</t>
         </is>
       </c>
       <c r="H243" s="9" t="inlineStr">
         <is>
-          <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
-        </is>
-      </c>
-      <c r="I243" s="4" t="n"/>
+          <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
+        </is>
+      </c>
+      <c r="I243" s="5" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="4" t="n"/>
       <c r="B244" s="4" t="n"/>
-      <c r="C244" s="4" t="n"/>
-      <c r="D244" s="4" t="n"/>
+      <c r="C244" s="8" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="D244" s="8" t="inlineStr">
+        <is>
+          <t>通知一覧</t>
+        </is>
+      </c>
       <c r="E244" s="8" t="inlineStr">
         <is>
-          <t>21-2-3</t>
+          <t>21-2-1</t>
         </is>
       </c>
       <c r="F244" s="9" t="inlineStr">
         <is>
-          <t>通知が1件もない場合の表示を確認する</t>
+          <t>未ログインの場合、通知一覧にアクセスできない</t>
         </is>
       </c>
       <c r="G244" s="9" t="inlineStr">
         <is>
-          <t>1.通知が1件もないユーザーでログインする
-2.通知一覧ページを開く</t>
+          <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H244" s="9" t="inlineStr">
         <is>
-          <t>「通知はありません。」と表示される</t>
-        </is>
-      </c>
-      <c r="I244" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I244" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationIndexTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="4" t="n"/>
@@ -8048,23 +8047,23 @@
       <c r="D245" s="4" t="n"/>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>21-2-4</t>
+          <t>21-2-2</t>
         </is>
       </c>
       <c r="F245" s="9" t="inlineStr">
         <is>
-          <t>通知のタイトル・本文が表示される</t>
+          <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
         </is>
       </c>
       <c r="G245" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
+          <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H245" s="9" t="inlineStr">
         <is>
-          <t>通知のtitleとbodyが一覧に表示される</t>
+          <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
         </is>
       </c>
       <c r="I245" s="4" t="n"/>
@@ -8072,138 +8071,194 @@
     <row r="246">
       <c r="A246" s="4" t="n"/>
       <c r="B246" s="4" t="n"/>
-      <c r="C246" s="5" t="n"/>
-      <c r="D246" s="5" t="n"/>
+      <c r="C246" s="4" t="n"/>
+      <c r="D246" s="4" t="n"/>
       <c r="E246" s="8" t="inlineStr">
         <is>
-          <t>21-2-5</t>
+          <t>21-2-3</t>
         </is>
       </c>
       <c r="F246" s="9" t="inlineStr">
         <is>
-          <t>未読と既読で表示が異なる</t>
+          <t>通知が1件もない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G246" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
+          <t>1.通知が1件もないユーザーでログインする
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H246" s="9" t="inlineStr">
         <is>
-          <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
-        </is>
-      </c>
-      <c r="I246" s="5" t="n"/>
+          <t>「通知はありません。」と表示される</t>
+        </is>
+      </c>
+      <c r="I246" s="4" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="n"/>
       <c r="B247" s="4" t="n"/>
-      <c r="C247" s="8" t="inlineStr">
-        <is>
-          <t>21-3</t>
-        </is>
-      </c>
-      <c r="D247" s="8" t="inlineStr">
-        <is>
-          <t>ヘッダーの未読件数</t>
-        </is>
-      </c>
+      <c r="C247" s="4" t="n"/>
+      <c r="D247" s="4" t="n"/>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>21-3-1</t>
+          <t>21-2-4</t>
         </is>
       </c>
       <c r="F247" s="9" t="inlineStr">
         <is>
-          <t>ヘッダーのベルアイコンに未読件数が表示される</t>
+          <t>通知のタイトル・本文が表示される</t>
         </is>
       </c>
       <c r="G247" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
+          <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
+2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H247" s="9" t="inlineStr">
         <is>
-          <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
-        </is>
-      </c>
-      <c r="I247" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
-        </is>
-      </c>
+          <t>通知のtitleとbodyが一覧に表示される</t>
+        </is>
+      </c>
+      <c r="I247" s="4" t="n"/>
     </row>
     <row r="248">
       <c r="A248" s="4" t="n"/>
       <c r="B248" s="4" t="n"/>
-      <c r="C248" s="4" t="n"/>
-      <c r="D248" s="4" t="n"/>
+      <c r="C248" s="5" t="n"/>
+      <c r="D248" s="5" t="n"/>
       <c r="E248" s="8" t="inlineStr">
         <is>
+          <t>21-2-5</t>
+        </is>
+      </c>
+      <c r="F248" s="9" t="inlineStr">
+        <is>
+          <t>未読と既読で表示が異なる</t>
+        </is>
+      </c>
+      <c r="G248" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
+2.通知一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H248" s="9" t="inlineStr">
+        <is>
+          <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
+        </is>
+      </c>
+      <c r="I248" s="5" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="n"/>
+      <c r="B249" s="4" t="n"/>
+      <c r="C249" s="8" t="inlineStr">
+        <is>
+          <t>21-3</t>
+        </is>
+      </c>
+      <c r="D249" s="8" t="inlineStr">
+        <is>
+          <t>ヘッダーの未読件数</t>
+        </is>
+      </c>
+      <c r="E249" s="8" t="inlineStr">
+        <is>
+          <t>21-3-1</t>
+        </is>
+      </c>
+      <c r="F249" s="9" t="inlineStr">
+        <is>
+          <t>ヘッダーのベルアイコンに未読件数が表示される</t>
+        </is>
+      </c>
+      <c r="G249" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
+        </is>
+      </c>
+      <c r="H249" s="9" t="inlineStr">
+        <is>
+          <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
+        </is>
+      </c>
+      <c r="I249" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="n"/>
+      <c r="B250" s="4" t="n"/>
+      <c r="C250" s="4" t="n"/>
+      <c r="D250" s="4" t="n"/>
+      <c r="E250" s="8" t="inlineStr">
+        <is>
           <t>21-3-2</t>
         </is>
       </c>
-      <c r="F248" s="9" t="inlineStr">
+      <c r="F250" s="9" t="inlineStr">
         <is>
           <t>通知を既読にすると、ヘッダーの未読件数が減る</t>
         </is>
       </c>
-      <c r="G248" s="9" t="inlineStr">
+      <c r="G250" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知を複数件用意する
 2.そのうち1件にPATCH /notifications/{id} を送信して既読にする
 3.画面を開き直す</t>
         </is>
       </c>
-      <c r="H248" s="9" t="inlineStr">
+      <c r="H250" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数が、既読にした1件分だけ減る</t>
         </is>
       </c>
-      <c r="I248" s="4" t="n"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="5" t="n"/>
-      <c r="B249" s="5" t="n"/>
-      <c r="C249" s="5" t="n"/>
-      <c r="D249" s="5" t="n"/>
-      <c r="E249" s="8" t="inlineStr">
+      <c r="I250" s="4" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="n"/>
+      <c r="B251" s="5" t="n"/>
+      <c r="C251" s="5" t="n"/>
+      <c r="D251" s="5" t="n"/>
+      <c r="E251" s="8" t="inlineStr">
         <is>
           <t>21-3-3</t>
         </is>
       </c>
-      <c r="F249" s="9" t="inlineStr">
+      <c r="F251" s="9" t="inlineStr">
         <is>
           <t>他ユーザーの通知は未読件数に含まれない</t>
         </is>
       </c>
-      <c r="G249" s="9" t="inlineStr">
+      <c r="G251" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知と、他ユーザー宛ての未読通知をそれぞれ用意する
 2.画面を開く</t>
         </is>
       </c>
-      <c r="H249" s="9" t="inlineStr">
+      <c r="H251" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数には、自分宛ての未読通知のみが数えられる</t>
         </is>
       </c>
-      <c r="I249" s="5" t="n"/>
+      <c r="I251" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="174">
+    <mergeCell ref="I31:I36"/>
+    <mergeCell ref="D50:D55"/>
     <mergeCell ref="D60:D63"/>
-    <mergeCell ref="D50:D55"/>
-    <mergeCell ref="I31:I36"/>
     <mergeCell ref="C95:C97"/>
-    <mergeCell ref="I192:I195"/>
-    <mergeCell ref="D156:D160"/>
-    <mergeCell ref="D227:D231"/>
+    <mergeCell ref="I194:I197"/>
+    <mergeCell ref="D157:D161"/>
+    <mergeCell ref="D229:D233"/>
     <mergeCell ref="I64:I68"/>
-    <mergeCell ref="B129:B160"/>
+    <mergeCell ref="B129:B161"/>
     <mergeCell ref="B60:B79"/>
     <mergeCell ref="I98:I100"/>
     <mergeCell ref="B27:B59"/>
@@ -8211,76 +8266,76 @@
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="D83:D87"/>
     <mergeCell ref="I56:I59"/>
-    <mergeCell ref="A239:A249"/>
+    <mergeCell ref="A241:A251"/>
     <mergeCell ref="C56:C59"/>
     <mergeCell ref="C101:C103"/>
     <mergeCell ref="C76:C79"/>
-    <mergeCell ref="A161:A167"/>
-    <mergeCell ref="C161:C167"/>
+    <mergeCell ref="A162:A168"/>
+    <mergeCell ref="C162:C168"/>
     <mergeCell ref="I90:I94"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="I129:I131"/>
     <mergeCell ref="C60:C63"/>
-    <mergeCell ref="I186:I191"/>
+    <mergeCell ref="I188:I193"/>
     <mergeCell ref="D80:D82"/>
-    <mergeCell ref="I239:I241"/>
+    <mergeCell ref="I241:I243"/>
     <mergeCell ref="C37:C49"/>
-    <mergeCell ref="A216:A226"/>
+    <mergeCell ref="A218:A228"/>
     <mergeCell ref="D10:D11"/>
-    <mergeCell ref="C216:C226"/>
-    <mergeCell ref="B192:B195"/>
-    <mergeCell ref="B232:B238"/>
+    <mergeCell ref="C218:C228"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="B234:B240"/>
     <mergeCell ref="I60:I63"/>
-    <mergeCell ref="D192:D195"/>
+    <mergeCell ref="D194:D197"/>
     <mergeCell ref="D7:D9"/>
-    <mergeCell ref="I156:I160"/>
-    <mergeCell ref="I232:I235"/>
+    <mergeCell ref="I157:I161"/>
+    <mergeCell ref="I234:I237"/>
     <mergeCell ref="C143:C149"/>
     <mergeCell ref="B111:B128"/>
-    <mergeCell ref="A173:A178"/>
-    <mergeCell ref="C247:C249"/>
-    <mergeCell ref="A196:A215"/>
-    <mergeCell ref="C196:C215"/>
-    <mergeCell ref="A179:A185"/>
-    <mergeCell ref="D236:D238"/>
+    <mergeCell ref="A174:A180"/>
+    <mergeCell ref="C249:C251"/>
+    <mergeCell ref="A198:A217"/>
+    <mergeCell ref="C198:C217"/>
+    <mergeCell ref="A181:A187"/>
+    <mergeCell ref="D238:D240"/>
     <mergeCell ref="I143:I149"/>
-    <mergeCell ref="I247:I249"/>
+    <mergeCell ref="I249:I251"/>
     <mergeCell ref="D27:D30"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="D107:D110"/>
     <mergeCell ref="D123:D127"/>
-    <mergeCell ref="D161:D167"/>
+    <mergeCell ref="D162:D168"/>
     <mergeCell ref="I69:I75"/>
     <mergeCell ref="A2:A12"/>
-    <mergeCell ref="D186:D191"/>
-    <mergeCell ref="A192:A195"/>
+    <mergeCell ref="D188:D193"/>
+    <mergeCell ref="A194:A197"/>
     <mergeCell ref="C69:C75"/>
-    <mergeCell ref="C192:C195"/>
-    <mergeCell ref="I150:I155"/>
+    <mergeCell ref="C194:C197"/>
+    <mergeCell ref="I150:I156"/>
     <mergeCell ref="B107:B110"/>
-    <mergeCell ref="I168:I172"/>
+    <mergeCell ref="I169:I173"/>
     <mergeCell ref="I80:I82"/>
     <mergeCell ref="C98:C100"/>
     <mergeCell ref="C31:C36"/>
-    <mergeCell ref="C232:C235"/>
+    <mergeCell ref="C234:C237"/>
     <mergeCell ref="D140:D142"/>
     <mergeCell ref="D69:D75"/>
     <mergeCell ref="C104:C106"/>
     <mergeCell ref="C64:C68"/>
-    <mergeCell ref="D239:D241"/>
-    <mergeCell ref="I242:I246"/>
+    <mergeCell ref="D241:D243"/>
+    <mergeCell ref="I244:I248"/>
     <mergeCell ref="D95:D97"/>
     <mergeCell ref="D88:D89"/>
-    <mergeCell ref="C156:C160"/>
-    <mergeCell ref="A227:A231"/>
-    <mergeCell ref="B179:B185"/>
-    <mergeCell ref="A129:A160"/>
-    <mergeCell ref="C227:C231"/>
+    <mergeCell ref="C157:C161"/>
+    <mergeCell ref="A229:A233"/>
+    <mergeCell ref="B181:B187"/>
+    <mergeCell ref="A129:A161"/>
+    <mergeCell ref="C229:C233"/>
     <mergeCell ref="A60:A79"/>
-    <mergeCell ref="D179:D185"/>
-    <mergeCell ref="I236:I238"/>
-    <mergeCell ref="B173:B178"/>
-    <mergeCell ref="D173:D178"/>
+    <mergeCell ref="D181:D187"/>
+    <mergeCell ref="I238:I240"/>
+    <mergeCell ref="B174:B180"/>
+    <mergeCell ref="D174:D180"/>
     <mergeCell ref="I111:I122"/>
     <mergeCell ref="I50:I55"/>
     <mergeCell ref="I27:I30"/>
@@ -8289,48 +8344,48 @@
     <mergeCell ref="I123:I127"/>
     <mergeCell ref="D31:D36"/>
     <mergeCell ref="A107:A110"/>
-    <mergeCell ref="I161:I167"/>
+    <mergeCell ref="I162:I168"/>
     <mergeCell ref="I13:I26"/>
-    <mergeCell ref="B168:B172"/>
-    <mergeCell ref="D168:D172"/>
-    <mergeCell ref="C239:C241"/>
+    <mergeCell ref="B169:B173"/>
+    <mergeCell ref="D169:D173"/>
+    <mergeCell ref="C241:C243"/>
     <mergeCell ref="D129:D131"/>
     <mergeCell ref="A13:A26"/>
     <mergeCell ref="D98:D100"/>
     <mergeCell ref="I83:I87"/>
     <mergeCell ref="C13:C26"/>
     <mergeCell ref="I37:I49"/>
-    <mergeCell ref="B239:B249"/>
+    <mergeCell ref="B241:B251"/>
     <mergeCell ref="D76:D79"/>
     <mergeCell ref="B98:B103"/>
     <mergeCell ref="D37:D49"/>
-    <mergeCell ref="B216:B226"/>
+    <mergeCell ref="B218:B228"/>
     <mergeCell ref="C50:C55"/>
     <mergeCell ref="I95:I97"/>
     <mergeCell ref="I88:I89"/>
-    <mergeCell ref="I196:I215"/>
+    <mergeCell ref="I198:I217"/>
     <mergeCell ref="I104:I106"/>
     <mergeCell ref="A111:A128"/>
     <mergeCell ref="D90:D94"/>
     <mergeCell ref="D111:D122"/>
     <mergeCell ref="I10:I11"/>
-    <mergeCell ref="A168:A172"/>
-    <mergeCell ref="C150:C155"/>
+    <mergeCell ref="A169:A173"/>
+    <mergeCell ref="C150:C156"/>
     <mergeCell ref="D101:D103"/>
-    <mergeCell ref="A232:A238"/>
+    <mergeCell ref="A234:A240"/>
     <mergeCell ref="I7:I9"/>
-    <mergeCell ref="B161:B167"/>
+    <mergeCell ref="B162:B168"/>
     <mergeCell ref="B13:B26"/>
-    <mergeCell ref="I227:I231"/>
-    <mergeCell ref="C236:C238"/>
+    <mergeCell ref="I229:I233"/>
+    <mergeCell ref="C238:C240"/>
     <mergeCell ref="D13:D26"/>
     <mergeCell ref="A104:A106"/>
     <mergeCell ref="C107:C110"/>
-    <mergeCell ref="C242:C246"/>
+    <mergeCell ref="C244:C248"/>
     <mergeCell ref="C123:C127"/>
     <mergeCell ref="A98:A103"/>
-    <mergeCell ref="A186:A191"/>
-    <mergeCell ref="C186:C191"/>
+    <mergeCell ref="A188:A193"/>
+    <mergeCell ref="C188:C193"/>
     <mergeCell ref="B2:B12"/>
     <mergeCell ref="I2:I5"/>
     <mergeCell ref="I76:I79"/>
@@ -8338,33 +8393,33 @@
     <mergeCell ref="D143:D149"/>
     <mergeCell ref="A27:A59"/>
     <mergeCell ref="C111:C122"/>
-    <mergeCell ref="D247:D249"/>
+    <mergeCell ref="D249:D251"/>
     <mergeCell ref="C140:C142"/>
-    <mergeCell ref="B196:B215"/>
+    <mergeCell ref="B198:B217"/>
     <mergeCell ref="D64:D68"/>
-    <mergeCell ref="D196:D215"/>
+    <mergeCell ref="D198:D217"/>
     <mergeCell ref="B104:B106"/>
     <mergeCell ref="B80:B97"/>
-    <mergeCell ref="I216:I226"/>
+    <mergeCell ref="I218:I228"/>
     <mergeCell ref="C27:C30"/>
     <mergeCell ref="I140:I142"/>
-    <mergeCell ref="D150:D155"/>
-    <mergeCell ref="B186:B191"/>
+    <mergeCell ref="D150:D156"/>
+    <mergeCell ref="B188:B193"/>
     <mergeCell ref="D56:D59"/>
     <mergeCell ref="I101:I103"/>
-    <mergeCell ref="B227:B231"/>
-    <mergeCell ref="C179:C185"/>
+    <mergeCell ref="B229:B233"/>
+    <mergeCell ref="C181:C187"/>
     <mergeCell ref="D104:D106"/>
-    <mergeCell ref="C173:C178"/>
+    <mergeCell ref="C174:C180"/>
     <mergeCell ref="I107:I110"/>
     <mergeCell ref="C83:C87"/>
-    <mergeCell ref="D216:D226"/>
-    <mergeCell ref="D242:D246"/>
+    <mergeCell ref="D218:D228"/>
+    <mergeCell ref="D244:D248"/>
     <mergeCell ref="C132:C139"/>
-    <mergeCell ref="D232:D235"/>
-    <mergeCell ref="I179:I185"/>
-    <mergeCell ref="I173:I178"/>
-    <mergeCell ref="C168:C172"/>
+    <mergeCell ref="D234:D237"/>
+    <mergeCell ref="I181:I187"/>
+    <mergeCell ref="I174:I180"/>
+    <mergeCell ref="C169:C173"/>
     <mergeCell ref="C80:C82"/>
     <mergeCell ref="I132:I139"/>
     <mergeCell ref="C129:C131"/>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -5069,7 +5069,7 @@
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>中間テーブル(book_genres)に指定したジャンルが保存され、レスポンスのgenresにも含まれる</t>
+          <t>中間テーブル(book_genre)に指定したジャンルが保存され、レスポンスのgenresにも含まれる</t>
         </is>
       </c>
       <c r="I146" s="4" t="n"/>
@@ -5309,8 +5309,8 @@
     <row r="155">
       <c r="A155" s="4" t="n"/>
       <c r="B155" s="4" t="n"/>
-      <c r="C155" s="5" t="n"/>
-      <c r="D155" s="5" t="n"/>
+      <c r="C155" s="4" t="n"/>
+      <c r="D155" s="4" t="n"/>
       <c r="E155" s="2" t="inlineStr">
         <is>
           <t>10-5-6</t>
@@ -5331,7 +5331,7 @@
           <t>422が返り、「書籍タイトルを入力してください」が返る。書籍は更新されない</t>
         </is>
       </c>
-      <c r="I155" s="5" t="n"/>
+      <c r="I155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n"/>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>book_genres・reviews・favorites・review_likesの該当データも削除される</t>
+          <t>book_genre・reviews・favorites・review_likesの該当データも削除される</t>
         </is>
       </c>
       <c r="I159" s="4" t="n"/>
@@ -6040,10 +6040,10 @@
       <c r="I178" s="4" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="n"/>
-      <c r="B179" s="5" t="n"/>
-      <c r="C179" s="5" t="n"/>
-      <c r="D179" s="5" t="n"/>
+      <c r="A179" s="4" t="n"/>
+      <c r="B179" s="4" t="n"/>
+      <c r="C179" s="4" t="n"/>
+      <c r="D179" s="4" t="n"/>
       <c r="E179" s="6" t="inlineStr">
         <is>
           <t>13-1-6</t>
@@ -6064,7 +6064,7 @@
           <t>いずれも403Forbiddenになり、データは変更されない</t>
         </is>
       </c>
-      <c r="I179" s="5" t="n"/>
+      <c r="I179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n"/>
@@ -8250,176 +8250,176 @@
     </row>
   </sheetData>
   <mergeCells count="174">
-    <mergeCell ref="I31:I36"/>
+    <mergeCell ref="I229:I233"/>
+    <mergeCell ref="A174:A180"/>
     <mergeCell ref="D50:D55"/>
     <mergeCell ref="D60:D63"/>
+    <mergeCell ref="I31:I36"/>
     <mergeCell ref="C95:C97"/>
-    <mergeCell ref="I194:I197"/>
-    <mergeCell ref="D157:D161"/>
-    <mergeCell ref="D229:D233"/>
     <mergeCell ref="I64:I68"/>
-    <mergeCell ref="B129:B161"/>
     <mergeCell ref="B60:B79"/>
+    <mergeCell ref="B234:B240"/>
     <mergeCell ref="I98:I100"/>
     <mergeCell ref="B27:B59"/>
     <mergeCell ref="C10:C11"/>
+    <mergeCell ref="I244:I248"/>
+    <mergeCell ref="D181:D187"/>
+    <mergeCell ref="C169:C173"/>
+    <mergeCell ref="B162:B168"/>
+    <mergeCell ref="I194:I197"/>
+    <mergeCell ref="D162:D168"/>
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="D83:D87"/>
     <mergeCell ref="I56:I59"/>
-    <mergeCell ref="A241:A251"/>
+    <mergeCell ref="I169:I173"/>
+    <mergeCell ref="D157:D161"/>
     <mergeCell ref="C56:C59"/>
+    <mergeCell ref="A129:A161"/>
     <mergeCell ref="C101:C103"/>
     <mergeCell ref="C76:C79"/>
-    <mergeCell ref="A162:A168"/>
-    <mergeCell ref="C162:C168"/>
+    <mergeCell ref="D249:D251"/>
     <mergeCell ref="I90:I94"/>
     <mergeCell ref="C2:C5"/>
     <mergeCell ref="I129:I131"/>
     <mergeCell ref="C60:C63"/>
-    <mergeCell ref="I188:I193"/>
     <mergeCell ref="D80:D82"/>
-    <mergeCell ref="I241:I243"/>
     <mergeCell ref="C37:C49"/>
-    <mergeCell ref="A218:A228"/>
     <mergeCell ref="D10:D11"/>
-    <mergeCell ref="C218:C228"/>
-    <mergeCell ref="B194:B197"/>
-    <mergeCell ref="B234:B240"/>
+    <mergeCell ref="D174:D180"/>
     <mergeCell ref="I60:I63"/>
-    <mergeCell ref="D194:D197"/>
     <mergeCell ref="D7:D9"/>
-    <mergeCell ref="I157:I161"/>
-    <mergeCell ref="I234:I237"/>
     <mergeCell ref="C143:C149"/>
     <mergeCell ref="B111:B128"/>
-    <mergeCell ref="A174:A180"/>
+    <mergeCell ref="B194:B197"/>
+    <mergeCell ref="C238:C240"/>
+    <mergeCell ref="A241:A251"/>
+    <mergeCell ref="I181:I187"/>
+    <mergeCell ref="I162:I168"/>
+    <mergeCell ref="I143:I149"/>
     <mergeCell ref="C249:C251"/>
     <mergeCell ref="A198:A217"/>
-    <mergeCell ref="C198:C217"/>
-    <mergeCell ref="A181:A187"/>
-    <mergeCell ref="D238:D240"/>
-    <mergeCell ref="I143:I149"/>
-    <mergeCell ref="I249:I251"/>
     <mergeCell ref="D27:D30"/>
     <mergeCell ref="D2:D5"/>
+    <mergeCell ref="C198:C217"/>
     <mergeCell ref="D107:D110"/>
+    <mergeCell ref="C150:C156"/>
+    <mergeCell ref="I188:I193"/>
     <mergeCell ref="D123:D127"/>
-    <mergeCell ref="D162:D168"/>
     <mergeCell ref="I69:I75"/>
     <mergeCell ref="A2:A12"/>
-    <mergeCell ref="D188:D193"/>
-    <mergeCell ref="A194:A197"/>
+    <mergeCell ref="C174:C180"/>
     <mergeCell ref="C69:C75"/>
-    <mergeCell ref="C194:C197"/>
-    <mergeCell ref="I150:I156"/>
     <mergeCell ref="B107:B110"/>
-    <mergeCell ref="I169:I173"/>
     <mergeCell ref="I80:I82"/>
+    <mergeCell ref="D234:D237"/>
     <mergeCell ref="C98:C100"/>
     <mergeCell ref="C31:C36"/>
-    <mergeCell ref="C234:C237"/>
+    <mergeCell ref="A194:A197"/>
     <mergeCell ref="D140:D142"/>
+    <mergeCell ref="B241:B251"/>
+    <mergeCell ref="I174:I180"/>
     <mergeCell ref="D69:D75"/>
     <mergeCell ref="C104:C106"/>
+    <mergeCell ref="A169:A173"/>
+    <mergeCell ref="D238:D240"/>
     <mergeCell ref="C64:C68"/>
-    <mergeCell ref="D241:D243"/>
-    <mergeCell ref="I244:I248"/>
+    <mergeCell ref="B229:B233"/>
+    <mergeCell ref="D229:D233"/>
     <mergeCell ref="D95:D97"/>
     <mergeCell ref="D88:D89"/>
-    <mergeCell ref="C157:C161"/>
-    <mergeCell ref="A229:A233"/>
-    <mergeCell ref="B181:B187"/>
-    <mergeCell ref="A129:A161"/>
-    <mergeCell ref="C229:C233"/>
     <mergeCell ref="A60:A79"/>
-    <mergeCell ref="D181:D187"/>
+    <mergeCell ref="I150:I156"/>
+    <mergeCell ref="I111:I122"/>
+    <mergeCell ref="A162:A168"/>
+    <mergeCell ref="I50:I55"/>
     <mergeCell ref="I238:I240"/>
-    <mergeCell ref="B174:B180"/>
-    <mergeCell ref="D174:D180"/>
-    <mergeCell ref="I111:I122"/>
-    <mergeCell ref="I50:I55"/>
+    <mergeCell ref="C162:C168"/>
+    <mergeCell ref="D198:D217"/>
     <mergeCell ref="I27:I30"/>
+    <mergeCell ref="B188:B193"/>
+    <mergeCell ref="D188:D193"/>
     <mergeCell ref="D132:D139"/>
     <mergeCell ref="C90:C94"/>
     <mergeCell ref="I123:I127"/>
     <mergeCell ref="D31:D36"/>
     <mergeCell ref="A107:A110"/>
-    <mergeCell ref="I162:I168"/>
     <mergeCell ref="I13:I26"/>
-    <mergeCell ref="B169:B173"/>
-    <mergeCell ref="D169:D173"/>
-    <mergeCell ref="C241:C243"/>
+    <mergeCell ref="I249:I251"/>
+    <mergeCell ref="D150:D156"/>
     <mergeCell ref="D129:D131"/>
     <mergeCell ref="A13:A26"/>
     <mergeCell ref="D98:D100"/>
     <mergeCell ref="I83:I87"/>
     <mergeCell ref="C13:C26"/>
     <mergeCell ref="I37:I49"/>
-    <mergeCell ref="B241:B251"/>
+    <mergeCell ref="A234:A240"/>
+    <mergeCell ref="I157:I161"/>
+    <mergeCell ref="B169:B173"/>
     <mergeCell ref="D76:D79"/>
+    <mergeCell ref="D241:D243"/>
     <mergeCell ref="B98:B103"/>
     <mergeCell ref="D37:D49"/>
-    <mergeCell ref="B218:B228"/>
     <mergeCell ref="C50:C55"/>
     <mergeCell ref="I95:I97"/>
     <mergeCell ref="I88:I89"/>
-    <mergeCell ref="I198:I217"/>
     <mergeCell ref="I104:I106"/>
     <mergeCell ref="A111:A128"/>
+    <mergeCell ref="B129:B161"/>
+    <mergeCell ref="B218:B228"/>
     <mergeCell ref="D90:D94"/>
     <mergeCell ref="D111:D122"/>
+    <mergeCell ref="C194:C197"/>
     <mergeCell ref="I10:I11"/>
-    <mergeCell ref="A169:A173"/>
-    <mergeCell ref="C150:C156"/>
     <mergeCell ref="D101:D103"/>
-    <mergeCell ref="A234:A240"/>
+    <mergeCell ref="I198:I217"/>
     <mergeCell ref="I7:I9"/>
-    <mergeCell ref="B162:B168"/>
     <mergeCell ref="B13:B26"/>
-    <mergeCell ref="I229:I233"/>
-    <mergeCell ref="C238:C240"/>
     <mergeCell ref="D13:D26"/>
     <mergeCell ref="A104:A106"/>
+    <mergeCell ref="B181:B187"/>
     <mergeCell ref="C107:C110"/>
-    <mergeCell ref="C244:C248"/>
+    <mergeCell ref="D218:D228"/>
     <mergeCell ref="C123:C127"/>
     <mergeCell ref="A98:A103"/>
+    <mergeCell ref="I218:I228"/>
+    <mergeCell ref="A218:A228"/>
+    <mergeCell ref="B2:B12"/>
+    <mergeCell ref="C218:C228"/>
+    <mergeCell ref="C244:C248"/>
+    <mergeCell ref="I2:I5"/>
+    <mergeCell ref="I76:I79"/>
+    <mergeCell ref="C234:C237"/>
+    <mergeCell ref="C88:C89"/>
+    <mergeCell ref="D143:D149"/>
+    <mergeCell ref="I241:I243"/>
+    <mergeCell ref="A27:A59"/>
+    <mergeCell ref="C111:C122"/>
+    <mergeCell ref="C140:C142"/>
+    <mergeCell ref="D64:D68"/>
+    <mergeCell ref="B174:B180"/>
+    <mergeCell ref="B104:B106"/>
+    <mergeCell ref="I234:I237"/>
+    <mergeCell ref="B80:B97"/>
+    <mergeCell ref="A181:A187"/>
+    <mergeCell ref="D194:D197"/>
+    <mergeCell ref="C181:C187"/>
+    <mergeCell ref="C27:C30"/>
+    <mergeCell ref="I140:I142"/>
+    <mergeCell ref="B198:B217"/>
+    <mergeCell ref="A229:A233"/>
+    <mergeCell ref="C229:C233"/>
+    <mergeCell ref="D56:D59"/>
+    <mergeCell ref="I101:I103"/>
+    <mergeCell ref="D169:D173"/>
+    <mergeCell ref="C157:C161"/>
+    <mergeCell ref="D104:D106"/>
+    <mergeCell ref="I107:I110"/>
+    <mergeCell ref="C83:C87"/>
     <mergeCell ref="A188:A193"/>
     <mergeCell ref="C188:C193"/>
-    <mergeCell ref="B2:B12"/>
-    <mergeCell ref="I2:I5"/>
-    <mergeCell ref="I76:I79"/>
-    <mergeCell ref="C88:C89"/>
-    <mergeCell ref="D143:D149"/>
-    <mergeCell ref="A27:A59"/>
-    <mergeCell ref="C111:C122"/>
-    <mergeCell ref="D249:D251"/>
-    <mergeCell ref="C140:C142"/>
-    <mergeCell ref="B198:B217"/>
-    <mergeCell ref="D64:D68"/>
-    <mergeCell ref="D198:D217"/>
-    <mergeCell ref="B104:B106"/>
-    <mergeCell ref="B80:B97"/>
-    <mergeCell ref="I218:I228"/>
-    <mergeCell ref="C27:C30"/>
-    <mergeCell ref="I140:I142"/>
-    <mergeCell ref="D150:D156"/>
-    <mergeCell ref="B188:B193"/>
-    <mergeCell ref="D56:D59"/>
-    <mergeCell ref="I101:I103"/>
-    <mergeCell ref="B229:B233"/>
-    <mergeCell ref="C181:C187"/>
-    <mergeCell ref="D104:D106"/>
-    <mergeCell ref="C174:C180"/>
-    <mergeCell ref="I107:I110"/>
-    <mergeCell ref="C83:C87"/>
-    <mergeCell ref="D218:D228"/>
+    <mergeCell ref="C132:C139"/>
+    <mergeCell ref="C241:C243"/>
     <mergeCell ref="D244:D248"/>
-    <mergeCell ref="C132:C139"/>
-    <mergeCell ref="D234:D237"/>
-    <mergeCell ref="I181:I187"/>
-    <mergeCell ref="I174:I180"/>
-    <mergeCell ref="C169:C173"/>
     <mergeCell ref="C80:C82"/>
     <mergeCell ref="I132:I139"/>
     <mergeCell ref="C129:C131"/>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I257"/>
+  <dimension ref="A1:I263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -675,10 +675,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="17" t="n"/>
-      <c r="B3" s="17" t="n"/>
-      <c r="C3" s="17" t="n"/>
-      <c r="D3" s="17" t="n"/>
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
           <t>1-1-2</t>
@@ -700,13 +700,13 @@
           <t>レビューが投稿日時の新しい順に取得できる</t>
         </is>
       </c>
-      <c r="I3" s="17" t="n"/>
+      <c r="I3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="n"/>
-      <c r="B4" s="17" t="n"/>
-      <c r="C4" s="18" t="n"/>
-      <c r="D4" s="18" t="n"/>
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="5" t="n"/>
+      <c r="D4" s="5" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>1-1-3</t>
@@ -728,11 +728,11 @@
           <t>紐づく読書計画のコレクションが取得できる</t>
         </is>
       </c>
-      <c r="I4" s="18" t="n"/>
+      <c r="I4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n"/>
-      <c r="B5" s="17" t="n"/>
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
       <c r="C5" s="19" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -771,8 +771,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="n"/>
-      <c r="B6" s="17" t="n"/>
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
       <c r="C6" s="3" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -811,10 +811,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="n"/>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="17" t="n"/>
-      <c r="D7" s="17" t="n"/>
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t>1-3-2</t>
@@ -836,13 +836,13 @@
           <t>いいねしたユーザーのコレクションが取得できる</t>
         </is>
       </c>
-      <c r="I7" s="17" t="n"/>
+      <c r="I7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="n"/>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
       <c r="E8" s="3" t="inlineStr">
         <is>
           <t>1-3-3</t>
@@ -864,11 +864,11 @@
           <t>$review-&gt;rating が integer 型の 4 として取得できる</t>
         </is>
       </c>
-      <c r="I8" s="18" t="n"/>
+      <c r="I8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="n"/>
-      <c r="B9" s="17" t="n"/>
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
       <c r="C9" s="20" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -907,10 +907,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n"/>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="20" t="n"/>
-      <c r="D10" s="20" t="n"/>
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
           <t>1-4-2</t>
@@ -932,11 +932,11 @@
           <t>$plan-&gt;status が ReadingPlanStatus::InProgress インスタンスとして取得できる</t>
         </is>
       </c>
-      <c r="I10" s="20" t="n"/>
+      <c r="I10" s="16" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n"/>
-      <c r="B11" s="17" t="n"/>
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
       <c r="C11" s="19" t="inlineStr">
         <is>
           <t>1-5</t>
@@ -974,8 +974,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="n"/>
-      <c r="B12" s="17" t="n"/>
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
       <c r="C12" s="3" t="inlineStr">
         <is>
           <t>1-6</t>
@@ -1014,10 +1014,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="n"/>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="17" t="n"/>
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
       <c r="E13" s="3" t="inlineStr">
         <is>
           <t>1-6-2</t>
@@ -1039,13 +1039,13 @@
           <t>いいねしたレビューのコレクションが取得できる（書籍詳細のいいねボタンの表示切り替えで使用）</t>
         </is>
       </c>
-      <c r="I13" s="17" t="n"/>
+      <c r="I13" s="4" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="n"/>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="17" t="n"/>
-      <c r="D14" s="17" t="n"/>
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
       <c r="E14" s="3" t="inlineStr">
         <is>
           <t>1-6-3</t>
@@ -1067,13 +1067,13 @@
           <t>そのユーザーが登録した書籍のコレクションが取得できる（書籍登録時に、登録者を設定するために使用）</t>
         </is>
       </c>
-      <c r="I14" s="17" t="n"/>
+      <c r="I14" s="4" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="n"/>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="17" t="n"/>
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
       <c r="E15" s="3" t="inlineStr">
         <is>
           <t>1-6-4</t>
@@ -1095,13 +1095,13 @@
           <t>そのユーザーが投稿したレビューのコレクションが取得できる（マイ読書レポートの集計で使用）</t>
         </is>
       </c>
-      <c r="I15" s="17" t="n"/>
+      <c r="I15" s="4" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n"/>
-      <c r="B16" s="18" t="n"/>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
       <c r="E16" s="3" t="inlineStr">
         <is>
           <t>1-6-5</t>
@@ -1123,7 +1123,7 @@
           <t>そのユーザーが作成した読書計画のコレクションが取得できる（読書計画の一覧・作成で使用）</t>
         </is>
       </c>
-      <c r="I16" s="18" t="n"/>
+      <c r="I16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -1173,10 +1173,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="n"/>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="17" t="n"/>
-      <c r="D18" s="17" t="n"/>
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
       <c r="E18" s="3" t="inlineStr">
         <is>
           <t>2-1-2</t>
@@ -1197,13 +1197,13 @@
           <t>200が返り、書籍詳細が表示される</t>
         </is>
       </c>
-      <c r="I18" s="17" t="n"/>
+      <c r="I18" s="4" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="n"/>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
       <c r="E19" s="3" t="inlineStr">
         <is>
           <t>2-1-3</t>
@@ -1224,13 +1224,13 @@
           <t>ログインページへリダイレクトされる</t>
         </is>
       </c>
-      <c r="I19" s="17" t="n"/>
+      <c r="I19" s="4" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="n"/>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="n"/>
-      <c r="D20" s="17" t="n"/>
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
       <c r="E20" s="3" t="inlineStr">
         <is>
           <t>2-1-4</t>
@@ -1251,13 +1251,13 @@
           <t>ログインページへリダイレクトされる</t>
         </is>
       </c>
-      <c r="I20" s="17" t="n"/>
+      <c r="I20" s="4" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="n"/>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="n"/>
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
       <c r="E21" s="3" t="inlineStr">
         <is>
           <t>2-1-5</t>
@@ -1278,13 +1278,13 @@
           <t>200が返り、ランキングが表示される</t>
         </is>
       </c>
-      <c r="I21" s="17" t="n"/>
+      <c r="I21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="n"/>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="n"/>
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
       <c r="E22" s="3" t="inlineStr">
         <is>
           <t>2-1-6</t>
@@ -1305,13 +1305,13 @@
           <t>ログインページへリダイレクトされる</t>
         </is>
       </c>
-      <c r="I22" s="17" t="n"/>
+      <c r="I22" s="4" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="n"/>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="n"/>
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
       <c r="E23" s="3" t="inlineStr">
         <is>
           <t>2-1-7</t>
@@ -1332,13 +1332,13 @@
           <t>ログインページへリダイレクトされる</t>
         </is>
       </c>
-      <c r="I23" s="17" t="n"/>
+      <c r="I23" s="4" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="n"/>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
       <c r="E24" s="3" t="inlineStr">
         <is>
           <t>2-1-8</t>
@@ -1359,13 +1359,13 @@
           <t>ログインページへリダイレクトされる</t>
         </is>
       </c>
-      <c r="I24" s="17" t="n"/>
+      <c r="I24" s="4" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="n"/>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
       <c r="E25" s="3" t="inlineStr">
         <is>
           <t>2-1-9</t>
@@ -1386,13 +1386,13 @@
           <t>ログインページへリダイレクトされる</t>
         </is>
       </c>
-      <c r="I25" s="17" t="n"/>
+      <c r="I25" s="4" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="n"/>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
       <c r="E26" s="3" t="inlineStr">
         <is>
           <t>2-1-10</t>
@@ -1413,13 +1413,13 @@
           <t>ログインページへリダイレクトされる</t>
         </is>
       </c>
-      <c r="I26" s="17" t="n"/>
+      <c r="I26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="n"/>
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="n"/>
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
       <c r="E27" s="3" t="inlineStr">
         <is>
           <t>2-1-11</t>
@@ -1440,13 +1440,13 @@
           <t>ログインページへリダイレクトされる</t>
         </is>
       </c>
-      <c r="I27" s="17" t="n"/>
+      <c r="I27" s="4" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="n"/>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="n"/>
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
       <c r="E28" s="3" t="inlineStr">
         <is>
           <t>2-1-12</t>
@@ -1467,13 +1467,13 @@
           <t>いずれもログインページへリダイレクトされる</t>
         </is>
       </c>
-      <c r="I28" s="17" t="n"/>
+      <c r="I28" s="4" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="n"/>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="17" t="n"/>
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
       <c r="E29" s="3" t="inlineStr">
         <is>
           <t>2-1-13</t>
@@ -1494,13 +1494,13 @@
           <t>ログインページへリダイレクトされる</t>
         </is>
       </c>
-      <c r="I29" s="17" t="n"/>
+      <c r="I29" s="4" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n"/>
-      <c r="B30" s="18" t="n"/>
-      <c r="C30" s="18" t="n"/>
-      <c r="D30" s="18" t="n"/>
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
       <c r="E30" s="3" t="inlineStr">
         <is>
           <t>2-1-14</t>
@@ -1521,7 +1521,7 @@
           <t>いずれも書籍一覧ページ(/)へリダイレクトされる</t>
         </is>
       </c>
-      <c r="I30" s="18" t="n"/>
+      <c r="I30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -1571,10 +1571,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="n"/>
-      <c r="B32" s="17" t="n"/>
-      <c r="C32" s="17" t="n"/>
-      <c r="D32" s="17" t="n"/>
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
       <c r="E32" s="3" t="inlineStr">
         <is>
           <t>3-1-2</t>
@@ -1596,13 +1596,13 @@
           <t>1ページに10件ずつ表示され、ページネーションで2ページ目以降を表示できる</t>
         </is>
       </c>
-      <c r="I32" s="17" t="n"/>
+      <c r="I32" s="4" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="n"/>
-      <c r="B33" s="17" t="n"/>
-      <c r="C33" s="17" t="n"/>
-      <c r="D33" s="17" t="n"/>
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
       <c r="E33" s="3" t="inlineStr">
         <is>
           <t>3-1-3</t>
@@ -1623,13 +1623,13 @@
           <t>「書籍が登録されていません。」と表示される</t>
         </is>
       </c>
-      <c r="I33" s="17" t="n"/>
+      <c r="I33" s="4" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="n"/>
-      <c r="B34" s="17" t="n"/>
-      <c r="C34" s="18" t="n"/>
-      <c r="D34" s="18" t="n"/>
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
       <c r="E34" s="3" t="inlineStr">
         <is>
           <t>3-1-4</t>
@@ -1650,11 +1650,11 @@
           <t>書籍一覧が表示される</t>
         </is>
       </c>
-      <c r="I34" s="18" t="n"/>
+      <c r="I34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="n"/>
-      <c r="B35" s="17" t="n"/>
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="4" t="n"/>
       <c r="C35" s="3" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -1692,10 +1692,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="n"/>
-      <c r="B36" s="17" t="n"/>
-      <c r="C36" s="17" t="n"/>
-      <c r="D36" s="17" t="n"/>
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
       <c r="E36" s="3" t="inlineStr">
         <is>
           <t>3-2-2</t>
@@ -1716,13 +1716,13 @@
           <t>「説明」の項目自体が表示されない</t>
         </is>
       </c>
-      <c r="I36" s="17" t="n"/>
+      <c r="I36" s="4" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="n"/>
-      <c r="B37" s="17" t="n"/>
-      <c r="C37" s="17" t="n"/>
-      <c r="D37" s="17" t="n"/>
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
       <c r="E37" s="3" t="inlineStr">
         <is>
           <t>3-2-3</t>
@@ -1743,13 +1743,13 @@
           <t>画像の代わりに「画像なし」と表示される</t>
         </is>
       </c>
-      <c r="I37" s="17" t="n"/>
+      <c r="I37" s="4" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="n"/>
-      <c r="B38" s="17" t="n"/>
-      <c r="C38" s="17" t="n"/>
-      <c r="D38" s="17" t="n"/>
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
       <c r="E38" s="3" t="inlineStr">
         <is>
           <t>3-2-4</t>
@@ -1771,13 +1771,13 @@
           <t>「編集」ボタンと「削除」ボタンが表示される</t>
         </is>
       </c>
-      <c r="I38" s="17" t="n"/>
+      <c r="I38" s="4" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="n"/>
-      <c r="B39" s="17" t="n"/>
-      <c r="C39" s="17" t="n"/>
-      <c r="D39" s="17" t="n"/>
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
       <c r="E39" s="3" t="inlineStr">
         <is>
           <t>3-2-5</t>
@@ -1799,13 +1799,13 @@
           <t>「編集」ボタンと「削除」ボタンが表示されない</t>
         </is>
       </c>
-      <c r="I39" s="17" t="n"/>
+      <c r="I39" s="4" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="n"/>
-      <c r="B40" s="17" t="n"/>
-      <c r="C40" s="17" t="n"/>
-      <c r="D40" s="17" t="n"/>
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
       <c r="E40" s="3" t="inlineStr">
         <is>
           <t>3-2-6</t>
@@ -1826,13 +1826,13 @@
           <t>「編集」ボタンと「削除」ボタンが表示されない</t>
         </is>
       </c>
-      <c r="I40" s="17" t="n"/>
+      <c r="I40" s="4" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="n"/>
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="18" t="n"/>
-      <c r="D41" s="18" t="n"/>
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="5" t="n"/>
+      <c r="D41" s="5" t="n"/>
       <c r="E41" s="3" t="inlineStr">
         <is>
           <t>3-2-7</t>
@@ -1853,11 +1853,11 @@
           <t>ISBN・出版日の欄に「未登録」と表示される</t>
         </is>
       </c>
-      <c r="I41" s="18" t="n"/>
+      <c r="I41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="n"/>
-      <c r="B42" s="17" t="n"/>
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="4" t="n"/>
       <c r="C42" s="3" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -1895,10 +1895,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="n"/>
-      <c r="B43" s="17" t="n"/>
-      <c r="C43" s="17" t="n"/>
-      <c r="D43" s="17" t="n"/>
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="4" t="n"/>
+      <c r="C43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
       <c r="E43" s="3" t="inlineStr">
         <is>
           <t>3-3-2</t>
@@ -1921,13 +1921,13 @@
           <t>「書籍タイトルを入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I43" s="17" t="n"/>
+      <c r="I43" s="4" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="n"/>
-      <c r="B44" s="17" t="n"/>
-      <c r="C44" s="17" t="n"/>
-      <c r="D44" s="17" t="n"/>
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="4" t="n"/>
+      <c r="C44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
       <c r="E44" s="3" t="inlineStr">
         <is>
           <t>3-3-3</t>
@@ -1950,13 +1950,13 @@
           <t>「書籍タイトルは255文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I44" s="17" t="n"/>
+      <c r="I44" s="4" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="n"/>
-      <c r="B45" s="17" t="n"/>
-      <c r="C45" s="17" t="n"/>
-      <c r="D45" s="17" t="n"/>
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
       <c r="E45" s="3" t="inlineStr">
         <is>
           <t>3-3-4</t>
@@ -1980,13 +1980,13 @@
           <t>タイトルの重複エラーにならず、書籍情報が登録される（タイトルは重複可能）</t>
         </is>
       </c>
-      <c r="I45" s="17" t="n"/>
+      <c r="I45" s="4" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="n"/>
-      <c r="B46" s="17" t="n"/>
-      <c r="C46" s="17" t="n"/>
-      <c r="D46" s="17" t="n"/>
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
       <c r="E46" s="3" t="inlineStr">
         <is>
           <t>3-3-5</t>
@@ -2009,13 +2009,13 @@
           <t>「著者名を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I46" s="17" t="n"/>
+      <c r="I46" s="4" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="n"/>
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="17" t="n"/>
-      <c r="D47" s="17" t="n"/>
+      <c r="A47" s="4" t="n"/>
+      <c r="B47" s="4" t="n"/>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
       <c r="E47" s="3" t="inlineStr">
         <is>
           <t>3-3-6</t>
@@ -2038,13 +2038,13 @@
           <t>ISBNのバリデーションエラーにならず、ISBNが未設定(null)の書籍情報が登録される（ISBNは任意項目）</t>
         </is>
       </c>
-      <c r="I47" s="17" t="n"/>
+      <c r="I47" s="4" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="n"/>
-      <c r="B48" s="17" t="n"/>
-      <c r="C48" s="17" t="n"/>
-      <c r="D48" s="17" t="n"/>
+      <c r="A48" s="4" t="n"/>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
       <c r="E48" s="3" t="inlineStr">
         <is>
           <t>3-3-7</t>
@@ -2067,13 +2067,13 @@
           <t>「ISBNは13桁の数字で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I48" s="17" t="n"/>
+      <c r="I48" s="4" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="n"/>
-      <c r="B49" s="17" t="n"/>
-      <c r="C49" s="17" t="n"/>
-      <c r="D49" s="17" t="n"/>
+      <c r="A49" s="4" t="n"/>
+      <c r="B49" s="4" t="n"/>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
       <c r="E49" s="3" t="inlineStr">
         <is>
           <t>3-3-8</t>
@@ -2096,13 +2096,13 @@
           <t>「このISBNはすでに登録されています」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I49" s="17" t="n"/>
+      <c r="I49" s="4" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="n"/>
-      <c r="B50" s="17" t="n"/>
-      <c r="C50" s="17" t="n"/>
-      <c r="D50" s="17" t="n"/>
+      <c r="A50" s="4" t="n"/>
+      <c r="B50" s="4" t="n"/>
+      <c r="C50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
       <c r="E50" s="3" t="inlineStr">
         <is>
           <t>3-3-9</t>
@@ -2125,13 +2125,13 @@
           <t>出版日のバリデーションエラーにならず、出版日が未設定(null)の書籍情報が登録される（出版日は任意項目）</t>
         </is>
       </c>
-      <c r="I50" s="17" t="n"/>
+      <c r="I50" s="4" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="17" t="n"/>
-      <c r="B51" s="17" t="n"/>
-      <c r="C51" s="17" t="n"/>
-      <c r="D51" s="17" t="n"/>
+      <c r="A51" s="4" t="n"/>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
       <c r="E51" s="3" t="inlineStr">
         <is>
           <t>3-3-10</t>
@@ -2154,13 +2154,13 @@
           <t>「説明は1000文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I51" s="17" t="n"/>
+      <c r="I51" s="4" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="17" t="n"/>
-      <c r="B52" s="17" t="n"/>
-      <c r="C52" s="17" t="n"/>
-      <c r="D52" s="17" t="n"/>
+      <c r="A52" s="4" t="n"/>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
       <c r="E52" s="3" t="inlineStr">
         <is>
           <t>3-3-11</t>
@@ -2183,13 +2183,13 @@
           <t>「URL形式で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I52" s="17" t="n"/>
+      <c r="I52" s="4" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="n"/>
-      <c r="B53" s="17" t="n"/>
-      <c r="C53" s="17" t="n"/>
-      <c r="D53" s="17" t="n"/>
+      <c r="A53" s="4" t="n"/>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
       <c r="E53" s="3" t="inlineStr">
         <is>
           <t>3-3-12</t>
@@ -2212,13 +2212,13 @@
           <t>「ジャンルを1つ以上選択してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I53" s="17" t="n"/>
+      <c r="I53" s="4" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="n"/>
-      <c r="B54" s="17" t="n"/>
-      <c r="C54" s="17" t="n"/>
-      <c r="D54" s="17" t="n"/>
+      <c r="A54" s="4" t="n"/>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
       <c r="E54" s="3" t="inlineStr">
         <is>
           <t>3-3-13</t>
@@ -2241,13 +2241,13 @@
           <t>書籍情報が登録され、書籍一覧画面に遷移し「「(タイトル)」を登録しました。」と表示される</t>
         </is>
       </c>
-      <c r="I54" s="17" t="n"/>
+      <c r="I54" s="4" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="n"/>
-      <c r="B55" s="17" t="n"/>
-      <c r="C55" s="18" t="n"/>
-      <c r="D55" s="18" t="n"/>
+      <c r="A55" s="4" t="n"/>
+      <c r="B55" s="4" t="n"/>
+      <c r="C55" s="5" t="n"/>
+      <c r="D55" s="5" t="n"/>
       <c r="E55" s="3" t="inlineStr">
         <is>
           <t>3-3-14</t>
@@ -2268,11 +2268,11 @@
           <t>タイトル・著者名・ジャンルには必須マーク(*)が表示され、ISBN・出版日には必須マークが表示されない</t>
         </is>
       </c>
-      <c r="I55" s="18" t="n"/>
+      <c r="I55" s="5" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="17" t="n"/>
-      <c r="B56" s="17" t="n"/>
+      <c r="A56" s="4" t="n"/>
+      <c r="B56" s="4" t="n"/>
       <c r="C56" s="3" t="inlineStr">
         <is>
           <t>3-4</t>
@@ -2310,10 +2310,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="17" t="n"/>
-      <c r="B57" s="17" t="n"/>
-      <c r="C57" s="17" t="n"/>
-      <c r="D57" s="17" t="n"/>
+      <c r="A57" s="4" t="n"/>
+      <c r="B57" s="4" t="n"/>
+      <c r="C57" s="4" t="n"/>
+      <c r="D57" s="4" t="n"/>
       <c r="E57" s="3" t="inlineStr">
         <is>
           <t>3-4-2</t>
@@ -2335,13 +2335,13 @@
           <t>編集できず、エラーになる（403Forbidden）</t>
         </is>
       </c>
-      <c r="I57" s="17" t="n"/>
+      <c r="I57" s="4" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="17" t="n"/>
-      <c r="B58" s="17" t="n"/>
-      <c r="C58" s="17" t="n"/>
-      <c r="D58" s="17" t="n"/>
+      <c r="A58" s="4" t="n"/>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
       <c r="E58" s="3" t="inlineStr">
         <is>
           <t>3-4-3</t>
@@ -2362,13 +2362,13 @@
           <t>タイトル・著者名・ISBN・出版日・説明・画像URL・選択済みジャンルに現在の登録内容が表示される</t>
         </is>
       </c>
-      <c r="I58" s="17" t="n"/>
+      <c r="I58" s="4" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="17" t="n"/>
-      <c r="B59" s="17" t="n"/>
-      <c r="C59" s="17" t="n"/>
-      <c r="D59" s="17" t="n"/>
+      <c r="A59" s="4" t="n"/>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
       <c r="E59" s="3" t="inlineStr">
         <is>
           <t>3-4-4</t>
@@ -2391,13 +2391,13 @@
           <t>書籍登録機能と同じ内容のバリデーションメッセージが表示される（未入力・文字数超過・形式不正など）</t>
         </is>
       </c>
-      <c r="I59" s="17" t="n"/>
+      <c r="I59" s="4" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="17" t="n"/>
-      <c r="B60" s="17" t="n"/>
-      <c r="C60" s="17" t="n"/>
-      <c r="D60" s="17" t="n"/>
+      <c r="A60" s="4" t="n"/>
+      <c r="B60" s="4" t="n"/>
+      <c r="C60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
       <c r="E60" s="3" t="inlineStr">
         <is>
           <t>3-4-5</t>
@@ -2420,13 +2420,13 @@
           <t>「このISBNはすでに登録されています」というエラーにならず、更新できる（タイトルは重複チェックの対象外）</t>
         </is>
       </c>
-      <c r="I60" s="17" t="n"/>
+      <c r="I60" s="4" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="17" t="n"/>
-      <c r="B61" s="17" t="n"/>
-      <c r="C61" s="18" t="n"/>
-      <c r="D61" s="18" t="n"/>
+      <c r="A61" s="4" t="n"/>
+      <c r="B61" s="4" t="n"/>
+      <c r="C61" s="5" t="n"/>
+      <c r="D61" s="5" t="n"/>
       <c r="E61" s="3" t="inlineStr">
         <is>
           <t>3-4-6</t>
@@ -2449,11 +2449,11 @@
           <t>書籍情報が更新され、書籍詳細画面に遷移し「「(タイトル)」の情報を更新しました。」と表示される</t>
         </is>
       </c>
-      <c r="I61" s="18" t="n"/>
+      <c r="I61" s="5" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="17" t="n"/>
-      <c r="B62" s="17" t="n"/>
+      <c r="A62" s="4" t="n"/>
+      <c r="B62" s="4" t="n"/>
       <c r="C62" s="3" t="inlineStr">
         <is>
           <t>3-5</t>
@@ -2491,10 +2491,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="17" t="n"/>
-      <c r="B63" s="17" t="n"/>
-      <c r="C63" s="17" t="n"/>
-      <c r="D63" s="17" t="n"/>
+      <c r="A63" s="4" t="n"/>
+      <c r="B63" s="4" t="n"/>
+      <c r="C63" s="4" t="n"/>
+      <c r="D63" s="4" t="n"/>
       <c r="E63" s="3" t="inlineStr">
         <is>
           <t>3-5-2</t>
@@ -2516,13 +2516,13 @@
           <t>「削除」ボタンが表示されず、削除できない（直接リクエストを送っても403Forbiddenになる）</t>
         </is>
       </c>
-      <c r="I63" s="17" t="n"/>
+      <c r="I63" s="4" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="17" t="n"/>
-      <c r="B64" s="17" t="n"/>
-      <c r="C64" s="17" t="n"/>
-      <c r="D64" s="17" t="n"/>
+      <c r="A64" s="4" t="n"/>
+      <c r="B64" s="4" t="n"/>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
       <c r="E64" s="3" t="inlineStr">
         <is>
           <t>3-5-3</t>
@@ -2544,13 +2544,13 @@
           <t>「本当に削除しますか？」という確認ダイアログが表示される</t>
         </is>
       </c>
-      <c r="I64" s="17" t="n"/>
+      <c r="I64" s="4" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n"/>
-      <c r="B65" s="18" t="n"/>
-      <c r="C65" s="18" t="n"/>
-      <c r="D65" s="18" t="n"/>
+      <c r="A65" s="5" t="n"/>
+      <c r="B65" s="5" t="n"/>
+      <c r="C65" s="5" t="n"/>
+      <c r="D65" s="5" t="n"/>
       <c r="E65" s="3" t="inlineStr">
         <is>
           <t>3-5-4</t>
@@ -2572,7 +2572,7 @@
           <t>書籍が削除され、書籍一覧画面に遷移し「書籍を削除しました。」と表示される</t>
         </is>
       </c>
-      <c r="I65" s="18" t="n"/>
+      <c r="I65" s="5" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
@@ -2622,10 +2622,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="17" t="n"/>
-      <c r="B67" s="17" t="n"/>
-      <c r="C67" s="17" t="n"/>
-      <c r="D67" s="17" t="n"/>
+      <c r="A67" s="4" t="n"/>
+      <c r="B67" s="4" t="n"/>
+      <c r="C67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
       <c r="E67" s="3" t="inlineStr">
         <is>
           <t>4-1-2</t>
@@ -2646,13 +2646,13 @@
           <t>「まだレビューはありません。」と表示される</t>
         </is>
       </c>
-      <c r="I67" s="17" t="n"/>
+      <c r="I67" s="4" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="17" t="n"/>
-      <c r="B68" s="17" t="n"/>
-      <c r="C68" s="17" t="n"/>
-      <c r="D68" s="17" t="n"/>
+      <c r="A68" s="4" t="n"/>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
       <c r="E68" s="3" t="inlineStr">
         <is>
           <t>4-1-3</t>
@@ -2673,13 +2673,13 @@
           <t>「レビューを投稿するにはログインしてください。」と表示され、投稿フォームは表示されない</t>
         </is>
       </c>
-      <c r="I68" s="17" t="n"/>
+      <c r="I68" s="4" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="17" t="n"/>
-      <c r="B69" s="17" t="n"/>
-      <c r="C69" s="18" t="n"/>
-      <c r="D69" s="18" t="n"/>
+      <c r="A69" s="4" t="n"/>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="5" t="n"/>
       <c r="E69" s="3" t="inlineStr">
         <is>
           <t>4-1-4</t>
@@ -2700,11 +2700,11 @@
           <t>「この書籍に対するあなたのレビューはすでに投稿されています。レビューは1書籍に1つまでです。」と表示され、投稿フォームは表示されない</t>
         </is>
       </c>
-      <c r="I69" s="18" t="n"/>
+      <c r="I69" s="5" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="17" t="n"/>
-      <c r="B70" s="17" t="n"/>
+      <c r="A70" s="4" t="n"/>
+      <c r="B70" s="4" t="n"/>
       <c r="C70" s="3" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -2743,10 +2743,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="17" t="n"/>
-      <c r="B71" s="17" t="n"/>
-      <c r="C71" s="17" t="n"/>
-      <c r="D71" s="17" t="n"/>
+      <c r="A71" s="4" t="n"/>
+      <c r="B71" s="4" t="n"/>
+      <c r="C71" s="4" t="n"/>
+      <c r="D71" s="4" t="n"/>
       <c r="E71" s="3" t="inlineStr">
         <is>
           <t>4-2-2</t>
@@ -2768,13 +2768,13 @@
           <t>「コメントは255文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I71" s="17" t="n"/>
+      <c r="I71" s="4" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="17" t="n"/>
-      <c r="B72" s="17" t="n"/>
-      <c r="C72" s="17" t="n"/>
-      <c r="D72" s="17" t="n"/>
+      <c r="A72" s="4" t="n"/>
+      <c r="B72" s="4" t="n"/>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="4" t="n"/>
       <c r="E72" s="3" t="inlineStr">
         <is>
           <t>4-2-3</t>
@@ -2796,13 +2796,13 @@
           <t>「コメントを入力してください」というバリデーションメッセージが表示され、レビューは投稿されない（コメントは必須項目）</t>
         </is>
       </c>
-      <c r="I72" s="17" t="n"/>
+      <c r="I72" s="4" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="17" t="n"/>
-      <c r="B73" s="17" t="n"/>
-      <c r="C73" s="17" t="n"/>
-      <c r="D73" s="17" t="n"/>
+      <c r="A73" s="4" t="n"/>
+      <c r="B73" s="4" t="n"/>
+      <c r="C73" s="4" t="n"/>
+      <c r="D73" s="4" t="n"/>
       <c r="E73" s="3" t="inlineStr">
         <is>
           <t>4-2-4</t>
@@ -2824,13 +2824,13 @@
           <t>レビューが投稿され、「レビューを投稿しました。」と表示されるとともにレビュー一覧に反映される</t>
         </is>
       </c>
-      <c r="I73" s="17" t="n"/>
+      <c r="I73" s="4" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="17" t="n"/>
-      <c r="B74" s="17" t="n"/>
-      <c r="C74" s="18" t="n"/>
-      <c r="D74" s="18" t="n"/>
+      <c r="A74" s="4" t="n"/>
+      <c r="B74" s="4" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="5" t="n"/>
       <c r="E74" s="3" t="inlineStr">
         <is>
           <t>4-2-5</t>
@@ -2851,11 +2851,11 @@
           <t>投稿できず、エラーになる（403Forbidden）。レビューは1書籍につき1人1件までしか投稿できない</t>
         </is>
       </c>
-      <c r="I74" s="18" t="n"/>
+      <c r="I74" s="5" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="17" t="n"/>
-      <c r="B75" s="17" t="n"/>
+      <c r="A75" s="4" t="n"/>
+      <c r="B75" s="4" t="n"/>
       <c r="C75" s="3" t="inlineStr">
         <is>
           <t>4-3</t>
@@ -2893,10 +2893,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="17" t="n"/>
-      <c r="B76" s="17" t="n"/>
-      <c r="C76" s="17" t="n"/>
-      <c r="D76" s="17" t="n"/>
+      <c r="A76" s="4" t="n"/>
+      <c r="B76" s="4" t="n"/>
+      <c r="C76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
       <c r="E76" s="3" t="inlineStr">
         <is>
           <t>4-3-2</t>
@@ -2917,13 +2917,13 @@
           <t>レビュー編集ページに現在の評価（星）とコメントが表示される</t>
         </is>
       </c>
-      <c r="I76" s="17" t="n"/>
+      <c r="I76" s="4" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="17" t="n"/>
-      <c r="B77" s="17" t="n"/>
-      <c r="C77" s="17" t="n"/>
-      <c r="D77" s="17" t="n"/>
+      <c r="A77" s="4" t="n"/>
+      <c r="B77" s="4" t="n"/>
+      <c r="C77" s="4" t="n"/>
+      <c r="D77" s="4" t="n"/>
       <c r="E77" s="3" t="inlineStr">
         <is>
           <t>4-3-3</t>
@@ -2945,13 +2945,13 @@
           <t>「評価を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I77" s="17" t="n"/>
+      <c r="I77" s="4" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="17" t="n"/>
-      <c r="B78" s="17" t="n"/>
-      <c r="C78" s="17" t="n"/>
-      <c r="D78" s="17" t="n"/>
+      <c r="A78" s="4" t="n"/>
+      <c r="B78" s="4" t="n"/>
+      <c r="C78" s="4" t="n"/>
+      <c r="D78" s="4" t="n"/>
       <c r="E78" s="3" t="inlineStr">
         <is>
           <t>4-3-4</t>
@@ -2973,13 +2973,13 @@
           <t>「コメントは255文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I78" s="17" t="n"/>
+      <c r="I78" s="4" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="17" t="n"/>
-      <c r="B79" s="17" t="n"/>
-      <c r="C79" s="17" t="n"/>
-      <c r="D79" s="17" t="n"/>
+      <c r="A79" s="4" t="n"/>
+      <c r="B79" s="4" t="n"/>
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="4" t="n"/>
       <c r="E79" s="3" t="inlineStr">
         <is>
           <t>4-3-5</t>
@@ -3000,13 +3000,13 @@
           <t>更新できず、エラーになる（403Forbidden）</t>
         </is>
       </c>
-      <c r="I79" s="17" t="n"/>
+      <c r="I79" s="4" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="17" t="n"/>
-      <c r="B80" s="17" t="n"/>
-      <c r="C80" s="17" t="n"/>
-      <c r="D80" s="17" t="n"/>
+      <c r="A80" s="4" t="n"/>
+      <c r="B80" s="4" t="n"/>
+      <c r="C80" s="4" t="n"/>
+      <c r="D80" s="4" t="n"/>
       <c r="E80" s="3" t="inlineStr">
         <is>
           <t>4-3-6</t>
@@ -3028,13 +3028,13 @@
           <t>レビューが更新され、書籍詳細画面に遷移し「レビューを更新しました。」と表示される</t>
         </is>
       </c>
-      <c r="I80" s="17" t="n"/>
+      <c r="I80" s="4" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="17" t="n"/>
-      <c r="B81" s="17" t="n"/>
-      <c r="C81" s="18" t="n"/>
-      <c r="D81" s="18" t="n"/>
+      <c r="A81" s="4" t="n"/>
+      <c r="B81" s="4" t="n"/>
+      <c r="C81" s="5" t="n"/>
+      <c r="D81" s="5" t="n"/>
       <c r="E81" s="3" t="inlineStr">
         <is>
           <t>4-3-7</t>
@@ -3056,11 +3056,11 @@
           <t>「コメントを入力してください」というバリデーションメッセージが表示され、レビューは更新されない（コメントは必須項目）</t>
         </is>
       </c>
-      <c r="I81" s="18" t="n"/>
+      <c r="I81" s="5" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="17" t="n"/>
-      <c r="B82" s="17" t="n"/>
+      <c r="A82" s="4" t="n"/>
+      <c r="B82" s="4" t="n"/>
       <c r="C82" s="3" t="inlineStr">
         <is>
           <t>4-4</t>
@@ -3098,10 +3098,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="17" t="n"/>
-      <c r="B83" s="17" t="n"/>
-      <c r="C83" s="17" t="n"/>
-      <c r="D83" s="17" t="n"/>
+      <c r="A83" s="4" t="n"/>
+      <c r="B83" s="4" t="n"/>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="n"/>
       <c r="E83" s="3" t="inlineStr">
         <is>
           <t>4-4-2</t>
@@ -3122,13 +3122,13 @@
           <t>削除できず、エラーになる（403Forbidden）</t>
         </is>
       </c>
-      <c r="I83" s="17" t="n"/>
+      <c r="I83" s="4" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="17" t="n"/>
-      <c r="B84" s="17" t="n"/>
-      <c r="C84" s="17" t="n"/>
-      <c r="D84" s="17" t="n"/>
+      <c r="A84" s="4" t="n"/>
+      <c r="B84" s="4" t="n"/>
+      <c r="C84" s="4" t="n"/>
+      <c r="D84" s="4" t="n"/>
       <c r="E84" s="3" t="inlineStr">
         <is>
           <t>4-4-3</t>
@@ -3149,13 +3149,13 @@
           <t>「本当に削除しますか？」という確認ダイアログが表示される</t>
         </is>
       </c>
-      <c r="I84" s="17" t="n"/>
+      <c r="I84" s="4" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="18" t="n"/>
-      <c r="B85" s="18" t="n"/>
-      <c r="C85" s="18" t="n"/>
-      <c r="D85" s="18" t="n"/>
+      <c r="A85" s="5" t="n"/>
+      <c r="B85" s="5" t="n"/>
+      <c r="C85" s="5" t="n"/>
+      <c r="D85" s="5" t="n"/>
       <c r="E85" s="3" t="inlineStr">
         <is>
           <t>4-4-4</t>
@@ -3176,7 +3176,7 @@
           <t>レビューが削除され、「レビューを削除しました。」と表示されるとともに一覧から消える</t>
         </is>
       </c>
-      <c r="I85" s="18" t="n"/>
+      <c r="I85" s="5" t="n"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -3226,10 +3226,10 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="17" t="n"/>
-      <c r="B87" s="17" t="n"/>
-      <c r="C87" s="17" t="n"/>
-      <c r="D87" s="17" t="n"/>
+      <c r="A87" s="4" t="n"/>
+      <c r="B87" s="4" t="n"/>
+      <c r="C87" s="4" t="n"/>
+      <c r="D87" s="4" t="n"/>
       <c r="E87" s="3" t="inlineStr">
         <is>
           <t>5-1-2</t>
@@ -3250,13 +3250,13 @@
           <t>「ジャンルが登録されていません。」と表示される</t>
         </is>
       </c>
-      <c r="I87" s="17" t="n"/>
+      <c r="I87" s="4" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="17" t="n"/>
-      <c r="B88" s="17" t="n"/>
-      <c r="C88" s="18" t="n"/>
-      <c r="D88" s="18" t="n"/>
+      <c r="A88" s="4" t="n"/>
+      <c r="B88" s="4" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
       <c r="E88" s="3" t="inlineStr">
         <is>
           <t>5-1-3</t>
@@ -3277,11 +3277,11 @@
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I88" s="18" t="n"/>
+      <c r="I88" s="5" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="17" t="n"/>
-      <c r="B89" s="17" t="n"/>
+      <c r="A89" s="4" t="n"/>
+      <c r="B89" s="4" t="n"/>
       <c r="C89" s="3" t="inlineStr">
         <is>
           <t>5-2</t>
@@ -3319,10 +3319,10 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="17" t="n"/>
-      <c r="B90" s="17" t="n"/>
-      <c r="C90" s="17" t="n"/>
-      <c r="D90" s="17" t="n"/>
+      <c r="A90" s="4" t="n"/>
+      <c r="B90" s="4" t="n"/>
+      <c r="C90" s="4" t="n"/>
+      <c r="D90" s="4" t="n"/>
       <c r="E90" s="3" t="inlineStr">
         <is>
           <t>5-2-2</t>
@@ -3344,13 +3344,13 @@
           <t>「ジャンル名を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I90" s="17" t="n"/>
+      <c r="I90" s="4" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="17" t="n"/>
-      <c r="B91" s="17" t="n"/>
-      <c r="C91" s="17" t="n"/>
-      <c r="D91" s="17" t="n"/>
+      <c r="A91" s="4" t="n"/>
+      <c r="B91" s="4" t="n"/>
+      <c r="C91" s="4" t="n"/>
+      <c r="D91" s="4" t="n"/>
       <c r="E91" s="3" t="inlineStr">
         <is>
           <t>5-2-3</t>
@@ -3372,13 +3372,13 @@
           <t>「ジャンル名は20文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I91" s="17" t="n"/>
+      <c r="I91" s="4" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="17" t="n"/>
-      <c r="B92" s="17" t="n"/>
-      <c r="C92" s="17" t="n"/>
-      <c r="D92" s="17" t="n"/>
+      <c r="A92" s="4" t="n"/>
+      <c r="B92" s="4" t="n"/>
+      <c r="C92" s="4" t="n"/>
+      <c r="D92" s="4" t="n"/>
       <c r="E92" s="3" t="inlineStr">
         <is>
           <t>5-2-4</t>
@@ -3400,13 +3400,13 @@
           <t>「このジャンル名はすでに登録されています」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I92" s="17" t="n"/>
+      <c r="I92" s="4" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="17" t="n"/>
-      <c r="B93" s="17" t="n"/>
-      <c r="C93" s="18" t="n"/>
-      <c r="D93" s="18" t="n"/>
+      <c r="A93" s="4" t="n"/>
+      <c r="B93" s="4" t="n"/>
+      <c r="C93" s="5" t="n"/>
+      <c r="D93" s="5" t="n"/>
       <c r="E93" s="3" t="inlineStr">
         <is>
           <t>5-2-5</t>
@@ -3428,11 +3428,11 @@
           <t>ジャンルが登録され、ジャンル一覧画面に遷移し「ジャンルを登録しました。」と表示される</t>
         </is>
       </c>
-      <c r="I93" s="18" t="n"/>
+      <c r="I93" s="5" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="17" t="n"/>
-      <c r="B94" s="17" t="n"/>
+      <c r="A94" s="4" t="n"/>
+      <c r="B94" s="4" t="n"/>
       <c r="C94" s="3" t="inlineStr">
         <is>
           <t>5-3</t>
@@ -3470,10 +3470,10 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="17" t="n"/>
-      <c r="B95" s="17" t="n"/>
-      <c r="C95" s="18" t="n"/>
-      <c r="D95" s="18" t="n"/>
+      <c r="A95" s="4" t="n"/>
+      <c r="B95" s="4" t="n"/>
+      <c r="C95" s="4" t="n"/>
+      <c r="D95" s="4" t="n"/>
       <c r="E95" s="3" t="inlineStr">
         <is>
           <t>5-3-2</t>
@@ -3494,5151 +3494,5319 @@
           <t>「このジャンルの書籍はまだ登録されていません。」と表示される</t>
         </is>
       </c>
-      <c r="I95" s="18" t="n"/>
+      <c r="I95" s="4" t="n"/>
     </row>
     <row r="96">
-      <c r="A96" s="17" t="n"/>
-      <c r="B96" s="17" t="n"/>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="A96" s="4" t="n"/>
+      <c r="B96" s="4" t="n"/>
+      <c r="C96" s="4" t="n"/>
+      <c r="D96" s="4" t="n"/>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>5-3-3</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="inlineStr">
+        <is>
+          <t>ジャンル一覧から遷移した場合、「ジャンル一覧に戻る」リンクが表示される</t>
+        </is>
+      </c>
+      <c r="G96" s="3" t="inlineStr">
+        <is>
+          <t>1.ジャンル一覧ページでジャンル名のリンクを押し、ジャンル詳細ページを開く
+2.画面左上の戻るリンクを確認する</t>
+        </is>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>「← ジャンル一覧に戻る」と表示され、押すとジャンル一覧ページへ遷移する（遷移元の指定がない場合も同様）</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n"/>
+      <c r="B97" s="4" t="n"/>
+      <c r="C97" s="4" t="n"/>
+      <c r="D97" s="4" t="n"/>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>5-3-4</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="inlineStr">
+        <is>
+          <t>マイ読書レポートから遷移した場合、「マイ読書レポートに戻る」リンクが表示される</t>
+        </is>
+      </c>
+      <c r="G97" s="3" t="inlineStr">
+        <is>
+          <t>1.マイ読書レポートページの「ジャンル別評価傾向 TOP5」でジャンルを押し、ジャンル詳細ページを開く
+2.画面左上の戻るリンクを確認する</t>
+        </is>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>「← マイ読書レポートに戻る」と表示され、押すとマイ読書レポートページへ遷移する</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n"/>
+      <c r="B98" s="4" t="n"/>
+      <c r="C98" s="4" t="n"/>
+      <c r="D98" s="4" t="n"/>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>5-3-5</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="inlineStr">
+        <is>
+          <t>ページを送っても、遷移元に応じた「戻る」リンクが維持される</t>
+        </is>
+      </c>
+      <c r="G98" s="3" t="inlineStr">
+        <is>
+          <t>1.書籍が11件以上紐づくジャンルの詳細ページを、マイ読書レポートから開く
+2.ページネーションで2ページ目を開く</t>
+        </is>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>2ページ目でも「← マイ読書レポートに戻る」と表示される</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n"/>
+      <c r="B99" s="4" t="n"/>
+      <c r="C99" s="5" t="n"/>
+      <c r="D99" s="5" t="n"/>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>5-3-6</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="inlineStr">
+        <is>
+          <t>ジャンルに紐づく書籍が登録日時の新しい順に表示される</t>
+        </is>
+      </c>
+      <c r="G99" s="3" t="inlineStr">
+        <is>
+          <t>1.登録日時の異なる複数の書籍を、同じジャンルに紐づける
+2.ジャンル詳細ページを開く</t>
+        </is>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>書籍一覧と同じく、書籍の登録日時の新しい順に表示される（ジャンルへの紐づけ順には関係しない）</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n"/>
+      <c r="B100" s="4" t="n"/>
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>5-4</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>ジャンル編集</t>
         </is>
       </c>
-      <c r="E96" s="3" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>5-4-1</t>
         </is>
       </c>
-      <c r="F96" s="3" t="inlineStr">
+      <c r="F100" s="3" t="inlineStr">
         <is>
           <t>未ログインの場合、ジャンル編集ページにアクセスできない</t>
         </is>
       </c>
-      <c r="G96" s="3" t="inlineStr">
+      <c r="G100" s="3" t="inlineStr">
         <is>
           <t>1.未ログイン状態でジャンル編集ページのURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H96" s="3" t="inlineStr">
+      <c r="H100" s="3" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I96" s="3" t="inlineStr">
+      <c r="I100" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Genre/GenreUpdateTest.php</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="17" t="n"/>
-      <c r="B97" s="17" t="n"/>
-      <c r="C97" s="17" t="n"/>
-      <c r="D97" s="17" t="n"/>
-      <c r="E97" s="3" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="4" t="n"/>
+      <c r="B101" s="4" t="n"/>
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="4" t="n"/>
+      <c r="E101" s="3" t="inlineStr">
         <is>
           <t>5-4-2</t>
         </is>
       </c>
-      <c r="F97" s="3" t="inlineStr">
+      <c r="F101" s="3" t="inlineStr">
         <is>
           <t>編集画面を開くと現在のジャンル名が初期表示される</t>
         </is>
       </c>
-      <c r="G97" s="3" t="inlineStr">
+      <c r="G101" s="3" t="inlineStr">
         <is>
           <t>1.ジャンル編集ページを開く</t>
         </is>
       </c>
-      <c r="H97" s="3" t="inlineStr">
+      <c r="H101" s="3" t="inlineStr">
         <is>
           <t>ジャンル名の入力欄に現在登録されているジャンル名が表示される</t>
         </is>
       </c>
-      <c r="I97" s="17" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="17" t="n"/>
-      <c r="B98" s="17" t="n"/>
-      <c r="C98" s="17" t="n"/>
-      <c r="D98" s="17" t="n"/>
-      <c r="E98" s="3" t="inlineStr">
+      <c r="I101" s="4" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n"/>
+      <c r="B102" s="4" t="n"/>
+      <c r="C102" s="4" t="n"/>
+      <c r="D102" s="4" t="n"/>
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>5-4-3</t>
         </is>
       </c>
-      <c r="F98" s="3" t="inlineStr">
+      <c r="F102" s="3" t="inlineStr">
         <is>
           <t>ジャンル名が入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G98" s="3" t="inlineStr">
+      <c r="G102" s="3" t="inlineStr">
         <is>
           <t>1.ジャンル編集ページを開く
 2.ジャンル名を空にして更新ボタンを押す</t>
         </is>
       </c>
-      <c r="H98" s="3" t="inlineStr">
+      <c r="H102" s="3" t="inlineStr">
         <is>
           <t>「ジャンル名を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I98" s="17" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="17" t="n"/>
-      <c r="B99" s="17" t="n"/>
-      <c r="C99" s="17" t="n"/>
-      <c r="D99" s="17" t="n"/>
-      <c r="E99" s="3" t="inlineStr">
+      <c r="I102" s="4" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n"/>
+      <c r="B103" s="4" t="n"/>
+      <c r="C103" s="4" t="n"/>
+      <c r="D103" s="4" t="n"/>
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>5-4-4</t>
         </is>
       </c>
-      <c r="F99" s="3" t="inlineStr">
+      <c r="F103" s="3" t="inlineStr">
         <is>
           <t>既に登録されている他のジャンル名に変更しようとした場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G99" s="3" t="inlineStr">
+      <c r="G103" s="3" t="inlineStr">
         <is>
           <t>1.ジャンル編集ページを開く
 2.他のジャンルで既に使われているジャンル名に変更し、更新ボタンを押す</t>
         </is>
       </c>
-      <c r="H99" s="3" t="inlineStr">
+      <c r="H103" s="3" t="inlineStr">
         <is>
           <t>「このジャンル名はすでに登録されています」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I99" s="17" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="17" t="n"/>
-      <c r="B100" s="17" t="n"/>
-      <c r="C100" s="18" t="n"/>
-      <c r="D100" s="18" t="n"/>
-      <c r="E100" s="3" t="inlineStr">
+      <c r="I103" s="4" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n"/>
+      <c r="B104" s="4" t="n"/>
+      <c r="C104" s="5" t="n"/>
+      <c r="D104" s="5" t="n"/>
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>5-4-5</t>
         </is>
       </c>
-      <c r="F100" s="3" t="inlineStr">
+      <c r="F104" s="3" t="inlineStr">
         <is>
           <t>正しくジャンル名が入力されている場合、ジャンル情報が更新される</t>
         </is>
       </c>
-      <c r="G100" s="3" t="inlineStr">
+      <c r="G104" s="3" t="inlineStr">
         <is>
           <t>1.ジャンル編集ページを開く
 2.ジャンル名を正しく変更し、更新ボタンを押す</t>
         </is>
       </c>
-      <c r="H100" s="3" t="inlineStr">
+      <c r="H104" s="3" t="inlineStr">
         <is>
           <t>ジャンル情報が更新され、ジャンル一覧画面に遷移し「ジャンルを更新しました。」と表示される</t>
         </is>
       </c>
-      <c r="I100" s="18" t="n"/>
-    </row>
-    <row r="101">
-      <c r="A101" s="17" t="n"/>
-      <c r="B101" s="17" t="n"/>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="I104" s="5" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n"/>
+      <c r="B105" s="4" t="n"/>
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>5-5</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>ジャンル削除</t>
         </is>
       </c>
-      <c r="E101" s="3" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>5-5-1</t>
         </is>
       </c>
-      <c r="F101" s="3" t="inlineStr">
+      <c r="F105" s="3" t="inlineStr">
         <is>
           <t>未ログインの場合、ジャンルを削除できない</t>
         </is>
       </c>
-      <c r="G101" s="3" t="inlineStr">
+      <c r="G105" s="3" t="inlineStr">
         <is>
           <t>1.未ログイン状態でジャンル削除のリクエストを直接送信する</t>
         </is>
       </c>
-      <c r="H101" s="3" t="inlineStr">
+      <c r="H105" s="3" t="inlineStr">
         <is>
           <t>削除できず、ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I101" s="3" t="inlineStr">
+      <c r="I105" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Genre/GenreDestroyTest.php</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="17" t="n"/>
-      <c r="B102" s="17" t="n"/>
-      <c r="C102" s="17" t="n"/>
-      <c r="D102" s="17" t="n"/>
-      <c r="E102" s="3" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="4" t="n"/>
+      <c r="B106" s="4" t="n"/>
+      <c r="C106" s="4" t="n"/>
+      <c r="D106" s="4" t="n"/>
+      <c r="E106" s="3" t="inlineStr">
         <is>
           <t>5-5-2</t>
         </is>
       </c>
-      <c r="F102" s="3" t="inlineStr">
+      <c r="F106" s="3" t="inlineStr">
         <is>
           <t>紐づく書籍が存在するジャンルは削除できない</t>
         </is>
       </c>
-      <c r="G102" s="3" t="inlineStr">
+      <c r="G106" s="3" t="inlineStr">
         <is>
           <t>1.書籍が紐づいているジャンルの削除ボタンを押し、確認ダイアログでOKを押す</t>
         </is>
       </c>
-      <c r="H102" s="3" t="inlineStr">
+      <c r="H106" s="3" t="inlineStr">
         <is>
           <t>「このジャンルは書籍に紐づいているため削除できません。」と表示され、ジャンルは削除されない</t>
         </is>
       </c>
-      <c r="I102" s="17" t="n"/>
-    </row>
-    <row r="103">
-      <c r="A103" s="18" t="n"/>
-      <c r="B103" s="18" t="n"/>
-      <c r="C103" s="18" t="n"/>
-      <c r="D103" s="18" t="n"/>
-      <c r="E103" s="3" t="inlineStr">
+      <c r="I106" s="4" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="n"/>
+      <c r="B107" s="5" t="n"/>
+      <c r="C107" s="5" t="n"/>
+      <c r="D107" s="5" t="n"/>
+      <c r="E107" s="3" t="inlineStr">
         <is>
           <t>5-5-3</t>
         </is>
       </c>
-      <c r="F103" s="3" t="inlineStr">
+      <c r="F107" s="3" t="inlineStr">
         <is>
           <t>紐づく書籍が存在しないジャンルは削除できる</t>
         </is>
       </c>
-      <c r="G103" s="3" t="inlineStr">
+      <c r="G107" s="3" t="inlineStr">
         <is>
           <t>1.書籍が紐づいていないジャンルの削除ボタンを押し、確認ダイアログでOKを押す</t>
         </is>
       </c>
-      <c r="H103" s="3" t="inlineStr">
+      <c r="H107" s="3" t="inlineStr">
         <is>
           <t>ジャンルが削除され、「ジャンルを削除しました。」と表示される</t>
         </is>
       </c>
-      <c r="I103" s="18" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="I107" s="5" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>お気に入り</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>6-1</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>お気に入り一覧表示</t>
         </is>
       </c>
-      <c r="E104" s="3" t="inlineStr">
+      <c r="E108" s="3" t="inlineStr">
         <is>
           <t>6-1-1</t>
         </is>
       </c>
-      <c r="F104" s="3" t="inlineStr">
+      <c r="F108" s="3" t="inlineStr">
         <is>
           <t>お気に入りに登録した書籍が一覧表示される</t>
         </is>
       </c>
-      <c r="G104" s="3" t="inlineStr">
+      <c r="G108" s="3" t="inlineStr">
         <is>
           <t>1.書籍をお気に入り登録した状態でお気に入り一覧ページを開く</t>
         </is>
       </c>
-      <c r="H104" s="3" t="inlineStr">
+      <c r="H108" s="3" t="inlineStr">
         <is>
           <t>お気に入り登録した書籍が一覧表示される</t>
         </is>
       </c>
-      <c r="I104" s="3" t="inlineStr">
+      <c r="I108" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Favorite/FavoriteIndexTest.php</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="17" t="n"/>
-      <c r="B105" s="17" t="n"/>
-      <c r="C105" s="17" t="n"/>
-      <c r="D105" s="17" t="n"/>
-      <c r="E105" s="3" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="4" t="n"/>
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="4" t="n"/>
+      <c r="D109" s="4" t="n"/>
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>6-1-2</t>
         </is>
       </c>
-      <c r="F105" s="3" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr">
         <is>
           <t>お気に入りが1件も登録されていない場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G105" s="3" t="inlineStr">
+      <c r="G109" s="3" t="inlineStr">
         <is>
           <t>1.お気に入りを1件も登録していない状態でお気に入り一覧ページを開く</t>
         </is>
       </c>
-      <c r="H105" s="3" t="inlineStr">
+      <c r="H109" s="3" t="inlineStr">
         <is>
           <t>「お気に入りに登録された書籍はありません。」と表示され、書籍一覧ページへのリンクが表示される</t>
         </is>
       </c>
-      <c r="I105" s="17" t="n"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="17" t="n"/>
-      <c r="B106" s="17" t="n"/>
-      <c r="C106" s="18" t="n"/>
-      <c r="D106" s="18" t="n"/>
-      <c r="E106" s="3" t="inlineStr">
+      <c r="I109" s="4" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="n"/>
+      <c r="B110" s="4" t="n"/>
+      <c r="C110" s="4" t="n"/>
+      <c r="D110" s="4" t="n"/>
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>6-1-3</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr">
         <is>
           <t>未ログインの場合、お気に入り一覧ページにアクセスできない</t>
         </is>
       </c>
-      <c r="G106" s="3" t="inlineStr">
+      <c r="G110" s="3" t="inlineStr">
         <is>
           <t>1.未ログイン状態でお気に入り一覧ページのURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
+      <c r="H110" s="3" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I106" s="18" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="17" t="n"/>
-      <c r="B107" s="17" t="n"/>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="I110" s="4" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n"/>
+      <c r="B111" s="4" t="n"/>
+      <c r="C111" s="5" t="n"/>
+      <c r="D111" s="5" t="n"/>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>6-1-4</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="inlineStr">
+        <is>
+          <t>お気に入りに登録した日時の新しい順に表示される</t>
+        </is>
+      </c>
+      <c r="G111" s="3" t="inlineStr">
+        <is>
+          <t>1.複数の書籍を、時間をずらしてお気に入り登録する
+2.お気に入り一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>お気に入りに登録した日時の新しい順に表示される（書籍自体の登録日時の順ではない）</t>
+        </is>
+      </c>
+      <c r="I111" s="5" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n"/>
+      <c r="B112" s="4" t="n"/>
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>6-2</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>お気に入りの登録・解除</t>
         </is>
       </c>
-      <c r="E107" s="3" t="inlineStr">
+      <c r="E112" s="3" t="inlineStr">
         <is>
           <t>6-2-1</t>
         </is>
       </c>
-      <c r="F107" s="3" t="inlineStr">
+      <c r="F112" s="3" t="inlineStr">
         <is>
           <t>未登録の書籍をお気に入りに登録できる</t>
         </is>
       </c>
-      <c r="G107" s="3" t="inlineStr">
+      <c r="G112" s="3" t="inlineStr">
         <is>
           <t>1.お気に入り未登録の書籍の詳細ページ（またはお気に入り一覧）を開く
 2.お気に入りボタン（ハートアイコン）を押す</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr">
+      <c r="H112" s="3" t="inlineStr">
         <is>
           <t>お気に入りに登録され、アイコンが登録済みの表示(塗りつぶし)に切り替わる</t>
         </is>
       </c>
-      <c r="I107" s="3" t="inlineStr">
+      <c r="I112" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Favorite/FavoriteToggleTest.php</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="17" t="n"/>
-      <c r="B108" s="17" t="n"/>
-      <c r="C108" s="17" t="n"/>
-      <c r="D108" s="17" t="n"/>
-      <c r="E108" s="3" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="4" t="n"/>
+      <c r="B113" s="4" t="n"/>
+      <c r="C113" s="4" t="n"/>
+      <c r="D113" s="4" t="n"/>
+      <c r="E113" s="3" t="inlineStr">
         <is>
           <t>6-2-2</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr">
+      <c r="F113" s="3" t="inlineStr">
         <is>
           <t>登録済みの書籍のお気に入りを解除できる</t>
         </is>
       </c>
-      <c r="G108" s="3" t="inlineStr">
+      <c r="G113" s="3" t="inlineStr">
         <is>
           <t>1.お気に入り登録済みの書籍の詳細ページ（またはお気に入り一覧）を開く
 2.お気に入りボタン（ハートアイコン）を押す</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
+      <c r="H113" s="3" t="inlineStr">
         <is>
           <t>お気に入りが解除され、アイコンが未登録の表示に切り替わる（お気に入り一覧では一覧から消える）</t>
         </is>
       </c>
-      <c r="I108" s="17" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="18" t="n"/>
-      <c r="B109" s="18" t="n"/>
-      <c r="C109" s="18" t="n"/>
-      <c r="D109" s="18" t="n"/>
-      <c r="E109" s="3" t="inlineStr">
+      <c r="I113" s="4" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="n"/>
+      <c r="B114" s="5" t="n"/>
+      <c r="C114" s="5" t="n"/>
+      <c r="D114" s="5" t="n"/>
+      <c r="E114" s="3" t="inlineStr">
         <is>
           <t>6-2-3</t>
         </is>
       </c>
-      <c r="F109" s="3" t="inlineStr">
+      <c r="F114" s="3" t="inlineStr">
         <is>
           <t>未ログインの場合、お気に入りボタンの代わりにログインへの案内が表示される</t>
         </is>
       </c>
-      <c r="G109" s="3" t="inlineStr">
+      <c r="G114" s="3" t="inlineStr">
         <is>
           <t>1.未ログイン状態で書籍詳細ページを開く</t>
         </is>
       </c>
-      <c r="H109" s="3" t="inlineStr">
+      <c r="H114" s="3" t="inlineStr">
         <is>
           <t>お気に入りボタンの代わりに、押すとログインページへ遷移するリンクが表示される</t>
         </is>
       </c>
-      <c r="I109" s="18" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="I114" s="5" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr">
         <is>
           <t>いいね</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C115" s="3" t="inlineStr">
         <is>
           <t>7-1</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D115" s="3" t="inlineStr">
         <is>
           <t>レビューへのいいねの切り替え</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr">
+      <c r="E115" s="3" t="inlineStr">
         <is>
           <t>7-1-1</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr">
+      <c r="F115" s="3" t="inlineStr">
         <is>
           <t>未いいねの状態からいいねできる</t>
         </is>
       </c>
-      <c r="G110" s="3" t="inlineStr">
+      <c r="G115" s="3" t="inlineStr">
         <is>
           <t>1.まだいいねしていないレビューの「いいね」ボタンを押す</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
+      <c r="H115" s="3" t="inlineStr">
         <is>
           <t>「いいね済み」の表示に切り替わり、いいね数が1件増える</t>
         </is>
       </c>
-      <c r="I110" s="3" t="inlineStr">
+      <c r="I115" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Like/LikeToggleTest.php</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="17" t="n"/>
-      <c r="B111" s="17" t="n"/>
-      <c r="C111" s="17" t="n"/>
-      <c r="D111" s="17" t="n"/>
-      <c r="E111" s="3" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="4" t="n"/>
+      <c r="B116" s="4" t="n"/>
+      <c r="C116" s="4" t="n"/>
+      <c r="D116" s="4" t="n"/>
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>7-1-2</t>
         </is>
       </c>
-      <c r="F111" s="3" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr">
         <is>
           <t>いいね済みの状態からいいねを解除できる</t>
         </is>
       </c>
-      <c r="G111" s="3" t="inlineStr">
+      <c r="G116" s="3" t="inlineStr">
         <is>
           <t>1.既にいいね済みのレビューの「いいね済み」ボタンを押す</t>
         </is>
       </c>
-      <c r="H111" s="3" t="inlineStr">
+      <c r="H116" s="3" t="inlineStr">
         <is>
           <t>「いいね」の表示に切り替わり、いいね数が1件減る</t>
         </is>
       </c>
-      <c r="I111" s="17" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="18" t="n"/>
-      <c r="B112" s="18" t="n"/>
-      <c r="C112" s="18" t="n"/>
-      <c r="D112" s="18" t="n"/>
-      <c r="E112" s="3" t="inlineStr">
+      <c r="I116" s="4" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n"/>
+      <c r="B117" s="5" t="n"/>
+      <c r="C117" s="5" t="n"/>
+      <c r="D117" s="5" t="n"/>
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>7-1-3</t>
         </is>
       </c>
-      <c r="F112" s="3" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr">
         <is>
           <t>未ログインの場合、いいねボタンを押せない</t>
         </is>
       </c>
-      <c r="G112" s="3" t="inlineStr">
+      <c r="G117" s="3" t="inlineStr">
         <is>
           <t>1.未ログイン状態で書籍詳細ページを開く
 2.いいねに関する直接リクエストを送信する</t>
         </is>
       </c>
-      <c r="H112" s="3" t="inlineStr">
+      <c r="H117" s="3" t="inlineStr">
         <is>
           <t>未ログインの場合はいいねボタンが操作できず、直接リクエストを送ってもログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I112" s="18" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="3" t="inlineStr">
+      <c r="I117" s="5" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>ランキング</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>8-1</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>ランキングページ表示</t>
         </is>
       </c>
-      <c r="E113" s="3" t="inlineStr">
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>8-1-1</t>
         </is>
       </c>
-      <c r="F113" s="3" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr">
         <is>
           <t>レビューの平均評価が高い順に書籍が表示される</t>
         </is>
       </c>
-      <c r="G113" s="3" t="inlineStr">
+      <c r="G118" s="3" t="inlineStr">
         <is>
           <t>1.複数の書籍にレビューを投稿する
 2.ランキングページを開く</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
+      <c r="H118" s="3" t="inlineStr">
         <is>
           <t>レビューが投稿されている書籍が、平均評価の高い順に上位10件表示される</t>
         </is>
       </c>
-      <c r="I113" s="3" t="inlineStr">
+      <c r="I118" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Ranking/RankingIndexTest.php</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="17" t="n"/>
-      <c r="B114" s="17" t="n"/>
-      <c r="C114" s="17" t="n"/>
-      <c r="D114" s="17" t="n"/>
-      <c r="E114" s="3" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="4" t="n"/>
+      <c r="B119" s="4" t="n"/>
+      <c r="C119" s="4" t="n"/>
+      <c r="D119" s="4" t="n"/>
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>8-1-2</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr">
         <is>
           <t>平均評価が同じ場合、レビュー件数が多い順に表示される</t>
         </is>
       </c>
-      <c r="G114" s="3" t="inlineStr">
+      <c r="G119" s="3" t="inlineStr">
         <is>
           <t>1.平均評価が同じになる書籍を複数用意する（レビュー件数を変える）
 2.ランキングページを開く</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
+      <c r="H119" s="3" t="inlineStr">
         <is>
           <t>平均評価が同じ書籍同士は、レビュー件数が多い順（さらに同じ場合は出版日が新しい順）に表示される</t>
         </is>
       </c>
-      <c r="I114" s="17" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="17" t="n"/>
-      <c r="B115" s="17" t="n"/>
-      <c r="C115" s="17" t="n"/>
-      <c r="D115" s="17" t="n"/>
-      <c r="E115" s="3" t="inlineStr">
+      <c r="I119" s="4" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="n"/>
+      <c r="B120" s="4" t="n"/>
+      <c r="C120" s="4" t="n"/>
+      <c r="D120" s="4" t="n"/>
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>8-1-3</t>
         </is>
       </c>
-      <c r="F115" s="3" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr">
         <is>
           <t>レビューが投稿された書籍が1件もない場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G115" s="3" t="inlineStr">
+      <c r="G120" s="3" t="inlineStr">
         <is>
           <t>1.どの書籍にもレビューが投稿されていない状態でランキングページを開く</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr">
+      <c r="H120" s="3" t="inlineStr">
         <is>
           <t>「まだレビューが投稿された書籍がありません。」と表示される</t>
         </is>
       </c>
-      <c r="I115" s="17" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="18" t="n"/>
-      <c r="B116" s="18" t="n"/>
-      <c r="C116" s="18" t="n"/>
-      <c r="D116" s="18" t="n"/>
-      <c r="E116" s="3" t="inlineStr">
+      <c r="I120" s="4" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="n"/>
+      <c r="B121" s="5" t="n"/>
+      <c r="C121" s="5" t="n"/>
+      <c r="D121" s="5" t="n"/>
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>8-1-4</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>未ログインの状態でもランキングページを閲覧できる</t>
         </is>
       </c>
-      <c r="G116" s="3" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr">
         <is>
           <t>1.未ログイン状態でランキングページを開く</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
+      <c r="H121" s="3" t="inlineStr">
         <is>
           <t>ランキングが表示される</t>
         </is>
       </c>
-      <c r="I116" s="18" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="I121" s="5" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t>認証</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>9-1</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>会員登録</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>9-1-1</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
+      <c r="F122" s="3" t="inlineStr">
         <is>
           <t>名前が入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G117" s="3" t="inlineStr">
+      <c r="G122" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.名前を入力せずに他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
+      <c r="H122" s="3" t="inlineStr">
         <is>
           <t>「お名前を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I117" s="3" t="inlineStr">
+      <c r="I122" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Auth/RegisterTest.php</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="17" t="n"/>
-      <c r="B118" s="17" t="n"/>
-      <c r="C118" s="17" t="n"/>
-      <c r="D118" s="17" t="n"/>
-      <c r="E118" s="3" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="4" t="n"/>
+      <c r="B123" s="4" t="n"/>
+      <c r="C123" s="4" t="n"/>
+      <c r="D123" s="4" t="n"/>
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>9-1-2</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>名前が21文字以上の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G118" s="3" t="inlineStr">
+      <c r="G123" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.名前を21文字以上入力し、他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
+      <c r="H123" s="3" t="inlineStr">
         <is>
           <t>「お名前は20文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I118" s="17" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="17" t="n"/>
-      <c r="B119" s="17" t="n"/>
-      <c r="C119" s="17" t="n"/>
-      <c r="D119" s="17" t="n"/>
-      <c r="E119" s="3" t="inlineStr">
+      <c r="I123" s="4" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="n"/>
+      <c r="B124" s="4" t="n"/>
+      <c r="C124" s="4" t="n"/>
+      <c r="D124" s="4" t="n"/>
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>9-1-3</t>
         </is>
       </c>
-      <c r="F119" s="3" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr">
         <is>
           <t>メールアドレスが入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G119" s="3" t="inlineStr">
+      <c r="G124" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.メールアドレスを入力せずに他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
+      <c r="H124" s="3" t="inlineStr">
         <is>
           <t>「メールアドレスを入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I119" s="17" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="17" t="n"/>
-      <c r="B120" s="17" t="n"/>
-      <c r="C120" s="17" t="n"/>
-      <c r="D120" s="17" t="n"/>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="I124" s="4" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="n"/>
+      <c r="B125" s="4" t="n"/>
+      <c r="C125" s="4" t="n"/>
+      <c r="D125" s="4" t="n"/>
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>9-1-4</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr">
         <is>
           <t>メールアドレスがメール形式でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G120" s="3" t="inlineStr">
+      <c r="G125" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.「abc」のようなメール形式でないメールアドレスと他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
+      <c r="H125" s="3" t="inlineStr">
         <is>
           <t>「メールアドレスはメール形式で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I120" s="17" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="17" t="n"/>
-      <c r="B121" s="17" t="n"/>
-      <c r="C121" s="17" t="n"/>
-      <c r="D121" s="17" t="n"/>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="I125" s="4" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="n"/>
+      <c r="B126" s="4" t="n"/>
+      <c r="C126" s="4" t="n"/>
+      <c r="D126" s="4" t="n"/>
+      <c r="E126" s="3" t="inlineStr">
         <is>
           <t>9-1-5</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr">
+      <c r="F126" s="3" t="inlineStr">
         <is>
           <t>メールアドレスが256文字以上の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G121" s="3" t="inlineStr">
+      <c r="G126" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.256文字以上のメールアドレスと他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H121" s="3" t="inlineStr">
+      <c r="H126" s="3" t="inlineStr">
         <is>
           <t>「メールアドレスは255文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I121" s="17" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="17" t="n"/>
-      <c r="B122" s="17" t="n"/>
-      <c r="C122" s="17" t="n"/>
-      <c r="D122" s="17" t="n"/>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="I126" s="4" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="n"/>
+      <c r="B127" s="4" t="n"/>
+      <c r="C127" s="4" t="n"/>
+      <c r="D127" s="4" t="n"/>
+      <c r="E127" s="3" t="inlineStr">
         <is>
           <t>9-1-6</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="F127" s="3" t="inlineStr">
         <is>
           <t>既に登録されているメールアドレスの場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G122" s="3" t="inlineStr">
+      <c r="G127" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.既に会員登録済みのメールアドレスと他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
+      <c r="H127" s="3" t="inlineStr">
         <is>
           <t>「このメールアドレスはすでに登録されています」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I122" s="17" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="17" t="n"/>
-      <c r="B123" s="17" t="n"/>
-      <c r="C123" s="17" t="n"/>
-      <c r="D123" s="17" t="n"/>
-      <c r="E123" s="3" t="inlineStr">
+      <c r="I127" s="4" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="n"/>
+      <c r="B128" s="4" t="n"/>
+      <c r="C128" s="4" t="n"/>
+      <c r="D128" s="4" t="n"/>
+      <c r="E128" s="3" t="inlineStr">
         <is>
           <t>9-1-7</t>
         </is>
       </c>
-      <c r="F123" s="3" t="inlineStr">
+      <c r="F128" s="3" t="inlineStr">
         <is>
           <t>パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G123" s="3" t="inlineStr">
+      <c r="G128" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.パスワードを入力せずに他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H123" s="3" t="inlineStr">
+      <c r="H128" s="3" t="inlineStr">
         <is>
           <t>「パスワードを入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I123" s="17" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="17" t="n"/>
-      <c r="B124" s="17" t="n"/>
-      <c r="C124" s="17" t="n"/>
-      <c r="D124" s="17" t="n"/>
-      <c r="E124" s="3" t="inlineStr">
+      <c r="I128" s="4" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n"/>
+      <c r="B129" s="4" t="n"/>
+      <c r="C129" s="4" t="n"/>
+      <c r="D129" s="4" t="n"/>
+      <c r="E129" s="3" t="inlineStr">
         <is>
           <t>9-1-8</t>
         </is>
       </c>
-      <c r="F124" s="3" t="inlineStr">
+      <c r="F129" s="3" t="inlineStr">
         <is>
           <t>パスワードが7文字以下の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G124" s="3" t="inlineStr">
+      <c r="G129" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.7文字以下のパスワードと他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
+      <c r="H129" s="3" t="inlineStr">
         <is>
           <t>「パスワードは8文字以上で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I124" s="17" t="n"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="17" t="n"/>
-      <c r="B125" s="17" t="n"/>
-      <c r="C125" s="17" t="n"/>
-      <c r="D125" s="17" t="n"/>
-      <c r="E125" s="3" t="inlineStr">
+      <c r="I129" s="4" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="n"/>
+      <c r="B130" s="4" t="n"/>
+      <c r="C130" s="4" t="n"/>
+      <c r="D130" s="4" t="n"/>
+      <c r="E130" s="3" t="inlineStr">
         <is>
           <t>9-1-9</t>
         </is>
       </c>
-      <c r="F125" s="3" t="inlineStr">
+      <c r="F130" s="3" t="inlineStr">
         <is>
           <t>パスワードが21文字以上の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G125" s="3" t="inlineStr">
+      <c r="G130" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.21文字以上のパスワードと他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H125" s="3" t="inlineStr">
+      <c r="H130" s="3" t="inlineStr">
         <is>
           <t>「パスワードは20文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I125" s="17" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="17" t="n"/>
-      <c r="B126" s="17" t="n"/>
-      <c r="C126" s="17" t="n"/>
-      <c r="D126" s="17" t="n"/>
-      <c r="E126" s="3" t="inlineStr">
+      <c r="I130" s="4" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="n"/>
+      <c r="B131" s="4" t="n"/>
+      <c r="C131" s="4" t="n"/>
+      <c r="D131" s="4" t="n"/>
+      <c r="E131" s="3" t="inlineStr">
         <is>
           <t>9-1-10</t>
         </is>
       </c>
-      <c r="F126" s="3" t="inlineStr">
+      <c r="F131" s="3" t="inlineStr">
         <is>
           <t>確認用パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G126" s="3" t="inlineStr">
+      <c r="G131" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.確認用パスワードを入力せずに他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H126" s="3" t="inlineStr">
+      <c r="H131" s="3" t="inlineStr">
         <is>
           <t>「確認用パスワードを入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I126" s="17" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="17" t="n"/>
-      <c r="B127" s="17" t="n"/>
-      <c r="C127" s="17" t="n"/>
-      <c r="D127" s="17" t="n"/>
-      <c r="E127" s="3" t="inlineStr">
+      <c r="I131" s="4" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n"/>
+      <c r="B132" s="4" t="n"/>
+      <c r="C132" s="4" t="n"/>
+      <c r="D132" s="4" t="n"/>
+      <c r="E132" s="3" t="inlineStr">
         <is>
           <t>9-1-11</t>
         </is>
       </c>
-      <c r="F127" s="3" t="inlineStr">
+      <c r="F132" s="3" t="inlineStr">
         <is>
           <t>パスワードが確認用パスワードと一致しない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G127" s="3" t="inlineStr">
+      <c r="G132" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.確認用パスワードと異なるパスワードを入力し、他の必要項目も入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H127" s="3" t="inlineStr">
+      <c r="H132" s="3" t="inlineStr">
         <is>
           <t>「パスワードが一致しません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I127" s="17" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="17" t="n"/>
-      <c r="B128" s="17" t="n"/>
-      <c r="C128" s="18" t="n"/>
-      <c r="D128" s="18" t="n"/>
-      <c r="E128" s="3" t="inlineStr">
+      <c r="I132" s="4" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="n"/>
+      <c r="B133" s="4" t="n"/>
+      <c r="C133" s="5" t="n"/>
+      <c r="D133" s="5" t="n"/>
+      <c r="E133" s="3" t="inlineStr">
         <is>
           <t>9-1-12</t>
         </is>
       </c>
-      <c r="F128" s="3" t="inlineStr">
+      <c r="F133" s="3" t="inlineStr">
         <is>
           <t>全ての項目が正しく入力されている場合、会員登録が完了する</t>
         </is>
       </c>
-      <c r="G128" s="3" t="inlineStr">
+      <c r="G133" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.全ての必要項目を正しく入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H128" s="3" t="inlineStr">
+      <c r="H133" s="3" t="inlineStr">
         <is>
           <t>会員情報が登録され、ログイン状態で書籍一覧画面（トップページ）に遷移する</t>
         </is>
       </c>
-      <c r="I128" s="18" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="17" t="n"/>
-      <c r="B129" s="17" t="n"/>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="I133" s="5" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n"/>
+      <c r="B134" s="4" t="n"/>
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>9-2</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>ログイン機能</t>
         </is>
       </c>
-      <c r="E129" s="3" t="inlineStr">
+      <c r="E134" s="3" t="inlineStr">
         <is>
           <t>9-2-1</t>
         </is>
       </c>
-      <c r="F129" s="3" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr">
         <is>
           <t>メールアドレスが入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G129" s="3" t="inlineStr">
+      <c r="G134" s="3" t="inlineStr">
         <is>
           <t>1.ログインページを開く
 2.メールアドレスを入力せずに他の必要項目を入力する
 3.ログインボタンを押す</t>
         </is>
       </c>
-      <c r="H129" s="3" t="inlineStr">
+      <c r="H134" s="3" t="inlineStr">
         <is>
           <t>「メールアドレスを入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I129" s="3" t="inlineStr">
+      <c r="I134" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Auth/LoginTest.php</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="17" t="n"/>
-      <c r="B130" s="17" t="n"/>
-      <c r="C130" s="17" t="n"/>
-      <c r="D130" s="17" t="n"/>
-      <c r="E130" s="3" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="4" t="n"/>
+      <c r="B135" s="4" t="n"/>
+      <c r="C135" s="4" t="n"/>
+      <c r="D135" s="4" t="n"/>
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>9-2-2</t>
         </is>
       </c>
-      <c r="F130" s="3" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr">
         <is>
           <t>メールアドレスがメール形式でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G130" s="3" t="inlineStr">
+      <c r="G135" s="3" t="inlineStr">
         <is>
           <t>1.ログインページを開く
 2.「abc」のようなメール形式でないメールアドレスと他の必要項目を入力する
 3.ログインボタンを押す</t>
         </is>
       </c>
-      <c r="H130" s="3" t="inlineStr">
+      <c r="H135" s="3" t="inlineStr">
         <is>
           <t>「メールアドレスはメール形式で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I130" s="17" t="n"/>
-    </row>
-    <row r="131">
-      <c r="A131" s="17" t="n"/>
-      <c r="B131" s="17" t="n"/>
-      <c r="C131" s="17" t="n"/>
-      <c r="D131" s="17" t="n"/>
-      <c r="E131" s="3" t="inlineStr">
+      <c r="I135" s="4" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="n"/>
+      <c r="B136" s="4" t="n"/>
+      <c r="C136" s="4" t="n"/>
+      <c r="D136" s="4" t="n"/>
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>9-2-3</t>
         </is>
       </c>
-      <c r="F131" s="3" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr">
         <is>
           <t>パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G131" s="3" t="inlineStr">
+      <c r="G136" s="3" t="inlineStr">
         <is>
           <t>1.ログインページを開く
 2.パスワードを入力せずに他の必要項目を入力する
 3.ログインボタンを押す</t>
         </is>
       </c>
-      <c r="H131" s="3" t="inlineStr">
+      <c r="H136" s="3" t="inlineStr">
         <is>
           <t>「パスワードを入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I131" s="17" t="n"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="17" t="n"/>
-      <c r="B132" s="17" t="n"/>
-      <c r="C132" s="17" t="n"/>
-      <c r="D132" s="17" t="n"/>
-      <c r="E132" s="3" t="inlineStr">
+      <c r="I136" s="4" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="n"/>
+      <c r="B137" s="4" t="n"/>
+      <c r="C137" s="4" t="n"/>
+      <c r="D137" s="4" t="n"/>
+      <c r="E137" s="3" t="inlineStr">
         <is>
           <t>9-2-4</t>
         </is>
       </c>
-      <c r="F132" s="3" t="inlineStr">
+      <c r="F137" s="3" t="inlineStr">
         <is>
           <t>入力情報が登録されている会員情報と一致しない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G132" s="3" t="inlineStr">
+      <c r="G137" s="3" t="inlineStr">
         <is>
           <t>1.ログインページを開く
 2.登録されていないメールアドレス、または誤ったパスワードを入力する
 3.ログインボタンを押す</t>
         </is>
       </c>
-      <c r="H132" s="3" t="inlineStr">
+      <c r="H137" s="3" t="inlineStr">
         <is>
           <t>「会員情報が登録されていません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I132" s="17" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="17" t="n"/>
-      <c r="B133" s="17" t="n"/>
-      <c r="C133" s="18" t="n"/>
-      <c r="D133" s="18" t="n"/>
-      <c r="E133" s="3" t="inlineStr">
+      <c r="I137" s="4" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="n"/>
+      <c r="B138" s="4" t="n"/>
+      <c r="C138" s="5" t="n"/>
+      <c r="D138" s="5" t="n"/>
+      <c r="E138" s="3" t="inlineStr">
         <is>
           <t>9-2-5</t>
         </is>
       </c>
-      <c r="F133" s="3" t="inlineStr">
+      <c r="F138" s="3" t="inlineStr">
         <is>
           <t>正しい情報が入力された場合、ログイン処理が実行される</t>
         </is>
       </c>
-      <c r="G133" s="3" t="inlineStr">
+      <c r="G138" s="3" t="inlineStr">
         <is>
           <t>1.ログインページを開く
 2.登録済みの正しいメールアドレス・パスワードを入力する
 3.ログインボタンを押す</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
+      <c r="H138" s="3" t="inlineStr">
         <is>
           <t>ログイン処理が実行され、書籍一覧画面（トップページ）に遷移する</t>
         </is>
       </c>
-      <c r="I133" s="18" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="18" t="n"/>
-      <c r="B134" s="18" t="n"/>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="I138" s="5" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="5" t="n"/>
+      <c r="B139" s="5" t="n"/>
+      <c r="C139" s="3" t="inlineStr">
         <is>
           <t>9-3</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
         <is>
           <t>ログアウト機能</t>
         </is>
       </c>
-      <c r="E134" s="3" t="inlineStr">
+      <c r="E139" s="3" t="inlineStr">
         <is>
           <t>9-3-1</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr">
         <is>
           <t>ログアウトができる</t>
         </is>
       </c>
-      <c r="G134" s="3" t="inlineStr">
+      <c r="G139" s="3" t="inlineStr">
         <is>
           <t>1.ユーザーがログインする
 2.ログアウトボタンを押す</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
+      <c r="H139" s="3" t="inlineStr">
         <is>
           <t>ログアウト処理が実行され、ログインページに遷移する</t>
         </is>
       </c>
-      <c r="I134" s="3" t="inlineStr">
+      <c r="I139" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Auth/LogoutTest.php</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
+      <c r="B140" s="3" t="inlineStr">
         <is>
           <t>公開API</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C140" s="3" t="inlineStr">
         <is>
           <t>10-1</t>
         </is>
       </c>
-      <c r="D135" s="3" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>ユーザー情報取得API(/api/user)</t>
         </is>
       </c>
-      <c r="E135" s="3" t="inlineStr">
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>10-1-1</t>
         </is>
       </c>
-      <c r="F135" s="3" t="inlineStr">
+      <c r="F140" s="3" t="inlineStr">
         <is>
           <t>未認証でアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G135" s="3" t="inlineStr">
+      <c r="G140" s="3" t="inlineStr">
         <is>
           <t>1.トークンやセッションを持たない状態でGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H135" s="3" t="inlineStr">
+      <c r="H140" s="3" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
         </is>
       </c>
-      <c r="I135" s="3" t="inlineStr">
+      <c r="I140" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/PublicApi/UserApiTest.php</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="17" t="n"/>
-      <c r="B136" s="17" t="n"/>
-      <c r="C136" s="17" t="n"/>
-      <c r="D136" s="17" t="n"/>
-      <c r="E136" s="3" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="4" t="n"/>
+      <c r="B141" s="4" t="n"/>
+      <c r="C141" s="4" t="n"/>
+      <c r="D141" s="4" t="n"/>
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>10-1-2</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr">
+      <c r="F141" s="3" t="inlineStr">
         <is>
           <t>有効なSanctumトークンでアクセスするとログインユーザーの情報が返る</t>
         </is>
       </c>
-      <c r="G136" s="3" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>1.ユーザーのpersonal access tokenを発行する
 2.そのトークンをBearerヘッダーに付与してGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
+      <c r="H141" s="3" t="inlineStr">
         <is>
           <t>200が返り、該当ユーザーのid・name・emailを含むJSONが返る</t>
         </is>
       </c>
-      <c r="I136" s="17" t="n"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="17" t="n"/>
-      <c r="B137" s="17" t="n"/>
-      <c r="C137" s="18" t="n"/>
-      <c r="D137" s="18" t="n"/>
-      <c r="E137" s="3" t="inlineStr">
+      <c r="I141" s="4" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="n"/>
+      <c r="B142" s="4" t="n"/>
+      <c r="C142" s="5" t="n"/>
+      <c r="D142" s="5" t="n"/>
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>10-1-3</t>
         </is>
       </c>
-      <c r="F137" s="3" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr">
         <is>
           <t>レスポンスにパスワードなど非公開情報が含まれない</t>
         </is>
       </c>
-      <c r="G137" s="3" t="inlineStr">
+      <c r="G142" s="3" t="inlineStr">
         <is>
           <t>1.有効なトークンでGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
+      <c r="H142" s="3" t="inlineStr">
         <is>
           <t>レスポンスJSONにpassword・remember_tokenが含まれない</t>
         </is>
       </c>
-      <c r="I137" s="18" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="17" t="n"/>
-      <c r="B138" s="17" t="n"/>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="I142" s="5" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="n"/>
+      <c r="B143" s="4" t="n"/>
+      <c r="C143" s="3" t="inlineStr">
         <is>
           <t>10-2</t>
         </is>
       </c>
-      <c r="D138" s="3" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>書籍一覧取得API(GET /api/v1/books)</t>
         </is>
       </c>
-      <c r="E138" s="3" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>10-2-1</t>
         </is>
       </c>
-      <c r="F138" s="3" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr">
         <is>
           <t>認証なしでもアクセスでき、書籍一覧が返る</t>
         </is>
       </c>
-      <c r="G138" s="3" t="inlineStr">
+      <c r="G143" s="3" t="inlineStr">
         <is>
           <t>1.書籍を複数用意する
 2.認証情報を付与せずGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
+      <c r="H143" s="3" t="inlineStr">
         <is>
           <t>200が返り、data・links・metaを含むJSONが返る</t>
         </is>
       </c>
-      <c r="I138" s="3" t="inlineStr">
+      <c r="I143" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/PublicApi/BookApiIndexTest.php</t>
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="17" t="n"/>
-      <c r="B139" s="17" t="n"/>
-      <c r="C139" s="17" t="n"/>
-      <c r="D139" s="17" t="n"/>
-      <c r="E139" s="3" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="4" t="n"/>
+      <c r="B144" s="4" t="n"/>
+      <c r="C144" s="4" t="n"/>
+      <c r="D144" s="4" t="n"/>
+      <c r="E144" s="3" t="inlineStr">
         <is>
           <t>10-2-2</t>
         </is>
       </c>
-      <c r="F139" s="3" t="inlineStr">
+      <c r="F144" s="3" t="inlineStr">
         <is>
           <t>各書籍にジャンル・平均評価・レビュー件数が含まれる</t>
         </is>
       </c>
-      <c r="G139" s="3" t="inlineStr">
+      <c r="G144" s="3" t="inlineStr">
         <is>
           <t>1.ジャンルと、評価4・5のレビューを持つ書籍を用意する
 2.GET /api/v1/booksにアクセスする</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr">
+      <c r="H144" s="3" t="inlineStr">
         <is>
           <t>dataの各書籍にgenres(id・name)、average_rating(4.5)、review_count(2)が含まれ、reviews(レビュー本文)は含まれない</t>
         </is>
       </c>
-      <c r="I139" s="17" t="n"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="17" t="n"/>
-      <c r="B140" s="17" t="n"/>
-      <c r="C140" s="17" t="n"/>
-      <c r="D140" s="17" t="n"/>
-      <c r="E140" s="3" t="inlineStr">
+      <c r="I144" s="4" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="n"/>
+      <c r="B145" s="4" t="n"/>
+      <c r="C145" s="4" t="n"/>
+      <c r="D145" s="4" t="n"/>
+      <c r="E145" s="3" t="inlineStr">
         <is>
           <t>10-2-3</t>
         </is>
       </c>
-      <c r="F140" s="3" t="inlineStr">
+      <c r="F145" s="3" t="inlineStr">
         <is>
           <t>レビューが無い書籍はaverage_ratingがnull、review_countが0になる</t>
         </is>
       </c>
-      <c r="G140" s="3" t="inlineStr">
+      <c r="G145" s="3" t="inlineStr">
         <is>
           <t>1.レビューが1件もない書籍を用意する
 2.GET /api/v1/booksにアクセスする</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
+      <c r="H145" s="3" t="inlineStr">
         <is>
           <t>その書籍のaverage_ratingがnull、review_countが0で返る</t>
         </is>
       </c>
-      <c r="I140" s="17" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="17" t="n"/>
-      <c r="B141" s="17" t="n"/>
-      <c r="C141" s="17" t="n"/>
-      <c r="D141" s="17" t="n"/>
-      <c r="E141" s="3" t="inlineStr">
+      <c r="I145" s="4" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="n"/>
+      <c r="B146" s="4" t="n"/>
+      <c r="C146" s="4" t="n"/>
+      <c r="D146" s="4" t="n"/>
+      <c r="E146" s="3" t="inlineStr">
         <is>
           <t>10-2-4</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr">
+      <c r="F146" s="3" t="inlineStr">
         <is>
           <t>新しい順(登録日時の降順、同一なら idの降順)で返る</t>
         </is>
       </c>
-      <c r="G141" s="3" t="inlineStr">
+      <c r="G146" s="3" t="inlineStr">
         <is>
           <t>1.登録日時の異なる書籍を複数用意する
 2.GET /api/v1/booksにアクセスする</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
+      <c r="H146" s="3" t="inlineStr">
         <is>
           <t>新しく登録された書籍から順に返る</t>
         </is>
       </c>
-      <c r="I141" s="17" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="17" t="n"/>
-      <c r="B142" s="17" t="n"/>
-      <c r="C142" s="17" t="n"/>
-      <c r="D142" s="17" t="n"/>
-      <c r="E142" s="3" t="inlineStr">
+      <c r="I146" s="4" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="n"/>
+      <c r="B147" s="4" t="n"/>
+      <c r="C147" s="4" t="n"/>
+      <c r="D147" s="4" t="n"/>
+      <c r="E147" s="3" t="inlineStr">
         <is>
           <t>10-2-5</t>
         </is>
       </c>
-      <c r="F142" s="3" t="inlineStr">
+      <c r="F147" s="3" t="inlineStr">
         <is>
           <t>keywordでタイトル・著者名の部分一致検索ができる</t>
         </is>
       </c>
-      <c r="G142" s="3" t="inlineStr">
+      <c r="G147" s="3" t="inlineStr">
         <is>
           <t>1.タイトルにキーワードを含む書籍、著者名にキーワードを含む書籍、含まない書籍を用意する
 2.keywordを指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
+      <c r="H147" s="3" t="inlineStr">
         <is>
           <t>タイトルまたは著者名にキーワードを含む書籍のみが返る</t>
         </is>
       </c>
-      <c r="I142" s="17" t="n"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="17" t="n"/>
-      <c r="B143" s="17" t="n"/>
-      <c r="C143" s="17" t="n"/>
-      <c r="D143" s="17" t="n"/>
-      <c r="E143" s="3" t="inlineStr">
+      <c r="I147" s="4" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="n"/>
+      <c r="B148" s="4" t="n"/>
+      <c r="C148" s="4" t="n"/>
+      <c r="D148" s="4" t="n"/>
+      <c r="E148" s="3" t="inlineStr">
         <is>
           <t>10-2-6</t>
         </is>
       </c>
-      <c r="F143" s="3" t="inlineStr">
+      <c r="F148" s="3" t="inlineStr">
         <is>
           <t>genreでジャンルIDによる絞り込みができる</t>
         </is>
       </c>
-      <c r="G143" s="3" t="inlineStr">
+      <c r="G148" s="3" t="inlineStr">
         <is>
           <t>1.異なるジャンルの書籍を用意する
 2.genreにジャンルIDを指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
-      <c r="H143" s="3" t="inlineStr">
+      <c r="H148" s="3" t="inlineStr">
         <is>
           <t>指定したジャンルに属する書籍のみが返る</t>
         </is>
       </c>
-      <c r="I143" s="17" t="n"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="17" t="n"/>
-      <c r="B144" s="17" t="n"/>
-      <c r="C144" s="17" t="n"/>
-      <c r="D144" s="17" t="n"/>
-      <c r="E144" s="3" t="inlineStr">
+      <c r="I148" s="4" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="n"/>
+      <c r="B149" s="4" t="n"/>
+      <c r="C149" s="4" t="n"/>
+      <c r="D149" s="4" t="n"/>
+      <c r="E149" s="3" t="inlineStr">
         <is>
           <t>10-2-7</t>
         </is>
       </c>
-      <c r="F144" s="3" t="inlineStr">
+      <c r="F149" s="3" t="inlineStr">
         <is>
           <t>per_page・pageでページネーションできる(指定なしの場合は1ページ10件)</t>
         </is>
       </c>
-      <c r="G144" s="3" t="inlineStr">
+      <c r="G149" s="3" t="inlineStr">
         <is>
           <t>1.11件以上の書籍を用意する
 2.パラメータなし、およびper_page・pageを指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
-      <c r="H144" s="3" t="inlineStr">
+      <c r="H149" s="3" t="inlineStr">
         <is>
           <t>パラメータなしでは10件、指定した場合は指定件数・指定ページの書籍が返り、meta・linksにページ情報が反映される</t>
         </is>
       </c>
-      <c r="I144" s="17" t="n"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="17" t="n"/>
-      <c r="B145" s="17" t="n"/>
-      <c r="C145" s="18" t="n"/>
-      <c r="D145" s="18" t="n"/>
-      <c r="E145" s="3" t="inlineStr">
+      <c r="I149" s="4" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="n"/>
+      <c r="B150" s="4" t="n"/>
+      <c r="C150" s="5" t="n"/>
+      <c r="D150" s="5" t="n"/>
+      <c r="E150" s="3" t="inlineStr">
         <is>
           <t>10-2-8</t>
         </is>
       </c>
-      <c r="F145" s="3" t="inlineStr">
+      <c r="F150" s="3" t="inlineStr">
         <is>
           <t>不正なクエリパラメータを指定すると422が返る</t>
         </is>
       </c>
-      <c r="G145" s="3" t="inlineStr">
+      <c r="G150" s="3" t="inlineStr">
         <is>
           <t>1.per_pageに101、genreに存在しないID、pageに0をそれぞれ指定してGET /api/v1/booksにアクセスする(Accept: application/json)</t>
         </is>
       </c>
-      <c r="H145" s="3" t="inlineStr">
+      <c r="H150" s="3" t="inlineStr">
         <is>
           <t>422が返り、「取得件数は100以下の値で指定してください」「指定されたジャンルは存在しません」「ページ番号は1以上の値で指定してください」が返る</t>
         </is>
       </c>
-      <c r="I145" s="18" t="n"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="17" t="n"/>
-      <c r="B146" s="17" t="n"/>
-      <c r="C146" s="3" t="inlineStr">
+      <c r="I150" s="5" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="n"/>
+      <c r="B151" s="4" t="n"/>
+      <c r="C151" s="3" t="inlineStr">
         <is>
           <t>10-3</t>
         </is>
       </c>
-      <c r="D146" s="3" t="inlineStr">
+      <c r="D151" s="3" t="inlineStr">
         <is>
           <t>書籍詳細取得API(GET /api/v1/books/{book})</t>
         </is>
       </c>
-      <c r="E146" s="3" t="inlineStr">
+      <c r="E151" s="3" t="inlineStr">
         <is>
           <t>10-3-1</t>
         </is>
       </c>
-      <c r="F146" s="3" t="inlineStr">
+      <c r="F151" s="3" t="inlineStr">
         <is>
           <t>認証なしでもアクセスでき、書籍の詳細が返る</t>
         </is>
       </c>
-      <c r="G146" s="3" t="inlineStr">
+      <c r="G151" s="3" t="inlineStr">
         <is>
           <t>1.ジャンルとレビューを持つ書籍を用意する
 2.認証情報を付与せずGET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H146" s="3" t="inlineStr">
+      <c r="H151" s="3" t="inlineStr">
         <is>
           <t>200が返り、書籍情報・genres・average_rating・review_countを含むJSONが返る</t>
         </is>
       </c>
-      <c r="I146" s="3" t="inlineStr">
+      <c r="I151" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/PublicApi/BookApiShowTest.php</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="17" t="n"/>
-      <c r="B147" s="17" t="n"/>
-      <c r="C147" s="17" t="n"/>
-      <c r="D147" s="17" t="n"/>
-      <c r="E147" s="3" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="4" t="n"/>
+      <c r="B152" s="4" t="n"/>
+      <c r="C152" s="4" t="n"/>
+      <c r="D152" s="4" t="n"/>
+      <c r="E152" s="3" t="inlineStr">
         <is>
           <t>10-3-2</t>
         </is>
       </c>
-      <c r="F147" s="3" t="inlineStr">
+      <c r="F152" s="3" t="inlineStr">
         <is>
           <t>レビュー(投稿者名・評価・コメント・投稿日時)が新しい順に含まれる</t>
         </is>
       </c>
-      <c r="G147" s="3" t="inlineStr">
+      <c r="G152" s="3" t="inlineStr">
         <is>
           <t>1.異なる日時に投稿された複数のレビューを持つ書籍を用意する
 2.GET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H147" s="3" t="inlineStr">
+      <c r="H152" s="3" t="inlineStr">
         <is>
           <t>reviewsにuser_name・rating・comment・created_atが含まれ、投稿日時の新しい順に並ぶ</t>
         </is>
       </c>
-      <c r="I147" s="17" t="n"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="17" t="n"/>
-      <c r="B148" s="17" t="n"/>
-      <c r="C148" s="18" t="n"/>
-      <c r="D148" s="18" t="n"/>
-      <c r="E148" s="3" t="inlineStr">
+      <c r="I152" s="4" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="n"/>
+      <c r="B153" s="4" t="n"/>
+      <c r="C153" s="5" t="n"/>
+      <c r="D153" s="5" t="n"/>
+      <c r="E153" s="3" t="inlineStr">
         <is>
           <t>10-3-3</t>
         </is>
       </c>
-      <c r="F148" s="3" t="inlineStr">
+      <c r="F153" s="3" t="inlineStr">
         <is>
           <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
-      <c r="G148" s="3" t="inlineStr">
+      <c r="G153" s="3" t="inlineStr">
         <is>
           <t>1.存在しない書籍IDでGET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H148" s="3" t="inlineStr">
+      <c r="H153" s="3" t="inlineStr">
         <is>
           <t>404が返り、「指定された書籍が見つかりません」が返る</t>
         </is>
       </c>
-      <c r="I148" s="18" t="n"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="17" t="n"/>
-      <c r="B149" s="17" t="n"/>
-      <c r="C149" s="3" t="inlineStr">
+      <c r="I153" s="5" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="n"/>
+      <c r="B154" s="4" t="n"/>
+      <c r="C154" s="3" t="inlineStr">
         <is>
           <t>10-4</t>
         </is>
       </c>
-      <c r="D149" s="3" t="inlineStr">
+      <c r="D154" s="3" t="inlineStr">
         <is>
           <t>書籍登録API(POST /api/v1/books)</t>
         </is>
       </c>
-      <c r="E149" s="3" t="inlineStr">
+      <c r="E154" s="3" t="inlineStr">
         <is>
           <t>10-4-1</t>
         </is>
       </c>
-      <c r="F149" s="3" t="inlineStr">
+      <c r="F154" s="3" t="inlineStr">
         <is>
           <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G149" s="3" t="inlineStr">
+      <c r="G154" s="3" t="inlineStr">
         <is>
           <t>1.認証情報を付与せずPOST /api/v1/booksにアクセスする(Accept: application/json)</t>
         </is>
       </c>
-      <c r="H149" s="3" t="inlineStr">
+      <c r="H154" s="3" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録されない</t>
         </is>
       </c>
-      <c r="I149" s="3" t="inlineStr">
+      <c r="I154" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/PublicApi/BookApiStoreTest.php</t>
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="17" t="n"/>
-      <c r="B150" s="17" t="n"/>
-      <c r="C150" s="17" t="n"/>
-      <c r="D150" s="17" t="n"/>
-      <c r="E150" s="3" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="4" t="n"/>
+      <c r="B155" s="4" t="n"/>
+      <c r="C155" s="4" t="n"/>
+      <c r="D155" s="4" t="n"/>
+      <c r="E155" s="3" t="inlineStr">
         <is>
           <t>10-4-2</t>
         </is>
       </c>
-      <c r="F150" s="3" t="inlineStr">
+      <c r="F155" s="3" t="inlineStr">
         <is>
           <t>有効なトークンで書籍を登録できる</t>
         </is>
       </c>
-      <c r="G150" s="3" t="inlineStr">
+      <c r="G155" s="3" t="inlineStr">
         <is>
           <t>1.ユーザーのトークンを発行する
 2.必要項目を指定し、Bearerトークンを付与してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
-      <c r="H150" s="3" t="inlineStr">
+      <c r="H155" s="3" t="inlineStr">
         <is>
           <t>201が返り、登録内容がJSONで返る。書籍がDBに保存される</t>
         </is>
       </c>
-      <c r="I150" s="17" t="n"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="17" t="n"/>
-      <c r="B151" s="17" t="n"/>
-      <c r="C151" s="17" t="n"/>
-      <c r="D151" s="17" t="n"/>
-      <c r="E151" s="3" t="inlineStr">
+      <c r="I155" s="4" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="n"/>
+      <c r="B156" s="4" t="n"/>
+      <c r="C156" s="4" t="n"/>
+      <c r="D156" s="4" t="n"/>
+      <c r="E156" s="3" t="inlineStr">
         <is>
           <t>10-4-3</t>
         </is>
       </c>
-      <c r="F151" s="3" t="inlineStr">
+      <c r="F156" s="3" t="inlineStr">
         <is>
           <t>登録者(user_id)は、リクエストの値ではなく認証ユーザーになる</t>
         </is>
       </c>
-      <c r="G151" s="3" t="inlineStr">
+      <c r="G156" s="3" t="inlineStr">
         <is>
           <t>1.他のユーザーのIDをuser_idに含めて、トークンを付与しPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
-      <c r="H151" s="3" t="inlineStr">
+      <c r="H156" s="3" t="inlineStr">
         <is>
           <t>登録された書籍のuser_idは、トークンの持ち主(認証ユーザー)のIDになる</t>
         </is>
       </c>
-      <c r="I151" s="17" t="n"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="17" t="n"/>
-      <c r="B152" s="17" t="n"/>
-      <c r="C152" s="17" t="n"/>
-      <c r="D152" s="17" t="n"/>
-      <c r="E152" s="3" t="inlineStr">
+      <c r="I156" s="4" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="n"/>
+      <c r="B157" s="4" t="n"/>
+      <c r="C157" s="4" t="n"/>
+      <c r="D157" s="4" t="n"/>
+      <c r="E157" s="3" t="inlineStr">
         <is>
           <t>10-4-4</t>
         </is>
       </c>
-      <c r="F152" s="3" t="inlineStr">
+      <c r="F157" s="3" t="inlineStr">
         <is>
           <t>選択したジャンルが書籍に紐づけられる</t>
         </is>
       </c>
-      <c r="G152" s="3" t="inlineStr">
+      <c r="G157" s="3" t="inlineStr">
         <is>
           <t>1.複数のジャンルIDをgenresに指定してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
-      <c r="H152" s="3" t="inlineStr">
+      <c r="H157" s="3" t="inlineStr">
         <is>
           <t>中間テーブル(book_genre)に指定したジャンルが保存され、レスポンスのgenresにも含まれる</t>
         </is>
       </c>
-      <c r="I152" s="17" t="n"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="17" t="n"/>
-      <c r="B153" s="17" t="n"/>
-      <c r="C153" s="17" t="n"/>
-      <c r="D153" s="17" t="n"/>
-      <c r="E153" s="3" t="inlineStr">
+      <c r="I157" s="4" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="n"/>
+      <c r="B158" s="4" t="n"/>
+      <c r="C158" s="4" t="n"/>
+      <c r="D158" s="4" t="n"/>
+      <c r="E158" s="3" t="inlineStr">
         <is>
           <t>10-4-5</t>
         </is>
       </c>
-      <c r="F153" s="3" t="inlineStr">
+      <c r="F158" s="3" t="inlineStr">
         <is>
           <t>必須項目(title・author・genres)が未入力の場合、422が返る</t>
         </is>
       </c>
-      <c r="G153" s="3" t="inlineStr">
+      <c r="G158" s="3" t="inlineStr">
         <is>
           <t>1.title・author・genresを指定せずにPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
-      <c r="H153" s="3" t="inlineStr">
+      <c r="H158" s="3" t="inlineStr">
         <is>
           <t>422が返り、「書籍タイトルを入力してください」「著者名を入力してください」「ジャンルを1つ以上選択してください」が返る</t>
         </is>
       </c>
-      <c r="I153" s="17" t="n"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="17" t="n"/>
-      <c r="B154" s="17" t="n"/>
-      <c r="C154" s="17" t="n"/>
-      <c r="D154" s="17" t="n"/>
-      <c r="E154" s="3" t="inlineStr">
+      <c r="I158" s="4" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="n"/>
+      <c r="B159" s="4" t="n"/>
+      <c r="C159" s="4" t="n"/>
+      <c r="D159" s="4" t="n"/>
+      <c r="E159" s="3" t="inlineStr">
         <is>
           <t>10-4-6</t>
         </is>
       </c>
-      <c r="F154" s="3" t="inlineStr">
+      <c r="F159" s="3" t="inlineStr">
         <is>
           <t>ISBNが13桁の数字でない、または登録済みの場合、422が返る</t>
         </is>
       </c>
-      <c r="G154" s="3" t="inlineStr">
+      <c r="G159" s="3" t="inlineStr">
         <is>
           <t>1.ISBNに13桁でない値を指定してPOST /api/v1/booksにアクセスする
 2.登録済みのISBNを指定して同様にアクセスする</t>
         </is>
       </c>
-      <c r="H154" s="3" t="inlineStr">
+      <c r="H159" s="3" t="inlineStr">
         <is>
           <t>422が返り、「ISBNは13桁の数字で入力してください」「このISBNはすでに登録されています」が返る</t>
         </is>
       </c>
-      <c r="I154" s="17" t="n"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="17" t="n"/>
-      <c r="B155" s="17" t="n"/>
-      <c r="C155" s="18" t="n"/>
-      <c r="D155" s="18" t="n"/>
-      <c r="E155" s="3" t="inlineStr">
+      <c r="I159" s="4" t="n"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="n"/>
+      <c r="B160" s="4" t="n"/>
+      <c r="C160" s="5" t="n"/>
+      <c r="D160" s="5" t="n"/>
+      <c r="E160" s="3" t="inlineStr">
         <is>
           <t>10-4-7</t>
         </is>
       </c>
-      <c r="F155" s="3" t="inlineStr">
+      <c r="F160" s="3" t="inlineStr">
         <is>
           <t>存在しないジャンルIDを指定すると422が返る</t>
         </is>
       </c>
-      <c r="G155" s="3" t="inlineStr">
+      <c r="G160" s="3" t="inlineStr">
         <is>
           <t>1.genresに存在しないジャンルIDを指定してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
-      <c r="H155" s="3" t="inlineStr">
+      <c r="H160" s="3" t="inlineStr">
         <is>
           <t>422が返り、「選択されたジャンルは存在しません」が返る</t>
         </is>
       </c>
-      <c r="I155" s="18" t="n"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="17" t="n"/>
-      <c r="B156" s="17" t="n"/>
-      <c r="C156" s="3" t="inlineStr">
+      <c r="I160" s="5" t="n"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="n"/>
+      <c r="B161" s="4" t="n"/>
+      <c r="C161" s="3" t="inlineStr">
         <is>
           <t>10-5</t>
         </is>
       </c>
-      <c r="D156" s="3" t="inlineStr">
+      <c r="D161" s="3" t="inlineStr">
         <is>
           <t>書籍更新API(PUT /api/v1/books/{book})</t>
         </is>
       </c>
-      <c r="E156" s="3" t="inlineStr">
+      <c r="E161" s="3" t="inlineStr">
         <is>
           <t>10-5-1</t>
         </is>
       </c>
-      <c r="F156" s="3" t="inlineStr">
+      <c r="F161" s="3" t="inlineStr">
         <is>
           <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G156" s="3" t="inlineStr">
+      <c r="G161" s="3" t="inlineStr">
         <is>
           <t>1.認証情報を付与せずPUT /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
         </is>
       </c>
-      <c r="H156" s="3" t="inlineStr">
+      <c r="H161" s="3" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は更新されない</t>
         </is>
       </c>
-      <c r="I156" s="3" t="inlineStr">
+      <c r="I161" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/PublicApi/BookApiUpdateTest.php</t>
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="17" t="n"/>
-      <c r="B157" s="17" t="n"/>
-      <c r="C157" s="17" t="n"/>
-      <c r="D157" s="17" t="n"/>
-      <c r="E157" s="3" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="4" t="n"/>
+      <c r="B162" s="4" t="n"/>
+      <c r="C162" s="4" t="n"/>
+      <c r="D162" s="4" t="n"/>
+      <c r="E162" s="3" t="inlineStr">
         <is>
           <t>10-5-2</t>
         </is>
       </c>
-      <c r="F157" s="3" t="inlineStr">
+      <c r="F162" s="3" t="inlineStr">
         <is>
           <t>自分が登録した書籍を更新できる</t>
         </is>
       </c>
-      <c r="G157" s="3" t="inlineStr">
+      <c r="G162" s="3" t="inlineStr">
         <is>
           <t>1.ユーザーが登録した書籍を用意する
 2.そのユーザーのトークンを付与し、変更内容・ジャンルを指定してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H157" s="3" t="inlineStr">
+      <c r="H162" s="3" t="inlineStr">
         <is>
           <t>200が返り、更新後の内容がJSONで返る。DBの書籍情報とジャンルの紐づけが更新される</t>
         </is>
       </c>
-      <c r="I157" s="17" t="n"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="17" t="n"/>
-      <c r="B158" s="17" t="n"/>
-      <c r="C158" s="17" t="n"/>
-      <c r="D158" s="17" t="n"/>
-      <c r="E158" s="3" t="inlineStr">
+      <c r="I162" s="4" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="n"/>
+      <c r="B163" s="4" t="n"/>
+      <c r="C163" s="4" t="n"/>
+      <c r="D163" s="4" t="n"/>
+      <c r="E163" s="3" t="inlineStr">
         <is>
           <t>10-5-3</t>
         </is>
       </c>
-      <c r="F158" s="3" t="inlineStr">
+      <c r="F163" s="3" t="inlineStr">
         <is>
           <t>自分の書籍のISBNを変更せずに更新しても、ISBNの重複エラーにならない</t>
         </is>
       </c>
-      <c r="G158" s="3" t="inlineStr">
+      <c r="G163" s="3" t="inlineStr">
         <is>
           <t>1.ユーザーが登録した書籍(ISBNあり)を用意する
 2.ISBNを変えずに他の項目を変更してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H158" s="3" t="inlineStr">
+      <c r="H163" s="3" t="inlineStr">
         <is>
           <t>200が返り、更新できる</t>
         </is>
       </c>
-      <c r="I158" s="17" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="17" t="n"/>
-      <c r="B159" s="17" t="n"/>
-      <c r="C159" s="17" t="n"/>
-      <c r="D159" s="17" t="n"/>
-      <c r="E159" s="3" t="inlineStr">
+      <c r="I163" s="4" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="n"/>
+      <c r="B164" s="4" t="n"/>
+      <c r="C164" s="4" t="n"/>
+      <c r="D164" s="4" t="n"/>
+      <c r="E164" s="3" t="inlineStr">
         <is>
           <t>10-5-4</t>
         </is>
       </c>
-      <c r="F159" s="3" t="inlineStr">
+      <c r="F164" s="3" t="inlineStr">
         <is>
           <t>他のユーザーが登録した書籍は更新できない</t>
         </is>
       </c>
-      <c r="G159" s="3" t="inlineStr">
+      <c r="G164" s="3" t="inlineStr">
         <is>
           <t>1.他のユーザーが登録した書籍を用意する
 2.別のユーザーのトークンを付与してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H159" s="3" t="inlineStr">
+      <c r="H164" s="3" t="inlineStr">
         <is>
           <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は更新されない</t>
         </is>
       </c>
-      <c r="I159" s="17" t="n"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="17" t="n"/>
-      <c r="B160" s="17" t="n"/>
-      <c r="C160" s="17" t="n"/>
-      <c r="D160" s="17" t="n"/>
-      <c r="E160" s="3" t="inlineStr">
+      <c r="I164" s="4" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="n"/>
+      <c r="B165" s="4" t="n"/>
+      <c r="C165" s="4" t="n"/>
+      <c r="D165" s="4" t="n"/>
+      <c r="E165" s="3" t="inlineStr">
         <is>
           <t>10-5-5</t>
         </is>
       </c>
-      <c r="F160" s="3" t="inlineStr">
+      <c r="F165" s="3" t="inlineStr">
         <is>
           <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
-      <c r="G160" s="3" t="inlineStr">
+      <c r="G165" s="3" t="inlineStr">
         <is>
           <t>1.トークンを付与し、存在しない書籍IDでPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H160" s="3" t="inlineStr">
+      <c r="H165" s="3" t="inlineStr">
         <is>
           <t>404が返り、「指定された書籍が見つかりません」が返る</t>
         </is>
       </c>
-      <c r="I160" s="17" t="n"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="17" t="n"/>
-      <c r="B161" s="17" t="n"/>
-      <c r="C161" s="17" t="n"/>
-      <c r="D161" s="17" t="n"/>
-      <c r="E161" s="3" t="inlineStr">
+      <c r="I165" s="4" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="n"/>
+      <c r="B166" s="4" t="n"/>
+      <c r="C166" s="4" t="n"/>
+      <c r="D166" s="4" t="n"/>
+      <c r="E166" s="3" t="inlineStr">
         <is>
           <t>10-5-6</t>
         </is>
       </c>
-      <c r="F161" s="3" t="inlineStr">
+      <c r="F166" s="3" t="inlineStr">
         <is>
           <t>入力内容が不正な場合、422が返る</t>
         </is>
       </c>
-      <c r="G161" s="3" t="inlineStr">
+      <c r="G166" s="3" t="inlineStr">
         <is>
           <t>1.自分の書籍に対し、titleを空にしてPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H161" s="3" t="inlineStr">
+      <c r="H166" s="3" t="inlineStr">
         <is>
           <t>422が返り、「書籍タイトルを入力してください」が返る。書籍は更新されない</t>
         </is>
       </c>
-      <c r="I161" s="17" t="n"/>
-    </row>
-    <row r="162">
-      <c r="A162" s="17" t="n"/>
-      <c r="B162" s="17" t="n"/>
-      <c r="C162" s="18" t="n"/>
-      <c r="D162" s="18" t="n"/>
-      <c r="E162" s="3" t="inlineStr">
+      <c r="I166" s="4" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="n"/>
+      <c r="B167" s="4" t="n"/>
+      <c r="C167" s="5" t="n"/>
+      <c r="D167" s="5" t="n"/>
+      <c r="E167" s="3" t="inlineStr">
         <is>
           <t>10-5-7</t>
         </is>
       </c>
-      <c r="F162" s="3" t="inlineStr">
+      <c r="F167" s="3" t="inlineStr">
         <is>
           <t>他のユーザーが登録した書籍に対して不正な入力で更新しようとしても、422ではなく403が返る</t>
         </is>
       </c>
-      <c r="G162" s="3" t="inlineStr">
+      <c r="G167" s="3" t="inlineStr">
         <is>
           <t>1.他のユーザーが登録した書籍を用意する
 2.別のユーザーのトークンを付与し、タイトルを空にするなど不正な内容でPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H162" s="3" t="inlineStr">
+      <c r="H167" s="3" t="inlineStr">
         <is>
           <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る（入力チェックより先に権限が判定される）。書籍は更新されない</t>
         </is>
       </c>
-      <c r="I162" s="18" t="n"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="17" t="n"/>
-      <c r="B163" s="17" t="n"/>
-      <c r="C163" s="3" t="inlineStr">
+      <c r="I167" s="5" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="n"/>
+      <c r="B168" s="4" t="n"/>
+      <c r="C168" s="3" t="inlineStr">
         <is>
           <t>10-6</t>
         </is>
       </c>
-      <c r="D163" s="3" t="inlineStr">
+      <c r="D168" s="3" t="inlineStr">
         <is>
           <t>書籍削除API(DELETE /api/v1/books/{book})</t>
         </is>
       </c>
-      <c r="E163" s="3" t="inlineStr">
+      <c r="E168" s="3" t="inlineStr">
         <is>
           <t>10-6-1</t>
         </is>
       </c>
-      <c r="F163" s="3" t="inlineStr">
+      <c r="F168" s="3" t="inlineStr">
         <is>
           <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G163" s="3" t="inlineStr">
+      <c r="G168" s="3" t="inlineStr">
         <is>
           <t>1.認証情報を付与せずDELETE /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
         </is>
       </c>
-      <c r="H163" s="3" t="inlineStr">
+      <c r="H168" s="3" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は削除されない</t>
         </is>
       </c>
-      <c r="I163" s="3" t="inlineStr">
+      <c r="I168" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/PublicApi/BookApiDestroyTest.php</t>
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="17" t="n"/>
-      <c r="B164" s="17" t="n"/>
-      <c r="C164" s="17" t="n"/>
-      <c r="D164" s="17" t="n"/>
-      <c r="E164" s="3" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="4" t="n"/>
+      <c r="B169" s="4" t="n"/>
+      <c r="C169" s="4" t="n"/>
+      <c r="D169" s="4" t="n"/>
+      <c r="E169" s="3" t="inlineStr">
         <is>
           <t>10-6-2</t>
         </is>
       </c>
-      <c r="F164" s="3" t="inlineStr">
+      <c r="F169" s="3" t="inlineStr">
         <is>
           <t>自分が登録した書籍を削除できる</t>
         </is>
       </c>
-      <c r="G164" s="3" t="inlineStr">
+      <c r="G169" s="3" t="inlineStr">
         <is>
           <t>1.ユーザーが登録した書籍を用意する
 2.そのユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H164" s="3" t="inlineStr">
+      <c r="H169" s="3" t="inlineStr">
         <is>
           <t>204が返り(レスポンスボディなし)、書籍がDBから削除される</t>
         </is>
       </c>
-      <c r="I164" s="17" t="n"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="17" t="n"/>
-      <c r="B165" s="17" t="n"/>
-      <c r="C165" s="17" t="n"/>
-      <c r="D165" s="17" t="n"/>
-      <c r="E165" s="3" t="inlineStr">
+      <c r="I169" s="4" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="n"/>
+      <c r="B170" s="4" t="n"/>
+      <c r="C170" s="4" t="n"/>
+      <c r="D170" s="4" t="n"/>
+      <c r="E170" s="3" t="inlineStr">
         <is>
           <t>10-6-3</t>
         </is>
       </c>
-      <c r="F165" s="3" t="inlineStr">
+      <c r="F170" s="3" t="inlineStr">
         <is>
           <t>書籍を削除すると、関連するデータも一緒に削除される</t>
         </is>
       </c>
-      <c r="G165" s="3" t="inlineStr">
+      <c r="G170" s="3" t="inlineStr">
         <is>
           <t>1.ジャンルの紐づけ・レビュー・お気に入り・レビューへのいいねを持つ書籍を用意する
 2.所有者のトークンでDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H165" s="3" t="inlineStr">
+      <c r="H170" s="3" t="inlineStr">
         <is>
           <t>book_genre・reviews・favorites・review_likesの該当データも削除される</t>
         </is>
       </c>
-      <c r="I165" s="17" t="n"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="17" t="n"/>
-      <c r="B166" s="17" t="n"/>
-      <c r="C166" s="17" t="n"/>
-      <c r="D166" s="17" t="n"/>
-      <c r="E166" s="3" t="inlineStr">
+      <c r="I170" s="4" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="n"/>
+      <c r="B171" s="4" t="n"/>
+      <c r="C171" s="4" t="n"/>
+      <c r="D171" s="4" t="n"/>
+      <c r="E171" s="3" t="inlineStr">
         <is>
           <t>10-6-4</t>
         </is>
       </c>
-      <c r="F166" s="3" t="inlineStr">
+      <c r="F171" s="3" t="inlineStr">
         <is>
           <t>他のユーザーが登録した書籍は削除できない</t>
         </is>
       </c>
-      <c r="G166" s="3" t="inlineStr">
+      <c r="G171" s="3" t="inlineStr">
         <is>
           <t>1.他のユーザーが登録した書籍を用意する
 2.別のユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H166" s="3" t="inlineStr">
+      <c r="H171" s="3" t="inlineStr">
         <is>
           <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は削除されない</t>
         </is>
       </c>
-      <c r="I166" s="17" t="n"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="18" t="n"/>
-      <c r="B167" s="18" t="n"/>
-      <c r="C167" s="18" t="n"/>
-      <c r="D167" s="18" t="n"/>
-      <c r="E167" s="3" t="inlineStr">
+      <c r="I171" s="4" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="5" t="n"/>
+      <c r="B172" s="5" t="n"/>
+      <c r="C172" s="5" t="n"/>
+      <c r="D172" s="5" t="n"/>
+      <c r="E172" s="3" t="inlineStr">
         <is>
           <t>10-6-5</t>
         </is>
       </c>
-      <c r="F167" s="3" t="inlineStr">
+      <c r="F172" s="3" t="inlineStr">
         <is>
           <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
-      <c r="G167" s="3" t="inlineStr">
+      <c r="G172" s="3" t="inlineStr">
         <is>
           <t>1.トークンを付与し、存在しない書籍IDでDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H167" s="3" t="inlineStr">
+      <c r="H172" s="3" t="inlineStr">
         <is>
           <t>404が返り、「指定された書籍が見つかりません」が返る</t>
         </is>
       </c>
-      <c r="I167" s="18" t="n"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="7" t="inlineStr">
+      <c r="I172" s="5" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B168" s="7" t="inlineStr">
+      <c r="B173" s="7" t="inlineStr">
         <is>
           <t>検索・フィルタ</t>
         </is>
       </c>
-      <c r="C168" s="7" t="inlineStr">
+      <c r="C173" s="7" t="inlineStr">
         <is>
           <t>11-1</t>
         </is>
       </c>
-      <c r="D168" s="7" t="inlineStr">
+      <c r="D173" s="7" t="inlineStr">
         <is>
           <t>書籍のキーワード検索・ジャンル絞り込み</t>
         </is>
       </c>
-      <c r="E168" s="7" t="inlineStr">
+      <c r="E173" s="7" t="inlineStr">
         <is>
           <t>11-1-1</t>
         </is>
       </c>
-      <c r="F168" s="7" t="inlineStr">
+      <c r="F173" s="7" t="inlineStr">
         <is>
           <t>タイトルにキーワードを含む書籍が検索結果に表示される</t>
         </is>
       </c>
-      <c r="G168" s="7" t="inlineStr">
+      <c r="G173" s="7" t="inlineStr">
         <is>
           <t>1.タイトルにキーワードを含む書籍を用意する
 2.書籍一覧ページでkeywordにそのキーワードを指定して検索する</t>
         </is>
       </c>
-      <c r="H168" s="7" t="inlineStr">
+      <c r="H173" s="7" t="inlineStr">
         <is>
           <t>該当する書籍が検索結果に表示される</t>
         </is>
       </c>
-      <c r="I168" s="7" t="inlineStr">
+      <c r="I173" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Search/SearchTest.php</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="17" t="n"/>
-      <c r="B169" s="17" t="n"/>
-      <c r="C169" s="17" t="n"/>
-      <c r="D169" s="17" t="n"/>
-      <c r="E169" s="7" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="4" t="n"/>
+      <c r="B174" s="4" t="n"/>
+      <c r="C174" s="4" t="n"/>
+      <c r="D174" s="4" t="n"/>
+      <c r="E174" s="7" t="inlineStr">
         <is>
           <t>11-1-2</t>
         </is>
       </c>
-      <c r="F169" s="7" t="inlineStr">
+      <c r="F174" s="7" t="inlineStr">
         <is>
           <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
         </is>
       </c>
-      <c r="G169" s="7" t="inlineStr">
+      <c r="G174" s="7" t="inlineStr">
         <is>
           <t>1.著者名にキーワードを含む書籍を用意する
 2.同キーワードで検索する</t>
         </is>
       </c>
-      <c r="H169" s="7" t="inlineStr">
+      <c r="H174" s="7" t="inlineStr">
         <is>
           <t>該当する書籍が検索結果に表示される</t>
         </is>
       </c>
-      <c r="I169" s="17" t="n"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="17" t="n"/>
-      <c r="B170" s="17" t="n"/>
-      <c r="C170" s="17" t="n"/>
-      <c r="D170" s="17" t="n"/>
-      <c r="E170" s="7" t="inlineStr">
+      <c r="I174" s="4" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="n"/>
+      <c r="B175" s="4" t="n"/>
+      <c r="C175" s="4" t="n"/>
+      <c r="D175" s="4" t="n"/>
+      <c r="E175" s="7" t="inlineStr">
         <is>
           <t>11-1-3</t>
         </is>
       </c>
-      <c r="F170" s="7" t="inlineStr">
+      <c r="F175" s="7" t="inlineStr">
         <is>
           <t>キーワードに一致しない書籍は検索結果に表示されない</t>
         </is>
       </c>
-      <c r="G170" s="7" t="inlineStr">
+      <c r="G175" s="7" t="inlineStr">
         <is>
           <t>1.キーワードに一致しない書籍を用意する
 2.検索する</t>
         </is>
       </c>
-      <c r="H170" s="7" t="inlineStr">
+      <c r="H175" s="7" t="inlineStr">
         <is>
           <t>その書籍は検索結果に表示されない</t>
         </is>
       </c>
-      <c r="I170" s="17" t="n"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="17" t="n"/>
-      <c r="B171" s="17" t="n"/>
-      <c r="C171" s="17" t="n"/>
-      <c r="D171" s="17" t="n"/>
-      <c r="E171" s="7" t="inlineStr">
+      <c r="I175" s="4" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="n"/>
+      <c r="B176" s="4" t="n"/>
+      <c r="C176" s="4" t="n"/>
+      <c r="D176" s="4" t="n"/>
+      <c r="E176" s="7" t="inlineStr">
         <is>
           <t>11-1-4</t>
         </is>
       </c>
-      <c r="F171" s="7" t="inlineStr">
+      <c r="F176" s="7" t="inlineStr">
         <is>
           <t>キーワード未入力の場合は全件が表示される</t>
         </is>
       </c>
-      <c r="G171" s="7" t="inlineStr">
+      <c r="G176" s="7" t="inlineStr">
         <is>
           <t>1.keywordを指定せずに書籍一覧ページを開く</t>
         </is>
       </c>
-      <c r="H171" s="7" t="inlineStr">
+      <c r="H176" s="7" t="inlineStr">
         <is>
           <t>登録されている全ての書籍が表示される</t>
         </is>
       </c>
-      <c r="I171" s="17" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="17" t="n"/>
-      <c r="B172" s="17" t="n"/>
-      <c r="C172" s="17" t="n"/>
-      <c r="D172" s="17" t="n"/>
-      <c r="E172" s="7" t="inlineStr">
+      <c r="I176" s="4" t="n"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="n"/>
+      <c r="B177" s="4" t="n"/>
+      <c r="C177" s="4" t="n"/>
+      <c r="D177" s="4" t="n"/>
+      <c r="E177" s="7" t="inlineStr">
         <is>
           <t>11-1-5</t>
         </is>
       </c>
-      <c r="F172" s="7" t="inlineStr">
+      <c r="F177" s="7" t="inlineStr">
         <is>
           <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
         </is>
       </c>
-      <c r="G172" s="7" t="inlineStr">
+      <c r="G177" s="7" t="inlineStr">
         <is>
           <t>1.複数ジャンルの書籍を用意する
 2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
         </is>
       </c>
-      <c r="H172" s="7" t="inlineStr">
+      <c r="H177" s="7" t="inlineStr">
         <is>
           <t>指定したジャンルに紐づく書籍のみ表示される</t>
         </is>
       </c>
-      <c r="I172" s="17" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="17" t="n"/>
-      <c r="B173" s="17" t="n"/>
-      <c r="C173" s="17" t="n"/>
-      <c r="D173" s="17" t="n"/>
-      <c r="E173" s="7" t="inlineStr">
+      <c r="I177" s="4" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="n"/>
+      <c r="B178" s="4" t="n"/>
+      <c r="C178" s="4" t="n"/>
+      <c r="D178" s="4" t="n"/>
+      <c r="E178" s="7" t="inlineStr">
         <is>
           <t>11-1-6</t>
         </is>
       </c>
-      <c r="F173" s="7" t="inlineStr">
+      <c r="F178" s="7" t="inlineStr">
         <is>
           <t>キーワード検索とジャンル絞り込みを組み合わせて使用できる</t>
         </is>
       </c>
-      <c r="G173" s="7" t="inlineStr">
+      <c r="G178" s="7" t="inlineStr">
         <is>
           <t>1.keywordとgenreの両方を指定して一覧を開く</t>
         </is>
       </c>
-      <c r="H173" s="7" t="inlineStr">
+      <c r="H178" s="7" t="inlineStr">
         <is>
           <t>キーワードとジャンルの両方の条件に一致する書籍のみ表示される</t>
         </is>
       </c>
-      <c r="I173" s="17" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="18" t="n"/>
-      <c r="B174" s="18" t="n"/>
-      <c r="C174" s="18" t="n"/>
-      <c r="D174" s="18" t="n"/>
-      <c r="E174" s="7" t="inlineStr">
+      <c r="I178" s="4" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="5" t="n"/>
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="5" t="n"/>
+      <c r="D179" s="5" t="n"/>
+      <c r="E179" s="7" t="inlineStr">
         <is>
           <t>11-1-7</t>
         </is>
       </c>
-      <c r="F174" s="7" t="inlineStr">
+      <c r="F179" s="7" t="inlineStr">
         <is>
           <t>検索結果が0件の場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G174" s="7" t="inlineStr">
+      <c r="G179" s="7" t="inlineStr">
         <is>
           <t>1.どの書籍にも一致しないキーワードで検索する</t>
         </is>
       </c>
-      <c r="H174" s="7" t="inlineStr">
+      <c r="H179" s="7" t="inlineStr">
         <is>
           <t>「条件に一致する書籍が見つかりませんでした。」と表示される</t>
         </is>
       </c>
-      <c r="I174" s="18" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="7" t="inlineStr">
+      <c r="I179" s="5" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B175" s="7" t="inlineStr">
+      <c r="B180" s="7" t="inlineStr">
         <is>
           <t>ソート</t>
         </is>
       </c>
-      <c r="C175" s="7" t="inlineStr">
+      <c r="C180" s="7" t="inlineStr">
         <is>
           <t>12-1</t>
         </is>
       </c>
-      <c r="D175" s="7" t="inlineStr">
+      <c r="D180" s="7" t="inlineStr">
         <is>
           <t>書籍一覧の並び替え</t>
         </is>
       </c>
-      <c r="E175" s="7" t="inlineStr">
+      <c r="E180" s="7" t="inlineStr">
         <is>
           <t>12-1-1</t>
         </is>
       </c>
-      <c r="F175" s="7" t="inlineStr">
+      <c r="F180" s="7" t="inlineStr">
         <is>
           <t>並び替え未指定時は新着順(登録が新しい順)で表示される</t>
         </is>
       </c>
-      <c r="G175" s="7" t="inlineStr">
+      <c r="G180" s="7" t="inlineStr">
         <is>
           <t>1.複数の書籍を異なる日時で登録する
 2.sortを指定せずに書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H175" s="7" t="inlineStr">
+      <c r="H180" s="7" t="inlineStr">
         <is>
           <t>登録日時が新しい順に表示される</t>
         </is>
       </c>
-      <c r="I175" s="7" t="inlineStr">
+      <c r="I180" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Sort/SortTest.php</t>
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="17" t="n"/>
-      <c r="B176" s="17" t="n"/>
-      <c r="C176" s="17" t="n"/>
-      <c r="D176" s="17" t="n"/>
-      <c r="E176" s="7" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="4" t="n"/>
+      <c r="B181" s="4" t="n"/>
+      <c r="C181" s="4" t="n"/>
+      <c r="D181" s="4" t="n"/>
+      <c r="E181" s="7" t="inlineStr">
         <is>
           <t>12-1-2</t>
         </is>
       </c>
-      <c r="F176" s="7" t="inlineStr">
+      <c r="F181" s="7" t="inlineStr">
         <is>
           <t>sort=oldestを指定すると登録が古い順に表示される</t>
         </is>
       </c>
-      <c r="G176" s="7" t="inlineStr">
+      <c r="G181" s="7" t="inlineStr">
         <is>
           <t>1.複数の書籍を異なる日時で登録する
 2.sort=oldestを指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H176" s="7" t="inlineStr">
+      <c r="H181" s="7" t="inlineStr">
         <is>
           <t>登録日時が古い順に表示される</t>
         </is>
       </c>
-      <c r="I176" s="17" t="n"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="17" t="n"/>
-      <c r="B177" s="17" t="n"/>
-      <c r="C177" s="17" t="n"/>
-      <c r="D177" s="17" t="n"/>
-      <c r="E177" s="7" t="inlineStr">
+      <c r="I181" s="4" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="n"/>
+      <c r="B182" s="4" t="n"/>
+      <c r="C182" s="4" t="n"/>
+      <c r="D182" s="4" t="n"/>
+      <c r="E182" s="7" t="inlineStr">
         <is>
           <t>12-1-3</t>
         </is>
       </c>
-      <c r="F177" s="7" t="inlineStr">
+      <c r="F182" s="7" t="inlineStr">
         <is>
           <t>sort=titleを指定するとタイトルの昇順で表示される</t>
         </is>
       </c>
-      <c r="G177" s="7" t="inlineStr">
+      <c r="G182" s="7" t="inlineStr">
         <is>
           <t>1.複数の書籍を用意する
 2.sort=titleを指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H177" s="7" t="inlineStr">
+      <c r="H182" s="7" t="inlineStr">
         <is>
           <t>タイトルの昇順で表示される</t>
         </is>
       </c>
-      <c r="I177" s="17" t="n"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="17" t="n"/>
-      <c r="B178" s="17" t="n"/>
-      <c r="C178" s="17" t="n"/>
-      <c r="D178" s="17" t="n"/>
-      <c r="E178" s="7" t="inlineStr">
+      <c r="I182" s="4" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="n"/>
+      <c r="B183" s="4" t="n"/>
+      <c r="C183" s="4" t="n"/>
+      <c r="D183" s="4" t="n"/>
+      <c r="E183" s="7" t="inlineStr">
         <is>
           <t>12-1-4</t>
         </is>
       </c>
-      <c r="F178" s="7" t="inlineStr">
+      <c r="F183" s="7" t="inlineStr">
         <is>
           <t>sort=ratingを指定すると平均評価が高い順に表示される</t>
         </is>
       </c>
-      <c r="G178" s="7" t="inlineStr">
+      <c r="G183" s="7" t="inlineStr">
         <is>
           <t>1.平均評価が異なる複数の書籍を用意する
 2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H178" s="7" t="inlineStr">
+      <c r="H183" s="7" t="inlineStr">
         <is>
           <t>平均評価が高い順に表示される</t>
         </is>
       </c>
-      <c r="I178" s="17" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="18" t="n"/>
-      <c r="B179" s="18" t="n"/>
-      <c r="C179" s="18" t="n"/>
-      <c r="D179" s="18" t="n"/>
-      <c r="E179" s="7" t="inlineStr">
+      <c r="I183" s="4" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="5" t="n"/>
+      <c r="B184" s="5" t="n"/>
+      <c r="C184" s="5" t="n"/>
+      <c r="D184" s="5" t="n"/>
+      <c r="E184" s="7" t="inlineStr">
         <is>
           <t>12-1-5</t>
         </is>
       </c>
-      <c r="F179" s="7" t="inlineStr">
+      <c r="F184" s="7" t="inlineStr">
         <is>
           <t>sort=rating指定時、平均評価が同じ書籍は新着順で表示される</t>
         </is>
       </c>
-      <c r="G179" s="7" t="inlineStr">
+      <c r="G184" s="7" t="inlineStr">
         <is>
           <t>1.平均評価が同じ複数の書籍を、異なる登録日時で用意する
 2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H179" s="7" t="inlineStr">
+      <c r="H184" s="7" t="inlineStr">
         <is>
           <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
         </is>
       </c>
-      <c r="I179" s="18" t="n"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="7" t="inlineStr">
+      <c r="I184" s="5" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B180" s="7" t="inlineStr">
+      <c r="B185" s="7" t="inlineStr">
         <is>
           <t>書籍CRUD（認可の詳細テスト）</t>
         </is>
       </c>
-      <c r="C180" s="7" t="inlineStr">
+      <c r="C185" s="7" t="inlineStr">
         <is>
           <t>13-1</t>
         </is>
       </c>
-      <c r="D180" s="7" t="inlineStr">
+      <c r="D185" s="7" t="inlineStr">
         <is>
           <t>BookPolicyの認可ロジック</t>
         </is>
       </c>
-      <c r="E180" s="7" t="inlineStr">
+      <c r="E185" s="7" t="inlineStr">
         <is>
           <t>13-1-1</t>
         </is>
       </c>
-      <c r="F180" s="7" t="inlineStr">
+      <c r="F185" s="7" t="inlineStr">
         <is>
           <t>ログインユーザーは誰でも書籍を作成できる</t>
         </is>
       </c>
-      <c r="G180" s="7" t="inlineStr">
+      <c r="G185" s="7" t="inlineStr">
         <is>
           <t>1.任意のログインユーザーで BookPolicy::create() を確認する</t>
         </is>
       </c>
-      <c r="H180" s="7" t="inlineStr">
+      <c r="H185" s="7" t="inlineStr">
         <is>
           <t>trueが返り、作成が許可される</t>
         </is>
       </c>
-      <c r="I180" s="7" t="inlineStr">
+      <c r="I185" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/BookAuthorization/BookAuthorizationTest.php</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="17" t="n"/>
-      <c r="B181" s="17" t="n"/>
-      <c r="C181" s="17" t="n"/>
-      <c r="D181" s="17" t="n"/>
-      <c r="E181" s="7" t="inlineStr">
+    <row r="186">
+      <c r="A186" s="4" t="n"/>
+      <c r="B186" s="4" t="n"/>
+      <c r="C186" s="4" t="n"/>
+      <c r="D186" s="4" t="n"/>
+      <c r="E186" s="7" t="inlineStr">
         <is>
           <t>13-1-2</t>
         </is>
       </c>
-      <c r="F181" s="7" t="inlineStr">
+      <c r="F186" s="7" t="inlineStr">
         <is>
           <t>書籍の登録者本人は更新が許可される</t>
         </is>
       </c>
-      <c r="G181" s="7" t="inlineStr">
+      <c r="G186" s="7" t="inlineStr">
         <is>
           <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
         </is>
       </c>
-      <c r="H181" s="7" t="inlineStr">
+      <c r="H186" s="7" t="inlineStr">
         <is>
           <t>trueが返る</t>
         </is>
       </c>
-      <c r="I181" s="17" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="17" t="n"/>
-      <c r="B182" s="17" t="n"/>
-      <c r="C182" s="17" t="n"/>
-      <c r="D182" s="17" t="n"/>
-      <c r="E182" s="7" t="inlineStr">
+      <c r="I186" s="4" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n"/>
+      <c r="B187" s="4" t="n"/>
+      <c r="C187" s="4" t="n"/>
+      <c r="D187" s="4" t="n"/>
+      <c r="E187" s="7" t="inlineStr">
         <is>
           <t>13-1-3</t>
         </is>
       </c>
-      <c r="F182" s="7" t="inlineStr">
+      <c r="F187" s="7" t="inlineStr">
         <is>
           <t>書籍の登録者以外は更新が許可されない</t>
         </is>
       </c>
-      <c r="G182" s="7" t="inlineStr">
+      <c r="G187" s="7" t="inlineStr">
         <is>
           <t>1.別ユーザーでBookPolicy::update()を確認する</t>
         </is>
       </c>
-      <c r="H182" s="7" t="inlineStr">
+      <c r="H187" s="7" t="inlineStr">
         <is>
           <t>falseが返る</t>
         </is>
       </c>
-      <c r="I182" s="17" t="n"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="17" t="n"/>
-      <c r="B183" s="17" t="n"/>
-      <c r="C183" s="17" t="n"/>
-      <c r="D183" s="17" t="n"/>
-      <c r="E183" s="7" t="inlineStr">
+      <c r="I187" s="4" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n"/>
+      <c r="B188" s="4" t="n"/>
+      <c r="C188" s="4" t="n"/>
+      <c r="D188" s="4" t="n"/>
+      <c r="E188" s="7" t="inlineStr">
         <is>
           <t>13-1-4</t>
         </is>
       </c>
-      <c r="F183" s="7" t="inlineStr">
+      <c r="F188" s="7" t="inlineStr">
         <is>
           <t>書籍の登録者本人は削除が許可される</t>
         </is>
       </c>
-      <c r="G183" s="7" t="inlineStr">
+      <c r="G188" s="7" t="inlineStr">
         <is>
           <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
         </is>
       </c>
-      <c r="H183" s="7" t="inlineStr">
+      <c r="H188" s="7" t="inlineStr">
         <is>
           <t>trueが返る</t>
         </is>
       </c>
-      <c r="I183" s="17" t="n"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="17" t="n"/>
-      <c r="B184" s="17" t="n"/>
-      <c r="C184" s="17" t="n"/>
-      <c r="D184" s="17" t="n"/>
-      <c r="E184" s="7" t="inlineStr">
+      <c r="I188" s="4" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n"/>
+      <c r="B189" s="4" t="n"/>
+      <c r="C189" s="4" t="n"/>
+      <c r="D189" s="4" t="n"/>
+      <c r="E189" s="7" t="inlineStr">
         <is>
           <t>13-1-5</t>
         </is>
       </c>
-      <c r="F184" s="7" t="inlineStr">
+      <c r="F189" s="7" t="inlineStr">
         <is>
           <t>書籍の登録者以外は削除が許可されない</t>
         </is>
       </c>
-      <c r="G184" s="7" t="inlineStr">
+      <c r="G189" s="7" t="inlineStr">
         <is>
           <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
         </is>
       </c>
-      <c r="H184" s="7" t="inlineStr">
+      <c r="H189" s="7" t="inlineStr">
         <is>
           <t>falseが返る</t>
         </is>
       </c>
-      <c r="I184" s="17" t="n"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="17" t="n"/>
-      <c r="B185" s="17" t="n"/>
-      <c r="C185" s="17" t="n"/>
-      <c r="D185" s="17" t="n"/>
-      <c r="E185" s="7" t="inlineStr">
+      <c r="I189" s="4" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n"/>
+      <c r="B190" s="4" t="n"/>
+      <c r="C190" s="4" t="n"/>
+      <c r="D190" s="4" t="n"/>
+      <c r="E190" s="7" t="inlineStr">
         <is>
           <t>13-1-6</t>
         </is>
       </c>
-      <c r="F185" s="7" t="inlineStr">
+      <c r="F190" s="7" t="inlineStr">
         <is>
           <t>フォームを介さない直接のPUT/DELETEリクエストでも他人の書籍は操作できない</t>
         </is>
       </c>
-      <c r="G185" s="7" t="inlineStr">
+      <c r="G190" s="7" t="inlineStr">
         <is>
           <t>1.他人が登録した書籍に対して、直接PUT・DELETEリクエストを送信する</t>
         </is>
       </c>
-      <c r="H185" s="7" t="inlineStr">
+      <c r="H190" s="7" t="inlineStr">
         <is>
           <t>いずれも403Forbiddenになり、データは変更されない</t>
         </is>
       </c>
-      <c r="I185" s="17" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="18" t="n"/>
-      <c r="B186" s="18" t="n"/>
-      <c r="C186" s="18" t="n"/>
-      <c r="D186" s="18" t="n"/>
-      <c r="E186" s="7" t="inlineStr">
+      <c r="I190" s="4" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="5" t="n"/>
+      <c r="B191" s="5" t="n"/>
+      <c r="C191" s="5" t="n"/>
+      <c r="D191" s="5" t="n"/>
+      <c r="E191" s="7" t="inlineStr">
         <is>
           <t>13-1-7</t>
         </is>
       </c>
-      <c r="F186" s="7" t="inlineStr">
+      <c r="F191" s="7" t="inlineStr">
         <is>
           <t>他人の書籍に対して不正な入力を直接PUTしても、入力エラーではなく403になる</t>
         </is>
       </c>
-      <c r="G186" s="7" t="inlineStr">
+      <c r="G191" s="7" t="inlineStr">
         <is>
           <t>1.他人が登録した書籍に対して、タイトルを空にするなど不正な内容で、直接PUTリクエストを送信する</t>
         </is>
       </c>
-      <c r="H186" s="7" t="inlineStr">
+      <c r="H191" s="7" t="inlineStr">
         <is>
           <t>バリデーションエラーにはならず、403Forbiddenになる（入力チェックより先に権限が判定される）。データは変更されない</t>
         </is>
       </c>
-      <c r="I186" s="18" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="7" t="inlineStr">
+      <c r="I191" s="5" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B187" s="7" t="inlineStr">
+      <c r="B192" s="7" t="inlineStr">
         <is>
           <t>ISBN検索</t>
         </is>
       </c>
-      <c r="C187" s="7" t="inlineStr">
+      <c r="C192" s="7" t="inlineStr">
         <is>
           <t>14-1</t>
         </is>
       </c>
-      <c r="D187" s="7" t="inlineStr">
+      <c r="D192" s="7" t="inlineStr">
         <is>
           <t>ISBNからの書籍情報取得(外部API連携)</t>
         </is>
       </c>
-      <c r="E187" s="7" t="inlineStr">
+      <c r="E192" s="7" t="inlineStr">
         <is>
           <t>14-1-1</t>
         </is>
       </c>
-      <c r="F187" s="7" t="inlineStr">
+      <c r="F192" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、ISBN検索エンドポイントにアクセスできない</t>
         </is>
       </c>
-      <c r="G187" s="7" t="inlineStr">
+      <c r="G192" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態でGET /books/isbn/{isbn} にアクセスする</t>
         </is>
       </c>
-      <c r="H187" s="7" t="inlineStr">
+      <c r="H192" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I187" s="7" t="inlineStr">
+      <c r="I192" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Isbn/IsbnSearchTest.php</t>
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="17" t="n"/>
-      <c r="B188" s="17" t="n"/>
-      <c r="C188" s="17" t="n"/>
-      <c r="D188" s="17" t="n"/>
-      <c r="E188" s="7" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="4" t="n"/>
+      <c r="B193" s="4" t="n"/>
+      <c r="C193" s="4" t="n"/>
+      <c r="D193" s="4" t="n"/>
+      <c r="E193" s="7" t="inlineStr">
         <is>
           <t>14-1-2</t>
         </is>
       </c>
-      <c r="F188" s="7" t="inlineStr">
+      <c r="F193" s="7" t="inlineStr">
         <is>
           <t>ISBNが空(空白のみ)の場合、バリデーションエラーが返る</t>
         </is>
       </c>
-      <c r="G188" s="7" t="inlineStr">
+      <c r="G193" s="7" t="inlineStr">
         <is>
           <t>1.ログイン状態で、ISBN部分を半角スペースのみにしてGET /books/isbn/%20 にリクエストする
 ※ISBN部分を完全に空にするとURLが /books/isbn となり、このルートに一致しないため空白で代用する</t>
         </is>
       </c>
-      <c r="H188" s="7" t="inlineStr">
+      <c r="H193" s="7" t="inlineStr">
         <is>
           <t>422が返り、「ISBNを入力してください」が返る</t>
         </is>
       </c>
-      <c r="I188" s="17" t="n"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="17" t="n"/>
-      <c r="B189" s="17" t="n"/>
-      <c r="C189" s="17" t="n"/>
-      <c r="D189" s="17" t="n"/>
-      <c r="E189" s="7" t="inlineStr">
+      <c r="I193" s="4" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="n"/>
+      <c r="B194" s="4" t="n"/>
+      <c r="C194" s="4" t="n"/>
+      <c r="D194" s="4" t="n"/>
+      <c r="E194" s="7" t="inlineStr">
         <is>
           <t>14-1-3</t>
         </is>
       </c>
-      <c r="F189" s="7" t="inlineStr">
+      <c r="F194" s="7" t="inlineStr">
         <is>
           <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
         </is>
       </c>
-      <c r="G189" s="7" t="inlineStr">
+      <c r="G194" s="7" t="inlineStr">
         <is>
           <t>1.13桁でないISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H189" s="7" t="inlineStr">
+      <c r="H194" s="7" t="inlineStr">
         <is>
           <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
         </is>
       </c>
-      <c r="I189" s="17" t="n"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="17" t="n"/>
-      <c r="B190" s="17" t="n"/>
-      <c r="C190" s="17" t="n"/>
-      <c r="D190" s="17" t="n"/>
-      <c r="E190" s="7" t="inlineStr">
+      <c r="I194" s="4" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="n"/>
+      <c r="B195" s="4" t="n"/>
+      <c r="C195" s="4" t="n"/>
+      <c r="D195" s="4" t="n"/>
+      <c r="E195" s="7" t="inlineStr">
         <is>
           <t>14-1-4</t>
         </is>
       </c>
-      <c r="F190" s="7" t="inlineStr">
+      <c r="F195" s="7" t="inlineStr">
         <is>
           <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
         </is>
       </c>
-      <c r="G190" s="7" t="inlineStr">
+      <c r="G195" s="7" t="inlineStr">
         <is>
           <t>1.登録済みのISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H190" s="7" t="inlineStr">
+      <c r="H195" s="7" t="inlineStr">
         <is>
           <t>422が返り、「このISBNはすでに登録されています」が返る</t>
         </is>
       </c>
-      <c r="I190" s="17" t="n"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="17" t="n"/>
-      <c r="B191" s="17" t="n"/>
-      <c r="C191" s="17" t="n"/>
-      <c r="D191" s="17" t="n"/>
-      <c r="E191" s="7" t="inlineStr">
+      <c r="I195" s="4" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="n"/>
+      <c r="B196" s="4" t="n"/>
+      <c r="C196" s="4" t="n"/>
+      <c r="D196" s="4" t="n"/>
+      <c r="E196" s="7" t="inlineStr">
         <is>
           <t>14-1-5</t>
         </is>
       </c>
-      <c r="F191" s="7" t="inlineStr">
+      <c r="F196" s="7" t="inlineStr">
         <is>
           <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
         </is>
       </c>
-      <c r="G191" s="7" t="inlineStr">
+      <c r="G196" s="7" t="inlineStr">
         <is>
           <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H191" s="7" t="inlineStr">
+      <c r="H196" s="7" t="inlineStr">
         <is>
           <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
         </is>
       </c>
-      <c r="I191" s="17" t="n"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="17" t="n"/>
-      <c r="B192" s="17" t="n"/>
-      <c r="C192" s="17" t="n"/>
-      <c r="D192" s="17" t="n"/>
-      <c r="E192" s="7" t="inlineStr">
+      <c r="I196" s="4" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="n"/>
+      <c r="B197" s="4" t="n"/>
+      <c r="C197" s="4" t="n"/>
+      <c r="D197" s="4" t="n"/>
+      <c r="E197" s="7" t="inlineStr">
         <is>
           <t>14-1-6</t>
         </is>
       </c>
-      <c r="F192" s="7" t="inlineStr">
+      <c r="F197" s="7" t="inlineStr">
         <is>
           <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
         </is>
       </c>
-      <c r="G192" s="7" t="inlineStr">
+      <c r="G197" s="7" t="inlineStr">
         <is>
           <t>1.Http::fake()でitemsが空のレスポンスをモックする
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H192" s="7" t="inlineStr">
+      <c r="H197" s="7" t="inlineStr">
         <is>
           <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
         </is>
       </c>
-      <c r="I192" s="17" t="n"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="18" t="n"/>
-      <c r="B193" s="18" t="n"/>
-      <c r="C193" s="18" t="n"/>
-      <c r="D193" s="18" t="n"/>
-      <c r="E193" s="7" t="inlineStr">
+      <c r="I197" s="4" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="n"/>
+      <c r="B198" s="5" t="n"/>
+      <c r="C198" s="5" t="n"/>
+      <c r="D198" s="5" t="n"/>
+      <c r="E198" s="7" t="inlineStr">
         <is>
           <t>14-1-7</t>
         </is>
       </c>
-      <c r="F193" s="7" t="inlineStr">
+      <c r="F198" s="7" t="inlineStr">
         <is>
           <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
         </is>
       </c>
-      <c r="G193" s="7" t="inlineStr">
+      <c r="G198" s="7" t="inlineStr">
         <is>
           <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H193" s="7" t="inlineStr">
+      <c r="H198" s="7" t="inlineStr">
         <is>
           <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
         </is>
       </c>
-      <c r="I193" s="18" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="7" t="inlineStr">
+      <c r="I198" s="5" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B194" s="7" t="inlineStr">
+      <c r="B199" s="7" t="inlineStr">
         <is>
           <t>マイ読書レポート</t>
         </is>
       </c>
-      <c r="C194" s="7" t="inlineStr">
+      <c r="C199" s="7" t="inlineStr">
         <is>
           <t>15-1</t>
         </is>
       </c>
-      <c r="D194" s="7" t="inlineStr">
+      <c r="D199" s="7" t="inlineStr">
         <is>
           <t>読書統計の表示</t>
         </is>
       </c>
-      <c r="E194" s="7" t="inlineStr">
+      <c r="E199" s="7" t="inlineStr">
         <is>
           <t>15-1-1</t>
         </is>
       </c>
-      <c r="F194" s="7" t="inlineStr">
+      <c r="F199" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
         </is>
       </c>
-      <c r="G194" s="7" t="inlineStr">
+      <c r="G199" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で/reportsを開く</t>
         </is>
       </c>
-      <c r="H194" s="7" t="inlineStr">
+      <c r="H199" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I194" s="7" t="inlineStr">
+      <c r="I199" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Report/ReportTest.php</t>
         </is>
       </c>
     </row>
-    <row r="195">
-      <c r="A195" s="17" t="n"/>
-      <c r="B195" s="17" t="n"/>
-      <c r="C195" s="17" t="n"/>
-      <c r="D195" s="17" t="n"/>
-      <c r="E195" s="7" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="4" t="n"/>
+      <c r="B200" s="4" t="n"/>
+      <c r="C200" s="4" t="n"/>
+      <c r="D200" s="4" t="n"/>
+      <c r="E200" s="7" t="inlineStr">
         <is>
           <t>15-1-2</t>
         </is>
       </c>
-      <c r="F195" s="7" t="inlineStr">
+      <c r="F200" s="7" t="inlineStr">
         <is>
           <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
         </is>
       </c>
-      <c r="G195" s="7" t="inlineStr">
+      <c r="G200" s="7" t="inlineStr">
         <is>
           <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H195" s="7" t="inlineStr">
+      <c r="H200" s="7" t="inlineStr">
         <is>
           <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
         </is>
       </c>
-      <c r="I195" s="17" t="n"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="17" t="n"/>
-      <c r="B196" s="17" t="n"/>
-      <c r="C196" s="17" t="n"/>
-      <c r="D196" s="17" t="n"/>
-      <c r="E196" s="7" t="inlineStr">
+      <c r="I200" s="4" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="n"/>
+      <c r="B201" s="4" t="n"/>
+      <c r="C201" s="4" t="n"/>
+      <c r="D201" s="4" t="n"/>
+      <c r="E201" s="7" t="inlineStr">
         <is>
           <t>15-1-3</t>
         </is>
       </c>
-      <c r="F196" s="7" t="inlineStr">
+      <c r="F201" s="7" t="inlineStr">
         <is>
           <t>評価分布(★1〜★5)が正しく表示される</t>
         </is>
       </c>
-      <c r="G196" s="7" t="inlineStr">
+      <c r="G201" s="7" t="inlineStr">
         <is>
           <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H196" s="7" t="inlineStr">
+      <c r="H201" s="7" t="inlineStr">
         <is>
           <t>各評価の件数が実データと一致して表示される</t>
         </is>
       </c>
-      <c r="I196" s="17" t="n"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="17" t="n"/>
-      <c r="B197" s="17" t="n"/>
-      <c r="C197" s="17" t="n"/>
-      <c r="D197" s="17" t="n"/>
-      <c r="E197" s="7" t="inlineStr">
+      <c r="I201" s="4" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="n"/>
+      <c r="B202" s="4" t="n"/>
+      <c r="C202" s="4" t="n"/>
+      <c r="D202" s="4" t="n"/>
+      <c r="E202" s="7" t="inlineStr">
         <is>
           <t>15-1-4</t>
         </is>
       </c>
-      <c r="F197" s="7" t="inlineStr">
+      <c r="F202" s="7" t="inlineStr">
         <is>
           <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
         </is>
       </c>
-      <c r="G197" s="7" t="inlineStr">
+      <c r="G202" s="7" t="inlineStr">
         <is>
           <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H197" s="7" t="inlineStr">
+      <c r="H202" s="7" t="inlineStr">
         <is>
           <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
         </is>
       </c>
-      <c r="I197" s="17" t="n"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="17" t="n"/>
-      <c r="B198" s="17" t="n"/>
-      <c r="C198" s="17" t="n"/>
-      <c r="D198" s="17" t="n"/>
-      <c r="E198" s="7" t="inlineStr">
+      <c r="I202" s="4" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="n"/>
+      <c r="B203" s="4" t="n"/>
+      <c r="C203" s="4" t="n"/>
+      <c r="D203" s="4" t="n"/>
+      <c r="E203" s="7" t="inlineStr">
         <is>
           <t>15-1-5</t>
         </is>
       </c>
-      <c r="F198" s="7" t="inlineStr">
+      <c r="F203" s="7" t="inlineStr">
         <is>
           <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
         </is>
       </c>
-      <c r="G198" s="7" t="inlineStr">
+      <c r="G203" s="7" t="inlineStr">
         <is>
           <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H198" s="7" t="inlineStr">
+      <c r="H203" s="7" t="inlineStr">
         <is>
           <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
         </is>
       </c>
-      <c r="I198" s="17" t="n"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="18" t="n"/>
-      <c r="B199" s="18" t="n"/>
-      <c r="C199" s="18" t="n"/>
-      <c r="D199" s="18" t="n"/>
-      <c r="E199" s="7" t="inlineStr">
+      <c r="I203" s="4" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="n"/>
+      <c r="B204" s="5" t="n"/>
+      <c r="C204" s="5" t="n"/>
+      <c r="D204" s="5" t="n"/>
+      <c r="E204" s="7" t="inlineStr">
         <is>
           <t>15-1-6</t>
         </is>
       </c>
-      <c r="F199" s="7" t="inlineStr">
+      <c r="F204" s="7" t="inlineStr">
         <is>
           <t>レビューを1件も投稿していない場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G199" s="7" t="inlineStr">
+      <c r="G204" s="7" t="inlineStr">
         <is>
           <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H199" s="7" t="inlineStr">
+      <c r="H204" s="7" t="inlineStr">
         <is>
           <t>総レビュー数・読了冊数が0（平均評価の集計値は0で、画面上は「-」と表示）となり、TOP5一覧には「4星以上の書籍がありません」「ジャンルが設定された書籍のレビューがありません」と表示される</t>
         </is>
       </c>
-      <c r="I199" s="18" t="n"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="7" t="inlineStr">
+      <c r="I204" s="5" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B200" s="7" t="inlineStr">
+      <c r="B205" s="7" t="inlineStr">
         <is>
           <t>Sanctum認証</t>
         </is>
       </c>
-      <c r="C200" s="7" t="inlineStr">
+      <c r="C205" s="7" t="inlineStr">
         <is>
           <t>16-1</t>
         </is>
       </c>
-      <c r="D200" s="7" t="inlineStr">
+      <c r="D205" s="7" t="inlineStr">
         <is>
           <t>APIトークン認証</t>
         </is>
       </c>
-      <c r="E200" s="7" t="inlineStr">
+      <c r="E205" s="7" t="inlineStr">
         <is>
           <t>16-1-1</t>
         </is>
       </c>
-      <c r="F200" s="7" t="inlineStr">
+      <c r="F205" s="7" t="inlineStr">
         <is>
           <t>有効なpersonal access tokenを付与すると/api/userにアクセスできる</t>
         </is>
       </c>
-      <c r="G200" s="7" t="inlineStr">
+      <c r="G205" s="7" t="inlineStr">
         <is>
           <t>1.$user-&gt;createToken()でトークンを発行する
 2.Authorization: Bearer {token}を付与してGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H200" s="7" t="inlineStr">
+      <c r="H205" s="7" t="inlineStr">
         <is>
           <t>200が返り、対象ユーザーの情報が返る</t>
         </is>
       </c>
-      <c r="I200" s="7" t="inlineStr">
+      <c r="I205" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="17" t="n"/>
-      <c r="B201" s="17" t="n"/>
-      <c r="C201" s="17" t="n"/>
-      <c r="D201" s="17" t="n"/>
-      <c r="E201" s="7" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="4" t="n"/>
+      <c r="B206" s="4" t="n"/>
+      <c r="C206" s="4" t="n"/>
+      <c r="D206" s="4" t="n"/>
+      <c r="E206" s="7" t="inlineStr">
         <is>
           <t>16-1-2</t>
         </is>
       </c>
-      <c r="F201" s="7" t="inlineStr">
+      <c r="F206" s="7" t="inlineStr">
         <is>
           <t>トークンなしでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G201" s="7" t="inlineStr">
+      <c r="G206" s="7" t="inlineStr">
         <is>
           <t>1.Authorizationヘッダーを付与せずにGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H201" s="7" t="inlineStr">
+      <c r="H206" s="7" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
         </is>
       </c>
-      <c r="I201" s="17" t="n"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="17" t="n"/>
-      <c r="B202" s="17" t="n"/>
-      <c r="C202" s="17" t="n"/>
-      <c r="D202" s="17" t="n"/>
-      <c r="E202" s="7" t="inlineStr">
+      <c r="I206" s="4" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="n"/>
+      <c r="B207" s="4" t="n"/>
+      <c r="C207" s="4" t="n"/>
+      <c r="D207" s="4" t="n"/>
+      <c r="E207" s="7" t="inlineStr">
         <is>
           <t>16-1-3</t>
         </is>
       </c>
-      <c r="F202" s="7" t="inlineStr">
+      <c r="F207" s="7" t="inlineStr">
         <is>
           <t>不正な(存在しない)トークンでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G202" s="7" t="inlineStr">
+      <c r="G207" s="7" t="inlineStr">
         <is>
           <t>1.ランダムな文字列をBearerトークンとして付与しGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H202" s="7" t="inlineStr">
+      <c r="H207" s="7" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
         </is>
       </c>
-      <c r="I202" s="17" t="n"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="18" t="n"/>
-      <c r="B203" s="18" t="n"/>
-      <c r="C203" s="18" t="n"/>
-      <c r="D203" s="18" t="n"/>
-      <c r="E203" s="7" t="inlineStr">
+      <c r="I207" s="4" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="5" t="n"/>
+      <c r="B208" s="5" t="n"/>
+      <c r="C208" s="5" t="n"/>
+      <c r="D208" s="5" t="n"/>
+      <c r="E208" s="7" t="inlineStr">
         <is>
           <t>16-1-4</t>
         </is>
       </c>
-      <c r="F203" s="7" t="inlineStr">
+      <c r="F208" s="7" t="inlineStr">
         <is>
           <t>削除済み(失効済み)のトークンでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G203" s="7" t="inlineStr">
+      <c r="G208" s="7" t="inlineStr">
         <is>
           <t>1.発行済みトークンを削除する
 2.そのトークンでGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H203" s="7" t="inlineStr">
+      <c r="H208" s="7" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
         </is>
       </c>
-      <c r="I203" s="18" t="n"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="7" t="inlineStr">
+      <c r="I208" s="5" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B204" s="7" t="inlineStr">
+      <c r="B209" s="7" t="inlineStr">
         <is>
           <t>読書計画</t>
         </is>
       </c>
-      <c r="C204" s="7" t="inlineStr">
+      <c r="C209" s="7" t="inlineStr">
         <is>
           <t>17-1</t>
         </is>
       </c>
-      <c r="D204" s="7" t="inlineStr">
+      <c r="D209" s="7" t="inlineStr">
         <is>
           <t>読書計画の作成・一覧・読了・削除</t>
         </is>
       </c>
-      <c r="E204" s="7" t="inlineStr">
+      <c r="E209" s="7" t="inlineStr">
         <is>
           <t>17-1-1</t>
         </is>
       </c>
-      <c r="F204" s="7" t="inlineStr">
+      <c r="F209" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
         </is>
       </c>
-      <c r="G204" s="7" t="inlineStr">
+      <c r="G209" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H204" s="7" t="inlineStr">
+      <c r="H209" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I204" s="7" t="inlineStr">
+      <c r="I209" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="17" t="n"/>
-      <c r="B205" s="17" t="n"/>
-      <c r="C205" s="17" t="n"/>
-      <c r="D205" s="17" t="n"/>
-      <c r="E205" s="7" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="4" t="n"/>
+      <c r="B210" s="4" t="n"/>
+      <c r="C210" s="4" t="n"/>
+      <c r="D210" s="4" t="n"/>
+      <c r="E210" s="7" t="inlineStr">
         <is>
           <t>17-1-2</t>
         </is>
       </c>
-      <c r="F205" s="7" t="inlineStr">
+      <c r="F210" s="7" t="inlineStr">
         <is>
           <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
         </is>
       </c>
-      <c r="G205" s="7" t="inlineStr">
+      <c r="G210" s="7" t="inlineStr">
         <is>
           <t>1.自分と他人の読書計画をそれぞれ用意する
 2.読書計画一覧ページを開く</t>
         </is>
       </c>
-      <c r="H205" s="7" t="inlineStr">
+      <c r="H210" s="7" t="inlineStr">
         <is>
           <t>自分の計画のみが、target_dateの昇順で表示される</t>
         </is>
       </c>
-      <c r="I205" s="17" t="n"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="17" t="n"/>
-      <c r="B206" s="17" t="n"/>
-      <c r="C206" s="17" t="n"/>
-      <c r="D206" s="17" t="n"/>
-      <c r="E206" s="7" t="inlineStr">
+      <c r="I210" s="4" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="n"/>
+      <c r="B211" s="4" t="n"/>
+      <c r="C211" s="4" t="n"/>
+      <c r="D211" s="4" t="n"/>
+      <c r="E211" s="7" t="inlineStr">
         <is>
           <t>17-1-3</t>
         </is>
       </c>
-      <c r="F206" s="7" t="inlineStr">
+      <c r="F211" s="7" t="inlineStr">
         <is>
           <t>ステータスで絞り込んで表示できる</t>
         </is>
       </c>
-      <c r="G206" s="7" t="inlineStr">
+      <c r="G211" s="7" t="inlineStr">
         <is>
           <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
 2.statusパラメータを指定して一覧を開く</t>
         </is>
       </c>
-      <c r="H206" s="7" t="inlineStr">
+      <c r="H211" s="7" t="inlineStr">
         <is>
           <t>指定したステータスの計画のみ表示される</t>
         </is>
       </c>
-      <c r="I206" s="17" t="n"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="17" t="n"/>
-      <c r="B207" s="17" t="n"/>
-      <c r="C207" s="17" t="n"/>
-      <c r="D207" s="17" t="n"/>
-      <c r="E207" s="7" t="inlineStr">
+      <c r="I211" s="4" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="n"/>
+      <c r="B212" s="4" t="n"/>
+      <c r="C212" s="4" t="n"/>
+      <c r="D212" s="4" t="n"/>
+      <c r="E212" s="7" t="inlineStr">
         <is>
           <t>17-1-4</t>
         </is>
       </c>
-      <c r="F207" s="7" t="inlineStr">
+      <c r="F212" s="7" t="inlineStr">
         <is>
           <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
         </is>
       </c>
-      <c r="G207" s="7" t="inlineStr">
+      <c r="G212" s="7" t="inlineStr">
         <is>
           <t>1.ある書籍について進行中の計画を作成する
 2.計画作成ページを開く</t>
         </is>
       </c>
-      <c r="H207" s="7" t="inlineStr">
+      <c r="H212" s="7" t="inlineStr">
         <is>
           <t>書籍選択肢にその書籍が表示されない</t>
         </is>
       </c>
-      <c r="I207" s="17" t="n"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="17" t="n"/>
-      <c r="B208" s="17" t="n"/>
-      <c r="C208" s="17" t="n"/>
-      <c r="D208" s="17" t="n"/>
-      <c r="E208" s="7" t="inlineStr">
+      <c r="I212" s="4" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="n"/>
+      <c r="B213" s="4" t="n"/>
+      <c r="C213" s="4" t="n"/>
+      <c r="D213" s="4" t="n"/>
+      <c r="E213" s="7" t="inlineStr">
         <is>
           <t>17-1-5</t>
         </is>
       </c>
-      <c r="F208" s="7" t="inlineStr">
+      <c r="F213" s="7" t="inlineStr">
         <is>
           <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
         </is>
       </c>
-      <c r="G208" s="7" t="inlineStr">
+      <c r="G213" s="7" t="inlineStr">
         <is>
           <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H208" s="7" t="inlineStr">
+      <c r="H213" s="7" t="inlineStr">
         <is>
           <t>403Forbiddenになり、計画は作成されない</t>
         </is>
       </c>
-      <c r="I208" s="17" t="n"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="17" t="n"/>
-      <c r="B209" s="17" t="n"/>
-      <c r="C209" s="17" t="n"/>
-      <c r="D209" s="17" t="n"/>
-      <c r="E209" s="7" t="inlineStr">
+      <c r="I213" s="4" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="n"/>
+      <c r="B214" s="4" t="n"/>
+      <c r="C214" s="4" t="n"/>
+      <c r="D214" s="4" t="n"/>
+      <c r="E214" s="7" t="inlineStr">
         <is>
           <t>17-1-6</t>
         </is>
       </c>
-      <c r="F209" s="7" t="inlineStr">
+      <c r="F214" s="7" t="inlineStr">
         <is>
           <t>完了済みの計画がある書籍は再度計画を作成できる</t>
         </is>
       </c>
-      <c r="G209" s="7" t="inlineStr">
+      <c r="G214" s="7" t="inlineStr">
         <is>
           <t>1.ある書籍の計画を読了(完了)状態にする
 2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H209" s="7" t="inlineStr">
+      <c r="H214" s="7" t="inlineStr">
         <is>
           <t>新しい計画が作成される</t>
         </is>
       </c>
-      <c r="I209" s="17" t="n"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="17" t="n"/>
-      <c r="B210" s="17" t="n"/>
-      <c r="C210" s="17" t="n"/>
-      <c r="D210" s="17" t="n"/>
-      <c r="E210" s="7" t="inlineStr">
+      <c r="I214" s="4" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="n"/>
+      <c r="B215" s="4" t="n"/>
+      <c r="C215" s="4" t="n"/>
+      <c r="D215" s="4" t="n"/>
+      <c r="E215" s="7" t="inlineStr">
         <is>
           <t>17-1-7</t>
         </is>
       </c>
-      <c r="F210" s="7" t="inlineStr">
+      <c r="F215" s="7" t="inlineStr">
         <is>
           <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
-      <c r="G210" s="7" t="inlineStr">
+      <c r="G215" s="7" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
 2.期日を入力せずに登録する</t>
         </is>
       </c>
-      <c r="H210" s="7" t="inlineStr">
+      <c r="H215" s="7" t="inlineStr">
         <is>
           <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I210" s="17" t="n"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="17" t="n"/>
-      <c r="B211" s="17" t="n"/>
-      <c r="C211" s="17" t="n"/>
-      <c r="D211" s="17" t="n"/>
-      <c r="E211" s="7" t="inlineStr">
+      <c r="I215" s="4" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="n"/>
+      <c r="B216" s="4" t="n"/>
+      <c r="C216" s="4" t="n"/>
+      <c r="D216" s="4" t="n"/>
+      <c r="E216" s="7" t="inlineStr">
         <is>
           <t>17-1-8</t>
         </is>
       </c>
-      <c r="F211" s="7" t="inlineStr">
+      <c r="F216" s="7" t="inlineStr">
         <is>
           <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
-      <c r="G211" s="7" t="inlineStr">
+      <c r="G216" s="7" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
 2.過去の日付を期日に指定して登録する</t>
         </is>
       </c>
-      <c r="H211" s="7" t="inlineStr">
+      <c r="H216" s="7" t="inlineStr">
         <is>
           <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I211" s="17" t="n"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="17" t="n"/>
-      <c r="B212" s="17" t="n"/>
-      <c r="C212" s="17" t="n"/>
-      <c r="D212" s="17" t="n"/>
-      <c r="E212" s="7" t="inlineStr">
+      <c r="I216" s="4" t="n"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="n"/>
+      <c r="B217" s="4" t="n"/>
+      <c r="C217" s="4" t="n"/>
+      <c r="D217" s="4" t="n"/>
+      <c r="E217" s="7" t="inlineStr">
         <is>
           <t>17-1-9</t>
         </is>
       </c>
-      <c r="F212" s="7" t="inlineStr">
+      <c r="F217" s="7" t="inlineStr">
         <is>
           <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
         </is>
       </c>
-      <c r="G212" s="7" t="inlineStr">
+      <c r="G217" s="7" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
 2.書籍・期日を正しく入力して登録する</t>
         </is>
       </c>
-      <c r="H212" s="7" t="inlineStr">
+      <c r="H217" s="7" t="inlineStr">
         <is>
           <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
         </is>
       </c>
-      <c r="I212" s="17" t="n"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="17" t="n"/>
-      <c r="B213" s="17" t="n"/>
-      <c r="C213" s="17" t="n"/>
-      <c r="D213" s="17" t="n"/>
-      <c r="E213" s="7" t="inlineStr">
+      <c r="I217" s="4" t="n"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="n"/>
+      <c r="B218" s="4" t="n"/>
+      <c r="C218" s="4" t="n"/>
+      <c r="D218" s="4" t="n"/>
+      <c r="E218" s="7" t="inlineStr">
         <is>
           <t>17-1-10</t>
         </is>
       </c>
-      <c r="F213" s="7" t="inlineStr">
+      <c r="F218" s="7" t="inlineStr">
         <is>
           <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
         </is>
       </c>
-      <c r="G213" s="7" t="inlineStr">
+      <c r="G218" s="7" t="inlineStr">
         <is>
           <t>1.進行中の計画に対して読了操作を行う</t>
         </is>
       </c>
-      <c r="H213" s="7" t="inlineStr">
+      <c r="H218" s="7" t="inlineStr">
         <is>
           <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
         </is>
       </c>
-      <c r="I213" s="17" t="n"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="17" t="n"/>
-      <c r="B214" s="17" t="n"/>
-      <c r="C214" s="17" t="n"/>
-      <c r="D214" s="17" t="n"/>
-      <c r="E214" s="7" t="inlineStr">
+      <c r="I218" s="4" t="n"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="n"/>
+      <c r="B219" s="4" t="n"/>
+      <c r="C219" s="4" t="n"/>
+      <c r="D219" s="4" t="n"/>
+      <c r="E219" s="7" t="inlineStr">
         <is>
           <t>17-1-11</t>
         </is>
       </c>
-      <c r="F214" s="7" t="inlineStr">
+      <c r="F219" s="7" t="inlineStr">
         <is>
           <t>他人が作成した読書計画は読了・削除できない</t>
         </is>
       </c>
-      <c r="G214" s="7" t="inlineStr">
+      <c r="G219" s="7" t="inlineStr">
         <is>
           <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
         </is>
       </c>
-      <c r="H214" s="7" t="inlineStr">
+      <c r="H219" s="7" t="inlineStr">
         <is>
           <t>いずれも403Forbiddenになる</t>
         </is>
       </c>
-      <c r="I214" s="17" t="n"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="17" t="n"/>
-      <c r="B215" s="17" t="n"/>
-      <c r="C215" s="17" t="n"/>
-      <c r="D215" s="17" t="n"/>
-      <c r="E215" s="7" t="inlineStr">
+      <c r="I219" s="4" t="n"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="n"/>
+      <c r="B220" s="4" t="n"/>
+      <c r="C220" s="4" t="n"/>
+      <c r="D220" s="4" t="n"/>
+      <c r="E220" s="7" t="inlineStr">
         <is>
           <t>17-1-12</t>
         </is>
       </c>
-      <c r="F215" s="7" t="inlineStr">
+      <c r="F220" s="7" t="inlineStr">
         <is>
           <t>自分が作成した読書計画は削除できる</t>
         </is>
       </c>
-      <c r="G215" s="7" t="inlineStr">
+      <c r="G220" s="7" t="inlineStr">
         <is>
           <t>1.自分が作成した計画の削除ボタンを押す</t>
         </is>
       </c>
-      <c r="H215" s="7" t="inlineStr">
+      <c r="H220" s="7" t="inlineStr">
         <is>
           <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
         </is>
       </c>
-      <c r="I215" s="17" t="n"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="17" t="n"/>
-      <c r="B216" s="17" t="n"/>
-      <c r="C216" s="17" t="n"/>
-      <c r="D216" s="17" t="n"/>
-      <c r="E216" s="9" t="inlineStr">
+      <c r="I220" s="4" t="n"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="n"/>
+      <c r="B221" s="4" t="n"/>
+      <c r="C221" s="4" t="n"/>
+      <c r="D221" s="4" t="n"/>
+      <c r="E221" s="9" t="inlineStr">
         <is>
           <t>17-1-13</t>
         </is>
       </c>
-      <c r="F216" s="9" t="inlineStr">
+      <c r="F221" s="9" t="inlineStr">
         <is>
           <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
         </is>
       </c>
-      <c r="G216" s="9" t="inlineStr">
+      <c r="G221" s="9" t="inlineStr">
         <is>
           <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
 2.その読書計画を削除する</t>
         </is>
       </c>
-      <c r="H216" s="9" t="inlineStr">
+      <c r="H221" s="9" t="inlineStr">
         <is>
           <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
         </is>
       </c>
-      <c r="I216" s="17" t="n"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="17" t="n"/>
-      <c r="B217" s="17" t="n"/>
-      <c r="C217" s="17" t="n"/>
-      <c r="D217" s="17" t="n"/>
-      <c r="E217" s="9" t="inlineStr">
+      <c r="I221" s="4" t="n"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="n"/>
+      <c r="B222" s="4" t="n"/>
+      <c r="C222" s="4" t="n"/>
+      <c r="D222" s="4" t="n"/>
+      <c r="E222" s="9" t="inlineStr">
         <is>
           <t>17-1-14</t>
         </is>
       </c>
-      <c r="F217" s="9" t="inlineStr">
+      <c r="F222" s="9" t="inlineStr">
         <is>
           <t>ステータスが「完了」の計画は、読了操作を行えない</t>
         </is>
       </c>
-      <c r="G217" s="9" t="inlineStr">
+      <c r="G222" s="9" t="inlineStr">
         <is>
           <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H217" s="9" t="inlineStr">
+      <c r="H222" s="9" t="inlineStr">
         <is>
           <t>403Forbiddenになり、completed_atは変更されない</t>
         </is>
       </c>
-      <c r="I217" s="17" t="n"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="17" t="n"/>
-      <c r="B218" s="17" t="n"/>
-      <c r="C218" s="17" t="n"/>
-      <c r="D218" s="17" t="n"/>
-      <c r="E218" s="9" t="inlineStr">
+      <c r="I222" s="4" t="n"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="n"/>
+      <c r="B223" s="4" t="n"/>
+      <c r="C223" s="4" t="n"/>
+      <c r="D223" s="4" t="n"/>
+      <c r="E223" s="9" t="inlineStr">
         <is>
           <t>17-1-15</t>
         </is>
       </c>
-      <c r="F218" s="9" t="inlineStr">
+      <c r="F223" s="9" t="inlineStr">
         <is>
           <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
         </is>
       </c>
-      <c r="G218" s="9" t="inlineStr">
+      <c r="G223" s="9" t="inlineStr">
         <is>
           <t>1.ある書籍の計画を「期限切れ」の状態にする
 2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H218" s="9" t="inlineStr">
+      <c r="H223" s="9" t="inlineStr">
         <is>
           <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
         </is>
       </c>
-      <c r="I218" s="17" t="n"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="17" t="n"/>
-      <c r="B219" s="17" t="n"/>
-      <c r="C219" s="17" t="n"/>
-      <c r="D219" s="17" t="n"/>
-      <c r="E219" s="9" t="inlineStr">
+      <c r="I223" s="4" t="n"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="n"/>
+      <c r="B224" s="4" t="n"/>
+      <c r="C224" s="4" t="n"/>
+      <c r="D224" s="4" t="n"/>
+      <c r="E224" s="9" t="inlineStr">
         <is>
           <t>17-1-16</t>
         </is>
       </c>
-      <c r="F219" s="9" t="inlineStr">
+      <c r="F224" s="9" t="inlineStr">
         <is>
           <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G219" s="9" t="inlineStr">
+      <c r="G224" s="9" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
 2.書籍を選択せずに期日を入力して登録する</t>
         </is>
       </c>
-      <c r="H219" s="9" t="inlineStr">
+      <c r="H224" s="9" t="inlineStr">
         <is>
           <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I219" s="17" t="n"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="17" t="n"/>
-      <c r="B220" s="17" t="n"/>
-      <c r="C220" s="17" t="n"/>
-      <c r="D220" s="17" t="n"/>
-      <c r="E220" s="9" t="inlineStr">
+      <c r="I224" s="4" t="n"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="n"/>
+      <c r="B225" s="4" t="n"/>
+      <c r="C225" s="4" t="n"/>
+      <c r="D225" s="4" t="n"/>
+      <c r="E225" s="9" t="inlineStr">
         <is>
           <t>17-1-17</t>
         </is>
       </c>
-      <c r="F220" s="9" t="inlineStr">
+      <c r="F225" s="9" t="inlineStr">
         <is>
           <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G220" s="9" t="inlineStr">
+      <c r="G225" s="9" t="inlineStr">
         <is>
           <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H220" s="9" t="inlineStr">
+      <c r="H225" s="9" t="inlineStr">
         <is>
           <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I220" s="17" t="n"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="17" t="n"/>
-      <c r="B221" s="17" t="n"/>
-      <c r="C221" s="17" t="n"/>
-      <c r="D221" s="17" t="n"/>
-      <c r="E221" s="9" t="inlineStr">
+      <c r="I225" s="4" t="n"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="n"/>
+      <c r="B226" s="4" t="n"/>
+      <c r="C226" s="4" t="n"/>
+      <c r="D226" s="4" t="n"/>
+      <c r="E226" s="9" t="inlineStr">
         <is>
           <t>17-1-18</t>
         </is>
       </c>
-      <c r="F221" s="9" t="inlineStr">
+      <c r="F226" s="9" t="inlineStr">
         <is>
           <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G221" s="9" t="inlineStr">
+      <c r="G226" s="9" t="inlineStr">
         <is>
           <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H221" s="9" t="inlineStr">
+      <c r="H226" s="9" t="inlineStr">
         <is>
           <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I221" s="17" t="n"/>
-    </row>
-    <row r="222">
-      <c r="A222" s="17" t="n"/>
-      <c r="B222" s="17" t="n"/>
-      <c r="C222" s="17" t="n"/>
-      <c r="D222" s="17" t="n"/>
-      <c r="E222" s="9" t="inlineStr">
+      <c r="I226" s="4" t="n"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="n"/>
+      <c r="B227" s="4" t="n"/>
+      <c r="C227" s="4" t="n"/>
+      <c r="D227" s="4" t="n"/>
+      <c r="E227" s="9" t="inlineStr">
         <is>
           <t>17-1-19</t>
         </is>
       </c>
-      <c r="F222" s="9" t="inlineStr">
+      <c r="F227" s="9" t="inlineStr">
         <is>
           <t>期日が日付形式でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G222" s="9" t="inlineStr">
+      <c r="G227" s="9" t="inlineStr">
         <is>
           <t>1.書籍と、日付として不正な期日(例:abc)を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H222" s="9" t="inlineStr">
+      <c r="H227" s="9" t="inlineStr">
         <is>
           <t>「正しい日付を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I222" s="17" t="n"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="18" t="n"/>
-      <c r="B223" s="18" t="n"/>
-      <c r="C223" s="18" t="n"/>
-      <c r="D223" s="18" t="n"/>
-      <c r="E223" s="9" t="inlineStr">
+      <c r="I227" s="4" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="5" t="n"/>
+      <c r="B228" s="5" t="n"/>
+      <c r="C228" s="5" t="n"/>
+      <c r="D228" s="5" t="n"/>
+      <c r="E228" s="9" t="inlineStr">
         <is>
           <t>17-1-20</t>
         </is>
       </c>
-      <c r="F223" s="9" t="inlineStr">
+      <c r="F228" s="9" t="inlineStr">
         <is>
           <t>期日に今日の日付を指定した場合、計画を作成できる</t>
         </is>
       </c>
-      <c r="G223" s="9" t="inlineStr">
+      <c r="G228" s="9" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
 2.書籍を選択し、期日に今日の日付を指定して登録する</t>
         </is>
       </c>
-      <c r="H223" s="9" t="inlineStr">
+      <c r="H228" s="9" t="inlineStr">
         <is>
           <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される（今日の日付は指定可能）</t>
         </is>
       </c>
-      <c r="I223" s="18" t="n"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="7" t="inlineStr">
+      <c r="I228" s="5" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="7" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B224" s="7" t="inlineStr">
+      <c r="B229" s="7" t="inlineStr">
         <is>
           <t>読書計画（期限変更）</t>
         </is>
       </c>
-      <c r="C224" s="7" t="inlineStr">
+      <c r="C229" s="7" t="inlineStr">
         <is>
           <t>18-1</t>
         </is>
       </c>
-      <c r="D224" s="7" t="inlineStr">
+      <c r="D229" s="7" t="inlineStr">
         <is>
           <t>読書計画の期日変更</t>
         </is>
       </c>
-      <c r="E224" s="7" t="inlineStr">
+      <c r="E229" s="7" t="inlineStr">
         <is>
           <t>18-1-1</t>
         </is>
       </c>
-      <c r="F224" s="7" t="inlineStr">
+      <c r="F229" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
         </is>
       </c>
-      <c r="G224" s="7" t="inlineStr">
+      <c r="G229" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H224" s="7" t="inlineStr">
+      <c r="H229" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I224" s="7" t="inlineStr">
+      <c r="I229" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="17" t="n"/>
-      <c r="B225" s="17" t="n"/>
-      <c r="C225" s="17" t="n"/>
-      <c r="D225" s="17" t="n"/>
-      <c r="E225" s="7" t="inlineStr">
+    <row r="230">
+      <c r="A230" s="4" t="n"/>
+      <c r="B230" s="4" t="n"/>
+      <c r="C230" s="4" t="n"/>
+      <c r="D230" s="4" t="n"/>
+      <c r="E230" s="7" t="inlineStr">
         <is>
           <t>18-1-2</t>
         </is>
       </c>
-      <c r="F225" s="7" t="inlineStr">
+      <c r="F230" s="7" t="inlineStr">
         <is>
           <t>他人が作成した読書計画の期日は変更できない</t>
         </is>
       </c>
-      <c r="G225" s="7" t="inlineStr">
+      <c r="G230" s="7" t="inlineStr">
         <is>
           <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
-      <c r="H225" s="7" t="inlineStr">
+      <c r="H230" s="7" t="inlineStr">
         <is>
           <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
-      <c r="I225" s="17" t="n"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="17" t="n"/>
-      <c r="B226" s="17" t="n"/>
-      <c r="C226" s="17" t="n"/>
-      <c r="D226" s="17" t="n"/>
-      <c r="E226" s="7" t="inlineStr">
+      <c r="I230" s="4" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="n"/>
+      <c r="B231" s="4" t="n"/>
+      <c r="C231" s="4" t="n"/>
+      <c r="D231" s="4" t="n"/>
+      <c r="E231" s="7" t="inlineStr">
         <is>
           <t>18-1-3</t>
         </is>
       </c>
-      <c r="F226" s="7" t="inlineStr">
+      <c r="F231" s="7" t="inlineStr">
         <is>
           <t>編集画面を開くと現在の期日が初期表示される</t>
         </is>
       </c>
-      <c r="G226" s="7" t="inlineStr">
+      <c r="G231" s="7" t="inlineStr">
         <is>
           <t>1.自分が作成した計画の編集ページを開く</t>
         </is>
       </c>
-      <c r="H226" s="7" t="inlineStr">
+      <c r="H231" s="7" t="inlineStr">
         <is>
           <t>現在登録されている期日が入力欄に表示される</t>
         </is>
       </c>
-      <c r="I226" s="17" t="n"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="17" t="n"/>
-      <c r="B227" s="17" t="n"/>
-      <c r="C227" s="17" t="n"/>
-      <c r="D227" s="17" t="n"/>
-      <c r="E227" s="7" t="inlineStr">
+      <c r="I231" s="4" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="n"/>
+      <c r="B232" s="4" t="n"/>
+      <c r="C232" s="4" t="n"/>
+      <c r="D232" s="4" t="n"/>
+      <c r="E232" s="7" t="inlineStr">
         <is>
           <t>18-1-4</t>
         </is>
       </c>
-      <c r="F227" s="7" t="inlineStr">
+      <c r="F232" s="7" t="inlineStr">
         <is>
           <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
-      <c r="G227" s="7" t="inlineStr">
+      <c r="G232" s="7" t="inlineStr">
         <is>
           <t>1.編集ページを開く
 2.期日を空にして更新する</t>
         </is>
       </c>
-      <c r="H227" s="7" t="inlineStr">
+      <c r="H232" s="7" t="inlineStr">
         <is>
           <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I227" s="17" t="n"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="17" t="n"/>
-      <c r="B228" s="17" t="n"/>
-      <c r="C228" s="17" t="n"/>
-      <c r="D228" s="17" t="n"/>
-      <c r="E228" s="7" t="inlineStr">
+      <c r="I232" s="4" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="n"/>
+      <c r="B233" s="4" t="n"/>
+      <c r="C233" s="4" t="n"/>
+      <c r="D233" s="4" t="n"/>
+      <c r="E233" s="7" t="inlineStr">
         <is>
           <t>18-1-5</t>
         </is>
       </c>
-      <c r="F228" s="7" t="inlineStr">
+      <c r="F233" s="7" t="inlineStr">
         <is>
           <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
-      <c r="G228" s="7" t="inlineStr">
+      <c r="G233" s="7" t="inlineStr">
         <is>
           <t>1.編集ページを開く
 2.過去の日付に変更して更新する</t>
         </is>
       </c>
-      <c r="H228" s="7" t="inlineStr">
+      <c r="H233" s="7" t="inlineStr">
         <is>
           <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I228" s="17" t="n"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="17" t="n"/>
-      <c r="B229" s="17" t="n"/>
-      <c r="C229" s="17" t="n"/>
-      <c r="D229" s="17" t="n"/>
-      <c r="E229" s="7" t="inlineStr">
+      <c r="I233" s="4" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="n"/>
+      <c r="B234" s="4" t="n"/>
+      <c r="C234" s="4" t="n"/>
+      <c r="D234" s="4" t="n"/>
+      <c r="E234" s="7" t="inlineStr">
         <is>
           <t>18-1-6</t>
         </is>
       </c>
-      <c r="F229" s="7" t="inlineStr">
+      <c r="F234" s="7" t="inlineStr">
         <is>
           <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
         </is>
       </c>
-      <c r="G229" s="7" t="inlineStr">
+      <c r="G234" s="7" t="inlineStr">
         <is>
           <t>1.編集ページを開く
 2.未来の日付に正しく変更して更新する</t>
         </is>
       </c>
-      <c r="H229" s="7" t="inlineStr">
+      <c r="H234" s="7" t="inlineStr">
         <is>
           <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
         </is>
       </c>
-      <c r="I229" s="17" t="n"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="17" t="n"/>
-      <c r="B230" s="17" t="n"/>
-      <c r="C230" s="17" t="n"/>
-      <c r="D230" s="17" t="n"/>
-      <c r="E230" s="7" t="inlineStr">
+      <c r="I234" s="4" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="n"/>
+      <c r="B235" s="4" t="n"/>
+      <c r="C235" s="4" t="n"/>
+      <c r="D235" s="4" t="n"/>
+      <c r="E235" s="7" t="inlineStr">
         <is>
           <t>18-1-7</t>
         </is>
       </c>
-      <c r="F230" s="7" t="inlineStr">
+      <c r="F235" s="7" t="inlineStr">
         <is>
           <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
         </is>
       </c>
-      <c r="G230" s="7" t="inlineStr">
+      <c r="G235" s="7" t="inlineStr">
         <is>
           <t>1.期日が過去で「進行中」の計画を用意する
 2.読書計画一覧または編集ページを開く</t>
         </is>
       </c>
-      <c r="H230" s="7" t="inlineStr">
+      <c r="H235" s="7" t="inlineStr">
         <is>
           <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
         </is>
       </c>
-      <c r="I230" s="17" t="n"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="17" t="n"/>
-      <c r="B231" s="17" t="n"/>
-      <c r="C231" s="17" t="n"/>
-      <c r="D231" s="17" t="n"/>
-      <c r="E231" s="7" t="inlineStr">
+      <c r="I235" s="4" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="n"/>
+      <c r="B236" s="4" t="n"/>
+      <c r="C236" s="4" t="n"/>
+      <c r="D236" s="4" t="n"/>
+      <c r="E236" s="7" t="inlineStr">
         <is>
           <t>18-1-8</t>
         </is>
       </c>
-      <c r="F231" s="7" t="inlineStr">
+      <c r="F236" s="7" t="inlineStr">
         <is>
           <t>ステータスが「完了」の計画は期日を変更できない</t>
         </is>
       </c>
-      <c r="G231" s="7" t="inlineStr">
+      <c r="G236" s="7" t="inlineStr">
         <is>
           <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
-      <c r="H231" s="7" t="inlineStr">
+      <c r="H236" s="7" t="inlineStr">
         <is>
           <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
-      <c r="I231" s="17" t="n"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="17" t="n"/>
-      <c r="B232" s="17" t="n"/>
-      <c r="C232" s="17" t="n"/>
-      <c r="D232" s="17" t="n"/>
-      <c r="E232" s="7" t="inlineStr">
+      <c r="I236" s="4" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="n"/>
+      <c r="B237" s="4" t="n"/>
+      <c r="C237" s="4" t="n"/>
+      <c r="D237" s="4" t="n"/>
+      <c r="E237" s="7" t="inlineStr">
         <is>
           <t>18-1-9</t>
         </is>
       </c>
-      <c r="F232" s="7" t="inlineStr">
+      <c r="F237" s="7" t="inlineStr">
         <is>
           <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
         </is>
       </c>
-      <c r="G232" s="7" t="inlineStr">
+      <c r="G237" s="7" t="inlineStr">
         <is>
           <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H232" s="7" t="inlineStr">
+      <c r="H237" s="7" t="inlineStr">
         <is>
           <t>403Forbiddenになり、編集ページは表示されない</t>
         </is>
       </c>
-      <c r="I232" s="17" t="n"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="17" t="n"/>
-      <c r="B233" s="17" t="n"/>
-      <c r="C233" s="17" t="n"/>
-      <c r="D233" s="17" t="n"/>
-      <c r="E233" s="7" t="inlineStr">
+      <c r="I237" s="4" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="n"/>
+      <c r="B238" s="4" t="n"/>
+      <c r="C238" s="4" t="n"/>
+      <c r="D238" s="4" t="n"/>
+      <c r="E238" s="7" t="inlineStr">
         <is>
           <t>18-1-10</t>
         </is>
       </c>
-      <c r="F233" s="7" t="inlineStr">
+      <c r="F238" s="7" t="inlineStr">
         <is>
           <t>他人が作成した読書計画の編集ページにはアクセスできない</t>
         </is>
       </c>
-      <c r="G233" s="7" t="inlineStr">
+      <c r="G238" s="7" t="inlineStr">
         <is>
           <t>1.他人が作成した計画の編集ページのURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H233" s="7" t="inlineStr">
+      <c r="H238" s="7" t="inlineStr">
         <is>
           <t>403Forbiddenになり、編集ページは表示されない</t>
         </is>
       </c>
-      <c r="I233" s="17" t="n"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="18" t="n"/>
-      <c r="B234" s="18" t="n"/>
-      <c r="C234" s="18" t="n"/>
-      <c r="D234" s="18" t="n"/>
-      <c r="E234" s="7" t="inlineStr">
+      <c r="I238" s="4" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="n"/>
+      <c r="B239" s="5" t="n"/>
+      <c r="C239" s="5" t="n"/>
+      <c r="D239" s="5" t="n"/>
+      <c r="E239" s="7" t="inlineStr">
         <is>
           <t>18-1-11</t>
         </is>
       </c>
-      <c r="F234" s="7" t="inlineStr">
+      <c r="F239" s="7" t="inlineStr">
         <is>
           <t>同じ書籍に「進行中」の計画がある場合、「期限切れ」の計画は編集・更新できない</t>
         </is>
       </c>
-      <c r="G234" s="7" t="inlineStr">
+      <c r="G239" s="7" t="inlineStr">
         <is>
           <t>1.同じ書籍について、「期限切れ」の計画と「進行中」の計画をそれぞれ用意する
 2.「期限切れ」の計画の編集ページのURLに直接アクセスする
 3.「期限切れ」の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
-      <c r="H234" s="7" t="inlineStr">
+      <c r="H239" s="7" t="inlineStr">
         <is>
           <t>いずれも403Forbiddenになり、「期限切れ」の計画のステータス・期日は変更されない（同じ書籍の「進行中」の計画が2件になることを防ぐ）</t>
         </is>
       </c>
-      <c r="I234" s="18" t="n"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="7" t="inlineStr">
+      <c r="I239" s="5" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B235" s="7" t="inlineStr">
+      <c r="B240" s="7" t="inlineStr">
         <is>
           <t>リマインダーバッチ</t>
         </is>
       </c>
-      <c r="C235" s="7" t="inlineStr">
+      <c r="C240" s="7" t="inlineStr">
         <is>
           <t>19-1</t>
         </is>
       </c>
-      <c r="D235" s="7" t="inlineStr">
+      <c r="D240" s="7" t="inlineStr">
         <is>
           <t>日次バッチ(reading-plans:daily)によるリマインダー通知</t>
         </is>
       </c>
-      <c r="E235" s="7" t="inlineStr">
+      <c r="E240" s="7" t="inlineStr">
         <is>
           <t>19-1-1</t>
         </is>
       </c>
-      <c r="F235" s="7" t="inlineStr">
+      <c r="F240" s="7" t="inlineStr">
         <is>
           <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
         </is>
       </c>
-      <c r="G235" s="7" t="inlineStr">
+      <c r="G240" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日後・ステータス進行中の計画を用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
-      <c r="H235" s="7" t="inlineStr">
+      <c r="H240" s="7" t="inlineStr">
         <is>
           <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_before)・title(「読書期限のお知らせ」)・body(「「(書籍名)」の読書期限まであと3日です。」)が含まれる</t>
         </is>
       </c>
-      <c r="I235" s="7" t="inlineStr">
+      <c r="I240" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="17" t="n"/>
-      <c r="B236" s="17" t="n"/>
-      <c r="C236" s="17" t="n"/>
-      <c r="D236" s="17" t="n"/>
-      <c r="E236" s="7" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="4" t="n"/>
+      <c r="B241" s="4" t="n"/>
+      <c r="C241" s="4" t="n"/>
+      <c r="D241" s="4" t="n"/>
+      <c r="E241" s="7" t="inlineStr">
         <is>
           <t>19-1-2</t>
         </is>
       </c>
-      <c r="F236" s="7" t="inlineStr">
+      <c r="F241" s="7" t="inlineStr">
         <is>
           <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
         </is>
       </c>
-      <c r="G236" s="7" t="inlineStr">
+      <c r="G241" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが本日・ステータス進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H236" s="7" t="inlineStr">
+      <c r="H241" s="7" t="inlineStr">
         <is>
           <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される。通知のdataには、plan_id・book_title・timing(on_due_date)・title(「読書期限当日のお知らせ」)・body(「「(書籍名)」の読書期限は本日までです。」)が含まれる</t>
         </is>
       </c>
-      <c r="I236" s="17" t="n"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="17" t="n"/>
-      <c r="B237" s="17" t="n"/>
-      <c r="C237" s="17" t="n"/>
-      <c r="D237" s="17" t="n"/>
-      <c r="E237" s="7" t="inlineStr">
+      <c r="I241" s="4" t="n"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="n"/>
+      <c r="B242" s="4" t="n"/>
+      <c r="C242" s="4" t="n"/>
+      <c r="D242" s="4" t="n"/>
+      <c r="E242" s="7" t="inlineStr">
         <is>
           <t>19-1-3</t>
         </is>
       </c>
-      <c r="F237" s="7" t="inlineStr">
+      <c r="F242" s="7" t="inlineStr">
         <is>
           <t>期限切れから3日後の計画に再エンゲージメント通知が送信される</t>
         </is>
       </c>
-      <c r="G237" s="7" t="inlineStr">
+      <c r="G242" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日前・ステータス期限切れの計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H237" s="7" t="inlineStr">
+      <c r="H242" s="7" t="inlineStr">
         <is>
           <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
         </is>
       </c>
-      <c r="I237" s="17" t="n"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="17" t="n"/>
-      <c r="B238" s="17" t="n"/>
-      <c r="C238" s="17" t="n"/>
-      <c r="D238" s="17" t="n"/>
-      <c r="E238" s="7" t="inlineStr">
+      <c r="I242" s="4" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="n"/>
+      <c r="B243" s="4" t="n"/>
+      <c r="C243" s="4" t="n"/>
+      <c r="D243" s="4" t="n"/>
+      <c r="E243" s="7" t="inlineStr">
         <is>
           <t>19-1-4</t>
         </is>
       </c>
-      <c r="F238" s="7" t="inlineStr">
+      <c r="F243" s="7" t="inlineStr">
         <is>
           <t>いずれの条件にも該当しない計画には通知が送信されない</t>
         </is>
       </c>
-      <c r="G238" s="7" t="inlineStr">
+      <c r="G243" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H238" s="7" t="inlineStr">
+      <c r="H243" s="7" t="inlineStr">
         <is>
           <t>その計画のユーザーに通知が送信されない</t>
         </is>
       </c>
-      <c r="I238" s="17" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="18" t="n"/>
-      <c r="B239" s="18" t="n"/>
-      <c r="C239" s="18" t="n"/>
-      <c r="D239" s="18" t="n"/>
-      <c r="E239" s="7" t="inlineStr">
+      <c r="I243" s="4" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="5" t="n"/>
+      <c r="B244" s="5" t="n"/>
+      <c r="C244" s="5" t="n"/>
+      <c r="D244" s="5" t="n"/>
+      <c r="E244" s="7" t="inlineStr">
         <is>
           <t>19-1-5</t>
         </is>
       </c>
-      <c r="F239" s="7" t="inlineStr">
+      <c r="F244" s="7" t="inlineStr">
         <is>
           <t>ステータスが「完了」の計画には、期日の条件に合っていても通知が送信されない</t>
         </is>
       </c>
-      <c r="G239" s="7" t="inlineStr">
+      <c r="G244" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日後・本日・3日前で、ステータスが完了の計画をそれぞれ用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
-      <c r="H239" s="7" t="inlineStr">
+      <c r="H244" s="7" t="inlineStr">
         <is>
           <t>いずれの計画のユーザーにも通知が送信されない</t>
         </is>
       </c>
-      <c r="I239" s="18" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="7" t="inlineStr">
+      <c r="I244" s="5" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B240" s="7" t="inlineStr">
+      <c r="B245" s="7" t="inlineStr">
         <is>
           <t>自動失効バッチ</t>
         </is>
       </c>
-      <c r="C240" s="7" t="inlineStr">
+      <c r="C245" s="7" t="inlineStr">
         <is>
           <t>20-1</t>
         </is>
       </c>
-      <c r="D240" s="7" t="inlineStr">
+      <c r="D245" s="7" t="inlineStr">
         <is>
           <t>日次バッチ(reading-plans:daily)による自動失効処理</t>
         </is>
       </c>
-      <c r="E240" s="7" t="inlineStr">
+      <c r="E245" s="7" t="inlineStr">
         <is>
           <t>20-1-1</t>
         </is>
       </c>
-      <c r="F240" s="7" t="inlineStr">
+      <c r="F245" s="7" t="inlineStr">
         <is>
           <t>期日を過ぎた「進行中」の計画が「期限切れ」に更新される</t>
         </is>
       </c>
-      <c r="G240" s="7" t="inlineStr">
+      <c r="G245" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが過去・ステータス進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H240" s="7" t="inlineStr">
+      <c r="H245" s="7" t="inlineStr">
         <is>
           <t>対象の計画のstatusが「期限切れ」に更新される</t>
         </is>
       </c>
-      <c r="I240" s="7" t="inlineStr">
+      <c r="I245" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="17" t="n"/>
-      <c r="B241" s="17" t="n"/>
-      <c r="C241" s="17" t="n"/>
-      <c r="D241" s="17" t="n"/>
-      <c r="E241" s="7" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="4" t="n"/>
+      <c r="B246" s="4" t="n"/>
+      <c r="C246" s="4" t="n"/>
+      <c r="D246" s="4" t="n"/>
+      <c r="E246" s="7" t="inlineStr">
         <is>
           <t>20-1-2</t>
         </is>
       </c>
-      <c r="F241" s="7" t="inlineStr">
+      <c r="F246" s="7" t="inlineStr">
         <is>
           <t>期日が今日以降の「進行中」の計画は失効しない</t>
         </is>
       </c>
-      <c r="G241" s="7" t="inlineStr">
+      <c r="G246" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H241" s="7" t="inlineStr">
+      <c r="H246" s="7" t="inlineStr">
         <is>
           <t>その計画のstatusは「進行中」のまま変化しない</t>
         </is>
       </c>
-      <c r="I241" s="17" t="n"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="17" t="n"/>
-      <c r="B242" s="17" t="n"/>
-      <c r="C242" s="17" t="n"/>
-      <c r="D242" s="17" t="n"/>
-      <c r="E242" s="7" t="inlineStr">
+      <c r="I246" s="4" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="n"/>
+      <c r="B247" s="4" t="n"/>
+      <c r="C247" s="4" t="n"/>
+      <c r="D247" s="4" t="n"/>
+      <c r="E247" s="7" t="inlineStr">
         <is>
           <t>20-1-3</t>
         </is>
       </c>
-      <c r="F242" s="7" t="inlineStr">
+      <c r="F247" s="7" t="inlineStr">
         <is>
           <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
         </is>
       </c>
-      <c r="G242" s="7" t="inlineStr">
+      <c r="G247" s="7" t="inlineStr">
         <is>
           <t>1.完了済み・期限切れの計画をそれぞれ用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H242" s="7" t="inlineStr">
+      <c r="H247" s="7" t="inlineStr">
         <is>
           <t>いずれの計画もstatusが変化しない</t>
         </is>
       </c>
-      <c r="I242" s="17" t="n"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="17" t="n"/>
-      <c r="B243" s="17" t="n"/>
-      <c r="C243" s="18" t="n"/>
-      <c r="D243" s="18" t="n"/>
-      <c r="E243" s="7" t="inlineStr">
+      <c r="I247" s="4" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="n"/>
+      <c r="B248" s="4" t="n"/>
+      <c r="C248" s="5" t="n"/>
+      <c r="D248" s="5" t="n"/>
+      <c r="E248" s="7" t="inlineStr">
         <is>
           <t>20-1-4</t>
         </is>
       </c>
-      <c r="F243" s="7" t="inlineStr">
+      <c r="F248" s="7" t="inlineStr">
         <is>
           <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
         </is>
       </c>
-      <c r="G243" s="7" t="inlineStr">
+      <c r="G248" s="7" t="inlineStr">
         <is>
           <t>1.失効対象の計画を用意し reading-plans:daily を実行する
 2.DBを直接確認する</t>
         </is>
       </c>
-      <c r="H243" s="7" t="inlineStr">
+      <c r="H248" s="7" t="inlineStr">
         <is>
           <t>assertDatabaseHasでstatus=expiredが確認できる</t>
         </is>
       </c>
-      <c r="I243" s="18" t="n"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="17" t="n"/>
-      <c r="B244" s="17" t="n"/>
-      <c r="C244" s="7" t="inlineStr">
+      <c r="I248" s="5" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="n"/>
+      <c r="B249" s="4" t="n"/>
+      <c r="C249" s="7" t="inlineStr">
         <is>
           <t>20-2</t>
         </is>
       </c>
-      <c r="D244" s="7" t="inlineStr">
+      <c r="D249" s="7" t="inlineStr">
         <is>
           <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
         </is>
       </c>
-      <c r="E244" s="7" t="inlineStr">
+      <c r="E249" s="7" t="inlineStr">
         <is>
           <t>20-2-1</t>
         </is>
       </c>
-      <c r="F244" s="7" t="inlineStr">
+      <c r="F249" s="7" t="inlineStr">
         <is>
           <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
         </is>
       </c>
-      <c r="G244" s="7" t="inlineStr">
+      <c r="G249" s="7" t="inlineStr">
         <is>
           <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
-      <c r="H244" s="7" t="inlineStr">
+      <c r="H249" s="7" t="inlineStr">
         <is>
           <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
         </is>
       </c>
-      <c r="I244" s="7" t="inlineStr">
+      <c r="I249" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="17" t="n"/>
-      <c r="B245" s="17" t="n"/>
-      <c r="C245" s="17" t="n"/>
-      <c r="D245" s="17" t="n"/>
-      <c r="E245" s="7" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="4" t="n"/>
+      <c r="B250" s="4" t="n"/>
+      <c r="C250" s="4" t="n"/>
+      <c r="D250" s="4" t="n"/>
+      <c r="E250" s="7" t="inlineStr">
         <is>
           <t>20-2-2</t>
         </is>
       </c>
-      <c r="F245" s="7" t="inlineStr">
+      <c r="F250" s="7" t="inlineStr">
         <is>
           <t>期限切れへの更新が、通知対象の抽出より先に行われる</t>
         </is>
       </c>
-      <c r="G245" s="7" t="inlineStr">
+      <c r="G250" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日前で、ステータスが「進行中」のまま(未更新)の計画を用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
-      <c r="H245" s="7" t="inlineStr">
+      <c r="H250" s="7" t="inlineStr">
         <is>
           <t>計画のstatusが「期限切れ」に更新され、そのユーザーに再エンゲージメント(re_engagement)通知が送信される</t>
         </is>
       </c>
-      <c r="I245" s="17" t="n"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="18" t="n"/>
-      <c r="B246" s="18" t="n"/>
-      <c r="C246" s="18" t="n"/>
-      <c r="D246" s="18" t="n"/>
-      <c r="E246" s="7" t="inlineStr">
+      <c r="I250" s="4" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="5" t="n"/>
+      <c r="B251" s="5" t="n"/>
+      <c r="C251" s="5" t="n"/>
+      <c r="D251" s="5" t="n"/>
+      <c r="E251" s="7" t="inlineStr">
         <is>
           <t>20-2-3</t>
         </is>
       </c>
-      <c r="F246" s="7" t="inlineStr">
+      <c r="F251" s="7" t="inlineStr">
         <is>
           <t>reading-plans:dailyが毎日20:00に実行されるようスケジュールされている</t>
         </is>
       </c>
-      <c r="G246" s="7" t="inlineStr">
+      <c r="G251" s="7" t="inlineStr">
         <is>
           <t>1.アプリケーションのスケジュール(Illuminate\Console\Scheduling\Schedule)から、登録済みのイベントを取得する</t>
         </is>
       </c>
-      <c r="H246" s="7" t="inlineStr">
+      <c r="H251" s="7" t="inlineStr">
         <is>
           <t>reading-plans:dailyのイベントが登録されており、cron式が毎日20:00(0 20 * * *)になっている</t>
         </is>
       </c>
-      <c r="I246" s="18" t="n"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="9" t="inlineStr">
+      <c r="I251" s="5" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B247" s="9" t="inlineStr">
+      <c r="B252" s="9" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="C247" s="9" t="inlineStr">
+      <c r="C252" s="9" t="inlineStr">
         <is>
           <t>21-1</t>
         </is>
       </c>
-      <c r="D247" s="9" t="inlineStr">
+      <c r="D252" s="9" t="inlineStr">
         <is>
           <t>通知の既読化</t>
         </is>
       </c>
-      <c r="E247" s="9" t="inlineStr">
+      <c r="E252" s="9" t="inlineStr">
         <is>
           <t>21-1-1</t>
         </is>
       </c>
-      <c r="F247" s="9" t="inlineStr">
+      <c r="F252" s="9" t="inlineStr">
         <is>
           <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
         </is>
       </c>
-      <c r="G247" s="9" t="inlineStr">
+      <c r="G252" s="9" t="inlineStr">
         <is>
           <t>1.未ログイン状態でPOST /notifications/{id}/read に直接リクエストを送信する</t>
         </is>
       </c>
-      <c r="H247" s="9" t="inlineStr">
+      <c r="H252" s="9" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
         </is>
       </c>
-      <c r="I247" s="9" t="inlineStr">
+      <c r="I252" s="9" t="inlineStr">
         <is>
           <t>tests/Feature/Notification/NotificationTest.php</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="A248" s="17" t="n"/>
-      <c r="B248" s="17" t="n"/>
-      <c r="C248" s="17" t="n"/>
-      <c r="D248" s="17" t="n"/>
-      <c r="E248" s="9" t="inlineStr">
+    <row r="253">
+      <c r="A253" s="4" t="n"/>
+      <c r="B253" s="4" t="n"/>
+      <c r="C253" s="4" t="n"/>
+      <c r="D253" s="4" t="n"/>
+      <c r="E253" s="9" t="inlineStr">
         <is>
           <t>21-1-2</t>
         </is>
       </c>
-      <c r="F248" s="9" t="inlineStr">
+      <c r="F253" s="9" t="inlineStr">
         <is>
           <t>自分の通知を既読にできる</t>
         </is>
       </c>
-      <c r="G248" s="9" t="inlineStr">
+      <c r="G253" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知を用意する
 2.その通知に対してPOST /notifications/{id}/read を送信する</t>
         </is>
       </c>
-      <c r="H248" s="9" t="inlineStr">
+      <c r="H253" s="9" t="inlineStr">
         <is>
           <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
         </is>
       </c>
-      <c r="I248" s="17" t="n"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="17" t="n"/>
-      <c r="B249" s="17" t="n"/>
-      <c r="C249" s="18" t="n"/>
-      <c r="D249" s="18" t="n"/>
-      <c r="E249" s="9" t="inlineStr">
+      <c r="I253" s="4" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="n"/>
+      <c r="B254" s="4" t="n"/>
+      <c r="C254" s="5" t="n"/>
+      <c r="D254" s="5" t="n"/>
+      <c r="E254" s="9" t="inlineStr">
         <is>
           <t>21-1-3</t>
         </is>
       </c>
-      <c r="F249" s="9" t="inlineStr">
+      <c r="F254" s="9" t="inlineStr">
         <is>
           <t>他ユーザーの通知は既読にできない</t>
         </is>
       </c>
-      <c r="G249" s="9" t="inlineStr">
+      <c r="G254" s="9" t="inlineStr">
         <is>
           <t>1.他ユーザー宛ての通知を用意する
 2.そのIDに対してPOST /notifications/{id}/read を送信する</t>
         </is>
       </c>
-      <c r="H249" s="9" t="inlineStr">
+      <c r="H254" s="9" t="inlineStr">
         <is>
           <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
         </is>
       </c>
-      <c r="I249" s="18" t="n"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="17" t="n"/>
-      <c r="B250" s="17" t="n"/>
-      <c r="C250" s="9" t="inlineStr">
+      <c r="I254" s="5" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="n"/>
+      <c r="B255" s="4" t="n"/>
+      <c r="C255" s="9" t="inlineStr">
         <is>
           <t>21-2</t>
         </is>
       </c>
-      <c r="D250" s="9" t="inlineStr">
+      <c r="D255" s="9" t="inlineStr">
         <is>
           <t>通知一覧</t>
         </is>
       </c>
-      <c r="E250" s="9" t="inlineStr">
+      <c r="E255" s="9" t="inlineStr">
         <is>
           <t>21-2-1</t>
         </is>
       </c>
-      <c r="F250" s="9" t="inlineStr">
+      <c r="F255" s="9" t="inlineStr">
         <is>
           <t>未ログインの場合、通知一覧にアクセスできない</t>
         </is>
       </c>
-      <c r="G250" s="9" t="inlineStr">
+      <c r="G255" s="9" t="inlineStr">
         <is>
           <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H250" s="9" t="inlineStr">
+      <c r="H255" s="9" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I250" s="9" t="inlineStr">
+      <c r="I255" s="9" t="inlineStr">
         <is>
           <t>tests/Feature/Notification/NotificationIndexTest.php</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="17" t="n"/>
-      <c r="B251" s="17" t="n"/>
-      <c r="C251" s="17" t="n"/>
-      <c r="D251" s="17" t="n"/>
-      <c r="E251" s="9" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="4" t="n"/>
+      <c r="B256" s="4" t="n"/>
+      <c r="C256" s="4" t="n"/>
+      <c r="D256" s="4" t="n"/>
+      <c r="E256" s="9" t="inlineStr">
         <is>
           <t>21-2-2</t>
         </is>
       </c>
-      <c r="F251" s="9" t="inlineStr">
+      <c r="F256" s="9" t="inlineStr">
         <is>
           <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
         </is>
       </c>
-      <c r="G251" s="9" t="inlineStr">
+      <c r="G256" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
 2.通知一覧ページを開く</t>
         </is>
       </c>
-      <c r="H251" s="9" t="inlineStr">
+      <c r="H256" s="9" t="inlineStr">
         <is>
           <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
         </is>
       </c>
-      <c r="I251" s="17" t="n"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="17" t="n"/>
-      <c r="B252" s="17" t="n"/>
-      <c r="C252" s="17" t="n"/>
-      <c r="D252" s="17" t="n"/>
-      <c r="E252" s="9" t="inlineStr">
+      <c r="I256" s="4" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="n"/>
+      <c r="B257" s="4" t="n"/>
+      <c r="C257" s="4" t="n"/>
+      <c r="D257" s="4" t="n"/>
+      <c r="E257" s="9" t="inlineStr">
         <is>
           <t>21-2-3</t>
         </is>
       </c>
-      <c r="F252" s="9" t="inlineStr">
+      <c r="F257" s="9" t="inlineStr">
         <is>
           <t>通知が1件もない場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G252" s="9" t="inlineStr">
+      <c r="G257" s="9" t="inlineStr">
         <is>
           <t>1.通知が1件もないユーザーでログインする
 2.通知一覧ページを開く</t>
         </is>
       </c>
-      <c r="H252" s="9" t="inlineStr">
+      <c r="H257" s="9" t="inlineStr">
         <is>
           <t>「通知はありません。」と表示される</t>
         </is>
       </c>
-      <c r="I252" s="17" t="n"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="17" t="n"/>
-      <c r="B253" s="17" t="n"/>
-      <c r="C253" s="17" t="n"/>
-      <c r="D253" s="17" t="n"/>
-      <c r="E253" s="9" t="inlineStr">
+      <c r="I257" s="4" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="n"/>
+      <c r="B258" s="4" t="n"/>
+      <c r="C258" s="4" t="n"/>
+      <c r="D258" s="4" t="n"/>
+      <c r="E258" s="9" t="inlineStr">
         <is>
           <t>21-2-4</t>
         </is>
       </c>
-      <c r="F253" s="9" t="inlineStr">
+      <c r="F258" s="9" t="inlineStr">
         <is>
           <t>通知のタイトル・本文が表示される</t>
         </is>
       </c>
-      <c r="G253" s="9" t="inlineStr">
+      <c r="G258" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
 2.通知一覧ページを開く</t>
         </is>
       </c>
-      <c r="H253" s="9" t="inlineStr">
+      <c r="H258" s="9" t="inlineStr">
         <is>
           <t>通知のtitleとbodyが一覧に表示される</t>
         </is>
       </c>
-      <c r="I253" s="17" t="n"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="17" t="n"/>
-      <c r="B254" s="17" t="n"/>
-      <c r="C254" s="18" t="n"/>
-      <c r="D254" s="18" t="n"/>
-      <c r="E254" s="9" t="inlineStr">
+      <c r="I258" s="4" t="n"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="n"/>
+      <c r="B259" s="4" t="n"/>
+      <c r="C259" s="4" t="n"/>
+      <c r="D259" s="4" t="n"/>
+      <c r="E259" s="9" t="inlineStr">
         <is>
           <t>21-2-5</t>
         </is>
       </c>
-      <c r="F254" s="9" t="inlineStr">
+      <c r="F259" s="9" t="inlineStr">
         <is>
           <t>未読と既読で表示が異なる</t>
         </is>
       </c>
-      <c r="G254" s="9" t="inlineStr">
+      <c r="G259" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
 2.通知一覧ページを開く</t>
         </is>
       </c>
-      <c r="H254" s="9" t="inlineStr">
+      <c r="H259" s="9" t="inlineStr">
         <is>
           <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
         </is>
       </c>
-      <c r="I254" s="18" t="n"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="17" t="n"/>
-      <c r="B255" s="17" t="n"/>
-      <c r="C255" s="9" t="inlineStr">
+      <c r="I259" s="4" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="n"/>
+      <c r="B260" s="4" t="n"/>
+      <c r="C260" s="5" t="n"/>
+      <c r="D260" s="5" t="n"/>
+      <c r="E260" s="9" t="inlineStr">
+        <is>
+          <t>21-2-6</t>
+        </is>
+      </c>
+      <c r="F260" s="9" t="inlineStr">
+        <is>
+          <t>同じ日時に作成された通知は、期日3日前→期日当日→期日3日後の順に表示される</t>
+        </is>
+      </c>
+      <c r="G260" s="9" t="inlineStr">
+        <is>
+          <t>1.同じ日時に作成された、期日3日前（予告）・期日当日（最終警告）・期日3日後（再エンゲージメント）の通知と、作成日時の異なる通知を用意する
+2.通知一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H260" s="9" t="inlineStr">
+        <is>
+          <t>第1優先で作成日時の新しい順、作成日時が同じ通知同士は第2優先で「期日3日前→期日当日→期日3日後」の順に表示される</t>
+        </is>
+      </c>
+      <c r="I260" s="5" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="n"/>
+      <c r="B261" s="4" t="n"/>
+      <c r="C261" s="9" t="inlineStr">
         <is>
           <t>21-3</t>
         </is>
       </c>
-      <c r="D255" s="9" t="inlineStr">
+      <c r="D261" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数</t>
         </is>
       </c>
-      <c r="E255" s="9" t="inlineStr">
+      <c r="E261" s="9" t="inlineStr">
         <is>
           <t>21-3-1</t>
         </is>
       </c>
-      <c r="F255" s="9" t="inlineStr">
+      <c r="F261" s="9" t="inlineStr">
         <is>
           <t>ヘッダーのベルアイコンに未読件数が表示される</t>
         </is>
       </c>
-      <c r="G255" s="9" t="inlineStr">
+      <c r="G261" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
         </is>
       </c>
-      <c r="H255" s="9" t="inlineStr">
+      <c r="H261" s="9" t="inlineStr">
         <is>
           <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
         </is>
       </c>
-      <c r="I255" s="9" t="inlineStr">
+      <c r="I261" s="9" t="inlineStr">
         <is>
           <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="A256" s="17" t="n"/>
-      <c r="B256" s="17" t="n"/>
-      <c r="C256" s="17" t="n"/>
-      <c r="D256" s="17" t="n"/>
-      <c r="E256" s="9" t="inlineStr">
+    <row r="262">
+      <c r="A262" s="4" t="n"/>
+      <c r="B262" s="4" t="n"/>
+      <c r="C262" s="4" t="n"/>
+      <c r="D262" s="4" t="n"/>
+      <c r="E262" s="9" t="inlineStr">
         <is>
           <t>21-3-2</t>
         </is>
       </c>
-      <c r="F256" s="9" t="inlineStr">
+      <c r="F262" s="9" t="inlineStr">
         <is>
           <t>通知を既読にすると、ヘッダーの未読件数が減る</t>
         </is>
       </c>
-      <c r="G256" s="9" t="inlineStr">
+      <c r="G262" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知を複数件用意する
 2.そのうち1件にPOST /notifications/{id}/read を送信して既読にする
 3.画面を開き直す</t>
         </is>
       </c>
-      <c r="H256" s="9" t="inlineStr">
+      <c r="H262" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数が、既読にした1件分だけ減る</t>
         </is>
       </c>
-      <c r="I256" s="17" t="n"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="18" t="n"/>
-      <c r="B257" s="18" t="n"/>
-      <c r="C257" s="18" t="n"/>
-      <c r="D257" s="18" t="n"/>
-      <c r="E257" s="9" t="inlineStr">
+      <c r="I262" s="4" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="n"/>
+      <c r="B263" s="5" t="n"/>
+      <c r="C263" s="5" t="n"/>
+      <c r="D263" s="5" t="n"/>
+      <c r="E263" s="9" t="inlineStr">
         <is>
           <t>21-3-3</t>
         </is>
       </c>
-      <c r="F257" s="9" t="inlineStr">
+      <c r="F263" s="9" t="inlineStr">
         <is>
           <t>他ユーザーの通知は未読件数に含まれない</t>
         </is>
       </c>
-      <c r="G257" s="9" t="inlineStr">
+      <c r="G263" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知と、他ユーザー宛ての未読通知をそれぞれ用意する
 2.画面を開く</t>
         </is>
       </c>
-      <c r="H257" s="9" t="inlineStr">
+      <c r="H263" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数には、自分宛ての未読通知のみが数えられる</t>
         </is>
       </c>
-      <c r="I257" s="18" t="n"/>
+      <c r="I263" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="177">
     <mergeCell ref="B31:B65"/>
-    <mergeCell ref="B194:B199"/>
     <mergeCell ref="A66:A85"/>
-    <mergeCell ref="D146:D148"/>
     <mergeCell ref="I17:I30"/>
-    <mergeCell ref="I180:I186"/>
     <mergeCell ref="A17:A30"/>
+    <mergeCell ref="C108:C111"/>
+    <mergeCell ref="A192:A198"/>
+    <mergeCell ref="C192:C198"/>
     <mergeCell ref="D12:D16"/>
-    <mergeCell ref="I235:I239"/>
-    <mergeCell ref="A175:A179"/>
-    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="I199:I204"/>
+    <mergeCell ref="D209:D228"/>
+    <mergeCell ref="I173:I179"/>
+    <mergeCell ref="A185:A191"/>
+    <mergeCell ref="C94:C99"/>
     <mergeCell ref="C70:C74"/>
-    <mergeCell ref="B110:B112"/>
-    <mergeCell ref="D110:D112"/>
-    <mergeCell ref="A240:A246"/>
-    <mergeCell ref="D224:D234"/>
+    <mergeCell ref="A86:A107"/>
+    <mergeCell ref="A122:A139"/>
+    <mergeCell ref="D240:D244"/>
     <mergeCell ref="C31:C34"/>
-    <mergeCell ref="C107:C109"/>
-    <mergeCell ref="I168:I174"/>
-    <mergeCell ref="C101:C103"/>
+    <mergeCell ref="B173:B179"/>
+    <mergeCell ref="D173:D179"/>
+    <mergeCell ref="D252:D254"/>
+    <mergeCell ref="I229:I239"/>
     <mergeCell ref="I56:I61"/>
     <mergeCell ref="D35:D41"/>
-    <mergeCell ref="C224:C234"/>
+    <mergeCell ref="I192:I198"/>
+    <mergeCell ref="D100:D104"/>
+    <mergeCell ref="D249:D251"/>
+    <mergeCell ref="A140:A172"/>
     <mergeCell ref="C56:C61"/>
-    <mergeCell ref="A113:A116"/>
     <mergeCell ref="C42:C55"/>
     <mergeCell ref="A2:A16"/>
-    <mergeCell ref="B204:B223"/>
-    <mergeCell ref="B135:B167"/>
+    <mergeCell ref="C161:C167"/>
     <mergeCell ref="C82:C85"/>
     <mergeCell ref="C89:C93"/>
     <mergeCell ref="D2:D4"/>
-    <mergeCell ref="A224:A234"/>
+    <mergeCell ref="C154:C160"/>
     <mergeCell ref="C66:C69"/>
-    <mergeCell ref="B180:B186"/>
     <mergeCell ref="D17:D30"/>
-    <mergeCell ref="D149:D155"/>
-    <mergeCell ref="B235:B239"/>
-    <mergeCell ref="A187:A193"/>
-    <mergeCell ref="C138:C145"/>
-    <mergeCell ref="C187:C193"/>
+    <mergeCell ref="C180:C184"/>
+    <mergeCell ref="D143:D150"/>
     <mergeCell ref="D82:D85"/>
-    <mergeCell ref="C156:C162"/>
+    <mergeCell ref="I115:I117"/>
     <mergeCell ref="I12:I16"/>
-    <mergeCell ref="B104:B109"/>
-    <mergeCell ref="B200:B203"/>
-    <mergeCell ref="D107:D109"/>
+    <mergeCell ref="C115:C117"/>
     <mergeCell ref="D70:D74"/>
+    <mergeCell ref="D185:D191"/>
     <mergeCell ref="C35:C41"/>
-    <mergeCell ref="C180:C186"/>
-    <mergeCell ref="C247:C249"/>
-    <mergeCell ref="C163:C167"/>
-    <mergeCell ref="I156:I162"/>
-    <mergeCell ref="C135:C137"/>
-    <mergeCell ref="A86:A103"/>
-    <mergeCell ref="D117:D128"/>
-    <mergeCell ref="C200:C203"/>
-    <mergeCell ref="B247:B257"/>
-    <mergeCell ref="B168:B174"/>
-    <mergeCell ref="A204:A223"/>
+    <mergeCell ref="I180:I184"/>
+    <mergeCell ref="B86:B107"/>
+    <mergeCell ref="I108:I111"/>
+    <mergeCell ref="B118:B121"/>
+    <mergeCell ref="D134:D138"/>
+    <mergeCell ref="A205:A208"/>
+    <mergeCell ref="C249:C251"/>
+    <mergeCell ref="C205:C208"/>
+    <mergeCell ref="B229:B239"/>
     <mergeCell ref="D42:D55"/>
-    <mergeCell ref="D168:D174"/>
-    <mergeCell ref="I247:I249"/>
-    <mergeCell ref="I224:I234"/>
-    <mergeCell ref="I200:I203"/>
-    <mergeCell ref="I255:I257"/>
+    <mergeCell ref="D229:D239"/>
+    <mergeCell ref="I252:I254"/>
+    <mergeCell ref="B245:B251"/>
+    <mergeCell ref="D161:D167"/>
+    <mergeCell ref="B252:B263"/>
+    <mergeCell ref="I168:I172"/>
     <mergeCell ref="I62:I65"/>
     <mergeCell ref="D6:D8"/>
+    <mergeCell ref="C255:C260"/>
     <mergeCell ref="I2:I4"/>
-    <mergeCell ref="D250:D254"/>
-    <mergeCell ref="C96:C100"/>
     <mergeCell ref="D9:D10"/>
-    <mergeCell ref="C235:C239"/>
-    <mergeCell ref="D187:D193"/>
-    <mergeCell ref="C250:C254"/>
-    <mergeCell ref="C104:C106"/>
+    <mergeCell ref="D140:D142"/>
+    <mergeCell ref="I105:I107"/>
+    <mergeCell ref="B205:B208"/>
+    <mergeCell ref="I143:I150"/>
+    <mergeCell ref="D205:D208"/>
     <mergeCell ref="I89:I93"/>
     <mergeCell ref="I82:I85"/>
-    <mergeCell ref="I129:I133"/>
     <mergeCell ref="D62:D65"/>
-    <mergeCell ref="A194:A199"/>
-    <mergeCell ref="C194:C199"/>
-    <mergeCell ref="C146:C148"/>
+    <mergeCell ref="D118:D121"/>
+    <mergeCell ref="B180:B184"/>
     <mergeCell ref="B66:B85"/>
-    <mergeCell ref="A31:A65"/>
+    <mergeCell ref="I185:I191"/>
     <mergeCell ref="D86:D88"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="D135:D137"/>
-    <mergeCell ref="B86:B103"/>
-    <mergeCell ref="D94:D95"/>
-    <mergeCell ref="I117:I128"/>
-    <mergeCell ref="I146:I148"/>
-    <mergeCell ref="C110:C112"/>
-    <mergeCell ref="B175:B179"/>
-    <mergeCell ref="D175:D179"/>
-    <mergeCell ref="B240:B246"/>
+    <mergeCell ref="A31:A65"/>
+    <mergeCell ref="C261:C263"/>
+    <mergeCell ref="I134:I138"/>
+    <mergeCell ref="B240:B244"/>
+    <mergeCell ref="C134:C138"/>
+    <mergeCell ref="D94:D99"/>
+    <mergeCell ref="D112:D114"/>
+    <mergeCell ref="C245:C248"/>
+    <mergeCell ref="I209:I228"/>
+    <mergeCell ref="C122:C133"/>
     <mergeCell ref="C2:C4"/>
-    <mergeCell ref="I113:I116"/>
-    <mergeCell ref="D255:D257"/>
-    <mergeCell ref="D235:D239"/>
-    <mergeCell ref="I110:I112"/>
-    <mergeCell ref="I194:I199"/>
+    <mergeCell ref="I161:I167"/>
+    <mergeCell ref="C173:C179"/>
+    <mergeCell ref="D168:D172"/>
+    <mergeCell ref="B199:B204"/>
+    <mergeCell ref="I249:I251"/>
+    <mergeCell ref="D199:D204"/>
     <mergeCell ref="I6:I8"/>
-    <mergeCell ref="I250:I254"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="I240:I244"/>
+    <mergeCell ref="C118:C121"/>
+    <mergeCell ref="A180:A184"/>
     <mergeCell ref="B2:B16"/>
+    <mergeCell ref="A240:A244"/>
+    <mergeCell ref="C240:C244"/>
     <mergeCell ref="C86:C88"/>
-    <mergeCell ref="A135:A167"/>
-    <mergeCell ref="I187:I193"/>
+    <mergeCell ref="B192:B198"/>
+    <mergeCell ref="D192:D198"/>
     <mergeCell ref="D89:D93"/>
-    <mergeCell ref="D129:D133"/>
+    <mergeCell ref="I205:I208"/>
     <mergeCell ref="I35:I41"/>
-    <mergeCell ref="D194:D199"/>
     <mergeCell ref="D66:D69"/>
-    <mergeCell ref="A180:A186"/>
-    <mergeCell ref="C149:C155"/>
+    <mergeCell ref="B115:B117"/>
+    <mergeCell ref="B185:B191"/>
+    <mergeCell ref="I118:I121"/>
+    <mergeCell ref="D115:D117"/>
+    <mergeCell ref="D105:D107"/>
+    <mergeCell ref="D56:D61"/>
     <mergeCell ref="I86:I88"/>
-    <mergeCell ref="D56:D61"/>
+    <mergeCell ref="C143:C150"/>
     <mergeCell ref="I70:I74"/>
-    <mergeCell ref="C175:C179"/>
-    <mergeCell ref="I104:I106"/>
-    <mergeCell ref="A104:A109"/>
-    <mergeCell ref="A200:A203"/>
-    <mergeCell ref="I94:I95"/>
-    <mergeCell ref="I149:I155"/>
-    <mergeCell ref="D101:D103"/>
-    <mergeCell ref="C255:C257"/>
+    <mergeCell ref="C112:C114"/>
+    <mergeCell ref="C185:C191"/>
+    <mergeCell ref="C252:C254"/>
+    <mergeCell ref="I94:I99"/>
+    <mergeCell ref="C100:C104"/>
     <mergeCell ref="C75:C81"/>
-    <mergeCell ref="I175:I179"/>
-    <mergeCell ref="B113:B116"/>
-    <mergeCell ref="C117:C128"/>
-    <mergeCell ref="D113:D116"/>
-    <mergeCell ref="B117:B134"/>
-    <mergeCell ref="A168:A174"/>
-    <mergeCell ref="I244:I246"/>
-    <mergeCell ref="C168:C174"/>
-    <mergeCell ref="C244:C246"/>
-    <mergeCell ref="C129:C133"/>
-    <mergeCell ref="B224:B234"/>
-    <mergeCell ref="D240:D243"/>
+    <mergeCell ref="D122:D133"/>
+    <mergeCell ref="B140:B172"/>
+    <mergeCell ref="D151:D153"/>
+    <mergeCell ref="A229:A239"/>
+    <mergeCell ref="C229:C239"/>
+    <mergeCell ref="D154:D160"/>
+    <mergeCell ref="I255:I260"/>
     <mergeCell ref="D75:D81"/>
+    <mergeCell ref="I245:I248"/>
+    <mergeCell ref="C105:C107"/>
     <mergeCell ref="C17:C30"/>
     <mergeCell ref="D31:D34"/>
-    <mergeCell ref="I96:I100"/>
-    <mergeCell ref="A235:A239"/>
-    <mergeCell ref="D204:D223"/>
-    <mergeCell ref="B187:B193"/>
+    <mergeCell ref="A115:A117"/>
+    <mergeCell ref="D180:D184"/>
     <mergeCell ref="I42:I55"/>
-    <mergeCell ref="I107:I109"/>
-    <mergeCell ref="D156:D162"/>
-    <mergeCell ref="D138:D145"/>
+    <mergeCell ref="D108:D111"/>
     <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D180:D186"/>
-    <mergeCell ref="D247:D249"/>
+    <mergeCell ref="C140:C142"/>
     <mergeCell ref="I66:I69"/>
-    <mergeCell ref="C113:C116"/>
-    <mergeCell ref="A247:A257"/>
-    <mergeCell ref="D200:D203"/>
+    <mergeCell ref="I261:I263"/>
+    <mergeCell ref="B108:B114"/>
+    <mergeCell ref="A209:A228"/>
+    <mergeCell ref="C209:C228"/>
     <mergeCell ref="C6:C8"/>
-    <mergeCell ref="A117:A134"/>
-    <mergeCell ref="A110:A112"/>
-    <mergeCell ref="I101:I103"/>
+    <mergeCell ref="C151:C153"/>
+    <mergeCell ref="I140:I142"/>
+    <mergeCell ref="A245:A251"/>
+    <mergeCell ref="I122:I133"/>
+    <mergeCell ref="D261:D263"/>
     <mergeCell ref="B17:B30"/>
-    <mergeCell ref="D104:D106"/>
-    <mergeCell ref="C204:C223"/>
-    <mergeCell ref="I163:I167"/>
-    <mergeCell ref="I135:I137"/>
-    <mergeCell ref="D96:D100"/>
-    <mergeCell ref="I240:I243"/>
+    <mergeCell ref="A252:A263"/>
+    <mergeCell ref="I151:I153"/>
+    <mergeCell ref="A173:A179"/>
+    <mergeCell ref="C199:C204"/>
+    <mergeCell ref="D255:D260"/>
+    <mergeCell ref="B122:B139"/>
+    <mergeCell ref="I154:I160"/>
+    <mergeCell ref="D245:D248"/>
     <mergeCell ref="I75:I81"/>
-    <mergeCell ref="C240:C243"/>
+    <mergeCell ref="I100:I104"/>
+    <mergeCell ref="B209:B228"/>
     <mergeCell ref="I31:I34"/>
-    <mergeCell ref="I204:I223"/>
     <mergeCell ref="C12:C16"/>
-    <mergeCell ref="I138:I145"/>
+    <mergeCell ref="C168:C172"/>
+    <mergeCell ref="I112:I114"/>
+    <mergeCell ref="A199:A204"/>
+    <mergeCell ref="A108:A114"/>
     <mergeCell ref="C62:C65"/>
-    <mergeCell ref="D163:D167"/>
-    <mergeCell ref="D244:D246"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -5166,18 +5166,18 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>per_page・pageでページネーションできる(指定なしの場合は1ページ10件)</t>
+          <t>pageでページを移動できる(1ページ10件固定)</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>1.11件以上の書籍を用意する
-2.パラメータなし、およびper_page・pageを指定してGET /api/v1/booksにアクセスする</t>
+          <t>1.11件の書籍を用意する
+2.pageを指定せずに、およびpage=2を指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>パラメータなしでは10件、指定した場合は指定件数・指定ページの書籍が返り、meta・linksにページ情報が反映される</t>
+          <t>pageなしでは1ページ目の10件、page=2では残りの1件が返り、meta・linksにページ情報が反映される</t>
         </is>
       </c>
       <c r="I149" s="4" t="n"/>
@@ -5199,12 +5199,12 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>1.per_pageに101、genreに存在しないID、pageに0をそれぞれ指定してGET /api/v1/booksにアクセスする(Accept: application/json)</t>
+          <t>1.genreに存在しないID、pageに0をそれぞれ指定してGET /api/v1/booksにアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「取得件数は100以下の値で指定してください」「指定されたジャンルは存在しません」「ページ番号は1以上の値で指定してください」が返る</t>
+          <t>422が返り、「指定されたジャンルは存在しません」「ページ番号は1以上の値で指定してください」が返る</t>
         </is>
       </c>
       <c r="I150" s="5" t="n"/>
@@ -8633,8 +8633,8 @@
     <mergeCell ref="B31:B65"/>
     <mergeCell ref="A66:A85"/>
     <mergeCell ref="I17:I30"/>
+    <mergeCell ref="C108:C111"/>
     <mergeCell ref="A17:A30"/>
-    <mergeCell ref="C108:C111"/>
     <mergeCell ref="A192:A198"/>
     <mergeCell ref="C192:C198"/>
     <mergeCell ref="D12:D16"/>
@@ -8647,21 +8647,22 @@
     <mergeCell ref="A86:A107"/>
     <mergeCell ref="A122:A139"/>
     <mergeCell ref="D240:D244"/>
+    <mergeCell ref="B173:B179"/>
     <mergeCell ref="C31:C34"/>
-    <mergeCell ref="B173:B179"/>
     <mergeCell ref="D173:D179"/>
     <mergeCell ref="D252:D254"/>
     <mergeCell ref="I229:I239"/>
     <mergeCell ref="I56:I61"/>
     <mergeCell ref="D35:D41"/>
-    <mergeCell ref="I192:I198"/>
+    <mergeCell ref="C56:C61"/>
+    <mergeCell ref="A140:A172"/>
     <mergeCell ref="D100:D104"/>
     <mergeCell ref="D249:D251"/>
-    <mergeCell ref="A140:A172"/>
-    <mergeCell ref="C56:C61"/>
+    <mergeCell ref="I192:I198"/>
     <mergeCell ref="C42:C55"/>
     <mergeCell ref="A2:A16"/>
     <mergeCell ref="C161:C167"/>
+    <mergeCell ref="B118:B121"/>
     <mergeCell ref="C82:C85"/>
     <mergeCell ref="C89:C93"/>
     <mergeCell ref="D2:D4"/>
@@ -8680,7 +8681,6 @@
     <mergeCell ref="I180:I184"/>
     <mergeCell ref="B86:B107"/>
     <mergeCell ref="I108:I111"/>
-    <mergeCell ref="B118:B121"/>
     <mergeCell ref="D134:D138"/>
     <mergeCell ref="A205:A208"/>
     <mergeCell ref="C249:C251"/>
@@ -8721,18 +8721,18 @@
     <mergeCell ref="D112:D114"/>
     <mergeCell ref="C245:C248"/>
     <mergeCell ref="I209:I228"/>
+    <mergeCell ref="C2:C4"/>
     <mergeCell ref="C122:C133"/>
-    <mergeCell ref="C2:C4"/>
     <mergeCell ref="I161:I167"/>
+    <mergeCell ref="D168:D172"/>
     <mergeCell ref="C173:C179"/>
-    <mergeCell ref="D168:D172"/>
     <mergeCell ref="B199:B204"/>
     <mergeCell ref="I249:I251"/>
     <mergeCell ref="D199:D204"/>
     <mergeCell ref="I6:I8"/>
     <mergeCell ref="A118:A121"/>
+    <mergeCell ref="C118:C121"/>
     <mergeCell ref="I240:I244"/>
-    <mergeCell ref="C118:C121"/>
     <mergeCell ref="A180:A184"/>
     <mergeCell ref="B2:B16"/>
     <mergeCell ref="A240:A244"/>
@@ -8743,14 +8743,14 @@
     <mergeCell ref="D89:D93"/>
     <mergeCell ref="I205:I208"/>
     <mergeCell ref="I35:I41"/>
-    <mergeCell ref="D66:D69"/>
     <mergeCell ref="B115:B117"/>
     <mergeCell ref="B185:B191"/>
+    <mergeCell ref="D66:D69"/>
     <mergeCell ref="I118:I121"/>
     <mergeCell ref="D115:D117"/>
+    <mergeCell ref="I86:I88"/>
     <mergeCell ref="D105:D107"/>
     <mergeCell ref="D56:D61"/>
-    <mergeCell ref="I86:I88"/>
     <mergeCell ref="C143:C150"/>
     <mergeCell ref="I70:I74"/>
     <mergeCell ref="C112:C114"/>
@@ -8766,9 +8766,9 @@
     <mergeCell ref="C229:C239"/>
     <mergeCell ref="D154:D160"/>
     <mergeCell ref="I255:I260"/>
+    <mergeCell ref="C105:C107"/>
+    <mergeCell ref="I245:I248"/>
     <mergeCell ref="D75:D81"/>
-    <mergeCell ref="I245:I248"/>
-    <mergeCell ref="C105:C107"/>
     <mergeCell ref="C17:C30"/>
     <mergeCell ref="D31:D34"/>
     <mergeCell ref="A115:A117"/>
@@ -8792,7 +8792,6 @@
     <mergeCell ref="A252:A263"/>
     <mergeCell ref="I151:I153"/>
     <mergeCell ref="A173:A179"/>
-    <mergeCell ref="C199:C204"/>
     <mergeCell ref="D255:D260"/>
     <mergeCell ref="B122:B139"/>
     <mergeCell ref="I154:I160"/>
@@ -8801,10 +8800,11 @@
     <mergeCell ref="I100:I104"/>
     <mergeCell ref="B209:B228"/>
     <mergeCell ref="I31:I34"/>
+    <mergeCell ref="C168:C172"/>
     <mergeCell ref="C12:C16"/>
-    <mergeCell ref="C168:C172"/>
     <mergeCell ref="I112:I114"/>
     <mergeCell ref="A199:A204"/>
+    <mergeCell ref="C199:C204"/>
     <mergeCell ref="A108:A114"/>
     <mergeCell ref="C62:C65"/>
   </mergeCells>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I263"/>
+  <dimension ref="A1:I267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2829,8 +2829,8 @@
     <row r="74">
       <c r="A74" s="4" t="n"/>
       <c r="B74" s="4" t="n"/>
-      <c r="C74" s="5" t="n"/>
-      <c r="D74" s="5" t="n"/>
+      <c r="C74" s="4" t="n"/>
+      <c r="D74" s="4" t="n"/>
       <c r="E74" s="3" t="inlineStr">
         <is>
           <t>4-2-5</t>
@@ -2851,73 +2851,73 @@
           <t>投稿できず、エラーになる（403Forbidden）。レビューは1書籍につき1人1件までしか投稿できない</t>
         </is>
       </c>
-      <c r="I74" s="5" t="n"/>
+      <c r="I74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="n"/>
       <c r="B75" s="4" t="n"/>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>4-3</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>レビュー編集</t>
-        </is>
-      </c>
+      <c r="C75" s="5" t="n"/>
+      <c r="D75" s="5" t="n"/>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>4-3-1</t>
+          <t>4-2-6</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>自分が投稿したレビューにのみ「編集」リンクが表示される</t>
+          <t>既にレビューを投稿済みの書籍に不正な入力で投稿しても、入力エラーではなく403になる</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>1.自分がレビューを投稿した書籍の詳細ページを開く</t>
+          <t>1.既にレビューを投稿済みの書籍に対して、評価・コメントを空にして直接レビュー投稿のリクエストを送信する</t>
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr">
         <is>
-          <t>自分のレビューには「編集」リンクが表示され、他人のレビューには表示されない</t>
-        </is>
-      </c>
-      <c r="I75" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/Review/ReviewUpdateTest.php</t>
-        </is>
-      </c>
+          <t>バリデーションエラーではなく403Forbiddenになり、レビューは投稿されない（認可チェックが入力チェックより先に行われる）</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="n"/>
       <c r="B76" s="4" t="n"/>
-      <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="n"/>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>レビュー編集</t>
+        </is>
+      </c>
       <c r="E76" s="3" t="inlineStr">
         <is>
-          <t>4-3-2</t>
+          <t>4-3-1</t>
         </is>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>編集画面を開くと現在の評価・コメントが初期表示される</t>
+          <t>自分が投稿したレビューにのみ「編集」リンクが表示される</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>1.自分が投稿したレビューの「編集」リンクを押す</t>
+          <t>1.自分がレビューを投稿した書籍の詳細ページを開く</t>
         </is>
       </c>
       <c r="H76" s="3" t="inlineStr">
         <is>
-          <t>レビュー編集ページに現在の評価（星）とコメントが表示される</t>
-        </is>
-      </c>
-      <c r="I76" s="4" t="n"/>
+          <t>自分のレビューには「編集」リンクが表示され、他人のレビューには表示されない</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/Review/ReviewUpdateTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="n"/>
@@ -2926,23 +2926,22 @@
       <c r="D77" s="4" t="n"/>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>4-3-3</t>
+          <t>4-3-2</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>評価が選択されていない場合、バリデーションメッセージが表示される</t>
+          <t>編集画面を開くと現在の評価・コメントが初期表示される</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>1.レビュー編集ページを開く
-2.評価の選択を外し、更新ボタンを押す</t>
+          <t>1.自分が投稿したレビューの「編集」リンクを押す</t>
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr">
         <is>
-          <t>「評価を入力してください」というバリデーションメッセージが表示される</t>
+          <t>レビュー編集ページに現在の評価（星）とコメントが表示される</t>
         </is>
       </c>
       <c r="I77" s="4" t="n"/>
@@ -2954,23 +2953,23 @@
       <c r="D78" s="4" t="n"/>
       <c r="E78" s="3" t="inlineStr">
         <is>
-          <t>4-3-4</t>
+          <t>4-3-3</t>
         </is>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>コメントが256文字以上の場合、バリデーションメッセージが表示される</t>
+          <t>評価が選択されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
           <t>1.レビュー編集ページを開く
-2.256文字以上のコメントを入力し、更新ボタンを押す</t>
+2.評価の選択を外し、更新ボタンを押す</t>
         </is>
       </c>
       <c r="H78" s="3" t="inlineStr">
         <is>
-          <t>「コメントは255文字以内で入力してください」というバリデーションメッセージが表示される</t>
+          <t>「評価を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I78" s="4" t="n"/>
@@ -2982,22 +2981,23 @@
       <c r="D79" s="4" t="n"/>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>4-3-5</t>
+          <t>4-3-4</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>他人が投稿したレビューは更新できない</t>
+          <t>コメントが256文字以上の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>1.他人が投稿したレビューに対して、直接レビュー更新のリクエストを送信する</t>
+          <t>1.レビュー編集ページを開く
+2.256文字以上のコメントを入力し、更新ボタンを押す</t>
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr">
         <is>
-          <t>更新できず、エラーになる（403Forbidden）</t>
+          <t>「コメントは255文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I79" s="4" t="n"/>
@@ -3009,23 +3009,22 @@
       <c r="D80" s="4" t="n"/>
       <c r="E80" s="3" t="inlineStr">
         <is>
-          <t>4-3-6</t>
+          <t>4-3-5</t>
         </is>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>全ての項目が正しく入力されている場合、レビューが更新される</t>
+          <t>他人が投稿したレビューは更新できない</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>1.レビュー編集ページを開く
-2.評価・コメントを変更し、更新ボタンを押す</t>
+          <t>1.他人が投稿したレビューに対して、直接レビュー更新のリクエストを送信する</t>
         </is>
       </c>
       <c r="H80" s="3" t="inlineStr">
         <is>
-          <t>レビューが更新され、書籍詳細画面に遷移し「レビューを更新しました。」と表示される</t>
+          <t>更新できず、エラーになる（403Forbidden）</t>
         </is>
       </c>
       <c r="I80" s="4" t="n"/>
@@ -3033,346 +3032,345 @@
     <row r="81">
       <c r="A81" s="4" t="n"/>
       <c r="B81" s="4" t="n"/>
-      <c r="C81" s="5" t="n"/>
-      <c r="D81" s="5" t="n"/>
+      <c r="C81" s="4" t="n"/>
+      <c r="D81" s="4" t="n"/>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>4-3-7</t>
+          <t>4-3-6</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>コメントが入力されていない場合、バリデーションメッセージが表示される</t>
+          <t>全ての項目が正しく入力されている場合、レビューが更新される</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
           <t>1.レビュー編集ページを開く
-2.コメントを空にし、更新ボタンを押す</t>
+2.評価・コメントを変更し、更新ボタンを押す</t>
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr">
         <is>
-          <t>「コメントを入力してください」というバリデーションメッセージが表示され、レビューは更新されない（コメントは必須項目）</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="n"/>
+          <t>レビューが更新され、書籍詳細画面に遷移し「レビューを更新しました。」と表示される</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="n"/>
       <c r="B82" s="4" t="n"/>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>4-4</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>レビュー削除</t>
-        </is>
-      </c>
+      <c r="C82" s="4" t="n"/>
+      <c r="D82" s="4" t="n"/>
       <c r="E82" s="3" t="inlineStr">
         <is>
-          <t>4-4-1</t>
+          <t>4-3-7</t>
         </is>
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>自分が投稿したレビューにのみ「削除」ボタンが表示される</t>
+          <t>コメントが入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>1.自分がレビューを投稿した書籍の詳細ページを開く</t>
+          <t>1.レビュー編集ページを開く
+2.コメントを空にし、更新ボタンを押す</t>
         </is>
       </c>
       <c r="H82" s="3" t="inlineStr">
         <is>
-          <t>自分のレビューには「削除」ボタンが表示され、他人のレビューには表示されない</t>
-        </is>
-      </c>
-      <c r="I82" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/Review/ReviewDestroyTest.php</t>
-        </is>
-      </c>
+          <t>「コメントを入力してください」というバリデーションメッセージが表示され、レビューは更新されない（コメントは必須項目）</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="n"/>
       <c r="B83" s="4" t="n"/>
-      <c r="C83" s="4" t="n"/>
-      <c r="D83" s="4" t="n"/>
+      <c r="C83" s="5" t="n"/>
+      <c r="D83" s="5" t="n"/>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>4-4-2</t>
+          <t>4-3-8</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>他人が投稿したレビューは削除できない</t>
+          <t>他人が投稿したレビューに不正な入力で更新しようとしても、入力エラーではなく403になる</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>1.他人が投稿したレビューに対して、直接レビュー削除のリクエストを送信する</t>
+          <t>1.他人が投稿したレビューに対して、評価・コメントを空にして直接レビュー更新のリクエストを送信する</t>
         </is>
       </c>
       <c r="H83" s="3" t="inlineStr">
         <is>
-          <t>削除できず、エラーになる（403Forbidden）</t>
-        </is>
-      </c>
-      <c r="I83" s="4" t="n"/>
+          <t>バリデーションエラーではなく403Forbiddenになり、レビューは更新されない（認可チェックが入力チェックより先に行われる）</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n"/>
       <c r="B84" s="4" t="n"/>
-      <c r="C84" s="4" t="n"/>
-      <c r="D84" s="4" t="n"/>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>4-4</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>レビュー削除</t>
+        </is>
+      </c>
       <c r="E84" s="3" t="inlineStr">
         <is>
+          <t>4-4-1</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>自分が投稿したレビューにのみ「削除」ボタンが表示される</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>1.自分がレビューを投稿した書籍の詳細ページを開く</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t>自分のレビューには「削除」ボタンが表示され、他人のレビューには表示されない</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/Review/ReviewDestroyTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n"/>
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="inlineStr">
+        <is>
+          <t>他人が投稿したレビューは削除できない</t>
+        </is>
+      </c>
+      <c r="G85" s="3" t="inlineStr">
+        <is>
+          <t>1.他人が投稿したレビューに対して、直接レビュー削除のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H85" s="3" t="inlineStr">
+        <is>
+          <t>削除できず、エラーになる（403Forbidden）</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n"/>
+      <c r="B86" s="4" t="n"/>
+      <c r="C86" s="4" t="n"/>
+      <c r="D86" s="4" t="n"/>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
           <t>4-4-3</t>
         </is>
       </c>
-      <c r="F84" s="3" t="inlineStr">
+      <c r="F86" s="3" t="inlineStr">
         <is>
           <t>削除ボタンを押すと確認ダイアログが表示される</t>
         </is>
       </c>
-      <c r="G84" s="3" t="inlineStr">
+      <c r="G86" s="3" t="inlineStr">
         <is>
           <t>1.自分が投稿したレビューの「削除」ボタンを押す</t>
         </is>
       </c>
-      <c r="H84" s="3" t="inlineStr">
+      <c r="H86" s="3" t="inlineStr">
         <is>
           <t>「本当に削除しますか？」という確認ダイアログが表示される</t>
         </is>
       </c>
-      <c r="I84" s="4" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="5" t="n"/>
-      <c r="B85" s="5" t="n"/>
-      <c r="C85" s="5" t="n"/>
-      <c r="D85" s="5" t="n"/>
-      <c r="E85" s="3" t="inlineStr">
+      <c r="I86" s="4" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n"/>
+      <c r="B87" s="5" t="n"/>
+      <c r="C87" s="5" t="n"/>
+      <c r="D87" s="5" t="n"/>
+      <c r="E87" s="3" t="inlineStr">
         <is>
           <t>4-4-4</t>
         </is>
       </c>
-      <c r="F85" s="3" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>確認ダイアログでOKを押すとレビューが削除される</t>
         </is>
       </c>
-      <c r="G85" s="3" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t>1.自分が投稿したレビューの「削除」ボタンを押し、確認ダイアログでOKを押す</t>
         </is>
       </c>
-      <c r="H85" s="3" t="inlineStr">
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>レビューが削除され、「レビューを削除しました。」と表示されるとともに一覧から消える</t>
         </is>
       </c>
-      <c r="I85" s="5" t="n"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="I87" s="5" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>ジャンル</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>5-1</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
         <is>
           <t>ジャンル一覧</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>5-1-1</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>ジャンル一覧ページを表示する</t>
         </is>
       </c>
-      <c r="G86" s="3" t="inlineStr">
+      <c r="G88" s="3" t="inlineStr">
         <is>
           <t>1.ジャンル一覧ページを開く</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
+      <c r="H88" s="3" t="inlineStr">
         <is>
           <t>登録されているジャンル名と、そのジャンルに紐づく書籍数が一覧表示される</t>
         </is>
       </c>
-      <c r="I86" s="3" t="inlineStr">
+      <c r="I88" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Genre/GenreIndexTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="4" t="n"/>
-      <c r="B87" s="4" t="n"/>
-      <c r="C87" s="4" t="n"/>
-      <c r="D87" s="4" t="n"/>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>5-1-2</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="inlineStr">
-        <is>
-          <t>ジャンルが1件も登録されていない場合の表示を確認する</t>
-        </is>
-      </c>
-      <c r="G87" s="3" t="inlineStr">
-        <is>
-          <t>1.ジャンルが1件も登録されていない状態でジャンル一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H87" s="3" t="inlineStr">
-        <is>
-          <t>「ジャンルが登録されていません。」と表示される</t>
-        </is>
-      </c>
-      <c r="I87" s="4" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="4" t="n"/>
-      <c r="B88" s="4" t="n"/>
-      <c r="C88" s="5" t="n"/>
-      <c r="D88" s="5" t="n"/>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>5-1-3</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="inlineStr">
-        <is>
-          <t>未ログインの場合、ジャンル一覧ページにアクセスできない</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態でジャンル一覧ページのURLに直接アクセスする</t>
-        </is>
-      </c>
-      <c r="H88" s="3" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="n"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n"/>
       <c r="B89" s="4" t="n"/>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>5-2</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>ジャンル登録</t>
-        </is>
-      </c>
+      <c r="C89" s="4" t="n"/>
+      <c r="D89" s="4" t="n"/>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>5-2-1</t>
+          <t>5-1-2</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>未ログインの場合、ジャンル登録ページにアクセスできない</t>
+          <t>ジャンルが1件も登録されていない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>1.未ログイン状態でジャンル登録ページのURLに直接アクセスする</t>
+          <t>1.ジャンルが1件も登録されていない状態でジャンル一覧ページを開く</t>
         </is>
       </c>
       <c r="H89" s="3" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I89" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/Genre/GenreStoreTest.php</t>
-        </is>
-      </c>
+          <t>「ジャンルが登録されていません。」と表示される</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n"/>
       <c r="B90" s="4" t="n"/>
-      <c r="C90" s="4" t="n"/>
-      <c r="D90" s="4" t="n"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="n"/>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>5-2-2</t>
+          <t>5-1-3</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>ジャンル名が入力されていない場合、バリデーションメッセージが表示される</t>
+          <t>未ログインの場合、ジャンル一覧ページにアクセスできない</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンル登録ページを開く
-2.ジャンル名を入力せずに登録ボタンを押す</t>
+          <t>1.未ログイン状態でジャンル一覧ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>「ジャンル名を入力してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I90" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n"/>
       <c r="B91" s="4" t="n"/>
-      <c r="C91" s="4" t="n"/>
-      <c r="D91" s="4" t="n"/>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>ジャンル登録</t>
+        </is>
+      </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>5-2-3</t>
+          <t>5-2-1</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>ジャンル名が21文字以上の場合、バリデーションメッセージが表示される</t>
+          <t>未ログインの場合、ジャンル登録ページにアクセスできない</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンル登録ページを開く
-2.21文字以上のジャンル名を入力し、登録ボタンを押す</t>
+          <t>1.未ログイン状態でジャンル登録ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
         <is>
-          <t>「ジャンル名は20文字以内で入力してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I91" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/Genre/GenreStoreTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n"/>
@@ -3381,23 +3379,23 @@
       <c r="D92" s="4" t="n"/>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>5-2-4</t>
+          <t>5-2-2</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>既に登録されているジャンル名の場合、バリデーションメッセージが表示される</t>
+          <t>ジャンル名が入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
           <t>1.ジャンル登録ページを開く
-2.既に登録済みのジャンル名を入力し、登録ボタンを押す</t>
+2.ジャンル名を入力せずに登録ボタンを押す</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>「このジャンル名はすでに登録されています」というバリデーションメッセージが表示される</t>
+          <t>「ジャンル名を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I92" s="4" t="n"/>
@@ -3405,124 +3403,125 @@
     <row r="93">
       <c r="A93" s="4" t="n"/>
       <c r="B93" s="4" t="n"/>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="n"/>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>5-2-5</t>
+          <t>5-2-3</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>正しくジャンル名が入力されている場合、ジャンルが登録される</t>
+          <t>ジャンル名が21文字以上の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
           <t>1.ジャンル登録ページを開く
-2.未登録のジャンル名を入力し、登録ボタンを押す</t>
+2.21文字以上のジャンル名を入力し、登録ボタンを押す</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>ジャンルが登録され、ジャンル一覧画面に遷移し「ジャンルを登録しました。」と表示される</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="n"/>
+          <t>「ジャンル名は20文字以内で入力してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="n"/>
       <c r="B94" s="4" t="n"/>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>5-3</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>ジャンル詳細</t>
-        </is>
-      </c>
+      <c r="C94" s="4" t="n"/>
+      <c r="D94" s="4" t="n"/>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>5-3-1</t>
+          <t>5-2-4</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>ジャンルに紐づく書籍が一覧表示される</t>
+          <t>既に登録されているジャンル名の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>1.書籍が紐づいているジャンルの詳細ページを開く</t>
+          <t>1.ジャンル登録ページを開く
+2.既に登録済みのジャンル名を入力し、登録ボタンを押す</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>そのジャンルに紐づく書籍が一覧表示される</t>
-        </is>
-      </c>
-      <c r="I94" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/Genre/GenreShowTest.php</t>
-        </is>
-      </c>
+          <t>「このジャンル名はすでに登録されています」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="n"/>
       <c r="B95" s="4" t="n"/>
-      <c r="C95" s="4" t="n"/>
-      <c r="D95" s="4" t="n"/>
+      <c r="C95" s="5" t="n"/>
+      <c r="D95" s="5" t="n"/>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>5-3-2</t>
+          <t>5-2-5</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>ジャンルに紐づく書籍が1件もない場合の表示を確認する</t>
+          <t>正しくジャンル名が入力されている場合、ジャンルが登録される</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>1.書籍が1件も紐づいていないジャンルの詳細ページを開く</t>
+          <t>1.ジャンル登録ページを開く
+2.未登録のジャンル名を入力し、登録ボタンを押す</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>「このジャンルの書籍はまだ登録されていません。」と表示される</t>
-        </is>
-      </c>
-      <c r="I95" s="4" t="n"/>
+          <t>ジャンルが登録され、ジャンル一覧画面に遷移し「ジャンルを登録しました。」と表示される</t>
+        </is>
+      </c>
+      <c r="I95" s="5" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n"/>
       <c r="B96" s="4" t="n"/>
-      <c r="C96" s="4" t="n"/>
-      <c r="D96" s="4" t="n"/>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>5-3</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>ジャンル詳細</t>
+        </is>
+      </c>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>5-3-3</t>
+          <t>5-3-1</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>ジャンル一覧から遷移した場合、「ジャンル一覧に戻る」リンクが表示される</t>
+          <t>ジャンルに紐づく書籍が一覧表示される</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンル一覧ページでジャンル名のリンクを押し、ジャンル詳細ページを開く
-2.画面左上の戻るリンクを確認する</t>
+          <t>1.書籍が紐づいているジャンルの詳細ページを開く</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>「← ジャンル一覧に戻る」と表示され、押すとジャンル一覧ページへ遷移する（遷移元の指定がない場合も同様）</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="n"/>
+          <t>そのジャンルに紐づく書籍が一覧表示される</t>
+        </is>
+      </c>
+      <c r="I96" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/Genre/GenreShowTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n"/>
@@ -3531,23 +3530,22 @@
       <c r="D97" s="4" t="n"/>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>5-3-4</t>
+          <t>5-3-2</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>マイ読書レポートから遷移した場合、「マイ読書レポートに戻る」リンクが表示される</t>
+          <t>ジャンルに紐づく書籍が1件もない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>1.マイ読書レポートページの「ジャンル別評価傾向 TOP5」でジャンルを押し、ジャンル詳細ページを開く
-2.画面左上の戻るリンクを確認する</t>
+          <t>1.書籍が1件も紐づいていないジャンルの詳細ページを開く</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>「← マイ読書レポートに戻る」と表示され、押すとマイ読書レポートページへ遷移する</t>
+          <t>「このジャンルの書籍はまだ登録されていません。」と表示される</t>
         </is>
       </c>
       <c r="I97" s="4" t="n"/>
@@ -3559,23 +3557,23 @@
       <c r="D98" s="4" t="n"/>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>5-3-5</t>
+          <t>5-3-3</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>ページを送っても、遷移元に応じた「戻る」リンクが維持される</t>
+          <t>ジャンル一覧から遷移した場合、「ジャンル一覧に戻る」リンクが表示される</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>1.書籍が11件以上紐づくジャンルの詳細ページを、マイ読書レポートから開く
-2.ページネーションで2ページ目を開く</t>
+          <t>1.ジャンル一覧ページでジャンル名のリンクを押し、ジャンル詳細ページを開く
+2.画面左上の戻るリンクを確認する</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>2ページ目でも「← マイ読書レポートに戻る」と表示される</t>
+          <t>「← ジャンル一覧に戻る」と表示され、押すとジャンル一覧ページへ遷移する（遷移元の指定がない場合も同様）</t>
         </is>
       </c>
       <c r="I98" s="4" t="n"/>
@@ -3583,124 +3581,125 @@
     <row r="99">
       <c r="A99" s="4" t="n"/>
       <c r="B99" s="4" t="n"/>
-      <c r="C99" s="5" t="n"/>
-      <c r="D99" s="5" t="n"/>
+      <c r="C99" s="4" t="n"/>
+      <c r="D99" s="4" t="n"/>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>5-3-6</t>
+          <t>5-3-4</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>ジャンルに紐づく書籍が登録日時の新しい順に表示される</t>
+          <t>マイ読書レポートから遷移した場合、「マイ読書レポートに戻る」リンクが表示される</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>1.登録日時の異なる複数の書籍を、同じジャンルに紐づける
-2.ジャンル詳細ページを開く</t>
+          <t>1.マイ読書レポートページの「ジャンル別評価傾向 TOP5」でジャンルを押し、ジャンル詳細ページを開く
+2.画面左上の戻るリンクを確認する</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>書籍一覧と同じく、書籍の登録日時の新しい順に表示される（ジャンルへの紐づけ順には関係しない）</t>
-        </is>
-      </c>
-      <c r="I99" s="5" t="n"/>
+          <t>「← マイ読書レポートに戻る」と表示され、押すとマイ読書レポートページへ遷移する</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="n"/>
     </row>
     <row r="100">
       <c r="A100" s="4" t="n"/>
       <c r="B100" s="4" t="n"/>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>5-4</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>ジャンル編集</t>
-        </is>
-      </c>
+      <c r="C100" s="4" t="n"/>
+      <c r="D100" s="4" t="n"/>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>5-4-1</t>
+          <t>5-3-5</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>未ログインの場合、ジャンル編集ページにアクセスできない</t>
+          <t>ページを送っても、遷移元に応じた「戻る」リンクが維持される</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>1.未ログイン状態でジャンル編集ページのURLに直接アクセスする</t>
+          <t>1.書籍が11件以上紐づくジャンルの詳細ページを、マイ読書レポートから開く
+2.ページネーションで2ページ目を開く</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/Genre/GenreUpdateTest.php</t>
-        </is>
-      </c>
+          <t>2ページ目でも「← マイ読書レポートに戻る」と表示される</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="4" t="n"/>
       <c r="B101" s="4" t="n"/>
-      <c r="C101" s="4" t="n"/>
-      <c r="D101" s="4" t="n"/>
+      <c r="C101" s="5" t="n"/>
+      <c r="D101" s="5" t="n"/>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>5-4-2</t>
+          <t>5-3-6</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>編集画面を開くと現在のジャンル名が初期表示される</t>
+          <t>ジャンルに紐づく書籍が登録日時の新しい順に表示される</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンル編集ページを開く</t>
+          <t>1.登録日時の異なる複数の書籍を、同じジャンルに紐づける
+2.ジャンル詳細ページを開く</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>ジャンル名の入力欄に現在登録されているジャンル名が表示される</t>
-        </is>
-      </c>
-      <c r="I101" s="4" t="n"/>
+          <t>書籍一覧と同じく、書籍の登録日時の新しい順に表示される（ジャンルへの紐づけ順には関係しない）</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n"/>
       <c r="B102" s="4" t="n"/>
-      <c r="C102" s="4" t="n"/>
-      <c r="D102" s="4" t="n"/>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>5-4</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>ジャンル編集</t>
+        </is>
+      </c>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>5-4-3</t>
+          <t>5-4-1</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>ジャンル名が入力されていない場合、バリデーションメッセージが表示される</t>
+          <t>未ログインの場合、ジャンル編集ページにアクセスできない</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンル編集ページを開く
-2.ジャンル名を空にして更新ボタンを押す</t>
+          <t>1.未ログイン状態でジャンル編集ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>「ジャンル名を入力してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I102" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I102" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/Genre/GenreUpdateTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n"/>
@@ -3709,23 +3708,22 @@
       <c r="D103" s="4" t="n"/>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>5-4-4</t>
+          <t>5-4-2</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>既に登録されている他のジャンル名に変更しようとした場合、バリデーションメッセージが表示される</t>
+          <t>編集画面を開くと現在のジャンル名が初期表示される</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンル編集ページを開く
-2.他のジャンルで既に使われているジャンル名に変更し、更新ボタンを押す</t>
+          <t>1.ジャンル編集ページを開く</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>「このジャンル名はすでに登録されています」というバリデーションメッセージが表示される</t>
+          <t>ジャンル名の入力欄に現在登録されているジャンル名が表示される</t>
         </is>
       </c>
       <c r="I103" s="4" t="n"/>
@@ -3733,686 +3731,684 @@
     <row r="104">
       <c r="A104" s="4" t="n"/>
       <c r="B104" s="4" t="n"/>
-      <c r="C104" s="5" t="n"/>
-      <c r="D104" s="5" t="n"/>
+      <c r="C104" s="4" t="n"/>
+      <c r="D104" s="4" t="n"/>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>5-4-5</t>
+          <t>5-4-3</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>正しくジャンル名が入力されている場合、ジャンル情報が更新される</t>
+          <t>ジャンル名が入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
           <t>1.ジャンル編集ページを開く
-2.ジャンル名を正しく変更し、更新ボタンを押す</t>
+2.ジャンル名を空にして更新ボタンを押す</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>ジャンル情報が更新され、ジャンル一覧画面に遷移し「ジャンルを更新しました。」と表示される</t>
-        </is>
-      </c>
-      <c r="I104" s="5" t="n"/>
+          <t>「ジャンル名を入力してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="4" t="n"/>
       <c r="B105" s="4" t="n"/>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>5-5</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>ジャンル削除</t>
-        </is>
-      </c>
+      <c r="C105" s="4" t="n"/>
+      <c r="D105" s="4" t="n"/>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>5-5-1</t>
+          <t>5-4-4</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>未ログインの場合、ジャンルを削除できない</t>
+          <t>既に登録されている他のジャンル名に変更しようとした場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>1.未ログイン状態でジャンル削除のリクエストを直接送信する</t>
+          <t>1.ジャンル編集ページを開く
+2.他のジャンルで既に使われているジャンル名に変更し、更新ボタンを押す</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>削除できず、ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I105" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/Genre/GenreDestroyTest.php</t>
-        </is>
-      </c>
+          <t>「このジャンル名はすでに登録されています」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="4" t="n"/>
       <c r="B106" s="4" t="n"/>
-      <c r="C106" s="4" t="n"/>
-      <c r="D106" s="4" t="n"/>
+      <c r="C106" s="5" t="n"/>
+      <c r="D106" s="5" t="n"/>
       <c r="E106" s="3" t="inlineStr">
         <is>
+          <t>5-4-5</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="inlineStr">
+        <is>
+          <t>正しくジャンル名が入力されている場合、ジャンル情報が更新される</t>
+        </is>
+      </c>
+      <c r="G106" s="3" t="inlineStr">
+        <is>
+          <t>1.ジャンル編集ページを開く
+2.ジャンル名を正しく変更し、更新ボタンを押す</t>
+        </is>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>ジャンル情報が更新され、ジャンル一覧画面に遷移し「ジャンルを更新しました。」と表示される</t>
+        </is>
+      </c>
+      <c r="I106" s="5" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n"/>
+      <c r="B107" s="4" t="n"/>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>5-5</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>ジャンル削除</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>5-5-1</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="inlineStr">
+        <is>
+          <t>未ログインの場合、ジャンルを削除できない</t>
+        </is>
+      </c>
+      <c r="G107" s="3" t="inlineStr">
+        <is>
+          <t>1.未ログイン状態でジャンル削除のリクエストを直接送信する</t>
+        </is>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>削除できず、ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/Genre/GenreDestroyTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n"/>
+      <c r="B108" s="4" t="n"/>
+      <c r="C108" s="4" t="n"/>
+      <c r="D108" s="4" t="n"/>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
           <t>5-5-2</t>
         </is>
       </c>
-      <c r="F106" s="3" t="inlineStr">
+      <c r="F108" s="3" t="inlineStr">
         <is>
           <t>紐づく書籍が存在するジャンルは削除できない</t>
         </is>
       </c>
-      <c r="G106" s="3" t="inlineStr">
+      <c r="G108" s="3" t="inlineStr">
         <is>
           <t>1.書籍が紐づいているジャンルの削除ボタンを押し、確認ダイアログでOKを押す</t>
         </is>
       </c>
-      <c r="H106" s="3" t="inlineStr">
+      <c r="H108" s="3" t="inlineStr">
         <is>
           <t>「このジャンルは書籍に紐づいているため削除できません。」と表示され、ジャンルは削除されない</t>
         </is>
       </c>
-      <c r="I106" s="4" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" s="5" t="n"/>
-      <c r="B107" s="5" t="n"/>
-      <c r="C107" s="5" t="n"/>
-      <c r="D107" s="5" t="n"/>
-      <c r="E107" s="3" t="inlineStr">
+      <c r="I108" s="4" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="5" t="n"/>
+      <c r="B109" s="5" t="n"/>
+      <c r="C109" s="5" t="n"/>
+      <c r="D109" s="5" t="n"/>
+      <c r="E109" s="3" t="inlineStr">
         <is>
           <t>5-5-3</t>
         </is>
       </c>
-      <c r="F107" s="3" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr">
         <is>
           <t>紐づく書籍が存在しないジャンルは削除できる</t>
         </is>
       </c>
-      <c r="G107" s="3" t="inlineStr">
+      <c r="G109" s="3" t="inlineStr">
         <is>
           <t>1.書籍が紐づいていないジャンルの削除ボタンを押し、確認ダイアログでOKを押す</t>
         </is>
       </c>
-      <c r="H107" s="3" t="inlineStr">
+      <c r="H109" s="3" t="inlineStr">
         <is>
           <t>ジャンルが削除され、「ジャンルを削除しました。」と表示される</t>
         </is>
       </c>
-      <c r="I107" s="5" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="I109" s="5" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>お気に入り</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>6-1</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>お気に入り一覧表示</t>
         </is>
       </c>
-      <c r="E108" s="3" t="inlineStr">
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>6-1-1</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr">
         <is>
           <t>お気に入りに登録した書籍が一覧表示される</t>
         </is>
       </c>
-      <c r="G108" s="3" t="inlineStr">
+      <c r="G110" s="3" t="inlineStr">
         <is>
           <t>1.書籍をお気に入り登録した状態でお気に入り一覧ページを開く</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
+      <c r="H110" s="3" t="inlineStr">
         <is>
           <t>お気に入り登録した書籍が一覧表示される</t>
         </is>
       </c>
-      <c r="I108" s="3" t="inlineStr">
+      <c r="I110" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Favorite/FavoriteIndexTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="4" t="n"/>
-      <c r="B109" s="4" t="n"/>
-      <c r="C109" s="4" t="n"/>
-      <c r="D109" s="4" t="n"/>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>6-1-2</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="inlineStr">
-        <is>
-          <t>お気に入りが1件も登録されていない場合の表示を確認する</t>
-        </is>
-      </c>
-      <c r="G109" s="3" t="inlineStr">
-        <is>
-          <t>1.お気に入りを1件も登録していない状態でお気に入り一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>「お気に入りに登録された書籍はありません。」と表示され、書籍一覧ページへのリンクが表示される</t>
-        </is>
-      </c>
-      <c r="I109" s="4" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="4" t="n"/>
-      <c r="B110" s="4" t="n"/>
-      <c r="C110" s="4" t="n"/>
-      <c r="D110" s="4" t="n"/>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>6-1-3</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="inlineStr">
-        <is>
-          <t>未ログインの場合、お気に入り一覧ページにアクセスできない</t>
-        </is>
-      </c>
-      <c r="G110" s="3" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態でお気に入り一覧ページのURLに直接アクセスする</t>
-        </is>
-      </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="n"/>
       <c r="B111" s="4" t="n"/>
-      <c r="C111" s="5" t="n"/>
-      <c r="D111" s="5" t="n"/>
+      <c r="C111" s="4" t="n"/>
+      <c r="D111" s="4" t="n"/>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>6-1-4</t>
+          <t>6-1-2</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>お気に入りに登録した日時の新しい順に表示される</t>
+          <t>お気に入りが1件も登録されていない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>1.複数の書籍を、時間をずらしてお気に入り登録する
-2.お気に入り一覧ページを開く</t>
+          <t>1.お気に入りを1件も登録していない状態でお気に入り一覧ページを開く</t>
         </is>
       </c>
       <c r="H111" s="3" t="inlineStr">
         <is>
-          <t>お気に入りに登録した日時の新しい順に表示される（書籍自体の登録日時の順ではない）</t>
-        </is>
-      </c>
-      <c r="I111" s="5" t="n"/>
+          <t>「お気に入りに登録された書籍はありません。」と表示され、書籍一覧ページへのリンクが表示される</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n"/>
       <c r="B112" s="4" t="n"/>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>6-2</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>お気に入りの登録・解除</t>
-        </is>
-      </c>
+      <c r="C112" s="4" t="n"/>
+      <c r="D112" s="4" t="n"/>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>6-2-1</t>
+          <t>6-1-3</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>未登録の書籍をお気に入りに登録できる</t>
+          <t>未ログインの場合、お気に入り一覧ページにアクセスできない</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>1.お気に入り未登録の書籍の詳細ページ（またはお気に入り一覧）を開く
-2.お気に入りボタン（ハートアイコン）を押す</t>
+          <t>1.未ログイン状態でお気に入り一覧ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>お気に入りに登録され、アイコンが登録済みの表示(塗りつぶし)に切り替わる</t>
-        </is>
-      </c>
-      <c r="I112" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/Favorite/FavoriteToggleTest.php</t>
-        </is>
-      </c>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="n"/>
       <c r="B113" s="4" t="n"/>
-      <c r="C113" s="4" t="n"/>
-      <c r="D113" s="4" t="n"/>
+      <c r="C113" s="5" t="n"/>
+      <c r="D113" s="5" t="n"/>
       <c r="E113" s="3" t="inlineStr">
         <is>
+          <t>6-1-4</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="inlineStr">
+        <is>
+          <t>お気に入りに登録した日時の新しい順に表示される</t>
+        </is>
+      </c>
+      <c r="G113" s="3" t="inlineStr">
+        <is>
+          <t>1.複数の書籍を、時間をずらしてお気に入り登録する
+2.お気に入り一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>お気に入りに登録した日時の新しい順に表示される（書籍自体の登録日時の順ではない）</t>
+        </is>
+      </c>
+      <c r="I113" s="5" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="n"/>
+      <c r="B114" s="4" t="n"/>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>6-2</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>お気に入りの登録・解除</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>6-2-1</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="inlineStr">
+        <is>
+          <t>未登録の書籍をお気に入りに登録できる</t>
+        </is>
+      </c>
+      <c r="G114" s="3" t="inlineStr">
+        <is>
+          <t>1.お気に入り未登録の書籍の詳細ページ（またはお気に入り一覧）を開く
+2.お気に入りボタン（ハートアイコン）を押す</t>
+        </is>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>お気に入りに登録され、アイコンが登録済みの表示(塗りつぶし)に切り替わる</t>
+        </is>
+      </c>
+      <c r="I114" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/Favorite/FavoriteToggleTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n"/>
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="4" t="n"/>
+      <c r="D115" s="4" t="n"/>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
           <t>6-2-2</t>
         </is>
       </c>
-      <c r="F113" s="3" t="inlineStr">
+      <c r="F115" s="3" t="inlineStr">
         <is>
           <t>登録済みの書籍のお気に入りを解除できる</t>
         </is>
       </c>
-      <c r="G113" s="3" t="inlineStr">
+      <c r="G115" s="3" t="inlineStr">
         <is>
           <t>1.お気に入り登録済みの書籍の詳細ページ（またはお気に入り一覧）を開く
 2.お気に入りボタン（ハートアイコン）を押す</t>
         </is>
       </c>
-      <c r="H113" s="3" t="inlineStr">
+      <c r="H115" s="3" t="inlineStr">
         <is>
           <t>お気に入りが解除され、アイコンが未登録の表示に切り替わる（お気に入り一覧では一覧から消える）</t>
         </is>
       </c>
-      <c r="I113" s="4" t="n"/>
-    </row>
-    <row r="114">
-      <c r="A114" s="5" t="n"/>
-      <c r="B114" s="5" t="n"/>
-      <c r="C114" s="5" t="n"/>
-      <c r="D114" s="5" t="n"/>
-      <c r="E114" s="3" t="inlineStr">
+      <c r="I115" s="4" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="n"/>
+      <c r="B116" s="5" t="n"/>
+      <c r="C116" s="5" t="n"/>
+      <c r="D116" s="5" t="n"/>
+      <c r="E116" s="3" t="inlineStr">
         <is>
           <t>6-2-3</t>
         </is>
       </c>
-      <c r="F114" s="3" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr">
         <is>
           <t>未ログインの場合、お気に入りボタンの代わりにログインへの案内が表示される</t>
         </is>
       </c>
-      <c r="G114" s="3" t="inlineStr">
+      <c r="G116" s="3" t="inlineStr">
         <is>
           <t>1.未ログイン状態で書籍詳細ページを開く</t>
         </is>
       </c>
-      <c r="H114" s="3" t="inlineStr">
+      <c r="H116" s="3" t="inlineStr">
         <is>
           <t>お気に入りボタンの代わりに、押すとログインページへ遷移するリンクが表示される</t>
         </is>
       </c>
-      <c r="I114" s="5" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="3" t="inlineStr">
+      <c r="I116" s="5" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
         <is>
           <t>いいね</t>
         </is>
       </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>7-1</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
         <is>
           <t>レビューへのいいねの切り替え</t>
         </is>
       </c>
-      <c r="E115" s="3" t="inlineStr">
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>7-1-1</t>
         </is>
       </c>
-      <c r="F115" s="3" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr">
         <is>
           <t>未いいねの状態からいいねできる</t>
         </is>
       </c>
-      <c r="G115" s="3" t="inlineStr">
+      <c r="G117" s="3" t="inlineStr">
         <is>
           <t>1.まだいいねしていないレビューの「いいね」ボタンを押す</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr">
+      <c r="H117" s="3" t="inlineStr">
         <is>
           <t>「いいね済み」の表示に切り替わり、いいね数が1件増える</t>
         </is>
       </c>
-      <c r="I115" s="3" t="inlineStr">
+      <c r="I117" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Like/LikeToggleTest.php</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="4" t="n"/>
-      <c r="B116" s="4" t="n"/>
-      <c r="C116" s="4" t="n"/>
-      <c r="D116" s="4" t="n"/>
-      <c r="E116" s="3" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="4" t="n"/>
+      <c r="B118" s="4" t="n"/>
+      <c r="C118" s="4" t="n"/>
+      <c r="D118" s="4" t="n"/>
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>7-1-2</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr">
         <is>
           <t>いいね済みの状態からいいねを解除できる</t>
         </is>
       </c>
-      <c r="G116" s="3" t="inlineStr">
+      <c r="G118" s="3" t="inlineStr">
         <is>
           <t>1.既にいいね済みのレビューの「いいね済み」ボタンを押す</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
+      <c r="H118" s="3" t="inlineStr">
         <is>
           <t>「いいね」の表示に切り替わり、いいね数が1件減る</t>
         </is>
       </c>
-      <c r="I116" s="4" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="n"/>
-      <c r="B117" s="5" t="n"/>
-      <c r="C117" s="5" t="n"/>
-      <c r="D117" s="5" t="n"/>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="I118" s="4" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="n"/>
+      <c r="B119" s="5" t="n"/>
+      <c r="C119" s="5" t="n"/>
+      <c r="D119" s="5" t="n"/>
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>7-1-3</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr">
         <is>
           <t>未ログインの場合、いいねボタンを押せない</t>
         </is>
       </c>
-      <c r="G117" s="3" t="inlineStr">
+      <c r="G119" s="3" t="inlineStr">
         <is>
           <t>1.未ログイン状態で書籍詳細ページを開く
 2.いいねに関する直接リクエストを送信する</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
+      <c r="H119" s="3" t="inlineStr">
         <is>
           <t>未ログインの場合はいいねボタンが操作できず、直接リクエストを送ってもログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I117" s="5" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
+      <c r="I119" s="5" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>ランキング</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>8-1</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>ランキングページ表示</t>
         </is>
       </c>
-      <c r="E118" s="3" t="inlineStr">
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>8-1-1</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr">
         <is>
           <t>レビューの平均評価が高い順に書籍が表示される</t>
         </is>
       </c>
-      <c r="G118" s="3" t="inlineStr">
+      <c r="G120" s="3" t="inlineStr">
         <is>
           <t>1.複数の書籍にレビューを投稿する
 2.ランキングページを開く</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
+      <c r="H120" s="3" t="inlineStr">
         <is>
           <t>レビューが投稿されている書籍が、平均評価の高い順に上位10件表示される</t>
         </is>
       </c>
-      <c r="I118" s="3" t="inlineStr">
+      <c r="I120" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Ranking/RankingIndexTest.php</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="4" t="n"/>
-      <c r="B119" s="4" t="n"/>
-      <c r="C119" s="4" t="n"/>
-      <c r="D119" s="4" t="n"/>
-      <c r="E119" s="3" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="4" t="n"/>
+      <c r="B121" s="4" t="n"/>
+      <c r="C121" s="4" t="n"/>
+      <c r="D121" s="4" t="n"/>
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>8-1-2</t>
         </is>
       </c>
-      <c r="F119" s="3" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>平均評価が同じ場合、レビュー件数が多い順に表示される</t>
         </is>
       </c>
-      <c r="G119" s="3" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr">
         <is>
           <t>1.平均評価が同じになる書籍を複数用意する（レビュー件数を変える）
 2.ランキングページを開く</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
+      <c r="H121" s="3" t="inlineStr">
         <is>
           <t>平均評価が同じ書籍同士は、レビュー件数が多い順（さらに同じ場合は出版日が新しい順）に表示される</t>
         </is>
       </c>
-      <c r="I119" s="4" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="4" t="n"/>
-      <c r="B120" s="4" t="n"/>
-      <c r="C120" s="4" t="n"/>
-      <c r="D120" s="4" t="n"/>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="I121" s="4" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="n"/>
+      <c r="B122" s="4" t="n"/>
+      <c r="C122" s="4" t="n"/>
+      <c r="D122" s="4" t="n"/>
+      <c r="E122" s="3" t="inlineStr">
         <is>
           <t>8-1-3</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr">
+      <c r="F122" s="3" t="inlineStr">
         <is>
           <t>レビューが投稿された書籍が1件もない場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G120" s="3" t="inlineStr">
+      <c r="G122" s="3" t="inlineStr">
         <is>
           <t>1.どの書籍にもレビューが投稿されていない状態でランキングページを開く</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
+      <c r="H122" s="3" t="inlineStr">
         <is>
           <t>「まだレビューが投稿された書籍がありません。」と表示される</t>
         </is>
       </c>
-      <c r="I120" s="4" t="n"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="n"/>
-      <c r="B121" s="5" t="n"/>
-      <c r="C121" s="5" t="n"/>
-      <c r="D121" s="5" t="n"/>
-      <c r="E121" s="3" t="inlineStr">
+      <c r="I122" s="4" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="n"/>
+      <c r="B123" s="5" t="n"/>
+      <c r="C123" s="5" t="n"/>
+      <c r="D123" s="5" t="n"/>
+      <c r="E123" s="3" t="inlineStr">
         <is>
           <t>8-1-4</t>
         </is>
       </c>
-      <c r="F121" s="3" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>未ログインの状態でもランキングページを閲覧できる</t>
         </is>
       </c>
-      <c r="G121" s="3" t="inlineStr">
+      <c r="G123" s="3" t="inlineStr">
         <is>
           <t>1.未ログイン状態でランキングページを開く</t>
         </is>
       </c>
-      <c r="H121" s="3" t="inlineStr">
+      <c r="H123" s="3" t="inlineStr">
         <is>
           <t>ランキングが表示される</t>
         </is>
       </c>
-      <c r="I121" s="5" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
+      <c r="I123" s="5" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t>認証</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>9-1</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>会員登録</t>
         </is>
       </c>
-      <c r="E122" s="3" t="inlineStr">
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>9-1-1</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr">
         <is>
           <t>名前が入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G122" s="3" t="inlineStr">
+      <c r="G124" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.名前を入力せずに他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
+      <c r="H124" s="3" t="inlineStr">
         <is>
           <t>「お名前を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I122" s="3" t="inlineStr">
+      <c r="I124" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Auth/RegisterTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="4" t="n"/>
-      <c r="B123" s="4" t="n"/>
-      <c r="C123" s="4" t="n"/>
-      <c r="D123" s="4" t="n"/>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>9-1-2</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="inlineStr">
-        <is>
-          <t>名前が21文字以上の場合、バリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="G123" s="3" t="inlineStr">
-        <is>
-          <t>1.会員登録ページを開く
-2.名前を21文字以上入力し、他の必要項目を入力する
-3.登録ボタンを押す</t>
-        </is>
-      </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>「お名前は20文字以内で入力してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I123" s="4" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="4" t="n"/>
-      <c r="B124" s="4" t="n"/>
-      <c r="C124" s="4" t="n"/>
-      <c r="D124" s="4" t="n"/>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>9-1-3</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="inlineStr">
-        <is>
-          <t>メールアドレスが入力されていない場合、バリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="G124" s="3" t="inlineStr">
-        <is>
-          <t>1.会員登録ページを開く
-2.メールアドレスを入力せずに他の必要項目を入力する
-3.登録ボタンを押す</t>
-        </is>
-      </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>「メールアドレスを入力してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I124" s="4" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n"/>
@@ -4421,24 +4417,24 @@
       <c r="D125" s="4" t="n"/>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>9-1-4</t>
+          <t>9-1-2</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
-          <t>メールアドレスがメール形式でない場合、バリデーションメッセージが表示される</t>
+          <t>名前が21文字以上の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.「abc」のようなメール形式でないメールアドレスと他の必要項目を入力する
+2.名前を21文字以上入力し、他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H125" s="3" t="inlineStr">
         <is>
-          <t>「メールアドレスはメール形式で入力してください」というバリデーションメッセージが表示される</t>
+          <t>「お名前は20文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I125" s="4" t="n"/>
@@ -4450,24 +4446,24 @@
       <c r="D126" s="4" t="n"/>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>9-1-5</t>
+          <t>9-1-3</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>メールアドレスが256文字以上の場合、バリデーションメッセージが表示される</t>
+          <t>メールアドレスが入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.256文字以上のメールアドレスと他の必要項目を入力する
+2.メールアドレスを入力せずに他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>「メールアドレスは255文字以内で入力してください」というバリデーションメッセージが表示される</t>
+          <t>「メールアドレスを入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I126" s="4" t="n"/>
@@ -4479,24 +4475,24 @@
       <c r="D127" s="4" t="n"/>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>9-1-6</t>
+          <t>9-1-4</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>既に登録されているメールアドレスの場合、バリデーションメッセージが表示される</t>
+          <t>メールアドレスがメール形式でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.既に会員登録済みのメールアドレスと他の必要項目を入力する
+2.「abc」のようなメール形式でないメールアドレスと他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>「このメールアドレスはすでに登録されています」というバリデーションメッセージが表示される</t>
+          <t>「メールアドレスはメール形式で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I127" s="4" t="n"/>
@@ -4508,24 +4504,24 @@
       <c r="D128" s="4" t="n"/>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>9-1-7</t>
+          <t>9-1-5</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
+          <t>メールアドレスが256文字以上の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.パスワードを入力せずに他の必要項目を入力する
+2.256文字以上のメールアドレスと他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>「パスワードを入力してください」というバリデーションメッセージが表示される</t>
+          <t>「メールアドレスは255文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I128" s="4" t="n"/>
@@ -4537,24 +4533,24 @@
       <c r="D129" s="4" t="n"/>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>9-1-8</t>
+          <t>9-1-6</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>パスワードが7文字以下の場合、バリデーションメッセージが表示される</t>
+          <t>既に登録されているメールアドレスの場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.7文字以下のパスワードと他の必要項目を入力する
+2.既に会員登録済みのメールアドレスと他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>「パスワードは8文字以上で入力してください」というバリデーションメッセージが表示される</t>
+          <t>「このメールアドレスはすでに登録されています」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I129" s="4" t="n"/>
@@ -4566,24 +4562,24 @@
       <c r="D130" s="4" t="n"/>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>9-1-9</t>
+          <t>9-1-7</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>パスワードが21文字以上の場合、バリデーションメッセージが表示される</t>
+          <t>パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.21文字以上のパスワードと他の必要項目を入力する
+2.パスワードを入力せずに他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>「パスワードは20文字以内で入力してください」というバリデーションメッセージが表示される</t>
+          <t>「パスワードを入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I130" s="4" t="n"/>
@@ -4595,24 +4591,24 @@
       <c r="D131" s="4" t="n"/>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>9-1-10</t>
+          <t>9-1-8</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>確認用パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
+          <t>パスワードが7文字以下の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.確認用パスワードを入力せずに他の必要項目を入力する
+2.7文字以下のパスワードと他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>「確認用パスワードを入力してください」というバリデーションメッセージが表示される</t>
+          <t>「パスワードは8文字以上で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I131" s="4" t="n"/>
@@ -4624,155 +4620,155 @@
       <c r="D132" s="4" t="n"/>
       <c r="E132" s="3" t="inlineStr">
         <is>
+          <t>9-1-9</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="inlineStr">
+        <is>
+          <t>パスワードが21文字以上の場合、バリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="G132" s="3" t="inlineStr">
+        <is>
+          <t>1.会員登録ページを開く
+2.21文字以上のパスワードと他の必要項目を入力する
+3.登録ボタンを押す</t>
+        </is>
+      </c>
+      <c r="H132" s="3" t="inlineStr">
+        <is>
+          <t>「パスワードは20文字以内で入力してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="n"/>
+      <c r="B133" s="4" t="n"/>
+      <c r="C133" s="4" t="n"/>
+      <c r="D133" s="4" t="n"/>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>9-1-10</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="inlineStr">
+        <is>
+          <t>確認用パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="G133" s="3" t="inlineStr">
+        <is>
+          <t>1.会員登録ページを開く
+2.確認用パスワードを入力せずに他の必要項目を入力する
+3.登録ボタンを押す</t>
+        </is>
+      </c>
+      <c r="H133" s="3" t="inlineStr">
+        <is>
+          <t>「確認用パスワードを入力してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="n"/>
+      <c r="B134" s="4" t="n"/>
+      <c r="C134" s="4" t="n"/>
+      <c r="D134" s="4" t="n"/>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
           <t>9-1-11</t>
         </is>
       </c>
-      <c r="F132" s="3" t="inlineStr">
+      <c r="F134" s="3" t="inlineStr">
         <is>
           <t>パスワードが確認用パスワードと一致しない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G132" s="3" t="inlineStr">
+      <c r="G134" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.確認用パスワードと異なるパスワードを入力し、他の必要項目も入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H132" s="3" t="inlineStr">
+      <c r="H134" s="3" t="inlineStr">
         <is>
           <t>「パスワードが一致しません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I132" s="4" t="n"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="4" t="n"/>
-      <c r="B133" s="4" t="n"/>
-      <c r="C133" s="5" t="n"/>
-      <c r="D133" s="5" t="n"/>
-      <c r="E133" s="3" t="inlineStr">
+      <c r="I134" s="4" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="n"/>
+      <c r="B135" s="4" t="n"/>
+      <c r="C135" s="5" t="n"/>
+      <c r="D135" s="5" t="n"/>
+      <c r="E135" s="3" t="inlineStr">
         <is>
           <t>9-1-12</t>
         </is>
       </c>
-      <c r="F133" s="3" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr">
         <is>
           <t>全ての項目が正しく入力されている場合、会員登録が完了する</t>
         </is>
       </c>
-      <c r="G133" s="3" t="inlineStr">
+      <c r="G135" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.全ての必要項目を正しく入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H133" s="3" t="inlineStr">
+      <c r="H135" s="3" t="inlineStr">
         <is>
           <t>会員情報が登録され、ログイン状態で書籍一覧画面（トップページ）に遷移する</t>
         </is>
       </c>
-      <c r="I133" s="5" t="n"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="4" t="n"/>
-      <c r="B134" s="4" t="n"/>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="I135" s="5" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="n"/>
+      <c r="B136" s="4" t="n"/>
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>9-2</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>ログイン機能</t>
         </is>
       </c>
-      <c r="E134" s="3" t="inlineStr">
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>9-2-1</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr">
         <is>
           <t>メールアドレスが入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G134" s="3" t="inlineStr">
+      <c r="G136" s="3" t="inlineStr">
         <is>
           <t>1.ログインページを開く
 2.メールアドレスを入力せずに他の必要項目を入力する
 3.ログインボタンを押す</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
+      <c r="H136" s="3" t="inlineStr">
         <is>
           <t>「メールアドレスを入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I134" s="3" t="inlineStr">
+      <c r="I136" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Auth/LoginTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="4" t="n"/>
-      <c r="B135" s="4" t="n"/>
-      <c r="C135" s="4" t="n"/>
-      <c r="D135" s="4" t="n"/>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>9-2-2</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="inlineStr">
-        <is>
-          <t>メールアドレスがメール形式でない場合、バリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="G135" s="3" t="inlineStr">
-        <is>
-          <t>1.ログインページを開く
-2.「abc」のようなメール形式でないメールアドレスと他の必要項目を入力する
-3.ログインボタンを押す</t>
-        </is>
-      </c>
-      <c r="H135" s="3" t="inlineStr">
-        <is>
-          <t>「メールアドレスはメール形式で入力してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I135" s="4" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="4" t="n"/>
-      <c r="B136" s="4" t="n"/>
-      <c r="C136" s="4" t="n"/>
-      <c r="D136" s="4" t="n"/>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>9-2-3</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="inlineStr">
-        <is>
-          <t>パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="G136" s="3" t="inlineStr">
-        <is>
-          <t>1.ログインページを開く
-2.パスワードを入力せずに他の必要項目を入力する
-3.ログインボタンを押す</t>
-        </is>
-      </c>
-      <c r="H136" s="3" t="inlineStr">
-        <is>
-          <t>「パスワードを入力してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I136" s="4" t="n"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="n"/>
@@ -4781,294 +4777,296 @@
       <c r="D137" s="4" t="n"/>
       <c r="E137" s="3" t="inlineStr">
         <is>
+          <t>9-2-2</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="inlineStr">
+        <is>
+          <t>メールアドレスがメール形式でない場合、バリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="G137" s="3" t="inlineStr">
+        <is>
+          <t>1.ログインページを開く
+2.「abc」のようなメール形式でないメールアドレスと他の必要項目を入力する
+3.ログインボタンを押す</t>
+        </is>
+      </c>
+      <c r="H137" s="3" t="inlineStr">
+        <is>
+          <t>「メールアドレスはメール形式で入力してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="n"/>
+      <c r="B138" s="4" t="n"/>
+      <c r="C138" s="4" t="n"/>
+      <c r="D138" s="4" t="n"/>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>9-2-3</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="inlineStr">
+        <is>
+          <t>パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="G138" s="3" t="inlineStr">
+        <is>
+          <t>1.ログインページを開く
+2.パスワードを入力せずに他の必要項目を入力する
+3.ログインボタンを押す</t>
+        </is>
+      </c>
+      <c r="H138" s="3" t="inlineStr">
+        <is>
+          <t>「パスワードを入力してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I138" s="4" t="n"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="n"/>
+      <c r="B139" s="4" t="n"/>
+      <c r="C139" s="4" t="n"/>
+      <c r="D139" s="4" t="n"/>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
           <t>9-2-4</t>
         </is>
       </c>
-      <c r="F137" s="3" t="inlineStr">
+      <c r="F139" s="3" t="inlineStr">
         <is>
           <t>入力情報が登録されている会員情報と一致しない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G137" s="3" t="inlineStr">
+      <c r="G139" s="3" t="inlineStr">
         <is>
           <t>1.ログインページを開く
 2.登録されていないメールアドレス、または誤ったパスワードを入力する
 3.ログインボタンを押す</t>
         </is>
       </c>
-      <c r="H137" s="3" t="inlineStr">
+      <c r="H139" s="3" t="inlineStr">
         <is>
           <t>「会員情報が登録されていません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I137" s="4" t="n"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="4" t="n"/>
-      <c r="B138" s="4" t="n"/>
-      <c r="C138" s="5" t="n"/>
-      <c r="D138" s="5" t="n"/>
-      <c r="E138" s="3" t="inlineStr">
+      <c r="I139" s="4" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="n"/>
+      <c r="B140" s="4" t="n"/>
+      <c r="C140" s="5" t="n"/>
+      <c r="D140" s="5" t="n"/>
+      <c r="E140" s="3" t="inlineStr">
         <is>
           <t>9-2-5</t>
         </is>
       </c>
-      <c r="F138" s="3" t="inlineStr">
+      <c r="F140" s="3" t="inlineStr">
         <is>
           <t>正しい情報が入力された場合、ログイン処理が実行される</t>
         </is>
       </c>
-      <c r="G138" s="3" t="inlineStr">
+      <c r="G140" s="3" t="inlineStr">
         <is>
           <t>1.ログインページを開く
 2.登録済みの正しいメールアドレス・パスワードを入力する
 3.ログインボタンを押す</t>
         </is>
       </c>
-      <c r="H138" s="3" t="inlineStr">
+      <c r="H140" s="3" t="inlineStr">
         <is>
           <t>ログイン処理が実行され、書籍一覧画面（トップページ）に遷移する</t>
         </is>
       </c>
-      <c r="I138" s="5" t="n"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="5" t="n"/>
-      <c r="B139" s="5" t="n"/>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="I140" s="5" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="5" t="n"/>
+      <c r="B141" s="5" t="n"/>
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>9-3</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>ログアウト機能</t>
         </is>
       </c>
-      <c r="E139" s="3" t="inlineStr">
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>9-3-1</t>
         </is>
       </c>
-      <c r="F139" s="3" t="inlineStr">
+      <c r="F141" s="3" t="inlineStr">
         <is>
           <t>ログアウトができる</t>
         </is>
       </c>
-      <c r="G139" s="3" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>1.ユーザーがログインする
 2.ログアウトボタンを押す</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr">
+      <c r="H141" s="3" t="inlineStr">
         <is>
           <t>ログアウト処理が実行され、ログインページに遷移する</t>
         </is>
       </c>
-      <c r="I139" s="3" t="inlineStr">
+      <c r="I141" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Auth/LogoutTest.php</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="3" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B140" s="3" t="inlineStr">
+      <c r="B142" s="3" t="inlineStr">
         <is>
           <t>公開API</t>
         </is>
       </c>
-      <c r="C140" s="3" t="inlineStr">
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t>10-1</t>
         </is>
       </c>
-      <c r="D140" s="3" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>ユーザー情報取得API(/api/user)</t>
         </is>
       </c>
-      <c r="E140" s="3" t="inlineStr">
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>10-1-1</t>
         </is>
       </c>
-      <c r="F140" s="3" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr">
         <is>
           <t>未認証でアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G140" s="3" t="inlineStr">
+      <c r="G142" s="3" t="inlineStr">
         <is>
           <t>1.トークンやセッションを持たない状態でGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
+      <c r="H142" s="3" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
         </is>
       </c>
-      <c r="I140" s="3" t="inlineStr">
+      <c r="I142" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/PublicApi/UserApiTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="4" t="n"/>
-      <c r="B141" s="4" t="n"/>
-      <c r="C141" s="4" t="n"/>
-      <c r="D141" s="4" t="n"/>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>10-1-2</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>有効なSanctumトークンでアクセスするとログインユーザーの情報が返る</t>
-        </is>
-      </c>
-      <c r="G141" s="3" t="inlineStr">
-        <is>
-          <t>1.ユーザーのpersonal access tokenを発行する
-2.そのトークンをBearerヘッダーに付与してGET /api/userにアクセスする</t>
-        </is>
-      </c>
-      <c r="H141" s="3" t="inlineStr">
-        <is>
-          <t>200が返り、該当ユーザーのid・name・emailを含むJSONが返る</t>
-        </is>
-      </c>
-      <c r="I141" s="4" t="n"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="4" t="n"/>
-      <c r="B142" s="4" t="n"/>
-      <c r="C142" s="5" t="n"/>
-      <c r="D142" s="5" t="n"/>
-      <c r="E142" s="3" t="inlineStr">
-        <is>
-          <t>10-1-3</t>
-        </is>
-      </c>
-      <c r="F142" s="3" t="inlineStr">
-        <is>
-          <t>レスポンスにパスワードなど非公開情報が含まれない</t>
-        </is>
-      </c>
-      <c r="G142" s="3" t="inlineStr">
-        <is>
-          <t>1.有効なトークンでGET /api/userにアクセスする</t>
-        </is>
-      </c>
-      <c r="H142" s="3" t="inlineStr">
-        <is>
-          <t>レスポンスJSONにpassword・remember_tokenが含まれない</t>
-        </is>
-      </c>
-      <c r="I142" s="5" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="4" t="n"/>
       <c r="B143" s="4" t="n"/>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>10-2</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>書籍一覧取得API(GET /api/v1/books)</t>
-        </is>
-      </c>
+      <c r="C143" s="4" t="n"/>
+      <c r="D143" s="4" t="n"/>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>10-2-1</t>
+          <t>10-1-2</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>認証なしでもアクセスでき、書籍一覧が返る</t>
+          <t>有効なSanctumトークンでアクセスするとログインユーザーの情報が返る</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>1.書籍を複数用意する
-2.認証情報を付与せずGET /api/v1/booksにアクセスする</t>
+          <t>1.ユーザーのpersonal access tokenを発行する
+2.そのトークンをBearerヘッダーに付与してGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>200が返り、data・links・metaを含むJSONが返る</t>
-        </is>
-      </c>
-      <c r="I143" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiIndexTest.php</t>
-        </is>
-      </c>
+          <t>200が返り、該当ユーザーのid・name・emailを含むJSONが返る</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="n"/>
       <c r="B144" s="4" t="n"/>
-      <c r="C144" s="4" t="n"/>
-      <c r="D144" s="4" t="n"/>
+      <c r="C144" s="5" t="n"/>
+      <c r="D144" s="5" t="n"/>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>10-2-2</t>
+          <t>10-1-3</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>各書籍にジャンル・平均評価・レビュー件数が含まれる</t>
+          <t>レスポンスにパスワードなど非公開情報が含まれない</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンルと、評価4・5のレビューを持つ書籍を用意する
-2.GET /api/v1/booksにアクセスする</t>
+          <t>1.有効なトークンでGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>dataの各書籍にgenres(id・name)、average_rating(4.5)、review_count(2)が含まれ、reviews(レビュー本文)は含まれない</t>
-        </is>
-      </c>
-      <c r="I144" s="4" t="n"/>
+          <t>レスポンスJSONにpassword・remember_tokenが含まれない</t>
+        </is>
+      </c>
+      <c r="I144" s="5" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n"/>
       <c r="B145" s="4" t="n"/>
-      <c r="C145" s="4" t="n"/>
-      <c r="D145" s="4" t="n"/>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>10-2</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>書籍一覧取得API(GET /api/v1/books)</t>
+        </is>
+      </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>10-2-3</t>
+          <t>10-2-1</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>レビューが無い書籍はaverage_ratingがnull、review_countが0になる</t>
+          <t>認証なしでもアクセスでき、書籍一覧が返る</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>1.レビューが1件もない書籍を用意する
-2.GET /api/v1/booksにアクセスする</t>
+          <t>1.書籍を複数用意する
+2.認証情報を付与せずGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>その書籍のaverage_ratingがnull、review_countが0で返る</t>
-        </is>
-      </c>
-      <c r="I145" s="4" t="n"/>
+          <t>200が返り、data・links・metaを含むJSONが返る</t>
+        </is>
+      </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiIndexTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n"/>
@@ -5077,23 +5075,23 @@
       <c r="D146" s="4" t="n"/>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>10-2-4</t>
+          <t>10-2-2</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>新しい順(登録日時の降順、同一なら idの降順)で返る</t>
+          <t>各書籍にジャンル・平均評価・レビュー件数が含まれる</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>1.登録日時の異なる書籍を複数用意する
+          <t>1.ジャンルと、評価4・5のレビューを持つ書籍を用意する
 2.GET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>新しく登録された書籍から順に返る</t>
+          <t>dataの各書籍にgenres(id・name)、average_rating(4.5)、review_count(2)が含まれ、reviews(レビュー本文)は含まれない</t>
         </is>
       </c>
       <c r="I146" s="4" t="n"/>
@@ -5105,23 +5103,23 @@
       <c r="D147" s="4" t="n"/>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>10-2-5</t>
+          <t>10-2-3</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>keywordでタイトル・著者名の部分一致検索ができる</t>
+          <t>レビューが無い書籍はaverage_ratingがnull、review_countが0になる</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>1.タイトルにキーワードを含む書籍、著者名にキーワードを含む書籍、含まない書籍を用意する
-2.keywordを指定してGET /api/v1/booksにアクセスする</t>
+          <t>1.レビューが1件もない書籍を用意する
+2.GET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>タイトルまたは著者名にキーワードを含む書籍のみが返る</t>
+          <t>その書籍のaverage_ratingがnull、review_countが0で返る</t>
         </is>
       </c>
       <c r="I147" s="4" t="n"/>
@@ -5133,23 +5131,23 @@
       <c r="D148" s="4" t="n"/>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>10-2-6</t>
+          <t>10-2-4</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>genreでジャンルIDによる絞り込みができる</t>
+          <t>新しい順(登録日時の降順、同一なら idの降順)で返る</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>1.異なるジャンルの書籍を用意する
-2.genreにジャンルIDを指定してGET /api/v1/booksにアクセスする</t>
+          <t>1.登録日時の異なる書籍を複数用意する
+2.GET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>指定したジャンルに属する書籍のみが返る</t>
+          <t>新しく登録された書籍から順に返る</t>
         </is>
       </c>
       <c r="I148" s="4" t="n"/>
@@ -5161,23 +5159,23 @@
       <c r="D149" s="4" t="n"/>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>10-2-7</t>
+          <t>10-2-5</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>pageでページを移動できる(1ページ10件固定)</t>
+          <t>keywordでタイトル・著者名の部分一致検索ができる</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>1.11件の書籍を用意する
-2.pageを指定せずに、およびpage=2を指定してGET /api/v1/booksにアクセスする</t>
+          <t>1.タイトルにキーワードを含む書籍、著者名にキーワードを含む書籍、含まない書籍を用意する
+2.keywordを指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>pageなしでは1ページ目の10件、page=2では残りの1件が返り、meta・linksにページ情報が反映される</t>
+          <t>タイトルまたは著者名にキーワードを含む書籍のみが返る</t>
         </is>
       </c>
       <c r="I149" s="4" t="n"/>
@@ -5185,218 +5183,219 @@
     <row r="150">
       <c r="A150" s="4" t="n"/>
       <c r="B150" s="4" t="n"/>
-      <c r="C150" s="5" t="n"/>
-      <c r="D150" s="5" t="n"/>
+      <c r="C150" s="4" t="n"/>
+      <c r="D150" s="4" t="n"/>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>10-2-8</t>
+          <t>10-2-6</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>不正なクエリパラメータを指定すると422が返る</t>
+          <t>genreでジャンルIDによる絞り込みができる</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>1.genreに存在しないID、pageに0をそれぞれ指定してGET /api/v1/booksにアクセスする(Accept: application/json)</t>
+          <t>1.異なるジャンルの書籍を用意する
+2.genreにジャンルIDを指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「指定されたジャンルは存在しません」「ページ番号は1以上の値で指定してください」が返る</t>
-        </is>
-      </c>
-      <c r="I150" s="5" t="n"/>
+          <t>指定したジャンルに属する書籍のみが返る</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n"/>
       <c r="B151" s="4" t="n"/>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>10-3</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>書籍詳細取得API(GET /api/v1/books/{book})</t>
-        </is>
-      </c>
+      <c r="C151" s="4" t="n"/>
+      <c r="D151" s="4" t="n"/>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>10-3-1</t>
+          <t>10-2-7</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>認証なしでもアクセスでき、書籍の詳細が返る</t>
+          <t>pageでページを移動できる(1ページ10件固定)</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンルとレビューを持つ書籍を用意する
-2.認証情報を付与せずGET /api/v1/books/{book}にアクセスする</t>
+          <t>1.11件の書籍を用意する
+2.pageを指定せずに、およびpage=2を指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>200が返り、書籍情報・genres・average_rating・review_countを含むJSONが返る</t>
-        </is>
-      </c>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiShowTest.php</t>
-        </is>
-      </c>
+          <t>pageなしでは1ページ目の10件、page=2では残りの1件が返り、meta・linksにページ情報が反映される</t>
+        </is>
+      </c>
+      <c r="I151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n"/>
       <c r="B152" s="4" t="n"/>
-      <c r="C152" s="4" t="n"/>
-      <c r="D152" s="4" t="n"/>
+      <c r="C152" s="5" t="n"/>
+      <c r="D152" s="5" t="n"/>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>10-3-2</t>
+          <t>10-2-8</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>レビュー(投稿者名・評価・コメント・投稿日時)が新しい順に含まれる</t>
+          <t>不正なクエリパラメータを指定すると422が返る</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>1.異なる日時に投稿された複数のレビューを持つ書籍を用意する
-2.GET /api/v1/books/{book}にアクセスする</t>
+          <t>1.genreに存在しないID、pageに0をそれぞれ指定してGET /api/v1/booksにアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>reviewsにuser_name・rating・comment・created_atが含まれ、投稿日時の新しい順に並ぶ</t>
-        </is>
-      </c>
-      <c r="I152" s="4" t="n"/>
+          <t>422が返り、「指定されたジャンルは存在しません」「ページ番号は1以上の値で指定してください」が返る</t>
+        </is>
+      </c>
+      <c r="I152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n"/>
       <c r="B153" s="4" t="n"/>
-      <c r="C153" s="5" t="n"/>
-      <c r="D153" s="5" t="n"/>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>10-3</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>書籍詳細取得API(GET /api/v1/books/{book})</t>
+        </is>
+      </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>10-3-3</t>
+          <t>10-3-1</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>存在しないIDを指定すると404が返る</t>
+          <t>認証なしでもアクセスでき、書籍の詳細が返る</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>1.存在しない書籍IDでGET /api/v1/books/{book}にアクセスする</t>
+          <t>1.ジャンルとレビューを持つ書籍を用意する
+2.認証情報を付与せずGET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
-        </is>
-      </c>
-      <c r="I153" s="5" t="n"/>
+          <t>200が返り、書籍情報・genres・average_rating・review_countを含むJSONが返る</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiShowTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="n"/>
       <c r="B154" s="4" t="n"/>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>10-4</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>書籍登録API(POST /api/v1/books)</t>
-        </is>
-      </c>
+      <c r="C154" s="4" t="n"/>
+      <c r="D154" s="4" t="n"/>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>10-4-1</t>
+          <t>10-3-2</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>認証なしでアクセスすると401が返る</t>
+          <t>レビュー(投稿者名・評価・コメント・投稿日時)が新しい順に含まれる</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>1.認証情報を付与せずPOST /api/v1/booksにアクセスする(Accept: application/json)</t>
+          <t>1.異なる日時に投稿された複数のレビューを持つ書籍を用意する
+2.GET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録されない</t>
-        </is>
-      </c>
-      <c r="I154" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiStoreTest.php</t>
-        </is>
-      </c>
+          <t>reviewsにuser_name・rating・comment・created_atが含まれ、投稿日時の新しい順に並ぶ</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n"/>
       <c r="B155" s="4" t="n"/>
-      <c r="C155" s="4" t="n"/>
-      <c r="D155" s="4" t="n"/>
+      <c r="C155" s="5" t="n"/>
+      <c r="D155" s="5" t="n"/>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>10-4-2</t>
+          <t>10-3-3</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>有効なトークンで書籍を登録できる</t>
+          <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーのトークンを発行する
-2.必要項目を指定し、Bearerトークンを付与してPOST /api/v1/booksにアクセスする</t>
+          <t>1.存在しない書籍IDでGET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>201が返り、登録内容がJSONで返る。書籍がDBに保存される</t>
-        </is>
-      </c>
-      <c r="I155" s="4" t="n"/>
+          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n"/>
       <c r="B156" s="4" t="n"/>
-      <c r="C156" s="4" t="n"/>
-      <c r="D156" s="4" t="n"/>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>10-4</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>書籍登録API(POST /api/v1/books)</t>
+        </is>
+      </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>10-4-3</t>
+          <t>10-4-1</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>登録者(user_id)は、リクエストの値ではなく認証ユーザーになる</t>
+          <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>1.他のユーザーのIDをuser_idに含めて、トークンを付与しPOST /api/v1/booksにアクセスする</t>
+          <t>1.認証情報を付与せずPOST /api/v1/booksにアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>登録された書籍のuser_idは、トークンの持ち主(認証ユーザー)のIDになる</t>
-        </is>
-      </c>
-      <c r="I156" s="4" t="n"/>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録されない</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiStoreTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n"/>
@@ -5405,22 +5404,23 @@
       <c r="D157" s="4" t="n"/>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>10-4-4</t>
+          <t>10-4-2</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>選択したジャンルが書籍に紐づけられる</t>
+          <t>有効なトークンで書籍を登録できる</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>1.複数のジャンルIDをgenresに指定してPOST /api/v1/booksにアクセスする</t>
+          <t>1.ユーザーのトークンを発行する
+2.必要項目を指定し、Bearerトークンを付与してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>中間テーブル(book_genre)に指定したジャンルが保存され、レスポンスのgenresにも含まれる</t>
+          <t>201が返り、登録内容がJSONで返る。書籍がDBに保存される</t>
         </is>
       </c>
       <c r="I157" s="4" t="n"/>
@@ -5432,22 +5432,22 @@
       <c r="D158" s="4" t="n"/>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>10-4-5</t>
+          <t>10-4-3</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>必須項目(title・author・genres)が未入力の場合、422が返る</t>
+          <t>登録者(user_id)は、リクエストの値ではなく認証ユーザーになる</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>1.title・author・genresを指定せずにPOST /api/v1/booksにアクセスする</t>
+          <t>1.他のユーザーのIDをuser_idに含めて、トークンを付与しPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「書籍タイトルを入力してください」「著者名を入力してください」「ジャンルを1つ以上選択してください」が返る</t>
+          <t>登録された書籍のuser_idは、トークンの持ち主(認証ユーザー)のIDになる</t>
         </is>
       </c>
       <c r="I158" s="4" t="n"/>
@@ -5459,23 +5459,22 @@
       <c r="D159" s="4" t="n"/>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>10-4-6</t>
+          <t>10-4-4</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>ISBNが13桁の数字でない、または登録済みの場合、422が返る</t>
+          <t>選択したジャンルが書籍に紐づけられる</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>1.ISBNに13桁でない値を指定してPOST /api/v1/booksにアクセスする
-2.登録済みのISBNを指定して同様にアクセスする</t>
+          <t>1.複数のジャンルIDをgenresに指定してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「ISBNは13桁の数字で入力してください」「このISBNはすでに登録されています」が返る</t>
+          <t>中間テーブル(book_genre)に指定したジャンルが保存され、レスポンスのgenresにも含まれる</t>
         </is>
       </c>
       <c r="I159" s="4" t="n"/>
@@ -5483,124 +5482,123 @@
     <row r="160">
       <c r="A160" s="4" t="n"/>
       <c r="B160" s="4" t="n"/>
-      <c r="C160" s="5" t="n"/>
-      <c r="D160" s="5" t="n"/>
+      <c r="C160" s="4" t="n"/>
+      <c r="D160" s="4" t="n"/>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>10-4-7</t>
+          <t>10-4-5</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>存在しないジャンルIDを指定すると422が返る</t>
+          <t>必須項目(title・author・genres)が未入力の場合、422が返る</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>1.genresに存在しないジャンルIDを指定してPOST /api/v1/booksにアクセスする</t>
+          <t>1.title・author・genresを指定せずにPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「選択されたジャンルは存在しません」が返る</t>
-        </is>
-      </c>
-      <c r="I160" s="5" t="n"/>
+          <t>422が返り、「書籍タイトルを入力してください」「著者名を入力してください」「ジャンルを1つ以上選択してください」が返る</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n"/>
       <c r="B161" s="4" t="n"/>
-      <c r="C161" s="3" t="inlineStr">
-        <is>
-          <t>10-5</t>
-        </is>
-      </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>書籍更新API(PUT /api/v1/books/{book})</t>
-        </is>
-      </c>
+      <c r="C161" s="4" t="n"/>
+      <c r="D161" s="4" t="n"/>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>10-5-1</t>
+          <t>10-4-6</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>認証なしでアクセスすると401が返る</t>
+          <t>ISBNが13桁の数字でない、または登録済みの場合、422が返る</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>1.認証情報を付与せずPUT /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
+          <t>1.ISBNに13桁でない値を指定してPOST /api/v1/booksにアクセスする
+2.登録済みのISBNを指定して同様にアクセスする</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は更新されない</t>
-        </is>
-      </c>
-      <c r="I161" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiUpdateTest.php</t>
-        </is>
-      </c>
+          <t>422が返り、「ISBNは13桁の数字で入力してください」「このISBNはすでに登録されています」が返る</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="n"/>
       <c r="B162" s="4" t="n"/>
-      <c r="C162" s="4" t="n"/>
-      <c r="D162" s="4" t="n"/>
+      <c r="C162" s="5" t="n"/>
+      <c r="D162" s="5" t="n"/>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>10-5-2</t>
+          <t>10-4-7</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>自分が登録した書籍を更新できる</t>
+          <t>存在しないジャンルIDを指定すると422が返る</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーが登録した書籍を用意する
-2.そのユーザーのトークンを付与し、変更内容・ジャンルを指定してPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.genresに存在しないジャンルIDを指定してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>200が返り、更新後の内容がJSONで返る。DBの書籍情報とジャンルの紐づけが更新される</t>
-        </is>
-      </c>
-      <c r="I162" s="4" t="n"/>
+          <t>422が返り、「選択されたジャンルは存在しません」が返る</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n"/>
       <c r="B163" s="4" t="n"/>
-      <c r="C163" s="4" t="n"/>
-      <c r="D163" s="4" t="n"/>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>10-5</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>書籍更新API(PUT /api/v1/books/{book})</t>
+        </is>
+      </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>10-5-3</t>
+          <t>10-5-1</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>自分の書籍のISBNを変更せずに更新しても、ISBNの重複エラーにならない</t>
+          <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーが登録した書籍(ISBNあり)を用意する
-2.ISBNを変えずに他の項目を変更してPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.認証情報を付与せずPUT /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>200が返り、更新できる</t>
-        </is>
-      </c>
-      <c r="I163" s="4" t="n"/>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiUpdateTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n"/>
@@ -5609,23 +5607,23 @@
       <c r="D164" s="4" t="n"/>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>10-5-4</t>
+          <t>10-5-2</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>他のユーザーが登録した書籍は更新できない</t>
+          <t>自分が登録した書籍を更新できる</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>1.他のユーザーが登録した書籍を用意する
-2.別のユーザーのトークンを付与してPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.ユーザーが登録した書籍を用意する
+2.そのユーザーのトークンを付与し、変更内容・ジャンルを指定してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は更新されない</t>
+          <t>200が返り、更新後の内容がJSONで返る。DBの書籍情報とジャンルの紐づけが更新される</t>
         </is>
       </c>
       <c r="I164" s="4" t="n"/>
@@ -5637,22 +5635,23 @@
       <c r="D165" s="4" t="n"/>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>10-5-5</t>
+          <t>10-5-3</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>存在しないIDを指定すると404が返る</t>
+          <t>自分の書籍のISBNを変更せずに更新しても、ISBNの重複エラーにならない</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>1.トークンを付与し、存在しない書籍IDでPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.ユーザーが登録した書籍(ISBNあり)を用意する
+2.ISBNを変えずに他の項目を変更してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
+          <t>200が返り、更新できる</t>
         </is>
       </c>
       <c r="I165" s="4" t="n"/>
@@ -5664,22 +5663,23 @@
       <c r="D166" s="4" t="n"/>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>10-5-6</t>
+          <t>10-5-4</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>入力内容が不正な場合、422が返る</t>
+          <t>他のユーザーが登録した書籍は更新できない</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>1.自分の書籍に対し、titleを空にしてPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.他のユーザーが登録した書籍を用意する
+2.別のユーザーのトークンを付与してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「書籍タイトルを入力してください」が返る。書籍は更新されない</t>
+          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は更新されない</t>
         </is>
       </c>
       <c r="I166" s="4" t="n"/>
@@ -5687,125 +5687,123 @@
     <row r="167">
       <c r="A167" s="4" t="n"/>
       <c r="B167" s="4" t="n"/>
-      <c r="C167" s="5" t="n"/>
-      <c r="D167" s="5" t="n"/>
+      <c r="C167" s="4" t="n"/>
+      <c r="D167" s="4" t="n"/>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>10-5-7</t>
+          <t>10-5-5</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>他のユーザーが登録した書籍に対して不正な入力で更新しようとしても、422ではなく403が返る</t>
+          <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>1.他のユーザーが登録した書籍を用意する
-2.別のユーザーのトークンを付与し、タイトルを空にするなど不正な内容でPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.トークンを付与し、存在しない書籍IDでPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る（入力チェックより先に権限が判定される）。書籍は更新されない</t>
-        </is>
-      </c>
-      <c r="I167" s="5" t="n"/>
+          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="n"/>
       <c r="B168" s="4" t="n"/>
-      <c r="C168" s="3" t="inlineStr">
-        <is>
-          <t>10-6</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>書籍削除API(DELETE /api/v1/books/{book})</t>
-        </is>
-      </c>
+      <c r="C168" s="4" t="n"/>
+      <c r="D168" s="4" t="n"/>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>10-6-1</t>
+          <t>10-5-6</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>認証なしでアクセスすると401が返る</t>
+          <t>入力内容が不正な場合、422が返る</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>1.認証情報を付与せずDELETE /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
+          <t>1.自分の書籍に対し、titleを空にしてPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は削除されない</t>
-        </is>
-      </c>
-      <c r="I168" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiDestroyTest.php</t>
-        </is>
-      </c>
+          <t>422が返り、「書籍タイトルを入力してください」が返る。書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n"/>
       <c r="B169" s="4" t="n"/>
-      <c r="C169" s="4" t="n"/>
-      <c r="D169" s="4" t="n"/>
+      <c r="C169" s="5" t="n"/>
+      <c r="D169" s="5" t="n"/>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>10-6-2</t>
+          <t>10-5-7</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>自分が登録した書籍を削除できる</t>
+          <t>他のユーザーが登録した書籍に対して不正な入力で更新しようとしても、422ではなく403が返る</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーが登録した書籍を用意する
-2.そのユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
+          <t>1.他のユーザーが登録した書籍を用意する
+2.別のユーザーのトークンを付与し、タイトルを空にするなど不正な内容でPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>204が返り(レスポンスボディなし)、書籍がDBから削除される</t>
-        </is>
-      </c>
-      <c r="I169" s="4" t="n"/>
+          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る（入力チェックより先に権限が判定される）。書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n"/>
       <c r="B170" s="4" t="n"/>
-      <c r="C170" s="4" t="n"/>
-      <c r="D170" s="4" t="n"/>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>10-6</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>書籍削除API(DELETE /api/v1/books/{book})</t>
+        </is>
+      </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>10-6-3</t>
+          <t>10-6-1</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>書籍を削除すると、関連するデータも一緒に削除される</t>
+          <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンルの紐づけ・レビュー・お気に入り・レビューへのいいねを持つ書籍を用意する
-2.所有者のトークンでDELETE /api/v1/books/{book}にアクセスする</t>
+          <t>1.認証情報を付与せずDELETE /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>book_genre・reviews・favorites・review_likesの該当データも削除される</t>
-        </is>
-      </c>
-      <c r="I170" s="4" t="n"/>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は削除されない</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiDestroyTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
@@ -5814,157 +5812,157 @@
       <c r="D171" s="4" t="n"/>
       <c r="E171" s="3" t="inlineStr">
         <is>
+          <t>10-6-2</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>自分が登録した書籍を削除できる</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>1.ユーザーが登録した書籍を用意する
+2.そのユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>204が返り(レスポンスボディなし)、書籍がDBから削除される</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="n"/>
+      <c r="B172" s="4" t="n"/>
+      <c r="C172" s="4" t="n"/>
+      <c r="D172" s="4" t="n"/>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>10-6-3</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>書籍を削除すると、関連するデータも一緒に削除される</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>1.ジャンルの紐づけ・レビュー・お気に入り・レビューへのいいねを持つ書籍を用意する
+2.所有者のトークンでDELETE /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>book_genre・reviews・favorites・review_likesの該当データも削除される</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="n"/>
+      <c r="B173" s="4" t="n"/>
+      <c r="C173" s="4" t="n"/>
+      <c r="D173" s="4" t="n"/>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
           <t>10-6-4</t>
         </is>
       </c>
-      <c r="F171" s="3" t="inlineStr">
+      <c r="F173" s="3" t="inlineStr">
         <is>
           <t>他のユーザーが登録した書籍は削除できない</t>
         </is>
       </c>
-      <c r="G171" s="3" t="inlineStr">
+      <c r="G173" s="3" t="inlineStr">
         <is>
           <t>1.他のユーザーが登録した書籍を用意する
 2.別のユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H171" s="3" t="inlineStr">
+      <c r="H173" s="3" t="inlineStr">
         <is>
           <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は削除されない</t>
         </is>
       </c>
-      <c r="I171" s="4" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="5" t="n"/>
-      <c r="B172" s="5" t="n"/>
-      <c r="C172" s="5" t="n"/>
-      <c r="D172" s="5" t="n"/>
-      <c r="E172" s="3" t="inlineStr">
+      <c r="I173" s="4" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="n"/>
+      <c r="B174" s="5" t="n"/>
+      <c r="C174" s="5" t="n"/>
+      <c r="D174" s="5" t="n"/>
+      <c r="E174" s="3" t="inlineStr">
         <is>
           <t>10-6-5</t>
         </is>
       </c>
-      <c r="F172" s="3" t="inlineStr">
+      <c r="F174" s="3" t="inlineStr">
         <is>
           <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
-      <c r="G172" s="3" t="inlineStr">
+      <c r="G174" s="3" t="inlineStr">
         <is>
           <t>1.トークンを付与し、存在しない書籍IDでDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H172" s="3" t="inlineStr">
+      <c r="H174" s="3" t="inlineStr">
         <is>
           <t>404が返り、「指定された書籍が見つかりません」が返る</t>
         </is>
       </c>
-      <c r="I172" s="5" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="7" t="inlineStr">
+      <c r="I174" s="5" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B173" s="7" t="inlineStr">
+      <c r="B175" s="7" t="inlineStr">
         <is>
           <t>検索・フィルタ</t>
         </is>
       </c>
-      <c r="C173" s="7" t="inlineStr">
+      <c r="C175" s="7" t="inlineStr">
         <is>
           <t>11-1</t>
         </is>
       </c>
-      <c r="D173" s="7" t="inlineStr">
+      <c r="D175" s="7" t="inlineStr">
         <is>
           <t>書籍のキーワード検索・ジャンル絞り込み</t>
         </is>
       </c>
-      <c r="E173" s="7" t="inlineStr">
+      <c r="E175" s="7" t="inlineStr">
         <is>
           <t>11-1-1</t>
         </is>
       </c>
-      <c r="F173" s="7" t="inlineStr">
+      <c r="F175" s="7" t="inlineStr">
         <is>
           <t>タイトルにキーワードを含む書籍が検索結果に表示される</t>
         </is>
       </c>
-      <c r="G173" s="7" t="inlineStr">
+      <c r="G175" s="7" t="inlineStr">
         <is>
           <t>1.タイトルにキーワードを含む書籍を用意する
 2.書籍一覧ページでkeywordにそのキーワードを指定して検索する</t>
         </is>
       </c>
-      <c r="H173" s="7" t="inlineStr">
+      <c r="H175" s="7" t="inlineStr">
         <is>
           <t>該当する書籍が検索結果に表示される</t>
         </is>
       </c>
-      <c r="I173" s="7" t="inlineStr">
+      <c r="I175" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Search/SearchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="4" t="n"/>
-      <c r="B174" s="4" t="n"/>
-      <c r="C174" s="4" t="n"/>
-      <c r="D174" s="4" t="n"/>
-      <c r="E174" s="7" t="inlineStr">
-        <is>
-          <t>11-1-2</t>
-        </is>
-      </c>
-      <c r="F174" s="7" t="inlineStr">
-        <is>
-          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="G174" s="7" t="inlineStr">
-        <is>
-          <t>1.著者名にキーワードを含む書籍を用意する
-2.同キーワードで検索する</t>
-        </is>
-      </c>
-      <c r="H174" s="7" t="inlineStr">
-        <is>
-          <t>該当する書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="I174" s="4" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="4" t="n"/>
-      <c r="B175" s="4" t="n"/>
-      <c r="C175" s="4" t="n"/>
-      <c r="D175" s="4" t="n"/>
-      <c r="E175" s="7" t="inlineStr">
-        <is>
-          <t>11-1-3</t>
-        </is>
-      </c>
-      <c r="F175" s="7" t="inlineStr">
-        <is>
-          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
-        </is>
-      </c>
-      <c r="G175" s="7" t="inlineStr">
-        <is>
-          <t>1.キーワードに一致しない書籍を用意する
-2.検索する</t>
-        </is>
-      </c>
-      <c r="H175" s="7" t="inlineStr">
-        <is>
-          <t>その書籍は検索結果に表示されない</t>
-        </is>
-      </c>
-      <c r="I175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n"/>
@@ -5973,22 +5971,23 @@
       <c r="D176" s="4" t="n"/>
       <c r="E176" s="7" t="inlineStr">
         <is>
-          <t>11-1-4</t>
+          <t>11-1-2</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>キーワード未入力の場合は全件が表示される</t>
+          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
+          <t>1.著者名にキーワードを含む書籍を用意する
+2.同キーワードで検索する</t>
         </is>
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
-          <t>登録されている全ての書籍が表示される</t>
+          <t>該当する書籍が検索結果に表示される</t>
         </is>
       </c>
       <c r="I176" s="4" t="n"/>
@@ -6000,23 +5999,23 @@
       <c r="D177" s="4" t="n"/>
       <c r="E177" s="7" t="inlineStr">
         <is>
-          <t>11-1-5</t>
+          <t>11-1-3</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
+          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>1.複数ジャンルの書籍を用意する
-2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
+          <t>1.キーワードに一致しない書籍を用意する
+2.検索する</t>
         </is>
       </c>
       <c r="H177" s="7" t="inlineStr">
         <is>
-          <t>指定したジャンルに紐づく書籍のみ表示される</t>
+          <t>その書籍は検索結果に表示されない</t>
         </is>
       </c>
       <c r="I177" s="4" t="n"/>
@@ -6028,156 +6027,155 @@
       <c r="D178" s="4" t="n"/>
       <c r="E178" s="7" t="inlineStr">
         <is>
+          <t>11-1-4</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>キーワード未入力の場合は全件が表示される</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H178" s="7" t="inlineStr">
+        <is>
+          <t>登録されている全ての書籍が表示される</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="n"/>
+      <c r="B179" s="4" t="n"/>
+      <c r="C179" s="4" t="n"/>
+      <c r="D179" s="4" t="n"/>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>11-1-5</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>1.複数ジャンルの書籍を用意する
+2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
+        </is>
+      </c>
+      <c r="H179" s="7" t="inlineStr">
+        <is>
+          <t>指定したジャンルに紐づく書籍のみ表示される</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="n"/>
+      <c r="B180" s="4" t="n"/>
+      <c r="C180" s="4" t="n"/>
+      <c r="D180" s="4" t="n"/>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
           <t>11-1-6</t>
         </is>
       </c>
-      <c r="F178" s="7" t="inlineStr">
+      <c r="F180" s="7" t="inlineStr">
         <is>
           <t>キーワード検索とジャンル絞り込みを組み合わせて使用できる</t>
         </is>
       </c>
-      <c r="G178" s="7" t="inlineStr">
+      <c r="G180" s="7" t="inlineStr">
         <is>
           <t>1.keywordとgenreの両方を指定して一覧を開く</t>
         </is>
       </c>
-      <c r="H178" s="7" t="inlineStr">
+      <c r="H180" s="7" t="inlineStr">
         <is>
           <t>キーワードとジャンルの両方の条件に一致する書籍のみ表示される</t>
         </is>
       </c>
-      <c r="I178" s="4" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="5" t="n"/>
-      <c r="B179" s="5" t="n"/>
-      <c r="C179" s="5" t="n"/>
-      <c r="D179" s="5" t="n"/>
-      <c r="E179" s="7" t="inlineStr">
+      <c r="I180" s="4" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="n"/>
+      <c r="B181" s="5" t="n"/>
+      <c r="C181" s="5" t="n"/>
+      <c r="D181" s="5" t="n"/>
+      <c r="E181" s="7" t="inlineStr">
         <is>
           <t>11-1-7</t>
         </is>
       </c>
-      <c r="F179" s="7" t="inlineStr">
+      <c r="F181" s="7" t="inlineStr">
         <is>
           <t>検索結果が0件の場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G179" s="7" t="inlineStr">
+      <c r="G181" s="7" t="inlineStr">
         <is>
           <t>1.どの書籍にも一致しないキーワードで検索する</t>
         </is>
       </c>
-      <c r="H179" s="7" t="inlineStr">
+      <c r="H181" s="7" t="inlineStr">
         <is>
           <t>「条件に一致する書籍が見つかりませんでした。」と表示される</t>
         </is>
       </c>
-      <c r="I179" s="5" t="n"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="7" t="inlineStr">
+      <c r="I181" s="5" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B180" s="7" t="inlineStr">
+      <c r="B182" s="7" t="inlineStr">
         <is>
           <t>ソート</t>
         </is>
       </c>
-      <c r="C180" s="7" t="inlineStr">
+      <c r="C182" s="7" t="inlineStr">
         <is>
           <t>12-1</t>
         </is>
       </c>
-      <c r="D180" s="7" t="inlineStr">
+      <c r="D182" s="7" t="inlineStr">
         <is>
           <t>書籍一覧の並び替え</t>
         </is>
       </c>
-      <c r="E180" s="7" t="inlineStr">
+      <c r="E182" s="7" t="inlineStr">
         <is>
           <t>12-1-1</t>
         </is>
       </c>
-      <c r="F180" s="7" t="inlineStr">
+      <c r="F182" s="7" t="inlineStr">
         <is>
           <t>並び替え未指定時は新着順(登録が新しい順)で表示される</t>
         </is>
       </c>
-      <c r="G180" s="7" t="inlineStr">
+      <c r="G182" s="7" t="inlineStr">
         <is>
           <t>1.複数の書籍を異なる日時で登録する
 2.sortを指定せずに書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H180" s="7" t="inlineStr">
+      <c r="H182" s="7" t="inlineStr">
         <is>
           <t>登録日時が新しい順に表示される</t>
         </is>
       </c>
-      <c r="I180" s="7" t="inlineStr">
+      <c r="I182" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Sort/SortTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="4" t="n"/>
-      <c r="B181" s="4" t="n"/>
-      <c r="C181" s="4" t="n"/>
-      <c r="D181" s="4" t="n"/>
-      <c r="E181" s="7" t="inlineStr">
-        <is>
-          <t>12-1-2</t>
-        </is>
-      </c>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
-          <t>sort=oldestを指定すると登録が古い順に表示される</t>
-        </is>
-      </c>
-      <c r="G181" s="7" t="inlineStr">
-        <is>
-          <t>1.複数の書籍を異なる日時で登録する
-2.sort=oldestを指定して書籍一覧を開く</t>
-        </is>
-      </c>
-      <c r="H181" s="7" t="inlineStr">
-        <is>
-          <t>登録日時が古い順に表示される</t>
-        </is>
-      </c>
-      <c r="I181" s="4" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="4" t="n"/>
-      <c r="B182" s="4" t="n"/>
-      <c r="C182" s="4" t="n"/>
-      <c r="D182" s="4" t="n"/>
-      <c r="E182" s="7" t="inlineStr">
-        <is>
-          <t>12-1-3</t>
-        </is>
-      </c>
-      <c r="F182" s="7" t="inlineStr">
-        <is>
-          <t>sort=titleを指定するとタイトルの昇順で表示される</t>
-        </is>
-      </c>
-      <c r="G182" s="7" t="inlineStr">
-        <is>
-          <t>1.複数の書籍を用意する
-2.sort=titleを指定して書籍一覧を開く</t>
-        </is>
-      </c>
-      <c r="H182" s="7" t="inlineStr">
-        <is>
-          <t>タイトルの昇順で表示される</t>
-        </is>
-      </c>
-      <c r="I182" s="4" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n"/>
@@ -6186,155 +6184,157 @@
       <c r="D183" s="4" t="n"/>
       <c r="E183" s="7" t="inlineStr">
         <is>
+          <t>12-1-2</t>
+        </is>
+      </c>
+      <c r="F183" s="7" t="inlineStr">
+        <is>
+          <t>sort=oldestを指定すると登録が古い順に表示される</t>
+        </is>
+      </c>
+      <c r="G183" s="7" t="inlineStr">
+        <is>
+          <t>1.複数の書籍を異なる日時で登録する
+2.sort=oldestを指定して書籍一覧を開く</t>
+        </is>
+      </c>
+      <c r="H183" s="7" t="inlineStr">
+        <is>
+          <t>登録日時が古い順に表示される</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="n"/>
+      <c r="B184" s="4" t="n"/>
+      <c r="C184" s="4" t="n"/>
+      <c r="D184" s="4" t="n"/>
+      <c r="E184" s="7" t="inlineStr">
+        <is>
+          <t>12-1-3</t>
+        </is>
+      </c>
+      <c r="F184" s="7" t="inlineStr">
+        <is>
+          <t>sort=titleを指定するとタイトルの昇順で表示される</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="inlineStr">
+        <is>
+          <t>1.複数の書籍を用意する
+2.sort=titleを指定して書籍一覧を開く</t>
+        </is>
+      </c>
+      <c r="H184" s="7" t="inlineStr">
+        <is>
+          <t>タイトルの昇順で表示される</t>
+        </is>
+      </c>
+      <c r="I184" s="4" t="n"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="n"/>
+      <c r="B185" s="4" t="n"/>
+      <c r="C185" s="4" t="n"/>
+      <c r="D185" s="4" t="n"/>
+      <c r="E185" s="7" t="inlineStr">
+        <is>
           <t>12-1-4</t>
         </is>
       </c>
-      <c r="F183" s="7" t="inlineStr">
+      <c r="F185" s="7" t="inlineStr">
         <is>
           <t>sort=ratingを指定すると平均評価が高い順に表示される</t>
         </is>
       </c>
-      <c r="G183" s="7" t="inlineStr">
+      <c r="G185" s="7" t="inlineStr">
         <is>
           <t>1.平均評価が異なる複数の書籍を用意する
 2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H183" s="7" t="inlineStr">
+      <c r="H185" s="7" t="inlineStr">
         <is>
           <t>平均評価が高い順に表示される</t>
         </is>
       </c>
-      <c r="I183" s="4" t="n"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="5" t="n"/>
-      <c r="B184" s="5" t="n"/>
-      <c r="C184" s="5" t="n"/>
-      <c r="D184" s="5" t="n"/>
-      <c r="E184" s="7" t="inlineStr">
+      <c r="I185" s="4" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="5" t="n"/>
+      <c r="B186" s="5" t="n"/>
+      <c r="C186" s="5" t="n"/>
+      <c r="D186" s="5" t="n"/>
+      <c r="E186" s="7" t="inlineStr">
         <is>
           <t>12-1-5</t>
         </is>
       </c>
-      <c r="F184" s="7" t="inlineStr">
+      <c r="F186" s="7" t="inlineStr">
         <is>
           <t>sort=rating指定時、平均評価が同じ書籍は新着順で表示される</t>
         </is>
       </c>
-      <c r="G184" s="7" t="inlineStr">
+      <c r="G186" s="7" t="inlineStr">
         <is>
           <t>1.平均評価が同じ複数の書籍を、異なる登録日時で用意する
 2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H184" s="7" t="inlineStr">
+      <c r="H186" s="7" t="inlineStr">
         <is>
           <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
         </is>
       </c>
-      <c r="I184" s="5" t="n"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="7" t="inlineStr">
+      <c r="I186" s="5" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B185" s="7" t="inlineStr">
+      <c r="B187" s="7" t="inlineStr">
         <is>
           <t>書籍CRUD（認可の詳細テスト）</t>
         </is>
       </c>
-      <c r="C185" s="7" t="inlineStr">
+      <c r="C187" s="7" t="inlineStr">
         <is>
           <t>13-1</t>
         </is>
       </c>
-      <c r="D185" s="7" t="inlineStr">
+      <c r="D187" s="7" t="inlineStr">
         <is>
           <t>BookPolicyの認可ロジック</t>
         </is>
       </c>
-      <c r="E185" s="7" t="inlineStr">
+      <c r="E187" s="7" t="inlineStr">
         <is>
           <t>13-1-1</t>
         </is>
       </c>
-      <c r="F185" s="7" t="inlineStr">
+      <c r="F187" s="7" t="inlineStr">
         <is>
           <t>ログインユーザーは誰でも書籍を作成できる</t>
         </is>
       </c>
-      <c r="G185" s="7" t="inlineStr">
+      <c r="G187" s="7" t="inlineStr">
         <is>
           <t>1.任意のログインユーザーで BookPolicy::create() を確認する</t>
         </is>
       </c>
-      <c r="H185" s="7" t="inlineStr">
+      <c r="H187" s="7" t="inlineStr">
         <is>
           <t>trueが返り、作成が許可される</t>
         </is>
       </c>
-      <c r="I185" s="7" t="inlineStr">
+      <c r="I187" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/BookAuthorization/BookAuthorizationTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="4" t="n"/>
-      <c r="B186" s="4" t="n"/>
-      <c r="C186" s="4" t="n"/>
-      <c r="D186" s="4" t="n"/>
-      <c r="E186" s="7" t="inlineStr">
-        <is>
-          <t>13-1-2</t>
-        </is>
-      </c>
-      <c r="F186" s="7" t="inlineStr">
-        <is>
-          <t>書籍の登録者本人は更新が許可される</t>
-        </is>
-      </c>
-      <c r="G186" s="7" t="inlineStr">
-        <is>
-          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
-        </is>
-      </c>
-      <c r="H186" s="7" t="inlineStr">
-        <is>
-          <t>trueが返る</t>
-        </is>
-      </c>
-      <c r="I186" s="4" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="4" t="n"/>
-      <c r="B187" s="4" t="n"/>
-      <c r="C187" s="4" t="n"/>
-      <c r="D187" s="4" t="n"/>
-      <c r="E187" s="7" t="inlineStr">
-        <is>
-          <t>13-1-3</t>
-        </is>
-      </c>
-      <c r="F187" s="7" t="inlineStr">
-        <is>
-          <t>書籍の登録者以外は更新が許可されない</t>
-        </is>
-      </c>
-      <c r="G187" s="7" t="inlineStr">
-        <is>
-          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
-        </is>
-      </c>
-      <c r="H187" s="7" t="inlineStr">
-        <is>
-          <t>falseが返る</t>
-        </is>
-      </c>
-      <c r="I187" s="4" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="4" t="n"/>
@@ -6343,17 +6343,17 @@
       <c r="D188" s="4" t="n"/>
       <c r="E188" s="7" t="inlineStr">
         <is>
-          <t>13-1-4</t>
+          <t>13-1-2</t>
         </is>
       </c>
       <c r="F188" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者本人は削除が許可される</t>
+          <t>書籍の登録者本人は更新が許可される</t>
         </is>
       </c>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
+          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H188" s="7" t="inlineStr">
@@ -6370,17 +6370,17 @@
       <c r="D189" s="4" t="n"/>
       <c r="E189" s="7" t="inlineStr">
         <is>
-          <t>13-1-5</t>
+          <t>13-1-3</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者以外は削除が許可されない</t>
+          <t>書籍の登録者以外は更新が許可されない</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
+          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H189" s="7" t="inlineStr">
@@ -6397,154 +6397,153 @@
       <c r="D190" s="4" t="n"/>
       <c r="E190" s="7" t="inlineStr">
         <is>
+          <t>13-1-4</t>
+        </is>
+      </c>
+      <c r="F190" s="7" t="inlineStr">
+        <is>
+          <t>書籍の登録者本人は削除が許可される</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="inlineStr">
+        <is>
+          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
+        </is>
+      </c>
+      <c r="H190" s="7" t="inlineStr">
+        <is>
+          <t>trueが返る</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="n"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n"/>
+      <c r="B191" s="4" t="n"/>
+      <c r="C191" s="4" t="n"/>
+      <c r="D191" s="4" t="n"/>
+      <c r="E191" s="7" t="inlineStr">
+        <is>
+          <t>13-1-5</t>
+        </is>
+      </c>
+      <c r="F191" s="7" t="inlineStr">
+        <is>
+          <t>書籍の登録者以外は削除が許可されない</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="inlineStr">
+        <is>
+          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
+        </is>
+      </c>
+      <c r="H191" s="7" t="inlineStr">
+        <is>
+          <t>falseが返る</t>
+        </is>
+      </c>
+      <c r="I191" s="4" t="n"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="n"/>
+      <c r="B192" s="4" t="n"/>
+      <c r="C192" s="4" t="n"/>
+      <c r="D192" s="4" t="n"/>
+      <c r="E192" s="7" t="inlineStr">
+        <is>
           <t>13-1-6</t>
         </is>
       </c>
-      <c r="F190" s="7" t="inlineStr">
+      <c r="F192" s="7" t="inlineStr">
         <is>
           <t>フォームを介さない直接のPUT/DELETEリクエストでも他人の書籍は操作できない</t>
         </is>
       </c>
-      <c r="G190" s="7" t="inlineStr">
+      <c r="G192" s="7" t="inlineStr">
         <is>
           <t>1.他人が登録した書籍に対して、直接PUT・DELETEリクエストを送信する</t>
         </is>
       </c>
-      <c r="H190" s="7" t="inlineStr">
+      <c r="H192" s="7" t="inlineStr">
         <is>
           <t>いずれも403Forbiddenになり、データは変更されない</t>
         </is>
       </c>
-      <c r="I190" s="4" t="n"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="5" t="n"/>
-      <c r="B191" s="5" t="n"/>
-      <c r="C191" s="5" t="n"/>
-      <c r="D191" s="5" t="n"/>
-      <c r="E191" s="7" t="inlineStr">
+      <c r="I192" s="4" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="5" t="n"/>
+      <c r="B193" s="5" t="n"/>
+      <c r="C193" s="5" t="n"/>
+      <c r="D193" s="5" t="n"/>
+      <c r="E193" s="7" t="inlineStr">
         <is>
           <t>13-1-7</t>
         </is>
       </c>
-      <c r="F191" s="7" t="inlineStr">
+      <c r="F193" s="7" t="inlineStr">
         <is>
           <t>他人の書籍に対して不正な入力を直接PUTしても、入力エラーではなく403になる</t>
         </is>
       </c>
-      <c r="G191" s="7" t="inlineStr">
+      <c r="G193" s="7" t="inlineStr">
         <is>
           <t>1.他人が登録した書籍に対して、タイトルを空にするなど不正な内容で、直接PUTリクエストを送信する</t>
         </is>
       </c>
-      <c r="H191" s="7" t="inlineStr">
+      <c r="H193" s="7" t="inlineStr">
         <is>
           <t>バリデーションエラーにはならず、403Forbiddenになる（入力チェックより先に権限が判定される）。データは変更されない</t>
         </is>
       </c>
-      <c r="I191" s="5" t="n"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="7" t="inlineStr">
+      <c r="I193" s="5" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B192" s="7" t="inlineStr">
+      <c r="B194" s="7" t="inlineStr">
         <is>
           <t>ISBN検索</t>
         </is>
       </c>
-      <c r="C192" s="7" t="inlineStr">
+      <c r="C194" s="7" t="inlineStr">
         <is>
           <t>14-1</t>
         </is>
       </c>
-      <c r="D192" s="7" t="inlineStr">
+      <c r="D194" s="7" t="inlineStr">
         <is>
           <t>ISBNからの書籍情報取得(外部API連携)</t>
         </is>
       </c>
-      <c r="E192" s="7" t="inlineStr">
+      <c r="E194" s="7" t="inlineStr">
         <is>
           <t>14-1-1</t>
         </is>
       </c>
-      <c r="F192" s="7" t="inlineStr">
+      <c r="F194" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、ISBN検索エンドポイントにアクセスできない</t>
         </is>
       </c>
-      <c r="G192" s="7" t="inlineStr">
+      <c r="G194" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態でGET /books/isbn/{isbn} にアクセスする</t>
         </is>
       </c>
-      <c r="H192" s="7" t="inlineStr">
+      <c r="H194" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I192" s="7" t="inlineStr">
+      <c r="I194" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Isbn/IsbnSearchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="4" t="n"/>
-      <c r="B193" s="4" t="n"/>
-      <c r="C193" s="4" t="n"/>
-      <c r="D193" s="4" t="n"/>
-      <c r="E193" s="7" t="inlineStr">
-        <is>
-          <t>14-1-2</t>
-        </is>
-      </c>
-      <c r="F193" s="7" t="inlineStr">
-        <is>
-          <t>ISBNが空(空白のみ)の場合、バリデーションエラーが返る</t>
-        </is>
-      </c>
-      <c r="G193" s="7" t="inlineStr">
-        <is>
-          <t>1.ログイン状態で、ISBN部分を半角スペースのみにしてGET /books/isbn/%20 にリクエストする
-※ISBN部分を完全に空にするとURLが /books/isbn となり、このルートに一致しないため空白で代用する</t>
-        </is>
-      </c>
-      <c r="H193" s="7" t="inlineStr">
-        <is>
-          <t>422が返り、「ISBNを入力してください」が返る</t>
-        </is>
-      </c>
-      <c r="I193" s="4" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="4" t="n"/>
-      <c r="B194" s="4" t="n"/>
-      <c r="C194" s="4" t="n"/>
-      <c r="D194" s="4" t="n"/>
-      <c r="E194" s="7" t="inlineStr">
-        <is>
-          <t>14-1-3</t>
-        </is>
-      </c>
-      <c r="F194" s="7" t="inlineStr">
-        <is>
-          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
-        </is>
-      </c>
-      <c r="G194" s="7" t="inlineStr">
-        <is>
-          <t>1.13桁でないISBNでリクエストする</t>
-        </is>
-      </c>
-      <c r="H194" s="7" t="inlineStr">
-        <is>
-          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
-        </is>
-      </c>
-      <c r="I194" s="4" t="n"/>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n"/>
@@ -6553,22 +6552,23 @@
       <c r="D195" s="4" t="n"/>
       <c r="E195" s="7" t="inlineStr">
         <is>
-          <t>14-1-4</t>
+          <t>14-1-2</t>
         </is>
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
-          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
+          <t>ISBNが空(空白のみ)の場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G195" s="7" t="inlineStr">
         <is>
-          <t>1.登録済みのISBNでリクエストする</t>
+          <t>1.ログイン状態で、ISBN部分を半角スペースのみにしてGET /books/isbn/%20 にリクエストする
+※ISBN部分を完全に空にするとURLが /books/isbn となり、このルートに一致しないため空白で代用する</t>
         </is>
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
+          <t>422が返り、「ISBNを入力してください」が返る</t>
         </is>
       </c>
       <c r="I195" s="4" t="n"/>
@@ -6580,23 +6580,22 @@
       <c r="D196" s="4" t="n"/>
       <c r="E196" s="7" t="inlineStr">
         <is>
-          <t>14-1-5</t>
+          <t>14-1-3</t>
         </is>
       </c>
       <c r="F196" s="7" t="inlineStr">
         <is>
-          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
+          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
-2.未登録ISBNでリクエストする</t>
+          <t>1.13桁でないISBNでリクエストする</t>
         </is>
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
-          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
+          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
         </is>
       </c>
       <c r="I196" s="4" t="n"/>
@@ -6608,155 +6607,156 @@
       <c r="D197" s="4" t="n"/>
       <c r="E197" s="7" t="inlineStr">
         <is>
+          <t>14-1-4</t>
+        </is>
+      </c>
+      <c r="F197" s="7" t="inlineStr">
+        <is>
+          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="inlineStr">
+        <is>
+          <t>1.登録済みのISBNでリクエストする</t>
+        </is>
+      </c>
+      <c r="H197" s="7" t="inlineStr">
+        <is>
+          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="n"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="n"/>
+      <c r="B198" s="4" t="n"/>
+      <c r="C198" s="4" t="n"/>
+      <c r="D198" s="4" t="n"/>
+      <c r="E198" s="7" t="inlineStr">
+        <is>
+          <t>14-1-5</t>
+        </is>
+      </c>
+      <c r="F198" s="7" t="inlineStr">
+        <is>
+          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="inlineStr">
+        <is>
+          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
+2.未登録ISBNでリクエストする</t>
+        </is>
+      </c>
+      <c r="H198" s="7" t="inlineStr">
+        <is>
+          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
+        </is>
+      </c>
+      <c r="I198" s="4" t="n"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="n"/>
+      <c r="B199" s="4" t="n"/>
+      <c r="C199" s="4" t="n"/>
+      <c r="D199" s="4" t="n"/>
+      <c r="E199" s="7" t="inlineStr">
+        <is>
           <t>14-1-6</t>
         </is>
       </c>
-      <c r="F197" s="7" t="inlineStr">
+      <c r="F199" s="7" t="inlineStr">
         <is>
           <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
         </is>
       </c>
-      <c r="G197" s="7" t="inlineStr">
+      <c r="G199" s="7" t="inlineStr">
         <is>
           <t>1.Http::fake()でitemsが空のレスポンスをモックする
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H197" s="7" t="inlineStr">
+      <c r="H199" s="7" t="inlineStr">
         <is>
           <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
         </is>
       </c>
-      <c r="I197" s="4" t="n"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="5" t="n"/>
-      <c r="B198" s="5" t="n"/>
-      <c r="C198" s="5" t="n"/>
-      <c r="D198" s="5" t="n"/>
-      <c r="E198" s="7" t="inlineStr">
+      <c r="I199" s="4" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="5" t="n"/>
+      <c r="B200" s="5" t="n"/>
+      <c r="C200" s="5" t="n"/>
+      <c r="D200" s="5" t="n"/>
+      <c r="E200" s="7" t="inlineStr">
         <is>
           <t>14-1-7</t>
         </is>
       </c>
-      <c r="F198" s="7" t="inlineStr">
+      <c r="F200" s="7" t="inlineStr">
         <is>
           <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
         </is>
       </c>
-      <c r="G198" s="7" t="inlineStr">
+      <c r="G200" s="7" t="inlineStr">
         <is>
           <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H198" s="7" t="inlineStr">
+      <c r="H200" s="7" t="inlineStr">
         <is>
           <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
         </is>
       </c>
-      <c r="I198" s="5" t="n"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="7" t="inlineStr">
+      <c r="I200" s="5" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B199" s="7" t="inlineStr">
+      <c r="B201" s="7" t="inlineStr">
         <is>
           <t>マイ読書レポート</t>
         </is>
       </c>
-      <c r="C199" s="7" t="inlineStr">
+      <c r="C201" s="7" t="inlineStr">
         <is>
           <t>15-1</t>
         </is>
       </c>
-      <c r="D199" s="7" t="inlineStr">
+      <c r="D201" s="7" t="inlineStr">
         <is>
           <t>読書統計の表示</t>
         </is>
       </c>
-      <c r="E199" s="7" t="inlineStr">
+      <c r="E201" s="7" t="inlineStr">
         <is>
           <t>15-1-1</t>
         </is>
       </c>
-      <c r="F199" s="7" t="inlineStr">
+      <c r="F201" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
         </is>
       </c>
-      <c r="G199" s="7" t="inlineStr">
+      <c r="G201" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で/reportsを開く</t>
         </is>
       </c>
-      <c r="H199" s="7" t="inlineStr">
+      <c r="H201" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I199" s="7" t="inlineStr">
+      <c r="I201" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Report/ReportTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="4" t="n"/>
-      <c r="B200" s="4" t="n"/>
-      <c r="C200" s="4" t="n"/>
-      <c r="D200" s="4" t="n"/>
-      <c r="E200" s="7" t="inlineStr">
-        <is>
-          <t>15-1-2</t>
-        </is>
-      </c>
-      <c r="F200" s="7" t="inlineStr">
-        <is>
-          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
-        </is>
-      </c>
-      <c r="G200" s="7" t="inlineStr">
-        <is>
-          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
-        </is>
-      </c>
-      <c r="H200" s="7" t="inlineStr">
-        <is>
-          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
-        </is>
-      </c>
-      <c r="I200" s="4" t="n"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="4" t="n"/>
-      <c r="B201" s="4" t="n"/>
-      <c r="C201" s="4" t="n"/>
-      <c r="D201" s="4" t="n"/>
-      <c r="E201" s="7" t="inlineStr">
-        <is>
-          <t>15-1-3</t>
-        </is>
-      </c>
-      <c r="F201" s="7" t="inlineStr">
-        <is>
-          <t>評価分布(★1〜★5)が正しく表示される</t>
-        </is>
-      </c>
-      <c r="G201" s="7" t="inlineStr">
-        <is>
-          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
-        </is>
-      </c>
-      <c r="H201" s="7" t="inlineStr">
-        <is>
-          <t>各評価の件数が実データと一致して表示される</t>
-        </is>
-      </c>
-      <c r="I201" s="4" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="4" t="n"/>
@@ -6765,22 +6765,22 @@
       <c r="D202" s="4" t="n"/>
       <c r="E202" s="7" t="inlineStr">
         <is>
-          <t>15-1-4</t>
+          <t>15-1-2</t>
         </is>
       </c>
       <c r="F202" s="7" t="inlineStr">
         <is>
-          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
+          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
         </is>
       </c>
       <c r="G202" s="7" t="inlineStr">
         <is>
-          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
+          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H202" s="7" t="inlineStr">
         <is>
-          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
+          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
         </is>
       </c>
       <c r="I202" s="4" t="n"/>
@@ -6792,285 +6792,283 @@
       <c r="D203" s="4" t="n"/>
       <c r="E203" s="7" t="inlineStr">
         <is>
+          <t>15-1-3</t>
+        </is>
+      </c>
+      <c r="F203" s="7" t="inlineStr">
+        <is>
+          <t>評価分布(★1〜★5)が正しく表示される</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="inlineStr">
+        <is>
+          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
+        </is>
+      </c>
+      <c r="H203" s="7" t="inlineStr">
+        <is>
+          <t>各評価の件数が実データと一致して表示される</t>
+        </is>
+      </c>
+      <c r="I203" s="4" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="n"/>
+      <c r="B204" s="4" t="n"/>
+      <c r="C204" s="4" t="n"/>
+      <c r="D204" s="4" t="n"/>
+      <c r="E204" s="7" t="inlineStr">
+        <is>
+          <t>15-1-4</t>
+        </is>
+      </c>
+      <c r="F204" s="7" t="inlineStr">
+        <is>
+          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="inlineStr">
+        <is>
+          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
+        </is>
+      </c>
+      <c r="H204" s="7" t="inlineStr">
+        <is>
+          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="n"/>
+      <c r="B205" s="4" t="n"/>
+      <c r="C205" s="4" t="n"/>
+      <c r="D205" s="4" t="n"/>
+      <c r="E205" s="7" t="inlineStr">
+        <is>
           <t>15-1-5</t>
         </is>
       </c>
-      <c r="F203" s="7" t="inlineStr">
+      <c r="F205" s="7" t="inlineStr">
         <is>
           <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
         </is>
       </c>
-      <c r="G203" s="7" t="inlineStr">
+      <c r="G205" s="7" t="inlineStr">
         <is>
           <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H203" s="7" t="inlineStr">
+      <c r="H205" s="7" t="inlineStr">
         <is>
           <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
         </is>
       </c>
-      <c r="I203" s="4" t="n"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="5" t="n"/>
-      <c r="B204" s="5" t="n"/>
-      <c r="C204" s="5" t="n"/>
-      <c r="D204" s="5" t="n"/>
-      <c r="E204" s="7" t="inlineStr">
+      <c r="I205" s="4" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="5" t="n"/>
+      <c r="B206" s="5" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="5" t="n"/>
+      <c r="E206" s="7" t="inlineStr">
         <is>
           <t>15-1-6</t>
         </is>
       </c>
-      <c r="F204" s="7" t="inlineStr">
+      <c r="F206" s="7" t="inlineStr">
         <is>
           <t>レビューを1件も投稿していない場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G204" s="7" t="inlineStr">
+      <c r="G206" s="7" t="inlineStr">
         <is>
           <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H204" s="7" t="inlineStr">
+      <c r="H206" s="7" t="inlineStr">
         <is>
           <t>総レビュー数・読了冊数が0（平均評価の集計値は0で、画面上は「-」と表示）となり、TOP5一覧には「4星以上の書籍がありません」「ジャンルが設定された書籍のレビューがありません」と表示される</t>
         </is>
       </c>
-      <c r="I204" s="5" t="n"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="7" t="inlineStr">
+      <c r="I206" s="5" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B205" s="7" t="inlineStr">
+      <c r="B207" s="7" t="inlineStr">
         <is>
           <t>Sanctum認証</t>
         </is>
       </c>
-      <c r="C205" s="7" t="inlineStr">
+      <c r="C207" s="7" t="inlineStr">
         <is>
           <t>16-1</t>
         </is>
       </c>
-      <c r="D205" s="7" t="inlineStr">
+      <c r="D207" s="7" t="inlineStr">
         <is>
           <t>APIトークン認証</t>
         </is>
       </c>
-      <c r="E205" s="7" t="inlineStr">
+      <c r="E207" s="7" t="inlineStr">
         <is>
           <t>16-1-1</t>
         </is>
       </c>
-      <c r="F205" s="7" t="inlineStr">
+      <c r="F207" s="7" t="inlineStr">
         <is>
           <t>有効なpersonal access tokenを付与すると/api/userにアクセスできる</t>
         </is>
       </c>
-      <c r="G205" s="7" t="inlineStr">
+      <c r="G207" s="7" t="inlineStr">
         <is>
           <t>1.$user-&gt;createToken()でトークンを発行する
 2.Authorization: Bearer {token}を付与してGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H205" s="7" t="inlineStr">
+      <c r="H207" s="7" t="inlineStr">
         <is>
           <t>200が返り、対象ユーザーの情報が返る</t>
         </is>
       </c>
-      <c r="I205" s="7" t="inlineStr">
+      <c r="I207" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="4" t="n"/>
-      <c r="B206" s="4" t="n"/>
-      <c r="C206" s="4" t="n"/>
-      <c r="D206" s="4" t="n"/>
-      <c r="E206" s="7" t="inlineStr">
+    <row r="208">
+      <c r="A208" s="4" t="n"/>
+      <c r="B208" s="4" t="n"/>
+      <c r="C208" s="4" t="n"/>
+      <c r="D208" s="4" t="n"/>
+      <c r="E208" s="7" t="inlineStr">
         <is>
           <t>16-1-2</t>
         </is>
       </c>
-      <c r="F206" s="7" t="inlineStr">
+      <c r="F208" s="7" t="inlineStr">
         <is>
           <t>トークンなしでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G206" s="7" t="inlineStr">
+      <c r="G208" s="7" t="inlineStr">
         <is>
           <t>1.Authorizationヘッダーを付与せずにGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H206" s="7" t="inlineStr">
+      <c r="H208" s="7" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
         </is>
       </c>
-      <c r="I206" s="4" t="n"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="4" t="n"/>
-      <c r="B207" s="4" t="n"/>
-      <c r="C207" s="4" t="n"/>
-      <c r="D207" s="4" t="n"/>
-      <c r="E207" s="7" t="inlineStr">
+      <c r="I208" s="4" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="n"/>
+      <c r="B209" s="4" t="n"/>
+      <c r="C209" s="4" t="n"/>
+      <c r="D209" s="4" t="n"/>
+      <c r="E209" s="7" t="inlineStr">
         <is>
           <t>16-1-3</t>
         </is>
       </c>
-      <c r="F207" s="7" t="inlineStr">
+      <c r="F209" s="7" t="inlineStr">
         <is>
           <t>不正な(存在しない)トークンでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G207" s="7" t="inlineStr">
+      <c r="G209" s="7" t="inlineStr">
         <is>
           <t>1.ランダムな文字列をBearerトークンとして付与しGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H207" s="7" t="inlineStr">
+      <c r="H209" s="7" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
         </is>
       </c>
-      <c r="I207" s="4" t="n"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="5" t="n"/>
-      <c r="B208" s="5" t="n"/>
-      <c r="C208" s="5" t="n"/>
-      <c r="D208" s="5" t="n"/>
-      <c r="E208" s="7" t="inlineStr">
+      <c r="I209" s="4" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="n"/>
+      <c r="B210" s="5" t="n"/>
+      <c r="C210" s="5" t="n"/>
+      <c r="D210" s="5" t="n"/>
+      <c r="E210" s="7" t="inlineStr">
         <is>
           <t>16-1-4</t>
         </is>
       </c>
-      <c r="F208" s="7" t="inlineStr">
+      <c r="F210" s="7" t="inlineStr">
         <is>
           <t>削除済み(失効済み)のトークンでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G208" s="7" t="inlineStr">
+      <c r="G210" s="7" t="inlineStr">
         <is>
           <t>1.発行済みトークンを削除する
 2.そのトークンでGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H208" s="7" t="inlineStr">
+      <c r="H210" s="7" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
         </is>
       </c>
-      <c r="I208" s="5" t="n"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="7" t="inlineStr">
+      <c r="I210" s="5" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B209" s="7" t="inlineStr">
+      <c r="B211" s="7" t="inlineStr">
         <is>
           <t>読書計画</t>
         </is>
       </c>
-      <c r="C209" s="7" t="inlineStr">
+      <c r="C211" s="7" t="inlineStr">
         <is>
           <t>17-1</t>
         </is>
       </c>
-      <c r="D209" s="7" t="inlineStr">
+      <c r="D211" s="7" t="inlineStr">
         <is>
           <t>読書計画の作成・一覧・読了・削除</t>
         </is>
       </c>
-      <c r="E209" s="7" t="inlineStr">
+      <c r="E211" s="7" t="inlineStr">
         <is>
           <t>17-1-1</t>
         </is>
       </c>
-      <c r="F209" s="7" t="inlineStr">
+      <c r="F211" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
         </is>
       </c>
-      <c r="G209" s="7" t="inlineStr">
+      <c r="G211" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H209" s="7" t="inlineStr">
+      <c r="H211" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I209" s="7" t="inlineStr">
+      <c r="I211" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="4" t="n"/>
-      <c r="B210" s="4" t="n"/>
-      <c r="C210" s="4" t="n"/>
-      <c r="D210" s="4" t="n"/>
-      <c r="E210" s="7" t="inlineStr">
-        <is>
-          <t>17-1-2</t>
-        </is>
-      </c>
-      <c r="F210" s="7" t="inlineStr">
-        <is>
-          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
-        </is>
-      </c>
-      <c r="G210" s="7" t="inlineStr">
-        <is>
-          <t>1.自分と他人の読書計画をそれぞれ用意する
-2.読書計画一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H210" s="7" t="inlineStr">
-        <is>
-          <t>自分の計画のみが、target_dateの昇順で表示される</t>
-        </is>
-      </c>
-      <c r="I210" s="4" t="n"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="4" t="n"/>
-      <c r="B211" s="4" t="n"/>
-      <c r="C211" s="4" t="n"/>
-      <c r="D211" s="4" t="n"/>
-      <c r="E211" s="7" t="inlineStr">
-        <is>
-          <t>17-1-3</t>
-        </is>
-      </c>
-      <c r="F211" s="7" t="inlineStr">
-        <is>
-          <t>ステータスで絞り込んで表示できる</t>
-        </is>
-      </c>
-      <c r="G211" s="7" t="inlineStr">
-        <is>
-          <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
-2.statusパラメータを指定して一覧を開く</t>
-        </is>
-      </c>
-      <c r="H211" s="7" t="inlineStr">
-        <is>
-          <t>指定したステータスの計画のみ表示される</t>
-        </is>
-      </c>
-      <c r="I211" s="4" t="n"/>
     </row>
     <row r="212">
       <c r="A212" s="4" t="n"/>
@@ -7079,23 +7077,23 @@
       <c r="D212" s="4" t="n"/>
       <c r="E212" s="7" t="inlineStr">
         <is>
-          <t>17-1-4</t>
+          <t>17-1-2</t>
         </is>
       </c>
       <c r="F212" s="7" t="inlineStr">
         <is>
-          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
+          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
         </is>
       </c>
       <c r="G212" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍について進行中の計画を作成する
-2.計画作成ページを開く</t>
+          <t>1.自分と他人の読書計画をそれぞれ用意する
+2.読書計画一覧ページを開く</t>
         </is>
       </c>
       <c r="H212" s="7" t="inlineStr">
         <is>
-          <t>書籍選択肢にその書籍が表示されない</t>
+          <t>自分の計画のみが、target_dateの昇順で表示される</t>
         </is>
       </c>
       <c r="I212" s="4" t="n"/>
@@ -7107,22 +7105,23 @@
       <c r="D213" s="4" t="n"/>
       <c r="E213" s="7" t="inlineStr">
         <is>
-          <t>17-1-5</t>
+          <t>17-1-3</t>
         </is>
       </c>
       <c r="F213" s="7" t="inlineStr">
         <is>
-          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
+          <t>ステータスで絞り込んで表示できる</t>
         </is>
       </c>
       <c r="G213" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
+          <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
+2.statusパラメータを指定して一覧を開く</t>
         </is>
       </c>
       <c r="H213" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、計画は作成されない</t>
+          <t>指定したステータスの計画のみ表示される</t>
         </is>
       </c>
       <c r="I213" s="4" t="n"/>
@@ -7134,23 +7133,23 @@
       <c r="D214" s="4" t="n"/>
       <c r="E214" s="7" t="inlineStr">
         <is>
-          <t>17-1-6</t>
+          <t>17-1-4</t>
         </is>
       </c>
       <c r="F214" s="7" t="inlineStr">
         <is>
-          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
+          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
         </is>
       </c>
       <c r="G214" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を読了(完了)状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.ある書籍について進行中の計画を作成する
+2.計画作成ページを開く</t>
         </is>
       </c>
       <c r="H214" s="7" t="inlineStr">
         <is>
-          <t>新しい計画が作成される</t>
+          <t>書籍選択肢にその書籍が表示されない</t>
         </is>
       </c>
       <c r="I214" s="4" t="n"/>
@@ -7162,23 +7161,22 @@
       <c r="D215" s="4" t="n"/>
       <c r="E215" s="7" t="inlineStr">
         <is>
-          <t>17-1-7</t>
+          <t>17-1-5</t>
         </is>
       </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
         </is>
       </c>
       <c r="G215" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.期日を入力せずに登録する</t>
+          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>403Forbiddenになり、計画は作成されない</t>
         </is>
       </c>
       <c r="I215" s="4" t="n"/>
@@ -7190,23 +7188,23 @@
       <c r="D216" s="4" t="n"/>
       <c r="E216" s="7" t="inlineStr">
         <is>
-          <t>17-1-8</t>
+          <t>17-1-6</t>
         </is>
       </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
         </is>
       </c>
       <c r="G216" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.過去の日付を期日に指定して登録する</t>
+          <t>1.ある書籍の計画を読了(完了)状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>新しい計画が作成される</t>
         </is>
       </c>
       <c r="I216" s="4" t="n"/>
@@ -7218,23 +7216,23 @@
       <c r="D217" s="4" t="n"/>
       <c r="E217" s="7" t="inlineStr">
         <is>
-          <t>17-1-9</t>
+          <t>17-1-7</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G217" s="7" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
-2.書籍・期日を正しく入力して登録する</t>
+2.期日を入力せずに登録する</t>
         </is>
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I217" s="4" t="n"/>
@@ -7246,22 +7244,23 @@
       <c r="D218" s="4" t="n"/>
       <c r="E218" s="7" t="inlineStr">
         <is>
-          <t>17-1-10</t>
+          <t>17-1-8</t>
         </is>
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画に対して読了操作を行う</t>
+          <t>1.計画作成ページを開く
+2.過去の日付を期日に指定して登録する</t>
         </is>
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I218" s="4" t="n"/>
@@ -7273,22 +7272,23 @@
       <c r="D219" s="4" t="n"/>
       <c r="E219" s="7" t="inlineStr">
         <is>
-          <t>17-1-11</t>
+          <t>17-1-9</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画は読了・削除できない</t>
+          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
         </is>
       </c>
       <c r="G219" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+          <t>1.計画作成ページを開く
+2.書籍・期日を正しく入力して登録する</t>
         </is>
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>いずれも403Forbiddenになる</t>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
         </is>
       </c>
       <c r="I219" s="4" t="n"/>
@@ -7300,22 +7300,22 @@
       <c r="D220" s="4" t="n"/>
       <c r="E220" s="7" t="inlineStr">
         <is>
-          <t>17-1-12</t>
+          <t>17-1-10</t>
         </is>
       </c>
       <c r="F220" s="7" t="inlineStr">
         <is>
-          <t>自分が作成した読書計画は削除できる</t>
+          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
         </is>
       </c>
       <c r="G220" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の削除ボタンを押す</t>
+          <t>1.進行中の計画に対して読了操作を行う</t>
         </is>
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
-          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
+          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
         </is>
       </c>
       <c r="I220" s="4" t="n"/>
@@ -7325,25 +7325,24 @@
       <c r="B221" s="4" t="n"/>
       <c r="C221" s="4" t="n"/>
       <c r="D221" s="4" t="n"/>
-      <c r="E221" s="9" t="inlineStr">
-        <is>
-          <t>17-1-13</t>
-        </is>
-      </c>
-      <c r="F221" s="9" t="inlineStr">
-        <is>
-          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
-        </is>
-      </c>
-      <c r="G221" s="9" t="inlineStr">
-        <is>
-          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
-2.その読書計画を削除する</t>
-        </is>
-      </c>
-      <c r="H221" s="9" t="inlineStr">
-        <is>
-          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
+      <c r="E221" s="7" t="inlineStr">
+        <is>
+          <t>17-1-11</t>
+        </is>
+      </c>
+      <c r="F221" s="7" t="inlineStr">
+        <is>
+          <t>他人が作成した読書計画は読了・削除できない</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="inlineStr">
+        <is>
+          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+        </is>
+      </c>
+      <c r="H221" s="7" t="inlineStr">
+        <is>
+          <t>いずれも403Forbiddenになる</t>
         </is>
       </c>
       <c r="I221" s="4" t="n"/>
@@ -7353,24 +7352,24 @@
       <c r="B222" s="4" t="n"/>
       <c r="C222" s="4" t="n"/>
       <c r="D222" s="4" t="n"/>
-      <c r="E222" s="9" t="inlineStr">
-        <is>
-          <t>17-1-14</t>
-        </is>
-      </c>
-      <c r="F222" s="9" t="inlineStr">
-        <is>
-          <t>ステータスが「完了」の計画は、読了操作を行えない</t>
-        </is>
-      </c>
-      <c r="G222" s="9" t="inlineStr">
-        <is>
-          <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H222" s="9" t="inlineStr">
-        <is>
-          <t>403Forbiddenになり、completed_atは変更されない</t>
+      <c r="E222" s="7" t="inlineStr">
+        <is>
+          <t>17-1-12</t>
+        </is>
+      </c>
+      <c r="F222" s="7" t="inlineStr">
+        <is>
+          <t>自分が作成した読書計画は削除できる</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="inlineStr">
+        <is>
+          <t>1.自分が作成した計画の削除ボタンを押す</t>
+        </is>
+      </c>
+      <c r="H222" s="7" t="inlineStr">
+        <is>
+          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
         </is>
       </c>
       <c r="I222" s="4" t="n"/>
@@ -7382,23 +7381,23 @@
       <c r="D223" s="4" t="n"/>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>17-1-15</t>
+          <t>17-1-13</t>
         </is>
       </c>
       <c r="F223" s="9" t="inlineStr">
         <is>
-          <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
+          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
         </is>
       </c>
       <c r="G223" s="9" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を「期限切れ」の状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
+2.その読書計画を削除する</t>
         </is>
       </c>
       <c r="H223" s="9" t="inlineStr">
         <is>
-          <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
+          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
         </is>
       </c>
       <c r="I223" s="4" t="n"/>
@@ -7410,23 +7409,22 @@
       <c r="D224" s="4" t="n"/>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>17-1-16</t>
+          <t>17-1-14</t>
         </is>
       </c>
       <c r="F224" s="9" t="inlineStr">
         <is>
-          <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
+          <t>ステータスが「完了」の計画は、読了操作を行えない</t>
         </is>
       </c>
       <c r="G224" s="9" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍を選択せずに期日を入力して登録する</t>
+          <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
         </is>
       </c>
       <c r="H224" s="9" t="inlineStr">
         <is>
-          <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
+          <t>403Forbiddenになり、completed_atは変更されない</t>
         </is>
       </c>
       <c r="I224" s="4" t="n"/>
@@ -7438,22 +7436,23 @@
       <c r="D225" s="4" t="n"/>
       <c r="E225" s="9" t="inlineStr">
         <is>
-          <t>17-1-17</t>
+          <t>17-1-15</t>
         </is>
       </c>
       <c r="F225" s="9" t="inlineStr">
         <is>
-          <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
+          <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
         </is>
       </c>
       <c r="G225" s="9" t="inlineStr">
         <is>
-          <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.ある書籍の計画を「期限切れ」の状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H225" s="9" t="inlineStr">
         <is>
-          <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
+          <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
         </is>
       </c>
       <c r="I225" s="4" t="n"/>
@@ -7465,22 +7464,23 @@
       <c r="D226" s="4" t="n"/>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>17-1-18</t>
+          <t>17-1-16</t>
         </is>
       </c>
       <c r="F226" s="9" t="inlineStr">
         <is>
-          <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
+          <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G226" s="9" t="inlineStr">
         <is>
-          <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.計画作成ページを開く
+2.書籍を選択せずに期日を入力して登録する</t>
         </is>
       </c>
       <c r="H226" s="9" t="inlineStr">
         <is>
-          <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
+          <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I226" s="4" t="n"/>
@@ -7492,182 +7492,181 @@
       <c r="D227" s="4" t="n"/>
       <c r="E227" s="9" t="inlineStr">
         <is>
+          <t>17-1-17</t>
+        </is>
+      </c>
+      <c r="F227" s="9" t="inlineStr">
+        <is>
+          <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="G227" s="9" t="inlineStr">
+        <is>
+          <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H227" s="9" t="inlineStr">
+        <is>
+          <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I227" s="4" t="n"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="n"/>
+      <c r="B228" s="4" t="n"/>
+      <c r="C228" s="4" t="n"/>
+      <c r="D228" s="4" t="n"/>
+      <c r="E228" s="9" t="inlineStr">
+        <is>
+          <t>17-1-18</t>
+        </is>
+      </c>
+      <c r="F228" s="9" t="inlineStr">
+        <is>
+          <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="G228" s="9" t="inlineStr">
+        <is>
+          <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H228" s="9" t="inlineStr">
+        <is>
+          <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I228" s="4" t="n"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="n"/>
+      <c r="B229" s="4" t="n"/>
+      <c r="C229" s="4" t="n"/>
+      <c r="D229" s="4" t="n"/>
+      <c r="E229" s="9" t="inlineStr">
+        <is>
           <t>17-1-19</t>
         </is>
       </c>
-      <c r="F227" s="9" t="inlineStr">
+      <c r="F229" s="9" t="inlineStr">
         <is>
           <t>期日が日付形式でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G227" s="9" t="inlineStr">
+      <c r="G229" s="9" t="inlineStr">
         <is>
           <t>1.書籍と、日付として不正な期日(例:abc)を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H227" s="9" t="inlineStr">
+      <c r="H229" s="9" t="inlineStr">
         <is>
           <t>「正しい日付を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I227" s="4" t="n"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="5" t="n"/>
-      <c r="B228" s="5" t="n"/>
-      <c r="C228" s="5" t="n"/>
-      <c r="D228" s="5" t="n"/>
-      <c r="E228" s="9" t="inlineStr">
-        <is>
-          <t>17-1-20</t>
-        </is>
-      </c>
-      <c r="F228" s="9" t="inlineStr">
-        <is>
-          <t>期日に今日の日付を指定した場合、計画を作成できる</t>
-        </is>
-      </c>
-      <c r="G228" s="9" t="inlineStr">
-        <is>
-          <t>1.計画作成ページを開く
-2.書籍を選択し、期日に今日の日付を指定して登録する</t>
-        </is>
-      </c>
-      <c r="H228" s="9" t="inlineStr">
-        <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される（今日の日付は指定可能）</t>
-        </is>
-      </c>
-      <c r="I228" s="5" t="n"/>
-    </row>
-    <row r="229">
-      <c r="A229" s="7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B229" s="7" t="inlineStr">
-        <is>
-          <t>読書計画（期限変更）</t>
-        </is>
-      </c>
-      <c r="C229" s="7" t="inlineStr">
-        <is>
-          <t>18-1</t>
-        </is>
-      </c>
-      <c r="D229" s="7" t="inlineStr">
-        <is>
-          <t>読書計画の期日変更</t>
-        </is>
-      </c>
-      <c r="E229" s="7" t="inlineStr">
-        <is>
-          <t>18-1-1</t>
-        </is>
-      </c>
-      <c r="F229" s="7" t="inlineStr">
-        <is>
-          <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
-        </is>
-      </c>
-      <c r="G229" s="7" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
-        </is>
-      </c>
-      <c r="H229" s="7" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I229" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
-        </is>
-      </c>
+      <c r="I229" s="4" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="4" t="n"/>
       <c r="B230" s="4" t="n"/>
       <c r="C230" s="4" t="n"/>
       <c r="D230" s="4" t="n"/>
-      <c r="E230" s="7" t="inlineStr">
-        <is>
-          <t>18-1-2</t>
-        </is>
-      </c>
-      <c r="F230" s="7" t="inlineStr">
-        <is>
-          <t>他人が作成した読書計画の期日は変更できない</t>
-        </is>
-      </c>
-      <c r="G230" s="7" t="inlineStr">
-        <is>
-          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H230" s="7" t="inlineStr">
-        <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
+      <c r="E230" s="9" t="inlineStr">
+        <is>
+          <t>17-1-20</t>
+        </is>
+      </c>
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>期日に今日の日付を指定した場合、計画を作成できる</t>
+        </is>
+      </c>
+      <c r="G230" s="9" t="inlineStr">
+        <is>
+          <t>1.計画作成ページを開く
+2.書籍を選択し、期日に今日の日付を指定して登録する</t>
+        </is>
+      </c>
+      <c r="H230" s="9" t="inlineStr">
+        <is>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される（今日の日付は指定可能）</t>
         </is>
       </c>
       <c r="I230" s="4" t="n"/>
     </row>
     <row r="231">
-      <c r="A231" s="4" t="n"/>
-      <c r="B231" s="4" t="n"/>
-      <c r="C231" s="4" t="n"/>
-      <c r="D231" s="4" t="n"/>
-      <c r="E231" s="7" t="inlineStr">
-        <is>
-          <t>18-1-3</t>
-        </is>
-      </c>
-      <c r="F231" s="7" t="inlineStr">
-        <is>
-          <t>編集画面を開くと現在の期日が初期表示される</t>
-        </is>
-      </c>
-      <c r="G231" s="7" t="inlineStr">
-        <is>
-          <t>1.自分が作成した計画の編集ページを開く</t>
-        </is>
-      </c>
-      <c r="H231" s="7" t="inlineStr">
-        <is>
-          <t>現在登録されている期日が入力欄に表示される</t>
-        </is>
-      </c>
-      <c r="I231" s="4" t="n"/>
+      <c r="A231" s="5" t="n"/>
+      <c r="B231" s="5" t="n"/>
+      <c r="C231" s="5" t="n"/>
+      <c r="D231" s="5" t="n"/>
+      <c r="E231" s="9" t="inlineStr">
+        <is>
+          <t>17-1-21</t>
+        </is>
+      </c>
+      <c r="F231" s="9" t="inlineStr">
+        <is>
+          <t>同じ書籍に進行中の計画がある状態で不正な期日を指定しても、入力エラーではなく403になる</t>
+        </is>
+      </c>
+      <c r="G231" s="9" t="inlineStr">
+        <is>
+          <t>1.進行中の計画がある書籍を指定し、期日を空にして直接計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H231" s="9" t="inlineStr">
+        <is>
+          <t>バリデーションエラーではなく403Forbiddenになり、計画は作成されない（認可チェックが入力チェックより先に行われる）</t>
+        </is>
+      </c>
+      <c r="I231" s="5" t="n"/>
     </row>
     <row r="232">
-      <c r="A232" s="4" t="n"/>
-      <c r="B232" s="4" t="n"/>
-      <c r="C232" s="4" t="n"/>
-      <c r="D232" s="4" t="n"/>
+      <c r="A232" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B232" s="7" t="inlineStr">
+        <is>
+          <t>読書計画（期限変更）</t>
+        </is>
+      </c>
+      <c r="C232" s="7" t="inlineStr">
+        <is>
+          <t>18-1</t>
+        </is>
+      </c>
+      <c r="D232" s="7" t="inlineStr">
+        <is>
+          <t>読書計画の期日変更</t>
+        </is>
+      </c>
       <c r="E232" s="7" t="inlineStr">
         <is>
-          <t>18-1-4</t>
+          <t>18-1-1</t>
         </is>
       </c>
       <c r="F232" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
         </is>
       </c>
       <c r="G232" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.期日を空にして更新する</t>
+          <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H232" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I232" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I232" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="4" t="n"/>
@@ -7676,23 +7675,22 @@
       <c r="D233" s="4" t="n"/>
       <c r="E233" s="7" t="inlineStr">
         <is>
-          <t>18-1-5</t>
+          <t>18-1-2</t>
         </is>
       </c>
       <c r="F233" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>他人が作成した読書計画の期日は変更できない</t>
         </is>
       </c>
       <c r="G233" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.過去の日付に変更して更新する</t>
+          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H233" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
       <c r="I233" s="4" t="n"/>
@@ -7704,23 +7702,22 @@
       <c r="D234" s="4" t="n"/>
       <c r="E234" s="7" t="inlineStr">
         <is>
-          <t>18-1-6</t>
+          <t>18-1-3</t>
         </is>
       </c>
       <c r="F234" s="7" t="inlineStr">
         <is>
-          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
+          <t>編集画面を開くと現在の期日が初期表示される</t>
         </is>
       </c>
       <c r="G234" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.未来の日付に正しく変更して更新する</t>
+          <t>1.自分が作成した計画の編集ページを開く</t>
         </is>
       </c>
       <c r="H234" s="7" t="inlineStr">
         <is>
-          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
+          <t>現在登録されている期日が入力欄に表示される</t>
         </is>
       </c>
       <c r="I234" s="4" t="n"/>
@@ -7732,23 +7729,23 @@
       <c r="D235" s="4" t="n"/>
       <c r="E235" s="7" t="inlineStr">
         <is>
-          <t>18-1-7</t>
+          <t>18-1-4</t>
         </is>
       </c>
       <c r="F235" s="7" t="inlineStr">
         <is>
-          <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G235" s="7" t="inlineStr">
         <is>
-          <t>1.期日が過去で「進行中」の計画を用意する
-2.読書計画一覧または編集ページを開く</t>
+          <t>1.編集ページを開く
+2.期日を空にして更新する</t>
         </is>
       </c>
       <c r="H235" s="7" t="inlineStr">
         <is>
-          <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I235" s="4" t="n"/>
@@ -7760,22 +7757,23 @@
       <c r="D236" s="4" t="n"/>
       <c r="E236" s="7" t="inlineStr">
         <is>
-          <t>18-1-8</t>
+          <t>18-1-5</t>
         </is>
       </c>
       <c r="F236" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は期日を変更できない</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G236" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
+          <t>1.編集ページを開く
+2.過去の日付に変更して更新する</t>
         </is>
       </c>
       <c r="H236" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I236" s="4" t="n"/>
@@ -7787,22 +7785,23 @@
       <c r="D237" s="4" t="n"/>
       <c r="E237" s="7" t="inlineStr">
         <is>
-          <t>18-1-9</t>
+          <t>18-1-6</t>
         </is>
       </c>
       <c r="F237" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
+          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
         </is>
       </c>
       <c r="G237" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
+          <t>1.編集ページを開く
+2.未来の日付に正しく変更して更新する</t>
         </is>
       </c>
       <c r="H237" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、編集ページは表示されない</t>
+          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
         </is>
       </c>
       <c r="I237" s="4" t="n"/>
@@ -7814,102 +7813,80 @@
       <c r="D238" s="4" t="n"/>
       <c r="E238" s="7" t="inlineStr">
         <is>
-          <t>18-1-10</t>
+          <t>18-1-7</t>
         </is>
       </c>
       <c r="F238" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画の編集ページにはアクセスできない</t>
+          <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
         </is>
       </c>
       <c r="G238" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画の編集ページのURLに直接アクセスする</t>
+          <t>1.期日が過去で「進行中」の計画を用意する
+2.読書計画一覧または編集ページを開く</t>
         </is>
       </c>
       <c r="H238" s="7" t="inlineStr">
         <is>
+          <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
+        </is>
+      </c>
+      <c r="I238" s="4" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="n"/>
+      <c r="B239" s="4" t="n"/>
+      <c r="C239" s="4" t="n"/>
+      <c r="D239" s="4" t="n"/>
+      <c r="E239" s="7" t="inlineStr">
+        <is>
+          <t>18-1-8</t>
+        </is>
+      </c>
+      <c r="F239" s="7" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」の計画は期日を変更できない</t>
+        </is>
+      </c>
+      <c r="G239" s="7" t="inlineStr">
+        <is>
+          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H239" s="7" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、期日は変更されない</t>
+        </is>
+      </c>
+      <c r="I239" s="4" t="n"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="n"/>
+      <c r="B240" s="4" t="n"/>
+      <c r="C240" s="4" t="n"/>
+      <c r="D240" s="4" t="n"/>
+      <c r="E240" s="7" t="inlineStr">
+        <is>
+          <t>18-1-9</t>
+        </is>
+      </c>
+      <c r="F240" s="7" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
+        </is>
+      </c>
+      <c r="G240" s="7" t="inlineStr">
+        <is>
+          <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
+        </is>
+      </c>
+      <c r="H240" s="7" t="inlineStr">
+        <is>
           <t>403Forbiddenになり、編集ページは表示されない</t>
         </is>
       </c>
-      <c r="I238" s="4" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="5" t="n"/>
-      <c r="B239" s="5" t="n"/>
-      <c r="C239" s="5" t="n"/>
-      <c r="D239" s="5" t="n"/>
-      <c r="E239" s="7" t="inlineStr">
-        <is>
-          <t>18-1-11</t>
-        </is>
-      </c>
-      <c r="F239" s="7" t="inlineStr">
-        <is>
-          <t>同じ書籍に「進行中」の計画がある場合、「期限切れ」の計画は編集・更新できない</t>
-        </is>
-      </c>
-      <c r="G239" s="7" t="inlineStr">
-        <is>
-          <t>1.同じ書籍について、「期限切れ」の計画と「進行中」の計画をそれぞれ用意する
-2.「期限切れ」の計画の編集ページのURLに直接アクセスする
-3.「期限切れ」の計画に対して、直接更新リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H239" s="7" t="inlineStr">
-        <is>
-          <t>いずれも403Forbiddenになり、「期限切れ」の計画のステータス・期日は変更されない（同じ書籍の「進行中」の計画が2件になることを防ぐ）</t>
-        </is>
-      </c>
-      <c r="I239" s="5" t="n"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B240" s="7" t="inlineStr">
-        <is>
-          <t>リマインダーバッチ</t>
-        </is>
-      </c>
-      <c r="C240" s="7" t="inlineStr">
-        <is>
-          <t>19-1</t>
-        </is>
-      </c>
-      <c r="D240" s="7" t="inlineStr">
-        <is>
-          <t>日次バッチ(reading-plans:daily)によるリマインダー通知</t>
-        </is>
-      </c>
-      <c r="E240" s="7" t="inlineStr">
-        <is>
-          <t>19-1-1</t>
-        </is>
-      </c>
-      <c r="F240" s="7" t="inlineStr">
-        <is>
-          <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
-        </is>
-      </c>
-      <c r="G240" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが3日後・ステータス進行中の計画を用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
-        </is>
-      </c>
-      <c r="H240" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_before)・title(「読書期限のお知らせ」)・body(「「(書籍名)」の読書期限まであと3日です。」)が含まれる</t>
-        </is>
-      </c>
-      <c r="I240" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
-        </is>
-      </c>
+      <c r="I240" s="4" t="n"/>
     </row>
     <row r="241">
       <c r="A241" s="4" t="n"/>
@@ -7918,23 +7895,22 @@
       <c r="D241" s="4" t="n"/>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>19-1-2</t>
+          <t>18-1-10</t>
         </is>
       </c>
       <c r="F241" s="7" t="inlineStr">
         <is>
-          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
+          <t>他人が作成した読書計画の編集ページにはアクセスできない</t>
         </is>
       </c>
       <c r="G241" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが本日・ステータス進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
+          <t>1.他人が作成した計画の編集ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H241" s="7" t="inlineStr">
         <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される。通知のdataには、plan_id・book_title・timing(on_due_date)・title(「読書期限当日のお知らせ」)・body(「「(書籍名)」の読書期限は本日までです。」)が含まれる</t>
+          <t>403Forbiddenになり、編集ページは表示されない</t>
         </is>
       </c>
       <c r="I241" s="4" t="n"/>
@@ -7946,130 +7922,130 @@
       <c r="D242" s="4" t="n"/>
       <c r="E242" s="7" t="inlineStr">
         <is>
-          <t>19-1-3</t>
+          <t>18-1-11</t>
         </is>
       </c>
       <c r="F242" s="7" t="inlineStr">
         <is>
-          <t>期限切れから3日後の計画に再エンゲージメント通知が送信される</t>
+          <t>同じ書籍に「進行中」の計画がある場合、「期限切れ」の計画は編集・更新できない</t>
         </is>
       </c>
       <c r="G242" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが3日前・ステータス期限切れの計画を用意する
+          <t>1.同じ書籍について、「期限切れ」の計画と「進行中」の計画をそれぞれ用意する
+2.「期限切れ」の計画の編集ページのURLに直接アクセスする
+3.「期限切れ」の計画に対して、直接更新リクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H242" s="7" t="inlineStr">
+        <is>
+          <t>いずれも403Forbiddenになり、「期限切れ」の計画のステータス・期日は変更されない（同じ書籍の「進行中」の計画が2件になることを防ぐ）</t>
+        </is>
+      </c>
+      <c r="I242" s="4" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="5" t="n"/>
+      <c r="B243" s="5" t="n"/>
+      <c r="C243" s="5" t="n"/>
+      <c r="D243" s="5" t="n"/>
+      <c r="E243" s="7" t="inlineStr">
+        <is>
+          <t>18-1-12</t>
+        </is>
+      </c>
+      <c r="F243" s="7" t="inlineStr">
+        <is>
+          <t>他人が作成した読書計画に不正な期日で更新しようとしても、入力エラーではなく403になる</t>
+        </is>
+      </c>
+      <c r="G243" s="7" t="inlineStr">
+        <is>
+          <t>1.他人が作成した読書計画に対して、期日を空にして直接計画更新のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H243" s="7" t="inlineStr">
+        <is>
+          <t>バリデーションエラーではなく403Forbiddenになり、期日は変更されない（認可チェックが入力チェックより先に行われる）</t>
+        </is>
+      </c>
+      <c r="I243" s="5" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B244" s="7" t="inlineStr">
+        <is>
+          <t>リマインダーバッチ</t>
+        </is>
+      </c>
+      <c r="C244" s="7" t="inlineStr">
+        <is>
+          <t>19-1</t>
+        </is>
+      </c>
+      <c r="D244" s="7" t="inlineStr">
+        <is>
+          <t>日次バッチ(reading-plans:daily)によるリマインダー通知</t>
+        </is>
+      </c>
+      <c r="E244" s="7" t="inlineStr">
+        <is>
+          <t>19-1-1</t>
+        </is>
+      </c>
+      <c r="F244" s="7" t="inlineStr">
+        <is>
+          <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
+        </is>
+      </c>
+      <c r="G244" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日後・ステータス進行中の計画を用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+        </is>
+      </c>
+      <c r="H244" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_before)・title(「読書期限のお知らせ」)・body(「「(書籍名)」の読書期限まであと3日です。」)が含まれる</t>
+        </is>
+      </c>
+      <c r="I244" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="n"/>
+      <c r="B245" s="4" t="n"/>
+      <c r="C245" s="4" t="n"/>
+      <c r="D245" s="4" t="n"/>
+      <c r="E245" s="7" t="inlineStr">
+        <is>
+          <t>19-1-2</t>
+        </is>
+      </c>
+      <c r="F245" s="7" t="inlineStr">
+        <is>
+          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
+        </is>
+      </c>
+      <c r="G245" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが本日・ステータス進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H242" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
-        </is>
-      </c>
-      <c r="I242" s="4" t="n"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="4" t="n"/>
-      <c r="B243" s="4" t="n"/>
-      <c r="C243" s="4" t="n"/>
-      <c r="D243" s="4" t="n"/>
-      <c r="E243" s="7" t="inlineStr">
-        <is>
-          <t>19-1-4</t>
-        </is>
-      </c>
-      <c r="F243" s="7" t="inlineStr">
-        <is>
-          <t>いずれの条件にも該当しない計画には通知が送信されない</t>
-        </is>
-      </c>
-      <c r="G243" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H243" s="7" t="inlineStr">
-        <is>
-          <t>その計画のユーザーに通知が送信されない</t>
-        </is>
-      </c>
-      <c r="I243" s="4" t="n"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="5" t="n"/>
-      <c r="B244" s="5" t="n"/>
-      <c r="C244" s="5" t="n"/>
-      <c r="D244" s="5" t="n"/>
-      <c r="E244" s="7" t="inlineStr">
-        <is>
-          <t>19-1-5</t>
-        </is>
-      </c>
-      <c r="F244" s="7" t="inlineStr">
-        <is>
-          <t>ステータスが「完了」の計画には、期日の条件に合っていても通知が送信されない</t>
-        </is>
-      </c>
-      <c r="G244" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが3日後・本日・3日前で、ステータスが完了の計画をそれぞれ用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
-        </is>
-      </c>
-      <c r="H244" s="7" t="inlineStr">
-        <is>
-          <t>いずれの計画のユーザーにも通知が送信されない</t>
-        </is>
-      </c>
-      <c r="I244" s="5" t="n"/>
-    </row>
-    <row r="245">
-      <c r="A245" s="7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B245" s="7" t="inlineStr">
-        <is>
-          <t>自動失効バッチ</t>
-        </is>
-      </c>
-      <c r="C245" s="7" t="inlineStr">
-        <is>
-          <t>20-1</t>
-        </is>
-      </c>
-      <c r="D245" s="7" t="inlineStr">
-        <is>
-          <t>日次バッチ(reading-plans:daily)による自動失効処理</t>
-        </is>
-      </c>
-      <c r="E245" s="7" t="inlineStr">
-        <is>
-          <t>20-1-1</t>
-        </is>
-      </c>
-      <c r="F245" s="7" t="inlineStr">
-        <is>
-          <t>期日を過ぎた「進行中」の計画が「期限切れ」に更新される</t>
-        </is>
-      </c>
-      <c r="G245" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが過去・ステータス進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
       <c r="H245" s="7" t="inlineStr">
         <is>
-          <t>対象の計画のstatusが「期限切れ」に更新される</t>
-        </is>
-      </c>
-      <c r="I245" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
-        </is>
-      </c>
+          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される。通知のdataには、plan_id・book_title・timing(on_due_date)・title(「読書期限当日のお知らせ」)・body(「「(書籍名)」の読書期限は本日までです。」)が含まれる</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="n"/>
     </row>
     <row r="246">
       <c r="A246" s="4" t="n"/>
@@ -8078,23 +8054,23 @@
       <c r="D246" s="4" t="n"/>
       <c r="E246" s="7" t="inlineStr">
         <is>
-          <t>20-1-2</t>
+          <t>19-1-3</t>
         </is>
       </c>
       <c r="F246" s="7" t="inlineStr">
         <is>
-          <t>期日が今日以降の「進行中」の計画は失効しない</t>
+          <t>期限切れから3日後の計画に再エンゲージメント通知が送信される</t>
         </is>
       </c>
       <c r="G246" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
+          <t>1.target_dateが3日前・ステータス期限切れの計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H246" s="7" t="inlineStr">
         <is>
-          <t>その計画のstatusは「進行中」のまま変化しない</t>
+          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
         </is>
       </c>
       <c r="I246" s="4" t="n"/>
@@ -8106,92 +8082,100 @@
       <c r="D247" s="4" t="n"/>
       <c r="E247" s="7" t="inlineStr">
         <is>
-          <t>20-1-3</t>
+          <t>19-1-4</t>
         </is>
       </c>
       <c r="F247" s="7" t="inlineStr">
         <is>
-          <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
+          <t>いずれの条件にも該当しない計画には通知が送信されない</t>
         </is>
       </c>
       <c r="G247" s="7" t="inlineStr">
         <is>
-          <t>1.完了済み・期限切れの計画をそれぞれ用意する
+          <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H247" s="7" t="inlineStr">
         <is>
-          <t>いずれの計画もstatusが変化しない</t>
+          <t>その計画のユーザーに通知が送信されない</t>
         </is>
       </c>
       <c r="I247" s="4" t="n"/>
     </row>
     <row r="248">
-      <c r="A248" s="4" t="n"/>
-      <c r="B248" s="4" t="n"/>
+      <c r="A248" s="5" t="n"/>
+      <c r="B248" s="5" t="n"/>
       <c r="C248" s="5" t="n"/>
       <c r="D248" s="5" t="n"/>
       <c r="E248" s="7" t="inlineStr">
         <is>
-          <t>20-1-4</t>
+          <t>19-1-5</t>
         </is>
       </c>
       <c r="F248" s="7" t="inlineStr">
         <is>
-          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+          <t>ステータスが「完了」の計画には、期日の条件に合っていても通知が送信されない</t>
         </is>
       </c>
       <c r="G248" s="7" t="inlineStr">
         <is>
-          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
-2.DBを直接確認する</t>
+          <t>1.target_dateが3日後・本日・3日前で、ステータスが完了の計画をそれぞれ用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
       <c r="H248" s="7" t="inlineStr">
         <is>
-          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
+          <t>いずれの計画のユーザーにも通知が送信されない</t>
         </is>
       </c>
       <c r="I248" s="5" t="n"/>
     </row>
     <row r="249">
-      <c r="A249" s="4" t="n"/>
-      <c r="B249" s="4" t="n"/>
+      <c r="A249" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B249" s="7" t="inlineStr">
+        <is>
+          <t>自動失効バッチ</t>
+        </is>
+      </c>
       <c r="C249" s="7" t="inlineStr">
         <is>
-          <t>20-2</t>
+          <t>20-1</t>
         </is>
       </c>
       <c r="D249" s="7" t="inlineStr">
         <is>
-          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
+          <t>日次バッチ(reading-plans:daily)による自動失効処理</t>
         </is>
       </c>
       <c r="E249" s="7" t="inlineStr">
         <is>
-          <t>20-2-1</t>
+          <t>20-1-1</t>
         </is>
       </c>
       <c r="F249" s="7" t="inlineStr">
         <is>
-          <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
+          <t>期日を過ぎた「進行中」の計画が「期限切れ」に更新される</t>
         </is>
       </c>
       <c r="G249" s="7" t="inlineStr">
         <is>
-          <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+          <t>1.target_dateが過去・ステータス進行中の計画を用意する
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H249" s="7" t="inlineStr">
         <is>
-          <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
+          <t>対象の計画のstatusが「期限切れ」に更新される</t>
         </is>
       </c>
       <c r="I249" s="7" t="inlineStr">
         <is>
-          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
+          <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
         </is>
       </c>
     </row>
@@ -8202,223 +8186,224 @@
       <c r="D250" s="4" t="n"/>
       <c r="E250" s="7" t="inlineStr">
         <is>
-          <t>20-2-2</t>
+          <t>20-1-2</t>
         </is>
       </c>
       <c r="F250" s="7" t="inlineStr">
         <is>
-          <t>期限切れへの更新が、通知対象の抽出より先に行われる</t>
+          <t>期日が今日以降の「進行中」の計画は失効しない</t>
         </is>
       </c>
       <c r="G250" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが3日前で、ステータスが「進行中」のまま(未更新)の計画を用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H250" s="7" t="inlineStr">
         <is>
-          <t>計画のstatusが「期限切れ」に更新され、そのユーザーに再エンゲージメント(re_engagement)通知が送信される</t>
+          <t>その計画のstatusは「進行中」のまま変化しない</t>
         </is>
       </c>
       <c r="I250" s="4" t="n"/>
     </row>
     <row r="251">
-      <c r="A251" s="5" t="n"/>
-      <c r="B251" s="5" t="n"/>
-      <c r="C251" s="5" t="n"/>
-      <c r="D251" s="5" t="n"/>
+      <c r="A251" s="4" t="n"/>
+      <c r="B251" s="4" t="n"/>
+      <c r="C251" s="4" t="n"/>
+      <c r="D251" s="4" t="n"/>
       <c r="E251" s="7" t="inlineStr">
         <is>
-          <t>20-2-3</t>
+          <t>20-1-3</t>
         </is>
       </c>
       <c r="F251" s="7" t="inlineStr">
         <is>
-          <t>reading-plans:dailyが毎日20:00に実行されるようスケジュールされている</t>
+          <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
         </is>
       </c>
       <c r="G251" s="7" t="inlineStr">
         <is>
-          <t>1.アプリケーションのスケジュール(Illuminate\Console\Scheduling\Schedule)から、登録済みのイベントを取得する</t>
+          <t>1.完了済み・期限切れの計画をそれぞれ用意する
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H251" s="7" t="inlineStr">
         <is>
-          <t>reading-plans:dailyのイベントが登録されており、cron式が毎日20:00(0 20 * * *)になっている</t>
-        </is>
-      </c>
-      <c r="I251" s="5" t="n"/>
+          <t>いずれの計画もstatusが変化しない</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="n"/>
     </row>
     <row r="252">
-      <c r="A252" s="9" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B252" s="9" t="inlineStr">
-        <is>
-          <t>通知</t>
-        </is>
-      </c>
-      <c r="C252" s="9" t="inlineStr">
-        <is>
-          <t>21-1</t>
-        </is>
-      </c>
-      <c r="D252" s="9" t="inlineStr">
-        <is>
-          <t>通知の既読化</t>
-        </is>
-      </c>
-      <c r="E252" s="9" t="inlineStr">
-        <is>
-          <t>21-1-1</t>
-        </is>
-      </c>
-      <c r="F252" s="9" t="inlineStr">
-        <is>
-          <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
-        </is>
-      </c>
-      <c r="G252" s="9" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態でPOST /notifications/{id}/read に直接リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H252" s="9" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
-        </is>
-      </c>
-      <c r="I252" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationTest.php</t>
-        </is>
-      </c>
+      <c r="A252" s="4" t="n"/>
+      <c r="B252" s="4" t="n"/>
+      <c r="C252" s="5" t="n"/>
+      <c r="D252" s="5" t="n"/>
+      <c r="E252" s="7" t="inlineStr">
+        <is>
+          <t>20-1-4</t>
+        </is>
+      </c>
+      <c r="F252" s="7" t="inlineStr">
+        <is>
+          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+        </is>
+      </c>
+      <c r="G252" s="7" t="inlineStr">
+        <is>
+          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
+2.DBを直接確認する</t>
+        </is>
+      </c>
+      <c r="H252" s="7" t="inlineStr">
+        <is>
+          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
+        </is>
+      </c>
+      <c r="I252" s="5" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="4" t="n"/>
       <c r="B253" s="4" t="n"/>
-      <c r="C253" s="4" t="n"/>
-      <c r="D253" s="4" t="n"/>
-      <c r="E253" s="9" t="inlineStr">
-        <is>
-          <t>21-1-2</t>
-        </is>
-      </c>
-      <c r="F253" s="9" t="inlineStr">
-        <is>
-          <t>自分の通知を既読にできる</t>
-        </is>
-      </c>
-      <c r="G253" s="9" t="inlineStr">
-        <is>
-          <t>1.自分宛ての未読通知を用意する
-2.その通知に対してPOST /notifications/{id}/read を送信する</t>
-        </is>
-      </c>
-      <c r="H253" s="9" t="inlineStr">
-        <is>
-          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
-        </is>
-      </c>
-      <c r="I253" s="4" t="n"/>
+      <c r="C253" s="7" t="inlineStr">
+        <is>
+          <t>20-2</t>
+        </is>
+      </c>
+      <c r="D253" s="7" t="inlineStr">
+        <is>
+          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
+        </is>
+      </c>
+      <c r="E253" s="7" t="inlineStr">
+        <is>
+          <t>20-2-1</t>
+        </is>
+      </c>
+      <c r="F253" s="7" t="inlineStr">
+        <is>
+          <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
+        </is>
+      </c>
+      <c r="G253" s="7" t="inlineStr">
+        <is>
+          <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+        </is>
+      </c>
+      <c r="H253" s="7" t="inlineStr">
+        <is>
+          <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I253" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="4" t="n"/>
       <c r="B254" s="4" t="n"/>
-      <c r="C254" s="5" t="n"/>
-      <c r="D254" s="5" t="n"/>
-      <c r="E254" s="9" t="inlineStr">
-        <is>
-          <t>21-1-3</t>
-        </is>
-      </c>
-      <c r="F254" s="9" t="inlineStr">
-        <is>
-          <t>他ユーザーの通知は既読にできない</t>
-        </is>
-      </c>
-      <c r="G254" s="9" t="inlineStr">
-        <is>
-          <t>1.他ユーザー宛ての通知を用意する
-2.そのIDに対してPOST /notifications/{id}/read を送信する</t>
-        </is>
-      </c>
-      <c r="H254" s="9" t="inlineStr">
-        <is>
-          <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
-        </is>
-      </c>
-      <c r="I254" s="5" t="n"/>
+      <c r="C254" s="4" t="n"/>
+      <c r="D254" s="4" t="n"/>
+      <c r="E254" s="7" t="inlineStr">
+        <is>
+          <t>20-2-2</t>
+        </is>
+      </c>
+      <c r="F254" s="7" t="inlineStr">
+        <is>
+          <t>期限切れへの更新が、通知対象の抽出より先に行われる</t>
+        </is>
+      </c>
+      <c r="G254" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日前で、ステータスが「進行中」のまま(未更新)の計画を用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+        </is>
+      </c>
+      <c r="H254" s="7" t="inlineStr">
+        <is>
+          <t>計画のstatusが「期限切れ」に更新され、そのユーザーに再エンゲージメント(re_engagement)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I254" s="4" t="n"/>
     </row>
     <row r="255">
-      <c r="A255" s="4" t="n"/>
-      <c r="B255" s="4" t="n"/>
-      <c r="C255" s="9" t="inlineStr">
-        <is>
-          <t>21-2</t>
-        </is>
-      </c>
-      <c r="D255" s="9" t="inlineStr">
-        <is>
-          <t>通知一覧</t>
-        </is>
-      </c>
-      <c r="E255" s="9" t="inlineStr">
-        <is>
-          <t>21-2-1</t>
-        </is>
-      </c>
-      <c r="F255" s="9" t="inlineStr">
-        <is>
-          <t>未ログインの場合、通知一覧にアクセスできない</t>
-        </is>
-      </c>
-      <c r="G255" s="9" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
-        </is>
-      </c>
-      <c r="H255" s="9" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I255" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationIndexTest.php</t>
-        </is>
-      </c>
+      <c r="A255" s="5" t="n"/>
+      <c r="B255" s="5" t="n"/>
+      <c r="C255" s="5" t="n"/>
+      <c r="D255" s="5" t="n"/>
+      <c r="E255" s="7" t="inlineStr">
+        <is>
+          <t>20-2-3</t>
+        </is>
+      </c>
+      <c r="F255" s="7" t="inlineStr">
+        <is>
+          <t>reading-plans:dailyが毎日20:00に実行されるようスケジュールされている</t>
+        </is>
+      </c>
+      <c r="G255" s="7" t="inlineStr">
+        <is>
+          <t>1.アプリケーションのスケジュール(Illuminate\Console\Scheduling\Schedule)から、登録済みのイベントを取得する</t>
+        </is>
+      </c>
+      <c r="H255" s="7" t="inlineStr">
+        <is>
+          <t>reading-plans:dailyのイベントが登録されており、cron式が毎日20:00(0 20 * * *)になっている</t>
+        </is>
+      </c>
+      <c r="I255" s="5" t="n"/>
     </row>
     <row r="256">
-      <c r="A256" s="4" t="n"/>
-      <c r="B256" s="4" t="n"/>
-      <c r="C256" s="4" t="n"/>
-      <c r="D256" s="4" t="n"/>
+      <c r="A256" s="9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B256" s="9" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="C256" s="9" t="inlineStr">
+        <is>
+          <t>21-1</t>
+        </is>
+      </c>
+      <c r="D256" s="9" t="inlineStr">
+        <is>
+          <t>通知の既読化</t>
+        </is>
+      </c>
       <c r="E256" s="9" t="inlineStr">
         <is>
-          <t>21-2-2</t>
+          <t>21-1-1</t>
         </is>
       </c>
       <c r="F256" s="9" t="inlineStr">
         <is>
-          <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
+          <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
         </is>
       </c>
       <c r="G256" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
-2.通知一覧ページを開く</t>
+          <t>1.未ログイン状態でPOST /notifications/{id}/read に直接リクエストを送信する</t>
         </is>
       </c>
       <c r="H256" s="9" t="inlineStr">
         <is>
-          <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
-        </is>
-      </c>
-      <c r="I256" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
+        </is>
+      </c>
+      <c r="I256" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n"/>
@@ -8427,23 +8412,23 @@
       <c r="D257" s="4" t="n"/>
       <c r="E257" s="9" t="inlineStr">
         <is>
-          <t>21-2-3</t>
+          <t>21-1-2</t>
         </is>
       </c>
       <c r="F257" s="9" t="inlineStr">
         <is>
-          <t>通知が1件もない場合の表示を確認する</t>
+          <t>自分の通知を既読にできる</t>
         </is>
       </c>
       <c r="G257" s="9" t="inlineStr">
         <is>
-          <t>1.通知が1件もないユーザーでログインする
-2.通知一覧ページを開く</t>
+          <t>1.自分宛ての未読通知を用意する
+2.その通知に対してPOST /notifications/{id}/read を送信する</t>
         </is>
       </c>
       <c r="H257" s="9" t="inlineStr">
         <is>
-          <t>「通知はありません。」と表示される</t>
+          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
         </is>
       </c>
       <c r="I257" s="4" t="n"/>
@@ -8451,125 +8436,125 @@
     <row r="258">
       <c r="A258" s="4" t="n"/>
       <c r="B258" s="4" t="n"/>
-      <c r="C258" s="4" t="n"/>
-      <c r="D258" s="4" t="n"/>
+      <c r="C258" s="5" t="n"/>
+      <c r="D258" s="5" t="n"/>
       <c r="E258" s="9" t="inlineStr">
         <is>
-          <t>21-2-4</t>
+          <t>21-1-3</t>
         </is>
       </c>
       <c r="F258" s="9" t="inlineStr">
         <is>
-          <t>通知のタイトル・本文が表示される</t>
+          <t>他ユーザーの通知は既読にできない</t>
         </is>
       </c>
       <c r="G258" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
-2.通知一覧ページを開く</t>
+          <t>1.他ユーザー宛ての通知を用意する
+2.そのIDに対してPOST /notifications/{id}/read を送信する</t>
         </is>
       </c>
       <c r="H258" s="9" t="inlineStr">
         <is>
-          <t>通知のtitleとbodyが一覧に表示される</t>
-        </is>
-      </c>
-      <c r="I258" s="4" t="n"/>
+          <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
+        </is>
+      </c>
+      <c r="I258" s="5" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n"/>
       <c r="B259" s="4" t="n"/>
-      <c r="C259" s="4" t="n"/>
-      <c r="D259" s="4" t="n"/>
+      <c r="C259" s="9" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="D259" s="9" t="inlineStr">
+        <is>
+          <t>通知一覧</t>
+        </is>
+      </c>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>21-2-5</t>
+          <t>21-2-1</t>
         </is>
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>未読と既読で表示が異なる</t>
+          <t>未ログインの場合、通知一覧にアクセスできない</t>
         </is>
       </c>
       <c r="G259" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
-2.通知一覧ページを開く</t>
+          <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H259" s="9" t="inlineStr">
         <is>
-          <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
-        </is>
-      </c>
-      <c r="I259" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I259" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationIndexTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="4" t="n"/>
       <c r="B260" s="4" t="n"/>
-      <c r="C260" s="5" t="n"/>
-      <c r="D260" s="5" t="n"/>
+      <c r="C260" s="4" t="n"/>
+      <c r="D260" s="4" t="n"/>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>21-2-6</t>
+          <t>21-2-2</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>同じ日時に作成された通知は、期日3日前→期日当日→期日3日後の順に表示される</t>
+          <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
         </is>
       </c>
       <c r="G260" s="9" t="inlineStr">
         <is>
-          <t>1.同じ日時に作成された、期日3日前（予告）・期日当日（最終警告）・期日3日後（再エンゲージメント）の通知と、作成日時の異なる通知を用意する
+          <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H260" s="9" t="inlineStr">
         <is>
-          <t>第1優先で作成日時の新しい順、作成日時が同じ通知同士は第2優先で「期日3日前→期日当日→期日3日後」の順に表示される</t>
-        </is>
-      </c>
-      <c r="I260" s="5" t="n"/>
+          <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
+        </is>
+      </c>
+      <c r="I260" s="4" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="4" t="n"/>
       <c r="B261" s="4" t="n"/>
-      <c r="C261" s="9" t="inlineStr">
-        <is>
-          <t>21-3</t>
-        </is>
-      </c>
-      <c r="D261" s="9" t="inlineStr">
-        <is>
-          <t>ヘッダーの未読件数</t>
-        </is>
-      </c>
+      <c r="C261" s="4" t="n"/>
+      <c r="D261" s="4" t="n"/>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>21-3-1</t>
+          <t>21-2-3</t>
         </is>
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>ヘッダーのベルアイコンに未読件数が表示される</t>
+          <t>通知が1件もない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G261" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
+          <t>1.通知が1件もないユーザーでログインする
+2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H261" s="9" t="inlineStr">
         <is>
-          <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
-        </is>
-      </c>
-      <c r="I261" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
-        </is>
-      </c>
+          <t>「通知はありません。」と表示される</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="4" t="n"/>
@@ -8578,235 +8563,358 @@
       <c r="D262" s="4" t="n"/>
       <c r="E262" s="9" t="inlineStr">
         <is>
+          <t>21-2-4</t>
+        </is>
+      </c>
+      <c r="F262" s="9" t="inlineStr">
+        <is>
+          <t>通知のタイトル・本文が表示される</t>
+        </is>
+      </c>
+      <c r="G262" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
+2.通知一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H262" s="9" t="inlineStr">
+        <is>
+          <t>通知のtitleとbodyが一覧に表示される</t>
+        </is>
+      </c>
+      <c r="I262" s="4" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="n"/>
+      <c r="B263" s="4" t="n"/>
+      <c r="C263" s="4" t="n"/>
+      <c r="D263" s="4" t="n"/>
+      <c r="E263" s="9" t="inlineStr">
+        <is>
+          <t>21-2-5</t>
+        </is>
+      </c>
+      <c r="F263" s="9" t="inlineStr">
+        <is>
+          <t>未読と既読で表示が異なる</t>
+        </is>
+      </c>
+      <c r="G263" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
+2.通知一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H263" s="9" t="inlineStr">
+        <is>
+          <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
+        </is>
+      </c>
+      <c r="I263" s="4" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="n"/>
+      <c r="B264" s="4" t="n"/>
+      <c r="C264" s="5" t="n"/>
+      <c r="D264" s="5" t="n"/>
+      <c r="E264" s="9" t="inlineStr">
+        <is>
+          <t>21-2-6</t>
+        </is>
+      </c>
+      <c r="F264" s="9" t="inlineStr">
+        <is>
+          <t>同じ日時に作成された通知は、期日3日前→期日当日→期日3日後の順に表示される</t>
+        </is>
+      </c>
+      <c r="G264" s="9" t="inlineStr">
+        <is>
+          <t>1.同じ日時に作成された、期日3日前（予告）・期日当日（最終警告）・期日3日後（再エンゲージメント）の通知と、作成日時の異なる通知を用意する
+2.通知一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H264" s="9" t="inlineStr">
+        <is>
+          <t>第1優先で作成日時の新しい順、作成日時が同じ通知同士は第2優先で「期日3日前→期日当日→期日3日後」の順に表示される</t>
+        </is>
+      </c>
+      <c r="I264" s="5" t="n"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="n"/>
+      <c r="B265" s="4" t="n"/>
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>21-3</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
+        <is>
+          <t>ヘッダーの未読件数</t>
+        </is>
+      </c>
+      <c r="E265" s="9" t="inlineStr">
+        <is>
+          <t>21-3-1</t>
+        </is>
+      </c>
+      <c r="F265" s="9" t="inlineStr">
+        <is>
+          <t>ヘッダーのベルアイコンに未読件数が表示される</t>
+        </is>
+      </c>
+      <c r="G265" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
+        </is>
+      </c>
+      <c r="H265" s="9" t="inlineStr">
+        <is>
+          <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
+        </is>
+      </c>
+      <c r="I265" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="n"/>
+      <c r="B266" s="4" t="n"/>
+      <c r="C266" s="4" t="n"/>
+      <c r="D266" s="4" t="n"/>
+      <c r="E266" s="9" t="inlineStr">
+        <is>
           <t>21-3-2</t>
         </is>
       </c>
-      <c r="F262" s="9" t="inlineStr">
+      <c r="F266" s="9" t="inlineStr">
         <is>
           <t>通知を既読にすると、ヘッダーの未読件数が減る</t>
         </is>
       </c>
-      <c r="G262" s="9" t="inlineStr">
+      <c r="G266" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知を複数件用意する
 2.そのうち1件にPOST /notifications/{id}/read を送信して既読にする
 3.画面を開き直す</t>
         </is>
       </c>
-      <c r="H262" s="9" t="inlineStr">
+      <c r="H266" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数が、既読にした1件分だけ減る</t>
         </is>
       </c>
-      <c r="I262" s="4" t="n"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="5" t="n"/>
-      <c r="B263" s="5" t="n"/>
-      <c r="C263" s="5" t="n"/>
-      <c r="D263" s="5" t="n"/>
-      <c r="E263" s="9" t="inlineStr">
+      <c r="I266" s="4" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="5" t="n"/>
+      <c r="B267" s="5" t="n"/>
+      <c r="C267" s="5" t="n"/>
+      <c r="D267" s="5" t="n"/>
+      <c r="E267" s="9" t="inlineStr">
         <is>
           <t>21-3-3</t>
         </is>
       </c>
-      <c r="F263" s="9" t="inlineStr">
+      <c r="F267" s="9" t="inlineStr">
         <is>
           <t>他ユーザーの通知は未読件数に含まれない</t>
         </is>
       </c>
-      <c r="G263" s="9" t="inlineStr">
+      <c r="G267" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知と、他ユーザー宛ての未読通知をそれぞれ用意する
 2.画面を開く</t>
         </is>
       </c>
-      <c r="H263" s="9" t="inlineStr">
+      <c r="H267" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数には、自分宛ての未読通知のみが数えられる</t>
         </is>
       </c>
-      <c r="I263" s="5" t="n"/>
+      <c r="I267" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="177">
     <mergeCell ref="B31:B65"/>
-    <mergeCell ref="A66:A85"/>
     <mergeCell ref="I17:I30"/>
-    <mergeCell ref="C108:C111"/>
+    <mergeCell ref="I114:I116"/>
+    <mergeCell ref="D91:D95"/>
     <mergeCell ref="A17:A30"/>
-    <mergeCell ref="A192:A198"/>
-    <mergeCell ref="C192:C198"/>
+    <mergeCell ref="C153:C155"/>
     <mergeCell ref="D12:D16"/>
-    <mergeCell ref="I199:I204"/>
-    <mergeCell ref="D209:D228"/>
-    <mergeCell ref="I173:I179"/>
-    <mergeCell ref="A185:A191"/>
-    <mergeCell ref="C94:C99"/>
-    <mergeCell ref="C70:C74"/>
-    <mergeCell ref="A86:A107"/>
-    <mergeCell ref="A122:A139"/>
-    <mergeCell ref="D240:D244"/>
-    <mergeCell ref="B173:B179"/>
+    <mergeCell ref="D194:D200"/>
+    <mergeCell ref="I244:I248"/>
+    <mergeCell ref="D117:D119"/>
+    <mergeCell ref="A66:A87"/>
+    <mergeCell ref="I120:I123"/>
+    <mergeCell ref="A194:A200"/>
+    <mergeCell ref="I124:I135"/>
+    <mergeCell ref="I70:I75"/>
+    <mergeCell ref="I88:I90"/>
+    <mergeCell ref="B88:B109"/>
+    <mergeCell ref="C194:C200"/>
+    <mergeCell ref="I153:I155"/>
+    <mergeCell ref="A175:A181"/>
+    <mergeCell ref="A249:A255"/>
+    <mergeCell ref="B124:B141"/>
+    <mergeCell ref="D182:D186"/>
+    <mergeCell ref="D265:D267"/>
+    <mergeCell ref="C170:C174"/>
     <mergeCell ref="C31:C34"/>
-    <mergeCell ref="D173:D179"/>
-    <mergeCell ref="D252:D254"/>
-    <mergeCell ref="I229:I239"/>
+    <mergeCell ref="C107:C109"/>
     <mergeCell ref="I56:I61"/>
     <mergeCell ref="D35:D41"/>
     <mergeCell ref="C56:C61"/>
-    <mergeCell ref="A140:A172"/>
-    <mergeCell ref="D100:D104"/>
-    <mergeCell ref="D249:D251"/>
-    <mergeCell ref="I192:I198"/>
+    <mergeCell ref="C201:C206"/>
+    <mergeCell ref="A2:A16"/>
     <mergeCell ref="C42:C55"/>
-    <mergeCell ref="A2:A16"/>
-    <mergeCell ref="C161:C167"/>
-    <mergeCell ref="B118:B121"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="C89:C93"/>
     <mergeCell ref="D2:D4"/>
-    <mergeCell ref="C154:C160"/>
     <mergeCell ref="C66:C69"/>
+    <mergeCell ref="I259:I264"/>
     <mergeCell ref="D17:D30"/>
-    <mergeCell ref="C180:C184"/>
-    <mergeCell ref="D143:D150"/>
-    <mergeCell ref="D82:D85"/>
-    <mergeCell ref="I115:I117"/>
+    <mergeCell ref="C232:C243"/>
+    <mergeCell ref="A187:A193"/>
+    <mergeCell ref="I91:I95"/>
+    <mergeCell ref="C156:C162"/>
+    <mergeCell ref="C187:C193"/>
+    <mergeCell ref="B244:B248"/>
     <mergeCell ref="I12:I16"/>
-    <mergeCell ref="C115:C117"/>
-    <mergeCell ref="D70:D74"/>
-    <mergeCell ref="D185:D191"/>
+    <mergeCell ref="D107:D109"/>
+    <mergeCell ref="I194:I200"/>
+    <mergeCell ref="I117:I119"/>
+    <mergeCell ref="A124:A141"/>
+    <mergeCell ref="C182:C186"/>
     <mergeCell ref="C35:C41"/>
-    <mergeCell ref="I180:I184"/>
-    <mergeCell ref="B86:B107"/>
-    <mergeCell ref="I108:I111"/>
-    <mergeCell ref="D134:D138"/>
-    <mergeCell ref="A205:A208"/>
-    <mergeCell ref="C249:C251"/>
-    <mergeCell ref="C205:C208"/>
-    <mergeCell ref="B229:B239"/>
+    <mergeCell ref="A207:A210"/>
+    <mergeCell ref="B175:B181"/>
+    <mergeCell ref="I156:I162"/>
+    <mergeCell ref="D175:D181"/>
+    <mergeCell ref="D249:D252"/>
+    <mergeCell ref="I142:I144"/>
+    <mergeCell ref="I182:I186"/>
+    <mergeCell ref="B120:B123"/>
+    <mergeCell ref="I265:I267"/>
     <mergeCell ref="D42:D55"/>
-    <mergeCell ref="D229:D239"/>
-    <mergeCell ref="I252:I254"/>
-    <mergeCell ref="B245:B251"/>
-    <mergeCell ref="D161:D167"/>
-    <mergeCell ref="B252:B263"/>
-    <mergeCell ref="I168:I172"/>
+    <mergeCell ref="D120:D123"/>
+    <mergeCell ref="D256:D258"/>
+    <mergeCell ref="C84:C87"/>
+    <mergeCell ref="D232:D243"/>
+    <mergeCell ref="C136:C140"/>
+    <mergeCell ref="D145:D152"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="A120:A123"/>
     <mergeCell ref="I62:I65"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="C255:C260"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="D9:D10"/>
-    <mergeCell ref="D140:D142"/>
-    <mergeCell ref="I105:I107"/>
-    <mergeCell ref="B205:B208"/>
-    <mergeCell ref="I143:I150"/>
-    <mergeCell ref="D205:D208"/>
-    <mergeCell ref="I89:I93"/>
-    <mergeCell ref="I82:I85"/>
+    <mergeCell ref="I136:I140"/>
+    <mergeCell ref="D259:D264"/>
+    <mergeCell ref="I96:I101"/>
+    <mergeCell ref="D76:D83"/>
+    <mergeCell ref="D187:D193"/>
+    <mergeCell ref="C120:C123"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="C70:C75"/>
     <mergeCell ref="D62:D65"/>
-    <mergeCell ref="D118:D121"/>
-    <mergeCell ref="B180:B184"/>
-    <mergeCell ref="B66:B85"/>
-    <mergeCell ref="I185:I191"/>
-    <mergeCell ref="D86:D88"/>
+    <mergeCell ref="C88:C90"/>
+    <mergeCell ref="D207:D210"/>
     <mergeCell ref="I9:I10"/>
     <mergeCell ref="A31:A65"/>
-    <mergeCell ref="C261:C263"/>
-    <mergeCell ref="I134:I138"/>
-    <mergeCell ref="B240:B244"/>
-    <mergeCell ref="C134:C138"/>
-    <mergeCell ref="D94:D99"/>
-    <mergeCell ref="D112:D114"/>
-    <mergeCell ref="C245:C248"/>
-    <mergeCell ref="I209:I228"/>
+    <mergeCell ref="D136:D140"/>
+    <mergeCell ref="D253:D255"/>
+    <mergeCell ref="I175:I181"/>
+    <mergeCell ref="C117:C119"/>
+    <mergeCell ref="B182:B186"/>
+    <mergeCell ref="D110:D113"/>
+    <mergeCell ref="D211:D231"/>
+    <mergeCell ref="D163:D169"/>
+    <mergeCell ref="A88:A109"/>
+    <mergeCell ref="I207:I210"/>
+    <mergeCell ref="A211:A231"/>
+    <mergeCell ref="A201:A206"/>
     <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C122:C133"/>
-    <mergeCell ref="I161:I167"/>
-    <mergeCell ref="D168:D172"/>
-    <mergeCell ref="C173:C179"/>
-    <mergeCell ref="B199:B204"/>
-    <mergeCell ref="I249:I251"/>
-    <mergeCell ref="D199:D204"/>
+    <mergeCell ref="I253:I255"/>
+    <mergeCell ref="B249:B255"/>
+    <mergeCell ref="C253:C255"/>
+    <mergeCell ref="D142:D144"/>
+    <mergeCell ref="B256:B267"/>
+    <mergeCell ref="C259:C264"/>
     <mergeCell ref="I6:I8"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="C118:C121"/>
-    <mergeCell ref="I240:I244"/>
-    <mergeCell ref="A180:A184"/>
+    <mergeCell ref="I145:I152"/>
+    <mergeCell ref="C163:C169"/>
+    <mergeCell ref="D96:D101"/>
+    <mergeCell ref="A232:A243"/>
+    <mergeCell ref="D70:D75"/>
     <mergeCell ref="B2:B16"/>
-    <mergeCell ref="A240:A244"/>
-    <mergeCell ref="C240:C244"/>
-    <mergeCell ref="C86:C88"/>
-    <mergeCell ref="B192:B198"/>
-    <mergeCell ref="D192:D198"/>
-    <mergeCell ref="D89:D93"/>
-    <mergeCell ref="I205:I208"/>
+    <mergeCell ref="D153:D155"/>
+    <mergeCell ref="I187:I193"/>
+    <mergeCell ref="I76:I83"/>
+    <mergeCell ref="C102:C106"/>
     <mergeCell ref="I35:I41"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="B185:B191"/>
+    <mergeCell ref="A182:A186"/>
     <mergeCell ref="D66:D69"/>
-    <mergeCell ref="I118:I121"/>
-    <mergeCell ref="D115:D117"/>
-    <mergeCell ref="I86:I88"/>
-    <mergeCell ref="D105:D107"/>
+    <mergeCell ref="B194:B200"/>
+    <mergeCell ref="B232:B243"/>
     <mergeCell ref="D56:D61"/>
-    <mergeCell ref="C143:C150"/>
-    <mergeCell ref="I70:I74"/>
-    <mergeCell ref="C112:C114"/>
-    <mergeCell ref="C185:C191"/>
-    <mergeCell ref="C252:C254"/>
-    <mergeCell ref="I94:I99"/>
-    <mergeCell ref="C100:C104"/>
-    <mergeCell ref="C75:C81"/>
-    <mergeCell ref="D122:D133"/>
-    <mergeCell ref="B140:B172"/>
-    <mergeCell ref="D151:D153"/>
-    <mergeCell ref="A229:A239"/>
-    <mergeCell ref="C229:C239"/>
-    <mergeCell ref="D154:D160"/>
-    <mergeCell ref="I255:I260"/>
-    <mergeCell ref="C105:C107"/>
-    <mergeCell ref="I245:I248"/>
-    <mergeCell ref="D75:D81"/>
+    <mergeCell ref="B142:B174"/>
+    <mergeCell ref="C256:C258"/>
+    <mergeCell ref="C265:C267"/>
+    <mergeCell ref="A142:A174"/>
+    <mergeCell ref="C124:C135"/>
+    <mergeCell ref="B207:B210"/>
+    <mergeCell ref="A110:A116"/>
+    <mergeCell ref="I163:I169"/>
+    <mergeCell ref="B66:B87"/>
+    <mergeCell ref="C114:C116"/>
+    <mergeCell ref="B201:B206"/>
+    <mergeCell ref="C175:C181"/>
+    <mergeCell ref="C249:C252"/>
+    <mergeCell ref="D201:D206"/>
+    <mergeCell ref="C96:C101"/>
+    <mergeCell ref="D84:D87"/>
     <mergeCell ref="C17:C30"/>
     <mergeCell ref="D31:D34"/>
-    <mergeCell ref="A115:A117"/>
-    <mergeCell ref="D180:D184"/>
+    <mergeCell ref="I170:I174"/>
+    <mergeCell ref="B187:B193"/>
     <mergeCell ref="I42:I55"/>
-    <mergeCell ref="D108:D111"/>
+    <mergeCell ref="A244:A248"/>
+    <mergeCell ref="I107:I109"/>
+    <mergeCell ref="C244:C248"/>
+    <mergeCell ref="C91:C95"/>
+    <mergeCell ref="D156:D162"/>
+    <mergeCell ref="D102:D106"/>
+    <mergeCell ref="C145:C152"/>
     <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C140:C142"/>
+    <mergeCell ref="D114:D116"/>
     <mergeCell ref="I66:I69"/>
-    <mergeCell ref="I261:I263"/>
-    <mergeCell ref="B108:B114"/>
-    <mergeCell ref="A209:A228"/>
-    <mergeCell ref="C209:C228"/>
+    <mergeCell ref="I232:I243"/>
+    <mergeCell ref="A117:A119"/>
     <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C151:C153"/>
-    <mergeCell ref="I140:I142"/>
-    <mergeCell ref="A245:A251"/>
-    <mergeCell ref="I122:I133"/>
-    <mergeCell ref="D261:D263"/>
+    <mergeCell ref="D88:D90"/>
+    <mergeCell ref="D124:D135"/>
+    <mergeCell ref="B110:B116"/>
+    <mergeCell ref="C207:C210"/>
+    <mergeCell ref="A256:A267"/>
+    <mergeCell ref="I201:I206"/>
     <mergeCell ref="B17:B30"/>
-    <mergeCell ref="A252:A263"/>
-    <mergeCell ref="I151:I153"/>
-    <mergeCell ref="A173:A179"/>
-    <mergeCell ref="D255:D260"/>
-    <mergeCell ref="B122:B139"/>
-    <mergeCell ref="I154:I160"/>
-    <mergeCell ref="D245:D248"/>
-    <mergeCell ref="I75:I81"/>
-    <mergeCell ref="I100:I104"/>
-    <mergeCell ref="B209:B228"/>
+    <mergeCell ref="I256:I258"/>
+    <mergeCell ref="C110:C113"/>
+    <mergeCell ref="C211:C231"/>
+    <mergeCell ref="C76:C83"/>
+    <mergeCell ref="B211:B231"/>
+    <mergeCell ref="I84:I87"/>
+    <mergeCell ref="I249:I252"/>
     <mergeCell ref="I31:I34"/>
-    <mergeCell ref="C168:C172"/>
+    <mergeCell ref="D170:D174"/>
+    <mergeCell ref="I110:I113"/>
+    <mergeCell ref="D244:D248"/>
     <mergeCell ref="C12:C16"/>
-    <mergeCell ref="I112:I114"/>
-    <mergeCell ref="A199:A204"/>
-    <mergeCell ref="C199:C204"/>
-    <mergeCell ref="A108:A114"/>
+    <mergeCell ref="I211:I231"/>
+    <mergeCell ref="C142:C144"/>
     <mergeCell ref="C62:C65"/>
+    <mergeCell ref="I102:I106"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8832,6 +8940,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -8856,6 +8965,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
@@ -8894,7 +9004,7 @@
     <row r="11" ht="40" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>・17-1-13「読書計画削除時に関連するリマインダー通知も同時に削除される」はレビュー指摘により追加した項目です。ReadingPlanモデルのdeletingイベントで、削除される計画に紐づく通知(dataのplan_idが一致するReadingPlanReminder)を削除する実装を追加済みです。モデル経由の削除($readingPlan-&gt;delete())でのみ動作します。</t>
+          <t>・17-1-13「読書計画削除時に関連するリマインダー通知も同時に削除される」はレビュー指摘により追加した項目です。ReadingPlanController@destroy で、削除する計画に紐づく通知(dataのplan_idが一致するReadingPlanReminder)の削除と計画の削除を、1つのトランザクションで行っています。</t>
         </is>
       </c>
     </row>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -8796,32 +8796,32 @@
     <mergeCell ref="I142:I144"/>
     <mergeCell ref="I182:I186"/>
     <mergeCell ref="B120:B123"/>
+    <mergeCell ref="D42:D55"/>
     <mergeCell ref="I265:I267"/>
-    <mergeCell ref="D42:D55"/>
     <mergeCell ref="D120:D123"/>
     <mergeCell ref="D256:D258"/>
     <mergeCell ref="C84:C87"/>
     <mergeCell ref="D232:D243"/>
     <mergeCell ref="C136:C140"/>
+    <mergeCell ref="I62:I65"/>
+    <mergeCell ref="D6:D8"/>
     <mergeCell ref="D145:D152"/>
-    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="I2:I4"/>
     <mergeCell ref="A120:A123"/>
-    <mergeCell ref="I62:I65"/>
-    <mergeCell ref="I2:I4"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="I136:I140"/>
     <mergeCell ref="D259:D264"/>
     <mergeCell ref="I96:I101"/>
+    <mergeCell ref="D187:D193"/>
     <mergeCell ref="D76:D83"/>
-    <mergeCell ref="D187:D193"/>
     <mergeCell ref="C120:C123"/>
     <mergeCell ref="B117:B119"/>
+    <mergeCell ref="D62:D65"/>
     <mergeCell ref="C70:C75"/>
-    <mergeCell ref="D62:D65"/>
     <mergeCell ref="C88:C90"/>
     <mergeCell ref="D207:D210"/>
+    <mergeCell ref="A31:A65"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="A31:A65"/>
     <mergeCell ref="D136:D140"/>
     <mergeCell ref="D253:D255"/>
     <mergeCell ref="I175:I181"/>
@@ -8863,8 +8863,8 @@
     <mergeCell ref="C265:C267"/>
     <mergeCell ref="A142:A174"/>
     <mergeCell ref="C124:C135"/>
+    <mergeCell ref="A110:A116"/>
     <mergeCell ref="B207:B210"/>
-    <mergeCell ref="A110:A116"/>
     <mergeCell ref="I163:I169"/>
     <mergeCell ref="B66:B87"/>
     <mergeCell ref="C114:C116"/>
@@ -8903,15 +8903,15 @@
     <mergeCell ref="C110:C113"/>
     <mergeCell ref="C211:C231"/>
     <mergeCell ref="C76:C83"/>
+    <mergeCell ref="I84:I87"/>
     <mergeCell ref="B211:B231"/>
-    <mergeCell ref="I84:I87"/>
     <mergeCell ref="I249:I252"/>
     <mergeCell ref="I31:I34"/>
     <mergeCell ref="D170:D174"/>
     <mergeCell ref="I110:I113"/>
+    <mergeCell ref="I211:I231"/>
     <mergeCell ref="D244:D248"/>
     <mergeCell ref="C12:C16"/>
-    <mergeCell ref="I211:I231"/>
     <mergeCell ref="C142:C144"/>
     <mergeCell ref="C62:C65"/>
     <mergeCell ref="I102:I106"/>
@@ -8940,7 +8940,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -8965,7 +8964,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
@@ -8997,7 +8995,7 @@
     <row r="10" ht="40" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>・レビュー指摘「通知・日次バッチのテスト」7項目のうち、期日3日前/当日/3日後の通知と対象外計画への非通知は19.リマインダーバッチ、期日超過によるステータス変更は20.自動失効バッチで、既読化に関する2項目は新設した21.通知でそれぞれカバーしています。</t>
+          <t>・レビュー指摘「通知・日次バッチのテスト」7項目のうち、期日3日前/当日/3日後の通知と対象外計画への非通知は19.リマインダーバッチ、期日を過ぎた計画のステータス変更は20.自動失効バッチで、既読化に関する2項目は新設した21.通知でそれぞれカバーしています。</t>
         </is>
       </c>
     </row>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I267"/>
+  <dimension ref="A1:I269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3088,8 +3088,8 @@
     <row r="83">
       <c r="A83" s="4" t="n"/>
       <c r="B83" s="4" t="n"/>
-      <c r="C83" s="5" t="n"/>
-      <c r="D83" s="5" t="n"/>
+      <c r="C83" s="4" t="n"/>
+      <c r="D83" s="4" t="n"/>
       <c r="E83" s="3" t="inlineStr">
         <is>
           <t>4-3-8</t>
@@ -3110,73 +3110,73 @@
           <t>バリデーションエラーではなく403Forbiddenになり、レビューは更新されない（認可チェックが入力チェックより先に行われる）</t>
         </is>
       </c>
-      <c r="I83" s="5" t="n"/>
+      <c r="I83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="n"/>
       <c r="B84" s="4" t="n"/>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>4-4</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>レビュー削除</t>
-        </is>
-      </c>
+      <c r="C84" s="5" t="n"/>
+      <c r="D84" s="5" t="n"/>
       <c r="E84" s="3" t="inlineStr">
         <is>
-          <t>4-4-1</t>
+          <t>4-3-9</t>
         </is>
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>自分が投稿したレビューにのみ「削除」ボタンが表示される</t>
+          <t>他人が投稿したレビューの編集画面には直接アクセスできない</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>1.自分がレビューを投稿した書籍の詳細ページを開く</t>
+          <t>1.他人が投稿したレビューの編集ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H84" s="3" t="inlineStr">
         <is>
-          <t>自分のレビューには「削除」ボタンが表示され、他人のレビューには表示されない</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/Review/ReviewDestroyTest.php</t>
-        </is>
-      </c>
+          <t>403Forbiddenになり、編集ページは表示されない</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="n"/>
       <c r="B85" s="4" t="n"/>
-      <c r="C85" s="4" t="n"/>
-      <c r="D85" s="4" t="n"/>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>4-4</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>レビュー削除</t>
+        </is>
+      </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>4-4-2</t>
+          <t>4-4-1</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>他人が投稿したレビューは削除できない</t>
+          <t>自分が投稿したレビューにのみ「削除」ボタンが表示される</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>1.他人が投稿したレビューに対して、直接レビュー削除のリクエストを送信する</t>
+          <t>1.自分がレビューを投稿した書籍の詳細ページを開く</t>
         </is>
       </c>
       <c r="H85" s="3" t="inlineStr">
         <is>
-          <t>削除できず、エラーになる（403Forbidden）</t>
-        </is>
-      </c>
-      <c r="I85" s="4" t="n"/>
+          <t>自分のレビューには「削除」ボタンが表示され、他人のレビューには表示されない</t>
+        </is>
+      </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/Review/ReviewDestroyTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="n"/>
@@ -3185,180 +3185,172 @@
       <c r="D86" s="4" t="n"/>
       <c r="E86" s="3" t="inlineStr">
         <is>
+          <t>4-4-2</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>他人が投稿したレビューは削除できない</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>1.他人が投稿したレビューに対して、直接レビュー削除のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H86" s="3" t="inlineStr">
+        <is>
+          <t>削除できず、エラーになる（403Forbidden）</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n"/>
+      <c r="B87" s="4" t="n"/>
+      <c r="C87" s="4" t="n"/>
+      <c r="D87" s="4" t="n"/>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
           <t>4-4-3</t>
         </is>
       </c>
-      <c r="F86" s="3" t="inlineStr">
+      <c r="F87" s="3" t="inlineStr">
         <is>
           <t>削除ボタンを押すと確認ダイアログが表示される</t>
         </is>
       </c>
-      <c r="G86" s="3" t="inlineStr">
+      <c r="G87" s="3" t="inlineStr">
         <is>
           <t>1.自分が投稿したレビューの「削除」ボタンを押す</t>
         </is>
       </c>
-      <c r="H86" s="3" t="inlineStr">
+      <c r="H87" s="3" t="inlineStr">
         <is>
           <t>「本当に削除しますか？」という確認ダイアログが表示される</t>
         </is>
       </c>
-      <c r="I86" s="4" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="n"/>
-      <c r="B87" s="5" t="n"/>
-      <c r="C87" s="5" t="n"/>
-      <c r="D87" s="5" t="n"/>
-      <c r="E87" s="3" t="inlineStr">
+      <c r="I87" s="4" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n"/>
+      <c r="B88" s="5" t="n"/>
+      <c r="C88" s="5" t="n"/>
+      <c r="D88" s="5" t="n"/>
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>4-4-4</t>
         </is>
       </c>
-      <c r="F87" s="3" t="inlineStr">
+      <c r="F88" s="3" t="inlineStr">
         <is>
           <t>確認ダイアログでOKを押すとレビューが削除される</t>
         </is>
       </c>
-      <c r="G87" s="3" t="inlineStr">
+      <c r="G88" s="3" t="inlineStr">
         <is>
           <t>1.自分が投稿したレビューの「削除」ボタンを押し、確認ダイアログでOKを押す</t>
         </is>
       </c>
-      <c r="H87" s="3" t="inlineStr">
+      <c r="H88" s="3" t="inlineStr">
         <is>
           <t>レビューが削除され、「レビューを削除しました。」と表示されるとともに一覧から消える</t>
         </is>
       </c>
-      <c r="I87" s="5" t="n"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="I88" s="5" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>ジャンル</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>5-1</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>ジャンル一覧</t>
         </is>
       </c>
-      <c r="E88" s="3" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>5-1-1</t>
         </is>
       </c>
-      <c r="F88" s="3" t="inlineStr">
+      <c r="F89" s="3" t="inlineStr">
         <is>
           <t>ジャンル一覧ページを表示する</t>
         </is>
       </c>
-      <c r="G88" s="3" t="inlineStr">
+      <c r="G89" s="3" t="inlineStr">
         <is>
           <t>1.ジャンル一覧ページを開く</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="H89" s="3" t="inlineStr">
         <is>
           <t>登録されているジャンル名と、そのジャンルに紐づく書籍数が一覧表示される</t>
         </is>
       </c>
-      <c r="I88" s="3" t="inlineStr">
+      <c r="I89" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Genre/GenreIndexTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="n"/>
-      <c r="B89" s="4" t="n"/>
-      <c r="C89" s="4" t="n"/>
-      <c r="D89" s="4" t="n"/>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>5-1-2</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="inlineStr">
-        <is>
-          <t>ジャンルが1件も登録されていない場合の表示を確認する</t>
-        </is>
-      </c>
-      <c r="G89" s="3" t="inlineStr">
-        <is>
-          <t>1.ジャンルが1件も登録されていない状態でジャンル一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H89" s="3" t="inlineStr">
-        <is>
-          <t>「ジャンルが登録されていません。」と表示される</t>
-        </is>
-      </c>
-      <c r="I89" s="4" t="n"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="n"/>
       <c r="B90" s="4" t="n"/>
-      <c r="C90" s="5" t="n"/>
-      <c r="D90" s="5" t="n"/>
+      <c r="C90" s="4" t="n"/>
+      <c r="D90" s="4" t="n"/>
       <c r="E90" s="3" t="inlineStr">
         <is>
-          <t>5-1-3</t>
+          <t>5-1-2</t>
         </is>
       </c>
       <c r="F90" s="3" t="inlineStr">
         <is>
-          <t>未ログインの場合、ジャンル一覧ページにアクセスできない</t>
+          <t>ジャンルが1件も登録されていない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>1.未ログイン状態でジャンル一覧ページのURLに直接アクセスする</t>
+          <t>1.ジャンルが1件も登録されていない状態でジャンル一覧ページを開く</t>
         </is>
       </c>
       <c r="H90" s="3" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="n"/>
+          <t>「ジャンルが登録されていません。」と表示される</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="n"/>
       <c r="B91" s="4" t="n"/>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>5-2</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>ジャンル登録</t>
-        </is>
-      </c>
+      <c r="C91" s="5" t="n"/>
+      <c r="D91" s="5" t="n"/>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>5-2-1</t>
+          <t>5-1-3</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>未ログインの場合、ジャンル登録ページにアクセスできない</t>
+          <t>未ログインの場合、ジャンル一覧ページにアクセスできない</t>
         </is>
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>1.未ログイン状態でジャンル登録ページのURLに直接アクセスする</t>
+          <t>1.未ログイン状態でジャンル一覧ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H91" s="3" t="inlineStr">
@@ -3366,39 +3358,46 @@
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I91" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/Genre/GenreStoreTest.php</t>
-        </is>
-      </c>
+      <c r="I91" s="5" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="n"/>
       <c r="B92" s="4" t="n"/>
-      <c r="C92" s="4" t="n"/>
-      <c r="D92" s="4" t="n"/>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>ジャンル登録</t>
+        </is>
+      </c>
       <c r="E92" s="3" t="inlineStr">
         <is>
-          <t>5-2-2</t>
+          <t>5-2-1</t>
         </is>
       </c>
       <c r="F92" s="3" t="inlineStr">
         <is>
-          <t>ジャンル名が入力されていない場合、バリデーションメッセージが表示される</t>
+          <t>未ログインの場合、ジャンル登録ページにアクセスできない</t>
         </is>
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンル登録ページを開く
-2.ジャンル名を入力せずに登録ボタンを押す</t>
+          <t>1.未ログイン状態でジャンル登録ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H92" s="3" t="inlineStr">
         <is>
-          <t>「ジャンル名を入力してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I92" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I92" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/Genre/GenreStoreTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="n"/>
@@ -3407,23 +3406,23 @@
       <c r="D93" s="4" t="n"/>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>5-2-3</t>
+          <t>5-2-2</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>ジャンル名が21文字以上の場合、バリデーションメッセージが表示される</t>
+          <t>ジャンル名が入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
           <t>1.ジャンル登録ページを開く
-2.21文字以上のジャンル名を入力し、登録ボタンを押す</t>
+2.ジャンル名を入力せずに登録ボタンを押す</t>
         </is>
       </c>
       <c r="H93" s="3" t="inlineStr">
         <is>
-          <t>「ジャンル名は20文字以内で入力してください」というバリデーションメッセージが表示される</t>
+          <t>「ジャンル名を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I93" s="4" t="n"/>
@@ -3435,23 +3434,23 @@
       <c r="D94" s="4" t="n"/>
       <c r="E94" s="3" t="inlineStr">
         <is>
-          <t>5-2-4</t>
+          <t>5-2-3</t>
         </is>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>既に登録されているジャンル名の場合、バリデーションメッセージが表示される</t>
+          <t>ジャンル名が21文字以上の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
           <t>1.ジャンル登録ページを開く
-2.既に登録済みのジャンル名を入力し、登録ボタンを押す</t>
+2.21文字以上のジャンル名を入力し、登録ボタンを押す</t>
         </is>
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>「このジャンル名はすでに登録されています」というバリデーションメッセージが表示される</t>
+          <t>「ジャンル名は20文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I94" s="4" t="n"/>
@@ -3459,96 +3458,97 @@
     <row r="95">
       <c r="A95" s="4" t="n"/>
       <c r="B95" s="4" t="n"/>
-      <c r="C95" s="5" t="n"/>
-      <c r="D95" s="5" t="n"/>
+      <c r="C95" s="4" t="n"/>
+      <c r="D95" s="4" t="n"/>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>5-2-5</t>
+          <t>5-2-4</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
-          <t>正しくジャンル名が入力されている場合、ジャンルが登録される</t>
+          <t>既に登録されているジャンル名の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
           <t>1.ジャンル登録ページを開く
-2.未登録のジャンル名を入力し、登録ボタンを押す</t>
+2.既に登録済みのジャンル名を入力し、登録ボタンを押す</t>
         </is>
       </c>
       <c r="H95" s="3" t="inlineStr">
         <is>
-          <t>ジャンルが登録され、ジャンル一覧画面に遷移し「ジャンルを登録しました。」と表示される</t>
-        </is>
-      </c>
-      <c r="I95" s="5" t="n"/>
+          <t>「このジャンル名はすでに登録されています」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="n"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n"/>
       <c r="B96" s="4" t="n"/>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>5-3</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>ジャンル詳細</t>
-        </is>
-      </c>
+      <c r="C96" s="5" t="n"/>
+      <c r="D96" s="5" t="n"/>
       <c r="E96" s="3" t="inlineStr">
         <is>
-          <t>5-3-1</t>
+          <t>5-2-5</t>
         </is>
       </c>
       <c r="F96" s="3" t="inlineStr">
         <is>
-          <t>ジャンルに紐づく書籍が一覧表示される</t>
+          <t>正しくジャンル名が入力されている場合、ジャンルが登録される</t>
         </is>
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>1.書籍が紐づいているジャンルの詳細ページを開く</t>
+          <t>1.ジャンル登録ページを開く
+2.未登録のジャンル名を入力し、登録ボタンを押す</t>
         </is>
       </c>
       <c r="H96" s="3" t="inlineStr">
         <is>
-          <t>そのジャンルに紐づく書籍が一覧表示される</t>
-        </is>
-      </c>
-      <c r="I96" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/Genre/GenreShowTest.php</t>
-        </is>
-      </c>
+          <t>ジャンルが登録され、ジャンル一覧画面に遷移し「ジャンルを登録しました。」と表示される</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="4" t="n"/>
       <c r="B97" s="4" t="n"/>
-      <c r="C97" s="4" t="n"/>
-      <c r="D97" s="4" t="n"/>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>5-3</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>ジャンル詳細</t>
+        </is>
+      </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>5-3-2</t>
+          <t>5-3-1</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>ジャンルに紐づく書籍が1件もない場合の表示を確認する</t>
+          <t>ジャンルに紐づく書籍が一覧表示される</t>
         </is>
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>1.書籍が1件も紐づいていないジャンルの詳細ページを開く</t>
+          <t>1.書籍が紐づいているジャンルの詳細ページを開く</t>
         </is>
       </c>
       <c r="H97" s="3" t="inlineStr">
         <is>
-          <t>「このジャンルの書籍はまだ登録されていません。」と表示される</t>
-        </is>
-      </c>
-      <c r="I97" s="4" t="n"/>
+          <t>そのジャンルに紐づく書籍が一覧表示される</t>
+        </is>
+      </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/Genre/GenreShowTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="n"/>
@@ -3557,23 +3557,22 @@
       <c r="D98" s="4" t="n"/>
       <c r="E98" s="3" t="inlineStr">
         <is>
-          <t>5-3-3</t>
+          <t>5-3-2</t>
         </is>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
-          <t>ジャンル一覧から遷移した場合、「ジャンル一覧に戻る」リンクが表示される</t>
+          <t>ジャンルに紐づく書籍が1件もない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンル一覧ページでジャンル名のリンクを押し、ジャンル詳細ページを開く
-2.画面左上の戻るリンクを確認する</t>
+          <t>1.書籍が1件も紐づいていないジャンルの詳細ページを開く</t>
         </is>
       </c>
       <c r="H98" s="3" t="inlineStr">
         <is>
-          <t>「← ジャンル一覧に戻る」と表示され、押すとジャンル一覧ページへ遷移する（遷移元の指定がない場合も同様）</t>
+          <t>「このジャンルの書籍はまだ登録されていません。」と表示される</t>
         </is>
       </c>
       <c r="I98" s="4" t="n"/>
@@ -3585,23 +3584,23 @@
       <c r="D99" s="4" t="n"/>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>5-3-4</t>
+          <t>5-3-3</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>マイ読書レポートから遷移した場合、「マイ読書レポートに戻る」リンクが表示される</t>
+          <t>ジャンル一覧から遷移した場合、「ジャンル一覧に戻る」リンクが表示される</t>
         </is>
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>1.マイ読書レポートページの「ジャンル別評価傾向 TOP5」でジャンルを押し、ジャンル詳細ページを開く
+          <t>1.ジャンル一覧ページでジャンル名のリンクを押し、ジャンル詳細ページを開く
 2.画面左上の戻るリンクを確認する</t>
         </is>
       </c>
       <c r="H99" s="3" t="inlineStr">
         <is>
-          <t>「← マイ読書レポートに戻る」と表示され、押すとマイ読書レポートページへ遷移する</t>
+          <t>「← ジャンル一覧に戻る」と表示され、押すとジャンル一覧ページへ遷移する（遷移元の指定がない場合も同様）</t>
         </is>
       </c>
       <c r="I99" s="4" t="n"/>
@@ -3613,23 +3612,23 @@
       <c r="D100" s="4" t="n"/>
       <c r="E100" s="3" t="inlineStr">
         <is>
-          <t>5-3-5</t>
+          <t>5-3-4</t>
         </is>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>ページを送っても、遷移元に応じた「戻る」リンクが維持される</t>
+          <t>マイ読書レポートから遷移した場合、「マイ読書レポートに戻る」リンクが表示される</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>1.書籍が11件以上紐づくジャンルの詳細ページを、マイ読書レポートから開く
-2.ページネーションで2ページ目を開く</t>
+          <t>1.マイ読書レポートページの「ジャンル別評価傾向 TOP5」でジャンルを押し、ジャンル詳細ページを開く
+2.画面左上の戻るリンクを確認する</t>
         </is>
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>2ページ目でも「← マイ読書レポートに戻る」と表示される</t>
+          <t>「← マイ読書レポートに戻る」と表示され、押すとマイ読書レポートページへ遷移する</t>
         </is>
       </c>
       <c r="I100" s="4" t="n"/>
@@ -3637,96 +3636,97 @@
     <row r="101">
       <c r="A101" s="4" t="n"/>
       <c r="B101" s="4" t="n"/>
-      <c r="C101" s="5" t="n"/>
-      <c r="D101" s="5" t="n"/>
+      <c r="C101" s="4" t="n"/>
+      <c r="D101" s="4" t="n"/>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>5-3-6</t>
+          <t>5-3-5</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>ジャンルに紐づく書籍が登録日時の新しい順に表示される</t>
+          <t>ページを送っても、遷移元に応じた「戻る」リンクが維持される</t>
         </is>
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>1.登録日時の異なる複数の書籍を、同じジャンルに紐づける
-2.ジャンル詳細ページを開く</t>
+          <t>1.書籍が11件以上紐づくジャンルの詳細ページを、マイ読書レポートから開く
+2.ページネーションで2ページ目を開く</t>
         </is>
       </c>
       <c r="H101" s="3" t="inlineStr">
         <is>
-          <t>書籍一覧と同じく、書籍の登録日時の新しい順に表示される（ジャンルへの紐づけ順には関係しない）</t>
-        </is>
-      </c>
-      <c r="I101" s="5" t="n"/>
+          <t>2ページ目でも「← マイ読書レポートに戻る」と表示される</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="n"/>
     </row>
     <row r="102">
       <c r="A102" s="4" t="n"/>
       <c r="B102" s="4" t="n"/>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>5-4</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>ジャンル編集</t>
-        </is>
-      </c>
+      <c r="C102" s="5" t="n"/>
+      <c r="D102" s="5" t="n"/>
       <c r="E102" s="3" t="inlineStr">
         <is>
-          <t>5-4-1</t>
+          <t>5-3-6</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>未ログインの場合、ジャンル編集ページにアクセスできない</t>
+          <t>ジャンルに紐づく書籍が登録日時の新しい順に表示される</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>1.未ログイン状態でジャンル編集ページのURLに直接アクセスする</t>
+          <t>1.登録日時の異なる複数の書籍を、同じジャンルに紐づける
+2.ジャンル詳細ページを開く</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I102" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/Genre/GenreUpdateTest.php</t>
-        </is>
-      </c>
+          <t>書籍一覧と同じく、書籍の登録日時の新しい順に表示される（ジャンルへの紐づけ順には関係しない）</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="4" t="n"/>
       <c r="B103" s="4" t="n"/>
-      <c r="C103" s="4" t="n"/>
-      <c r="D103" s="4" t="n"/>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>5-4</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>ジャンル編集</t>
+        </is>
+      </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>5-4-2</t>
+          <t>5-4-1</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>編集画面を開くと現在のジャンル名が初期表示される</t>
+          <t>未ログインの場合、ジャンル編集ページにアクセスできない</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンル編集ページを開く</t>
+          <t>1.未ログイン状態でジャンル編集ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>ジャンル名の入力欄に現在登録されているジャンル名が表示される</t>
-        </is>
-      </c>
-      <c r="I103" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/Genre/GenreUpdateTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="n"/>
@@ -3735,23 +3735,22 @@
       <c r="D104" s="4" t="n"/>
       <c r="E104" s="3" t="inlineStr">
         <is>
-          <t>5-4-3</t>
+          <t>5-4-2</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>ジャンル名が入力されていない場合、バリデーションメッセージが表示される</t>
+          <t>編集画面を開くと現在のジャンル名が初期表示される</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンル編集ページを開く
-2.ジャンル名を空にして更新ボタンを押す</t>
+          <t>1.ジャンル編集ページを開く</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>「ジャンル名を入力してください」というバリデーションメッセージが表示される</t>
+          <t>ジャンル名の入力欄に現在登録されているジャンル名が表示される</t>
         </is>
       </c>
       <c r="I104" s="4" t="n"/>
@@ -3763,23 +3762,23 @@
       <c r="D105" s="4" t="n"/>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>5-4-4</t>
+          <t>5-4-3</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>既に登録されている他のジャンル名に変更しようとした場合、バリデーションメッセージが表示される</t>
+          <t>ジャンル名が入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
           <t>1.ジャンル編集ページを開く
-2.他のジャンルで既に使われているジャンル名に変更し、更新ボタンを押す</t>
+2.ジャンル名を空にして更新ボタンを押す</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>「このジャンル名はすでに登録されています」というバリデーションメッセージが表示される</t>
+          <t>「ジャンル名を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I105" s="4" t="n"/>
@@ -3787,197 +3786,198 @@
     <row r="106">
       <c r="A106" s="4" t="n"/>
       <c r="B106" s="4" t="n"/>
-      <c r="C106" s="5" t="n"/>
-      <c r="D106" s="5" t="n"/>
+      <c r="C106" s="4" t="n"/>
+      <c r="D106" s="4" t="n"/>
       <c r="E106" s="3" t="inlineStr">
         <is>
-          <t>5-4-5</t>
+          <t>5-4-4</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>正しくジャンル名が入力されている場合、ジャンル情報が更新される</t>
+          <t>既に登録されている他のジャンル名に変更しようとした場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
           <t>1.ジャンル編集ページを開く
-2.ジャンル名を正しく変更し、更新ボタンを押す</t>
+2.他のジャンルで既に使われているジャンル名に変更し、更新ボタンを押す</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>ジャンル情報が更新され、ジャンル一覧画面に遷移し「ジャンルを更新しました。」と表示される</t>
-        </is>
-      </c>
-      <c r="I106" s="5" t="n"/>
+          <t>「このジャンル名はすでに登録されています」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="4" t="n"/>
       <c r="B107" s="4" t="n"/>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>5-5</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>ジャンル削除</t>
-        </is>
-      </c>
+      <c r="C107" s="5" t="n"/>
+      <c r="D107" s="5" t="n"/>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>5-5-1</t>
+          <t>5-4-5</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>未ログインの場合、ジャンルを削除できない</t>
+          <t>正しくジャンル名が入力されている場合、ジャンル情報が更新される</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>1.未ログイン状態でジャンル削除のリクエストを直接送信する</t>
+          <t>1.ジャンル編集ページを開く
+2.ジャンル名を正しく変更し、更新ボタンを押す</t>
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>削除できず、ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I107" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/Genre/GenreDestroyTest.php</t>
-        </is>
-      </c>
+          <t>ジャンル情報が更新され、ジャンル一覧画面に遷移し「ジャンルを更新しました。」と表示される</t>
+        </is>
+      </c>
+      <c r="I107" s="5" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="4" t="n"/>
       <c r="B108" s="4" t="n"/>
-      <c r="C108" s="4" t="n"/>
-      <c r="D108" s="4" t="n"/>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>5-5</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>ジャンル削除</t>
+        </is>
+      </c>
       <c r="E108" s="3" t="inlineStr">
         <is>
+          <t>5-5-1</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="inlineStr">
+        <is>
+          <t>未ログインの場合、ジャンルを削除できない</t>
+        </is>
+      </c>
+      <c r="G108" s="3" t="inlineStr">
+        <is>
+          <t>1.未ログイン状態でジャンル削除のリクエストを直接送信する</t>
+        </is>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>削除できず、ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I108" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/Genre/GenreDestroyTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n"/>
+      <c r="B109" s="4" t="n"/>
+      <c r="C109" s="4" t="n"/>
+      <c r="D109" s="4" t="n"/>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
           <t>5-5-2</t>
         </is>
       </c>
-      <c r="F108" s="3" t="inlineStr">
+      <c r="F109" s="3" t="inlineStr">
         <is>
           <t>紐づく書籍が存在するジャンルは削除できない</t>
         </is>
       </c>
-      <c r="G108" s="3" t="inlineStr">
+      <c r="G109" s="3" t="inlineStr">
         <is>
           <t>1.書籍が紐づいているジャンルの削除ボタンを押し、確認ダイアログでOKを押す</t>
         </is>
       </c>
-      <c r="H108" s="3" t="inlineStr">
+      <c r="H109" s="3" t="inlineStr">
         <is>
           <t>「このジャンルは書籍に紐づいているため削除できません。」と表示され、ジャンルは削除されない</t>
         </is>
       </c>
-      <c r="I108" s="4" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="5" t="n"/>
-      <c r="B109" s="5" t="n"/>
-      <c r="C109" s="5" t="n"/>
-      <c r="D109" s="5" t="n"/>
-      <c r="E109" s="3" t="inlineStr">
+      <c r="I109" s="4" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="5" t="n"/>
+      <c r="B110" s="5" t="n"/>
+      <c r="C110" s="5" t="n"/>
+      <c r="D110" s="5" t="n"/>
+      <c r="E110" s="3" t="inlineStr">
         <is>
           <t>5-5-3</t>
         </is>
       </c>
-      <c r="F109" s="3" t="inlineStr">
+      <c r="F110" s="3" t="inlineStr">
         <is>
           <t>紐づく書籍が存在しないジャンルは削除できる</t>
         </is>
       </c>
-      <c r="G109" s="3" t="inlineStr">
+      <c r="G110" s="3" t="inlineStr">
         <is>
           <t>1.書籍が紐づいていないジャンルの削除ボタンを押し、確認ダイアログでOKを押す</t>
         </is>
       </c>
-      <c r="H109" s="3" t="inlineStr">
+      <c r="H110" s="3" t="inlineStr">
         <is>
           <t>ジャンルが削除され、「ジャンルを削除しました。」と表示される</t>
         </is>
       </c>
-      <c r="I109" s="5" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="I110" s="5" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>お気に入り</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>6-1</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>お気に入り一覧表示</t>
         </is>
       </c>
-      <c r="E110" s="3" t="inlineStr">
+      <c r="E111" s="3" t="inlineStr">
         <is>
           <t>6-1-1</t>
         </is>
       </c>
-      <c r="F110" s="3" t="inlineStr">
+      <c r="F111" s="3" t="inlineStr">
         <is>
           <t>お気に入りに登録した書籍が一覧表示される</t>
         </is>
       </c>
-      <c r="G110" s="3" t="inlineStr">
+      <c r="G111" s="3" t="inlineStr">
         <is>
           <t>1.書籍をお気に入り登録した状態でお気に入り一覧ページを開く</t>
         </is>
       </c>
-      <c r="H110" s="3" t="inlineStr">
+      <c r="H111" s="3" t="inlineStr">
         <is>
           <t>お気に入り登録した書籍が一覧表示される</t>
         </is>
       </c>
-      <c r="I110" s="3" t="inlineStr">
+      <c r="I111" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Favorite/FavoriteIndexTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="4" t="n"/>
-      <c r="B111" s="4" t="n"/>
-      <c r="C111" s="4" t="n"/>
-      <c r="D111" s="4" t="n"/>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>6-1-2</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="inlineStr">
-        <is>
-          <t>お気に入りが1件も登録されていない場合の表示を確認する</t>
-        </is>
-      </c>
-      <c r="G111" s="3" t="inlineStr">
-        <is>
-          <t>1.お気に入りを1件も登録していない状態でお気に入り一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>「お気に入りに登録された書籍はありません。」と表示され、書籍一覧ページへのリンクが表示される</t>
-        </is>
-      </c>
-      <c r="I111" s="4" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="n"/>
@@ -3986,22 +3986,22 @@
       <c r="D112" s="4" t="n"/>
       <c r="E112" s="3" t="inlineStr">
         <is>
-          <t>6-1-3</t>
+          <t>6-1-2</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
         <is>
-          <t>未ログインの場合、お気に入り一覧ページにアクセスできない</t>
+          <t>お気に入りが1件も登録されていない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>1.未ログイン状態でお気に入り一覧ページのURLに直接アクセスする</t>
+          <t>1.お気に入りを1件も登録していない状態でお気に入り一覧ページを開く</t>
         </is>
       </c>
       <c r="H112" s="3" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
+          <t>「お気に入りに登録された書籍はありません。」と表示され、書籍一覧ページへのリンクが表示される</t>
         </is>
       </c>
       <c r="I112" s="4" t="n"/>
@@ -4009,303 +4009,302 @@
     <row r="113">
       <c r="A113" s="4" t="n"/>
       <c r="B113" s="4" t="n"/>
-      <c r="C113" s="5" t="n"/>
-      <c r="D113" s="5" t="n"/>
+      <c r="C113" s="4" t="n"/>
+      <c r="D113" s="4" t="n"/>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>6-1-4</t>
+          <t>6-1-3</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
         <is>
-          <t>お気に入りに登録した日時の新しい順に表示される</t>
+          <t>未ログインの場合、お気に入り一覧ページにアクセスできない</t>
         </is>
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>1.複数の書籍を、時間をずらしてお気に入り登録する
-2.お気に入り一覧ページを開く</t>
+          <t>1.未ログイン状態でお気に入り一覧ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H113" s="3" t="inlineStr">
         <is>
-          <t>お気に入りに登録した日時の新しい順に表示される（書籍自体の登録日時の順ではない）</t>
-        </is>
-      </c>
-      <c r="I113" s="5" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="n"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="n"/>
       <c r="B114" s="4" t="n"/>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>6-2</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>お気に入りの登録・解除</t>
-        </is>
-      </c>
+      <c r="C114" s="5" t="n"/>
+      <c r="D114" s="5" t="n"/>
       <c r="E114" s="3" t="inlineStr">
         <is>
-          <t>6-2-1</t>
+          <t>6-1-4</t>
         </is>
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>未登録の書籍をお気に入りに登録できる</t>
+          <t>お気に入りに登録した日時の新しい順に表示される</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>1.お気に入り未登録の書籍の詳細ページ（またはお気に入り一覧）を開く
-2.お気に入りボタン（ハートアイコン）を押す</t>
+          <t>1.複数の書籍を、時間をずらしてお気に入り登録する
+2.お気に入り一覧ページを開く</t>
         </is>
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>お気に入りに登録され、アイコンが登録済みの表示(塗りつぶし)に切り替わる</t>
-        </is>
-      </c>
-      <c r="I114" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/Favorite/FavoriteToggleTest.php</t>
-        </is>
-      </c>
+          <t>お気に入りに登録した日時の新しい順に表示される（書籍自体の登録日時の順ではない）</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="n"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="n"/>
       <c r="B115" s="4" t="n"/>
-      <c r="C115" s="4" t="n"/>
-      <c r="D115" s="4" t="n"/>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>6-2</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>お気に入りの登録・解除</t>
+        </is>
+      </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
+          <t>6-2-1</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>未登録の書籍をお気に入りに登録できる</t>
+        </is>
+      </c>
+      <c r="G115" s="3" t="inlineStr">
+        <is>
+          <t>1.お気に入り未登録の書籍の詳細ページ（またはお気に入り一覧）を開く
+2.お気に入りボタン（ハートアイコン）を押す</t>
+        </is>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>お気に入りに登録され、アイコンが登録済みの表示(塗りつぶし)に切り替わる</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/Favorite/FavoriteToggleTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="n"/>
+      <c r="B116" s="4" t="n"/>
+      <c r="C116" s="4" t="n"/>
+      <c r="D116" s="4" t="n"/>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
           <t>6-2-2</t>
         </is>
       </c>
-      <c r="F115" s="3" t="inlineStr">
+      <c r="F116" s="3" t="inlineStr">
         <is>
           <t>登録済みの書籍のお気に入りを解除できる</t>
         </is>
       </c>
-      <c r="G115" s="3" t="inlineStr">
+      <c r="G116" s="3" t="inlineStr">
         <is>
           <t>1.お気に入り登録済みの書籍の詳細ページ（またはお気に入り一覧）を開く
 2.お気に入りボタン（ハートアイコン）を押す</t>
         </is>
       </c>
-      <c r="H115" s="3" t="inlineStr">
+      <c r="H116" s="3" t="inlineStr">
         <is>
           <t>お気に入りが解除され、アイコンが未登録の表示に切り替わる（お気に入り一覧では一覧から消える）</t>
         </is>
       </c>
-      <c r="I115" s="4" t="n"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="5" t="n"/>
-      <c r="B116" s="5" t="n"/>
-      <c r="C116" s="5" t="n"/>
-      <c r="D116" s="5" t="n"/>
-      <c r="E116" s="3" t="inlineStr">
+      <c r="I116" s="4" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="n"/>
+      <c r="B117" s="5" t="n"/>
+      <c r="C117" s="5" t="n"/>
+      <c r="D117" s="5" t="n"/>
+      <c r="E117" s="3" t="inlineStr">
         <is>
           <t>6-2-3</t>
         </is>
       </c>
-      <c r="F116" s="3" t="inlineStr">
+      <c r="F117" s="3" t="inlineStr">
         <is>
           <t>未ログインの場合、お気に入りボタンの代わりにログインへの案内が表示される</t>
         </is>
       </c>
-      <c r="G116" s="3" t="inlineStr">
+      <c r="G117" s="3" t="inlineStr">
         <is>
           <t>1.未ログイン状態で書籍詳細ページを開く</t>
         </is>
       </c>
-      <c r="H116" s="3" t="inlineStr">
+      <c r="H117" s="3" t="inlineStr">
         <is>
           <t>お気に入りボタンの代わりに、押すとログインページへ遷移するリンクが表示される</t>
         </is>
       </c>
-      <c r="I116" s="5" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="I117" s="5" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
         <is>
           <t>いいね</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>7-1</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
         <is>
           <t>レビューへのいいねの切り替え</t>
         </is>
       </c>
-      <c r="E117" s="3" t="inlineStr">
+      <c r="E118" s="3" t="inlineStr">
         <is>
           <t>7-1-1</t>
         </is>
       </c>
-      <c r="F117" s="3" t="inlineStr">
+      <c r="F118" s="3" t="inlineStr">
         <is>
           <t>未いいねの状態からいいねできる</t>
         </is>
       </c>
-      <c r="G117" s="3" t="inlineStr">
+      <c r="G118" s="3" t="inlineStr">
         <is>
           <t>1.まだいいねしていないレビューの「いいね」ボタンを押す</t>
         </is>
       </c>
-      <c r="H117" s="3" t="inlineStr">
+      <c r="H118" s="3" t="inlineStr">
         <is>
           <t>「いいね済み」の表示に切り替わり、いいね数が1件増える</t>
         </is>
       </c>
-      <c r="I117" s="3" t="inlineStr">
+      <c r="I118" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Like/LikeToggleTest.php</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="4" t="n"/>
-      <c r="B118" s="4" t="n"/>
-      <c r="C118" s="4" t="n"/>
-      <c r="D118" s="4" t="n"/>
-      <c r="E118" s="3" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="4" t="n"/>
+      <c r="B119" s="4" t="n"/>
+      <c r="C119" s="4" t="n"/>
+      <c r="D119" s="4" t="n"/>
+      <c r="E119" s="3" t="inlineStr">
         <is>
           <t>7-1-2</t>
         </is>
       </c>
-      <c r="F118" s="3" t="inlineStr">
+      <c r="F119" s="3" t="inlineStr">
         <is>
           <t>いいね済みの状態からいいねを解除できる</t>
         </is>
       </c>
-      <c r="G118" s="3" t="inlineStr">
+      <c r="G119" s="3" t="inlineStr">
         <is>
           <t>1.既にいいね済みのレビューの「いいね済み」ボタンを押す</t>
         </is>
       </c>
-      <c r="H118" s="3" t="inlineStr">
+      <c r="H119" s="3" t="inlineStr">
         <is>
           <t>「いいね」の表示に切り替わり、いいね数が1件減る</t>
         </is>
       </c>
-      <c r="I118" s="4" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="n"/>
-      <c r="B119" s="5" t="n"/>
-      <c r="C119" s="5" t="n"/>
-      <c r="D119" s="5" t="n"/>
-      <c r="E119" s="3" t="inlineStr">
+      <c r="I119" s="4" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="n"/>
+      <c r="B120" s="5" t="n"/>
+      <c r="C120" s="5" t="n"/>
+      <c r="D120" s="5" t="n"/>
+      <c r="E120" s="3" t="inlineStr">
         <is>
           <t>7-1-3</t>
         </is>
       </c>
-      <c r="F119" s="3" t="inlineStr">
+      <c r="F120" s="3" t="inlineStr">
         <is>
           <t>未ログインの場合、いいねボタンを押せない</t>
         </is>
       </c>
-      <c r="G119" s="3" t="inlineStr">
+      <c r="G120" s="3" t="inlineStr">
         <is>
           <t>1.未ログイン状態で書籍詳細ページを開く
 2.いいねに関する直接リクエストを送信する</t>
         </is>
       </c>
-      <c r="H119" s="3" t="inlineStr">
+      <c r="H120" s="3" t="inlineStr">
         <is>
           <t>未ログインの場合はいいねボタンが操作できず、直接リクエストを送ってもログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I119" s="5" t="n"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
+      <c r="I120" s="5" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>ランキング</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>8-1</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
         <is>
           <t>ランキングページ表示</t>
         </is>
       </c>
-      <c r="E120" s="3" t="inlineStr">
+      <c r="E121" s="3" t="inlineStr">
         <is>
           <t>8-1-1</t>
         </is>
       </c>
-      <c r="F120" s="3" t="inlineStr">
+      <c r="F121" s="3" t="inlineStr">
         <is>
           <t>レビューの平均評価が高い順に書籍が表示される</t>
         </is>
       </c>
-      <c r="G120" s="3" t="inlineStr">
+      <c r="G121" s="3" t="inlineStr">
         <is>
           <t>1.複数の書籍にレビューを投稿する
 2.ランキングページを開く</t>
         </is>
       </c>
-      <c r="H120" s="3" t="inlineStr">
+      <c r="H121" s="3" t="inlineStr">
         <is>
           <t>レビューが投稿されている書籍が、平均評価の高い順に上位10件表示される</t>
         </is>
       </c>
-      <c r="I120" s="3" t="inlineStr">
+      <c r="I121" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Ranking/RankingIndexTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="4" t="n"/>
-      <c r="B121" s="4" t="n"/>
-      <c r="C121" s="4" t="n"/>
-      <c r="D121" s="4" t="n"/>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>8-1-2</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="inlineStr">
-        <is>
-          <t>平均評価が同じ場合、レビュー件数が多い順に表示される</t>
-        </is>
-      </c>
-      <c r="G121" s="3" t="inlineStr">
-        <is>
-          <t>1.平均評価が同じになる書籍を複数用意する（レビュー件数を変える）
-2.ランキングページを開く</t>
-        </is>
-      </c>
-      <c r="H121" s="3" t="inlineStr">
-        <is>
-          <t>平均評価が同じ書籍同士は、レビュー件数が多い順（さらに同じ場合は出版日が新しい順）に表示される</t>
-        </is>
-      </c>
-      <c r="I121" s="4" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n"/>
@@ -4314,130 +4313,129 @@
       <c r="D122" s="4" t="n"/>
       <c r="E122" s="3" t="inlineStr">
         <is>
+          <t>8-1-2</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="inlineStr">
+        <is>
+          <t>平均評価が同じ場合、レビュー件数が多い順に表示される</t>
+        </is>
+      </c>
+      <c r="G122" s="3" t="inlineStr">
+        <is>
+          <t>1.平均評価が同じになる書籍を複数用意する（レビュー件数を変える）
+2.ランキングページを開く</t>
+        </is>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>平均評価が同じ書籍同士は、レビュー件数が多い順（さらに同じ場合は出版日が新しい順）に表示される</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="n"/>
+      <c r="B123" s="4" t="n"/>
+      <c r="C123" s="4" t="n"/>
+      <c r="D123" s="4" t="n"/>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
           <t>8-1-3</t>
         </is>
       </c>
-      <c r="F122" s="3" t="inlineStr">
+      <c r="F123" s="3" t="inlineStr">
         <is>
           <t>レビューが投稿された書籍が1件もない場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G122" s="3" t="inlineStr">
+      <c r="G123" s="3" t="inlineStr">
         <is>
           <t>1.どの書籍にもレビューが投稿されていない状態でランキングページを開く</t>
         </is>
       </c>
-      <c r="H122" s="3" t="inlineStr">
+      <c r="H123" s="3" t="inlineStr">
         <is>
           <t>「まだレビューが投稿された書籍がありません。」と表示される</t>
         </is>
       </c>
-      <c r="I122" s="4" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="5" t="n"/>
-      <c r="B123" s="5" t="n"/>
-      <c r="C123" s="5" t="n"/>
-      <c r="D123" s="5" t="n"/>
-      <c r="E123" s="3" t="inlineStr">
+      <c r="I123" s="4" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="n"/>
+      <c r="B124" s="5" t="n"/>
+      <c r="C124" s="5" t="n"/>
+      <c r="D124" s="5" t="n"/>
+      <c r="E124" s="3" t="inlineStr">
         <is>
           <t>8-1-4</t>
         </is>
       </c>
-      <c r="F123" s="3" t="inlineStr">
+      <c r="F124" s="3" t="inlineStr">
         <is>
           <t>未ログインの状態でもランキングページを閲覧できる</t>
         </is>
       </c>
-      <c r="G123" s="3" t="inlineStr">
+      <c r="G124" s="3" t="inlineStr">
         <is>
           <t>1.未ログイン状態でランキングページを開く</t>
         </is>
       </c>
-      <c r="H123" s="3" t="inlineStr">
+      <c r="H124" s="3" t="inlineStr">
         <is>
           <t>ランキングが表示される</t>
         </is>
       </c>
-      <c r="I123" s="5" t="n"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
+      <c r="I124" s="5" t="n"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>認証</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>9-1</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>会員登録</t>
         </is>
       </c>
-      <c r="E124" s="3" t="inlineStr">
+      <c r="E125" s="3" t="inlineStr">
         <is>
           <t>9-1-1</t>
         </is>
       </c>
-      <c r="F124" s="3" t="inlineStr">
+      <c r="F125" s="3" t="inlineStr">
         <is>
           <t>名前が入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G124" s="3" t="inlineStr">
+      <c r="G125" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.名前を入力せずに他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H124" s="3" t="inlineStr">
+      <c r="H125" s="3" t="inlineStr">
         <is>
           <t>「お名前を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I124" s="3" t="inlineStr">
+      <c r="I125" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Auth/RegisterTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="4" t="n"/>
-      <c r="B125" s="4" t="n"/>
-      <c r="C125" s="4" t="n"/>
-      <c r="D125" s="4" t="n"/>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>9-1-2</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="inlineStr">
-        <is>
-          <t>名前が21文字以上の場合、バリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>1.会員登録ページを開く
-2.名前を21文字以上入力し、他の必要項目を入力する
-3.登録ボタンを押す</t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="inlineStr">
-        <is>
-          <t>「お名前は20文字以内で入力してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I125" s="4" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="n"/>
@@ -4446,24 +4444,24 @@
       <c r="D126" s="4" t="n"/>
       <c r="E126" s="3" t="inlineStr">
         <is>
-          <t>9-1-3</t>
+          <t>9-1-2</t>
         </is>
       </c>
       <c r="F126" s="3" t="inlineStr">
         <is>
-          <t>メールアドレスが入力されていない場合、バリデーションメッセージが表示される</t>
+          <t>名前が21文字以上の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.メールアドレスを入力せずに他の必要項目を入力する
+2.名前を21文字以上入力し、他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H126" s="3" t="inlineStr">
         <is>
-          <t>「メールアドレスを入力してください」というバリデーションメッセージが表示される</t>
+          <t>「お名前は20文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I126" s="4" t="n"/>
@@ -4475,24 +4473,24 @@
       <c r="D127" s="4" t="n"/>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>9-1-4</t>
+          <t>9-1-3</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>メールアドレスがメール形式でない場合、バリデーションメッセージが表示される</t>
+          <t>メールアドレスが入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.「abc」のようなメール形式でないメールアドレスと他の必要項目を入力する
+2.メールアドレスを入力せずに他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H127" s="3" t="inlineStr">
         <is>
-          <t>「メールアドレスはメール形式で入力してください」というバリデーションメッセージが表示される</t>
+          <t>「メールアドレスを入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I127" s="4" t="n"/>
@@ -4504,24 +4502,24 @@
       <c r="D128" s="4" t="n"/>
       <c r="E128" s="3" t="inlineStr">
         <is>
-          <t>9-1-5</t>
+          <t>9-1-4</t>
         </is>
       </c>
       <c r="F128" s="3" t="inlineStr">
         <is>
-          <t>メールアドレスが256文字以上の場合、バリデーションメッセージが表示される</t>
+          <t>メールアドレスがメール形式でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.256文字以上のメールアドレスと他の必要項目を入力する
+2.「abc」のようなメール形式でないメールアドレスと他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H128" s="3" t="inlineStr">
         <is>
-          <t>「メールアドレスは255文字以内で入力してください」というバリデーションメッセージが表示される</t>
+          <t>「メールアドレスはメール形式で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I128" s="4" t="n"/>
@@ -4533,24 +4531,24 @@
       <c r="D129" s="4" t="n"/>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>9-1-6</t>
+          <t>9-1-5</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
         <is>
-          <t>既に登録されているメールアドレスの場合、バリデーションメッセージが表示される</t>
+          <t>メールアドレスが256文字以上の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.既に会員登録済みのメールアドレスと他の必要項目を入力する
+2.256文字以上のメールアドレスと他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H129" s="3" t="inlineStr">
         <is>
-          <t>「このメールアドレスはすでに登録されています」というバリデーションメッセージが表示される</t>
+          <t>「メールアドレスは255文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I129" s="4" t="n"/>
@@ -4562,24 +4560,24 @@
       <c r="D130" s="4" t="n"/>
       <c r="E130" s="3" t="inlineStr">
         <is>
-          <t>9-1-7</t>
+          <t>9-1-6</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
         <is>
-          <t>パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
+          <t>既に登録されているメールアドレスの場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.パスワードを入力せずに他の必要項目を入力する
+2.既に会員登録済みのメールアドレスと他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H130" s="3" t="inlineStr">
         <is>
-          <t>「パスワードを入力してください」というバリデーションメッセージが表示される</t>
+          <t>「このメールアドレスはすでに登録されています」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I130" s="4" t="n"/>
@@ -4591,24 +4589,24 @@
       <c r="D131" s="4" t="n"/>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>9-1-8</t>
+          <t>9-1-7</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
-          <t>パスワードが7文字以下の場合、バリデーションメッセージが表示される</t>
+          <t>パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.7文字以下のパスワードと他の必要項目を入力する
+2.パスワードを入力せずに他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H131" s="3" t="inlineStr">
         <is>
-          <t>「パスワードは8文字以上で入力してください」というバリデーションメッセージが表示される</t>
+          <t>「パスワードを入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I131" s="4" t="n"/>
@@ -4620,24 +4618,24 @@
       <c r="D132" s="4" t="n"/>
       <c r="E132" s="3" t="inlineStr">
         <is>
-          <t>9-1-9</t>
+          <t>9-1-8</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>パスワードが21文字以上の場合、バリデーションメッセージが表示される</t>
+          <t>パスワードが7文字以下の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.21文字以上のパスワードと他の必要項目を入力する
+2.7文字以下のパスワードと他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H132" s="3" t="inlineStr">
         <is>
-          <t>「パスワードは20文字以内で入力してください」というバリデーションメッセージが表示される</t>
+          <t>「パスワードは8文字以上で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I132" s="4" t="n"/>
@@ -4649,24 +4647,24 @@
       <c r="D133" s="4" t="n"/>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>9-1-10</t>
+          <t>9-1-9</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
-          <t>確認用パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
+          <t>パスワードが21文字以上の場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
-2.確認用パスワードを入力せずに他の必要項目を入力する
+2.21文字以上のパスワードと他の必要項目を入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
       <c r="H133" s="3" t="inlineStr">
         <is>
-          <t>「確認用パスワードを入力してください」というバリデーションメッセージが表示される</t>
+          <t>「パスワードは20文字以内で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I133" s="4" t="n"/>
@@ -4678,126 +4676,126 @@
       <c r="D134" s="4" t="n"/>
       <c r="E134" s="3" t="inlineStr">
         <is>
+          <t>9-1-10</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="inlineStr">
+        <is>
+          <t>確認用パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="G134" s="3" t="inlineStr">
+        <is>
+          <t>1.会員登録ページを開く
+2.確認用パスワードを入力せずに他の必要項目を入力する
+3.登録ボタンを押す</t>
+        </is>
+      </c>
+      <c r="H134" s="3" t="inlineStr">
+        <is>
+          <t>「確認用パスワードを入力してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="n"/>
+      <c r="B135" s="4" t="n"/>
+      <c r="C135" s="4" t="n"/>
+      <c r="D135" s="4" t="n"/>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
           <t>9-1-11</t>
         </is>
       </c>
-      <c r="F134" s="3" t="inlineStr">
+      <c r="F135" s="3" t="inlineStr">
         <is>
           <t>パスワードが確認用パスワードと一致しない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G134" s="3" t="inlineStr">
+      <c r="G135" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.確認用パスワードと異なるパスワードを入力し、他の必要項目も入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H134" s="3" t="inlineStr">
+      <c r="H135" s="3" t="inlineStr">
         <is>
           <t>「パスワードが一致しません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I134" s="4" t="n"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="4" t="n"/>
-      <c r="B135" s="4" t="n"/>
-      <c r="C135" s="5" t="n"/>
-      <c r="D135" s="5" t="n"/>
-      <c r="E135" s="3" t="inlineStr">
+      <c r="I135" s="4" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="n"/>
+      <c r="B136" s="4" t="n"/>
+      <c r="C136" s="5" t="n"/>
+      <c r="D136" s="5" t="n"/>
+      <c r="E136" s="3" t="inlineStr">
         <is>
           <t>9-1-12</t>
         </is>
       </c>
-      <c r="F135" s="3" t="inlineStr">
+      <c r="F136" s="3" t="inlineStr">
         <is>
           <t>全ての項目が正しく入力されている場合、会員登録が完了する</t>
         </is>
       </c>
-      <c r="G135" s="3" t="inlineStr">
+      <c r="G136" s="3" t="inlineStr">
         <is>
           <t>1.会員登録ページを開く
 2.全ての必要項目を正しく入力する
 3.登録ボタンを押す</t>
         </is>
       </c>
-      <c r="H135" s="3" t="inlineStr">
+      <c r="H136" s="3" t="inlineStr">
         <is>
           <t>会員情報が登録され、ログイン状態で書籍一覧画面（トップページ）に遷移する</t>
         </is>
       </c>
-      <c r="I135" s="5" t="n"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="4" t="n"/>
-      <c r="B136" s="4" t="n"/>
-      <c r="C136" s="3" t="inlineStr">
+      <c r="I136" s="5" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="4" t="n"/>
+      <c r="B137" s="4" t="n"/>
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>9-2</t>
         </is>
       </c>
-      <c r="D136" s="3" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>ログイン機能</t>
         </is>
       </c>
-      <c r="E136" s="3" t="inlineStr">
+      <c r="E137" s="3" t="inlineStr">
         <is>
           <t>9-2-1</t>
         </is>
       </c>
-      <c r="F136" s="3" t="inlineStr">
+      <c r="F137" s="3" t="inlineStr">
         <is>
           <t>メールアドレスが入力されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G136" s="3" t="inlineStr">
+      <c r="G137" s="3" t="inlineStr">
         <is>
           <t>1.ログインページを開く
 2.メールアドレスを入力せずに他の必要項目を入力する
 3.ログインボタンを押す</t>
         </is>
       </c>
-      <c r="H136" s="3" t="inlineStr">
+      <c r="H137" s="3" t="inlineStr">
         <is>
           <t>「メールアドレスを入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I136" s="3" t="inlineStr">
+      <c r="I137" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Auth/LoginTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="4" t="n"/>
-      <c r="B137" s="4" t="n"/>
-      <c r="C137" s="4" t="n"/>
-      <c r="D137" s="4" t="n"/>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>9-2-2</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="inlineStr">
-        <is>
-          <t>メールアドレスがメール形式でない場合、バリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="G137" s="3" t="inlineStr">
-        <is>
-          <t>1.ログインページを開く
-2.「abc」のようなメール形式でないメールアドレスと他の必要項目を入力する
-3.ログインボタンを押す</t>
-        </is>
-      </c>
-      <c r="H137" s="3" t="inlineStr">
-        <is>
-          <t>「メールアドレスはメール形式で入力してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I137" s="4" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="n"/>
@@ -4806,24 +4804,24 @@
       <c r="D138" s="4" t="n"/>
       <c r="E138" s="3" t="inlineStr">
         <is>
-          <t>9-2-3</t>
+          <t>9-2-2</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
         <is>
-          <t>パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
+          <t>メールアドレスがメール形式でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
           <t>1.ログインページを開く
-2.パスワードを入力せずに他の必要項目を入力する
+2.「abc」のようなメール形式でないメールアドレスと他の必要項目を入力する
 3.ログインボタンを押す</t>
         </is>
       </c>
       <c r="H138" s="3" t="inlineStr">
         <is>
-          <t>「パスワードを入力してください」というバリデーションメッセージが表示される</t>
+          <t>「メールアドレスはメール形式で入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I138" s="4" t="n"/>
@@ -4835,266 +4833,267 @@
       <c r="D139" s="4" t="n"/>
       <c r="E139" s="3" t="inlineStr">
         <is>
+          <t>9-2-3</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="inlineStr">
+        <is>
+          <t>パスワードが入力されていない場合、バリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="G139" s="3" t="inlineStr">
+        <is>
+          <t>1.ログインページを開く
+2.パスワードを入力せずに他の必要項目を入力する
+3.ログインボタンを押す</t>
+        </is>
+      </c>
+      <c r="H139" s="3" t="inlineStr">
+        <is>
+          <t>「パスワードを入力してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="n"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="n"/>
+      <c r="B140" s="4" t="n"/>
+      <c r="C140" s="4" t="n"/>
+      <c r="D140" s="4" t="n"/>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
           <t>9-2-4</t>
         </is>
       </c>
-      <c r="F139" s="3" t="inlineStr">
+      <c r="F140" s="3" t="inlineStr">
         <is>
           <t>入力情報が登録されている会員情報と一致しない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="G139" s="3" t="inlineStr">
+      <c r="G140" s="3" t="inlineStr">
         <is>
           <t>1.ログインページを開く
 2.登録されていないメールアドレス、または誤ったパスワードを入力する
 3.ログインボタンを押す</t>
         </is>
       </c>
-      <c r="H139" s="3" t="inlineStr">
+      <c r="H140" s="3" t="inlineStr">
         <is>
           <t>「会員情報が登録されていません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
-      <c r="I139" s="4" t="n"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="4" t="n"/>
-      <c r="B140" s="4" t="n"/>
-      <c r="C140" s="5" t="n"/>
-      <c r="D140" s="5" t="n"/>
-      <c r="E140" s="3" t="inlineStr">
+      <c r="I140" s="4" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="n"/>
+      <c r="B141" s="4" t="n"/>
+      <c r="C141" s="5" t="n"/>
+      <c r="D141" s="5" t="n"/>
+      <c r="E141" s="3" t="inlineStr">
         <is>
           <t>9-2-5</t>
         </is>
       </c>
-      <c r="F140" s="3" t="inlineStr">
+      <c r="F141" s="3" t="inlineStr">
         <is>
           <t>正しい情報が入力された場合、ログイン処理が実行される</t>
         </is>
       </c>
-      <c r="G140" s="3" t="inlineStr">
+      <c r="G141" s="3" t="inlineStr">
         <is>
           <t>1.ログインページを開く
 2.登録済みの正しいメールアドレス・パスワードを入力する
 3.ログインボタンを押す</t>
         </is>
       </c>
-      <c r="H140" s="3" t="inlineStr">
+      <c r="H141" s="3" t="inlineStr">
         <is>
           <t>ログイン処理が実行され、書籍一覧画面（トップページ）に遷移する</t>
         </is>
       </c>
-      <c r="I140" s="5" t="n"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="5" t="n"/>
-      <c r="B141" s="5" t="n"/>
-      <c r="C141" s="3" t="inlineStr">
+      <c r="I141" s="5" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="5" t="n"/>
+      <c r="B142" s="5" t="n"/>
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t>9-3</t>
         </is>
       </c>
-      <c r="D141" s="3" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>ログアウト機能</t>
         </is>
       </c>
-      <c r="E141" s="3" t="inlineStr">
+      <c r="E142" s="3" t="inlineStr">
         <is>
           <t>9-3-1</t>
         </is>
       </c>
-      <c r="F141" s="3" t="inlineStr">
+      <c r="F142" s="3" t="inlineStr">
         <is>
           <t>ログアウトができる</t>
         </is>
       </c>
-      <c r="G141" s="3" t="inlineStr">
+      <c r="G142" s="3" t="inlineStr">
         <is>
           <t>1.ユーザーがログインする
 2.ログアウトボタンを押す</t>
         </is>
       </c>
-      <c r="H141" s="3" t="inlineStr">
+      <c r="H142" s="3" t="inlineStr">
         <is>
           <t>ログアウト処理が実行され、ログインページに遷移する</t>
         </is>
       </c>
-      <c r="I141" s="3" t="inlineStr">
+      <c r="I142" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/Auth/LogoutTest.php</t>
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="3" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B142" s="3" t="inlineStr">
+      <c r="B143" s="3" t="inlineStr">
         <is>
           <t>公開API</t>
         </is>
       </c>
-      <c r="C142" s="3" t="inlineStr">
+      <c r="C143" s="3" t="inlineStr">
         <is>
           <t>10-1</t>
         </is>
       </c>
-      <c r="D142" s="3" t="inlineStr">
+      <c r="D143" s="3" t="inlineStr">
         <is>
           <t>ユーザー情報取得API(/api/user)</t>
         </is>
       </c>
-      <c r="E142" s="3" t="inlineStr">
+      <c r="E143" s="3" t="inlineStr">
         <is>
           <t>10-1-1</t>
         </is>
       </c>
-      <c r="F142" s="3" t="inlineStr">
+      <c r="F143" s="3" t="inlineStr">
         <is>
           <t>未認証でアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G142" s="3" t="inlineStr">
+      <c r="G143" s="3" t="inlineStr">
         <is>
           <t>1.トークンやセッションを持たない状態でGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H142" s="3" t="inlineStr">
+      <c r="H143" s="3" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
         </is>
       </c>
-      <c r="I142" s="3" t="inlineStr">
+      <c r="I143" s="3" t="inlineStr">
         <is>
           <t>tests/Feature/PublicApi/UserApiTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="4" t="n"/>
-      <c r="B143" s="4" t="n"/>
-      <c r="C143" s="4" t="n"/>
-      <c r="D143" s="4" t="n"/>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>10-1-2</t>
-        </is>
-      </c>
-      <c r="F143" s="3" t="inlineStr">
-        <is>
-          <t>有効なSanctumトークンでアクセスするとログインユーザーの情報が返る</t>
-        </is>
-      </c>
-      <c r="G143" s="3" t="inlineStr">
-        <is>
-          <t>1.ユーザーのpersonal access tokenを発行する
-2.そのトークンをBearerヘッダーに付与してGET /api/userにアクセスする</t>
-        </is>
-      </c>
-      <c r="H143" s="3" t="inlineStr">
-        <is>
-          <t>200が返り、該当ユーザーのid・name・emailを含むJSONが返る</t>
-        </is>
-      </c>
-      <c r="I143" s="4" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="n"/>
       <c r="B144" s="4" t="n"/>
-      <c r="C144" s="5" t="n"/>
-      <c r="D144" s="5" t="n"/>
+      <c r="C144" s="4" t="n"/>
+      <c r="D144" s="4" t="n"/>
       <c r="E144" s="3" t="inlineStr">
         <is>
-          <t>10-1-3</t>
+          <t>10-1-2</t>
         </is>
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>レスポンスにパスワードなど非公開情報が含まれない</t>
+          <t>有効なSanctumトークンでアクセスするとログインユーザーの情報が返る</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>1.有効なトークンでGET /api/userにアクセスする</t>
+          <t>1.ユーザーのpersonal access tokenを発行する
+2.そのトークンをBearerヘッダーに付与してGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>レスポンスJSONにpassword・remember_tokenが含まれない</t>
-        </is>
-      </c>
-      <c r="I144" s="5" t="n"/>
+          <t>200が返り、該当ユーザーのid・name・emailを含むJSONが返る</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="n"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n"/>
       <c r="B145" s="4" t="n"/>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>10-2</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>書籍一覧取得API(GET /api/v1/books)</t>
-        </is>
-      </c>
+      <c r="C145" s="5" t="n"/>
+      <c r="D145" s="5" t="n"/>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>10-2-1</t>
+          <t>10-1-3</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>認証なしでもアクセスでき、書籍一覧が返る</t>
+          <t>レスポンスにパスワードなど非公開情報が含まれない</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>1.書籍を複数用意する
-2.認証情報を付与せずGET /api/v1/booksにアクセスする</t>
+          <t>1.有効なトークンでGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>200が返り、data・links・metaを含むJSONが返る</t>
-        </is>
-      </c>
-      <c r="I145" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiIndexTest.php</t>
-        </is>
-      </c>
+          <t>レスポンスJSONにpassword・remember_tokenが含まれない</t>
+        </is>
+      </c>
+      <c r="I145" s="5" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n"/>
       <c r="B146" s="4" t="n"/>
-      <c r="C146" s="4" t="n"/>
-      <c r="D146" s="4" t="n"/>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>10-2</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>書籍一覧取得API(GET /api/v1/books)</t>
+        </is>
+      </c>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>10-2-2</t>
+          <t>10-2-1</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>各書籍にジャンル・平均評価・レビュー件数が含まれる</t>
+          <t>認証なしでもアクセスでき、書籍一覧が返る</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンルと、評価4・5のレビューを持つ書籍を用意する
-2.GET /api/v1/booksにアクセスする</t>
+          <t>1.書籍を複数用意する
+2.認証情報を付与せずGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>dataの各書籍にgenres(id・name)、average_rating(4.5)、review_count(2)が含まれ、reviews(レビュー本文)は含まれない</t>
-        </is>
-      </c>
-      <c r="I146" s="4" t="n"/>
+          <t>200が返り、data・links・metaを含むJSONが返る</t>
+        </is>
+      </c>
+      <c r="I146" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiIndexTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n"/>
@@ -5103,23 +5102,23 @@
       <c r="D147" s="4" t="n"/>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>10-2-3</t>
+          <t>10-2-2</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>レビューが無い書籍はaverage_ratingがnull、review_countが0になる</t>
+          <t>各書籍にジャンル・平均評価・レビュー件数が含まれる</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>1.レビューが1件もない書籍を用意する
+          <t>1.ジャンルと、評価4・5のレビューを持つ書籍を用意する
 2.GET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>その書籍のaverage_ratingがnull、review_countが0で返る</t>
+          <t>dataの各書籍にgenres(id・name)、average_rating(4.5)、review_count(2)が含まれ、reviews(レビュー本文)は含まれない</t>
         </is>
       </c>
       <c r="I147" s="4" t="n"/>
@@ -5131,23 +5130,23 @@
       <c r="D148" s="4" t="n"/>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>10-2-4</t>
+          <t>10-2-3</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>新しい順(登録日時の降順、同一なら idの降順)で返る</t>
+          <t>レビューが無い書籍はaverage_ratingがnull、review_countが0になる</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>1.登録日時の異なる書籍を複数用意する
+          <t>1.レビューが1件もない書籍を用意する
 2.GET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>新しく登録された書籍から順に返る</t>
+          <t>その書籍のaverage_ratingがnull、review_countが0で返る</t>
         </is>
       </c>
       <c r="I148" s="4" t="n"/>
@@ -5159,23 +5158,23 @@
       <c r="D149" s="4" t="n"/>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>10-2-5</t>
+          <t>10-2-4</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>keywordでタイトル・著者名の部分一致検索ができる</t>
+          <t>新しい順(登録日時の降順、同一なら idの降順)で返る</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>1.タイトルにキーワードを含む書籍、著者名にキーワードを含む書籍、含まない書籍を用意する
-2.keywordを指定してGET /api/v1/booksにアクセスする</t>
+          <t>1.登録日時の異なる書籍を複数用意する
+2.GET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>タイトルまたは著者名にキーワードを含む書籍のみが返る</t>
+          <t>新しく登録された書籍から順に返る</t>
         </is>
       </c>
       <c r="I149" s="4" t="n"/>
@@ -5187,23 +5186,23 @@
       <c r="D150" s="4" t="n"/>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>10-2-6</t>
+          <t>10-2-5</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>genreでジャンルIDによる絞り込みができる</t>
+          <t>keywordでタイトル・著者名の部分一致検索ができる</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>1.異なるジャンルの書籍を用意する
-2.genreにジャンルIDを指定してGET /api/v1/booksにアクセスする</t>
+          <t>1.タイトルにキーワードを含む書籍、著者名にキーワードを含む書籍、含まない書籍を用意する
+2.keywordを指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>指定したジャンルに属する書籍のみが返る</t>
+          <t>タイトルまたは著者名にキーワードを含む書籍のみが返る</t>
         </is>
       </c>
       <c r="I150" s="4" t="n"/>
@@ -5215,23 +5214,23 @@
       <c r="D151" s="4" t="n"/>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>10-2-7</t>
+          <t>10-2-6</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>pageでページを移動できる(1ページ10件固定)</t>
+          <t>genreでジャンルIDによる絞り込みができる</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>1.11件の書籍を用意する
-2.pageを指定せずに、およびpage=2を指定してGET /api/v1/booksにアクセスする</t>
+          <t>1.異なるジャンルの書籍を用意する
+2.genreにジャンルIDを指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>pageなしでは1ページ目の10件、page=2では残りの1件が返り、meta・linksにページ情報が反映される</t>
+          <t>指定したジャンルに属する書籍のみが返る</t>
         </is>
       </c>
       <c r="I151" s="4" t="n"/>
@@ -5239,191 +5238,191 @@
     <row r="152">
       <c r="A152" s="4" t="n"/>
       <c r="B152" s="4" t="n"/>
-      <c r="C152" s="5" t="n"/>
-      <c r="D152" s="5" t="n"/>
+      <c r="C152" s="4" t="n"/>
+      <c r="D152" s="4" t="n"/>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>10-2-8</t>
+          <t>10-2-7</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>不正なクエリパラメータを指定すると422が返る</t>
+          <t>pageでページを移動できる(1ページ10件固定)</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>1.genreに存在しないID、pageに0をそれぞれ指定してGET /api/v1/booksにアクセスする(Accept: application/json)</t>
+          <t>1.11件の書籍を用意する
+2.pageを指定せずに、およびpage=2を指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「指定されたジャンルは存在しません」「ページ番号は1以上の値で指定してください」が返る</t>
-        </is>
-      </c>
-      <c r="I152" s="5" t="n"/>
+          <t>pageなしでは1ページ目の10件、page=2では残りの1件が返り、meta・linksにページ情報が反映される</t>
+        </is>
+      </c>
+      <c r="I152" s="4" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n"/>
       <c r="B153" s="4" t="n"/>
-      <c r="C153" s="3" t="inlineStr">
-        <is>
-          <t>10-3</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>書籍詳細取得API(GET /api/v1/books/{book})</t>
-        </is>
-      </c>
+      <c r="C153" s="5" t="n"/>
+      <c r="D153" s="5" t="n"/>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>10-3-1</t>
+          <t>10-2-8</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>認証なしでもアクセスでき、書籍の詳細が返る</t>
+          <t>不正なクエリパラメータを指定すると422が返る</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンルとレビューを持つ書籍を用意する
-2.認証情報を付与せずGET /api/v1/books/{book}にアクセスする</t>
+          <t>1.genreに存在しないID、pageに0をそれぞれ指定してGET /api/v1/booksにアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>200が返り、書籍情報・genres・average_rating・review_countを含むJSONが返る</t>
-        </is>
-      </c>
-      <c r="I153" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiShowTest.php</t>
-        </is>
-      </c>
+          <t>422が返り、「指定されたジャンルは存在しません」「ページ番号は1以上の値で指定してください」が返る</t>
+        </is>
+      </c>
+      <c r="I153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="n"/>
       <c r="B154" s="4" t="n"/>
-      <c r="C154" s="4" t="n"/>
-      <c r="D154" s="4" t="n"/>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>10-3</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>書籍詳細取得API(GET /api/v1/books/{book})</t>
+        </is>
+      </c>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>10-3-2</t>
+          <t>10-3-1</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>レビュー(投稿者名・評価・コメント・投稿日時)が新しい順に含まれる</t>
+          <t>認証なしでもアクセスでき、書籍の詳細が返る</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>1.異なる日時に投稿された複数のレビューを持つ書籍を用意する
-2.GET /api/v1/books/{book}にアクセスする</t>
+          <t>1.ジャンルとレビューを持つ書籍を用意する
+2.認証情報を付与せずGET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>reviewsにuser_name・rating・comment・created_atが含まれ、投稿日時の新しい順に並ぶ</t>
-        </is>
-      </c>
-      <c r="I154" s="4" t="n"/>
+          <t>200が返り、書籍情報・genres・average_rating・review_countを含むJSONが返る</t>
+        </is>
+      </c>
+      <c r="I154" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiShowTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n"/>
       <c r="B155" s="4" t="n"/>
-      <c r="C155" s="5" t="n"/>
-      <c r="D155" s="5" t="n"/>
+      <c r="C155" s="4" t="n"/>
+      <c r="D155" s="4" t="n"/>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>10-3-3</t>
+          <t>10-3-2</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>存在しないIDを指定すると404が返る</t>
+          <t>レビュー(投稿者名・評価・コメント・投稿日時)が新しい順に含まれる</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>1.存在しない書籍IDでGET /api/v1/books/{book}にアクセスする</t>
+          <t>1.異なる日時に投稿された複数のレビューを持つ書籍を用意する
+2.GET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
-        </is>
-      </c>
-      <c r="I155" s="5" t="n"/>
+          <t>reviewsにuser_name・rating・comment・created_atが含まれ、投稿日時の新しい順に並ぶ</t>
+        </is>
+      </c>
+      <c r="I155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n"/>
       <c r="B156" s="4" t="n"/>
-      <c r="C156" s="3" t="inlineStr">
-        <is>
-          <t>10-4</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
-        <is>
-          <t>書籍登録API(POST /api/v1/books)</t>
-        </is>
-      </c>
+      <c r="C156" s="5" t="n"/>
+      <c r="D156" s="5" t="n"/>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>10-4-1</t>
+          <t>10-3-3</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>認証なしでアクセスすると401が返る</t>
+          <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>1.認証情報を付与せずPOST /api/v1/booksにアクセスする(Accept: application/json)</t>
+          <t>1.存在しない書籍IDでGET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録されない</t>
-        </is>
-      </c>
-      <c r="I156" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiStoreTest.php</t>
-        </is>
-      </c>
+          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
+        </is>
+      </c>
+      <c r="I156" s="5" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n"/>
       <c r="B157" s="4" t="n"/>
-      <c r="C157" s="4" t="n"/>
-      <c r="D157" s="4" t="n"/>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>10-4</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>書籍登録API(POST /api/v1/books)</t>
+        </is>
+      </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>10-4-2</t>
+          <t>10-4-1</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>有効なトークンで書籍を登録できる</t>
+          <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーのトークンを発行する
-2.必要項目を指定し、Bearerトークンを付与してPOST /api/v1/booksにアクセスする</t>
+          <t>1.認証情報を付与せずPOST /api/v1/booksにアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>201が返り、登録内容がJSONで返る。書籍がDBに保存される</t>
-        </is>
-      </c>
-      <c r="I157" s="4" t="n"/>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録されない</t>
+        </is>
+      </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiStoreTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n"/>
@@ -5432,22 +5431,23 @@
       <c r="D158" s="4" t="n"/>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>10-4-3</t>
+          <t>10-4-2</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>登録者(user_id)は、リクエストの値ではなく認証ユーザーになる</t>
+          <t>有効なトークンで書籍を登録できる</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>1.他のユーザーのIDをuser_idに含めて、トークンを付与しPOST /api/v1/booksにアクセスする</t>
+          <t>1.ユーザーのトークンを発行する
+2.必要項目を指定し、Bearerトークンを付与してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>登録された書籍のuser_idは、トークンの持ち主(認証ユーザー)のIDになる</t>
+          <t>201が返り、登録内容がJSONで返る。書籍がDBに保存される</t>
         </is>
       </c>
       <c r="I158" s="4" t="n"/>
@@ -5459,22 +5459,22 @@
       <c r="D159" s="4" t="n"/>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>10-4-4</t>
+          <t>10-4-3</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>選択したジャンルが書籍に紐づけられる</t>
+          <t>登録者(user_id)は、リクエストの値ではなく認証ユーザーになる</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>1.複数のジャンルIDをgenresに指定してPOST /api/v1/booksにアクセスする</t>
+          <t>1.他のユーザーのIDをuser_idに含めて、トークンを付与しPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>中間テーブル(book_genre)に指定したジャンルが保存され、レスポンスのgenresにも含まれる</t>
+          <t>登録された書籍のuser_idは、トークンの持ち主(認証ユーザー)のIDになる</t>
         </is>
       </c>
       <c r="I159" s="4" t="n"/>
@@ -5486,22 +5486,22 @@
       <c r="D160" s="4" t="n"/>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>10-4-5</t>
+          <t>10-4-4</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>必須項目(title・author・genres)が未入力の場合、422が返る</t>
+          <t>選択したジャンルが書籍に紐づけられる</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>1.title・author・genresを指定せずにPOST /api/v1/booksにアクセスする</t>
+          <t>1.複数のジャンルIDをgenresに指定してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「書籍タイトルを入力してください」「著者名を入力してください」「ジャンルを1つ以上選択してください」が返る</t>
+          <t>中間テーブル(book_genre)に指定したジャンルが保存され、レスポンスのgenresにも含まれる</t>
         </is>
       </c>
       <c r="I160" s="4" t="n"/>
@@ -5513,23 +5513,22 @@
       <c r="D161" s="4" t="n"/>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>10-4-6</t>
+          <t>10-4-5</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>ISBNが13桁の数字でない、または登録済みの場合、422が返る</t>
+          <t>必須項目(title・author・genres)が未入力の場合、422が返る</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>1.ISBNに13桁でない値を指定してPOST /api/v1/booksにアクセスする
-2.登録済みのISBNを指定して同様にアクセスする</t>
+          <t>1.title・author・genresを指定せずにPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「ISBNは13桁の数字で入力してください」「このISBNはすでに登録されています」が返る</t>
+          <t>422が返り、「書籍タイトルを入力してください」「著者名を入力してください」「ジャンルを1つ以上選択してください」が返る</t>
         </is>
       </c>
       <c r="I161" s="4" t="n"/>
@@ -5537,96 +5536,96 @@
     <row r="162">
       <c r="A162" s="4" t="n"/>
       <c r="B162" s="4" t="n"/>
-      <c r="C162" s="5" t="n"/>
-      <c r="D162" s="5" t="n"/>
+      <c r="C162" s="4" t="n"/>
+      <c r="D162" s="4" t="n"/>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>10-4-7</t>
+          <t>10-4-6</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>存在しないジャンルIDを指定すると422が返る</t>
+          <t>ISBNが13桁の数字でない、または登録済みの場合、422が返る</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>1.genresに存在しないジャンルIDを指定してPOST /api/v1/booksにアクセスする</t>
+          <t>1.ISBNに13桁でない値を指定してPOST /api/v1/booksにアクセスする
+2.登録済みのISBNを指定して同様にアクセスする</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「選択されたジャンルは存在しません」が返る</t>
-        </is>
-      </c>
-      <c r="I162" s="5" t="n"/>
+          <t>422が返り、「ISBNは13桁の数字で入力してください」「このISBNはすでに登録されています」が返る</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n"/>
       <c r="B163" s="4" t="n"/>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>10-5</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>書籍更新API(PUT /api/v1/books/{book})</t>
-        </is>
-      </c>
+      <c r="C163" s="5" t="n"/>
+      <c r="D163" s="5" t="n"/>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>10-5-1</t>
+          <t>10-4-7</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>認証なしでアクセスすると401が返る</t>
+          <t>存在しないジャンルIDを指定すると422が返る</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>1.認証情報を付与せずPUT /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
+          <t>1.genresに存在しないジャンルIDを指定してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は更新されない</t>
-        </is>
-      </c>
-      <c r="I163" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiUpdateTest.php</t>
-        </is>
-      </c>
+          <t>422が返り、「選択されたジャンルは存在しません」が返る</t>
+        </is>
+      </c>
+      <c r="I163" s="5" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n"/>
       <c r="B164" s="4" t="n"/>
-      <c r="C164" s="4" t="n"/>
-      <c r="D164" s="4" t="n"/>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>10-5</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>書籍更新API(PUT /api/v1/books/{book})</t>
+        </is>
+      </c>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>10-5-2</t>
+          <t>10-5-1</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>自分が登録した書籍を更新できる</t>
+          <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーが登録した書籍を用意する
-2.そのユーザーのトークンを付与し、変更内容・ジャンルを指定してPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.認証情報を付与せずPUT /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>200が返り、更新後の内容がJSONで返る。DBの書籍情報とジャンルの紐づけが更新される</t>
-        </is>
-      </c>
-      <c r="I164" s="4" t="n"/>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I164" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiUpdateTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n"/>
@@ -5635,23 +5634,23 @@
       <c r="D165" s="4" t="n"/>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>10-5-3</t>
+          <t>10-5-2</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>自分の書籍のISBNを変更せずに更新しても、ISBNの重複エラーにならない</t>
+          <t>自分が登録した書籍を更新できる</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーが登録した書籍(ISBNあり)を用意する
-2.ISBNを変えずに他の項目を変更してPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.ユーザーが登録した書籍を用意する
+2.そのユーザーのトークンを付与し、変更内容・ジャンルを指定してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>200が返り、更新できる</t>
+          <t>200が返り、更新後の内容がJSONで返る。DBの書籍情報とジャンルの紐づけが更新される</t>
         </is>
       </c>
       <c r="I165" s="4" t="n"/>
@@ -5663,23 +5662,23 @@
       <c r="D166" s="4" t="n"/>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>10-5-4</t>
+          <t>10-5-3</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>他のユーザーが登録した書籍は更新できない</t>
+          <t>自分の書籍のISBNを変更せずに更新しても、ISBNの重複エラーにならない</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>1.他のユーザーが登録した書籍を用意する
-2.別のユーザーのトークンを付与してPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.ユーザーが登録した書籍(ISBNあり)を用意する
+2.ISBNを変えずに他の項目を変更してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は更新されない</t>
+          <t>200が返り、更新できる</t>
         </is>
       </c>
       <c r="I166" s="4" t="n"/>
@@ -5691,22 +5690,23 @@
       <c r="D167" s="4" t="n"/>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>10-5-5</t>
+          <t>10-5-4</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>存在しないIDを指定すると404が返る</t>
+          <t>他のユーザーが登録した書籍は更新できない</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>1.トークンを付与し、存在しない書籍IDでPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.他のユーザーが登録した書籍を用意する
+2.別のユーザーのトークンを付与してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
+          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は更新されない</t>
         </is>
       </c>
       <c r="I167" s="4" t="n"/>
@@ -5718,22 +5718,22 @@
       <c r="D168" s="4" t="n"/>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>10-5-6</t>
+          <t>10-5-5</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>入力内容が不正な場合、422が返る</t>
+          <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>1.自分の書籍に対し、titleを空にしてPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.トークンを付与し、存在しない書籍IDでPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「書籍タイトルを入力してください」が返る。書籍は更新されない</t>
+          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
         </is>
       </c>
       <c r="I168" s="4" t="n"/>
@@ -5741,97 +5741,96 @@
     <row r="169">
       <c r="A169" s="4" t="n"/>
       <c r="B169" s="4" t="n"/>
-      <c r="C169" s="5" t="n"/>
-      <c r="D169" s="5" t="n"/>
+      <c r="C169" s="4" t="n"/>
+      <c r="D169" s="4" t="n"/>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>10-5-7</t>
+          <t>10-5-6</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>他のユーザーが登録した書籍に対して不正な入力で更新しようとしても、422ではなく403が返る</t>
+          <t>入力内容が不正な場合、422が返る</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>1.他のユーザーが登録した書籍を用意する
-2.別のユーザーのトークンを付与し、タイトルを空にするなど不正な内容でPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.自分の書籍に対し、titleを空にしてPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る（入力チェックより先に権限が判定される）。書籍は更新されない</t>
-        </is>
-      </c>
-      <c r="I169" s="5" t="n"/>
+          <t>422が返り、「書籍タイトルを入力してください」が返る。書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n"/>
       <c r="B170" s="4" t="n"/>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>10-6</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>書籍削除API(DELETE /api/v1/books/{book})</t>
-        </is>
-      </c>
+      <c r="C170" s="5" t="n"/>
+      <c r="D170" s="5" t="n"/>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>10-6-1</t>
+          <t>10-5-7</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>認証なしでアクセスすると401が返る</t>
+          <t>他のユーザーが登録した書籍に対して不正な入力で更新しようとしても、422ではなく403が返る</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>1.認証情報を付与せずDELETE /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
+          <t>1.他のユーザーが登録した書籍を用意する
+2.別のユーザーのトークンを付与し、タイトルを空にするなど不正な内容でPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は削除されない</t>
-        </is>
-      </c>
-      <c r="I170" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiDestroyTest.php</t>
-        </is>
-      </c>
+          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る（入力チェックより先に権限が判定される）。書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I170" s="5" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
       <c r="B171" s="4" t="n"/>
-      <c r="C171" s="4" t="n"/>
-      <c r="D171" s="4" t="n"/>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>10-6</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>書籍削除API(DELETE /api/v1/books/{book})</t>
+        </is>
+      </c>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>10-6-2</t>
+          <t>10-6-1</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>自分が登録した書籍を削除できる</t>
+          <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーが登録した書籍を用意する
-2.そのユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
+          <t>1.認証情報を付与せずDELETE /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>204が返り(レスポンスボディなし)、書籍がDBから削除される</t>
-        </is>
-      </c>
-      <c r="I171" s="4" t="n"/>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は削除されない</t>
+        </is>
+      </c>
+      <c r="I171" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiDestroyTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n"/>
@@ -5840,23 +5839,23 @@
       <c r="D172" s="4" t="n"/>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>10-6-3</t>
+          <t>10-6-2</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>書籍を削除すると、関連するデータも一緒に削除される</t>
+          <t>自分が登録した書籍を削除できる</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンルの紐づけ・レビュー・お気に入り・レビューへのいいねを持つ書籍を用意する
-2.所有者のトークンでDELETE /api/v1/books/{book}にアクセスする</t>
+          <t>1.ユーザーが登録した書籍を用意する
+2.そのユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>book_genre・reviews・favorites・review_likesの該当データも削除される</t>
+          <t>204が返り(レスポンスボディなし)、書籍がDBから削除される</t>
         </is>
       </c>
       <c r="I172" s="4" t="n"/>
@@ -5868,129 +5867,129 @@
       <c r="D173" s="4" t="n"/>
       <c r="E173" s="3" t="inlineStr">
         <is>
+          <t>10-6-3</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="inlineStr">
+        <is>
+          <t>書籍を削除すると、関連するデータも一緒に削除される</t>
+        </is>
+      </c>
+      <c r="G173" s="3" t="inlineStr">
+        <is>
+          <t>1.ジャンルの紐づけ・レビュー・お気に入り・レビューへのいいねを持つ書籍を用意する
+2.所有者のトークンでDELETE /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H173" s="3" t="inlineStr">
+        <is>
+          <t>book_genre・reviews・favorites・review_likesの該当データも削除される</t>
+        </is>
+      </c>
+      <c r="I173" s="4" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="n"/>
+      <c r="B174" s="4" t="n"/>
+      <c r="C174" s="4" t="n"/>
+      <c r="D174" s="4" t="n"/>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
           <t>10-6-4</t>
         </is>
       </c>
-      <c r="F173" s="3" t="inlineStr">
+      <c r="F174" s="3" t="inlineStr">
         <is>
           <t>他のユーザーが登録した書籍は削除できない</t>
         </is>
       </c>
-      <c r="G173" s="3" t="inlineStr">
+      <c r="G174" s="3" t="inlineStr">
         <is>
           <t>1.他のユーザーが登録した書籍を用意する
 2.別のユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H173" s="3" t="inlineStr">
+      <c r="H174" s="3" t="inlineStr">
         <is>
           <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は削除されない</t>
         </is>
       </c>
-      <c r="I173" s="4" t="n"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="5" t="n"/>
-      <c r="B174" s="5" t="n"/>
-      <c r="C174" s="5" t="n"/>
-      <c r="D174" s="5" t="n"/>
-      <c r="E174" s="3" t="inlineStr">
+      <c r="I174" s="4" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="5" t="n"/>
+      <c r="B175" s="5" t="n"/>
+      <c r="C175" s="5" t="n"/>
+      <c r="D175" s="5" t="n"/>
+      <c r="E175" s="3" t="inlineStr">
         <is>
           <t>10-6-5</t>
         </is>
       </c>
-      <c r="F174" s="3" t="inlineStr">
+      <c r="F175" s="3" t="inlineStr">
         <is>
           <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
-      <c r="G174" s="3" t="inlineStr">
+      <c r="G175" s="3" t="inlineStr">
         <is>
           <t>1.トークンを付与し、存在しない書籍IDでDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H174" s="3" t="inlineStr">
+      <c r="H175" s="3" t="inlineStr">
         <is>
           <t>404が返り、「指定された書籍が見つかりません」が返る</t>
         </is>
       </c>
-      <c r="I174" s="5" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="7" t="inlineStr">
+      <c r="I175" s="5" t="n"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B175" s="7" t="inlineStr">
+      <c r="B176" s="7" t="inlineStr">
         <is>
           <t>検索・フィルタ</t>
         </is>
       </c>
-      <c r="C175" s="7" t="inlineStr">
+      <c r="C176" s="7" t="inlineStr">
         <is>
           <t>11-1</t>
         </is>
       </c>
-      <c r="D175" s="7" t="inlineStr">
+      <c r="D176" s="7" t="inlineStr">
         <is>
           <t>書籍のキーワード検索・ジャンル絞り込み</t>
         </is>
       </c>
-      <c r="E175" s="7" t="inlineStr">
+      <c r="E176" s="7" t="inlineStr">
         <is>
           <t>11-1-1</t>
         </is>
       </c>
-      <c r="F175" s="7" t="inlineStr">
+      <c r="F176" s="7" t="inlineStr">
         <is>
           <t>タイトルにキーワードを含む書籍が検索結果に表示される</t>
         </is>
       </c>
-      <c r="G175" s="7" t="inlineStr">
+      <c r="G176" s="7" t="inlineStr">
         <is>
           <t>1.タイトルにキーワードを含む書籍を用意する
 2.書籍一覧ページでkeywordにそのキーワードを指定して検索する</t>
         </is>
       </c>
-      <c r="H175" s="7" t="inlineStr">
+      <c r="H176" s="7" t="inlineStr">
         <is>
           <t>該当する書籍が検索結果に表示される</t>
         </is>
       </c>
-      <c r="I175" s="7" t="inlineStr">
+      <c r="I176" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Search/SearchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="4" t="n"/>
-      <c r="B176" s="4" t="n"/>
-      <c r="C176" s="4" t="n"/>
-      <c r="D176" s="4" t="n"/>
-      <c r="E176" s="7" t="inlineStr">
-        <is>
-          <t>11-1-2</t>
-        </is>
-      </c>
-      <c r="F176" s="7" t="inlineStr">
-        <is>
-          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="G176" s="7" t="inlineStr">
-        <is>
-          <t>1.著者名にキーワードを含む書籍を用意する
-2.同キーワードで検索する</t>
-        </is>
-      </c>
-      <c r="H176" s="7" t="inlineStr">
-        <is>
-          <t>該当する書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="I176" s="4" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n"/>
@@ -5999,23 +5998,23 @@
       <c r="D177" s="4" t="n"/>
       <c r="E177" s="7" t="inlineStr">
         <is>
-          <t>11-1-3</t>
+          <t>11-1-2</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
+          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>1.キーワードに一致しない書籍を用意する
-2.検索する</t>
+          <t>1.著者名にキーワードを含む書籍を用意する
+2.同キーワードで検索する</t>
         </is>
       </c>
       <c r="H177" s="7" t="inlineStr">
         <is>
-          <t>その書籍は検索結果に表示されない</t>
+          <t>該当する書籍が検索結果に表示される</t>
         </is>
       </c>
       <c r="I177" s="4" t="n"/>
@@ -6027,22 +6026,23 @@
       <c r="D178" s="4" t="n"/>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>11-1-4</t>
+          <t>11-1-3</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>キーワード未入力の場合は全件が表示される</t>
+          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
         </is>
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
+          <t>1.キーワードに一致しない書籍を用意する
+2.検索する</t>
         </is>
       </c>
       <c r="H178" s="7" t="inlineStr">
         <is>
-          <t>登録されている全ての書籍が表示される</t>
+          <t>その書籍は検索結果に表示されない</t>
         </is>
       </c>
       <c r="I178" s="4" t="n"/>
@@ -6054,23 +6054,22 @@
       <c r="D179" s="4" t="n"/>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>11-1-5</t>
+          <t>11-1-4</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
+          <t>キーワード未入力の場合は全件が表示される</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>1.複数ジャンルの書籍を用意する
-2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
+          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
         </is>
       </c>
       <c r="H179" s="7" t="inlineStr">
         <is>
-          <t>指定したジャンルに紐づく書籍のみ表示される</t>
+          <t>登録されている全ての書籍が表示される</t>
         </is>
       </c>
       <c r="I179" s="4" t="n"/>
@@ -6082,128 +6081,128 @@
       <c r="D180" s="4" t="n"/>
       <c r="E180" s="7" t="inlineStr">
         <is>
+          <t>11-1-5</t>
+        </is>
+      </c>
+      <c r="F180" s="7" t="inlineStr">
+        <is>
+          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
+        </is>
+      </c>
+      <c r="G180" s="7" t="inlineStr">
+        <is>
+          <t>1.複数ジャンルの書籍を用意する
+2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
+        </is>
+      </c>
+      <c r="H180" s="7" t="inlineStr">
+        <is>
+          <t>指定したジャンルに紐づく書籍のみ表示される</t>
+        </is>
+      </c>
+      <c r="I180" s="4" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="n"/>
+      <c r="B181" s="4" t="n"/>
+      <c r="C181" s="4" t="n"/>
+      <c r="D181" s="4" t="n"/>
+      <c r="E181" s="7" t="inlineStr">
+        <is>
           <t>11-1-6</t>
         </is>
       </c>
-      <c r="F180" s="7" t="inlineStr">
+      <c r="F181" s="7" t="inlineStr">
         <is>
           <t>キーワード検索とジャンル絞り込みを組み合わせて使用できる</t>
         </is>
       </c>
-      <c r="G180" s="7" t="inlineStr">
+      <c r="G181" s="7" t="inlineStr">
         <is>
           <t>1.keywordとgenreの両方を指定して一覧を開く</t>
         </is>
       </c>
-      <c r="H180" s="7" t="inlineStr">
+      <c r="H181" s="7" t="inlineStr">
         <is>
           <t>キーワードとジャンルの両方の条件に一致する書籍のみ表示される</t>
         </is>
       </c>
-      <c r="I180" s="4" t="n"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="5" t="n"/>
-      <c r="B181" s="5" t="n"/>
-      <c r="C181" s="5" t="n"/>
-      <c r="D181" s="5" t="n"/>
-      <c r="E181" s="7" t="inlineStr">
+      <c r="I181" s="4" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="n"/>
+      <c r="B182" s="5" t="n"/>
+      <c r="C182" s="5" t="n"/>
+      <c r="D182" s="5" t="n"/>
+      <c r="E182" s="7" t="inlineStr">
         <is>
           <t>11-1-7</t>
         </is>
       </c>
-      <c r="F181" s="7" t="inlineStr">
+      <c r="F182" s="7" t="inlineStr">
         <is>
           <t>検索結果が0件の場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G181" s="7" t="inlineStr">
+      <c r="G182" s="7" t="inlineStr">
         <is>
           <t>1.どの書籍にも一致しないキーワードで検索する</t>
         </is>
       </c>
-      <c r="H181" s="7" t="inlineStr">
+      <c r="H182" s="7" t="inlineStr">
         <is>
           <t>「条件に一致する書籍が見つかりませんでした。」と表示される</t>
         </is>
       </c>
-      <c r="I181" s="5" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="7" t="inlineStr">
+      <c r="I182" s="5" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B182" s="7" t="inlineStr">
+      <c r="B183" s="7" t="inlineStr">
         <is>
           <t>ソート</t>
         </is>
       </c>
-      <c r="C182" s="7" t="inlineStr">
+      <c r="C183" s="7" t="inlineStr">
         <is>
           <t>12-1</t>
         </is>
       </c>
-      <c r="D182" s="7" t="inlineStr">
+      <c r="D183" s="7" t="inlineStr">
         <is>
           <t>書籍一覧の並び替え</t>
         </is>
       </c>
-      <c r="E182" s="7" t="inlineStr">
+      <c r="E183" s="7" t="inlineStr">
         <is>
           <t>12-1-1</t>
         </is>
       </c>
-      <c r="F182" s="7" t="inlineStr">
+      <c r="F183" s="7" t="inlineStr">
         <is>
           <t>並び替え未指定時は新着順(登録が新しい順)で表示される</t>
         </is>
       </c>
-      <c r="G182" s="7" t="inlineStr">
+      <c r="G183" s="7" t="inlineStr">
         <is>
           <t>1.複数の書籍を異なる日時で登録する
 2.sortを指定せずに書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H182" s="7" t="inlineStr">
+      <c r="H183" s="7" t="inlineStr">
         <is>
           <t>登録日時が新しい順に表示される</t>
         </is>
       </c>
-      <c r="I182" s="7" t="inlineStr">
+      <c r="I183" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Sort/SortTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="4" t="n"/>
-      <c r="B183" s="4" t="n"/>
-      <c r="C183" s="4" t="n"/>
-      <c r="D183" s="4" t="n"/>
-      <c r="E183" s="7" t="inlineStr">
-        <is>
-          <t>12-1-2</t>
-        </is>
-      </c>
-      <c r="F183" s="7" t="inlineStr">
-        <is>
-          <t>sort=oldestを指定すると登録が古い順に表示される</t>
-        </is>
-      </c>
-      <c r="G183" s="7" t="inlineStr">
-        <is>
-          <t>1.複数の書籍を異なる日時で登録する
-2.sort=oldestを指定して書籍一覧を開く</t>
-        </is>
-      </c>
-      <c r="H183" s="7" t="inlineStr">
-        <is>
-          <t>登録日時が古い順に表示される</t>
-        </is>
-      </c>
-      <c r="I183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="4" t="n"/>
@@ -6212,23 +6211,23 @@
       <c r="D184" s="4" t="n"/>
       <c r="E184" s="7" t="inlineStr">
         <is>
-          <t>12-1-3</t>
+          <t>12-1-2</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>sort=titleを指定するとタイトルの昇順で表示される</t>
+          <t>sort=oldestを指定すると登録が古い順に表示される</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
-          <t>1.複数の書籍を用意する
-2.sort=titleを指定して書籍一覧を開く</t>
+          <t>1.複数の書籍を異なる日時で登録する
+2.sort=oldestを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>タイトルの昇順で表示される</t>
+          <t>登録日時が古い順に表示される</t>
         </is>
       </c>
       <c r="I184" s="4" t="n"/>
@@ -6240,128 +6239,129 @@
       <c r="D185" s="4" t="n"/>
       <c r="E185" s="7" t="inlineStr">
         <is>
+          <t>12-1-3</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>sort=titleを指定するとタイトルの昇順で表示される</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>1.複数の書籍を用意する
+2.sort=titleを指定して書籍一覧を開く</t>
+        </is>
+      </c>
+      <c r="H185" s="7" t="inlineStr">
+        <is>
+          <t>タイトルの昇順で表示される</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n"/>
+      <c r="B186" s="4" t="n"/>
+      <c r="C186" s="4" t="n"/>
+      <c r="D186" s="4" t="n"/>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
           <t>12-1-4</t>
         </is>
       </c>
-      <c r="F185" s="7" t="inlineStr">
+      <c r="F186" s="7" t="inlineStr">
         <is>
           <t>sort=ratingを指定すると平均評価が高い順に表示される</t>
         </is>
       </c>
-      <c r="G185" s="7" t="inlineStr">
+      <c r="G186" s="7" t="inlineStr">
         <is>
           <t>1.平均評価が異なる複数の書籍を用意する
 2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H185" s="7" t="inlineStr">
+      <c r="H186" s="7" t="inlineStr">
         <is>
           <t>平均評価が高い順に表示される</t>
         </is>
       </c>
-      <c r="I185" s="4" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="5" t="n"/>
-      <c r="B186" s="5" t="n"/>
-      <c r="C186" s="5" t="n"/>
-      <c r="D186" s="5" t="n"/>
-      <c r="E186" s="7" t="inlineStr">
+      <c r="I186" s="4" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="5" t="n"/>
+      <c r="B187" s="5" t="n"/>
+      <c r="C187" s="5" t="n"/>
+      <c r="D187" s="5" t="n"/>
+      <c r="E187" s="7" t="inlineStr">
         <is>
           <t>12-1-5</t>
         </is>
       </c>
-      <c r="F186" s="7" t="inlineStr">
+      <c r="F187" s="7" t="inlineStr">
         <is>
           <t>sort=rating指定時、平均評価が同じ書籍は新着順で表示される</t>
         </is>
       </c>
-      <c r="G186" s="7" t="inlineStr">
+      <c r="G187" s="7" t="inlineStr">
         <is>
           <t>1.平均評価が同じ複数の書籍を、異なる登録日時で用意する
 2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H186" s="7" t="inlineStr">
+      <c r="H187" s="7" t="inlineStr">
         <is>
           <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
         </is>
       </c>
-      <c r="I186" s="5" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="7" t="inlineStr">
+      <c r="I187" s="5" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B187" s="7" t="inlineStr">
+      <c r="B188" s="7" t="inlineStr">
         <is>
           <t>書籍CRUD（認可の詳細テスト）</t>
         </is>
       </c>
-      <c r="C187" s="7" t="inlineStr">
+      <c r="C188" s="7" t="inlineStr">
         <is>
           <t>13-1</t>
         </is>
       </c>
-      <c r="D187" s="7" t="inlineStr">
+      <c r="D188" s="7" t="inlineStr">
         <is>
           <t>BookPolicyの認可ロジック</t>
         </is>
       </c>
-      <c r="E187" s="7" t="inlineStr">
+      <c r="E188" s="7" t="inlineStr">
         <is>
           <t>13-1-1</t>
         </is>
       </c>
-      <c r="F187" s="7" t="inlineStr">
+      <c r="F188" s="7" t="inlineStr">
         <is>
           <t>ログインユーザーは誰でも書籍を作成できる</t>
         </is>
       </c>
-      <c r="G187" s="7" t="inlineStr">
+      <c r="G188" s="7" t="inlineStr">
         <is>
           <t>1.任意のログインユーザーで BookPolicy::create() を確認する</t>
         </is>
       </c>
-      <c r="H187" s="7" t="inlineStr">
+      <c r="H188" s="7" t="inlineStr">
         <is>
           <t>trueが返り、作成が許可される</t>
         </is>
       </c>
-      <c r="I187" s="7" t="inlineStr">
+      <c r="I188" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/BookAuthorization/BookAuthorizationTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="4" t="n"/>
-      <c r="B188" s="4" t="n"/>
-      <c r="C188" s="4" t="n"/>
-      <c r="D188" s="4" t="n"/>
-      <c r="E188" s="7" t="inlineStr">
-        <is>
-          <t>13-1-2</t>
-        </is>
-      </c>
-      <c r="F188" s="7" t="inlineStr">
-        <is>
-          <t>書籍の登録者本人は更新が許可される</t>
-        </is>
-      </c>
-      <c r="G188" s="7" t="inlineStr">
-        <is>
-          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
-        </is>
-      </c>
-      <c r="H188" s="7" t="inlineStr">
-        <is>
-          <t>trueが返る</t>
-        </is>
-      </c>
-      <c r="I188" s="4" t="n"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="n"/>
@@ -6370,22 +6370,22 @@
       <c r="D189" s="4" t="n"/>
       <c r="E189" s="7" t="inlineStr">
         <is>
-          <t>13-1-3</t>
+          <t>13-1-2</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者以外は更新が許可されない</t>
+          <t>書籍の登録者本人は更新が許可される</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
+          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>falseが返る</t>
+          <t>trueが返る</t>
         </is>
       </c>
       <c r="I189" s="4" t="n"/>
@@ -6397,22 +6397,22 @@
       <c r="D190" s="4" t="n"/>
       <c r="E190" s="7" t="inlineStr">
         <is>
-          <t>13-1-4</t>
+          <t>13-1-3</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者本人は削除が許可される</t>
+          <t>書籍の登録者以外は更新が許可されない</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
+          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
-          <t>trueが返る</t>
+          <t>falseが返る</t>
         </is>
       </c>
       <c r="I190" s="4" t="n"/>
@@ -6424,22 +6424,22 @@
       <c r="D191" s="4" t="n"/>
       <c r="E191" s="7" t="inlineStr">
         <is>
-          <t>13-1-5</t>
+          <t>13-1-4</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者以外は削除が許可されない</t>
+          <t>書籍の登録者本人は削除が許可される</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
+          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
         </is>
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
-          <t>falseが返る</t>
+          <t>trueが返る</t>
         </is>
       </c>
       <c r="I191" s="4" t="n"/>
@@ -6451,127 +6451,126 @@
       <c r="D192" s="4" t="n"/>
       <c r="E192" s="7" t="inlineStr">
         <is>
+          <t>13-1-5</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>書籍の登録者以外は削除が許可されない</t>
+        </is>
+      </c>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
+        </is>
+      </c>
+      <c r="H192" s="7" t="inlineStr">
+        <is>
+          <t>falseが返る</t>
+        </is>
+      </c>
+      <c r="I192" s="4" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="n"/>
+      <c r="B193" s="4" t="n"/>
+      <c r="C193" s="4" t="n"/>
+      <c r="D193" s="4" t="n"/>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
           <t>13-1-6</t>
         </is>
       </c>
-      <c r="F192" s="7" t="inlineStr">
+      <c r="F193" s="7" t="inlineStr">
         <is>
           <t>フォームを介さない直接のPUT/DELETEリクエストでも他人の書籍は操作できない</t>
         </is>
       </c>
-      <c r="G192" s="7" t="inlineStr">
+      <c r="G193" s="7" t="inlineStr">
         <is>
           <t>1.他人が登録した書籍に対して、直接PUT・DELETEリクエストを送信する</t>
         </is>
       </c>
-      <c r="H192" s="7" t="inlineStr">
+      <c r="H193" s="7" t="inlineStr">
         <is>
           <t>いずれも403Forbiddenになり、データは変更されない</t>
         </is>
       </c>
-      <c r="I192" s="4" t="n"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="5" t="n"/>
-      <c r="B193" s="5" t="n"/>
-      <c r="C193" s="5" t="n"/>
-      <c r="D193" s="5" t="n"/>
-      <c r="E193" s="7" t="inlineStr">
+      <c r="I193" s="4" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="5" t="n"/>
+      <c r="B194" s="5" t="n"/>
+      <c r="C194" s="5" t="n"/>
+      <c r="D194" s="5" t="n"/>
+      <c r="E194" s="7" t="inlineStr">
         <is>
           <t>13-1-7</t>
         </is>
       </c>
-      <c r="F193" s="7" t="inlineStr">
+      <c r="F194" s="7" t="inlineStr">
         <is>
           <t>他人の書籍に対して不正な入力を直接PUTしても、入力エラーではなく403になる</t>
         </is>
       </c>
-      <c r="G193" s="7" t="inlineStr">
+      <c r="G194" s="7" t="inlineStr">
         <is>
           <t>1.他人が登録した書籍に対して、タイトルを空にするなど不正な内容で、直接PUTリクエストを送信する</t>
         </is>
       </c>
-      <c r="H193" s="7" t="inlineStr">
+      <c r="H194" s="7" t="inlineStr">
         <is>
           <t>バリデーションエラーにはならず、403Forbiddenになる（入力チェックより先に権限が判定される）。データは変更されない</t>
         </is>
       </c>
-      <c r="I193" s="5" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="7" t="inlineStr">
+      <c r="I194" s="5" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B194" s="7" t="inlineStr">
+      <c r="B195" s="7" t="inlineStr">
         <is>
           <t>ISBN検索</t>
         </is>
       </c>
-      <c r="C194" s="7" t="inlineStr">
+      <c r="C195" s="7" t="inlineStr">
         <is>
           <t>14-1</t>
         </is>
       </c>
-      <c r="D194" s="7" t="inlineStr">
+      <c r="D195" s="7" t="inlineStr">
         <is>
           <t>ISBNからの書籍情報取得(外部API連携)</t>
         </is>
       </c>
-      <c r="E194" s="7" t="inlineStr">
+      <c r="E195" s="7" t="inlineStr">
         <is>
           <t>14-1-1</t>
         </is>
       </c>
-      <c r="F194" s="7" t="inlineStr">
+      <c r="F195" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、ISBN検索エンドポイントにアクセスできない</t>
         </is>
       </c>
-      <c r="G194" s="7" t="inlineStr">
+      <c r="G195" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態でGET /books/isbn/{isbn} にアクセスする</t>
         </is>
       </c>
-      <c r="H194" s="7" t="inlineStr">
+      <c r="H195" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I194" s="7" t="inlineStr">
+      <c r="I195" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Isbn/IsbnSearchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="4" t="n"/>
-      <c r="B195" s="4" t="n"/>
-      <c r="C195" s="4" t="n"/>
-      <c r="D195" s="4" t="n"/>
-      <c r="E195" s="7" t="inlineStr">
-        <is>
-          <t>14-1-2</t>
-        </is>
-      </c>
-      <c r="F195" s="7" t="inlineStr">
-        <is>
-          <t>ISBNが空(空白のみ)の場合、バリデーションエラーが返る</t>
-        </is>
-      </c>
-      <c r="G195" s="7" t="inlineStr">
-        <is>
-          <t>1.ログイン状態で、ISBN部分を半角スペースのみにしてGET /books/isbn/%20 にリクエストする
-※ISBN部分を完全に空にするとURLが /books/isbn となり、このルートに一致しないため空白で代用する</t>
-        </is>
-      </c>
-      <c r="H195" s="7" t="inlineStr">
-        <is>
-          <t>422が返り、「ISBNを入力してください」が返る</t>
-        </is>
-      </c>
-      <c r="I195" s="4" t="n"/>
     </row>
     <row r="196">
       <c r="A196" s="4" t="n"/>
@@ -6580,22 +6579,23 @@
       <c r="D196" s="4" t="n"/>
       <c r="E196" s="7" t="inlineStr">
         <is>
-          <t>14-1-3</t>
+          <t>14-1-2</t>
         </is>
       </c>
       <c r="F196" s="7" t="inlineStr">
         <is>
-          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
+          <t>ISBNが空(空白のみ)の場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>1.13桁でないISBNでリクエストする</t>
+          <t>1.ログイン状態で、ISBN部分を半角スペースのみにしてGET /books/isbn/%20 にリクエストする
+※ISBN部分を完全に空にするとURLが /books/isbn となり、このルートに一致しないため空白で代用する</t>
         </is>
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
+          <t>422が返り、「ISBNを入力してください」が返る</t>
         </is>
       </c>
       <c r="I196" s="4" t="n"/>
@@ -6607,22 +6607,22 @@
       <c r="D197" s="4" t="n"/>
       <c r="E197" s="7" t="inlineStr">
         <is>
-          <t>14-1-4</t>
+          <t>14-1-3</t>
         </is>
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
-          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
+          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>1.登録済みのISBNでリクエストする</t>
+          <t>1.13桁でないISBNでリクエストする</t>
         </is>
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
+          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
         </is>
       </c>
       <c r="I197" s="4" t="n"/>
@@ -6634,23 +6634,22 @@
       <c r="D198" s="4" t="n"/>
       <c r="E198" s="7" t="inlineStr">
         <is>
-          <t>14-1-5</t>
+          <t>14-1-4</t>
         </is>
       </c>
       <c r="F198" s="7" t="inlineStr">
         <is>
-          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
+          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G198" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
-2.未登録ISBNでリクエストする</t>
+          <t>1.登録済みのISBNでリクエストする</t>
         </is>
       </c>
       <c r="H198" s="7" t="inlineStr">
         <is>
-          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
+          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
         </is>
       </c>
       <c r="I198" s="4" t="n"/>
@@ -6662,128 +6661,129 @@
       <c r="D199" s="4" t="n"/>
       <c r="E199" s="7" t="inlineStr">
         <is>
+          <t>14-1-5</t>
+        </is>
+      </c>
+      <c r="F199" s="7" t="inlineStr">
+        <is>
+          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
+        </is>
+      </c>
+      <c r="G199" s="7" t="inlineStr">
+        <is>
+          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
+2.未登録ISBNでリクエストする</t>
+        </is>
+      </c>
+      <c r="H199" s="7" t="inlineStr">
+        <is>
+          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
+        </is>
+      </c>
+      <c r="I199" s="4" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="n"/>
+      <c r="B200" s="4" t="n"/>
+      <c r="C200" s="4" t="n"/>
+      <c r="D200" s="4" t="n"/>
+      <c r="E200" s="7" t="inlineStr">
+        <is>
           <t>14-1-6</t>
         </is>
       </c>
-      <c r="F199" s="7" t="inlineStr">
+      <c r="F200" s="7" t="inlineStr">
         <is>
           <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
         </is>
       </c>
-      <c r="G199" s="7" t="inlineStr">
+      <c r="G200" s="7" t="inlineStr">
         <is>
           <t>1.Http::fake()でitemsが空のレスポンスをモックする
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H199" s="7" t="inlineStr">
+      <c r="H200" s="7" t="inlineStr">
         <is>
           <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
         </is>
       </c>
-      <c r="I199" s="4" t="n"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="5" t="n"/>
-      <c r="B200" s="5" t="n"/>
-      <c r="C200" s="5" t="n"/>
-      <c r="D200" s="5" t="n"/>
-      <c r="E200" s="7" t="inlineStr">
+      <c r="I200" s="4" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="5" t="n"/>
+      <c r="B201" s="5" t="n"/>
+      <c r="C201" s="5" t="n"/>
+      <c r="D201" s="5" t="n"/>
+      <c r="E201" s="7" t="inlineStr">
         <is>
           <t>14-1-7</t>
         </is>
       </c>
-      <c r="F200" s="7" t="inlineStr">
+      <c r="F201" s="7" t="inlineStr">
         <is>
           <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
         </is>
       </c>
-      <c r="G200" s="7" t="inlineStr">
+      <c r="G201" s="7" t="inlineStr">
         <is>
           <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H200" s="7" t="inlineStr">
+      <c r="H201" s="7" t="inlineStr">
         <is>
           <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
         </is>
       </c>
-      <c r="I200" s="5" t="n"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="7" t="inlineStr">
+      <c r="I201" s="5" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B201" s="7" t="inlineStr">
+      <c r="B202" s="7" t="inlineStr">
         <is>
           <t>マイ読書レポート</t>
         </is>
       </c>
-      <c r="C201" s="7" t="inlineStr">
+      <c r="C202" s="7" t="inlineStr">
         <is>
           <t>15-1</t>
         </is>
       </c>
-      <c r="D201" s="7" t="inlineStr">
+      <c r="D202" s="7" t="inlineStr">
         <is>
           <t>読書統計の表示</t>
         </is>
       </c>
-      <c r="E201" s="7" t="inlineStr">
+      <c r="E202" s="7" t="inlineStr">
         <is>
           <t>15-1-1</t>
         </is>
       </c>
-      <c r="F201" s="7" t="inlineStr">
+      <c r="F202" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
         </is>
       </c>
-      <c r="G201" s="7" t="inlineStr">
+      <c r="G202" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で/reportsを開く</t>
         </is>
       </c>
-      <c r="H201" s="7" t="inlineStr">
+      <c r="H202" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I201" s="7" t="inlineStr">
+      <c r="I202" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Report/ReportTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="4" t="n"/>
-      <c r="B202" s="4" t="n"/>
-      <c r="C202" s="4" t="n"/>
-      <c r="D202" s="4" t="n"/>
-      <c r="E202" s="7" t="inlineStr">
-        <is>
-          <t>15-1-2</t>
-        </is>
-      </c>
-      <c r="F202" s="7" t="inlineStr">
-        <is>
-          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
-        </is>
-      </c>
-      <c r="G202" s="7" t="inlineStr">
-        <is>
-          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
-        </is>
-      </c>
-      <c r="H202" s="7" t="inlineStr">
-        <is>
-          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
-        </is>
-      </c>
-      <c r="I202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n"/>
@@ -6792,22 +6792,22 @@
       <c r="D203" s="4" t="n"/>
       <c r="E203" s="7" t="inlineStr">
         <is>
-          <t>15-1-3</t>
+          <t>15-1-2</t>
         </is>
       </c>
       <c r="F203" s="7" t="inlineStr">
         <is>
-          <t>評価分布(★1〜★5)が正しく表示される</t>
+          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
         </is>
       </c>
       <c r="G203" s="7" t="inlineStr">
         <is>
-          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
+          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
-          <t>各評価の件数が実データと一致して表示される</t>
+          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
         </is>
       </c>
       <c r="I203" s="4" t="n"/>
@@ -6819,22 +6819,22 @@
       <c r="D204" s="4" t="n"/>
       <c r="E204" s="7" t="inlineStr">
         <is>
-          <t>15-1-4</t>
+          <t>15-1-3</t>
         </is>
       </c>
       <c r="F204" s="7" t="inlineStr">
         <is>
-          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
+          <t>評価分布(★1〜★5)が正しく表示される</t>
         </is>
       </c>
       <c r="G204" s="7" t="inlineStr">
         <is>
-          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
+          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
-          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
+          <t>各評価の件数が実データと一致して表示される</t>
         </is>
       </c>
       <c r="I204" s="4" t="n"/>
@@ -6846,127 +6846,127 @@
       <c r="D205" s="4" t="n"/>
       <c r="E205" s="7" t="inlineStr">
         <is>
+          <t>15-1-4</t>
+        </is>
+      </c>
+      <c r="F205" s="7" t="inlineStr">
+        <is>
+          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="inlineStr">
+        <is>
+          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
+        </is>
+      </c>
+      <c r="H205" s="7" t="inlineStr">
+        <is>
+          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
+        </is>
+      </c>
+      <c r="I205" s="4" t="n"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="n"/>
+      <c r="B206" s="4" t="n"/>
+      <c r="C206" s="4" t="n"/>
+      <c r="D206" s="4" t="n"/>
+      <c r="E206" s="7" t="inlineStr">
+        <is>
           <t>15-1-5</t>
         </is>
       </c>
-      <c r="F205" s="7" t="inlineStr">
+      <c r="F206" s="7" t="inlineStr">
         <is>
           <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
         </is>
       </c>
-      <c r="G205" s="7" t="inlineStr">
+      <c r="G206" s="7" t="inlineStr">
         <is>
           <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H205" s="7" t="inlineStr">
+      <c r="H206" s="7" t="inlineStr">
         <is>
           <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
         </is>
       </c>
-      <c r="I205" s="4" t="n"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="5" t="n"/>
-      <c r="B206" s="5" t="n"/>
-      <c r="C206" s="5" t="n"/>
-      <c r="D206" s="5" t="n"/>
-      <c r="E206" s="7" t="inlineStr">
+      <c r="I206" s="4" t="n"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="5" t="n"/>
+      <c r="B207" s="5" t="n"/>
+      <c r="C207" s="5" t="n"/>
+      <c r="D207" s="5" t="n"/>
+      <c r="E207" s="7" t="inlineStr">
         <is>
           <t>15-1-6</t>
         </is>
       </c>
-      <c r="F206" s="7" t="inlineStr">
+      <c r="F207" s="7" t="inlineStr">
         <is>
           <t>レビューを1件も投稿していない場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G206" s="7" t="inlineStr">
+      <c r="G207" s="7" t="inlineStr">
         <is>
           <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H206" s="7" t="inlineStr">
+      <c r="H207" s="7" t="inlineStr">
         <is>
           <t>総レビュー数・読了冊数が0（平均評価の集計値は0で、画面上は「-」と表示）となり、TOP5一覧には「4星以上の書籍がありません」「ジャンルが設定された書籍のレビューがありません」と表示される</t>
         </is>
       </c>
-      <c r="I206" s="5" t="n"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="7" t="inlineStr">
+      <c r="I207" s="5" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B207" s="7" t="inlineStr">
+      <c r="B208" s="7" t="inlineStr">
         <is>
           <t>Sanctum認証</t>
         </is>
       </c>
-      <c r="C207" s="7" t="inlineStr">
+      <c r="C208" s="7" t="inlineStr">
         <is>
           <t>16-1</t>
         </is>
       </c>
-      <c r="D207" s="7" t="inlineStr">
+      <c r="D208" s="7" t="inlineStr">
         <is>
           <t>APIトークン認証</t>
         </is>
       </c>
-      <c r="E207" s="7" t="inlineStr">
+      <c r="E208" s="7" t="inlineStr">
         <is>
           <t>16-1-1</t>
         </is>
       </c>
-      <c r="F207" s="7" t="inlineStr">
+      <c r="F208" s="7" t="inlineStr">
         <is>
           <t>有効なpersonal access tokenを付与すると/api/userにアクセスできる</t>
         </is>
       </c>
-      <c r="G207" s="7" t="inlineStr">
+      <c r="G208" s="7" t="inlineStr">
         <is>
           <t>1.$user-&gt;createToken()でトークンを発行する
 2.Authorization: Bearer {token}を付与してGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H207" s="7" t="inlineStr">
+      <c r="H208" s="7" t="inlineStr">
         <is>
           <t>200が返り、対象ユーザーの情報が返る</t>
         </is>
       </c>
-      <c r="I207" s="7" t="inlineStr">
+      <c r="I208" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="4" t="n"/>
-      <c r="B208" s="4" t="n"/>
-      <c r="C208" s="4" t="n"/>
-      <c r="D208" s="4" t="n"/>
-      <c r="E208" s="7" t="inlineStr">
-        <is>
-          <t>16-1-2</t>
-        </is>
-      </c>
-      <c r="F208" s="7" t="inlineStr">
-        <is>
-          <t>トークンなしでアクセスすると401が返る</t>
-        </is>
-      </c>
-      <c r="G208" s="7" t="inlineStr">
-        <is>
-          <t>1.Authorizationヘッダーを付与せずにGET /api/userにアクセスする</t>
-        </is>
-      </c>
-      <c r="H208" s="7" t="inlineStr">
-        <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
-        </is>
-      </c>
-      <c r="I208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="n"/>
@@ -6975,128 +6975,127 @@
       <c r="D209" s="4" t="n"/>
       <c r="E209" s="7" t="inlineStr">
         <is>
+          <t>16-1-2</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>トークンなしでアクセスすると401が返る</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>1.Authorizationヘッダーを付与せずにGET /api/userにアクセスする</t>
+        </is>
+      </c>
+      <c r="H209" s="7" t="inlineStr">
+        <is>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n"/>
+      <c r="B210" s="4" t="n"/>
+      <c r="C210" s="4" t="n"/>
+      <c r="D210" s="4" t="n"/>
+      <c r="E210" s="7" t="inlineStr">
+        <is>
           <t>16-1-3</t>
         </is>
       </c>
-      <c r="F209" s="7" t="inlineStr">
+      <c r="F210" s="7" t="inlineStr">
         <is>
           <t>不正な(存在しない)トークンでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G209" s="7" t="inlineStr">
+      <c r="G210" s="7" t="inlineStr">
         <is>
           <t>1.ランダムな文字列をBearerトークンとして付与しGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H209" s="7" t="inlineStr">
+      <c r="H210" s="7" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
         </is>
       </c>
-      <c r="I209" s="4" t="n"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="5" t="n"/>
-      <c r="B210" s="5" t="n"/>
-      <c r="C210" s="5" t="n"/>
-      <c r="D210" s="5" t="n"/>
-      <c r="E210" s="7" t="inlineStr">
+      <c r="I210" s="4" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="n"/>
+      <c r="B211" s="5" t="n"/>
+      <c r="C211" s="5" t="n"/>
+      <c r="D211" s="5" t="n"/>
+      <c r="E211" s="7" t="inlineStr">
         <is>
           <t>16-1-4</t>
         </is>
       </c>
-      <c r="F210" s="7" t="inlineStr">
+      <c r="F211" s="7" t="inlineStr">
         <is>
           <t>削除済み(失効済み)のトークンでアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G210" s="7" t="inlineStr">
+      <c r="G211" s="7" t="inlineStr">
         <is>
           <t>1.発行済みトークンを削除する
 2.そのトークンでGET /api/userにアクセスする</t>
         </is>
       </c>
-      <c r="H210" s="7" t="inlineStr">
+      <c r="H211" s="7" t="inlineStr">
         <is>
           <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
         </is>
       </c>
-      <c r="I210" s="5" t="n"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="7" t="inlineStr">
+      <c r="I211" s="5" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B211" s="7" t="inlineStr">
+      <c r="B212" s="7" t="inlineStr">
         <is>
           <t>読書計画</t>
         </is>
       </c>
-      <c r="C211" s="7" t="inlineStr">
+      <c r="C212" s="7" t="inlineStr">
         <is>
           <t>17-1</t>
         </is>
       </c>
-      <c r="D211" s="7" t="inlineStr">
+      <c r="D212" s="7" t="inlineStr">
         <is>
           <t>読書計画の作成・一覧・読了・削除</t>
         </is>
       </c>
-      <c r="E211" s="7" t="inlineStr">
+      <c r="E212" s="7" t="inlineStr">
         <is>
           <t>17-1-1</t>
         </is>
       </c>
-      <c r="F211" s="7" t="inlineStr">
+      <c r="F212" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
         </is>
       </c>
-      <c r="G211" s="7" t="inlineStr">
+      <c r="G212" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H211" s="7" t="inlineStr">
+      <c r="H212" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I211" s="7" t="inlineStr">
+      <c r="I212" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="4" t="n"/>
-      <c r="B212" s="4" t="n"/>
-      <c r="C212" s="4" t="n"/>
-      <c r="D212" s="4" t="n"/>
-      <c r="E212" s="7" t="inlineStr">
-        <is>
-          <t>17-1-2</t>
-        </is>
-      </c>
-      <c r="F212" s="7" t="inlineStr">
-        <is>
-          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
-        </is>
-      </c>
-      <c r="G212" s="7" t="inlineStr">
-        <is>
-          <t>1.自分と他人の読書計画をそれぞれ用意する
-2.読書計画一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H212" s="7" t="inlineStr">
-        <is>
-          <t>自分の計画のみが、target_dateの昇順で表示される</t>
-        </is>
-      </c>
-      <c r="I212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="4" t="n"/>
@@ -7105,23 +7104,23 @@
       <c r="D213" s="4" t="n"/>
       <c r="E213" s="7" t="inlineStr">
         <is>
-          <t>17-1-3</t>
+          <t>17-1-2</t>
         </is>
       </c>
       <c r="F213" s="7" t="inlineStr">
         <is>
-          <t>ステータスで絞り込んで表示できる</t>
+          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
         </is>
       </c>
       <c r="G213" s="7" t="inlineStr">
         <is>
-          <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
-2.statusパラメータを指定して一覧を開く</t>
+          <t>1.自分と他人の読書計画をそれぞれ用意する
+2.読書計画一覧ページを開く</t>
         </is>
       </c>
       <c r="H213" s="7" t="inlineStr">
         <is>
-          <t>指定したステータスの計画のみ表示される</t>
+          <t>自分の計画のみが、target_dateの昇順で表示される</t>
         </is>
       </c>
       <c r="I213" s="4" t="n"/>
@@ -7133,23 +7132,23 @@
       <c r="D214" s="4" t="n"/>
       <c r="E214" s="7" t="inlineStr">
         <is>
-          <t>17-1-4</t>
+          <t>17-1-3</t>
         </is>
       </c>
       <c r="F214" s="7" t="inlineStr">
         <is>
-          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
+          <t>ステータスで絞り込んで表示できる</t>
         </is>
       </c>
       <c r="G214" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍について進行中の計画を作成する
-2.計画作成ページを開く</t>
+          <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
+2.statusパラメータを指定して一覧を開く</t>
         </is>
       </c>
       <c r="H214" s="7" t="inlineStr">
         <is>
-          <t>書籍選択肢にその書籍が表示されない</t>
+          <t>指定したステータスの計画のみ表示される</t>
         </is>
       </c>
       <c r="I214" s="4" t="n"/>
@@ -7161,22 +7160,23 @@
       <c r="D215" s="4" t="n"/>
       <c r="E215" s="7" t="inlineStr">
         <is>
-          <t>17-1-5</t>
+          <t>17-1-4</t>
         </is>
       </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
-          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
+          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
         </is>
       </c>
       <c r="G215" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
+          <t>1.ある書籍について進行中の計画を作成する
+2.計画作成ページを開く</t>
         </is>
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、計画は作成されない</t>
+          <t>書籍選択肢にその書籍が表示されない</t>
         </is>
       </c>
       <c r="I215" s="4" t="n"/>
@@ -7188,23 +7188,22 @@
       <c r="D216" s="4" t="n"/>
       <c r="E216" s="7" t="inlineStr">
         <is>
-          <t>17-1-6</t>
+          <t>17-1-5</t>
         </is>
       </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
-          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
+          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
         </is>
       </c>
       <c r="G216" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を読了(完了)状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
-          <t>新しい計画が作成される</t>
+          <t>403Forbiddenになり、計画は作成されない</t>
         </is>
       </c>
       <c r="I216" s="4" t="n"/>
@@ -7216,23 +7215,23 @@
       <c r="D217" s="4" t="n"/>
       <c r="E217" s="7" t="inlineStr">
         <is>
-          <t>17-1-7</t>
+          <t>17-1-6</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
         </is>
       </c>
       <c r="G217" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.期日を入力せずに登録する</t>
+          <t>1.ある書籍の計画を読了(完了)状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>新しい計画が作成される</t>
         </is>
       </c>
       <c r="I217" s="4" t="n"/>
@@ -7244,23 +7243,23 @@
       <c r="D218" s="4" t="n"/>
       <c r="E218" s="7" t="inlineStr">
         <is>
-          <t>17-1-8</t>
+          <t>17-1-7</t>
         </is>
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
-2.過去の日付を期日に指定して登録する</t>
+2.期日を入力せずに登録する</t>
         </is>
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I218" s="4" t="n"/>
@@ -7272,23 +7271,23 @@
       <c r="D219" s="4" t="n"/>
       <c r="E219" s="7" t="inlineStr">
         <is>
-          <t>17-1-9</t>
+          <t>17-1-8</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G219" s="7" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
-2.書籍・期日を正しく入力して登録する</t>
+2.過去の日付を期日に指定して登録する</t>
         </is>
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I219" s="4" t="n"/>
@@ -7300,22 +7299,23 @@
       <c r="D220" s="4" t="n"/>
       <c r="E220" s="7" t="inlineStr">
         <is>
-          <t>17-1-10</t>
+          <t>17-1-9</t>
         </is>
       </c>
       <c r="F220" s="7" t="inlineStr">
         <is>
-          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
+          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
         </is>
       </c>
       <c r="G220" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画に対して読了操作を行う</t>
+          <t>1.計画作成ページを開く
+2.書籍・期日を正しく入力して登録する</t>
         </is>
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
         </is>
       </c>
       <c r="I220" s="4" t="n"/>
@@ -7327,22 +7327,22 @@
       <c r="D221" s="4" t="n"/>
       <c r="E221" s="7" t="inlineStr">
         <is>
-          <t>17-1-11</t>
+          <t>17-1-10</t>
         </is>
       </c>
       <c r="F221" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画は読了・削除できない</t>
+          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
         </is>
       </c>
       <c r="G221" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+          <t>1.進行中の計画に対して読了操作を行う</t>
         </is>
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
-          <t>いずれも403Forbiddenになる</t>
+          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
         </is>
       </c>
       <c r="I221" s="4" t="n"/>
@@ -7354,22 +7354,22 @@
       <c r="D222" s="4" t="n"/>
       <c r="E222" s="7" t="inlineStr">
         <is>
-          <t>17-1-12</t>
+          <t>17-1-11</t>
         </is>
       </c>
       <c r="F222" s="7" t="inlineStr">
         <is>
-          <t>自分が作成した読書計画は削除できる</t>
+          <t>他人が作成した読書計画は読了・削除できない</t>
         </is>
       </c>
       <c r="G222" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の削除ボタンを押す</t>
+          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
         </is>
       </c>
       <c r="H222" s="7" t="inlineStr">
         <is>
-          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
+          <t>いずれも403Forbiddenになる</t>
         </is>
       </c>
       <c r="I222" s="4" t="n"/>
@@ -7379,25 +7379,24 @@
       <c r="B223" s="4" t="n"/>
       <c r="C223" s="4" t="n"/>
       <c r="D223" s="4" t="n"/>
-      <c r="E223" s="9" t="inlineStr">
-        <is>
-          <t>17-1-13</t>
-        </is>
-      </c>
-      <c r="F223" s="9" t="inlineStr">
-        <is>
-          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
-        </is>
-      </c>
-      <c r="G223" s="9" t="inlineStr">
-        <is>
-          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
-2.その読書計画を削除する</t>
-        </is>
-      </c>
-      <c r="H223" s="9" t="inlineStr">
-        <is>
-          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
+      <c r="E223" s="7" t="inlineStr">
+        <is>
+          <t>17-1-12</t>
+        </is>
+      </c>
+      <c r="F223" s="7" t="inlineStr">
+        <is>
+          <t>自分が作成した読書計画は削除できる</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="inlineStr">
+        <is>
+          <t>1.自分が作成した計画の削除ボタンを押す</t>
+        </is>
+      </c>
+      <c r="H223" s="7" t="inlineStr">
+        <is>
+          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
         </is>
       </c>
       <c r="I223" s="4" t="n"/>
@@ -7409,22 +7408,23 @@
       <c r="D224" s="4" t="n"/>
       <c r="E224" s="9" t="inlineStr">
         <is>
-          <t>17-1-14</t>
+          <t>17-1-13</t>
         </is>
       </c>
       <c r="F224" s="9" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は、読了操作を行えない</t>
+          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
         </is>
       </c>
       <c r="G224" s="9" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
+          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
+2.その読書計画を削除する</t>
         </is>
       </c>
       <c r="H224" s="9" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、completed_atは変更されない</t>
+          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
         </is>
       </c>
       <c r="I224" s="4" t="n"/>
@@ -7436,23 +7436,22 @@
       <c r="D225" s="4" t="n"/>
       <c r="E225" s="9" t="inlineStr">
         <is>
-          <t>17-1-15</t>
+          <t>17-1-14</t>
         </is>
       </c>
       <c r="F225" s="9" t="inlineStr">
         <is>
-          <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
+          <t>ステータスが「完了」の計画は、読了操作を行えない</t>
         </is>
       </c>
       <c r="G225" s="9" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を「期限切れ」の状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
         </is>
       </c>
       <c r="H225" s="9" t="inlineStr">
         <is>
-          <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
+          <t>403Forbiddenになり、completed_atは変更されない</t>
         </is>
       </c>
       <c r="I225" s="4" t="n"/>
@@ -7464,23 +7463,23 @@
       <c r="D226" s="4" t="n"/>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>17-1-16</t>
+          <t>17-1-15</t>
         </is>
       </c>
       <c r="F226" s="9" t="inlineStr">
         <is>
-          <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
+          <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
         </is>
       </c>
       <c r="G226" s="9" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍を選択せずに期日を入力して登録する</t>
+          <t>1.ある書籍の計画を「期限切れ」の状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H226" s="9" t="inlineStr">
         <is>
-          <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
+          <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
         </is>
       </c>
       <c r="I226" s="4" t="n"/>
@@ -7492,22 +7491,23 @@
       <c r="D227" s="4" t="n"/>
       <c r="E227" s="9" t="inlineStr">
         <is>
-          <t>17-1-17</t>
+          <t>17-1-16</t>
         </is>
       </c>
       <c r="F227" s="9" t="inlineStr">
         <is>
-          <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
+          <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G227" s="9" t="inlineStr">
         <is>
-          <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.計画作成ページを開く
+2.書籍を選択せずに期日を入力して登録する</t>
         </is>
       </c>
       <c r="H227" s="9" t="inlineStr">
         <is>
-          <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
+          <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I227" s="4" t="n"/>
@@ -7519,22 +7519,22 @@
       <c r="D228" s="4" t="n"/>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>17-1-18</t>
+          <t>17-1-17</t>
         </is>
       </c>
       <c r="F228" s="9" t="inlineStr">
         <is>
-          <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
+          <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G228" s="9" t="inlineStr">
         <is>
-          <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H228" s="9" t="inlineStr">
         <is>
-          <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
+          <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I228" s="4" t="n"/>
@@ -7546,22 +7546,22 @@
       <c r="D229" s="4" t="n"/>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>17-1-19</t>
+          <t>17-1-18</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>期日が日付形式でない場合、バリデーションメッセージが表示される</t>
+          <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G229" s="9" t="inlineStr">
         <is>
-          <t>1.書籍と、日付として不正な期日(例:abc)を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H229" s="9" t="inlineStr">
         <is>
-          <t>「正しい日付を入力してください」というバリデーションメッセージが表示される</t>
+          <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I229" s="4" t="n"/>
@@ -7573,154 +7573,154 @@
       <c r="D230" s="4" t="n"/>
       <c r="E230" s="9" t="inlineStr">
         <is>
+          <t>17-1-19</t>
+        </is>
+      </c>
+      <c r="F230" s="9" t="inlineStr">
+        <is>
+          <t>期日が日付形式でない場合、バリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="G230" s="9" t="inlineStr">
+        <is>
+          <t>1.書籍と、日付として不正な期日(例:abc)を指定して、直接計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H230" s="9" t="inlineStr">
+        <is>
+          <t>「正しい日付を入力してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I230" s="4" t="n"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="n"/>
+      <c r="B231" s="4" t="n"/>
+      <c r="C231" s="4" t="n"/>
+      <c r="D231" s="4" t="n"/>
+      <c r="E231" s="9" t="inlineStr">
+        <is>
           <t>17-1-20</t>
         </is>
       </c>
-      <c r="F230" s="9" t="inlineStr">
+      <c r="F231" s="9" t="inlineStr">
         <is>
           <t>期日に今日の日付を指定した場合、計画を作成できる</t>
         </is>
       </c>
-      <c r="G230" s="9" t="inlineStr">
+      <c r="G231" s="9" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
 2.書籍を選択し、期日に今日の日付を指定して登録する</t>
         </is>
       </c>
-      <c r="H230" s="9" t="inlineStr">
+      <c r="H231" s="9" t="inlineStr">
         <is>
           <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される（今日の日付は指定可能）</t>
         </is>
       </c>
-      <c r="I230" s="4" t="n"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="5" t="n"/>
-      <c r="B231" s="5" t="n"/>
-      <c r="C231" s="5" t="n"/>
-      <c r="D231" s="5" t="n"/>
-      <c r="E231" s="9" t="inlineStr">
+      <c r="I231" s="4" t="n"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="n"/>
+      <c r="B232" s="4" t="n"/>
+      <c r="C232" s="4" t="n"/>
+      <c r="D232" s="4" t="n"/>
+      <c r="E232" s="9" t="inlineStr">
         <is>
           <t>17-1-21</t>
         </is>
       </c>
-      <c r="F231" s="9" t="inlineStr">
+      <c r="F232" s="9" t="inlineStr">
         <is>
           <t>同じ書籍に進行中の計画がある状態で不正な期日を指定しても、入力エラーではなく403になる</t>
         </is>
       </c>
-      <c r="G231" s="9" t="inlineStr">
+      <c r="G232" s="9" t="inlineStr">
         <is>
           <t>1.進行中の計画がある書籍を指定し、期日を空にして直接計画作成のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H231" s="9" t="inlineStr">
+      <c r="H232" s="9" t="inlineStr">
         <is>
           <t>バリデーションエラーではなく403Forbiddenになり、計画は作成されない（認可チェックが入力チェックより先に行われる）</t>
         </is>
       </c>
-      <c r="I231" s="5" t="n"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="7" t="inlineStr">
+      <c r="I232" s="4" t="n"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="5" t="n"/>
+      <c r="B233" s="5" t="n"/>
+      <c r="C233" s="5" t="n"/>
+      <c r="D233" s="5" t="n"/>
+      <c r="E233" s="9" t="inlineStr">
+        <is>
+          <t>17-1-22</t>
+        </is>
+      </c>
+      <c r="F233" s="9" t="inlineStr">
+        <is>
+          <t>ステータスが「期限切れ」の計画は、読了操作を行える</t>
+        </is>
+      </c>
+      <c r="G233" s="9" t="inlineStr">
+        <is>
+          <t>1.「期限切れ」の計画に対して、読了操作を行う</t>
+        </is>
+      </c>
+      <c r="H233" s="9" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」になり、completed_atに現在日時が記録され、「「(タイトル)」を読了しました。」と表示される</t>
+        </is>
+      </c>
+      <c r="I233" s="5" t="n"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="7" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B232" s="7" t="inlineStr">
+      <c r="B234" s="7" t="inlineStr">
         <is>
           <t>読書計画（期限変更）</t>
         </is>
       </c>
-      <c r="C232" s="7" t="inlineStr">
+      <c r="C234" s="7" t="inlineStr">
         <is>
           <t>18-1</t>
         </is>
       </c>
-      <c r="D232" s="7" t="inlineStr">
+      <c r="D234" s="7" t="inlineStr">
         <is>
           <t>読書計画の期日変更</t>
         </is>
       </c>
-      <c r="E232" s="7" t="inlineStr">
+      <c r="E234" s="7" t="inlineStr">
         <is>
           <t>18-1-1</t>
         </is>
       </c>
-      <c r="F232" s="7" t="inlineStr">
+      <c r="F234" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
         </is>
       </c>
-      <c r="G232" s="7" t="inlineStr">
+      <c r="G234" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H232" s="7" t="inlineStr">
+      <c r="H234" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I232" s="7" t="inlineStr">
+      <c r="I234" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="233">
-      <c r="A233" s="4" t="n"/>
-      <c r="B233" s="4" t="n"/>
-      <c r="C233" s="4" t="n"/>
-      <c r="D233" s="4" t="n"/>
-      <c r="E233" s="7" t="inlineStr">
-        <is>
-          <t>18-1-2</t>
-        </is>
-      </c>
-      <c r="F233" s="7" t="inlineStr">
-        <is>
-          <t>他人が作成した読書計画の期日は変更できない</t>
-        </is>
-      </c>
-      <c r="G233" s="7" t="inlineStr">
-        <is>
-          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H233" s="7" t="inlineStr">
-        <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
-        </is>
-      </c>
-      <c r="I233" s="4" t="n"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="4" t="n"/>
-      <c r="B234" s="4" t="n"/>
-      <c r="C234" s="4" t="n"/>
-      <c r="D234" s="4" t="n"/>
-      <c r="E234" s="7" t="inlineStr">
-        <is>
-          <t>18-1-3</t>
-        </is>
-      </c>
-      <c r="F234" s="7" t="inlineStr">
-        <is>
-          <t>編集画面を開くと現在の期日が初期表示される</t>
-        </is>
-      </c>
-      <c r="G234" s="7" t="inlineStr">
-        <is>
-          <t>1.自分が作成した計画の編集ページを開く</t>
-        </is>
-      </c>
-      <c r="H234" s="7" t="inlineStr">
-        <is>
-          <t>現在登録されている期日が入力欄に表示される</t>
-        </is>
-      </c>
-      <c r="I234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="n"/>
@@ -7729,23 +7729,22 @@
       <c r="D235" s="4" t="n"/>
       <c r="E235" s="7" t="inlineStr">
         <is>
-          <t>18-1-4</t>
+          <t>18-1-2</t>
         </is>
       </c>
       <c r="F235" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>他人が作成した読書計画の期日は変更できない</t>
         </is>
       </c>
       <c r="G235" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.期日を空にして更新する</t>
+          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H235" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
       <c r="I235" s="4" t="n"/>
@@ -7757,23 +7756,22 @@
       <c r="D236" s="4" t="n"/>
       <c r="E236" s="7" t="inlineStr">
         <is>
-          <t>18-1-5</t>
+          <t>18-1-3</t>
         </is>
       </c>
       <c r="F236" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>編集画面を開くと現在の期日が初期表示される</t>
         </is>
       </c>
       <c r="G236" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.過去の日付に変更して更新する</t>
+          <t>1.自分が作成した計画の編集ページを開く</t>
         </is>
       </c>
       <c r="H236" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>現在登録されている期日が入力欄に表示される</t>
         </is>
       </c>
       <c r="I236" s="4" t="n"/>
@@ -7785,23 +7783,23 @@
       <c r="D237" s="4" t="n"/>
       <c r="E237" s="7" t="inlineStr">
         <is>
-          <t>18-1-6</t>
+          <t>18-1-4</t>
         </is>
       </c>
       <c r="F237" s="7" t="inlineStr">
         <is>
-          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G237" s="7" t="inlineStr">
         <is>
           <t>1.編集ページを開く
-2.未来の日付に正しく変更して更新する</t>
+2.期日を空にして更新する</t>
         </is>
       </c>
       <c r="H237" s="7" t="inlineStr">
         <is>
-          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I237" s="4" t="n"/>
@@ -7813,23 +7811,23 @@
       <c r="D238" s="4" t="n"/>
       <c r="E238" s="7" t="inlineStr">
         <is>
-          <t>18-1-7</t>
+          <t>18-1-5</t>
         </is>
       </c>
       <c r="F238" s="7" t="inlineStr">
         <is>
-          <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G238" s="7" t="inlineStr">
         <is>
-          <t>1.期日が過去で「進行中」の計画を用意する
-2.読書計画一覧または編集ページを開く</t>
+          <t>1.編集ページを開く
+2.過去の日付に変更して更新する</t>
         </is>
       </c>
       <c r="H238" s="7" t="inlineStr">
         <is>
-          <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I238" s="4" t="n"/>
@@ -7841,22 +7839,23 @@
       <c r="D239" s="4" t="n"/>
       <c r="E239" s="7" t="inlineStr">
         <is>
-          <t>18-1-8</t>
+          <t>18-1-6</t>
         </is>
       </c>
       <c r="F239" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は期日を変更できない</t>
+          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
         </is>
       </c>
       <c r="G239" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
+          <t>1.編集ページを開く
+2.未来の日付に正しく変更して更新する</t>
         </is>
       </c>
       <c r="H239" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
+          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
         </is>
       </c>
       <c r="I239" s="4" t="n"/>
@@ -7868,22 +7867,23 @@
       <c r="D240" s="4" t="n"/>
       <c r="E240" s="7" t="inlineStr">
         <is>
-          <t>18-1-9</t>
+          <t>18-1-7</t>
         </is>
       </c>
       <c r="F240" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
+          <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
         </is>
       </c>
       <c r="G240" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
+          <t>1.期日が過去で「進行中」の計画を用意する
+2.読書計画一覧または編集ページを開く</t>
         </is>
       </c>
       <c r="H240" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、編集ページは表示されない</t>
+          <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
         </is>
       </c>
       <c r="I240" s="4" t="n"/>
@@ -7895,22 +7895,22 @@
       <c r="D241" s="4" t="n"/>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>18-1-10</t>
+          <t>18-1-8</t>
         </is>
       </c>
       <c r="F241" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画の編集ページにはアクセスできない</t>
+          <t>ステータスが「完了」の計画は期日を変更できない</t>
         </is>
       </c>
       <c r="G241" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画の編集ページのURLに直接アクセスする</t>
+          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H241" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、編集ページは表示されない</t>
+          <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
       <c r="I241" s="4" t="n"/>
@@ -7922,158 +7922,156 @@
       <c r="D242" s="4" t="n"/>
       <c r="E242" s="7" t="inlineStr">
         <is>
+          <t>18-1-9</t>
+        </is>
+      </c>
+      <c r="F242" s="7" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
+        </is>
+      </c>
+      <c r="G242" s="7" t="inlineStr">
+        <is>
+          <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
+        </is>
+      </c>
+      <c r="H242" s="7" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、編集ページは表示されない</t>
+        </is>
+      </c>
+      <c r="I242" s="4" t="n"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="n"/>
+      <c r="B243" s="4" t="n"/>
+      <c r="C243" s="4" t="n"/>
+      <c r="D243" s="4" t="n"/>
+      <c r="E243" s="7" t="inlineStr">
+        <is>
+          <t>18-1-10</t>
+        </is>
+      </c>
+      <c r="F243" s="7" t="inlineStr">
+        <is>
+          <t>他人が作成した読書計画の編集ページにはアクセスできない</t>
+        </is>
+      </c>
+      <c r="G243" s="7" t="inlineStr">
+        <is>
+          <t>1.他人が作成した計画の編集ページのURLに直接アクセスする</t>
+        </is>
+      </c>
+      <c r="H243" s="7" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、編集ページは表示されない</t>
+        </is>
+      </c>
+      <c r="I243" s="4" t="n"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="n"/>
+      <c r="B244" s="4" t="n"/>
+      <c r="C244" s="4" t="n"/>
+      <c r="D244" s="4" t="n"/>
+      <c r="E244" s="7" t="inlineStr">
+        <is>
           <t>18-1-11</t>
         </is>
       </c>
-      <c r="F242" s="7" t="inlineStr">
+      <c r="F244" s="7" t="inlineStr">
         <is>
           <t>同じ書籍に「進行中」の計画がある場合、「期限切れ」の計画は編集・更新できない</t>
         </is>
       </c>
-      <c r="G242" s="7" t="inlineStr">
+      <c r="G244" s="7" t="inlineStr">
         <is>
           <t>1.同じ書籍について、「期限切れ」の計画と「進行中」の計画をそれぞれ用意する
 2.「期限切れ」の計画の編集ページのURLに直接アクセスする
 3.「期限切れ」の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
-      <c r="H242" s="7" t="inlineStr">
+      <c r="H244" s="7" t="inlineStr">
         <is>
           <t>いずれも403Forbiddenになり、「期限切れ」の計画のステータス・期日は変更されない（同じ書籍の「進行中」の計画が2件になることを防ぐ）</t>
         </is>
       </c>
-      <c r="I242" s="4" t="n"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="5" t="n"/>
-      <c r="B243" s="5" t="n"/>
-      <c r="C243" s="5" t="n"/>
-      <c r="D243" s="5" t="n"/>
-      <c r="E243" s="7" t="inlineStr">
+      <c r="I244" s="4" t="n"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="5" t="n"/>
+      <c r="B245" s="5" t="n"/>
+      <c r="C245" s="5" t="n"/>
+      <c r="D245" s="5" t="n"/>
+      <c r="E245" s="7" t="inlineStr">
         <is>
           <t>18-1-12</t>
         </is>
       </c>
-      <c r="F243" s="7" t="inlineStr">
+      <c r="F245" s="7" t="inlineStr">
         <is>
           <t>他人が作成した読書計画に不正な期日で更新しようとしても、入力エラーではなく403になる</t>
         </is>
       </c>
-      <c r="G243" s="7" t="inlineStr">
+      <c r="G245" s="7" t="inlineStr">
         <is>
           <t>1.他人が作成した読書計画に対して、期日を空にして直接計画更新のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H243" s="7" t="inlineStr">
+      <c r="H245" s="7" t="inlineStr">
         <is>
           <t>バリデーションエラーではなく403Forbiddenになり、期日は変更されない（認可チェックが入力チェックより先に行われる）</t>
         </is>
       </c>
-      <c r="I243" s="5" t="n"/>
-    </row>
-    <row r="244">
-      <c r="A244" s="7" t="inlineStr">
+      <c r="I245" s="5" t="n"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B244" s="7" t="inlineStr">
+      <c r="B246" s="7" t="inlineStr">
         <is>
           <t>リマインダーバッチ</t>
         </is>
       </c>
-      <c r="C244" s="7" t="inlineStr">
+      <c r="C246" s="7" t="inlineStr">
         <is>
           <t>19-1</t>
         </is>
       </c>
-      <c r="D244" s="7" t="inlineStr">
+      <c r="D246" s="7" t="inlineStr">
         <is>
           <t>日次バッチ(reading-plans:daily)によるリマインダー通知</t>
         </is>
       </c>
-      <c r="E244" s="7" t="inlineStr">
+      <c r="E246" s="7" t="inlineStr">
         <is>
           <t>19-1-1</t>
         </is>
       </c>
-      <c r="F244" s="7" t="inlineStr">
+      <c r="F246" s="7" t="inlineStr">
         <is>
           <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
         </is>
       </c>
-      <c r="G244" s="7" t="inlineStr">
+      <c r="G246" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日後・ステータス進行中の計画を用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
-      <c r="H244" s="7" t="inlineStr">
+      <c r="H246" s="7" t="inlineStr">
         <is>
           <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_before)・title(「読書期限のお知らせ」)・body(「「(書籍名)」の読書期限まであと3日です。」)が含まれる</t>
         </is>
       </c>
-      <c r="I244" s="7" t="inlineStr">
+      <c r="I246" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="4" t="n"/>
-      <c r="B245" s="4" t="n"/>
-      <c r="C245" s="4" t="n"/>
-      <c r="D245" s="4" t="n"/>
-      <c r="E245" s="7" t="inlineStr">
-        <is>
-          <t>19-1-2</t>
-        </is>
-      </c>
-      <c r="F245" s="7" t="inlineStr">
-        <is>
-          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
-        </is>
-      </c>
-      <c r="G245" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが本日・ステータス進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H245" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される。通知のdataには、plan_id・book_title・timing(on_due_date)・title(「読書期限当日のお知らせ」)・body(「「(書籍名)」の読書期限は本日までです。」)が含まれる</t>
-        </is>
-      </c>
-      <c r="I245" s="4" t="n"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="4" t="n"/>
-      <c r="B246" s="4" t="n"/>
-      <c r="C246" s="4" t="n"/>
-      <c r="D246" s="4" t="n"/>
-      <c r="E246" s="7" t="inlineStr">
-        <is>
-          <t>19-1-3</t>
-        </is>
-      </c>
-      <c r="F246" s="7" t="inlineStr">
-        <is>
-          <t>期限切れから3日後の計画に再エンゲージメント通知が送信される</t>
-        </is>
-      </c>
-      <c r="G246" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが3日前・ステータス期限切れの計画を用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H246" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
-        </is>
-      </c>
-      <c r="I246" s="4" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="n"/>
@@ -8082,479 +8080,479 @@
       <c r="D247" s="4" t="n"/>
       <c r="E247" s="7" t="inlineStr">
         <is>
+          <t>19-1-2</t>
+        </is>
+      </c>
+      <c r="F247" s="7" t="inlineStr">
+        <is>
+          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
+        </is>
+      </c>
+      <c r="G247" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが本日・ステータス進行中の計画を用意する
+2.reading-plans:dailyを実行する</t>
+        </is>
+      </c>
+      <c r="H247" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される。通知のdataには、plan_id・book_title・timing(on_due_date)・title(「読書期限当日のお知らせ」)・body(「「(書籍名)」の読書期限は本日までです。」)が含まれる</t>
+        </is>
+      </c>
+      <c r="I247" s="4" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="n"/>
+      <c r="B248" s="4" t="n"/>
+      <c r="C248" s="4" t="n"/>
+      <c r="D248" s="4" t="n"/>
+      <c r="E248" s="7" t="inlineStr">
+        <is>
+          <t>19-1-3</t>
+        </is>
+      </c>
+      <c r="F248" s="7" t="inlineStr">
+        <is>
+          <t>期限切れから3日後の計画に再エンゲージメント通知が送信される</t>
+        </is>
+      </c>
+      <c r="G248" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日前・ステータス期限切れの計画を用意する
+2.reading-plans:dailyを実行する</t>
+        </is>
+      </c>
+      <c r="H248" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="n"/>
+      <c r="B249" s="4" t="n"/>
+      <c r="C249" s="4" t="n"/>
+      <c r="D249" s="4" t="n"/>
+      <c r="E249" s="7" t="inlineStr">
+        <is>
           <t>19-1-4</t>
         </is>
       </c>
-      <c r="F247" s="7" t="inlineStr">
+      <c r="F249" s="7" t="inlineStr">
         <is>
           <t>いずれの条件にも該当しない計画には通知が送信されない</t>
         </is>
       </c>
-      <c r="G247" s="7" t="inlineStr">
+      <c r="G249" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H247" s="7" t="inlineStr">
+      <c r="H249" s="7" t="inlineStr">
         <is>
           <t>その計画のユーザーに通知が送信されない</t>
         </is>
       </c>
-      <c r="I247" s="4" t="n"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="5" t="n"/>
-      <c r="B248" s="5" t="n"/>
-      <c r="C248" s="5" t="n"/>
-      <c r="D248" s="5" t="n"/>
-      <c r="E248" s="7" t="inlineStr">
+      <c r="I249" s="4" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="n"/>
+      <c r="B250" s="5" t="n"/>
+      <c r="C250" s="5" t="n"/>
+      <c r="D250" s="5" t="n"/>
+      <c r="E250" s="7" t="inlineStr">
         <is>
           <t>19-1-5</t>
         </is>
       </c>
-      <c r="F248" s="7" t="inlineStr">
+      <c r="F250" s="7" t="inlineStr">
         <is>
           <t>ステータスが「完了」の計画には、期日の条件に合っていても通知が送信されない</t>
         </is>
       </c>
-      <c r="G248" s="7" t="inlineStr">
+      <c r="G250" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日後・本日・3日前で、ステータスが完了の計画をそれぞれ用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
-      <c r="H248" s="7" t="inlineStr">
+      <c r="H250" s="7" t="inlineStr">
         <is>
           <t>いずれの計画のユーザーにも通知が送信されない</t>
         </is>
       </c>
-      <c r="I248" s="5" t="n"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="7" t="inlineStr">
+      <c r="I250" s="5" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B249" s="7" t="inlineStr">
+      <c r="B251" s="7" t="inlineStr">
         <is>
           <t>自動失効バッチ</t>
         </is>
       </c>
-      <c r="C249" s="7" t="inlineStr">
+      <c r="C251" s="7" t="inlineStr">
         <is>
           <t>20-1</t>
         </is>
       </c>
-      <c r="D249" s="7" t="inlineStr">
+      <c r="D251" s="7" t="inlineStr">
         <is>
           <t>日次バッチ(reading-plans:daily)による自動失効処理</t>
         </is>
       </c>
-      <c r="E249" s="7" t="inlineStr">
+      <c r="E251" s="7" t="inlineStr">
         <is>
           <t>20-1-1</t>
         </is>
       </c>
-      <c r="F249" s="7" t="inlineStr">
+      <c r="F251" s="7" t="inlineStr">
         <is>
           <t>期日を過ぎた「進行中」の計画が「期限切れ」に更新される</t>
         </is>
       </c>
-      <c r="G249" s="7" t="inlineStr">
+      <c r="G251" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが過去・ステータス進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H249" s="7" t="inlineStr">
+      <c r="H251" s="7" t="inlineStr">
         <is>
           <t>対象の計画のstatusが「期限切れ」に更新される</t>
         </is>
       </c>
-      <c r="I249" s="7" t="inlineStr">
+      <c r="I251" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="4" t="n"/>
-      <c r="B250" s="4" t="n"/>
-      <c r="C250" s="4" t="n"/>
-      <c r="D250" s="4" t="n"/>
-      <c r="E250" s="7" t="inlineStr">
-        <is>
-          <t>20-1-2</t>
-        </is>
-      </c>
-      <c r="F250" s="7" t="inlineStr">
-        <is>
-          <t>期日が今日以降の「進行中」の計画は失効しない</t>
-        </is>
-      </c>
-      <c r="G250" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H250" s="7" t="inlineStr">
-        <is>
-          <t>その計画のstatusは「進行中」のまま変化しない</t>
-        </is>
-      </c>
-      <c r="I250" s="4" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="4" t="n"/>
-      <c r="B251" s="4" t="n"/>
-      <c r="C251" s="4" t="n"/>
-      <c r="D251" s="4" t="n"/>
-      <c r="E251" s="7" t="inlineStr">
-        <is>
-          <t>20-1-3</t>
-        </is>
-      </c>
-      <c r="F251" s="7" t="inlineStr">
-        <is>
-          <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
-        </is>
-      </c>
-      <c r="G251" s="7" t="inlineStr">
-        <is>
-          <t>1.完了済み・期限切れの計画をそれぞれ用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H251" s="7" t="inlineStr">
-        <is>
-          <t>いずれの計画もstatusが変化しない</t>
-        </is>
-      </c>
-      <c r="I251" s="4" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="4" t="n"/>
       <c r="B252" s="4" t="n"/>
-      <c r="C252" s="5" t="n"/>
-      <c r="D252" s="5" t="n"/>
+      <c r="C252" s="4" t="n"/>
+      <c r="D252" s="4" t="n"/>
       <c r="E252" s="7" t="inlineStr">
         <is>
-          <t>20-1-4</t>
+          <t>20-1-2</t>
         </is>
       </c>
       <c r="F252" s="7" t="inlineStr">
         <is>
-          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+          <t>期日が今日以降の「進行中」の計画は失効しない</t>
         </is>
       </c>
       <c r="G252" s="7" t="inlineStr">
         <is>
-          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
-2.DBを直接確認する</t>
+          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H252" s="7" t="inlineStr">
         <is>
-          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
-        </is>
-      </c>
-      <c r="I252" s="5" t="n"/>
+          <t>その計画のstatusは「進行中」のまま変化しない</t>
+        </is>
+      </c>
+      <c r="I252" s="4" t="n"/>
     </row>
     <row r="253">
       <c r="A253" s="4" t="n"/>
       <c r="B253" s="4" t="n"/>
-      <c r="C253" s="7" t="inlineStr">
-        <is>
-          <t>20-2</t>
-        </is>
-      </c>
-      <c r="D253" s="7" t="inlineStr">
-        <is>
-          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
-        </is>
-      </c>
+      <c r="C253" s="4" t="n"/>
+      <c r="D253" s="4" t="n"/>
       <c r="E253" s="7" t="inlineStr">
         <is>
-          <t>20-2-1</t>
+          <t>20-1-3</t>
         </is>
       </c>
       <c r="F253" s="7" t="inlineStr">
         <is>
-          <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
+          <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
         </is>
       </c>
       <c r="G253" s="7" t="inlineStr">
         <is>
-          <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+          <t>1.完了済み・期限切れの計画をそれぞれ用意する
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H253" s="7" t="inlineStr">
         <is>
-          <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I253" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
-        </is>
-      </c>
+          <t>いずれの計画もstatusが変化しない</t>
+        </is>
+      </c>
+      <c r="I253" s="4" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="4" t="n"/>
       <c r="B254" s="4" t="n"/>
-      <c r="C254" s="4" t="n"/>
-      <c r="D254" s="4" t="n"/>
+      <c r="C254" s="5" t="n"/>
+      <c r="D254" s="5" t="n"/>
       <c r="E254" s="7" t="inlineStr">
         <is>
+          <t>20-1-4</t>
+        </is>
+      </c>
+      <c r="F254" s="7" t="inlineStr">
+        <is>
+          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+        </is>
+      </c>
+      <c r="G254" s="7" t="inlineStr">
+        <is>
+          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
+2.DBを直接確認する</t>
+        </is>
+      </c>
+      <c r="H254" s="7" t="inlineStr">
+        <is>
+          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
+        </is>
+      </c>
+      <c r="I254" s="5" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="n"/>
+      <c r="B255" s="4" t="n"/>
+      <c r="C255" s="7" t="inlineStr">
+        <is>
+          <t>20-2</t>
+        </is>
+      </c>
+      <c r="D255" s="7" t="inlineStr">
+        <is>
+          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
+        </is>
+      </c>
+      <c r="E255" s="7" t="inlineStr">
+        <is>
+          <t>20-2-1</t>
+        </is>
+      </c>
+      <c r="F255" s="7" t="inlineStr">
+        <is>
+          <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
+        </is>
+      </c>
+      <c r="G255" s="7" t="inlineStr">
+        <is>
+          <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+        </is>
+      </c>
+      <c r="H255" s="7" t="inlineStr">
+        <is>
+          <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I255" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="n"/>
+      <c r="B256" s="4" t="n"/>
+      <c r="C256" s="4" t="n"/>
+      <c r="D256" s="4" t="n"/>
+      <c r="E256" s="7" t="inlineStr">
+        <is>
           <t>20-2-2</t>
         </is>
       </c>
-      <c r="F254" s="7" t="inlineStr">
+      <c r="F256" s="7" t="inlineStr">
         <is>
           <t>期限切れへの更新が、通知対象の抽出より先に行われる</t>
         </is>
       </c>
-      <c r="G254" s="7" t="inlineStr">
+      <c r="G256" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日前で、ステータスが「進行中」のまま(未更新)の計画を用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
-      <c r="H254" s="7" t="inlineStr">
+      <c r="H256" s="7" t="inlineStr">
         <is>
           <t>計画のstatusが「期限切れ」に更新され、そのユーザーに再エンゲージメント(re_engagement)通知が送信される</t>
         </is>
       </c>
-      <c r="I254" s="4" t="n"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="5" t="n"/>
-      <c r="B255" s="5" t="n"/>
-      <c r="C255" s="5" t="n"/>
-      <c r="D255" s="5" t="n"/>
-      <c r="E255" s="7" t="inlineStr">
+      <c r="I256" s="4" t="n"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="5" t="n"/>
+      <c r="B257" s="5" t="n"/>
+      <c r="C257" s="5" t="n"/>
+      <c r="D257" s="5" t="n"/>
+      <c r="E257" s="7" t="inlineStr">
         <is>
           <t>20-2-3</t>
         </is>
       </c>
-      <c r="F255" s="7" t="inlineStr">
+      <c r="F257" s="7" t="inlineStr">
         <is>
           <t>reading-plans:dailyが毎日20:00に実行されるようスケジュールされている</t>
         </is>
       </c>
-      <c r="G255" s="7" t="inlineStr">
+      <c r="G257" s="7" t="inlineStr">
         <is>
           <t>1.アプリケーションのスケジュール(Illuminate\Console\Scheduling\Schedule)から、登録済みのイベントを取得する</t>
         </is>
       </c>
-      <c r="H255" s="7" t="inlineStr">
+      <c r="H257" s="7" t="inlineStr">
         <is>
           <t>reading-plans:dailyのイベントが登録されており、cron式が毎日20:00(0 20 * * *)になっている</t>
         </is>
       </c>
-      <c r="I255" s="5" t="n"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="9" t="inlineStr">
+      <c r="I257" s="5" t="n"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B256" s="9" t="inlineStr">
+      <c r="B258" s="9" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="C256" s="9" t="inlineStr">
+      <c r="C258" s="9" t="inlineStr">
         <is>
           <t>21-1</t>
         </is>
       </c>
-      <c r="D256" s="9" t="inlineStr">
+      <c r="D258" s="9" t="inlineStr">
         <is>
           <t>通知の既読化</t>
         </is>
       </c>
-      <c r="E256" s="9" t="inlineStr">
+      <c r="E258" s="9" t="inlineStr">
         <is>
           <t>21-1-1</t>
         </is>
       </c>
-      <c r="F256" s="9" t="inlineStr">
+      <c r="F258" s="9" t="inlineStr">
         <is>
           <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
         </is>
       </c>
-      <c r="G256" s="9" t="inlineStr">
+      <c r="G258" s="9" t="inlineStr">
         <is>
           <t>1.未ログイン状態でPOST /notifications/{id}/read に直接リクエストを送信する</t>
         </is>
       </c>
-      <c r="H256" s="9" t="inlineStr">
+      <c r="H258" s="9" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
         </is>
       </c>
-      <c r="I256" s="9" t="inlineStr">
+      <c r="I258" s="9" t="inlineStr">
         <is>
           <t>tests/Feature/Notification/NotificationTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="4" t="n"/>
-      <c r="B257" s="4" t="n"/>
-      <c r="C257" s="4" t="n"/>
-      <c r="D257" s="4" t="n"/>
-      <c r="E257" s="9" t="inlineStr">
-        <is>
-          <t>21-1-2</t>
-        </is>
-      </c>
-      <c r="F257" s="9" t="inlineStr">
-        <is>
-          <t>自分の通知を既読にできる</t>
-        </is>
-      </c>
-      <c r="G257" s="9" t="inlineStr">
-        <is>
-          <t>1.自分宛ての未読通知を用意する
-2.その通知に対してPOST /notifications/{id}/read を送信する</t>
-        </is>
-      </c>
-      <c r="H257" s="9" t="inlineStr">
-        <is>
-          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
-        </is>
-      </c>
-      <c r="I257" s="4" t="n"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="4" t="n"/>
-      <c r="B258" s="4" t="n"/>
-      <c r="C258" s="5" t="n"/>
-      <c r="D258" s="5" t="n"/>
-      <c r="E258" s="9" t="inlineStr">
-        <is>
-          <t>21-1-3</t>
-        </is>
-      </c>
-      <c r="F258" s="9" t="inlineStr">
-        <is>
-          <t>他ユーザーの通知は既読にできない</t>
-        </is>
-      </c>
-      <c r="G258" s="9" t="inlineStr">
-        <is>
-          <t>1.他ユーザー宛ての通知を用意する
-2.そのIDに対してPOST /notifications/{id}/read を送信する</t>
-        </is>
-      </c>
-      <c r="H258" s="9" t="inlineStr">
-        <is>
-          <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
-        </is>
-      </c>
-      <c r="I258" s="5" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n"/>
       <c r="B259" s="4" t="n"/>
-      <c r="C259" s="9" t="inlineStr">
-        <is>
-          <t>21-2</t>
-        </is>
-      </c>
-      <c r="D259" s="9" t="inlineStr">
-        <is>
-          <t>通知一覧</t>
-        </is>
-      </c>
+      <c r="C259" s="4" t="n"/>
+      <c r="D259" s="4" t="n"/>
       <c r="E259" s="9" t="inlineStr">
         <is>
-          <t>21-2-1</t>
+          <t>21-1-2</t>
         </is>
       </c>
       <c r="F259" s="9" t="inlineStr">
         <is>
-          <t>未ログインの場合、通知一覧にアクセスできない</t>
+          <t>自分の通知を既読にできる</t>
         </is>
       </c>
       <c r="G259" s="9" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
+          <t>1.自分宛ての未読通知を用意する
+2.その通知に対してPOST /notifications/{id}/read を送信する</t>
         </is>
       </c>
       <c r="H259" s="9" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I259" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationIndexTest.php</t>
-        </is>
-      </c>
+          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
+        </is>
+      </c>
+      <c r="I259" s="4" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="4" t="n"/>
       <c r="B260" s="4" t="n"/>
-      <c r="C260" s="4" t="n"/>
-      <c r="D260" s="4" t="n"/>
+      <c r="C260" s="5" t="n"/>
+      <c r="D260" s="5" t="n"/>
       <c r="E260" s="9" t="inlineStr">
         <is>
-          <t>21-2-2</t>
+          <t>21-1-3</t>
         </is>
       </c>
       <c r="F260" s="9" t="inlineStr">
         <is>
-          <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
+          <t>他ユーザーの通知は既読にできない</t>
         </is>
       </c>
       <c r="G260" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
-2.通知一覧ページを開く</t>
+          <t>1.他ユーザー宛ての通知を用意する
+2.そのIDに対してPOST /notifications/{id}/read を送信する</t>
         </is>
       </c>
       <c r="H260" s="9" t="inlineStr">
         <is>
-          <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
-        </is>
-      </c>
-      <c r="I260" s="4" t="n"/>
+          <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
+        </is>
+      </c>
+      <c r="I260" s="5" t="n"/>
     </row>
     <row r="261">
       <c r="A261" s="4" t="n"/>
       <c r="B261" s="4" t="n"/>
-      <c r="C261" s="4" t="n"/>
-      <c r="D261" s="4" t="n"/>
+      <c r="C261" s="9" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="D261" s="9" t="inlineStr">
+        <is>
+          <t>通知一覧</t>
+        </is>
+      </c>
       <c r="E261" s="9" t="inlineStr">
         <is>
-          <t>21-2-3</t>
+          <t>21-2-1</t>
         </is>
       </c>
       <c r="F261" s="9" t="inlineStr">
         <is>
-          <t>通知が1件もない場合の表示を確認する</t>
+          <t>未ログインの場合、通知一覧にアクセスできない</t>
         </is>
       </c>
       <c r="G261" s="9" t="inlineStr">
         <is>
-          <t>1.通知が1件もないユーザーでログインする
-2.通知一覧ページを開く</t>
+          <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H261" s="9" t="inlineStr">
         <is>
-          <t>「通知はありません。」と表示される</t>
-        </is>
-      </c>
-      <c r="I261" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I261" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationIndexTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="4" t="n"/>
@@ -8563,23 +8561,23 @@
       <c r="D262" s="4" t="n"/>
       <c r="E262" s="9" t="inlineStr">
         <is>
-          <t>21-2-4</t>
+          <t>21-2-2</t>
         </is>
       </c>
       <c r="F262" s="9" t="inlineStr">
         <is>
-          <t>通知のタイトル・本文が表示される</t>
+          <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
         </is>
       </c>
       <c r="G262" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
+          <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H262" s="9" t="inlineStr">
         <is>
-          <t>通知のtitleとbodyが一覧に表示される</t>
+          <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
         </is>
       </c>
       <c r="I262" s="4" t="n"/>
@@ -8591,23 +8589,23 @@
       <c r="D263" s="4" t="n"/>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>21-2-5</t>
+          <t>21-2-3</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>未読と既読で表示が異なる</t>
+          <t>通知が1件もない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G263" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
+          <t>1.通知が1件もないユーザーでログインする
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H263" s="9" t="inlineStr">
         <is>
-          <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
+          <t>「通知はありません。」と表示される</t>
         </is>
       </c>
       <c r="I263" s="4" t="n"/>
@@ -8615,306 +8613,362 @@
     <row r="264">
       <c r="A264" s="4" t="n"/>
       <c r="B264" s="4" t="n"/>
-      <c r="C264" s="5" t="n"/>
-      <c r="D264" s="5" t="n"/>
+      <c r="C264" s="4" t="n"/>
+      <c r="D264" s="4" t="n"/>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>21-2-6</t>
+          <t>21-2-4</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>同じ日時に作成された通知は、期日3日前→期日当日→期日3日後の順に表示される</t>
+          <t>通知のタイトル・本文が表示される</t>
         </is>
       </c>
       <c r="G264" s="9" t="inlineStr">
         <is>
-          <t>1.同じ日時に作成された、期日3日前（予告）・期日当日（最終警告）・期日3日後（再エンゲージメント）の通知と、作成日時の異なる通知を用意する
+          <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H264" s="9" t="inlineStr">
         <is>
-          <t>第1優先で作成日時の新しい順、作成日時が同じ通知同士は第2優先で「期日3日前→期日当日→期日3日後」の順に表示される</t>
-        </is>
-      </c>
-      <c r="I264" s="5" t="n"/>
+          <t>通知のtitleとbodyが一覧に表示される</t>
+        </is>
+      </c>
+      <c r="I264" s="4" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="4" t="n"/>
       <c r="B265" s="4" t="n"/>
-      <c r="C265" s="9" t="inlineStr">
-        <is>
-          <t>21-3</t>
-        </is>
-      </c>
-      <c r="D265" s="9" t="inlineStr">
-        <is>
-          <t>ヘッダーの未読件数</t>
-        </is>
-      </c>
+      <c r="C265" s="4" t="n"/>
+      <c r="D265" s="4" t="n"/>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>21-3-1</t>
+          <t>21-2-5</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>ヘッダーのベルアイコンに未読件数が表示される</t>
+          <t>未読と既読で表示が異なる</t>
         </is>
       </c>
       <c r="G265" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
+          <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
+2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H265" s="9" t="inlineStr">
         <is>
-          <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
-        </is>
-      </c>
-      <c r="I265" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
-        </is>
-      </c>
+          <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
+        </is>
+      </c>
+      <c r="I265" s="4" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="4" t="n"/>
       <c r="B266" s="4" t="n"/>
-      <c r="C266" s="4" t="n"/>
-      <c r="D266" s="4" t="n"/>
+      <c r="C266" s="5" t="n"/>
+      <c r="D266" s="5" t="n"/>
       <c r="E266" s="9" t="inlineStr">
         <is>
+          <t>21-2-6</t>
+        </is>
+      </c>
+      <c r="F266" s="9" t="inlineStr">
+        <is>
+          <t>同じ日時に作成された通知は、期日3日前→期日当日→期日3日後の順に表示される</t>
+        </is>
+      </c>
+      <c r="G266" s="9" t="inlineStr">
+        <is>
+          <t>1.同じ日時に作成された、期日3日前（予告）・期日当日（最終警告）・期日3日後（再エンゲージメント）の通知と、作成日時の異なる通知を用意する
+2.通知一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H266" s="9" t="inlineStr">
+        <is>
+          <t>第1優先で作成日時の新しい順、作成日時が同じ通知同士は第2優先で「期日3日前→期日当日→期日3日後」の順に表示される</t>
+        </is>
+      </c>
+      <c r="I266" s="5" t="n"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="n"/>
+      <c r="B267" s="4" t="n"/>
+      <c r="C267" s="9" t="inlineStr">
+        <is>
+          <t>21-3</t>
+        </is>
+      </c>
+      <c r="D267" s="9" t="inlineStr">
+        <is>
+          <t>ヘッダーの未読件数</t>
+        </is>
+      </c>
+      <c r="E267" s="9" t="inlineStr">
+        <is>
+          <t>21-3-1</t>
+        </is>
+      </c>
+      <c r="F267" s="9" t="inlineStr">
+        <is>
+          <t>ヘッダーのベルアイコンに未読件数が表示される</t>
+        </is>
+      </c>
+      <c r="G267" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
+        </is>
+      </c>
+      <c r="H267" s="9" t="inlineStr">
+        <is>
+          <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
+        </is>
+      </c>
+      <c r="I267" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="n"/>
+      <c r="B268" s="4" t="n"/>
+      <c r="C268" s="4" t="n"/>
+      <c r="D268" s="4" t="n"/>
+      <c r="E268" s="9" t="inlineStr">
+        <is>
           <t>21-3-2</t>
         </is>
       </c>
-      <c r="F266" s="9" t="inlineStr">
+      <c r="F268" s="9" t="inlineStr">
         <is>
           <t>通知を既読にすると、ヘッダーの未読件数が減る</t>
         </is>
       </c>
-      <c r="G266" s="9" t="inlineStr">
+      <c r="G268" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知を複数件用意する
 2.そのうち1件にPOST /notifications/{id}/read を送信して既読にする
 3.画面を開き直す</t>
         </is>
       </c>
-      <c r="H266" s="9" t="inlineStr">
+      <c r="H268" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数が、既読にした1件分だけ減る</t>
         </is>
       </c>
-      <c r="I266" s="4" t="n"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="5" t="n"/>
-      <c r="B267" s="5" t="n"/>
-      <c r="C267" s="5" t="n"/>
-      <c r="D267" s="5" t="n"/>
-      <c r="E267" s="9" t="inlineStr">
+      <c r="I268" s="4" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="5" t="n"/>
+      <c r="B269" s="5" t="n"/>
+      <c r="C269" s="5" t="n"/>
+      <c r="D269" s="5" t="n"/>
+      <c r="E269" s="9" t="inlineStr">
         <is>
           <t>21-3-3</t>
         </is>
       </c>
-      <c r="F267" s="9" t="inlineStr">
+      <c r="F269" s="9" t="inlineStr">
         <is>
           <t>他ユーザーの通知は未読件数に含まれない</t>
         </is>
       </c>
-      <c r="G267" s="9" t="inlineStr">
+      <c r="G269" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知と、他ユーザー宛ての未読通知をそれぞれ用意する
 2.画面を開く</t>
         </is>
       </c>
-      <c r="H267" s="9" t="inlineStr">
+      <c r="H269" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数には、自分宛ての未読通知のみが数えられる</t>
         </is>
       </c>
-      <c r="I267" s="5" t="n"/>
+      <c r="I269" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="177">
-    <mergeCell ref="B31:B65"/>
-    <mergeCell ref="I17:I30"/>
-    <mergeCell ref="I114:I116"/>
-    <mergeCell ref="D91:D95"/>
-    <mergeCell ref="A17:A30"/>
-    <mergeCell ref="C153:C155"/>
-    <mergeCell ref="D12:D16"/>
-    <mergeCell ref="D194:D200"/>
-    <mergeCell ref="I244:I248"/>
-    <mergeCell ref="D117:D119"/>
-    <mergeCell ref="A66:A87"/>
-    <mergeCell ref="I120:I123"/>
-    <mergeCell ref="A194:A200"/>
-    <mergeCell ref="I124:I135"/>
+    <mergeCell ref="B121:B124"/>
     <mergeCell ref="I70:I75"/>
-    <mergeCell ref="I88:I90"/>
-    <mergeCell ref="B88:B109"/>
-    <mergeCell ref="C194:C200"/>
-    <mergeCell ref="I153:I155"/>
-    <mergeCell ref="A175:A181"/>
-    <mergeCell ref="A249:A255"/>
-    <mergeCell ref="B124:B141"/>
-    <mergeCell ref="D182:D186"/>
-    <mergeCell ref="D265:D267"/>
-    <mergeCell ref="C170:C174"/>
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="C107:C109"/>
+    <mergeCell ref="D164:D170"/>
+    <mergeCell ref="C251:C254"/>
     <mergeCell ref="I56:I61"/>
+    <mergeCell ref="D246:D250"/>
+    <mergeCell ref="D157:D163"/>
     <mergeCell ref="D35:D41"/>
     <mergeCell ref="C56:C61"/>
-    <mergeCell ref="C201:C206"/>
+    <mergeCell ref="I154:I156"/>
+    <mergeCell ref="C42:C55"/>
     <mergeCell ref="A2:A16"/>
-    <mergeCell ref="C42:C55"/>
-    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D183:D187"/>
+    <mergeCell ref="B125:B142"/>
+    <mergeCell ref="C157:C163"/>
     <mergeCell ref="C66:C69"/>
-    <mergeCell ref="I259:I264"/>
+    <mergeCell ref="C171:C175"/>
     <mergeCell ref="D17:D30"/>
-    <mergeCell ref="C232:C243"/>
-    <mergeCell ref="A187:A193"/>
-    <mergeCell ref="I91:I95"/>
-    <mergeCell ref="C156:C162"/>
-    <mergeCell ref="C187:C193"/>
-    <mergeCell ref="B244:B248"/>
-    <mergeCell ref="I12:I16"/>
-    <mergeCell ref="D107:D109"/>
-    <mergeCell ref="I194:I200"/>
-    <mergeCell ref="I117:I119"/>
-    <mergeCell ref="A124:A141"/>
-    <mergeCell ref="C182:C186"/>
-    <mergeCell ref="C35:C41"/>
-    <mergeCell ref="A207:A210"/>
-    <mergeCell ref="B175:B181"/>
-    <mergeCell ref="I156:I162"/>
-    <mergeCell ref="D175:D181"/>
-    <mergeCell ref="D249:D252"/>
-    <mergeCell ref="I142:I144"/>
-    <mergeCell ref="I182:I186"/>
-    <mergeCell ref="B120:B123"/>
+    <mergeCell ref="C143:C145"/>
+    <mergeCell ref="B111:B117"/>
+    <mergeCell ref="I143:I145"/>
+    <mergeCell ref="D137:D141"/>
+    <mergeCell ref="A212:A233"/>
+    <mergeCell ref="C212:C233"/>
     <mergeCell ref="D42:D55"/>
-    <mergeCell ref="I265:I267"/>
-    <mergeCell ref="D120:D123"/>
-    <mergeCell ref="D256:D258"/>
-    <mergeCell ref="C84:C87"/>
-    <mergeCell ref="D232:D243"/>
-    <mergeCell ref="C136:C140"/>
-    <mergeCell ref="I62:I65"/>
+    <mergeCell ref="A258:A269"/>
+    <mergeCell ref="I246:I250"/>
+    <mergeCell ref="I157:I163"/>
     <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D145:D152"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="A120:A123"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="I136:I140"/>
-    <mergeCell ref="D259:D264"/>
-    <mergeCell ref="I96:I101"/>
-    <mergeCell ref="D187:D193"/>
-    <mergeCell ref="D76:D83"/>
-    <mergeCell ref="C120:C123"/>
-    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="I89:I91"/>
+    <mergeCell ref="C154:C156"/>
+    <mergeCell ref="C202:C207"/>
+    <mergeCell ref="A111:A117"/>
+    <mergeCell ref="C92:C96"/>
+    <mergeCell ref="I125:I136"/>
     <mergeCell ref="D62:D65"/>
-    <mergeCell ref="C70:C75"/>
-    <mergeCell ref="C88:C90"/>
-    <mergeCell ref="D207:D210"/>
+    <mergeCell ref="B212:B233"/>
+    <mergeCell ref="A176:A182"/>
+    <mergeCell ref="D146:D153"/>
     <mergeCell ref="A31:A65"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="D136:D140"/>
-    <mergeCell ref="D253:D255"/>
-    <mergeCell ref="I175:I181"/>
-    <mergeCell ref="C117:C119"/>
-    <mergeCell ref="B182:B186"/>
-    <mergeCell ref="D110:D113"/>
-    <mergeCell ref="D211:D231"/>
-    <mergeCell ref="D163:D169"/>
-    <mergeCell ref="A88:A109"/>
-    <mergeCell ref="I207:I210"/>
-    <mergeCell ref="A211:A231"/>
-    <mergeCell ref="A201:A206"/>
+    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="A121:A124"/>
     <mergeCell ref="C2:C4"/>
-    <mergeCell ref="I253:I255"/>
-    <mergeCell ref="B249:B255"/>
-    <mergeCell ref="C253:C255"/>
-    <mergeCell ref="D142:D144"/>
-    <mergeCell ref="B256:B267"/>
-    <mergeCell ref="C259:C264"/>
+    <mergeCell ref="C164:C170"/>
+    <mergeCell ref="I85:I88"/>
+    <mergeCell ref="D255:D257"/>
+    <mergeCell ref="C85:C88"/>
     <mergeCell ref="I6:I8"/>
-    <mergeCell ref="I145:I152"/>
-    <mergeCell ref="C163:C169"/>
-    <mergeCell ref="D96:D101"/>
-    <mergeCell ref="A232:A243"/>
+    <mergeCell ref="C76:C84"/>
+    <mergeCell ref="B2:B16"/>
+    <mergeCell ref="C261:C266"/>
+    <mergeCell ref="A125:A142"/>
+    <mergeCell ref="I35:I41"/>
+    <mergeCell ref="D176:D182"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="D115:D117"/>
+    <mergeCell ref="I183:I187"/>
+    <mergeCell ref="D258:D260"/>
+    <mergeCell ref="D121:D124"/>
+    <mergeCell ref="D108:D110"/>
+    <mergeCell ref="I111:I114"/>
+    <mergeCell ref="I258:I260"/>
+    <mergeCell ref="C255:C257"/>
+    <mergeCell ref="C137:C141"/>
+    <mergeCell ref="D76:D84"/>
+    <mergeCell ref="C176:C182"/>
+    <mergeCell ref="I42:I55"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="A195:A201"/>
+    <mergeCell ref="B208:B211"/>
+    <mergeCell ref="D208:D211"/>
+    <mergeCell ref="B251:B257"/>
+    <mergeCell ref="I176:I182"/>
+    <mergeCell ref="I66:I69"/>
+    <mergeCell ref="D92:D96"/>
+    <mergeCell ref="I121:I124"/>
+    <mergeCell ref="I108:I110"/>
+    <mergeCell ref="I137:I141"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C146:C153"/>
+    <mergeCell ref="D97:D102"/>
+    <mergeCell ref="I164:I170"/>
+    <mergeCell ref="I146:I153"/>
+    <mergeCell ref="A118:A120"/>
+    <mergeCell ref="B258:B269"/>
+    <mergeCell ref="B195:B201"/>
+    <mergeCell ref="D85:D88"/>
+    <mergeCell ref="B31:B65"/>
+    <mergeCell ref="A234:A245"/>
+    <mergeCell ref="I202:I207"/>
+    <mergeCell ref="I17:I30"/>
+    <mergeCell ref="D118:D120"/>
+    <mergeCell ref="A17:A30"/>
+    <mergeCell ref="I92:I96"/>
+    <mergeCell ref="D12:D16"/>
+    <mergeCell ref="D261:D266"/>
+    <mergeCell ref="A208:A211"/>
+    <mergeCell ref="I97:I102"/>
+    <mergeCell ref="C258:C260"/>
+    <mergeCell ref="C121:C124"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="C89:C91"/>
+    <mergeCell ref="B188:B194"/>
+    <mergeCell ref="D188:D194"/>
+    <mergeCell ref="I267:I269"/>
+    <mergeCell ref="C118:C120"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="B234:B245"/>
+    <mergeCell ref="D234:D245"/>
+    <mergeCell ref="I118:I120"/>
+    <mergeCell ref="I115:I117"/>
+    <mergeCell ref="I12:I16"/>
+    <mergeCell ref="I261:I266"/>
+    <mergeCell ref="I76:I84"/>
+    <mergeCell ref="C115:C117"/>
+    <mergeCell ref="I251:I254"/>
+    <mergeCell ref="A251:A257"/>
+    <mergeCell ref="C35:C41"/>
+    <mergeCell ref="I212:I233"/>
+    <mergeCell ref="B202:B207"/>
+    <mergeCell ref="A188:A194"/>
+    <mergeCell ref="C188:C194"/>
+    <mergeCell ref="C97:C102"/>
+    <mergeCell ref="I255:I257"/>
+    <mergeCell ref="I62:I65"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="B89:B110"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="D267:D269"/>
+    <mergeCell ref="C70:C75"/>
+    <mergeCell ref="B246:B250"/>
+    <mergeCell ref="I171:I175"/>
+    <mergeCell ref="D103:D107"/>
+    <mergeCell ref="B183:B187"/>
+    <mergeCell ref="D89:D91"/>
+    <mergeCell ref="C125:C136"/>
     <mergeCell ref="D70:D75"/>
-    <mergeCell ref="B2:B16"/>
-    <mergeCell ref="D153:D155"/>
-    <mergeCell ref="I187:I193"/>
-    <mergeCell ref="I76:I83"/>
-    <mergeCell ref="C102:C106"/>
-    <mergeCell ref="I35:I41"/>
-    <mergeCell ref="A182:A186"/>
-    <mergeCell ref="D66:D69"/>
-    <mergeCell ref="B194:B200"/>
-    <mergeCell ref="B232:B243"/>
+    <mergeCell ref="C108:C110"/>
+    <mergeCell ref="C234:C245"/>
     <mergeCell ref="D56:D61"/>
-    <mergeCell ref="B142:B174"/>
-    <mergeCell ref="C256:C258"/>
-    <mergeCell ref="C265:C267"/>
-    <mergeCell ref="A142:A174"/>
-    <mergeCell ref="C124:C135"/>
-    <mergeCell ref="A110:A116"/>
-    <mergeCell ref="B207:B210"/>
-    <mergeCell ref="I163:I169"/>
-    <mergeCell ref="B66:B87"/>
-    <mergeCell ref="C114:C116"/>
-    <mergeCell ref="B201:B206"/>
-    <mergeCell ref="C175:C181"/>
-    <mergeCell ref="C249:C252"/>
-    <mergeCell ref="D201:D206"/>
-    <mergeCell ref="C96:C101"/>
-    <mergeCell ref="D84:D87"/>
+    <mergeCell ref="A66:A88"/>
+    <mergeCell ref="I234:I245"/>
+    <mergeCell ref="C208:C211"/>
+    <mergeCell ref="D251:D254"/>
+    <mergeCell ref="D195:D201"/>
+    <mergeCell ref="I103:I107"/>
+    <mergeCell ref="I208:I211"/>
+    <mergeCell ref="A202:A207"/>
     <mergeCell ref="C17:C30"/>
     <mergeCell ref="D31:D34"/>
-    <mergeCell ref="I170:I174"/>
-    <mergeCell ref="B187:B193"/>
-    <mergeCell ref="I42:I55"/>
-    <mergeCell ref="A244:A248"/>
-    <mergeCell ref="I107:I109"/>
-    <mergeCell ref="C244:C248"/>
-    <mergeCell ref="C91:C95"/>
-    <mergeCell ref="D156:D162"/>
-    <mergeCell ref="D102:D106"/>
-    <mergeCell ref="C145:C152"/>
+    <mergeCell ref="D171:D175"/>
+    <mergeCell ref="D143:D145"/>
+    <mergeCell ref="A89:A110"/>
     <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D114:D116"/>
-    <mergeCell ref="I66:I69"/>
-    <mergeCell ref="I232:I243"/>
-    <mergeCell ref="A117:A119"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D88:D90"/>
-    <mergeCell ref="D124:D135"/>
-    <mergeCell ref="B110:B116"/>
-    <mergeCell ref="C207:C210"/>
-    <mergeCell ref="A256:A267"/>
-    <mergeCell ref="I201:I206"/>
+    <mergeCell ref="C267:C269"/>
+    <mergeCell ref="B66:B88"/>
+    <mergeCell ref="D111:D114"/>
+    <mergeCell ref="D212:D233"/>
+    <mergeCell ref="C195:C201"/>
+    <mergeCell ref="B143:B175"/>
     <mergeCell ref="B17:B30"/>
-    <mergeCell ref="I256:I258"/>
-    <mergeCell ref="C110:C113"/>
-    <mergeCell ref="C211:C231"/>
-    <mergeCell ref="C76:C83"/>
-    <mergeCell ref="I84:I87"/>
-    <mergeCell ref="B211:B231"/>
-    <mergeCell ref="I249:I252"/>
+    <mergeCell ref="A143:A175"/>
+    <mergeCell ref="I195:I201"/>
+    <mergeCell ref="D202:D207"/>
+    <mergeCell ref="D154:D156"/>
+    <mergeCell ref="A246:A250"/>
+    <mergeCell ref="C246:C250"/>
+    <mergeCell ref="D125:D136"/>
+    <mergeCell ref="I188:I194"/>
     <mergeCell ref="I31:I34"/>
-    <mergeCell ref="D170:D174"/>
-    <mergeCell ref="I110:I113"/>
-    <mergeCell ref="I211:I231"/>
-    <mergeCell ref="D244:D248"/>
+    <mergeCell ref="C103:C107"/>
+    <mergeCell ref="A183:A187"/>
+    <mergeCell ref="C183:C187"/>
     <mergeCell ref="C12:C16"/>
-    <mergeCell ref="C142:C144"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="I102:I106"/>
+    <mergeCell ref="C111:C114"/>
+    <mergeCell ref="B176:B182"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I269"/>
+  <dimension ref="A1:I275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6289,10 +6289,10 @@
       <c r="I186" s="4" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="n"/>
-      <c r="B187" s="5" t="n"/>
-      <c r="C187" s="5" t="n"/>
-      <c r="D187" s="5" t="n"/>
+      <c r="A187" s="4" t="n"/>
+      <c r="B187" s="4" t="n"/>
+      <c r="C187" s="4" t="n"/>
+      <c r="D187" s="4" t="n"/>
       <c r="E187" s="7" t="inlineStr">
         <is>
           <t>12-1-5</t>
@@ -6314,108 +6314,110 @@
           <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
         </is>
       </c>
-      <c r="I187" s="5" t="n"/>
+      <c r="I187" s="4" t="n"/>
     </row>
     <row r="188">
-      <c r="A188" s="7" t="inlineStr">
+      <c r="A188" s="4" t="n"/>
+      <c r="B188" s="4" t="n"/>
+      <c r="C188" s="4" t="n"/>
+      <c r="D188" s="4" t="n"/>
+      <c r="E188" s="7" t="inlineStr">
+        <is>
+          <t>12-1-6</t>
+        </is>
+      </c>
+      <c r="F188" s="7" t="inlineStr">
+        <is>
+          <t>登録日時が同じ書籍は、IDの順に並ぶ(新しい順はIDの降順、古い順はIDの昇順)</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="inlineStr">
+        <is>
+          <t>1.登録日時が同じ書籍を複数用意する
+2.sort=latest、sort=oldestをそれぞれ指定して書籍一覧を開く</t>
+        </is>
+      </c>
+      <c r="H188" s="7" t="inlineStr">
+        <is>
+          <t>新しい順ではIDの降順(後に登録した順)、古い順ではIDの昇順(先に登録した順)に表示される</t>
+        </is>
+      </c>
+      <c r="I188" s="4" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="5" t="n"/>
+      <c r="B189" s="5" t="n"/>
+      <c r="C189" s="5" t="n"/>
+      <c r="D189" s="5" t="n"/>
+      <c r="E189" s="7" t="inlineStr">
+        <is>
+          <t>12-1-7</t>
+        </is>
+      </c>
+      <c r="F189" s="7" t="inlineStr">
+        <is>
+          <t>sort=rating指定時、レビューがない書籍は最後に表示される</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="inlineStr">
+        <is>
+          <t>1.レビューがある書籍と、レビューがない書籍(登録が最も新しい)を用意する
+2.sort=ratingを指定して書籍一覧を開く</t>
+        </is>
+      </c>
+      <c r="H189" s="7" t="inlineStr">
+        <is>
+          <t>レビューがある書籍が平均評価の高い順に表示され、レビューがない書籍は最後に表示される</t>
+        </is>
+      </c>
+      <c r="I189" s="5" t="n"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B188" s="7" t="inlineStr">
+      <c r="B190" s="7" t="inlineStr">
         <is>
           <t>書籍CRUD（認可の詳細テスト）</t>
         </is>
       </c>
-      <c r="C188" s="7" t="inlineStr">
+      <c r="C190" s="7" t="inlineStr">
         <is>
           <t>13-1</t>
         </is>
       </c>
-      <c r="D188" s="7" t="inlineStr">
+      <c r="D190" s="7" t="inlineStr">
         <is>
           <t>BookPolicyの認可ロジック</t>
         </is>
       </c>
-      <c r="E188" s="7" t="inlineStr">
+      <c r="E190" s="7" t="inlineStr">
         <is>
           <t>13-1-1</t>
         </is>
       </c>
-      <c r="F188" s="7" t="inlineStr">
+      <c r="F190" s="7" t="inlineStr">
         <is>
           <t>ログインユーザーは誰でも書籍を作成できる</t>
         </is>
       </c>
-      <c r="G188" s="7" t="inlineStr">
+      <c r="G190" s="7" t="inlineStr">
         <is>
           <t>1.任意のログインユーザーで BookPolicy::create() を確認する</t>
         </is>
       </c>
-      <c r="H188" s="7" t="inlineStr">
+      <c r="H190" s="7" t="inlineStr">
         <is>
           <t>trueが返り、作成が許可される</t>
         </is>
       </c>
-      <c r="I188" s="7" t="inlineStr">
+      <c r="I190" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/BookAuthorization/BookAuthorizationTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="4" t="n"/>
-      <c r="B189" s="4" t="n"/>
-      <c r="C189" s="4" t="n"/>
-      <c r="D189" s="4" t="n"/>
-      <c r="E189" s="7" t="inlineStr">
-        <is>
-          <t>13-1-2</t>
-        </is>
-      </c>
-      <c r="F189" s="7" t="inlineStr">
-        <is>
-          <t>書籍の登録者本人は更新が許可される</t>
-        </is>
-      </c>
-      <c r="G189" s="7" t="inlineStr">
-        <is>
-          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
-        </is>
-      </c>
-      <c r="H189" s="7" t="inlineStr">
-        <is>
-          <t>trueが返る</t>
-        </is>
-      </c>
-      <c r="I189" s="4" t="n"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="4" t="n"/>
-      <c r="B190" s="4" t="n"/>
-      <c r="C190" s="4" t="n"/>
-      <c r="D190" s="4" t="n"/>
-      <c r="E190" s="7" t="inlineStr">
-        <is>
-          <t>13-1-3</t>
-        </is>
-      </c>
-      <c r="F190" s="7" t="inlineStr">
-        <is>
-          <t>書籍の登録者以外は更新が許可されない</t>
-        </is>
-      </c>
-      <c r="G190" s="7" t="inlineStr">
-        <is>
-          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
-        </is>
-      </c>
-      <c r="H190" s="7" t="inlineStr">
-        <is>
-          <t>falseが返る</t>
-        </is>
-      </c>
-      <c r="I190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n"/>
@@ -6424,17 +6426,17 @@
       <c r="D191" s="4" t="n"/>
       <c r="E191" s="7" t="inlineStr">
         <is>
-          <t>13-1-4</t>
+          <t>13-1-2</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者本人は削除が許可される</t>
+          <t>書籍の登録者本人は更新が許可される</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
+          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H191" s="7" t="inlineStr">
@@ -6451,17 +6453,17 @@
       <c r="D192" s="4" t="n"/>
       <c r="E192" s="7" t="inlineStr">
         <is>
-          <t>13-1-5</t>
+          <t>13-1-3</t>
         </is>
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者以外は削除が許可されない</t>
+          <t>書籍の登録者以外は更新が許可されない</t>
         </is>
       </c>
       <c r="G192" s="7" t="inlineStr">
         <is>
-          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
+          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H192" s="7" t="inlineStr">
@@ -6478,154 +6480,153 @@
       <c r="D193" s="4" t="n"/>
       <c r="E193" s="7" t="inlineStr">
         <is>
+          <t>13-1-4</t>
+        </is>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>書籍の登録者本人は削除が許可される</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="inlineStr">
+        <is>
+          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
+        </is>
+      </c>
+      <c r="H193" s="7" t="inlineStr">
+        <is>
+          <t>trueが返る</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="n"/>
+      <c r="B194" s="4" t="n"/>
+      <c r="C194" s="4" t="n"/>
+      <c r="D194" s="4" t="n"/>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
+          <t>13-1-5</t>
+        </is>
+      </c>
+      <c r="F194" s="7" t="inlineStr">
+        <is>
+          <t>書籍の登録者以外は削除が許可されない</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
+          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
+        </is>
+      </c>
+      <c r="H194" s="7" t="inlineStr">
+        <is>
+          <t>falseが返る</t>
+        </is>
+      </c>
+      <c r="I194" s="4" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="n"/>
+      <c r="B195" s="4" t="n"/>
+      <c r="C195" s="4" t="n"/>
+      <c r="D195" s="4" t="n"/>
+      <c r="E195" s="7" t="inlineStr">
+        <is>
           <t>13-1-6</t>
         </is>
       </c>
-      <c r="F193" s="7" t="inlineStr">
+      <c r="F195" s="7" t="inlineStr">
         <is>
           <t>フォームを介さない直接のPUT/DELETEリクエストでも他人の書籍は操作できない</t>
         </is>
       </c>
-      <c r="G193" s="7" t="inlineStr">
+      <c r="G195" s="7" t="inlineStr">
         <is>
           <t>1.他人が登録した書籍に対して、直接PUT・DELETEリクエストを送信する</t>
         </is>
       </c>
-      <c r="H193" s="7" t="inlineStr">
+      <c r="H195" s="7" t="inlineStr">
         <is>
           <t>いずれも403Forbiddenになり、データは変更されない</t>
         </is>
       </c>
-      <c r="I193" s="4" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="5" t="n"/>
-      <c r="B194" s="5" t="n"/>
-      <c r="C194" s="5" t="n"/>
-      <c r="D194" s="5" t="n"/>
-      <c r="E194" s="7" t="inlineStr">
+      <c r="I195" s="4" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="n"/>
+      <c r="B196" s="5" t="n"/>
+      <c r="C196" s="5" t="n"/>
+      <c r="D196" s="5" t="n"/>
+      <c r="E196" s="7" t="inlineStr">
         <is>
           <t>13-1-7</t>
         </is>
       </c>
-      <c r="F194" s="7" t="inlineStr">
+      <c r="F196" s="7" t="inlineStr">
         <is>
           <t>他人の書籍に対して不正な入力を直接PUTしても、入力エラーではなく403になる</t>
         </is>
       </c>
-      <c r="G194" s="7" t="inlineStr">
+      <c r="G196" s="7" t="inlineStr">
         <is>
           <t>1.他人が登録した書籍に対して、タイトルを空にするなど不正な内容で、直接PUTリクエストを送信する</t>
         </is>
       </c>
-      <c r="H194" s="7" t="inlineStr">
+      <c r="H196" s="7" t="inlineStr">
         <is>
           <t>バリデーションエラーにはならず、403Forbiddenになる（入力チェックより先に権限が判定される）。データは変更されない</t>
         </is>
       </c>
-      <c r="I194" s="5" t="n"/>
-    </row>
-    <row r="195">
-      <c r="A195" s="7" t="inlineStr">
+      <c r="I196" s="5" t="n"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B195" s="7" t="inlineStr">
+      <c r="B197" s="7" t="inlineStr">
         <is>
           <t>ISBN検索</t>
         </is>
       </c>
-      <c r="C195" s="7" t="inlineStr">
+      <c r="C197" s="7" t="inlineStr">
         <is>
           <t>14-1</t>
         </is>
       </c>
-      <c r="D195" s="7" t="inlineStr">
+      <c r="D197" s="7" t="inlineStr">
         <is>
           <t>ISBNからの書籍情報取得(外部API連携)</t>
         </is>
       </c>
-      <c r="E195" s="7" t="inlineStr">
+      <c r="E197" s="7" t="inlineStr">
         <is>
           <t>14-1-1</t>
         </is>
       </c>
-      <c r="F195" s="7" t="inlineStr">
+      <c r="F197" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、ISBN検索エンドポイントにアクセスできない</t>
         </is>
       </c>
-      <c r="G195" s="7" t="inlineStr">
+      <c r="G197" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態でGET /books/isbn/{isbn} にアクセスする</t>
         </is>
       </c>
-      <c r="H195" s="7" t="inlineStr">
+      <c r="H197" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I195" s="7" t="inlineStr">
+      <c r="I197" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Isbn/IsbnSearchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="4" t="n"/>
-      <c r="B196" s="4" t="n"/>
-      <c r="C196" s="4" t="n"/>
-      <c r="D196" s="4" t="n"/>
-      <c r="E196" s="7" t="inlineStr">
-        <is>
-          <t>14-1-2</t>
-        </is>
-      </c>
-      <c r="F196" s="7" t="inlineStr">
-        <is>
-          <t>ISBNが空(空白のみ)の場合、バリデーションエラーが返る</t>
-        </is>
-      </c>
-      <c r="G196" s="7" t="inlineStr">
-        <is>
-          <t>1.ログイン状態で、ISBN部分を半角スペースのみにしてGET /books/isbn/%20 にリクエストする
-※ISBN部分を完全に空にするとURLが /books/isbn となり、このルートに一致しないため空白で代用する</t>
-        </is>
-      </c>
-      <c r="H196" s="7" t="inlineStr">
-        <is>
-          <t>422が返り、「ISBNを入力してください」が返る</t>
-        </is>
-      </c>
-      <c r="I196" s="4" t="n"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="4" t="n"/>
-      <c r="B197" s="4" t="n"/>
-      <c r="C197" s="4" t="n"/>
-      <c r="D197" s="4" t="n"/>
-      <c r="E197" s="7" t="inlineStr">
-        <is>
-          <t>14-1-3</t>
-        </is>
-      </c>
-      <c r="F197" s="7" t="inlineStr">
-        <is>
-          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
-        </is>
-      </c>
-      <c r="G197" s="7" t="inlineStr">
-        <is>
-          <t>1.13桁でないISBNでリクエストする</t>
-        </is>
-      </c>
-      <c r="H197" s="7" t="inlineStr">
-        <is>
-          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
-        </is>
-      </c>
-      <c r="I197" s="4" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="n"/>
@@ -6634,22 +6635,23 @@
       <c r="D198" s="4" t="n"/>
       <c r="E198" s="7" t="inlineStr">
         <is>
-          <t>14-1-4</t>
+          <t>14-1-2</t>
         </is>
       </c>
       <c r="F198" s="7" t="inlineStr">
         <is>
-          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
+          <t>ISBNが空(空白のみ)の場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G198" s="7" t="inlineStr">
         <is>
-          <t>1.登録済みのISBNでリクエストする</t>
+          <t>1.ログイン状態で、ISBN部分を半角スペースのみにしてGET /books/isbn/%20 にリクエストする
+※ISBN部分を完全に空にするとURLが /books/isbn となり、このルートに一致しないため空白で代用する</t>
         </is>
       </c>
       <c r="H198" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
+          <t>422が返り、「ISBNを入力してください」が返る</t>
         </is>
       </c>
       <c r="I198" s="4" t="n"/>
@@ -6661,23 +6663,22 @@
       <c r="D199" s="4" t="n"/>
       <c r="E199" s="7" t="inlineStr">
         <is>
-          <t>14-1-5</t>
+          <t>14-1-3</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
+          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G199" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
-2.未登録ISBNでリクエストする</t>
+          <t>1.13桁でないISBNでリクエストする</t>
         </is>
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
+          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
         </is>
       </c>
       <c r="I199" s="4" t="n"/>
@@ -6689,101 +6690,81 @@
       <c r="D200" s="4" t="n"/>
       <c r="E200" s="7" t="inlineStr">
         <is>
+          <t>14-1-4</t>
+        </is>
+      </c>
+      <c r="F200" s="7" t="inlineStr">
+        <is>
+          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="inlineStr">
+        <is>
+          <t>1.登録済みのISBNでリクエストする</t>
+        </is>
+      </c>
+      <c r="H200" s="7" t="inlineStr">
+        <is>
+          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
+        </is>
+      </c>
+      <c r="I200" s="4" t="n"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="n"/>
+      <c r="B201" s="4" t="n"/>
+      <c r="C201" s="4" t="n"/>
+      <c r="D201" s="4" t="n"/>
+      <c r="E201" s="7" t="inlineStr">
+        <is>
+          <t>14-1-5</t>
+        </is>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
+2.未登録ISBNでリクエストする</t>
+        </is>
+      </c>
+      <c r="H201" s="7" t="inlineStr">
+        <is>
+          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="n"/>
+      <c r="B202" s="4" t="n"/>
+      <c r="C202" s="4" t="n"/>
+      <c r="D202" s="4" t="n"/>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
           <t>14-1-6</t>
         </is>
       </c>
-      <c r="F200" s="7" t="inlineStr">
+      <c r="F202" s="7" t="inlineStr">
         <is>
           <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
         </is>
       </c>
-      <c r="G200" s="7" t="inlineStr">
+      <c r="G202" s="7" t="inlineStr">
         <is>
           <t>1.Http::fake()でitemsが空のレスポンスをモックする
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H200" s="7" t="inlineStr">
+      <c r="H202" s="7" t="inlineStr">
         <is>
           <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
         </is>
       </c>
-      <c r="I200" s="4" t="n"/>
-    </row>
-    <row r="201">
-      <c r="A201" s="5" t="n"/>
-      <c r="B201" s="5" t="n"/>
-      <c r="C201" s="5" t="n"/>
-      <c r="D201" s="5" t="n"/>
-      <c r="E201" s="7" t="inlineStr">
-        <is>
-          <t>14-1-7</t>
-        </is>
-      </c>
-      <c r="F201" s="7" t="inlineStr">
-        <is>
-          <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
-        </is>
-      </c>
-      <c r="G201" s="7" t="inlineStr">
-        <is>
-          <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
-2.未登録ISBNでリクエストする</t>
-        </is>
-      </c>
-      <c r="H201" s="7" t="inlineStr">
-        <is>
-          <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
-        </is>
-      </c>
-      <c r="I201" s="5" t="n"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B202" s="7" t="inlineStr">
-        <is>
-          <t>マイ読書レポート</t>
-        </is>
-      </c>
-      <c r="C202" s="7" t="inlineStr">
-        <is>
-          <t>15-1</t>
-        </is>
-      </c>
-      <c r="D202" s="7" t="inlineStr">
-        <is>
-          <t>読書統計の表示</t>
-        </is>
-      </c>
-      <c r="E202" s="7" t="inlineStr">
-        <is>
-          <t>15-1-1</t>
-        </is>
-      </c>
-      <c r="F202" s="7" t="inlineStr">
-        <is>
-          <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
-        </is>
-      </c>
-      <c r="G202" s="7" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態で/reportsを開く</t>
-        </is>
-      </c>
-      <c r="H202" s="7" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I202" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Report/ReportTest.php</t>
-        </is>
-      </c>
+      <c r="I202" s="4" t="n"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n"/>
@@ -6792,79 +6773,101 @@
       <c r="D203" s="4" t="n"/>
       <c r="E203" s="7" t="inlineStr">
         <is>
-          <t>15-1-2</t>
+          <t>14-1-7</t>
         </is>
       </c>
       <c r="F203" s="7" t="inlineStr">
         <is>
-          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
+          <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
         </is>
       </c>
       <c r="G203" s="7" t="inlineStr">
         <is>
-          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
+          <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
+2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
-          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
+          <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
         </is>
       </c>
       <c r="I203" s="4" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="4" t="n"/>
-      <c r="B204" s="4" t="n"/>
-      <c r="C204" s="4" t="n"/>
-      <c r="D204" s="4" t="n"/>
+      <c r="A204" s="5" t="n"/>
+      <c r="B204" s="5" t="n"/>
+      <c r="C204" s="5" t="n"/>
+      <c r="D204" s="5" t="n"/>
       <c r="E204" s="7" t="inlineStr">
         <is>
-          <t>15-1-3</t>
+          <t>14-1-8</t>
         </is>
       </c>
       <c r="F204" s="7" t="inlineStr">
         <is>
-          <t>評価分布(★1〜★5)が正しく表示される</t>
+          <t>APIの検索結果はあるが、ISBNが一致する書籍がない場合も404エラーが返る</t>
         </is>
       </c>
       <c r="G204" s="7" t="inlineStr">
         <is>
-          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
+          <t>1.Http::fake()で、別のISBNを持つ書籍のみを含むitemsを返すようモックする
+2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
-          <t>各評価の件数が実データと一致して表示される</t>
-        </is>
-      </c>
-      <c r="I204" s="4" t="n"/>
+          <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
+        </is>
+      </c>
+      <c r="I204" s="5" t="n"/>
     </row>
     <row r="205">
-      <c r="A205" s="4" t="n"/>
-      <c r="B205" s="4" t="n"/>
-      <c r="C205" s="4" t="n"/>
-      <c r="D205" s="4" t="n"/>
+      <c r="A205" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B205" s="7" t="inlineStr">
+        <is>
+          <t>マイ読書レポート</t>
+        </is>
+      </c>
+      <c r="C205" s="7" t="inlineStr">
+        <is>
+          <t>15-1</t>
+        </is>
+      </c>
+      <c r="D205" s="7" t="inlineStr">
+        <is>
+          <t>読書統計の表示</t>
+        </is>
+      </c>
       <c r="E205" s="7" t="inlineStr">
         <is>
-          <t>15-1-4</t>
+          <t>15-1-1</t>
         </is>
       </c>
       <c r="F205" s="7" t="inlineStr">
         <is>
-          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
+          <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
         </is>
       </c>
       <c r="G205" s="7" t="inlineStr">
         <is>
-          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
+          <t>1.未ログイン状態で/reportsを開く</t>
         </is>
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
-          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
-        </is>
-      </c>
-      <c r="I205" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I205" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Report/ReportTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="n"/>
@@ -6873,100 +6876,79 @@
       <c r="D206" s="4" t="n"/>
       <c r="E206" s="7" t="inlineStr">
         <is>
-          <t>15-1-5</t>
+          <t>15-1-2</t>
         </is>
       </c>
       <c r="F206" s="7" t="inlineStr">
         <is>
-          <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
+          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
         </is>
       </c>
       <c r="G206" s="7" t="inlineStr">
         <is>
-          <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
+          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
+          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
         </is>
       </c>
       <c r="I206" s="4" t="n"/>
     </row>
     <row r="207">
-      <c r="A207" s="5" t="n"/>
-      <c r="B207" s="5" t="n"/>
-      <c r="C207" s="5" t="n"/>
-      <c r="D207" s="5" t="n"/>
+      <c r="A207" s="4" t="n"/>
+      <c r="B207" s="4" t="n"/>
+      <c r="C207" s="4" t="n"/>
+      <c r="D207" s="4" t="n"/>
       <c r="E207" s="7" t="inlineStr">
         <is>
-          <t>15-1-6</t>
+          <t>15-1-3</t>
         </is>
       </c>
       <c r="F207" s="7" t="inlineStr">
         <is>
-          <t>レビューを1件も投稿していない場合の表示を確認する</t>
+          <t>評価分布(★1〜★5)が正しく表示される</t>
         </is>
       </c>
       <c r="G207" s="7" t="inlineStr">
         <is>
-          <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
+          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
-          <t>総レビュー数・読了冊数が0（平均評価の集計値は0で、画面上は「-」と表示）となり、TOP5一覧には「4星以上の書籍がありません」「ジャンルが設定された書籍のレビューがありません」と表示される</t>
-        </is>
-      </c>
-      <c r="I207" s="5" t="n"/>
+          <t>各評価の件数が実データと一致して表示される</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B208" s="7" t="inlineStr">
-        <is>
-          <t>Sanctum認証</t>
-        </is>
-      </c>
-      <c r="C208" s="7" t="inlineStr">
-        <is>
-          <t>16-1</t>
-        </is>
-      </c>
-      <c r="D208" s="7" t="inlineStr">
-        <is>
-          <t>APIトークン認証</t>
-        </is>
-      </c>
+      <c r="A208" s="4" t="n"/>
+      <c r="B208" s="4" t="n"/>
+      <c r="C208" s="4" t="n"/>
+      <c r="D208" s="4" t="n"/>
       <c r="E208" s="7" t="inlineStr">
         <is>
-          <t>16-1-1</t>
+          <t>15-1-4</t>
         </is>
       </c>
       <c r="F208" s="7" t="inlineStr">
         <is>
-          <t>有効なpersonal access tokenを付与すると/api/userにアクセスできる</t>
+          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
         </is>
       </c>
       <c r="G208" s="7" t="inlineStr">
         <is>
-          <t>1.$user-&gt;createToken()でトークンを発行する
-2.Authorization: Bearer {token}を付与してGET /api/userにアクセスする</t>
+          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
-          <t>200が返り、対象ユーザーの情報が返る</t>
-        </is>
-      </c>
-      <c r="I208" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
-        </is>
-      </c>
+          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
+        </is>
+      </c>
+      <c r="I208" s="4" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="n"/>
@@ -6975,22 +6957,22 @@
       <c r="D209" s="4" t="n"/>
       <c r="E209" s="7" t="inlineStr">
         <is>
-          <t>16-1-2</t>
+          <t>15-1-5</t>
         </is>
       </c>
       <c r="F209" s="7" t="inlineStr">
         <is>
-          <t>トークンなしでアクセスすると401が返る</t>
+          <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
         </is>
       </c>
       <c r="G209" s="7" t="inlineStr">
         <is>
-          <t>1.Authorizationヘッダーを付与せずにGET /api/userにアクセスする</t>
+          <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H209" s="7" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
+          <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
         </is>
       </c>
       <c r="I209" s="4" t="n"/>
@@ -7002,22 +6984,22 @@
       <c r="D210" s="4" t="n"/>
       <c r="E210" s="7" t="inlineStr">
         <is>
-          <t>16-1-3</t>
+          <t>15-1-6</t>
         </is>
       </c>
       <c r="F210" s="7" t="inlineStr">
         <is>
-          <t>不正な(存在しない)トークンでアクセスすると401が返る</t>
+          <t>レビューを1件も投稿していない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G210" s="7" t="inlineStr">
         <is>
-          <t>1.ランダムな文字列をBearerトークンとして付与しGET /api/userにアクセスする</t>
+          <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H210" s="7" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
+          <t>総レビュー数・読了冊数が0（平均評価の集計値は0で、画面上は「-」と表示）となり、TOP5一覧には「4星以上の書籍がありません」「ジャンルが設定された書籍のレビューがありません」と表示される</t>
         </is>
       </c>
       <c r="I210" s="4" t="n"/>
@@ -7029,23 +7011,22 @@
       <c r="D211" s="5" t="n"/>
       <c r="E211" s="7" t="inlineStr">
         <is>
-          <t>16-1-4</t>
+          <t>15-1-7</t>
         </is>
       </c>
       <c r="F211" s="7" t="inlineStr">
         <is>
-          <t>削除済み(失効済み)のトークンでアクセスすると401が返る</t>
+          <t>ジャンル別評価傾向で、平均評価が同じジャンルはレビュー件数の多い順に表示される</t>
         </is>
       </c>
       <c r="G211" s="7" t="inlineStr">
         <is>
-          <t>1.発行済みトークンを削除する
-2.そのトークンでGET /api/userにアクセスする</t>
+          <t>1.平均評価が同じで、レビュー件数が異なる2つのジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H211" s="7" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
+          <t>平均評価が同じジャンル同士は、レビュー件数の多い順に表示される</t>
         </is>
       </c>
       <c r="I211" s="5" t="n"/>
@@ -7053,47 +7034,48 @@
     <row r="212">
       <c r="A212" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B212" s="7" t="inlineStr">
         <is>
-          <t>読書計画</t>
+          <t>Sanctum認証</t>
         </is>
       </c>
       <c r="C212" s="7" t="inlineStr">
         <is>
-          <t>17-1</t>
+          <t>16-1</t>
         </is>
       </c>
       <c r="D212" s="7" t="inlineStr">
         <is>
-          <t>読書計画の作成・一覧・読了・削除</t>
+          <t>APIトークン認証</t>
         </is>
       </c>
       <c r="E212" s="7" t="inlineStr">
         <is>
-          <t>17-1-1</t>
+          <t>16-1-1</t>
         </is>
       </c>
       <c r="F212" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
+          <t>有効なpersonal access tokenを付与すると/api/userにアクセスできる</t>
         </is>
       </c>
       <c r="G212" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
+          <t>1.$user-&gt;createToken()でトークンを発行する
+2.Authorization: Bearer {token}を付与してGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H212" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
+          <t>200が返り、対象ユーザーの情報が返る</t>
         </is>
       </c>
       <c r="I212" s="7" t="inlineStr">
         <is>
-          <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
+          <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
         </is>
       </c>
     </row>
@@ -7104,23 +7086,22 @@
       <c r="D213" s="4" t="n"/>
       <c r="E213" s="7" t="inlineStr">
         <is>
-          <t>17-1-2</t>
+          <t>16-1-2</t>
         </is>
       </c>
       <c r="F213" s="7" t="inlineStr">
         <is>
-          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
+          <t>トークンなしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G213" s="7" t="inlineStr">
         <is>
-          <t>1.自分と他人の読書計画をそれぞれ用意する
-2.読書計画一覧ページを開く</t>
+          <t>1.Authorizationヘッダーを付与せずにGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H213" s="7" t="inlineStr">
         <is>
-          <t>自分の計画のみが、target_dateの昇順で表示される</t>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
         </is>
       </c>
       <c r="I213" s="4" t="n"/>
@@ -7132,81 +7113,100 @@
       <c r="D214" s="4" t="n"/>
       <c r="E214" s="7" t="inlineStr">
         <is>
-          <t>17-1-3</t>
+          <t>16-1-3</t>
         </is>
       </c>
       <c r="F214" s="7" t="inlineStr">
         <is>
-          <t>ステータスで絞り込んで表示できる</t>
+          <t>不正な(存在しない)トークンでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G214" s="7" t="inlineStr">
         <is>
-          <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
-2.statusパラメータを指定して一覧を開く</t>
+          <t>1.ランダムな文字列をBearerトークンとして付与しGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H214" s="7" t="inlineStr">
         <is>
-          <t>指定したステータスの計画のみ表示される</t>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
         </is>
       </c>
       <c r="I214" s="4" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="4" t="n"/>
-      <c r="B215" s="4" t="n"/>
-      <c r="C215" s="4" t="n"/>
-      <c r="D215" s="4" t="n"/>
+      <c r="A215" s="5" t="n"/>
+      <c r="B215" s="5" t="n"/>
+      <c r="C215" s="5" t="n"/>
+      <c r="D215" s="5" t="n"/>
       <c r="E215" s="7" t="inlineStr">
         <is>
-          <t>17-1-4</t>
+          <t>16-1-4</t>
         </is>
       </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
-          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
+          <t>削除済み(失効済み)のトークンでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G215" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍について進行中の計画を作成する
-2.計画作成ページを開く</t>
+          <t>1.発行済みトークンを削除する
+2.そのトークンでGET /api/userにアクセスする</t>
         </is>
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
-          <t>書籍選択肢にその書籍が表示されない</t>
-        </is>
-      </c>
-      <c r="I215" s="4" t="n"/>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
+        </is>
+      </c>
+      <c r="I215" s="5" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="4" t="n"/>
-      <c r="B216" s="4" t="n"/>
-      <c r="C216" s="4" t="n"/>
-      <c r="D216" s="4" t="n"/>
+      <c r="A216" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B216" s="7" t="inlineStr">
+        <is>
+          <t>読書計画</t>
+        </is>
+      </c>
+      <c r="C216" s="7" t="inlineStr">
+        <is>
+          <t>17-1</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="inlineStr">
+        <is>
+          <t>読書計画の作成・一覧・読了・削除</t>
+        </is>
+      </c>
       <c r="E216" s="7" t="inlineStr">
         <is>
-          <t>17-1-5</t>
+          <t>17-1-1</t>
         </is>
       </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
-          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
+          <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
         </is>
       </c>
       <c r="G216" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
+          <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、計画は作成されない</t>
-        </is>
-      </c>
-      <c r="I216" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I216" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="n"/>
@@ -7215,23 +7215,23 @@
       <c r="D217" s="4" t="n"/>
       <c r="E217" s="7" t="inlineStr">
         <is>
-          <t>17-1-6</t>
+          <t>17-1-2</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
+          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
         </is>
       </c>
       <c r="G217" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を読了(完了)状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.自分と他人の読書計画をそれぞれ用意する
+2.読書計画一覧ページを開く</t>
         </is>
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
-          <t>新しい計画が作成される</t>
+          <t>自分の計画のみが、target_dateの昇順で表示される</t>
         </is>
       </c>
       <c r="I217" s="4" t="n"/>
@@ -7243,23 +7243,23 @@
       <c r="D218" s="4" t="n"/>
       <c r="E218" s="7" t="inlineStr">
         <is>
-          <t>17-1-7</t>
+          <t>17-1-3</t>
         </is>
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>ステータスで絞り込んで表示できる</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.期日を入力せずに登録する</t>
+          <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
+2.statusパラメータを指定して一覧を開く</t>
         </is>
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>指定したステータスの計画のみ表示される</t>
         </is>
       </c>
       <c r="I218" s="4" t="n"/>
@@ -7271,23 +7271,23 @@
       <c r="D219" s="4" t="n"/>
       <c r="E219" s="7" t="inlineStr">
         <is>
-          <t>17-1-8</t>
+          <t>17-1-4</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
         </is>
       </c>
       <c r="G219" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.過去の日付を期日に指定して登録する</t>
+          <t>1.ある書籍について進行中の計画を作成する
+2.計画作成ページを開く</t>
         </is>
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>書籍選択肢にその書籍が表示されない</t>
         </is>
       </c>
       <c r="I219" s="4" t="n"/>
@@ -7299,23 +7299,22 @@
       <c r="D220" s="4" t="n"/>
       <c r="E220" s="7" t="inlineStr">
         <is>
-          <t>17-1-9</t>
+          <t>17-1-5</t>
         </is>
       </c>
       <c r="F220" s="7" t="inlineStr">
         <is>
-          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
+          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
         </is>
       </c>
       <c r="G220" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍・期日を正しく入力して登録する</t>
+          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
+          <t>403Forbiddenになり、計画は作成されない</t>
         </is>
       </c>
       <c r="I220" s="4" t="n"/>
@@ -7327,22 +7326,23 @@
       <c r="D221" s="4" t="n"/>
       <c r="E221" s="7" t="inlineStr">
         <is>
-          <t>17-1-10</t>
+          <t>17-1-6</t>
         </is>
       </c>
       <c r="F221" s="7" t="inlineStr">
         <is>
-          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
+          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
         </is>
       </c>
       <c r="G221" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画に対して読了操作を行う</t>
+          <t>1.ある書籍の計画を読了(完了)状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
+          <t>新しい計画が作成される</t>
         </is>
       </c>
       <c r="I221" s="4" t="n"/>
@@ -7354,22 +7354,23 @@
       <c r="D222" s="4" t="n"/>
       <c r="E222" s="7" t="inlineStr">
         <is>
-          <t>17-1-11</t>
+          <t>17-1-7</t>
         </is>
       </c>
       <c r="F222" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画は読了・削除できない</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G222" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+          <t>1.計画作成ページを開く
+2.期日を入力せずに登録する</t>
         </is>
       </c>
       <c r="H222" s="7" t="inlineStr">
         <is>
-          <t>いずれも403Forbiddenになる</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I222" s="4" t="n"/>
@@ -7381,22 +7382,23 @@
       <c r="D223" s="4" t="n"/>
       <c r="E223" s="7" t="inlineStr">
         <is>
-          <t>17-1-12</t>
+          <t>17-1-8</t>
         </is>
       </c>
       <c r="F223" s="7" t="inlineStr">
         <is>
-          <t>自分が作成した読書計画は削除できる</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G223" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の削除ボタンを押す</t>
+          <t>1.計画作成ページを開く
+2.過去の日付を期日に指定して登録する</t>
         </is>
       </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
-          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I223" s="4" t="n"/>
@@ -7406,25 +7408,25 @@
       <c r="B224" s="4" t="n"/>
       <c r="C224" s="4" t="n"/>
       <c r="D224" s="4" t="n"/>
-      <c r="E224" s="9" t="inlineStr">
-        <is>
-          <t>17-1-13</t>
-        </is>
-      </c>
-      <c r="F224" s="9" t="inlineStr">
-        <is>
-          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
-        </is>
-      </c>
-      <c r="G224" s="9" t="inlineStr">
-        <is>
-          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
-2.その読書計画を削除する</t>
-        </is>
-      </c>
-      <c r="H224" s="9" t="inlineStr">
-        <is>
-          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
+      <c r="E224" s="7" t="inlineStr">
+        <is>
+          <t>17-1-9</t>
+        </is>
+      </c>
+      <c r="F224" s="7" t="inlineStr">
+        <is>
+          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="inlineStr">
+        <is>
+          <t>1.計画作成ページを開く
+2.書籍・期日を正しく入力して登録する</t>
+        </is>
+      </c>
+      <c r="H224" s="7" t="inlineStr">
+        <is>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
         </is>
       </c>
       <c r="I224" s="4" t="n"/>
@@ -7434,24 +7436,24 @@
       <c r="B225" s="4" t="n"/>
       <c r="C225" s="4" t="n"/>
       <c r="D225" s="4" t="n"/>
-      <c r="E225" s="9" t="inlineStr">
-        <is>
-          <t>17-1-14</t>
-        </is>
-      </c>
-      <c r="F225" s="9" t="inlineStr">
-        <is>
-          <t>ステータスが「完了」の計画は、読了操作を行えない</t>
-        </is>
-      </c>
-      <c r="G225" s="9" t="inlineStr">
-        <is>
-          <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H225" s="9" t="inlineStr">
-        <is>
-          <t>403Forbiddenになり、completed_atは変更されない</t>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t>17-1-10</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>1.進行中の計画に対して読了操作を行う</t>
+        </is>
+      </c>
+      <c r="H225" s="7" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
         </is>
       </c>
       <c r="I225" s="4" t="n"/>
@@ -7461,25 +7463,24 @@
       <c r="B226" s="4" t="n"/>
       <c r="C226" s="4" t="n"/>
       <c r="D226" s="4" t="n"/>
-      <c r="E226" s="9" t="inlineStr">
-        <is>
-          <t>17-1-15</t>
-        </is>
-      </c>
-      <c r="F226" s="9" t="inlineStr">
-        <is>
-          <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
-        </is>
-      </c>
-      <c r="G226" s="9" t="inlineStr">
-        <is>
-          <t>1.ある書籍の計画を「期限切れ」の状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H226" s="9" t="inlineStr">
-        <is>
-          <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t>17-1-11</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>他人が作成した読書計画は読了・削除できない</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr">
+        <is>
+          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+        </is>
+      </c>
+      <c r="H226" s="7" t="inlineStr">
+        <is>
+          <t>いずれも403Forbiddenになる</t>
         </is>
       </c>
       <c r="I226" s="4" t="n"/>
@@ -7489,25 +7490,24 @@
       <c r="B227" s="4" t="n"/>
       <c r="C227" s="4" t="n"/>
       <c r="D227" s="4" t="n"/>
-      <c r="E227" s="9" t="inlineStr">
-        <is>
-          <t>17-1-16</t>
-        </is>
-      </c>
-      <c r="F227" s="9" t="inlineStr">
-        <is>
-          <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="G227" s="9" t="inlineStr">
-        <is>
-          <t>1.計画作成ページを開く
-2.書籍を選択せずに期日を入力して登録する</t>
-        </is>
-      </c>
-      <c r="H227" s="9" t="inlineStr">
-        <is>
-          <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>17-1-12</t>
+        </is>
+      </c>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>自分が作成した読書計画は削除できる</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="inlineStr">
+        <is>
+          <t>1.自分が作成した計画の削除ボタンを押す</t>
+        </is>
+      </c>
+      <c r="H227" s="7" t="inlineStr">
+        <is>
+          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
         </is>
       </c>
       <c r="I227" s="4" t="n"/>
@@ -7519,22 +7519,23 @@
       <c r="D228" s="4" t="n"/>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>17-1-17</t>
+          <t>17-1-13</t>
         </is>
       </c>
       <c r="F228" s="9" t="inlineStr">
         <is>
-          <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
+          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
         </is>
       </c>
       <c r="G228" s="9" t="inlineStr">
         <is>
-          <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
+2.その読書計画を削除する</t>
         </is>
       </c>
       <c r="H228" s="9" t="inlineStr">
         <is>
-          <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
+          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
         </is>
       </c>
       <c r="I228" s="4" t="n"/>
@@ -7546,22 +7547,22 @@
       <c r="D229" s="4" t="n"/>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>17-1-18</t>
+          <t>17-1-14</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
+          <t>ステータスが「完了」の計画は、読了操作を行えない</t>
         </is>
       </c>
       <c r="G229" s="9" t="inlineStr">
         <is>
-          <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
         </is>
       </c>
       <c r="H229" s="9" t="inlineStr">
         <is>
-          <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
+          <t>403Forbiddenになり、completed_atは変更されない</t>
         </is>
       </c>
       <c r="I229" s="4" t="n"/>
@@ -7573,22 +7574,23 @@
       <c r="D230" s="4" t="n"/>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>17-1-19</t>
+          <t>17-1-15</t>
         </is>
       </c>
       <c r="F230" s="9" t="inlineStr">
         <is>
-          <t>期日が日付形式でない場合、バリデーションメッセージが表示される</t>
+          <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
         </is>
       </c>
       <c r="G230" s="9" t="inlineStr">
         <is>
-          <t>1.書籍と、日付として不正な期日(例:abc)を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.ある書籍の計画を「期限切れ」の状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H230" s="9" t="inlineStr">
         <is>
-          <t>「正しい日付を入力してください」というバリデーションメッセージが表示される</t>
+          <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
         </is>
       </c>
       <c r="I230" s="4" t="n"/>
@@ -7600,23 +7602,23 @@
       <c r="D231" s="4" t="n"/>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>17-1-20</t>
+          <t>17-1-16</t>
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr">
         <is>
-          <t>期日に今日の日付を指定した場合、計画を作成できる</t>
+          <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G231" s="9" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
-2.書籍を選択し、期日に今日の日付を指定して登録する</t>
+2.書籍を選択せずに期日を入力して登録する</t>
         </is>
       </c>
       <c r="H231" s="9" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される（今日の日付は指定可能）</t>
+          <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I231" s="4" t="n"/>
@@ -7628,123 +7630,104 @@
       <c r="D232" s="4" t="n"/>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>17-1-21</t>
+          <t>17-1-17</t>
         </is>
       </c>
       <c r="F232" s="9" t="inlineStr">
         <is>
-          <t>同じ書籍に進行中の計画がある状態で不正な期日を指定しても、入力エラーではなく403になる</t>
+          <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G232" s="9" t="inlineStr">
         <is>
-          <t>1.進行中の計画がある書籍を指定し、期日を空にして直接計画作成のリクエストを送信する</t>
+          <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H232" s="9" t="inlineStr">
         <is>
-          <t>バリデーションエラーではなく403Forbiddenになり、計画は作成されない（認可チェックが入力チェックより先に行われる）</t>
+          <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I232" s="4" t="n"/>
     </row>
     <row r="233">
-      <c r="A233" s="5" t="n"/>
-      <c r="B233" s="5" t="n"/>
-      <c r="C233" s="5" t="n"/>
-      <c r="D233" s="5" t="n"/>
+      <c r="A233" s="4" t="n"/>
+      <c r="B233" s="4" t="n"/>
+      <c r="C233" s="4" t="n"/>
+      <c r="D233" s="4" t="n"/>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>17-1-22</t>
+          <t>17-1-18</t>
         </is>
       </c>
       <c r="F233" s="9" t="inlineStr">
         <is>
-          <t>ステータスが「期限切れ」の計画は、読了操作を行える</t>
+          <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G233" s="9" t="inlineStr">
         <is>
-          <t>1.「期限切れ」の計画に対して、読了操作を行う</t>
+          <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H233" s="9" t="inlineStr">
         <is>
-          <t>ステータスが「完了」になり、completed_atに現在日時が記録され、「「(タイトル)」を読了しました。」と表示される</t>
-        </is>
-      </c>
-      <c r="I233" s="5" t="n"/>
+          <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I233" s="4" t="n"/>
     </row>
     <row r="234">
-      <c r="A234" s="7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B234" s="7" t="inlineStr">
-        <is>
-          <t>読書計画（期限変更）</t>
-        </is>
-      </c>
-      <c r="C234" s="7" t="inlineStr">
-        <is>
-          <t>18-1</t>
-        </is>
-      </c>
-      <c r="D234" s="7" t="inlineStr">
-        <is>
-          <t>読書計画の期日変更</t>
-        </is>
-      </c>
-      <c r="E234" s="7" t="inlineStr">
-        <is>
-          <t>18-1-1</t>
-        </is>
-      </c>
-      <c r="F234" s="7" t="inlineStr">
-        <is>
-          <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
-        </is>
-      </c>
-      <c r="G234" s="7" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
-        </is>
-      </c>
-      <c r="H234" s="7" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I234" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
-        </is>
-      </c>
+      <c r="A234" s="4" t="n"/>
+      <c r="B234" s="4" t="n"/>
+      <c r="C234" s="4" t="n"/>
+      <c r="D234" s="4" t="n"/>
+      <c r="E234" s="9" t="inlineStr">
+        <is>
+          <t>17-1-19</t>
+        </is>
+      </c>
+      <c r="F234" s="9" t="inlineStr">
+        <is>
+          <t>期日が日付形式でない場合、バリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="G234" s="9" t="inlineStr">
+        <is>
+          <t>1.書籍と、日付として不正な期日(例:abc)を指定して、直接計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H234" s="9" t="inlineStr">
+        <is>
+          <t>「正しい日付を入力してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="4" t="n"/>
       <c r="B235" s="4" t="n"/>
       <c r="C235" s="4" t="n"/>
       <c r="D235" s="4" t="n"/>
-      <c r="E235" s="7" t="inlineStr">
-        <is>
-          <t>18-1-2</t>
-        </is>
-      </c>
-      <c r="F235" s="7" t="inlineStr">
-        <is>
-          <t>他人が作成した読書計画の期日は変更できない</t>
-        </is>
-      </c>
-      <c r="G235" s="7" t="inlineStr">
-        <is>
-          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H235" s="7" t="inlineStr">
-        <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
+      <c r="E235" s="9" t="inlineStr">
+        <is>
+          <t>17-1-20</t>
+        </is>
+      </c>
+      <c r="F235" s="9" t="inlineStr">
+        <is>
+          <t>期日に今日の日付を指定した場合、計画を作成できる</t>
+        </is>
+      </c>
+      <c r="G235" s="9" t="inlineStr">
+        <is>
+          <t>1.計画作成ページを開く
+2.書籍を選択し、期日に今日の日付を指定して登録する</t>
+        </is>
+      </c>
+      <c r="H235" s="9" t="inlineStr">
+        <is>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される（今日の日付は指定可能）</t>
         </is>
       </c>
       <c r="I235" s="4" t="n"/>
@@ -7754,24 +7737,24 @@
       <c r="B236" s="4" t="n"/>
       <c r="C236" s="4" t="n"/>
       <c r="D236" s="4" t="n"/>
-      <c r="E236" s="7" t="inlineStr">
-        <is>
-          <t>18-1-3</t>
-        </is>
-      </c>
-      <c r="F236" s="7" t="inlineStr">
-        <is>
-          <t>編集画面を開くと現在の期日が初期表示される</t>
-        </is>
-      </c>
-      <c r="G236" s="7" t="inlineStr">
-        <is>
-          <t>1.自分が作成した計画の編集ページを開く</t>
-        </is>
-      </c>
-      <c r="H236" s="7" t="inlineStr">
-        <is>
-          <t>現在登録されている期日が入力欄に表示される</t>
+      <c r="E236" s="9" t="inlineStr">
+        <is>
+          <t>17-1-21</t>
+        </is>
+      </c>
+      <c r="F236" s="9" t="inlineStr">
+        <is>
+          <t>同じ書籍に進行中の計画がある状態で不正な期日を指定しても、入力エラーではなく403になる</t>
+        </is>
+      </c>
+      <c r="G236" s="9" t="inlineStr">
+        <is>
+          <t>1.進行中の計画がある書籍を指定し、期日を空にして直接計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H236" s="9" t="inlineStr">
+        <is>
+          <t>バリデーションエラーではなく403Forbiddenになり、計画は作成されない（認可チェックが入力チェックより先に行われる）</t>
         </is>
       </c>
       <c r="I236" s="4" t="n"/>
@@ -7781,84 +7764,103 @@
       <c r="B237" s="4" t="n"/>
       <c r="C237" s="4" t="n"/>
       <c r="D237" s="4" t="n"/>
-      <c r="E237" s="7" t="inlineStr">
-        <is>
-          <t>18-1-4</t>
-        </is>
-      </c>
-      <c r="F237" s="7" t="inlineStr">
-        <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
-        </is>
-      </c>
-      <c r="G237" s="7" t="inlineStr">
-        <is>
-          <t>1.編集ページを開く
-2.期日を空にして更新する</t>
-        </is>
-      </c>
-      <c r="H237" s="7" t="inlineStr">
-        <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+      <c r="E237" s="9" t="inlineStr">
+        <is>
+          <t>17-1-22</t>
+        </is>
+      </c>
+      <c r="F237" s="9" t="inlineStr">
+        <is>
+          <t>ステータスが「期限切れ」の計画は、読了操作を行える</t>
+        </is>
+      </c>
+      <c r="G237" s="9" t="inlineStr">
+        <is>
+          <t>1.「期限切れ」の計画に対して、読了操作を行う</t>
+        </is>
+      </c>
+      <c r="H237" s="9" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」になり、completed_atに現在日時が記録され、「「(タイトル)」を読了しました。」と表示される</t>
         </is>
       </c>
       <c r="I237" s="4" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="4" t="n"/>
-      <c r="B238" s="4" t="n"/>
-      <c r="C238" s="4" t="n"/>
-      <c r="D238" s="4" t="n"/>
-      <c r="E238" s="7" t="inlineStr">
-        <is>
-          <t>18-1-5</t>
-        </is>
-      </c>
-      <c r="F238" s="7" t="inlineStr">
-        <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
-        </is>
-      </c>
-      <c r="G238" s="7" t="inlineStr">
-        <is>
-          <t>1.編集ページを開く
-2.過去の日付に変更して更新する</t>
-        </is>
-      </c>
-      <c r="H238" s="7" t="inlineStr">
-        <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
-        </is>
-      </c>
-      <c r="I238" s="4" t="n"/>
+      <c r="A238" s="5" t="n"/>
+      <c r="B238" s="5" t="n"/>
+      <c r="C238" s="5" t="n"/>
+      <c r="D238" s="5" t="n"/>
+      <c r="E238" s="9" t="inlineStr">
+        <is>
+          <t>17-1-23</t>
+        </is>
+      </c>
+      <c r="F238" s="9" t="inlineStr">
+        <is>
+          <t>他のユーザーの「進行中」の計画は、自分の計画作成に影響しない</t>
+        </is>
+      </c>
+      <c r="G238" s="9" t="inlineStr">
+        <is>
+          <t>1.他のユーザーが「進行中」の計画を持つ書籍を用意する
+2.計画作成ページを開く
+3.その書籍で計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H238" s="9" t="inlineStr">
+        <is>
+          <t>その書籍は作成画面の選択肢に表示され、自分の計画が「進行中」で作成される（進行中の重複チェックはユーザーごとに行われる）</t>
+        </is>
+      </c>
+      <c r="I238" s="5" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="4" t="n"/>
-      <c r="B239" s="4" t="n"/>
-      <c r="C239" s="4" t="n"/>
-      <c r="D239" s="4" t="n"/>
+      <c r="A239" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B239" s="7" t="inlineStr">
+        <is>
+          <t>読書計画（期限変更）</t>
+        </is>
+      </c>
+      <c r="C239" s="7" t="inlineStr">
+        <is>
+          <t>18-1</t>
+        </is>
+      </c>
+      <c r="D239" s="7" t="inlineStr">
+        <is>
+          <t>読書計画の期日変更</t>
+        </is>
+      </c>
       <c r="E239" s="7" t="inlineStr">
         <is>
-          <t>18-1-6</t>
+          <t>18-1-1</t>
         </is>
       </c>
       <c r="F239" s="7" t="inlineStr">
         <is>
-          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
+          <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
         </is>
       </c>
       <c r="G239" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.未来の日付に正しく変更して更新する</t>
+          <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H239" s="7" t="inlineStr">
         <is>
-          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
-        </is>
-      </c>
-      <c r="I239" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I239" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="4" t="n"/>
@@ -7867,23 +7869,22 @@
       <c r="D240" s="4" t="n"/>
       <c r="E240" s="7" t="inlineStr">
         <is>
-          <t>18-1-7</t>
+          <t>18-1-2</t>
         </is>
       </c>
       <c r="F240" s="7" t="inlineStr">
         <is>
-          <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
+          <t>他人が作成した読書計画の期日は変更できない</t>
         </is>
       </c>
       <c r="G240" s="7" t="inlineStr">
         <is>
-          <t>1.期日が過去で「進行中」の計画を用意する
-2.読書計画一覧または編集ページを開く</t>
+          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H240" s="7" t="inlineStr">
         <is>
-          <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
+          <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
       <c r="I240" s="4" t="n"/>
@@ -7895,22 +7896,22 @@
       <c r="D241" s="4" t="n"/>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>18-1-8</t>
+          <t>18-1-3</t>
         </is>
       </c>
       <c r="F241" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は期日を変更できない</t>
+          <t>編集画面を開くと現在の期日が初期表示される</t>
         </is>
       </c>
       <c r="G241" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
+          <t>1.自分が作成した計画の編集ページを開く</t>
         </is>
       </c>
       <c r="H241" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
+          <t>現在登録されている期日が入力欄に表示される</t>
         </is>
       </c>
       <c r="I241" s="4" t="n"/>
@@ -7922,22 +7923,23 @@
       <c r="D242" s="4" t="n"/>
       <c r="E242" s="7" t="inlineStr">
         <is>
-          <t>18-1-9</t>
+          <t>18-1-4</t>
         </is>
       </c>
       <c r="F242" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G242" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
+          <t>1.編集ページを開く
+2.期日を空にして更新する</t>
         </is>
       </c>
       <c r="H242" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、編集ページは表示されない</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I242" s="4" t="n"/>
@@ -7949,22 +7951,23 @@
       <c r="D243" s="4" t="n"/>
       <c r="E243" s="7" t="inlineStr">
         <is>
-          <t>18-1-10</t>
+          <t>18-1-5</t>
         </is>
       </c>
       <c r="F243" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画の編集ページにはアクセスできない</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G243" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画の編集ページのURLに直接アクセスする</t>
+          <t>1.編集ページを開く
+2.過去の日付に変更して更新する</t>
         </is>
       </c>
       <c r="H243" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、編集ページは表示されない</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I243" s="4" t="n"/>
@@ -7976,102 +7979,81 @@
       <c r="D244" s="4" t="n"/>
       <c r="E244" s="7" t="inlineStr">
         <is>
-          <t>18-1-11</t>
+          <t>18-1-6</t>
         </is>
       </c>
       <c r="F244" s="7" t="inlineStr">
         <is>
-          <t>同じ書籍に「進行中」の計画がある場合、「期限切れ」の計画は編集・更新できない</t>
+          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
         </is>
       </c>
       <c r="G244" s="7" t="inlineStr">
         <is>
-          <t>1.同じ書籍について、「期限切れ」の計画と「進行中」の計画をそれぞれ用意する
-2.「期限切れ」の計画の編集ページのURLに直接アクセスする
-3.「期限切れ」の計画に対して、直接更新リクエストを送信する</t>
+          <t>1.編集ページを開く
+2.未来の日付に正しく変更して更新する</t>
         </is>
       </c>
       <c r="H244" s="7" t="inlineStr">
         <is>
-          <t>いずれも403Forbiddenになり、「期限切れ」の計画のステータス・期日は変更されない（同じ書籍の「進行中」の計画が2件になることを防ぐ）</t>
+          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
         </is>
       </c>
       <c r="I244" s="4" t="n"/>
     </row>
     <row r="245">
-      <c r="A245" s="5" t="n"/>
-      <c r="B245" s="5" t="n"/>
-      <c r="C245" s="5" t="n"/>
-      <c r="D245" s="5" t="n"/>
+      <c r="A245" s="4" t="n"/>
+      <c r="B245" s="4" t="n"/>
+      <c r="C245" s="4" t="n"/>
+      <c r="D245" s="4" t="n"/>
       <c r="E245" s="7" t="inlineStr">
         <is>
-          <t>18-1-12</t>
+          <t>18-1-7</t>
         </is>
       </c>
       <c r="F245" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画に不正な期日で更新しようとしても、入力エラーではなく403になる</t>
+          <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
         </is>
       </c>
       <c r="G245" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した読書計画に対して、期日を空にして直接計画更新のリクエストを送信する</t>
+          <t>1.期日が過去で「進行中」の計画を用意する
+2.読書計画一覧または編集ページを開く</t>
         </is>
       </c>
       <c r="H245" s="7" t="inlineStr">
         <is>
-          <t>バリデーションエラーではなく403Forbiddenになり、期日は変更されない（認可チェックが入力チェックより先に行われる）</t>
-        </is>
-      </c>
-      <c r="I245" s="5" t="n"/>
+          <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
+        </is>
+      </c>
+      <c r="I245" s="4" t="n"/>
     </row>
     <row r="246">
-      <c r="A246" s="7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B246" s="7" t="inlineStr">
-        <is>
-          <t>リマインダーバッチ</t>
-        </is>
-      </c>
-      <c r="C246" s="7" t="inlineStr">
-        <is>
-          <t>19-1</t>
-        </is>
-      </c>
-      <c r="D246" s="7" t="inlineStr">
-        <is>
-          <t>日次バッチ(reading-plans:daily)によるリマインダー通知</t>
-        </is>
-      </c>
+      <c r="A246" s="4" t="n"/>
+      <c r="B246" s="4" t="n"/>
+      <c r="C246" s="4" t="n"/>
+      <c r="D246" s="4" t="n"/>
       <c r="E246" s="7" t="inlineStr">
         <is>
-          <t>19-1-1</t>
+          <t>18-1-8</t>
         </is>
       </c>
       <c r="F246" s="7" t="inlineStr">
         <is>
-          <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
+          <t>ステータスが「完了」の計画は期日を変更できない</t>
         </is>
       </c>
       <c r="G246" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが3日後・ステータス進行中の計画を用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H246" s="7" t="inlineStr">
         <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_before)・title(「読書期限のお知らせ」)・body(「「(書籍名)」の読書期限まであと3日です。」)が含まれる</t>
-        </is>
-      </c>
-      <c r="I246" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
-        </is>
-      </c>
+          <t>403Forbiddenになり、期日は変更されない</t>
+        </is>
+      </c>
+      <c r="I246" s="4" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="4" t="n"/>
@@ -8080,23 +8062,22 @@
       <c r="D247" s="4" t="n"/>
       <c r="E247" s="7" t="inlineStr">
         <is>
-          <t>19-1-2</t>
+          <t>18-1-9</t>
         </is>
       </c>
       <c r="F247" s="7" t="inlineStr">
         <is>
-          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
+          <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
         </is>
       </c>
       <c r="G247" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが本日・ステータス進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
+          <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H247" s="7" t="inlineStr">
         <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される。通知のdataには、plan_id・book_title・timing(on_due_date)・title(「読書期限当日のお知らせ」)・body(「「(書籍名)」の読書期限は本日までです。」)が含まれる</t>
+          <t>403Forbiddenになり、編集ページは表示されない</t>
         </is>
       </c>
       <c r="I247" s="4" t="n"/>
@@ -8108,23 +8089,22 @@
       <c r="D248" s="4" t="n"/>
       <c r="E248" s="7" t="inlineStr">
         <is>
-          <t>19-1-3</t>
+          <t>18-1-10</t>
         </is>
       </c>
       <c r="F248" s="7" t="inlineStr">
         <is>
-          <t>期限切れから3日後の計画に再エンゲージメント通知が送信される</t>
+          <t>他人が作成した読書計画の編集ページにはアクセスできない</t>
         </is>
       </c>
       <c r="G248" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが3日前・ステータス期限切れの計画を用意する
-2.reading-plans:dailyを実行する</t>
+          <t>1.他人が作成した計画の編集ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H248" s="7" t="inlineStr">
         <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
+          <t>403Forbiddenになり、編集ページは表示されない</t>
         </is>
       </c>
       <c r="I248" s="4" t="n"/>
@@ -8136,23 +8116,24 @@
       <c r="D249" s="4" t="n"/>
       <c r="E249" s="7" t="inlineStr">
         <is>
-          <t>19-1-4</t>
+          <t>18-1-11</t>
         </is>
       </c>
       <c r="F249" s="7" t="inlineStr">
         <is>
-          <t>いずれの条件にも該当しない計画には通知が送信されない</t>
+          <t>同じ書籍に「進行中」の計画がある場合、「期限切れ」の計画は編集・更新できない</t>
         </is>
       </c>
       <c r="G249" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
+          <t>1.同じ書籍について、「期限切れ」の計画と「進行中」の計画をそれぞれ用意する
+2.「期限切れ」の計画の編集ページのURLに直接アクセスする
+3.「期限切れ」の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H249" s="7" t="inlineStr">
         <is>
-          <t>その計画のユーザーに通知が送信されない</t>
+          <t>いずれも403Forbiddenになり、「期限切れ」の計画のステータス・期日は変更されない（同じ書籍の「進行中」の計画が2件になることを防ぐ）</t>
         </is>
       </c>
       <c r="I249" s="4" t="n"/>
@@ -8164,23 +8145,22 @@
       <c r="D250" s="5" t="n"/>
       <c r="E250" s="7" t="inlineStr">
         <is>
-          <t>19-1-5</t>
+          <t>18-1-12</t>
         </is>
       </c>
       <c r="F250" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画には、期日の条件に合っていても通知が送信されない</t>
+          <t>他人が作成した読書計画に不正な期日で更新しようとしても、入力エラーではなく403になる</t>
         </is>
       </c>
       <c r="G250" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが3日後・本日・3日前で、ステータスが完了の計画をそれぞれ用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+          <t>1.他人が作成した読書計画に対して、期日を空にして直接計画更新のリクエストを送信する</t>
         </is>
       </c>
       <c r="H250" s="7" t="inlineStr">
         <is>
-          <t>いずれの計画のユーザーにも通知が送信されない</t>
+          <t>バリデーションエラーではなく403Forbiddenになり、期日は変更されない（認可チェックが入力チェックより先に行われる）</t>
         </is>
       </c>
       <c r="I250" s="5" t="n"/>
@@ -8188,48 +8168,48 @@
     <row r="251">
       <c r="A251" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B251" s="7" t="inlineStr">
         <is>
-          <t>自動失効バッチ</t>
+          <t>リマインダーバッチ</t>
         </is>
       </c>
       <c r="C251" s="7" t="inlineStr">
         <is>
-          <t>20-1</t>
+          <t>19-1</t>
         </is>
       </c>
       <c r="D251" s="7" t="inlineStr">
         <is>
-          <t>日次バッチ(reading-plans:daily)による自動失効処理</t>
+          <t>日次バッチ(reading-plans:daily)によるリマインダー通知</t>
         </is>
       </c>
       <c r="E251" s="7" t="inlineStr">
         <is>
-          <t>20-1-1</t>
+          <t>19-1-1</t>
         </is>
       </c>
       <c r="F251" s="7" t="inlineStr">
         <is>
-          <t>期日を過ぎた「進行中」の計画が「期限切れ」に更新される</t>
+          <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
         </is>
       </c>
       <c r="G251" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが過去・ステータス進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
+          <t>1.target_dateが3日後・ステータス進行中の計画を用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
       <c r="H251" s="7" t="inlineStr">
         <is>
-          <t>対象の計画のstatusが「期限切れ」に更新される</t>
+          <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_before)・title(「読書期限のお知らせ」)・body(「「(書籍名)」の読書期限まであと3日です。」)が含まれる</t>
         </is>
       </c>
       <c r="I251" s="7" t="inlineStr">
         <is>
-          <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
+          <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
         </is>
       </c>
     </row>
@@ -8240,23 +8220,23 @@
       <c r="D252" s="4" t="n"/>
       <c r="E252" s="7" t="inlineStr">
         <is>
-          <t>20-1-2</t>
+          <t>19-1-2</t>
         </is>
       </c>
       <c r="F252" s="7" t="inlineStr">
         <is>
-          <t>期日が今日以降の「進行中」の計画は失効しない</t>
+          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
         </is>
       </c>
       <c r="G252" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
+          <t>1.target_dateが本日・ステータス進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H252" s="7" t="inlineStr">
         <is>
-          <t>その計画のstatusは「進行中」のまま変化しない</t>
+          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される。通知のdataには、plan_id・book_title・timing(on_due_date)・title(「読書期限当日のお知らせ」)・body(「「(書籍名)」の読書期限は本日までです。」)が含まれる</t>
         </is>
       </c>
       <c r="I252" s="4" t="n"/>
@@ -8268,23 +8248,23 @@
       <c r="D253" s="4" t="n"/>
       <c r="E253" s="7" t="inlineStr">
         <is>
-          <t>20-1-3</t>
+          <t>19-1-3</t>
         </is>
       </c>
       <c r="F253" s="7" t="inlineStr">
         <is>
-          <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
+          <t>期限切れから3日後の計画に再エンゲージメント通知が送信される</t>
         </is>
       </c>
       <c r="G253" s="7" t="inlineStr">
         <is>
-          <t>1.完了済み・期限切れの計画をそれぞれ用意する
+          <t>1.target_dateが3日前・ステータス期限切れの計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H253" s="7" t="inlineStr">
         <is>
-          <t>いずれの計画もstatusが変化しない</t>
+          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
         </is>
       </c>
       <c r="I253" s="4" t="n"/>
@@ -8292,351 +8272,361 @@
     <row r="254">
       <c r="A254" s="4" t="n"/>
       <c r="B254" s="4" t="n"/>
-      <c r="C254" s="5" t="n"/>
-      <c r="D254" s="5" t="n"/>
+      <c r="C254" s="4" t="n"/>
+      <c r="D254" s="4" t="n"/>
       <c r="E254" s="7" t="inlineStr">
         <is>
-          <t>20-1-4</t>
+          <t>19-1-4</t>
         </is>
       </c>
       <c r="F254" s="7" t="inlineStr">
         <is>
-          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+          <t>いずれの条件にも該当しない計画には通知が送信されない</t>
         </is>
       </c>
       <c r="G254" s="7" t="inlineStr">
         <is>
-          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
-2.DBを直接確認する</t>
+          <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H254" s="7" t="inlineStr">
         <is>
-          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
-        </is>
-      </c>
-      <c r="I254" s="5" t="n"/>
+          <t>その計画のユーザーに通知が送信されない</t>
+        </is>
+      </c>
+      <c r="I254" s="4" t="n"/>
     </row>
     <row r="255">
-      <c r="A255" s="4" t="n"/>
-      <c r="B255" s="4" t="n"/>
-      <c r="C255" s="7" t="inlineStr">
-        <is>
-          <t>20-2</t>
-        </is>
-      </c>
-      <c r="D255" s="7" t="inlineStr">
-        <is>
-          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
-        </is>
-      </c>
+      <c r="A255" s="5" t="n"/>
+      <c r="B255" s="5" t="n"/>
+      <c r="C255" s="5" t="n"/>
+      <c r="D255" s="5" t="n"/>
       <c r="E255" s="7" t="inlineStr">
         <is>
-          <t>20-2-1</t>
+          <t>19-1-5</t>
         </is>
       </c>
       <c r="F255" s="7" t="inlineStr">
         <is>
-          <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
+          <t>ステータスが「完了」の計画には、期日の条件に合っていても通知が送信されない</t>
         </is>
       </c>
       <c r="G255" s="7" t="inlineStr">
         <is>
-          <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
+          <t>1.target_dateが3日後・本日・3日前で、ステータスが完了の計画をそれぞれ用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
       <c r="H255" s="7" t="inlineStr">
         <is>
-          <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I255" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
-        </is>
-      </c>
+          <t>いずれの計画のユーザーにも通知が送信されない</t>
+        </is>
+      </c>
+      <c r="I255" s="5" t="n"/>
     </row>
     <row r="256">
-      <c r="A256" s="4" t="n"/>
-      <c r="B256" s="4" t="n"/>
-      <c r="C256" s="4" t="n"/>
-      <c r="D256" s="4" t="n"/>
+      <c r="A256" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B256" s="7" t="inlineStr">
+        <is>
+          <t>自動失効バッチ</t>
+        </is>
+      </c>
+      <c r="C256" s="7" t="inlineStr">
+        <is>
+          <t>20-1</t>
+        </is>
+      </c>
+      <c r="D256" s="7" t="inlineStr">
+        <is>
+          <t>日次バッチ(reading-plans:daily)による自動失効処理</t>
+        </is>
+      </c>
       <c r="E256" s="7" t="inlineStr">
         <is>
-          <t>20-2-2</t>
+          <t>20-1-1</t>
         </is>
       </c>
       <c r="F256" s="7" t="inlineStr">
         <is>
-          <t>期限切れへの更新が、通知対象の抽出より先に行われる</t>
+          <t>期日を過ぎた「進行中」の計画が「期限切れ」に更新される</t>
         </is>
       </c>
       <c r="G256" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが3日前で、ステータスが「進行中」のまま(未更新)の計画を用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+          <t>1.target_dateが過去・ステータス進行中の計画を用意する
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H256" s="7" t="inlineStr">
         <is>
-          <t>計画のstatusが「期限切れ」に更新され、そのユーザーに再エンゲージメント(re_engagement)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I256" s="4" t="n"/>
+          <t>対象の計画のstatusが「期限切れ」に更新される</t>
+        </is>
+      </c>
+      <c r="I256" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="257">
-      <c r="A257" s="5" t="n"/>
-      <c r="B257" s="5" t="n"/>
-      <c r="C257" s="5" t="n"/>
-      <c r="D257" s="5" t="n"/>
+      <c r="A257" s="4" t="n"/>
+      <c r="B257" s="4" t="n"/>
+      <c r="C257" s="4" t="n"/>
+      <c r="D257" s="4" t="n"/>
       <c r="E257" s="7" t="inlineStr">
         <is>
-          <t>20-2-3</t>
+          <t>20-1-2</t>
         </is>
       </c>
       <c r="F257" s="7" t="inlineStr">
         <is>
-          <t>reading-plans:dailyが毎日20:00に実行されるようスケジュールされている</t>
+          <t>期日が今日以降の「進行中」の計画は失効しない</t>
         </is>
       </c>
       <c r="G257" s="7" t="inlineStr">
         <is>
-          <t>1.アプリケーションのスケジュール(Illuminate\Console\Scheduling\Schedule)から、登録済みのイベントを取得する</t>
+          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H257" s="7" t="inlineStr">
         <is>
-          <t>reading-plans:dailyのイベントが登録されており、cron式が毎日20:00(0 20 * * *)になっている</t>
-        </is>
-      </c>
-      <c r="I257" s="5" t="n"/>
+          <t>その計画のstatusは「進行中」のまま変化しない</t>
+        </is>
+      </c>
+      <c r="I257" s="4" t="n"/>
     </row>
     <row r="258">
-      <c r="A258" s="9" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B258" s="9" t="inlineStr">
-        <is>
-          <t>通知</t>
-        </is>
-      </c>
-      <c r="C258" s="9" t="inlineStr">
-        <is>
-          <t>21-1</t>
-        </is>
-      </c>
-      <c r="D258" s="9" t="inlineStr">
-        <is>
-          <t>通知の既読化</t>
-        </is>
-      </c>
-      <c r="E258" s="9" t="inlineStr">
-        <is>
-          <t>21-1-1</t>
-        </is>
-      </c>
-      <c r="F258" s="9" t="inlineStr">
-        <is>
-          <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
-        </is>
-      </c>
-      <c r="G258" s="9" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態でPOST /notifications/{id}/read に直接リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H258" s="9" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
-        </is>
-      </c>
-      <c r="I258" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationTest.php</t>
-        </is>
-      </c>
+      <c r="A258" s="4" t="n"/>
+      <c r="B258" s="4" t="n"/>
+      <c r="C258" s="4" t="n"/>
+      <c r="D258" s="4" t="n"/>
+      <c r="E258" s="7" t="inlineStr">
+        <is>
+          <t>20-1-3</t>
+        </is>
+      </c>
+      <c r="F258" s="7" t="inlineStr">
+        <is>
+          <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
+        </is>
+      </c>
+      <c r="G258" s="7" t="inlineStr">
+        <is>
+          <t>1.完了済み・期限切れの計画をそれぞれ用意する
+2.reading-plans:dailyを実行する</t>
+        </is>
+      </c>
+      <c r="H258" s="7" t="inlineStr">
+        <is>
+          <t>いずれの計画もstatusが変化しない</t>
+        </is>
+      </c>
+      <c r="I258" s="4" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n"/>
       <c r="B259" s="4" t="n"/>
-      <c r="C259" s="4" t="n"/>
-      <c r="D259" s="4" t="n"/>
-      <c r="E259" s="9" t="inlineStr">
-        <is>
-          <t>21-1-2</t>
-        </is>
-      </c>
-      <c r="F259" s="9" t="inlineStr">
-        <is>
-          <t>自分の通知を既読にできる</t>
-        </is>
-      </c>
-      <c r="G259" s="9" t="inlineStr">
-        <is>
-          <t>1.自分宛ての未読通知を用意する
-2.その通知に対してPOST /notifications/{id}/read を送信する</t>
-        </is>
-      </c>
-      <c r="H259" s="9" t="inlineStr">
-        <is>
-          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
-        </is>
-      </c>
-      <c r="I259" s="4" t="n"/>
+      <c r="C259" s="5" t="n"/>
+      <c r="D259" s="5" t="n"/>
+      <c r="E259" s="7" t="inlineStr">
+        <is>
+          <t>20-1-4</t>
+        </is>
+      </c>
+      <c r="F259" s="7" t="inlineStr">
+        <is>
+          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+        </is>
+      </c>
+      <c r="G259" s="7" t="inlineStr">
+        <is>
+          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
+2.DBを直接確認する</t>
+        </is>
+      </c>
+      <c r="H259" s="7" t="inlineStr">
+        <is>
+          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
+        </is>
+      </c>
+      <c r="I259" s="5" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="4" t="n"/>
       <c r="B260" s="4" t="n"/>
-      <c r="C260" s="5" t="n"/>
-      <c r="D260" s="5" t="n"/>
-      <c r="E260" s="9" t="inlineStr">
-        <is>
-          <t>21-1-3</t>
-        </is>
-      </c>
-      <c r="F260" s="9" t="inlineStr">
-        <is>
-          <t>他ユーザーの通知は既読にできない</t>
-        </is>
-      </c>
-      <c r="G260" s="9" t="inlineStr">
-        <is>
-          <t>1.他ユーザー宛ての通知を用意する
-2.そのIDに対してPOST /notifications/{id}/read を送信する</t>
-        </is>
-      </c>
-      <c r="H260" s="9" t="inlineStr">
-        <is>
-          <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
-        </is>
-      </c>
-      <c r="I260" s="5" t="n"/>
+      <c r="C260" s="7" t="inlineStr">
+        <is>
+          <t>20-2</t>
+        </is>
+      </c>
+      <c r="D260" s="7" t="inlineStr">
+        <is>
+          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
+        </is>
+      </c>
+      <c r="E260" s="7" t="inlineStr">
+        <is>
+          <t>20-2-1</t>
+        </is>
+      </c>
+      <c r="F260" s="7" t="inlineStr">
+        <is>
+          <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
+        </is>
+      </c>
+      <c r="G260" s="7" t="inlineStr">
+        <is>
+          <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+        </is>
+      </c>
+      <c r="H260" s="7" t="inlineStr">
+        <is>
+          <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I260" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="4" t="n"/>
       <c r="B261" s="4" t="n"/>
-      <c r="C261" s="9" t="inlineStr">
-        <is>
-          <t>21-2</t>
-        </is>
-      </c>
-      <c r="D261" s="9" t="inlineStr">
-        <is>
-          <t>通知一覧</t>
-        </is>
-      </c>
-      <c r="E261" s="9" t="inlineStr">
-        <is>
-          <t>21-2-1</t>
-        </is>
-      </c>
-      <c r="F261" s="9" t="inlineStr">
-        <is>
-          <t>未ログインの場合、通知一覧にアクセスできない</t>
-        </is>
-      </c>
-      <c r="G261" s="9" t="inlineStr">
-        <is>
-          <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
-        </is>
-      </c>
-      <c r="H261" s="9" t="inlineStr">
-        <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I261" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationIndexTest.php</t>
-        </is>
-      </c>
+      <c r="C261" s="4" t="n"/>
+      <c r="D261" s="4" t="n"/>
+      <c r="E261" s="7" t="inlineStr">
+        <is>
+          <t>20-2-2</t>
+        </is>
+      </c>
+      <c r="F261" s="7" t="inlineStr">
+        <is>
+          <t>期限切れへの更新が、通知対象の抽出より先に行われる</t>
+        </is>
+      </c>
+      <c r="G261" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日前で、ステータスが「進行中」のまま(未更新)の計画を用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+        </is>
+      </c>
+      <c r="H261" s="7" t="inlineStr">
+        <is>
+          <t>計画のstatusが「期限切れ」に更新され、そのユーザーに再エンゲージメント(re_engagement)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="n"/>
     </row>
     <row r="262">
       <c r="A262" s="4" t="n"/>
       <c r="B262" s="4" t="n"/>
       <c r="C262" s="4" t="n"/>
       <c r="D262" s="4" t="n"/>
-      <c r="E262" s="9" t="inlineStr">
-        <is>
-          <t>21-2-2</t>
-        </is>
-      </c>
-      <c r="F262" s="9" t="inlineStr">
-        <is>
-          <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
-        </is>
-      </c>
-      <c r="G262" s="9" t="inlineStr">
-        <is>
-          <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
-2.通知一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H262" s="9" t="inlineStr">
-        <is>
-          <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
+      <c r="E262" s="7" t="inlineStr">
+        <is>
+          <t>20-2-3</t>
+        </is>
+      </c>
+      <c r="F262" s="7" t="inlineStr">
+        <is>
+          <t>reading-plans:dailyが毎日20:00に実行されるようスケジュールされている</t>
+        </is>
+      </c>
+      <c r="G262" s="7" t="inlineStr">
+        <is>
+          <t>1.アプリケーションのスケジュール(Illuminate\Console\Scheduling\Schedule)から、登録済みのイベントを取得する</t>
+        </is>
+      </c>
+      <c r="H262" s="7" t="inlineStr">
+        <is>
+          <t>reading-plans:dailyのイベントが登録されており、cron式が毎日20:00(0 20 * * *)になっている</t>
         </is>
       </c>
       <c r="I262" s="4" t="n"/>
     </row>
     <row r="263">
-      <c r="A263" s="4" t="n"/>
-      <c r="B263" s="4" t="n"/>
-      <c r="C263" s="4" t="n"/>
-      <c r="D263" s="4" t="n"/>
-      <c r="E263" s="9" t="inlineStr">
-        <is>
-          <t>21-2-3</t>
-        </is>
-      </c>
-      <c r="F263" s="9" t="inlineStr">
-        <is>
-          <t>通知が1件もない場合の表示を確認する</t>
-        </is>
-      </c>
-      <c r="G263" s="9" t="inlineStr">
-        <is>
-          <t>1.通知が1件もないユーザーでログインする
-2.通知一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H263" s="9" t="inlineStr">
-        <is>
-          <t>「通知はありません。」と表示される</t>
-        </is>
-      </c>
-      <c r="I263" s="4" t="n"/>
+      <c r="A263" s="5" t="n"/>
+      <c r="B263" s="5" t="n"/>
+      <c r="C263" s="5" t="n"/>
+      <c r="D263" s="5" t="n"/>
+      <c r="E263" s="7" t="inlineStr">
+        <is>
+          <t>20-2-4</t>
+        </is>
+      </c>
+      <c r="F263" s="7" t="inlineStr">
+        <is>
+          <t>日次バッチで送信した通知がnotificationsテーブルに保存され、通知一覧に表示される</t>
+        </is>
+      </c>
+      <c r="G263" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日後(期日の3日前)・ステータス進行中の計画を用意する
+2.Notification::fake()を使わずに reading-plans:daily を実行する
+3.計画のユーザーで通知一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H263" s="7" t="inlineStr">
+        <is>
+          <t>notificationsテーブルにReadingPlanReminderの通知(未読、dataのplan_id・timingが対象の計画のもの)が1件保存され、通知一覧に「読書期限のお知らせ」と本文が未読として表示される</t>
+        </is>
+      </c>
+      <c r="I263" s="5" t="n"/>
     </row>
     <row r="264">
-      <c r="A264" s="4" t="n"/>
-      <c r="B264" s="4" t="n"/>
-      <c r="C264" s="4" t="n"/>
-      <c r="D264" s="4" t="n"/>
+      <c r="A264" s="9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B264" s="9" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="C264" s="9" t="inlineStr">
+        <is>
+          <t>21-1</t>
+        </is>
+      </c>
+      <c r="D264" s="9" t="inlineStr">
+        <is>
+          <t>通知の既読化</t>
+        </is>
+      </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>21-2-4</t>
+          <t>21-1-1</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>通知のタイトル・本文が表示される</t>
+          <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
         </is>
       </c>
       <c r="G264" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
-2.通知一覧ページを開く</t>
+          <t>1.未ログイン状態でPOST /notifications/{id}/read に直接リクエストを送信する</t>
         </is>
       </c>
       <c r="H264" s="9" t="inlineStr">
         <is>
-          <t>通知のtitleとbodyが一覧に表示される</t>
-        </is>
-      </c>
-      <c r="I264" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
+        </is>
+      </c>
+      <c r="I264" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="4" t="n"/>
@@ -8645,23 +8635,23 @@
       <c r="D265" s="4" t="n"/>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>21-2-5</t>
+          <t>21-1-2</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>未読と既読で表示が異なる</t>
+          <t>自分の通知を既読にできる</t>
         </is>
       </c>
       <c r="G265" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
-2.通知一覧ページを開く</t>
+          <t>1.自分宛ての未読通知を用意する
+2.その通知に対してPOST /notifications/{id}/read を送信する</t>
         </is>
       </c>
       <c r="H265" s="9" t="inlineStr">
         <is>
-          <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
+          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
         </is>
       </c>
       <c r="I265" s="4" t="n"/>
@@ -8673,23 +8663,23 @@
       <c r="D266" s="5" t="n"/>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>21-2-6</t>
+          <t>21-1-3</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>同じ日時に作成された通知は、期日3日前→期日当日→期日3日後の順に表示される</t>
+          <t>他ユーザーの通知は既読にできない</t>
         </is>
       </c>
       <c r="G266" s="9" t="inlineStr">
         <is>
-          <t>1.同じ日時に作成された、期日3日前（予告）・期日当日（最終警告）・期日3日後（再エンゲージメント）の通知と、作成日時の異なる通知を用意する
-2.通知一覧ページを開く</t>
+          <t>1.他ユーザー宛ての通知を用意する
+2.そのIDに対してPOST /notifications/{id}/read を送信する</t>
         </is>
       </c>
       <c r="H266" s="9" t="inlineStr">
         <is>
-          <t>第1優先で作成日時の新しい順、作成日時が同じ通知同士は第2優先で「期日3日前→期日当日→期日3日後」の順に表示される</t>
+          <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
         </is>
       </c>
       <c r="I266" s="5" t="n"/>
@@ -8699,37 +8689,37 @@
       <c r="B267" s="4" t="n"/>
       <c r="C267" s="9" t="inlineStr">
         <is>
-          <t>21-3</t>
+          <t>21-2</t>
         </is>
       </c>
       <c r="D267" s="9" t="inlineStr">
         <is>
-          <t>ヘッダーの未読件数</t>
+          <t>通知一覧</t>
         </is>
       </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>21-3-1</t>
+          <t>21-2-1</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>ヘッダーのベルアイコンに未読件数が表示される</t>
+          <t>未ログインの場合、通知一覧にアクセスできない</t>
         </is>
       </c>
       <c r="G267" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
+          <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H267" s="9" t="inlineStr">
         <is>
-          <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
+          <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
       <c r="I267" s="9" t="inlineStr">
         <is>
-          <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
+          <t>tests/Feature/Notification/NotificationIndexTest.php</t>
         </is>
       </c>
     </row>
@@ -8740,234 +8730,413 @@
       <c r="D268" s="4" t="n"/>
       <c r="E268" s="9" t="inlineStr">
         <is>
+          <t>21-2-2</t>
+        </is>
+      </c>
+      <c r="F268" s="9" t="inlineStr">
+        <is>
+          <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
+        </is>
+      </c>
+      <c r="G268" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
+2.通知一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H268" s="9" t="inlineStr">
+        <is>
+          <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
+        </is>
+      </c>
+      <c r="I268" s="4" t="n"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="n"/>
+      <c r="B269" s="4" t="n"/>
+      <c r="C269" s="4" t="n"/>
+      <c r="D269" s="4" t="n"/>
+      <c r="E269" s="9" t="inlineStr">
+        <is>
+          <t>21-2-3</t>
+        </is>
+      </c>
+      <c r="F269" s="9" t="inlineStr">
+        <is>
+          <t>通知が1件もない場合の表示を確認する</t>
+        </is>
+      </c>
+      <c r="G269" s="9" t="inlineStr">
+        <is>
+          <t>1.通知が1件もないユーザーでログインする
+2.通知一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H269" s="9" t="inlineStr">
+        <is>
+          <t>「通知はありません。」と表示される</t>
+        </is>
+      </c>
+      <c r="I269" s="4" t="n"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="n"/>
+      <c r="B270" s="4" t="n"/>
+      <c r="C270" s="4" t="n"/>
+      <c r="D270" s="4" t="n"/>
+      <c r="E270" s="9" t="inlineStr">
+        <is>
+          <t>21-2-4</t>
+        </is>
+      </c>
+      <c r="F270" s="9" t="inlineStr">
+        <is>
+          <t>通知のタイトル・本文が表示される</t>
+        </is>
+      </c>
+      <c r="G270" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
+2.通知一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H270" s="9" t="inlineStr">
+        <is>
+          <t>通知のtitleとbodyが一覧に表示される</t>
+        </is>
+      </c>
+      <c r="I270" s="4" t="n"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="n"/>
+      <c r="B271" s="4" t="n"/>
+      <c r="C271" s="4" t="n"/>
+      <c r="D271" s="4" t="n"/>
+      <c r="E271" s="9" t="inlineStr">
+        <is>
+          <t>21-2-5</t>
+        </is>
+      </c>
+      <c r="F271" s="9" t="inlineStr">
+        <is>
+          <t>未読と既読で表示が異なる</t>
+        </is>
+      </c>
+      <c r="G271" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
+2.通知一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H271" s="9" t="inlineStr">
+        <is>
+          <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
+        </is>
+      </c>
+      <c r="I271" s="4" t="n"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="n"/>
+      <c r="B272" s="4" t="n"/>
+      <c r="C272" s="5" t="n"/>
+      <c r="D272" s="5" t="n"/>
+      <c r="E272" s="9" t="inlineStr">
+        <is>
+          <t>21-2-6</t>
+        </is>
+      </c>
+      <c r="F272" s="9" t="inlineStr">
+        <is>
+          <t>同じ日時に作成された通知は、期日3日前→期日当日→期日3日後の順に表示される</t>
+        </is>
+      </c>
+      <c r="G272" s="9" t="inlineStr">
+        <is>
+          <t>1.同じ日時に作成された、期日3日前（予告）・期日当日（最終警告）・期日3日後（再エンゲージメント）の通知と、作成日時の異なる通知を用意する
+2.通知一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H272" s="9" t="inlineStr">
+        <is>
+          <t>第1優先で作成日時の新しい順、作成日時が同じ通知同士は第2優先で「期日3日前→期日当日→期日3日後」の順に表示される</t>
+        </is>
+      </c>
+      <c r="I272" s="5" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="n"/>
+      <c r="B273" s="4" t="n"/>
+      <c r="C273" s="9" t="inlineStr">
+        <is>
+          <t>21-3</t>
+        </is>
+      </c>
+      <c r="D273" s="9" t="inlineStr">
+        <is>
+          <t>ヘッダーの未読件数</t>
+        </is>
+      </c>
+      <c r="E273" s="9" t="inlineStr">
+        <is>
+          <t>21-3-1</t>
+        </is>
+      </c>
+      <c r="F273" s="9" t="inlineStr">
+        <is>
+          <t>ヘッダーのベルアイコンに未読件数が表示される</t>
+        </is>
+      </c>
+      <c r="G273" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
+        </is>
+      </c>
+      <c r="H273" s="9" t="inlineStr">
+        <is>
+          <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
+        </is>
+      </c>
+      <c r="I273" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="n"/>
+      <c r="B274" s="4" t="n"/>
+      <c r="C274" s="4" t="n"/>
+      <c r="D274" s="4" t="n"/>
+      <c r="E274" s="9" t="inlineStr">
+        <is>
           <t>21-3-2</t>
         </is>
       </c>
-      <c r="F268" s="9" t="inlineStr">
+      <c r="F274" s="9" t="inlineStr">
         <is>
           <t>通知を既読にすると、ヘッダーの未読件数が減る</t>
         </is>
       </c>
-      <c r="G268" s="9" t="inlineStr">
+      <c r="G274" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知を複数件用意する
 2.そのうち1件にPOST /notifications/{id}/read を送信して既読にする
 3.画面を開き直す</t>
         </is>
       </c>
-      <c r="H268" s="9" t="inlineStr">
+      <c r="H274" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数が、既読にした1件分だけ減る</t>
         </is>
       </c>
-      <c r="I268" s="4" t="n"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="5" t="n"/>
-      <c r="B269" s="5" t="n"/>
-      <c r="C269" s="5" t="n"/>
-      <c r="D269" s="5" t="n"/>
-      <c r="E269" s="9" t="inlineStr">
+      <c r="I274" s="4" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="n"/>
+      <c r="B275" s="5" t="n"/>
+      <c r="C275" s="5" t="n"/>
+      <c r="D275" s="5" t="n"/>
+      <c r="E275" s="9" t="inlineStr">
         <is>
           <t>21-3-3</t>
         </is>
       </c>
-      <c r="F269" s="9" t="inlineStr">
+      <c r="F275" s="9" t="inlineStr">
         <is>
           <t>他ユーザーの通知は未読件数に含まれない</t>
         </is>
       </c>
-      <c r="G269" s="9" t="inlineStr">
+      <c r="G275" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知と、他ユーザー宛ての未読通知をそれぞれ用意する
 2.画面を開く</t>
         </is>
       </c>
-      <c r="H269" s="9" t="inlineStr">
+      <c r="H275" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数には、自分宛ての未読通知のみが数えられる</t>
         </is>
       </c>
-      <c r="I269" s="5" t="n"/>
+      <c r="I275" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="177">
     <mergeCell ref="B121:B124"/>
     <mergeCell ref="I70:I75"/>
+    <mergeCell ref="D267:D272"/>
     <mergeCell ref="D164:D170"/>
-    <mergeCell ref="C251:C254"/>
+    <mergeCell ref="C216:C238"/>
     <mergeCell ref="I56:I61"/>
-    <mergeCell ref="D246:D250"/>
     <mergeCell ref="D157:D163"/>
     <mergeCell ref="D35:D41"/>
+    <mergeCell ref="I154:I156"/>
     <mergeCell ref="C56:C61"/>
-    <mergeCell ref="I154:I156"/>
     <mergeCell ref="C42:C55"/>
     <mergeCell ref="A2:A16"/>
-    <mergeCell ref="D183:D187"/>
+    <mergeCell ref="C157:C163"/>
     <mergeCell ref="B125:B142"/>
-    <mergeCell ref="C157:C163"/>
     <mergeCell ref="C66:C69"/>
     <mergeCell ref="C171:C175"/>
     <mergeCell ref="D17:D30"/>
     <mergeCell ref="C143:C145"/>
+    <mergeCell ref="C267:C272"/>
     <mergeCell ref="B111:B117"/>
+    <mergeCell ref="B212:B215"/>
+    <mergeCell ref="B216:B238"/>
     <mergeCell ref="I143:I145"/>
     <mergeCell ref="D137:D141"/>
-    <mergeCell ref="A212:A233"/>
-    <mergeCell ref="C212:C233"/>
+    <mergeCell ref="I267:I272"/>
     <mergeCell ref="D42:D55"/>
-    <mergeCell ref="A258:A269"/>
-    <mergeCell ref="I246:I250"/>
     <mergeCell ref="I157:I163"/>
     <mergeCell ref="D6:D8"/>
+    <mergeCell ref="A111:A117"/>
+    <mergeCell ref="C154:C156"/>
     <mergeCell ref="I89:I91"/>
-    <mergeCell ref="C154:C156"/>
-    <mergeCell ref="C202:C207"/>
-    <mergeCell ref="A111:A117"/>
     <mergeCell ref="C92:C96"/>
     <mergeCell ref="I125:I136"/>
     <mergeCell ref="D62:D65"/>
-    <mergeCell ref="B212:B233"/>
     <mergeCell ref="A176:A182"/>
+    <mergeCell ref="D197:D204"/>
     <mergeCell ref="D146:D153"/>
     <mergeCell ref="A31:A65"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="C62:C65"/>
     <mergeCell ref="A121:A124"/>
+    <mergeCell ref="A264:A275"/>
+    <mergeCell ref="C251:C255"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="C164:C170"/>
     <mergeCell ref="I85:I88"/>
-    <mergeCell ref="D255:D257"/>
+    <mergeCell ref="I256:I259"/>
     <mergeCell ref="C85:C88"/>
     <mergeCell ref="I6:I8"/>
     <mergeCell ref="C76:C84"/>
+    <mergeCell ref="I197:I204"/>
+    <mergeCell ref="B205:B211"/>
+    <mergeCell ref="B183:B189"/>
     <mergeCell ref="B2:B16"/>
-    <mergeCell ref="C261:C266"/>
+    <mergeCell ref="D205:D211"/>
+    <mergeCell ref="C264:C266"/>
     <mergeCell ref="A125:A142"/>
     <mergeCell ref="I35:I41"/>
     <mergeCell ref="D176:D182"/>
+    <mergeCell ref="D115:D117"/>
     <mergeCell ref="D66:D69"/>
-    <mergeCell ref="D115:D117"/>
-    <mergeCell ref="I183:I187"/>
-    <mergeCell ref="D258:D260"/>
     <mergeCell ref="D121:D124"/>
     <mergeCell ref="D108:D110"/>
     <mergeCell ref="I111:I114"/>
-    <mergeCell ref="I258:I260"/>
-    <mergeCell ref="C255:C257"/>
     <mergeCell ref="C137:C141"/>
+    <mergeCell ref="I260:I263"/>
+    <mergeCell ref="C260:C263"/>
     <mergeCell ref="D76:D84"/>
     <mergeCell ref="C176:C182"/>
     <mergeCell ref="I42:I55"/>
+    <mergeCell ref="I205:I211"/>
+    <mergeCell ref="C239:C250"/>
     <mergeCell ref="B118:B120"/>
-    <mergeCell ref="A195:A201"/>
-    <mergeCell ref="B208:B211"/>
-    <mergeCell ref="D208:D211"/>
-    <mergeCell ref="B251:B257"/>
-    <mergeCell ref="I176:I182"/>
     <mergeCell ref="I66:I69"/>
     <mergeCell ref="D92:D96"/>
+    <mergeCell ref="I176:I182"/>
     <mergeCell ref="I121:I124"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="I137:I141"/>
     <mergeCell ref="I108:I110"/>
-    <mergeCell ref="I137:I141"/>
-    <mergeCell ref="C6:C8"/>
     <mergeCell ref="C146:C153"/>
     <mergeCell ref="D97:D102"/>
     <mergeCell ref="I164:I170"/>
     <mergeCell ref="I146:I153"/>
     <mergeCell ref="A118:A120"/>
-    <mergeCell ref="B258:B269"/>
-    <mergeCell ref="B195:B201"/>
     <mergeCell ref="D85:D88"/>
     <mergeCell ref="B31:B65"/>
-    <mergeCell ref="A234:A245"/>
-    <mergeCell ref="I202:I207"/>
+    <mergeCell ref="A205:A211"/>
+    <mergeCell ref="C183:C189"/>
+    <mergeCell ref="A183:A189"/>
+    <mergeCell ref="I92:I96"/>
+    <mergeCell ref="A17:A30"/>
     <mergeCell ref="I17:I30"/>
     <mergeCell ref="D118:D120"/>
-    <mergeCell ref="A17:A30"/>
-    <mergeCell ref="I92:I96"/>
     <mergeCell ref="D12:D16"/>
-    <mergeCell ref="D261:D266"/>
-    <mergeCell ref="A208:A211"/>
+    <mergeCell ref="D264:D266"/>
+    <mergeCell ref="D273:D275"/>
+    <mergeCell ref="I212:I215"/>
     <mergeCell ref="I97:I102"/>
-    <mergeCell ref="C258:C260"/>
     <mergeCell ref="C121:C124"/>
+    <mergeCell ref="A256:A263"/>
     <mergeCell ref="C31:C34"/>
     <mergeCell ref="C89:C91"/>
-    <mergeCell ref="B188:B194"/>
-    <mergeCell ref="D188:D194"/>
-    <mergeCell ref="I267:I269"/>
     <mergeCell ref="C118:C120"/>
+    <mergeCell ref="B190:B196"/>
+    <mergeCell ref="D190:D196"/>
     <mergeCell ref="D2:D4"/>
-    <mergeCell ref="B234:B245"/>
-    <mergeCell ref="D234:D245"/>
+    <mergeCell ref="D260:D263"/>
+    <mergeCell ref="D183:D189"/>
     <mergeCell ref="I118:I120"/>
+    <mergeCell ref="B239:B250"/>
     <mergeCell ref="I115:I117"/>
     <mergeCell ref="I12:I16"/>
-    <mergeCell ref="I261:I266"/>
+    <mergeCell ref="I264:I266"/>
     <mergeCell ref="I76:I84"/>
+    <mergeCell ref="C205:C211"/>
+    <mergeCell ref="I273:I275"/>
     <mergeCell ref="C115:C117"/>
-    <mergeCell ref="I251:I254"/>
-    <mergeCell ref="A251:A257"/>
     <mergeCell ref="C35:C41"/>
-    <mergeCell ref="I212:I233"/>
-    <mergeCell ref="B202:B207"/>
-    <mergeCell ref="A188:A194"/>
-    <mergeCell ref="C188:C194"/>
+    <mergeCell ref="C256:C259"/>
+    <mergeCell ref="A197:A204"/>
     <mergeCell ref="C97:C102"/>
-    <mergeCell ref="I255:I257"/>
+    <mergeCell ref="B251:B255"/>
+    <mergeCell ref="C197:C204"/>
+    <mergeCell ref="D251:D255"/>
+    <mergeCell ref="D216:D238"/>
     <mergeCell ref="I62:I65"/>
+    <mergeCell ref="A216:A238"/>
+    <mergeCell ref="D212:D215"/>
+    <mergeCell ref="B89:B110"/>
     <mergeCell ref="I2:I4"/>
-    <mergeCell ref="B89:B110"/>
     <mergeCell ref="D9:D10"/>
-    <mergeCell ref="D267:D269"/>
+    <mergeCell ref="I183:I189"/>
+    <mergeCell ref="I239:I250"/>
+    <mergeCell ref="A239:A250"/>
     <mergeCell ref="C70:C75"/>
-    <mergeCell ref="B246:B250"/>
     <mergeCell ref="I171:I175"/>
+    <mergeCell ref="B256:B263"/>
     <mergeCell ref="D103:D107"/>
-    <mergeCell ref="B183:B187"/>
+    <mergeCell ref="I216:I238"/>
     <mergeCell ref="D89:D91"/>
     <mergeCell ref="C125:C136"/>
     <mergeCell ref="D70:D75"/>
+    <mergeCell ref="A190:A196"/>
     <mergeCell ref="C108:C110"/>
-    <mergeCell ref="C234:C245"/>
+    <mergeCell ref="C190:C196"/>
     <mergeCell ref="D56:D61"/>
     <mergeCell ref="A66:A88"/>
-    <mergeCell ref="I234:I245"/>
-    <mergeCell ref="C208:C211"/>
-    <mergeCell ref="D251:D254"/>
-    <mergeCell ref="D195:D201"/>
+    <mergeCell ref="C111:C114"/>
+    <mergeCell ref="D256:D259"/>
     <mergeCell ref="I103:I107"/>
-    <mergeCell ref="I208:I211"/>
-    <mergeCell ref="A202:A207"/>
+    <mergeCell ref="A251:A255"/>
+    <mergeCell ref="B197:B204"/>
+    <mergeCell ref="D171:D175"/>
     <mergeCell ref="C17:C30"/>
     <mergeCell ref="D31:D34"/>
-    <mergeCell ref="D171:D175"/>
     <mergeCell ref="D143:D145"/>
+    <mergeCell ref="A212:A215"/>
+    <mergeCell ref="C212:C215"/>
     <mergeCell ref="A89:A110"/>
     <mergeCell ref="C9:C10"/>
-    <mergeCell ref="C267:C269"/>
     <mergeCell ref="B66:B88"/>
     <mergeCell ref="D111:D114"/>
-    <mergeCell ref="D212:D233"/>
-    <mergeCell ref="C195:C201"/>
+    <mergeCell ref="B264:B275"/>
     <mergeCell ref="B143:B175"/>
+    <mergeCell ref="D239:D250"/>
     <mergeCell ref="B17:B30"/>
     <mergeCell ref="A143:A175"/>
-    <mergeCell ref="I195:I201"/>
-    <mergeCell ref="D202:D207"/>
+    <mergeCell ref="I251:I255"/>
+    <mergeCell ref="D125:D136"/>
     <mergeCell ref="D154:D156"/>
-    <mergeCell ref="A246:A250"/>
-    <mergeCell ref="C246:C250"/>
-    <mergeCell ref="D125:D136"/>
-    <mergeCell ref="I188:I194"/>
+    <mergeCell ref="C103:C107"/>
     <mergeCell ref="I31:I34"/>
-    <mergeCell ref="C103:C107"/>
-    <mergeCell ref="A183:A187"/>
-    <mergeCell ref="C183:C187"/>
     <mergeCell ref="C12:C16"/>
-    <mergeCell ref="C111:C114"/>
+    <mergeCell ref="C273:C275"/>
+    <mergeCell ref="I190:I196"/>
+    <mergeCell ref="C62:C65"/>
     <mergeCell ref="B176:B182"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I275"/>
+  <dimension ref="A1:I272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="D143" s="3" t="inlineStr">
         <is>
-          <t>ユーザー情報取得API(/api/user)</t>
+          <t>AP01:書籍一覧API(GET /api/v1/books)</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
@@ -4981,22 +4981,23 @@
       </c>
       <c r="F143" s="3" t="inlineStr">
         <is>
-          <t>未認証でアクセスすると401が返る</t>
+          <t>認証なしでもアクセスでき、書籍一覧が返る</t>
         </is>
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>1.トークンやセッションを持たない状態でGET /api/userにアクセスする</t>
+          <t>1.書籍を複数用意する
+2.認証情報を付与せずGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H143" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
+          <t>200が返り、data・links・metaを含むJSONが返る</t>
         </is>
       </c>
       <c r="I143" s="3" t="inlineStr">
         <is>
-          <t>tests/Feature/PublicApi/UserApiTest.php</t>
+          <t>tests/Feature/PublicApi/BookApiIndexTest.php</t>
         </is>
       </c>
     </row>
@@ -5012,18 +5013,18 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>有効なSanctumトークンでアクセスするとログインユーザーの情報が返る</t>
+          <t>各書籍にジャンル・平均評価・レビュー件数が含まれる</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーのpersonal access tokenを発行する
-2.そのトークンをBearerヘッダーに付与してGET /api/userにアクセスする</t>
+          <t>1.ジャンルと、評価4・5のレビューを持つ書籍を用意する
+2.GET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>200が返り、該当ユーザーのid・name・emailを含むJSONが返る</t>
+          <t>dataの各書籍にgenres(id・name)、average_rating(4.5)、review_count(2)が含まれ、reviews(レビュー本文)は含まれない</t>
         </is>
       </c>
       <c r="I144" s="4" t="n"/>
@@ -5031,8 +5032,8 @@
     <row r="145">
       <c r="A145" s="4" t="n"/>
       <c r="B145" s="4" t="n"/>
-      <c r="C145" s="5" t="n"/>
-      <c r="D145" s="5" t="n"/>
+      <c r="C145" s="4" t="n"/>
+      <c r="D145" s="4" t="n"/>
       <c r="E145" s="3" t="inlineStr">
         <is>
           <t>10-1-3</t>
@@ -5040,60 +5041,49 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>レスポンスにパスワードなど非公開情報が含まれない</t>
+          <t>レビューが無い書籍はaverage_ratingがnull、review_countが0になる</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>1.有効なトークンでGET /api/userにアクセスする</t>
+          <t>1.レビューが1件もない書籍を用意する
+2.GET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>レスポンスJSONにpassword・remember_tokenが含まれない</t>
-        </is>
-      </c>
-      <c r="I145" s="5" t="n"/>
+          <t>その書籍のaverage_ratingがnull、review_countが0で返る</t>
+        </is>
+      </c>
+      <c r="I145" s="4" t="n"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="n"/>
       <c r="B146" s="4" t="n"/>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>10-2</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>書籍一覧取得API(GET /api/v1/books)</t>
-        </is>
-      </c>
+      <c r="C146" s="4" t="n"/>
+      <c r="D146" s="4" t="n"/>
       <c r="E146" s="3" t="inlineStr">
         <is>
-          <t>10-2-1</t>
+          <t>10-1-4</t>
         </is>
       </c>
       <c r="F146" s="3" t="inlineStr">
         <is>
-          <t>認証なしでもアクセスでき、書籍一覧が返る</t>
+          <t>新しい順(登録日時の降順、同一なら idの降順)で返る</t>
         </is>
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>1.書籍を複数用意する
-2.認証情報を付与せずGET /api/v1/booksにアクセスする</t>
+          <t>1.登録日時の異なる書籍を複数用意する
+2.GET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H146" s="3" t="inlineStr">
         <is>
-          <t>200が返り、data・links・metaを含むJSONが返る</t>
-        </is>
-      </c>
-      <c r="I146" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiIndexTest.php</t>
-        </is>
-      </c>
+          <t>新しく登録された書籍から順に返る</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="n"/>
@@ -5102,23 +5092,23 @@
       <c r="D147" s="4" t="n"/>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>10-2-2</t>
+          <t>10-1-5</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
         <is>
-          <t>各書籍にジャンル・平均評価・レビュー件数が含まれる</t>
+          <t>keywordでタイトル・著者名の部分一致検索ができる</t>
         </is>
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンルと、評価4・5のレビューを持つ書籍を用意する
-2.GET /api/v1/booksにアクセスする</t>
+          <t>1.タイトルにキーワードを含む書籍、著者名にキーワードを含む書籍、含まない書籍を用意する
+2.keywordを指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>dataの各書籍にgenres(id・name)、average_rating(4.5)、review_count(2)が含まれ、reviews(レビュー本文)は含まれない</t>
+          <t>タイトルまたは著者名にキーワードを含む書籍のみが返る</t>
         </is>
       </c>
       <c r="I147" s="4" t="n"/>
@@ -5130,23 +5120,23 @@
       <c r="D148" s="4" t="n"/>
       <c r="E148" s="3" t="inlineStr">
         <is>
-          <t>10-2-3</t>
+          <t>10-1-6</t>
         </is>
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>レビューが無い書籍はaverage_ratingがnull、review_countが0になる</t>
+          <t>genreでジャンルIDによる絞り込みができる</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>1.レビューが1件もない書籍を用意する
-2.GET /api/v1/booksにアクセスする</t>
+          <t>1.異なるジャンルの書籍を用意する
+2.genreにジャンルIDを指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
         <is>
-          <t>その書籍のaverage_ratingがnull、review_countが0で返る</t>
+          <t>指定したジャンルに属する書籍のみが返る</t>
         </is>
       </c>
       <c r="I148" s="4" t="n"/>
@@ -5158,23 +5148,23 @@
       <c r="D149" s="4" t="n"/>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>10-2-4</t>
+          <t>10-1-7</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>新しい順(登録日時の降順、同一なら idの降順)で返る</t>
+          <t>pageでページを移動できる(1ページ10件固定)</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>1.登録日時の異なる書籍を複数用意する
-2.GET /api/v1/booksにアクセスする</t>
+          <t>1.11件の書籍を用意する
+2.pageを指定せずに、およびpage=2を指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>新しく登録された書籍から順に返る</t>
+          <t>pageなしでは1ページ目の10件、page=2では残りの1件が返り、meta・linksにページ情報が反映される</t>
         </is>
       </c>
       <c r="I149" s="4" t="n"/>
@@ -5182,58 +5172,69 @@
     <row r="150">
       <c r="A150" s="4" t="n"/>
       <c r="B150" s="4" t="n"/>
-      <c r="C150" s="4" t="n"/>
-      <c r="D150" s="4" t="n"/>
+      <c r="C150" s="5" t="n"/>
+      <c r="D150" s="5" t="n"/>
       <c r="E150" s="3" t="inlineStr">
         <is>
-          <t>10-2-5</t>
+          <t>10-1-8</t>
         </is>
       </c>
       <c r="F150" s="3" t="inlineStr">
         <is>
-          <t>keywordでタイトル・著者名の部分一致検索ができる</t>
+          <t>不正なクエリパラメータを指定すると422が返る</t>
         </is>
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>1.タイトルにキーワードを含む書籍、著者名にキーワードを含む書籍、含まない書籍を用意する
-2.keywordを指定してGET /api/v1/booksにアクセスする</t>
+          <t>1.genreに存在しないID、pageに0をそれぞれ指定してGET /api/v1/booksにアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
         <is>
-          <t>タイトルまたは著者名にキーワードを含む書籍のみが返る</t>
-        </is>
-      </c>
-      <c r="I150" s="4" t="n"/>
+          <t>422が返り、「指定されたジャンルは存在しません」「ページ番号は1以上の値で指定してください」が返る</t>
+        </is>
+      </c>
+      <c r="I150" s="5" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n"/>
       <c r="B151" s="4" t="n"/>
-      <c r="C151" s="4" t="n"/>
-      <c r="D151" s="4" t="n"/>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>10-2</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>AP02:書籍詳細API(GET /api/v1/books/{book})</t>
+        </is>
+      </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>10-2-6</t>
+          <t>10-2-1</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>genreでジャンルIDによる絞り込みができる</t>
+          <t>認証なしでもアクセスでき、書籍の詳細が返る</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>1.異なるジャンルの書籍を用意する
-2.genreにジャンルIDを指定してGET /api/v1/booksにアクセスする</t>
+          <t>1.ジャンルとレビューを持つ書籍を用意する
+2.認証情報を付与せずGET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>指定したジャンルに属する書籍のみが返る</t>
-        </is>
-      </c>
-      <c r="I151" s="4" t="n"/>
+          <t>200が返り、書籍情報・genres・average_rating・review_countを含むJSONが返る</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiShowTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n"/>
@@ -5242,23 +5243,23 @@
       <c r="D152" s="4" t="n"/>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>10-2-7</t>
+          <t>10-2-2</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>pageでページを移動できる(1ページ10件固定)</t>
+          <t>レビュー(投稿者名・評価・コメント・投稿日時)が新しい順に含まれる</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>1.11件の書籍を用意する
-2.pageを指定せずに、およびpage=2を指定してGET /api/v1/booksにアクセスする</t>
+          <t>1.異なる日時に投稿された複数のレビューを持つ書籍を用意する
+2.GET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>pageなしでは1ページ目の10件、page=2では残りの1件が返り、meta・linksにページ情報が反映される</t>
+          <t>reviewsにuser_name・rating・comment・created_atが含まれ、投稿日時の新しい順に並ぶ</t>
         </is>
       </c>
       <c r="I152" s="4" t="n"/>
@@ -5270,22 +5271,22 @@
       <c r="D153" s="5" t="n"/>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>10-2-8</t>
+          <t>10-2-3</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>不正なクエリパラメータを指定すると422が返る</t>
+          <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>1.genreに存在しないID、pageに0をそれぞれ指定してGET /api/v1/booksにアクセスする(Accept: application/json)</t>
+          <t>1.存在しない書籍IDでGET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「指定されたジャンルは存在しません」「ページ番号は1以上の値で指定してください」が返る</t>
+          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
         </is>
       </c>
       <c r="I153" s="5" t="n"/>
@@ -5300,7 +5301,7 @@
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>書籍詳細取得API(GET /api/v1/books/{book})</t>
+          <t>AP03:書籍登録API(POST /api/v1/books)</t>
         </is>
       </c>
       <c r="E154" s="3" t="inlineStr">
@@ -5310,23 +5311,22 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>認証なしでもアクセスでき、書籍の詳細が返る</t>
+          <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンルとレビューを持つ書籍を用意する
-2.認証情報を付与せずGET /api/v1/books/{book}にアクセスする</t>
+          <t>1.認証情報を付与せずPOST /api/v1/booksにアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>200が返り、書籍情報・genres・average_rating・review_countを含むJSONが返る</t>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録されない</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>tests/Feature/PublicApi/BookApiShowTest.php</t>
+          <t>tests/Feature/PublicApi/BookApiStoreTest.php</t>
         </is>
       </c>
     </row>
@@ -5342,18 +5342,18 @@
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>レビュー(投稿者名・評価・コメント・投稿日時)が新しい順に含まれる</t>
+          <t>有効なトークンで書籍を登録できる</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>1.異なる日時に投稿された複数のレビューを持つ書籍を用意する
-2.GET /api/v1/books/{book}にアクセスする</t>
+          <t>1.ユーザーのトークンを発行する
+2.必要項目を指定し、Bearerトークンを付与してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>reviewsにuser_name・rating・comment・created_atが含まれ、投稿日時の新しい順に並ぶ</t>
+          <t>201が返り、登録内容がJSONで返る。書籍がDBに保存される</t>
         </is>
       </c>
       <c r="I155" s="4" t="n"/>
@@ -5361,8 +5361,8 @@
     <row r="156">
       <c r="A156" s="4" t="n"/>
       <c r="B156" s="4" t="n"/>
-      <c r="C156" s="5" t="n"/>
-      <c r="D156" s="5" t="n"/>
+      <c r="C156" s="4" t="n"/>
+      <c r="D156" s="4" t="n"/>
       <c r="E156" s="3" t="inlineStr">
         <is>
           <t>10-3-3</t>
@@ -5370,59 +5370,47 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>存在しないIDを指定すると404が返る</t>
+          <t>登録者(user_id)は、リクエストの値ではなく認証ユーザーになる</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>1.存在しない書籍IDでGET /api/v1/books/{book}にアクセスする</t>
+          <t>1.他のユーザーのIDをuser_idに含めて、トークンを付与しPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
-        </is>
-      </c>
-      <c r="I156" s="5" t="n"/>
+          <t>登録された書籍のuser_idは、トークンの持ち主(認証ユーザー)のIDになる</t>
+        </is>
+      </c>
+      <c r="I156" s="4" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n"/>
       <c r="B157" s="4" t="n"/>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>10-4</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>書籍登録API(POST /api/v1/books)</t>
-        </is>
-      </c>
+      <c r="C157" s="4" t="n"/>
+      <c r="D157" s="4" t="n"/>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>10-4-1</t>
+          <t>10-3-4</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>認証なしでアクセスすると401が返る</t>
+          <t>選択したジャンルが書籍に紐づけられる</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>1.認証情報を付与せずPOST /api/v1/booksにアクセスする(Accept: application/json)</t>
+          <t>1.複数のジャンルIDをgenresに指定してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録されない</t>
-        </is>
-      </c>
-      <c r="I157" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiStoreTest.php</t>
-        </is>
-      </c>
+          <t>中間テーブル(book_genre)に指定したジャンルが保存され、レスポンスのgenresにも含まれる</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="n"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="n"/>
@@ -5431,23 +5419,22 @@
       <c r="D158" s="4" t="n"/>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>10-4-2</t>
+          <t>10-3-5</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>有効なトークンで書籍を登録できる</t>
+          <t>必須項目(title・author・genres)が未入力の場合、422が返る</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーのトークンを発行する
-2.必要項目を指定し、Bearerトークンを付与してPOST /api/v1/booksにアクセスする</t>
+          <t>1.title・author・genresを指定せずにPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>201が返り、登録内容がJSONで返る。書籍がDBに保存される</t>
+          <t>422が返り、「書籍タイトルを入力してください」「著者名を入力してください」「ジャンルを1つ以上選択してください」が返る</t>
         </is>
       </c>
       <c r="I158" s="4" t="n"/>
@@ -5459,22 +5446,23 @@
       <c r="D159" s="4" t="n"/>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>10-4-3</t>
+          <t>10-3-6</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>登録者(user_id)は、リクエストの値ではなく認証ユーザーになる</t>
+          <t>ISBNが13桁の数字でない、または登録済みの場合、422が返る</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>1.他のユーザーのIDをuser_idに含めて、トークンを付与しPOST /api/v1/booksにアクセスする</t>
+          <t>1.ISBNに13桁でない値を指定してPOST /api/v1/booksにアクセスする
+2.登録済みのISBNを指定して同様にアクセスする</t>
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>登録された書籍のuser_idは、トークンの持ち主(認証ユーザー)のIDになる</t>
+          <t>422が返り、「ISBNは13桁の数字で入力してください」「このISBNはすでに登録されています」が返る</t>
         </is>
       </c>
       <c r="I159" s="4" t="n"/>
@@ -5482,56 +5470,68 @@
     <row r="160">
       <c r="A160" s="4" t="n"/>
       <c r="B160" s="4" t="n"/>
-      <c r="C160" s="4" t="n"/>
-      <c r="D160" s="4" t="n"/>
+      <c r="C160" s="5" t="n"/>
+      <c r="D160" s="5" t="n"/>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>10-4-4</t>
+          <t>10-3-7</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>選択したジャンルが書籍に紐づけられる</t>
+          <t>存在しないジャンルIDを指定すると422が返る</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>1.複数のジャンルIDをgenresに指定してPOST /api/v1/booksにアクセスする</t>
+          <t>1.genresに存在しないジャンルIDを指定してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>中間テーブル(book_genre)に指定したジャンルが保存され、レスポンスのgenresにも含まれる</t>
-        </is>
-      </c>
-      <c r="I160" s="4" t="n"/>
+          <t>422が返り、「選択されたジャンルは存在しません」が返る</t>
+        </is>
+      </c>
+      <c r="I160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n"/>
       <c r="B161" s="4" t="n"/>
-      <c r="C161" s="4" t="n"/>
-      <c r="D161" s="4" t="n"/>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>10-4</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>AP04:書籍更新API(PUT /api/v1/books/{book})</t>
+        </is>
+      </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>10-4-5</t>
+          <t>10-4-1</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>必須項目(title・author・genres)が未入力の場合、422が返る</t>
+          <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>1.title・author・genresを指定せずにPOST /api/v1/booksにアクセスする</t>
+          <t>1.認証情報を付与せずPUT /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「書籍タイトルを入力してください」「著者名を入力してください」「ジャンルを1つ以上選択してください」が返る</t>
-        </is>
-      </c>
-      <c r="I161" s="4" t="n"/>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I161" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiUpdateTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="n"/>
@@ -5540,23 +5540,23 @@
       <c r="D162" s="4" t="n"/>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>10-4-6</t>
+          <t>10-4-2</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>ISBNが13桁の数字でない、または登録済みの場合、422が返る</t>
+          <t>自分が登録した書籍を更新できる</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>1.ISBNに13桁でない値を指定してPOST /api/v1/booksにアクセスする
-2.登録済みのISBNを指定して同様にアクセスする</t>
+          <t>1.ユーザーが登録した書籍を用意する
+2.そのユーザーのトークンを付与し、変更内容・ジャンルを指定してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「ISBNは13桁の数字で入力してください」「このISBNはすでに登録されています」が返る</t>
+          <t>200が返り、更新後の内容がJSONで返る。DBの書籍情報とジャンルの紐づけが更新される</t>
         </is>
       </c>
       <c r="I162" s="4" t="n"/>
@@ -5564,68 +5564,58 @@
     <row r="163">
       <c r="A163" s="4" t="n"/>
       <c r="B163" s="4" t="n"/>
-      <c r="C163" s="5" t="n"/>
-      <c r="D163" s="5" t="n"/>
+      <c r="C163" s="4" t="n"/>
+      <c r="D163" s="4" t="n"/>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>10-4-7</t>
+          <t>10-4-3</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>存在しないジャンルIDを指定すると422が返る</t>
+          <t>自分の書籍のISBNを変更せずに更新しても、ISBNの重複エラーにならない</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>1.genresに存在しないジャンルIDを指定してPOST /api/v1/booksにアクセスする</t>
+          <t>1.ユーザーが登録した書籍(ISBNあり)を用意する
+2.ISBNを変えずに他の項目を変更してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「選択されたジャンルは存在しません」が返る</t>
-        </is>
-      </c>
-      <c r="I163" s="5" t="n"/>
+          <t>200が返り、更新できる</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="n"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n"/>
       <c r="B164" s="4" t="n"/>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>10-5</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>書籍更新API(PUT /api/v1/books/{book})</t>
-        </is>
-      </c>
+      <c r="C164" s="4" t="n"/>
+      <c r="D164" s="4" t="n"/>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>10-5-1</t>
+          <t>10-4-4</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>認証なしでアクセスすると401が返る</t>
+          <t>他のユーザーが登録した書籍は更新できない</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>1.認証情報を付与せずPUT /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
+          <t>1.他のユーザーが登録した書籍を用意する
+2.別のユーザーのトークンを付与してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は更新されない</t>
-        </is>
-      </c>
-      <c r="I164" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiUpdateTest.php</t>
-        </is>
-      </c>
+          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="n"/>
@@ -5634,23 +5624,22 @@
       <c r="D165" s="4" t="n"/>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>10-5-2</t>
+          <t>10-4-5</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>自分が登録した書籍を更新できる</t>
+          <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーが登録した書籍を用意する
-2.そのユーザーのトークンを付与し、変更内容・ジャンルを指定してPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.トークンを付与し、存在しない書籍IDでPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>200が返り、更新後の内容がJSONで返る。DBの書籍情報とジャンルの紐づけが更新される</t>
+          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
         </is>
       </c>
       <c r="I165" s="4" t="n"/>
@@ -5662,23 +5651,22 @@
       <c r="D166" s="4" t="n"/>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>10-5-3</t>
+          <t>10-4-6</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>自分の書籍のISBNを変更せずに更新しても、ISBNの重複エラーにならない</t>
+          <t>入力内容が不正な場合、422が返る</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーが登録した書籍(ISBNあり)を用意する
-2.ISBNを変えずに他の項目を変更してPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.自分の書籍に対し、titleを空にしてPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>200が返り、更新できる</t>
+          <t>422が返り、「書籍タイトルを入力してください」が返る。書籍は更新されない</t>
         </is>
       </c>
       <c r="I166" s="4" t="n"/>
@@ -5686,57 +5674,69 @@
     <row r="167">
       <c r="A167" s="4" t="n"/>
       <c r="B167" s="4" t="n"/>
-      <c r="C167" s="4" t="n"/>
-      <c r="D167" s="4" t="n"/>
+      <c r="C167" s="5" t="n"/>
+      <c r="D167" s="5" t="n"/>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>10-5-4</t>
+          <t>10-4-7</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>他のユーザーが登録した書籍は更新できない</t>
+          <t>他のユーザーが登録した書籍に対して不正な入力で更新しようとしても、422ではなく403が返る</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
           <t>1.他のユーザーが登録した書籍を用意する
-2.別のユーザーのトークンを付与してPUT /api/v1/books/{book}にアクセスする</t>
+2.別のユーザーのトークンを付与し、タイトルを空にするなど不正な内容でPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は更新されない</t>
-        </is>
-      </c>
-      <c r="I167" s="4" t="n"/>
+          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る（入力チェックより先に権限が判定される）。書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I167" s="5" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="n"/>
       <c r="B168" s="4" t="n"/>
-      <c r="C168" s="4" t="n"/>
-      <c r="D168" s="4" t="n"/>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>10-5</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>AP05:書籍削除API(DELETE /api/v1/books/{book})</t>
+        </is>
+      </c>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>10-5-5</t>
+          <t>10-5-1</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>存在しないIDを指定すると404が返る</t>
+          <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>1.トークンを付与し、存在しない書籍IDでPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.認証情報を付与せずDELETE /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
-        </is>
-      </c>
-      <c r="I168" s="4" t="n"/>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は削除されない</t>
+        </is>
+      </c>
+      <c r="I168" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiDestroyTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n"/>
@@ -5745,22 +5745,23 @@
       <c r="D169" s="4" t="n"/>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>10-5-6</t>
+          <t>10-5-2</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>入力内容が不正な場合、422が返る</t>
+          <t>自分が登録した書籍を削除できる</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>1.自分の書籍に対し、titleを空にしてPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.ユーザーが登録した書籍を用意する
+2.そのユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「書籍タイトルを入力してください」が返る。書籍は更新されない</t>
+          <t>204が返り(レスポンスボディなし)、書籍がDBから削除される</t>
         </is>
       </c>
       <c r="I169" s="4" t="n"/>
@@ -5768,228 +5769,216 @@
     <row r="170">
       <c r="A170" s="4" t="n"/>
       <c r="B170" s="4" t="n"/>
-      <c r="C170" s="5" t="n"/>
-      <c r="D170" s="5" t="n"/>
+      <c r="C170" s="4" t="n"/>
+      <c r="D170" s="4" t="n"/>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>10-5-7</t>
+          <t>10-5-3</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>他のユーザーが登録した書籍に対して不正な入力で更新しようとしても、422ではなく403が返る</t>
+          <t>書籍を削除すると、関連するデータも一緒に削除される</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>1.他のユーザーが登録した書籍を用意する
-2.別のユーザーのトークンを付与し、タイトルを空にするなど不正な内容でPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.ジャンルの紐づけ・レビュー・お気に入り・レビューへのいいねを持つ書籍を用意する
+2.所有者のトークンでDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る（入力チェックより先に権限が判定される）。書籍は更新されない</t>
-        </is>
-      </c>
-      <c r="I170" s="5" t="n"/>
+          <t>book_genre・reviews・favorites・review_likesの該当データも削除される</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
       <c r="B171" s="4" t="n"/>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>10-6</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>書籍削除API(DELETE /api/v1/books/{book})</t>
-        </is>
-      </c>
+      <c r="C171" s="4" t="n"/>
+      <c r="D171" s="4" t="n"/>
       <c r="E171" s="3" t="inlineStr">
         <is>
-          <t>10-6-1</t>
+          <t>10-5-4</t>
         </is>
       </c>
       <c r="F171" s="3" t="inlineStr">
         <is>
-          <t>認証なしでアクセスすると401が返る</t>
+          <t>他のユーザーが登録した書籍は削除できない</t>
         </is>
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>1.認証情報を付与せずDELETE /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
+          <t>1.他のユーザーが登録した書籍を用意する
+2.別のユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H171" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は削除されない</t>
-        </is>
-      </c>
-      <c r="I171" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiDestroyTest.php</t>
-        </is>
-      </c>
+          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は削除されない</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="4" t="n"/>
-      <c r="B172" s="4" t="n"/>
-      <c r="C172" s="4" t="n"/>
-      <c r="D172" s="4" t="n"/>
+      <c r="A172" s="5" t="n"/>
+      <c r="B172" s="5" t="n"/>
+      <c r="C172" s="5" t="n"/>
+      <c r="D172" s="5" t="n"/>
       <c r="E172" s="3" t="inlineStr">
         <is>
-          <t>10-6-2</t>
+          <t>10-5-5</t>
         </is>
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>自分が登録した書籍を削除できる</t>
+          <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーが登録した書籍を用意する
-2.そのユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
+          <t>1.トークンを付与し、存在しない書籍IDでDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H172" s="3" t="inlineStr">
         <is>
-          <t>204が返り(レスポンスボディなし)、書籍がDBから削除される</t>
-        </is>
-      </c>
-      <c r="I172" s="4" t="n"/>
+          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
+        </is>
+      </c>
+      <c r="I172" s="5" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="4" t="n"/>
-      <c r="B173" s="4" t="n"/>
-      <c r="C173" s="4" t="n"/>
-      <c r="D173" s="4" t="n"/>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>10-6-3</t>
-        </is>
-      </c>
-      <c r="F173" s="3" t="inlineStr">
-        <is>
-          <t>書籍を削除すると、関連するデータも一緒に削除される</t>
-        </is>
-      </c>
-      <c r="G173" s="3" t="inlineStr">
-        <is>
-          <t>1.ジャンルの紐づけ・レビュー・お気に入り・レビューへのいいねを持つ書籍を用意する
-2.所有者のトークンでDELETE /api/v1/books/{book}にアクセスする</t>
-        </is>
-      </c>
-      <c r="H173" s="3" t="inlineStr">
-        <is>
-          <t>book_genre・reviews・favorites・review_likesの該当データも削除される</t>
-        </is>
-      </c>
-      <c r="I173" s="4" t="n"/>
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B173" s="7" t="inlineStr">
+        <is>
+          <t>検索・フィルタ</t>
+        </is>
+      </c>
+      <c r="C173" s="7" t="inlineStr">
+        <is>
+          <t>11-1</t>
+        </is>
+      </c>
+      <c r="D173" s="7" t="inlineStr">
+        <is>
+          <t>書籍のキーワード検索・ジャンル絞り込み</t>
+        </is>
+      </c>
+      <c r="E173" s="7" t="inlineStr">
+        <is>
+          <t>11-1-1</t>
+        </is>
+      </c>
+      <c r="F173" s="7" t="inlineStr">
+        <is>
+          <t>タイトルにキーワードを含む書籍が検索結果に表示される</t>
+        </is>
+      </c>
+      <c r="G173" s="7" t="inlineStr">
+        <is>
+          <t>1.タイトルにキーワードを含む書籍を用意する
+2.書籍一覧ページでkeywordにそのキーワードを指定して検索する</t>
+        </is>
+      </c>
+      <c r="H173" s="7" t="inlineStr">
+        <is>
+          <t>該当する書籍が検索結果に表示される</t>
+        </is>
+      </c>
+      <c r="I173" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Search/SearchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="n"/>
       <c r="B174" s="4" t="n"/>
       <c r="C174" s="4" t="n"/>
       <c r="D174" s="4" t="n"/>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>10-6-4</t>
-        </is>
-      </c>
-      <c r="F174" s="3" t="inlineStr">
-        <is>
-          <t>他のユーザーが登録した書籍は削除できない</t>
-        </is>
-      </c>
-      <c r="G174" s="3" t="inlineStr">
-        <is>
-          <t>1.他のユーザーが登録した書籍を用意する
-2.別のユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
-        </is>
-      </c>
-      <c r="H174" s="3" t="inlineStr">
-        <is>
-          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は削除されない</t>
+      <c r="E174" s="7" t="inlineStr">
+        <is>
+          <t>11-1-2</t>
+        </is>
+      </c>
+      <c r="F174" s="7" t="inlineStr">
+        <is>
+          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
+        </is>
+      </c>
+      <c r="G174" s="7" t="inlineStr">
+        <is>
+          <t>1.著者名にキーワードを含む書籍を用意する
+2.同キーワードで検索する</t>
+        </is>
+      </c>
+      <c r="H174" s="7" t="inlineStr">
+        <is>
+          <t>該当する書籍が検索結果に表示される</t>
         </is>
       </c>
       <c r="I174" s="4" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="n"/>
-      <c r="B175" s="5" t="n"/>
-      <c r="C175" s="5" t="n"/>
-      <c r="D175" s="5" t="n"/>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>10-6-5</t>
-        </is>
-      </c>
-      <c r="F175" s="3" t="inlineStr">
-        <is>
-          <t>存在しないIDを指定すると404が返る</t>
-        </is>
-      </c>
-      <c r="G175" s="3" t="inlineStr">
-        <is>
-          <t>1.トークンを付与し、存在しない書籍IDでDELETE /api/v1/books/{book}にアクセスする</t>
-        </is>
-      </c>
-      <c r="H175" s="3" t="inlineStr">
-        <is>
-          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
-        </is>
-      </c>
-      <c r="I175" s="5" t="n"/>
+      <c r="A175" s="4" t="n"/>
+      <c r="B175" s="4" t="n"/>
+      <c r="C175" s="4" t="n"/>
+      <c r="D175" s="4" t="n"/>
+      <c r="E175" s="7" t="inlineStr">
+        <is>
+          <t>11-1-3</t>
+        </is>
+      </c>
+      <c r="F175" s="7" t="inlineStr">
+        <is>
+          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
+        </is>
+      </c>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>1.キーワードに一致しない書籍を用意する
+2.検索する</t>
+        </is>
+      </c>
+      <c r="H175" s="7" t="inlineStr">
+        <is>
+          <t>その書籍は検索結果に表示されない</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B176" s="7" t="inlineStr">
-        <is>
-          <t>検索・フィルタ</t>
-        </is>
-      </c>
-      <c r="C176" s="7" t="inlineStr">
-        <is>
-          <t>11-1</t>
-        </is>
-      </c>
-      <c r="D176" s="7" t="inlineStr">
-        <is>
-          <t>書籍のキーワード検索・ジャンル絞り込み</t>
-        </is>
-      </c>
+      <c r="A176" s="4" t="n"/>
+      <c r="B176" s="4" t="n"/>
+      <c r="C176" s="4" t="n"/>
+      <c r="D176" s="4" t="n"/>
       <c r="E176" s="7" t="inlineStr">
         <is>
-          <t>11-1-1</t>
+          <t>11-1-4</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>タイトルにキーワードを含む書籍が検索結果に表示される</t>
+          <t>キーワード未入力の場合は全件が表示される</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>1.タイトルにキーワードを含む書籍を用意する
-2.書籍一覧ページでkeywordにそのキーワードを指定して検索する</t>
+          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
         </is>
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
-          <t>該当する書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="I176" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Search/SearchTest.php</t>
-        </is>
-      </c>
+          <t>登録されている全ての書籍が表示される</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="n"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="n"/>
@@ -5998,23 +5987,23 @@
       <c r="D177" s="4" t="n"/>
       <c r="E177" s="7" t="inlineStr">
         <is>
-          <t>11-1-2</t>
+          <t>11-1-5</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
+          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>1.著者名にキーワードを含む書籍を用意する
-2.同キーワードで検索する</t>
+          <t>1.複数ジャンルの書籍を用意する
+2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
         </is>
       </c>
       <c r="H177" s="7" t="inlineStr">
         <is>
-          <t>該当する書籍が検索結果に表示される</t>
+          <t>指定したジャンルに紐づく書籍のみ表示される</t>
         </is>
       </c>
       <c r="I177" s="4" t="n"/>
@@ -6026,81 +6015,100 @@
       <c r="D178" s="4" t="n"/>
       <c r="E178" s="7" t="inlineStr">
         <is>
-          <t>11-1-3</t>
+          <t>11-1-6</t>
         </is>
       </c>
       <c r="F178" s="7" t="inlineStr">
         <is>
-          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
+          <t>キーワード検索とジャンル絞り込みを組み合わせて使用できる</t>
         </is>
       </c>
       <c r="G178" s="7" t="inlineStr">
         <is>
-          <t>1.キーワードに一致しない書籍を用意する
-2.検索する</t>
+          <t>1.keywordとgenreの両方を指定して一覧を開く</t>
         </is>
       </c>
       <c r="H178" s="7" t="inlineStr">
         <is>
-          <t>その書籍は検索結果に表示されない</t>
+          <t>キーワードとジャンルの両方の条件に一致する書籍のみ表示される</t>
         </is>
       </c>
       <c r="I178" s="4" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="4" t="n"/>
-      <c r="B179" s="4" t="n"/>
-      <c r="C179" s="4" t="n"/>
-      <c r="D179" s="4" t="n"/>
+      <c r="A179" s="5" t="n"/>
+      <c r="B179" s="5" t="n"/>
+      <c r="C179" s="5" t="n"/>
+      <c r="D179" s="5" t="n"/>
       <c r="E179" s="7" t="inlineStr">
         <is>
-          <t>11-1-4</t>
+          <t>11-1-7</t>
         </is>
       </c>
       <c r="F179" s="7" t="inlineStr">
         <is>
-          <t>キーワード未入力の場合は全件が表示される</t>
+          <t>検索結果が0件の場合の表示を確認する</t>
         </is>
       </c>
       <c r="G179" s="7" t="inlineStr">
         <is>
-          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
+          <t>1.どの書籍にも一致しないキーワードで検索する</t>
         </is>
       </c>
       <c r="H179" s="7" t="inlineStr">
         <is>
-          <t>登録されている全ての書籍が表示される</t>
-        </is>
-      </c>
-      <c r="I179" s="4" t="n"/>
+          <t>「条件に一致する書籍が見つかりませんでした。」と表示される</t>
+        </is>
+      </c>
+      <c r="I179" s="5" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="4" t="n"/>
-      <c r="B180" s="4" t="n"/>
-      <c r="C180" s="4" t="n"/>
-      <c r="D180" s="4" t="n"/>
+      <c r="A180" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B180" s="7" t="inlineStr">
+        <is>
+          <t>ソート</t>
+        </is>
+      </c>
+      <c r="C180" s="7" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="D180" s="7" t="inlineStr">
+        <is>
+          <t>書籍一覧の並び替え</t>
+        </is>
+      </c>
       <c r="E180" s="7" t="inlineStr">
         <is>
-          <t>11-1-5</t>
+          <t>12-1-1</t>
         </is>
       </c>
       <c r="F180" s="7" t="inlineStr">
         <is>
-          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
+          <t>並び替え未指定時は新着順(登録が新しい順)で表示される</t>
         </is>
       </c>
       <c r="G180" s="7" t="inlineStr">
         <is>
-          <t>1.複数ジャンルの書籍を用意する
-2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
+          <t>1.複数の書籍を異なる日時で登録する
+2.sortを指定せずに書籍一覧を開く</t>
         </is>
       </c>
       <c r="H180" s="7" t="inlineStr">
         <is>
-          <t>指定したジャンルに紐づく書籍のみ表示される</t>
-        </is>
-      </c>
-      <c r="I180" s="4" t="n"/>
+          <t>登録日時が新しい順に表示される</t>
+        </is>
+      </c>
+      <c r="I180" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Sort/SortTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="n"/>
@@ -6109,100 +6117,82 @@
       <c r="D181" s="4" t="n"/>
       <c r="E181" s="7" t="inlineStr">
         <is>
-          <t>11-1-6</t>
+          <t>12-1-2</t>
         </is>
       </c>
       <c r="F181" s="7" t="inlineStr">
         <is>
-          <t>キーワード検索とジャンル絞り込みを組み合わせて使用できる</t>
+          <t>sort=oldestを指定すると登録が古い順に表示される</t>
         </is>
       </c>
       <c r="G181" s="7" t="inlineStr">
         <is>
-          <t>1.keywordとgenreの両方を指定して一覧を開く</t>
+          <t>1.複数の書籍を異なる日時で登録する
+2.sort=oldestを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H181" s="7" t="inlineStr">
         <is>
-          <t>キーワードとジャンルの両方の条件に一致する書籍のみ表示される</t>
+          <t>登録日時が古い順に表示される</t>
         </is>
       </c>
       <c r="I181" s="4" t="n"/>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="n"/>
-      <c r="B182" s="5" t="n"/>
-      <c r="C182" s="5" t="n"/>
-      <c r="D182" s="5" t="n"/>
+      <c r="A182" s="4" t="n"/>
+      <c r="B182" s="4" t="n"/>
+      <c r="C182" s="4" t="n"/>
+      <c r="D182" s="4" t="n"/>
       <c r="E182" s="7" t="inlineStr">
         <is>
-          <t>11-1-7</t>
+          <t>12-1-3</t>
         </is>
       </c>
       <c r="F182" s="7" t="inlineStr">
         <is>
-          <t>検索結果が0件の場合の表示を確認する</t>
+          <t>sort=titleを指定するとタイトルの昇順で表示される</t>
         </is>
       </c>
       <c r="G182" s="7" t="inlineStr">
         <is>
-          <t>1.どの書籍にも一致しないキーワードで検索する</t>
+          <t>1.複数の書籍を用意する
+2.sort=titleを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H182" s="7" t="inlineStr">
         <is>
-          <t>「条件に一致する書籍が見つかりませんでした。」と表示される</t>
-        </is>
-      </c>
-      <c r="I182" s="5" t="n"/>
+          <t>タイトルの昇順で表示される</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B183" s="7" t="inlineStr">
-        <is>
-          <t>ソート</t>
-        </is>
-      </c>
-      <c r="C183" s="7" t="inlineStr">
-        <is>
-          <t>12-1</t>
-        </is>
-      </c>
-      <c r="D183" s="7" t="inlineStr">
-        <is>
-          <t>書籍一覧の並び替え</t>
-        </is>
-      </c>
+      <c r="A183" s="4" t="n"/>
+      <c r="B183" s="4" t="n"/>
+      <c r="C183" s="4" t="n"/>
+      <c r="D183" s="4" t="n"/>
       <c r="E183" s="7" t="inlineStr">
         <is>
-          <t>12-1-1</t>
+          <t>12-1-4</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>並び替え未指定時は新着順(登録が新しい順)で表示される</t>
+          <t>sort=ratingを指定すると平均評価が高い順に表示される</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>1.複数の書籍を異なる日時で登録する
-2.sortを指定せずに書籍一覧を開く</t>
+          <t>1.平均評価が異なる複数の書籍を用意する
+2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>登録日時が新しい順に表示される</t>
-        </is>
-      </c>
-      <c r="I183" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Sort/SortTest.php</t>
-        </is>
-      </c>
+          <t>平均評価が高い順に表示される</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="n"/>
     </row>
     <row r="184">
       <c r="A184" s="4" t="n"/>
@@ -6211,23 +6201,23 @@
       <c r="D184" s="4" t="n"/>
       <c r="E184" s="7" t="inlineStr">
         <is>
-          <t>12-1-2</t>
+          <t>12-1-5</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>sort=oldestを指定すると登録が古い順に表示される</t>
+          <t>sort=rating指定時、平均評価が同じ書籍は新着順で表示される</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
-          <t>1.複数の書籍を異なる日時で登録する
-2.sort=oldestを指定して書籍一覧を開く</t>
+          <t>1.平均評価が同じ複数の書籍を、異なる登録日時で用意する
+2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>登録日時が古い順に表示される</t>
+          <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
         </is>
       </c>
       <c r="I184" s="4" t="n"/>
@@ -6239,82 +6229,101 @@
       <c r="D185" s="4" t="n"/>
       <c r="E185" s="7" t="inlineStr">
         <is>
-          <t>12-1-3</t>
+          <t>12-1-6</t>
         </is>
       </c>
       <c r="F185" s="7" t="inlineStr">
         <is>
-          <t>sort=titleを指定するとタイトルの昇順で表示される</t>
+          <t>登録日時が同じ書籍は、IDの順に並ぶ(新しい順はIDの降順、古い順はIDの昇順)</t>
         </is>
       </c>
       <c r="G185" s="7" t="inlineStr">
         <is>
-          <t>1.複数の書籍を用意する
-2.sort=titleを指定して書籍一覧を開く</t>
+          <t>1.登録日時が同じ書籍を複数用意する
+2.sort=latest、sort=oldestをそれぞれ指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H185" s="7" t="inlineStr">
         <is>
-          <t>タイトルの昇順で表示される</t>
+          <t>新しい順ではIDの降順(後に登録した順)、古い順ではIDの昇順(先に登録した順)に表示される</t>
         </is>
       </c>
       <c r="I185" s="4" t="n"/>
     </row>
     <row r="186">
-      <c r="A186" s="4" t="n"/>
-      <c r="B186" s="4" t="n"/>
-      <c r="C186" s="4" t="n"/>
-      <c r="D186" s="4" t="n"/>
+      <c r="A186" s="5" t="n"/>
+      <c r="B186" s="5" t="n"/>
+      <c r="C186" s="5" t="n"/>
+      <c r="D186" s="5" t="n"/>
       <c r="E186" s="7" t="inlineStr">
         <is>
-          <t>12-1-4</t>
+          <t>12-1-7</t>
         </is>
       </c>
       <c r="F186" s="7" t="inlineStr">
         <is>
-          <t>sort=ratingを指定すると平均評価が高い順に表示される</t>
+          <t>sort=rating指定時、レビューがない書籍は最後に表示される</t>
         </is>
       </c>
       <c r="G186" s="7" t="inlineStr">
         <is>
-          <t>1.平均評価が異なる複数の書籍を用意する
+          <t>1.レビューがある書籍と、レビューがない書籍(登録が最も新しい)を用意する
 2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H186" s="7" t="inlineStr">
         <is>
-          <t>平均評価が高い順に表示される</t>
-        </is>
-      </c>
-      <c r="I186" s="4" t="n"/>
+          <t>レビューがある書籍が平均評価の高い順に表示され、レビューがない書籍は最後に表示される</t>
+        </is>
+      </c>
+      <c r="I186" s="5" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="4" t="n"/>
-      <c r="B187" s="4" t="n"/>
-      <c r="C187" s="4" t="n"/>
-      <c r="D187" s="4" t="n"/>
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B187" s="7" t="inlineStr">
+        <is>
+          <t>書籍CRUD（認可の詳細テスト）</t>
+        </is>
+      </c>
+      <c r="C187" s="7" t="inlineStr">
+        <is>
+          <t>13-1</t>
+        </is>
+      </c>
+      <c r="D187" s="7" t="inlineStr">
+        <is>
+          <t>BookPolicyの認可ロジック</t>
+        </is>
+      </c>
       <c r="E187" s="7" t="inlineStr">
         <is>
-          <t>12-1-5</t>
+          <t>13-1-1</t>
         </is>
       </c>
       <c r="F187" s="7" t="inlineStr">
         <is>
-          <t>sort=rating指定時、平均評価が同じ書籍は新着順で表示される</t>
+          <t>ログインユーザーは誰でも書籍を作成できる</t>
         </is>
       </c>
       <c r="G187" s="7" t="inlineStr">
         <is>
-          <t>1.平均評価が同じ複数の書籍を、異なる登録日時で用意する
-2.sort=ratingを指定して書籍一覧を開く</t>
+          <t>1.任意のログインユーザーで BookPolicy::create() を確認する</t>
         </is>
       </c>
       <c r="H187" s="7" t="inlineStr">
         <is>
-          <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
-        </is>
-      </c>
-      <c r="I187" s="4" t="n"/>
+          <t>trueが返り、作成が許可される</t>
+        </is>
+      </c>
+      <c r="I187" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/BookAuthorization/BookAuthorizationTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="n"/>
@@ -6323,101 +6332,79 @@
       <c r="D188" s="4" t="n"/>
       <c r="E188" s="7" t="inlineStr">
         <is>
-          <t>12-1-6</t>
+          <t>13-1-2</t>
         </is>
       </c>
       <c r="F188" s="7" t="inlineStr">
         <is>
-          <t>登録日時が同じ書籍は、IDの順に並ぶ(新しい順はIDの降順、古い順はIDの昇順)</t>
+          <t>書籍の登録者本人は更新が許可される</t>
         </is>
       </c>
       <c r="G188" s="7" t="inlineStr">
         <is>
-          <t>1.登録日時が同じ書籍を複数用意する
-2.sort=latest、sort=oldestをそれぞれ指定して書籍一覧を開く</t>
+          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H188" s="7" t="inlineStr">
         <is>
-          <t>新しい順ではIDの降順(後に登録した順)、古い順ではIDの昇順(先に登録した順)に表示される</t>
+          <t>trueが返る</t>
         </is>
       </c>
       <c r="I188" s="4" t="n"/>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="n"/>
-      <c r="B189" s="5" t="n"/>
-      <c r="C189" s="5" t="n"/>
-      <c r="D189" s="5" t="n"/>
+      <c r="A189" s="4" t="n"/>
+      <c r="B189" s="4" t="n"/>
+      <c r="C189" s="4" t="n"/>
+      <c r="D189" s="4" t="n"/>
       <c r="E189" s="7" t="inlineStr">
         <is>
-          <t>12-1-7</t>
+          <t>13-1-3</t>
         </is>
       </c>
       <c r="F189" s="7" t="inlineStr">
         <is>
-          <t>sort=rating指定時、レビューがない書籍は最後に表示される</t>
+          <t>書籍の登録者以外は更新が許可されない</t>
         </is>
       </c>
       <c r="G189" s="7" t="inlineStr">
         <is>
-          <t>1.レビューがある書籍と、レビューがない書籍(登録が最も新しい)を用意する
-2.sort=ratingを指定して書籍一覧を開く</t>
+          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H189" s="7" t="inlineStr">
         <is>
-          <t>レビューがある書籍が平均評価の高い順に表示され、レビューがない書籍は最後に表示される</t>
-        </is>
-      </c>
-      <c r="I189" s="5" t="n"/>
+          <t>falseが返る</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="n"/>
     </row>
     <row r="190">
-      <c r="A190" s="7" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B190" s="7" t="inlineStr">
-        <is>
-          <t>書籍CRUD（認可の詳細テスト）</t>
-        </is>
-      </c>
-      <c r="C190" s="7" t="inlineStr">
-        <is>
-          <t>13-1</t>
-        </is>
-      </c>
-      <c r="D190" s="7" t="inlineStr">
-        <is>
-          <t>BookPolicyの認可ロジック</t>
-        </is>
-      </c>
+      <c r="A190" s="4" t="n"/>
+      <c r="B190" s="4" t="n"/>
+      <c r="C190" s="4" t="n"/>
+      <c r="D190" s="4" t="n"/>
       <c r="E190" s="7" t="inlineStr">
         <is>
-          <t>13-1-1</t>
+          <t>13-1-4</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>ログインユーザーは誰でも書籍を作成できる</t>
+          <t>書籍の登録者本人は削除が許可される</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>1.任意のログインユーザーで BookPolicy::create() を確認する</t>
+          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
         </is>
       </c>
       <c r="H190" s="7" t="inlineStr">
         <is>
-          <t>trueが返り、作成が許可される</t>
-        </is>
-      </c>
-      <c r="I190" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/BookAuthorization/BookAuthorizationTest.php</t>
-        </is>
-      </c>
+          <t>trueが返る</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="n"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="n"/>
@@ -6426,22 +6413,22 @@
       <c r="D191" s="4" t="n"/>
       <c r="E191" s="7" t="inlineStr">
         <is>
-          <t>13-1-2</t>
+          <t>13-1-5</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者本人は更新が許可される</t>
+          <t>書籍の登録者以外は削除が許可されない</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
+          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
         </is>
       </c>
       <c r="H191" s="7" t="inlineStr">
         <is>
-          <t>trueが返る</t>
+          <t>falseが返る</t>
         </is>
       </c>
       <c r="I191" s="4" t="n"/>
@@ -6453,79 +6440,99 @@
       <c r="D192" s="4" t="n"/>
       <c r="E192" s="7" t="inlineStr">
         <is>
-          <t>13-1-3</t>
+          <t>13-1-6</t>
         </is>
       </c>
       <c r="F192" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者以外は更新が許可されない</t>
+          <t>フォームを介さない直接のPUT/DELETEリクエストでも他人の書籍は操作できない</t>
         </is>
       </c>
       <c r="G192" s="7" t="inlineStr">
         <is>
-          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
+          <t>1.他人が登録した書籍に対して、直接PUT・DELETEリクエストを送信する</t>
         </is>
       </c>
       <c r="H192" s="7" t="inlineStr">
         <is>
-          <t>falseが返る</t>
+          <t>いずれも403Forbiddenになり、データは変更されない</t>
         </is>
       </c>
       <c r="I192" s="4" t="n"/>
     </row>
     <row r="193">
-      <c r="A193" s="4" t="n"/>
-      <c r="B193" s="4" t="n"/>
-      <c r="C193" s="4" t="n"/>
-      <c r="D193" s="4" t="n"/>
+      <c r="A193" s="5" t="n"/>
+      <c r="B193" s="5" t="n"/>
+      <c r="C193" s="5" t="n"/>
+      <c r="D193" s="5" t="n"/>
       <c r="E193" s="7" t="inlineStr">
         <is>
-          <t>13-1-4</t>
+          <t>13-1-7</t>
         </is>
       </c>
       <c r="F193" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者本人は削除が許可される</t>
+          <t>他人の書籍に対して不正な入力を直接PUTしても、入力エラーではなく403になる</t>
         </is>
       </c>
       <c r="G193" s="7" t="inlineStr">
         <is>
-          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
+          <t>1.他人が登録した書籍に対して、タイトルを空にするなど不正な内容で、直接PUTリクエストを送信する</t>
         </is>
       </c>
       <c r="H193" s="7" t="inlineStr">
         <is>
-          <t>trueが返る</t>
-        </is>
-      </c>
-      <c r="I193" s="4" t="n"/>
+          <t>バリデーションエラーにはならず、403Forbiddenになる（入力チェックより先に権限が判定される）。データは変更されない</t>
+        </is>
+      </c>
+      <c r="I193" s="5" t="n"/>
     </row>
     <row r="194">
-      <c r="A194" s="4" t="n"/>
-      <c r="B194" s="4" t="n"/>
-      <c r="C194" s="4" t="n"/>
-      <c r="D194" s="4" t="n"/>
+      <c r="A194" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B194" s="7" t="inlineStr">
+        <is>
+          <t>ISBN検索</t>
+        </is>
+      </c>
+      <c r="C194" s="7" t="inlineStr">
+        <is>
+          <t>14-1</t>
+        </is>
+      </c>
+      <c r="D194" s="7" t="inlineStr">
+        <is>
+          <t>ISBNからの書籍情報取得(外部API連携)</t>
+        </is>
+      </c>
       <c r="E194" s="7" t="inlineStr">
         <is>
-          <t>13-1-5</t>
+          <t>14-1-1</t>
         </is>
       </c>
       <c r="F194" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者以外は削除が許可されない</t>
+          <t>未ログインの場合、ISBN検索エンドポイントにアクセスできない</t>
         </is>
       </c>
       <c r="G194" s="7" t="inlineStr">
         <is>
-          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
+          <t>1.未ログイン状態でGET /books/isbn/{isbn} にアクセスする</t>
         </is>
       </c>
       <c r="H194" s="7" t="inlineStr">
         <is>
-          <t>falseが返る</t>
-        </is>
-      </c>
-      <c r="I194" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I194" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Isbn/IsbnSearchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="n"/>
@@ -6534,99 +6541,80 @@
       <c r="D195" s="4" t="n"/>
       <c r="E195" s="7" t="inlineStr">
         <is>
-          <t>13-1-6</t>
+          <t>14-1-2</t>
         </is>
       </c>
       <c r="F195" s="7" t="inlineStr">
         <is>
-          <t>フォームを介さない直接のPUT/DELETEリクエストでも他人の書籍は操作できない</t>
+          <t>ISBNが空(空白のみ)の場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G195" s="7" t="inlineStr">
         <is>
-          <t>1.他人が登録した書籍に対して、直接PUT・DELETEリクエストを送信する</t>
+          <t>1.ログイン状態で、ISBN部分を半角スペースのみにしてGET /books/isbn/%20 にリクエストする
+※ISBN部分を完全に空にするとURLが /books/isbn となり、このルートに一致しないため空白で代用する</t>
         </is>
       </c>
       <c r="H195" s="7" t="inlineStr">
         <is>
-          <t>いずれも403Forbiddenになり、データは変更されない</t>
+          <t>422が返り、「ISBNを入力してください」が返る</t>
         </is>
       </c>
       <c r="I195" s="4" t="n"/>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="n"/>
-      <c r="B196" s="5" t="n"/>
-      <c r="C196" s="5" t="n"/>
-      <c r="D196" s="5" t="n"/>
+      <c r="A196" s="4" t="n"/>
+      <c r="B196" s="4" t="n"/>
+      <c r="C196" s="4" t="n"/>
+      <c r="D196" s="4" t="n"/>
       <c r="E196" s="7" t="inlineStr">
         <is>
-          <t>13-1-7</t>
+          <t>14-1-3</t>
         </is>
       </c>
       <c r="F196" s="7" t="inlineStr">
         <is>
-          <t>他人の書籍に対して不正な入力を直接PUTしても、入力エラーではなく403になる</t>
+          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G196" s="7" t="inlineStr">
         <is>
-          <t>1.他人が登録した書籍に対して、タイトルを空にするなど不正な内容で、直接PUTリクエストを送信する</t>
+          <t>1.13桁でないISBNでリクエストする</t>
         </is>
       </c>
       <c r="H196" s="7" t="inlineStr">
         <is>
-          <t>バリデーションエラーにはならず、403Forbiddenになる（入力チェックより先に権限が判定される）。データは変更されない</t>
-        </is>
-      </c>
-      <c r="I196" s="5" t="n"/>
+          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
+        </is>
+      </c>
+      <c r="I196" s="4" t="n"/>
     </row>
     <row r="197">
-      <c r="A197" s="7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B197" s="7" t="inlineStr">
-        <is>
-          <t>ISBN検索</t>
-        </is>
-      </c>
-      <c r="C197" s="7" t="inlineStr">
-        <is>
-          <t>14-1</t>
-        </is>
-      </c>
-      <c r="D197" s="7" t="inlineStr">
-        <is>
-          <t>ISBNからの書籍情報取得(外部API連携)</t>
-        </is>
-      </c>
+      <c r="A197" s="4" t="n"/>
+      <c r="B197" s="4" t="n"/>
+      <c r="C197" s="4" t="n"/>
+      <c r="D197" s="4" t="n"/>
       <c r="E197" s="7" t="inlineStr">
         <is>
-          <t>14-1-1</t>
+          <t>14-1-4</t>
         </is>
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、ISBN検索エンドポイントにアクセスできない</t>
+          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態でGET /books/isbn/{isbn} にアクセスする</t>
+          <t>1.登録済みのISBNでリクエストする</t>
         </is>
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I197" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Isbn/IsbnSearchTest.php</t>
-        </is>
-      </c>
+          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
+        </is>
+      </c>
+      <c r="I197" s="4" t="n"/>
     </row>
     <row r="198">
       <c r="A198" s="4" t="n"/>
@@ -6635,23 +6623,23 @@
       <c r="D198" s="4" t="n"/>
       <c r="E198" s="7" t="inlineStr">
         <is>
-          <t>14-1-2</t>
+          <t>14-1-5</t>
         </is>
       </c>
       <c r="F198" s="7" t="inlineStr">
         <is>
-          <t>ISBNが空(空白のみ)の場合、バリデーションエラーが返る</t>
+          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
         </is>
       </c>
       <c r="G198" s="7" t="inlineStr">
         <is>
-          <t>1.ログイン状態で、ISBN部分を半角スペースのみにしてGET /books/isbn/%20 にリクエストする
-※ISBN部分を完全に空にするとURLが /books/isbn となり、このルートに一致しないため空白で代用する</t>
+          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
+2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H198" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「ISBNを入力してください」が返る</t>
+          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
         </is>
       </c>
       <c r="I198" s="4" t="n"/>
@@ -6663,22 +6651,23 @@
       <c r="D199" s="4" t="n"/>
       <c r="E199" s="7" t="inlineStr">
         <is>
-          <t>14-1-3</t>
+          <t>14-1-6</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
+          <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
         </is>
       </c>
       <c r="G199" s="7" t="inlineStr">
         <is>
-          <t>1.13桁でないISBNでリクエストする</t>
+          <t>1.Http::fake()でitemsが空のレスポンスをモックする
+2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
+          <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
         </is>
       </c>
       <c r="I199" s="4" t="n"/>
@@ -6690,81 +6679,101 @@
       <c r="D200" s="4" t="n"/>
       <c r="E200" s="7" t="inlineStr">
         <is>
-          <t>14-1-4</t>
+          <t>14-1-7</t>
         </is>
       </c>
       <c r="F200" s="7" t="inlineStr">
         <is>
-          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
+          <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
         </is>
       </c>
       <c r="G200" s="7" t="inlineStr">
         <is>
-          <t>1.登録済みのISBNでリクエストする</t>
+          <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
+2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
+          <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
         </is>
       </c>
       <c r="I200" s="4" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="4" t="n"/>
-      <c r="B201" s="4" t="n"/>
-      <c r="C201" s="4" t="n"/>
-      <c r="D201" s="4" t="n"/>
+      <c r="A201" s="5" t="n"/>
+      <c r="B201" s="5" t="n"/>
+      <c r="C201" s="5" t="n"/>
+      <c r="D201" s="5" t="n"/>
       <c r="E201" s="7" t="inlineStr">
         <is>
-          <t>14-1-5</t>
+          <t>14-1-8</t>
         </is>
       </c>
       <c r="F201" s="7" t="inlineStr">
         <is>
-          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
+          <t>APIの検索結果はあるが、ISBNが一致する書籍がない場合も404エラーが返る</t>
         </is>
       </c>
       <c r="G201" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
+          <t>1.Http::fake()で、別のISBNを持つ書籍のみを含むitemsを返すようモックする
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
-          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
-        </is>
-      </c>
-      <c r="I201" s="4" t="n"/>
+          <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
+        </is>
+      </c>
+      <c r="I201" s="5" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="4" t="n"/>
-      <c r="B202" s="4" t="n"/>
-      <c r="C202" s="4" t="n"/>
-      <c r="D202" s="4" t="n"/>
+      <c r="A202" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B202" s="7" t="inlineStr">
+        <is>
+          <t>マイ読書レポート</t>
+        </is>
+      </c>
+      <c r="C202" s="7" t="inlineStr">
+        <is>
+          <t>15-1</t>
+        </is>
+      </c>
+      <c r="D202" s="7" t="inlineStr">
+        <is>
+          <t>読書統計の表示</t>
+        </is>
+      </c>
       <c r="E202" s="7" t="inlineStr">
         <is>
-          <t>14-1-6</t>
+          <t>15-1-1</t>
         </is>
       </c>
       <c r="F202" s="7" t="inlineStr">
         <is>
-          <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
+          <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
         </is>
       </c>
       <c r="G202" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でitemsが空のレスポンスをモックする
-2.未登録ISBNでリクエストする</t>
+          <t>1.未ログイン状態で/reportsを開く</t>
         </is>
       </c>
       <c r="H202" s="7" t="inlineStr">
         <is>
-          <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
-        </is>
-      </c>
-      <c r="I202" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I202" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/Report/ReportTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="n"/>
@@ -6773,101 +6782,79 @@
       <c r="D203" s="4" t="n"/>
       <c r="E203" s="7" t="inlineStr">
         <is>
-          <t>14-1-7</t>
+          <t>15-1-2</t>
         </is>
       </c>
       <c r="F203" s="7" t="inlineStr">
         <is>
-          <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
+          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
         </is>
       </c>
       <c r="G203" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
-2.未登録ISBNでリクエストする</t>
+          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H203" s="7" t="inlineStr">
         <is>
-          <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
+          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
         </is>
       </c>
       <c r="I203" s="4" t="n"/>
     </row>
     <row r="204">
-      <c r="A204" s="5" t="n"/>
-      <c r="B204" s="5" t="n"/>
-      <c r="C204" s="5" t="n"/>
-      <c r="D204" s="5" t="n"/>
+      <c r="A204" s="4" t="n"/>
+      <c r="B204" s="4" t="n"/>
+      <c r="C204" s="4" t="n"/>
+      <c r="D204" s="4" t="n"/>
       <c r="E204" s="7" t="inlineStr">
         <is>
-          <t>14-1-8</t>
+          <t>15-1-3</t>
         </is>
       </c>
       <c r="F204" s="7" t="inlineStr">
         <is>
-          <t>APIの検索結果はあるが、ISBNが一致する書籍がない場合も404エラーが返る</t>
+          <t>評価分布(★1〜★5)が正しく表示される</t>
         </is>
       </c>
       <c r="G204" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()で、別のISBNを持つ書籍のみを含むitemsを返すようモックする
-2.未登録ISBNでリクエストする</t>
+          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
-          <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
-        </is>
-      </c>
-      <c r="I204" s="5" t="n"/>
+          <t>各評価の件数が実データと一致して表示される</t>
+        </is>
+      </c>
+      <c r="I204" s="4" t="n"/>
     </row>
     <row r="205">
-      <c r="A205" s="7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B205" s="7" t="inlineStr">
-        <is>
-          <t>マイ読書レポート</t>
-        </is>
-      </c>
-      <c r="C205" s="7" t="inlineStr">
-        <is>
-          <t>15-1</t>
-        </is>
-      </c>
-      <c r="D205" s="7" t="inlineStr">
-        <is>
-          <t>読書統計の表示</t>
-        </is>
-      </c>
+      <c r="A205" s="4" t="n"/>
+      <c r="B205" s="4" t="n"/>
+      <c r="C205" s="4" t="n"/>
+      <c r="D205" s="4" t="n"/>
       <c r="E205" s="7" t="inlineStr">
         <is>
-          <t>15-1-1</t>
+          <t>15-1-4</t>
         </is>
       </c>
       <c r="F205" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
+          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
         </is>
       </c>
       <c r="G205" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で/reportsを開く</t>
+          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I205" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/Report/ReportTest.php</t>
-        </is>
-      </c>
+          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
+        </is>
+      </c>
+      <c r="I205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="4" t="n"/>
@@ -6876,22 +6863,22 @@
       <c r="D206" s="4" t="n"/>
       <c r="E206" s="7" t="inlineStr">
         <is>
-          <t>15-1-2</t>
+          <t>15-1-5</t>
         </is>
       </c>
       <c r="F206" s="7" t="inlineStr">
         <is>
-          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
+          <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
         </is>
       </c>
       <c r="G206" s="7" t="inlineStr">
         <is>
-          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
+          <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
+          <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
         </is>
       </c>
       <c r="I206" s="4" t="n"/>
@@ -6903,79 +6890,100 @@
       <c r="D207" s="4" t="n"/>
       <c r="E207" s="7" t="inlineStr">
         <is>
-          <t>15-1-3</t>
+          <t>15-1-6</t>
         </is>
       </c>
       <c r="F207" s="7" t="inlineStr">
         <is>
-          <t>評価分布(★1〜★5)が正しく表示される</t>
+          <t>レビューを1件も投稿していない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G207" s="7" t="inlineStr">
         <is>
-          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
+          <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
-          <t>各評価の件数が実データと一致して表示される</t>
+          <t>総レビュー数・読了冊数が0（平均評価の集計値は0で、画面上は「-」と表示）となり、TOP5一覧には「4星以上の書籍がありません」「ジャンルが設定された書籍のレビューがありません」と表示される</t>
         </is>
       </c>
       <c r="I207" s="4" t="n"/>
     </row>
     <row r="208">
-      <c r="A208" s="4" t="n"/>
-      <c r="B208" s="4" t="n"/>
-      <c r="C208" s="4" t="n"/>
-      <c r="D208" s="4" t="n"/>
+      <c r="A208" s="5" t="n"/>
+      <c r="B208" s="5" t="n"/>
+      <c r="C208" s="5" t="n"/>
+      <c r="D208" s="5" t="n"/>
       <c r="E208" s="7" t="inlineStr">
         <is>
-          <t>15-1-4</t>
+          <t>15-1-7</t>
         </is>
       </c>
       <c r="F208" s="7" t="inlineStr">
         <is>
-          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
+          <t>ジャンル別評価傾向で、平均評価が同じジャンルはレビュー件数の多い順に表示される</t>
         </is>
       </c>
       <c r="G208" s="7" t="inlineStr">
         <is>
-          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
+          <t>1.平均評価が同じで、レビュー件数が異なる2つのジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H208" s="7" t="inlineStr">
         <is>
-          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
-        </is>
-      </c>
-      <c r="I208" s="4" t="n"/>
+          <t>平均評価が同じジャンル同士は、レビュー件数の多い順に表示される</t>
+        </is>
+      </c>
+      <c r="I208" s="5" t="n"/>
     </row>
     <row r="209">
-      <c r="A209" s="4" t="n"/>
-      <c r="B209" s="4" t="n"/>
-      <c r="C209" s="4" t="n"/>
-      <c r="D209" s="4" t="n"/>
+      <c r="A209" s="7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B209" s="7" t="inlineStr">
+        <is>
+          <t>Sanctum認証</t>
+        </is>
+      </c>
+      <c r="C209" s="7" t="inlineStr">
+        <is>
+          <t>16-1</t>
+        </is>
+      </c>
+      <c r="D209" s="7" t="inlineStr">
+        <is>
+          <t>AP06:SanctumAPIトークン認証</t>
+        </is>
+      </c>
       <c r="E209" s="7" t="inlineStr">
         <is>
-          <t>15-1-5</t>
+          <t>16-1-1</t>
         </is>
       </c>
       <c r="F209" s="7" t="inlineStr">
         <is>
-          <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
+          <t>有効なpersonal access tokenを付与すると、書き込み系API(POST /api/v1/books)を利用できる</t>
         </is>
       </c>
       <c r="G209" s="7" t="inlineStr">
         <is>
-          <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
+          <t>1.$user-&gt;createToken()でトークンを発行する
+2.Authorization: Bearer {token}を付与して、正しい入力値でPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H209" s="7" t="inlineStr">
         <is>
-          <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
-        </is>
-      </c>
-      <c r="I209" s="4" t="n"/>
+          <t>201が返り、トークンの持ち主を登録者(user_id)として書籍が登録される</t>
+        </is>
+      </c>
+      <c r="I209" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="n"/>
@@ -6984,127 +6992,127 @@
       <c r="D210" s="4" t="n"/>
       <c r="E210" s="7" t="inlineStr">
         <is>
-          <t>15-1-6</t>
+          <t>16-1-2</t>
         </is>
       </c>
       <c r="F210" s="7" t="inlineStr">
         <is>
-          <t>レビューを1件も投稿していない場合の表示を確認する</t>
+          <t>トークンなしで書き込み系API(POST/PUT/DELETE)にアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G210" s="7" t="inlineStr">
         <is>
-          <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
+          <t>1.Authorizationヘッダーを付与せずに、POST /api/v1/books、PUT・DELETE /api/v1/books/{book}にそれぞれアクセスする</t>
         </is>
       </c>
       <c r="H210" s="7" t="inlineStr">
         <is>
-          <t>総レビュー数・読了冊数が0（平均評価の集計値は0で、画面上は「-」と表示）となり、TOP5一覧には「4星以上の書籍がありません」「ジャンルが設定された書籍のレビューがありません」と表示される</t>
+          <t>いずれも401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録・更新・削除されない</t>
         </is>
       </c>
       <c r="I210" s="4" t="n"/>
     </row>
     <row r="211">
-      <c r="A211" s="5" t="n"/>
-      <c r="B211" s="5" t="n"/>
-      <c r="C211" s="5" t="n"/>
-      <c r="D211" s="5" t="n"/>
+      <c r="A211" s="4" t="n"/>
+      <c r="B211" s="4" t="n"/>
+      <c r="C211" s="4" t="n"/>
+      <c r="D211" s="4" t="n"/>
       <c r="E211" s="7" t="inlineStr">
         <is>
-          <t>15-1-7</t>
+          <t>16-1-3</t>
         </is>
       </c>
       <c r="F211" s="7" t="inlineStr">
         <is>
-          <t>ジャンル別評価傾向で、平均評価が同じジャンルはレビュー件数の多い順に表示される</t>
+          <t>不正な(存在しない)トークンで書き込み系API(POST/PUT/DELETE)にアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G211" s="7" t="inlineStr">
         <is>
-          <t>1.平均評価が同じで、レビュー件数が異なる2つのジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
+          <t>1.ランダムな文字列をBearerトークンとして付与し、POST /api/v1/books、PUT・DELETE /api/v1/books/{book}にそれぞれアクセスする</t>
         </is>
       </c>
       <c r="H211" s="7" t="inlineStr">
         <is>
-          <t>平均評価が同じジャンル同士は、レビュー件数の多い順に表示される</t>
-        </is>
-      </c>
-      <c r="I211" s="5" t="n"/>
+          <t>いずれも401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録・更新・削除されない</t>
+        </is>
+      </c>
+      <c r="I211" s="4" t="n"/>
     </row>
     <row r="212">
-      <c r="A212" s="7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B212" s="7" t="inlineStr">
-        <is>
-          <t>Sanctum認証</t>
-        </is>
-      </c>
-      <c r="C212" s="7" t="inlineStr">
-        <is>
-          <t>16-1</t>
-        </is>
-      </c>
-      <c r="D212" s="7" t="inlineStr">
-        <is>
-          <t>APIトークン認証</t>
-        </is>
-      </c>
+      <c r="A212" s="5" t="n"/>
+      <c r="B212" s="5" t="n"/>
+      <c r="C212" s="5" t="n"/>
+      <c r="D212" s="5" t="n"/>
       <c r="E212" s="7" t="inlineStr">
         <is>
-          <t>16-1-1</t>
+          <t>16-1-4</t>
         </is>
       </c>
       <c r="F212" s="7" t="inlineStr">
         <is>
-          <t>有効なpersonal access tokenを付与すると/api/userにアクセスできる</t>
+          <t>削除済み(失効済み)のトークンで書き込み系API(POST/PUT/DELETE)にアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G212" s="7" t="inlineStr">
         <is>
-          <t>1.$user-&gt;createToken()でトークンを発行する
-2.Authorization: Bearer {token}を付与してGET /api/userにアクセスする</t>
+          <t>1.書籍の登録者のトークンを発行し、そのトークンを削除する
+2.そのトークンで、POST /api/v1/books、PUT・DELETE /api/v1/books/{book}(自分の書籍)にそれぞれアクセスする</t>
         </is>
       </c>
       <c r="H212" s="7" t="inlineStr">
         <is>
-          <t>200が返り、対象ユーザーの情報が返る</t>
-        </is>
-      </c>
-      <c r="I212" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
-        </is>
-      </c>
+          <t>いずれも401 Unauthorizedが返り、「認証が必要です」が返る。登録者本人のトークンでも、失効後は書籍を更新・削除できない</t>
+        </is>
+      </c>
+      <c r="I212" s="5" t="n"/>
     </row>
     <row r="213">
-      <c r="A213" s="4" t="n"/>
-      <c r="B213" s="4" t="n"/>
-      <c r="C213" s="4" t="n"/>
-      <c r="D213" s="4" t="n"/>
+      <c r="A213" s="7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B213" s="7" t="inlineStr">
+        <is>
+          <t>読書計画</t>
+        </is>
+      </c>
+      <c r="C213" s="7" t="inlineStr">
+        <is>
+          <t>17-1</t>
+        </is>
+      </c>
+      <c r="D213" s="7" t="inlineStr">
+        <is>
+          <t>読書計画の作成・一覧・読了・削除</t>
+        </is>
+      </c>
       <c r="E213" s="7" t="inlineStr">
         <is>
-          <t>16-1-2</t>
+          <t>17-1-1</t>
         </is>
       </c>
       <c r="F213" s="7" t="inlineStr">
         <is>
-          <t>トークンなしでアクセスすると401が返る</t>
+          <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
         </is>
       </c>
       <c r="G213" s="7" t="inlineStr">
         <is>
-          <t>1.Authorizationヘッダーを付与せずにGET /api/userにアクセスする</t>
+          <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H213" s="7" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
-        </is>
-      </c>
-      <c r="I213" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I213" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="n"/>
@@ -7113,100 +7121,82 @@
       <c r="D214" s="4" t="n"/>
       <c r="E214" s="7" t="inlineStr">
         <is>
-          <t>16-1-3</t>
+          <t>17-1-2</t>
         </is>
       </c>
       <c r="F214" s="7" t="inlineStr">
         <is>
-          <t>不正な(存在しない)トークンでアクセスすると401が返る</t>
+          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
         </is>
       </c>
       <c r="G214" s="7" t="inlineStr">
         <is>
-          <t>1.ランダムな文字列をBearerトークンとして付与しGET /api/userにアクセスする</t>
+          <t>1.自分と他人の読書計画をそれぞれ用意する
+2.読書計画一覧ページを開く</t>
         </is>
       </c>
       <c r="H214" s="7" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
+          <t>自分の計画のみが、target_dateの昇順で表示される</t>
         </is>
       </c>
       <c r="I214" s="4" t="n"/>
     </row>
     <row r="215">
-      <c r="A215" s="5" t="n"/>
-      <c r="B215" s="5" t="n"/>
-      <c r="C215" s="5" t="n"/>
-      <c r="D215" s="5" t="n"/>
+      <c r="A215" s="4" t="n"/>
+      <c r="B215" s="4" t="n"/>
+      <c r="C215" s="4" t="n"/>
+      <c r="D215" s="4" t="n"/>
       <c r="E215" s="7" t="inlineStr">
         <is>
-          <t>16-1-4</t>
+          <t>17-1-3</t>
         </is>
       </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
-          <t>削除済み(失効済み)のトークンでアクセスすると401が返る</t>
+          <t>ステータスで絞り込んで表示できる</t>
         </is>
       </c>
       <c r="G215" s="7" t="inlineStr">
         <is>
-          <t>1.発行済みトークンを削除する
-2.そのトークンでGET /api/userにアクセスする</t>
+          <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
+2.statusパラメータを指定して一覧を開く</t>
         </is>
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る</t>
-        </is>
-      </c>
-      <c r="I215" s="5" t="n"/>
+          <t>指定したステータスの計画のみ表示される</t>
+        </is>
+      </c>
+      <c r="I215" s="4" t="n"/>
     </row>
     <row r="216">
-      <c r="A216" s="7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B216" s="7" t="inlineStr">
-        <is>
-          <t>読書計画</t>
-        </is>
-      </c>
-      <c r="C216" s="7" t="inlineStr">
-        <is>
-          <t>17-1</t>
-        </is>
-      </c>
-      <c r="D216" s="7" t="inlineStr">
-        <is>
-          <t>読書計画の作成・一覧・読了・削除</t>
-        </is>
-      </c>
+      <c r="A216" s="4" t="n"/>
+      <c r="B216" s="4" t="n"/>
+      <c r="C216" s="4" t="n"/>
+      <c r="D216" s="4" t="n"/>
       <c r="E216" s="7" t="inlineStr">
         <is>
-          <t>17-1-1</t>
+          <t>17-1-4</t>
         </is>
       </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
+          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
         </is>
       </c>
       <c r="G216" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
+          <t>1.ある書籍について進行中の計画を作成する
+2.計画作成ページを開く</t>
         </is>
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I216" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
-        </is>
-      </c>
+          <t>書籍選択肢にその書籍が表示されない</t>
+        </is>
+      </c>
+      <c r="I216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="n"/>
@@ -7215,23 +7205,22 @@
       <c r="D217" s="4" t="n"/>
       <c r="E217" s="7" t="inlineStr">
         <is>
-          <t>17-1-2</t>
+          <t>17-1-5</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
+          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
         </is>
       </c>
       <c r="G217" s="7" t="inlineStr">
         <is>
-          <t>1.自分と他人の読書計画をそれぞれ用意する
-2.読書計画一覧ページを開く</t>
+          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
-          <t>自分の計画のみが、target_dateの昇順で表示される</t>
+          <t>403Forbiddenになり、計画は作成されない</t>
         </is>
       </c>
       <c r="I217" s="4" t="n"/>
@@ -7243,23 +7232,23 @@
       <c r="D218" s="4" t="n"/>
       <c r="E218" s="7" t="inlineStr">
         <is>
-          <t>17-1-3</t>
+          <t>17-1-6</t>
         </is>
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>ステータスで絞り込んで表示できる</t>
+          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
-          <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
-2.statusパラメータを指定して一覧を開く</t>
+          <t>1.ある書籍の計画を読了(完了)状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>指定したステータスの計画のみ表示される</t>
+          <t>新しい計画が作成される</t>
         </is>
       </c>
       <c r="I218" s="4" t="n"/>
@@ -7271,23 +7260,23 @@
       <c r="D219" s="4" t="n"/>
       <c r="E219" s="7" t="inlineStr">
         <is>
-          <t>17-1-4</t>
+          <t>17-1-7</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G219" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍について進行中の計画を作成する
-2.計画作成ページを開く</t>
+          <t>1.計画作成ページを開く
+2.期日を入力せずに登録する</t>
         </is>
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>書籍選択肢にその書籍が表示されない</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I219" s="4" t="n"/>
@@ -7299,22 +7288,23 @@
       <c r="D220" s="4" t="n"/>
       <c r="E220" s="7" t="inlineStr">
         <is>
-          <t>17-1-5</t>
+          <t>17-1-8</t>
         </is>
       </c>
       <c r="F220" s="7" t="inlineStr">
         <is>
-          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G220" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
+          <t>1.計画作成ページを開く
+2.過去の日付を期日に指定して登録する</t>
         </is>
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、計画は作成されない</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I220" s="4" t="n"/>
@@ -7326,23 +7316,23 @@
       <c r="D221" s="4" t="n"/>
       <c r="E221" s="7" t="inlineStr">
         <is>
-          <t>17-1-6</t>
+          <t>17-1-9</t>
         </is>
       </c>
       <c r="F221" s="7" t="inlineStr">
         <is>
-          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
+          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
         </is>
       </c>
       <c r="G221" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を読了(完了)状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.計画作成ページを開く
+2.書籍・期日を正しく入力して登録する</t>
         </is>
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
-          <t>新しい計画が作成される</t>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
         </is>
       </c>
       <c r="I221" s="4" t="n"/>
@@ -7354,23 +7344,22 @@
       <c r="D222" s="4" t="n"/>
       <c r="E222" s="7" t="inlineStr">
         <is>
-          <t>17-1-7</t>
+          <t>17-1-10</t>
         </is>
       </c>
       <c r="F222" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
         </is>
       </c>
       <c r="G222" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.期日を入力せずに登録する</t>
+          <t>1.進行中の計画に対して読了操作を行う</t>
         </is>
       </c>
       <c r="H222" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
         </is>
       </c>
       <c r="I222" s="4" t="n"/>
@@ -7382,23 +7371,22 @@
       <c r="D223" s="4" t="n"/>
       <c r="E223" s="7" t="inlineStr">
         <is>
-          <t>17-1-8</t>
+          <t>17-1-11</t>
         </is>
       </c>
       <c r="F223" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>他人が作成した読書計画は読了・削除できない</t>
         </is>
       </c>
       <c r="G223" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.過去の日付を期日に指定して登録する</t>
+          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
         </is>
       </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>いずれも403Forbiddenになる</t>
         </is>
       </c>
       <c r="I223" s="4" t="n"/>
@@ -7410,23 +7398,22 @@
       <c r="D224" s="4" t="n"/>
       <c r="E224" s="7" t="inlineStr">
         <is>
-          <t>17-1-9</t>
+          <t>17-1-12</t>
         </is>
       </c>
       <c r="F224" s="7" t="inlineStr">
         <is>
-          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
+          <t>自分が作成した読書計画は削除できる</t>
         </is>
       </c>
       <c r="G224" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍・期日を正しく入力して登録する</t>
+          <t>1.自分が作成した計画の削除ボタンを押す</t>
         </is>
       </c>
       <c r="H224" s="7" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
+          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
         </is>
       </c>
       <c r="I224" s="4" t="n"/>
@@ -7436,24 +7423,25 @@
       <c r="B225" s="4" t="n"/>
       <c r="C225" s="4" t="n"/>
       <c r="D225" s="4" t="n"/>
-      <c r="E225" s="7" t="inlineStr">
-        <is>
-          <t>17-1-10</t>
-        </is>
-      </c>
-      <c r="F225" s="7" t="inlineStr">
-        <is>
-          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
-        </is>
-      </c>
-      <c r="G225" s="7" t="inlineStr">
-        <is>
-          <t>1.進行中の計画に対して読了操作を行う</t>
-        </is>
-      </c>
-      <c r="H225" s="7" t="inlineStr">
-        <is>
-          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
+      <c r="E225" s="9" t="inlineStr">
+        <is>
+          <t>17-1-13</t>
+        </is>
+      </c>
+      <c r="F225" s="9" t="inlineStr">
+        <is>
+          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
+        </is>
+      </c>
+      <c r="G225" s="9" t="inlineStr">
+        <is>
+          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
+2.その読書計画を削除する</t>
+        </is>
+      </c>
+      <c r="H225" s="9" t="inlineStr">
+        <is>
+          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
         </is>
       </c>
       <c r="I225" s="4" t="n"/>
@@ -7463,24 +7451,24 @@
       <c r="B226" s="4" t="n"/>
       <c r="C226" s="4" t="n"/>
       <c r="D226" s="4" t="n"/>
-      <c r="E226" s="7" t="inlineStr">
-        <is>
-          <t>17-1-11</t>
-        </is>
-      </c>
-      <c r="F226" s="7" t="inlineStr">
-        <is>
-          <t>他人が作成した読書計画は読了・削除できない</t>
-        </is>
-      </c>
-      <c r="G226" s="7" t="inlineStr">
-        <is>
-          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
-        </is>
-      </c>
-      <c r="H226" s="7" t="inlineStr">
-        <is>
-          <t>いずれも403Forbiddenになる</t>
+      <c r="E226" s="9" t="inlineStr">
+        <is>
+          <t>17-1-14</t>
+        </is>
+      </c>
+      <c r="F226" s="9" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」の計画は、読了操作を行えない</t>
+        </is>
+      </c>
+      <c r="G226" s="9" t="inlineStr">
+        <is>
+          <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H226" s="9" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、completed_atは変更されない</t>
         </is>
       </c>
       <c r="I226" s="4" t="n"/>
@@ -7490,24 +7478,25 @@
       <c r="B227" s="4" t="n"/>
       <c r="C227" s="4" t="n"/>
       <c r="D227" s="4" t="n"/>
-      <c r="E227" s="7" t="inlineStr">
-        <is>
-          <t>17-1-12</t>
-        </is>
-      </c>
-      <c r="F227" s="7" t="inlineStr">
-        <is>
-          <t>自分が作成した読書計画は削除できる</t>
-        </is>
-      </c>
-      <c r="G227" s="7" t="inlineStr">
-        <is>
-          <t>1.自分が作成した計画の削除ボタンを押す</t>
-        </is>
-      </c>
-      <c r="H227" s="7" t="inlineStr">
-        <is>
-          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
+      <c r="E227" s="9" t="inlineStr">
+        <is>
+          <t>17-1-15</t>
+        </is>
+      </c>
+      <c r="F227" s="9" t="inlineStr">
+        <is>
+          <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
+        </is>
+      </c>
+      <c r="G227" s="9" t="inlineStr">
+        <is>
+          <t>1.ある書籍の計画を「期限切れ」の状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H227" s="9" t="inlineStr">
+        <is>
+          <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
         </is>
       </c>
       <c r="I227" s="4" t="n"/>
@@ -7519,23 +7508,23 @@
       <c r="D228" s="4" t="n"/>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>17-1-13</t>
+          <t>17-1-16</t>
         </is>
       </c>
       <c r="F228" s="9" t="inlineStr">
         <is>
-          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
+          <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G228" s="9" t="inlineStr">
         <is>
-          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
-2.その読書計画を削除する</t>
+          <t>1.計画作成ページを開く
+2.書籍を選択せずに期日を入力して登録する</t>
         </is>
       </c>
       <c r="H228" s="9" t="inlineStr">
         <is>
-          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
+          <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I228" s="4" t="n"/>
@@ -7547,22 +7536,22 @@
       <c r="D229" s="4" t="n"/>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>17-1-14</t>
+          <t>17-1-17</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は、読了操作を行えない</t>
+          <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G229" s="9" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
+          <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H229" s="9" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、completed_atは変更されない</t>
+          <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I229" s="4" t="n"/>
@@ -7574,23 +7563,22 @@
       <c r="D230" s="4" t="n"/>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>17-1-15</t>
+          <t>17-1-18</t>
         </is>
       </c>
       <c r="F230" s="9" t="inlineStr">
         <is>
-          <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
+          <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G230" s="9" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を「期限切れ」の状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H230" s="9" t="inlineStr">
         <is>
-          <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
+          <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I230" s="4" t="n"/>
@@ -7602,23 +7590,22 @@
       <c r="D231" s="4" t="n"/>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>17-1-16</t>
+          <t>17-1-19</t>
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr">
         <is>
-          <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
+          <t>期日が日付形式でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G231" s="9" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍を選択せずに期日を入力して登録する</t>
+          <t>1.書籍と、日付として不正な期日(例:abc)を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H231" s="9" t="inlineStr">
         <is>
-          <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
+          <t>「正しい日付を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I231" s="4" t="n"/>
@@ -7630,22 +7617,23 @@
       <c r="D232" s="4" t="n"/>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>17-1-17</t>
+          <t>17-1-20</t>
         </is>
       </c>
       <c r="F232" s="9" t="inlineStr">
         <is>
-          <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
+          <t>期日に今日の日付を指定した場合、計画を作成できる</t>
         </is>
       </c>
       <c r="G232" s="9" t="inlineStr">
         <is>
-          <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.計画作成ページを開く
+2.書籍を選択し、期日に今日の日付を指定して登録する</t>
         </is>
       </c>
       <c r="H232" s="9" t="inlineStr">
         <is>
-          <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される（今日の日付は指定可能）</t>
         </is>
       </c>
       <c r="I232" s="4" t="n"/>
@@ -7657,22 +7645,22 @@
       <c r="D233" s="4" t="n"/>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>17-1-18</t>
+          <t>17-1-21</t>
         </is>
       </c>
       <c r="F233" s="9" t="inlineStr">
         <is>
-          <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
+          <t>同じ書籍に進行中の計画がある状態で不正な期日を指定しても、入力エラーではなく403になる</t>
         </is>
       </c>
       <c r="G233" s="9" t="inlineStr">
         <is>
-          <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.進行中の計画がある書籍を指定し、期日を空にして直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H233" s="9" t="inlineStr">
         <is>
-          <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
+          <t>バリデーションエラーではなく403Forbiddenになり、計画は作成されない（認可チェックが入力チェックより先に行われる）</t>
         </is>
       </c>
       <c r="I233" s="4" t="n"/>
@@ -7684,183 +7672,183 @@
       <c r="D234" s="4" t="n"/>
       <c r="E234" s="9" t="inlineStr">
         <is>
-          <t>17-1-19</t>
+          <t>17-1-22</t>
         </is>
       </c>
       <c r="F234" s="9" t="inlineStr">
         <is>
-          <t>期日が日付形式でない場合、バリデーションメッセージが表示される</t>
+          <t>ステータスが「期限切れ」の計画は、読了操作を行える</t>
         </is>
       </c>
       <c r="G234" s="9" t="inlineStr">
         <is>
-          <t>1.書籍と、日付として不正な期日(例:abc)を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.「期限切れ」の計画に対して、読了操作を行う</t>
         </is>
       </c>
       <c r="H234" s="9" t="inlineStr">
         <is>
-          <t>「正しい日付を入力してください」というバリデーションメッセージが表示される</t>
+          <t>ステータスが「完了」になり、completed_atに現在日時が記録され、「「(タイトル)」を読了しました。」と表示される</t>
         </is>
       </c>
       <c r="I234" s="4" t="n"/>
     </row>
     <row r="235">
-      <c r="A235" s="4" t="n"/>
-      <c r="B235" s="4" t="n"/>
-      <c r="C235" s="4" t="n"/>
-      <c r="D235" s="4" t="n"/>
+      <c r="A235" s="5" t="n"/>
+      <c r="B235" s="5" t="n"/>
+      <c r="C235" s="5" t="n"/>
+      <c r="D235" s="5" t="n"/>
       <c r="E235" s="9" t="inlineStr">
         <is>
-          <t>17-1-20</t>
+          <t>17-1-23</t>
         </is>
       </c>
       <c r="F235" s="9" t="inlineStr">
         <is>
-          <t>期日に今日の日付を指定した場合、計画を作成できる</t>
+          <t>他のユーザーの「進行中」の計画は、自分の計画作成に影響しない</t>
         </is>
       </c>
       <c r="G235" s="9" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍を選択し、期日に今日の日付を指定して登録する</t>
+          <t>1.他のユーザーが「進行中」の計画を持つ書籍を用意する
+2.計画作成ページを開く
+3.その書籍で計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H235" s="9" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される（今日の日付は指定可能）</t>
-        </is>
-      </c>
-      <c r="I235" s="4" t="n"/>
+          <t>その書籍は作成画面の選択肢に表示され、自分の計画が「進行中」で作成される（進行中の重複チェックはユーザーごとに行われる）</t>
+        </is>
+      </c>
+      <c r="I235" s="5" t="n"/>
     </row>
     <row r="236">
-      <c r="A236" s="4" t="n"/>
-      <c r="B236" s="4" t="n"/>
-      <c r="C236" s="4" t="n"/>
-      <c r="D236" s="4" t="n"/>
-      <c r="E236" s="9" t="inlineStr">
-        <is>
-          <t>17-1-21</t>
-        </is>
-      </c>
-      <c r="F236" s="9" t="inlineStr">
-        <is>
-          <t>同じ書籍に進行中の計画がある状態で不正な期日を指定しても、入力エラーではなく403になる</t>
-        </is>
-      </c>
-      <c r="G236" s="9" t="inlineStr">
-        <is>
-          <t>1.進行中の計画がある書籍を指定し、期日を空にして直接計画作成のリクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H236" s="9" t="inlineStr">
-        <is>
-          <t>バリデーションエラーではなく403Forbiddenになり、計画は作成されない（認可チェックが入力チェックより先に行われる）</t>
-        </is>
-      </c>
-      <c r="I236" s="4" t="n"/>
+      <c r="A236" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B236" s="7" t="inlineStr">
+        <is>
+          <t>読書計画（期限変更）</t>
+        </is>
+      </c>
+      <c r="C236" s="7" t="inlineStr">
+        <is>
+          <t>18-1</t>
+        </is>
+      </c>
+      <c r="D236" s="7" t="inlineStr">
+        <is>
+          <t>読書計画の期日変更</t>
+        </is>
+      </c>
+      <c r="E236" s="7" t="inlineStr">
+        <is>
+          <t>18-1-1</t>
+        </is>
+      </c>
+      <c r="F236" s="7" t="inlineStr">
+        <is>
+          <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
+        </is>
+      </c>
+      <c r="G236" s="7" t="inlineStr">
+        <is>
+          <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
+        </is>
+      </c>
+      <c r="H236" s="7" t="inlineStr">
+        <is>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I236" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="4" t="n"/>
       <c r="B237" s="4" t="n"/>
       <c r="C237" s="4" t="n"/>
       <c r="D237" s="4" t="n"/>
-      <c r="E237" s="9" t="inlineStr">
-        <is>
-          <t>17-1-22</t>
-        </is>
-      </c>
-      <c r="F237" s="9" t="inlineStr">
-        <is>
-          <t>ステータスが「期限切れ」の計画は、読了操作を行える</t>
-        </is>
-      </c>
-      <c r="G237" s="9" t="inlineStr">
-        <is>
-          <t>1.「期限切れ」の計画に対して、読了操作を行う</t>
-        </is>
-      </c>
-      <c r="H237" s="9" t="inlineStr">
-        <is>
-          <t>ステータスが「完了」になり、completed_atに現在日時が記録され、「「(タイトル)」を読了しました。」と表示される</t>
+      <c r="E237" s="7" t="inlineStr">
+        <is>
+          <t>18-1-2</t>
+        </is>
+      </c>
+      <c r="F237" s="7" t="inlineStr">
+        <is>
+          <t>他人が作成した読書計画の期日は変更できない</t>
+        </is>
+      </c>
+      <c r="G237" s="7" t="inlineStr">
+        <is>
+          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H237" s="7" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
       <c r="I237" s="4" t="n"/>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="n"/>
-      <c r="B238" s="5" t="n"/>
-      <c r="C238" s="5" t="n"/>
-      <c r="D238" s="5" t="n"/>
-      <c r="E238" s="9" t="inlineStr">
-        <is>
-          <t>17-1-23</t>
-        </is>
-      </c>
-      <c r="F238" s="9" t="inlineStr">
-        <is>
-          <t>他のユーザーの「進行中」の計画は、自分の計画作成に影響しない</t>
-        </is>
-      </c>
-      <c r="G238" s="9" t="inlineStr">
-        <is>
-          <t>1.他のユーザーが「進行中」の計画を持つ書籍を用意する
-2.計画作成ページを開く
-3.その書籍で計画作成のリクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H238" s="9" t="inlineStr">
-        <is>
-          <t>その書籍は作成画面の選択肢に表示され、自分の計画が「進行中」で作成される（進行中の重複チェックはユーザーごとに行われる）</t>
-        </is>
-      </c>
-      <c r="I238" s="5" t="n"/>
+      <c r="A238" s="4" t="n"/>
+      <c r="B238" s="4" t="n"/>
+      <c r="C238" s="4" t="n"/>
+      <c r="D238" s="4" t="n"/>
+      <c r="E238" s="7" t="inlineStr">
+        <is>
+          <t>18-1-3</t>
+        </is>
+      </c>
+      <c r="F238" s="7" t="inlineStr">
+        <is>
+          <t>編集画面を開くと現在の期日が初期表示される</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="inlineStr">
+        <is>
+          <t>1.自分が作成した計画の編集ページを開く</t>
+        </is>
+      </c>
+      <c r="H238" s="7" t="inlineStr">
+        <is>
+          <t>現在登録されている期日が入力欄に表示される</t>
+        </is>
+      </c>
+      <c r="I238" s="4" t="n"/>
     </row>
     <row r="239">
-      <c r="A239" s="7" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B239" s="7" t="inlineStr">
-        <is>
-          <t>読書計画（期限変更）</t>
-        </is>
-      </c>
-      <c r="C239" s="7" t="inlineStr">
-        <is>
-          <t>18-1</t>
-        </is>
-      </c>
-      <c r="D239" s="7" t="inlineStr">
-        <is>
-          <t>読書計画の期日変更</t>
-        </is>
-      </c>
+      <c r="A239" s="4" t="n"/>
+      <c r="B239" s="4" t="n"/>
+      <c r="C239" s="4" t="n"/>
+      <c r="D239" s="4" t="n"/>
       <c r="E239" s="7" t="inlineStr">
         <is>
-          <t>18-1-1</t>
+          <t>18-1-4</t>
         </is>
       </c>
       <c r="F239" s="7" t="inlineStr">
         <is>
-          <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G239" s="7" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
+          <t>1.編集ページを開く
+2.期日を空にして更新する</t>
         </is>
       </c>
       <c r="H239" s="7" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I239" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
-        </is>
-      </c>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+        </is>
+      </c>
+      <c r="I239" s="4" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="4" t="n"/>
@@ -7869,22 +7857,23 @@
       <c r="D240" s="4" t="n"/>
       <c r="E240" s="7" t="inlineStr">
         <is>
-          <t>18-1-2</t>
+          <t>18-1-5</t>
         </is>
       </c>
       <c r="F240" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画の期日は変更できない</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G240" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
+          <t>1.編集ページを開く
+2.過去の日付に変更して更新する</t>
         </is>
       </c>
       <c r="H240" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I240" s="4" t="n"/>
@@ -7896,22 +7885,23 @@
       <c r="D241" s="4" t="n"/>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>18-1-3</t>
+          <t>18-1-6</t>
         </is>
       </c>
       <c r="F241" s="7" t="inlineStr">
         <is>
-          <t>編集画面を開くと現在の期日が初期表示される</t>
+          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
         </is>
       </c>
       <c r="G241" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の編集ページを開く</t>
+          <t>1.編集ページを開く
+2.未来の日付に正しく変更して更新する</t>
         </is>
       </c>
       <c r="H241" s="7" t="inlineStr">
         <is>
-          <t>現在登録されている期日が入力欄に表示される</t>
+          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
         </is>
       </c>
       <c r="I241" s="4" t="n"/>
@@ -7923,23 +7913,23 @@
       <c r="D242" s="4" t="n"/>
       <c r="E242" s="7" t="inlineStr">
         <is>
-          <t>18-1-4</t>
+          <t>18-1-7</t>
         </is>
       </c>
       <c r="F242" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
         </is>
       </c>
       <c r="G242" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.期日を空にして更新する</t>
+          <t>1.期日が過去で「進行中」の計画を用意する
+2.読書計画一覧または編集ページを開く</t>
         </is>
       </c>
       <c r="H242" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
         </is>
       </c>
       <c r="I242" s="4" t="n"/>
@@ -7951,23 +7941,22 @@
       <c r="D243" s="4" t="n"/>
       <c r="E243" s="7" t="inlineStr">
         <is>
-          <t>18-1-5</t>
+          <t>18-1-8</t>
         </is>
       </c>
       <c r="F243" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>ステータスが「完了」の計画は期日を変更できない</t>
         </is>
       </c>
       <c r="G243" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.過去の日付に変更して更新する</t>
+          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H243" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
       <c r="I243" s="4" t="n"/>
@@ -7979,23 +7968,22 @@
       <c r="D244" s="4" t="n"/>
       <c r="E244" s="7" t="inlineStr">
         <is>
-          <t>18-1-6</t>
+          <t>18-1-9</t>
         </is>
       </c>
       <c r="F244" s="7" t="inlineStr">
         <is>
-          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
+          <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
         </is>
       </c>
       <c r="G244" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.未来の日付に正しく変更して更新する</t>
+          <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H244" s="7" t="inlineStr">
         <is>
-          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
+          <t>403Forbiddenになり、編集ページは表示されない</t>
         </is>
       </c>
       <c r="I244" s="4" t="n"/>
@@ -8007,23 +7995,22 @@
       <c r="D245" s="4" t="n"/>
       <c r="E245" s="7" t="inlineStr">
         <is>
-          <t>18-1-7</t>
+          <t>18-1-10</t>
         </is>
       </c>
       <c r="F245" s="7" t="inlineStr">
         <is>
-          <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
+          <t>他人が作成した読書計画の編集ページにはアクセスできない</t>
         </is>
       </c>
       <c r="G245" s="7" t="inlineStr">
         <is>
-          <t>1.期日が過去で「進行中」の計画を用意する
-2.読書計画一覧または編集ページを開く</t>
+          <t>1.他人が作成した計画の編集ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H245" s="7" t="inlineStr">
         <is>
-          <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
+          <t>403Forbiddenになり、編集ページは表示されない</t>
         </is>
       </c>
       <c r="I245" s="4" t="n"/>
@@ -8035,79 +8022,102 @@
       <c r="D246" s="4" t="n"/>
       <c r="E246" s="7" t="inlineStr">
         <is>
-          <t>18-1-8</t>
+          <t>18-1-11</t>
         </is>
       </c>
       <c r="F246" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は期日を変更できない</t>
+          <t>同じ書籍に「進行中」の計画がある場合、「期限切れ」の計画は編集・更新できない</t>
         </is>
       </c>
       <c r="G246" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
+          <t>1.同じ書籍について、「期限切れ」の計画と「進行中」の計画をそれぞれ用意する
+2.「期限切れ」の計画の編集ページのURLに直接アクセスする
+3.「期限切れ」の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H246" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
+          <t>いずれも403Forbiddenになり、「期限切れ」の計画のステータス・期日は変更されない（同じ書籍の「進行中」の計画が2件になることを防ぐ）</t>
         </is>
       </c>
       <c r="I246" s="4" t="n"/>
     </row>
     <row r="247">
-      <c r="A247" s="4" t="n"/>
-      <c r="B247" s="4" t="n"/>
-      <c r="C247" s="4" t="n"/>
-      <c r="D247" s="4" t="n"/>
+      <c r="A247" s="5" t="n"/>
+      <c r="B247" s="5" t="n"/>
+      <c r="C247" s="5" t="n"/>
+      <c r="D247" s="5" t="n"/>
       <c r="E247" s="7" t="inlineStr">
         <is>
-          <t>18-1-9</t>
+          <t>18-1-12</t>
         </is>
       </c>
       <c r="F247" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
+          <t>他人が作成した読書計画に不正な期日で更新しようとしても、入力エラーではなく403になる</t>
         </is>
       </c>
       <c r="G247" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
+          <t>1.他人が作成した読書計画に対して、期日を空にして直接計画更新のリクエストを送信する</t>
         </is>
       </c>
       <c r="H247" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、編集ページは表示されない</t>
-        </is>
-      </c>
-      <c r="I247" s="4" t="n"/>
+          <t>バリデーションエラーではなく403Forbiddenになり、期日は変更されない（認可チェックが入力チェックより先に行われる）</t>
+        </is>
+      </c>
+      <c r="I247" s="5" t="n"/>
     </row>
     <row r="248">
-      <c r="A248" s="4" t="n"/>
-      <c r="B248" s="4" t="n"/>
-      <c r="C248" s="4" t="n"/>
-      <c r="D248" s="4" t="n"/>
+      <c r="A248" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B248" s="7" t="inlineStr">
+        <is>
+          <t>リマインダーバッチ</t>
+        </is>
+      </c>
+      <c r="C248" s="7" t="inlineStr">
+        <is>
+          <t>19-1</t>
+        </is>
+      </c>
+      <c r="D248" s="7" t="inlineStr">
+        <is>
+          <t>日次バッチ(reading-plans:daily)によるリマインダー通知</t>
+        </is>
+      </c>
       <c r="E248" s="7" t="inlineStr">
         <is>
-          <t>18-1-10</t>
+          <t>19-1-1</t>
         </is>
       </c>
       <c r="F248" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画の編集ページにはアクセスできない</t>
+          <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
         </is>
       </c>
       <c r="G248" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画の編集ページのURLに直接アクセスする</t>
+          <t>1.target_dateが3日後・ステータス進行中の計画を用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
       <c r="H248" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、編集ページは表示されない</t>
-        </is>
-      </c>
-      <c r="I248" s="4" t="n"/>
+          <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_before)・title(「読書期限のお知らせ」)・body(「「(書籍名)」の読書期限まであと3日です。」)が含まれる</t>
+        </is>
+      </c>
+      <c r="I248" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="4" t="n"/>
@@ -8116,158 +8126,158 @@
       <c r="D249" s="4" t="n"/>
       <c r="E249" s="7" t="inlineStr">
         <is>
-          <t>18-1-11</t>
+          <t>19-1-2</t>
         </is>
       </c>
       <c r="F249" s="7" t="inlineStr">
         <is>
-          <t>同じ書籍に「進行中」の計画がある場合、「期限切れ」の計画は編集・更新できない</t>
+          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
         </is>
       </c>
       <c r="G249" s="7" t="inlineStr">
-        <is>
-          <t>1.同じ書籍について、「期限切れ」の計画と「進行中」の計画をそれぞれ用意する
-2.「期限切れ」の計画の編集ページのURLに直接アクセスする
-3.「期限切れ」の計画に対して、直接更新リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H249" s="7" t="inlineStr">
-        <is>
-          <t>いずれも403Forbiddenになり、「期限切れ」の計画のステータス・期日は変更されない（同じ書籍の「進行中」の計画が2件になることを防ぐ）</t>
-        </is>
-      </c>
-      <c r="I249" s="4" t="n"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="5" t="n"/>
-      <c r="B250" s="5" t="n"/>
-      <c r="C250" s="5" t="n"/>
-      <c r="D250" s="5" t="n"/>
-      <c r="E250" s="7" t="inlineStr">
-        <is>
-          <t>18-1-12</t>
-        </is>
-      </c>
-      <c r="F250" s="7" t="inlineStr">
-        <is>
-          <t>他人が作成した読書計画に不正な期日で更新しようとしても、入力エラーではなく403になる</t>
-        </is>
-      </c>
-      <c r="G250" s="7" t="inlineStr">
-        <is>
-          <t>1.他人が作成した読書計画に対して、期日を空にして直接計画更新のリクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H250" s="7" t="inlineStr">
-        <is>
-          <t>バリデーションエラーではなく403Forbiddenになり、期日は変更されない（認可チェックが入力チェックより先に行われる）</t>
-        </is>
-      </c>
-      <c r="I250" s="5" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B251" s="7" t="inlineStr">
-        <is>
-          <t>リマインダーバッチ</t>
-        </is>
-      </c>
-      <c r="C251" s="7" t="inlineStr">
-        <is>
-          <t>19-1</t>
-        </is>
-      </c>
-      <c r="D251" s="7" t="inlineStr">
-        <is>
-          <t>日次バッチ(reading-plans:daily)によるリマインダー通知</t>
-        </is>
-      </c>
-      <c r="E251" s="7" t="inlineStr">
-        <is>
-          <t>19-1-1</t>
-        </is>
-      </c>
-      <c r="F251" s="7" t="inlineStr">
-        <is>
-          <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
-        </is>
-      </c>
-      <c r="G251" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが3日後・ステータス進行中の計画を用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
-        </is>
-      </c>
-      <c r="H251" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_before)・title(「読書期限のお知らせ」)・body(「「(書籍名)」の読書期限まであと3日です。」)が含まれる</t>
-        </is>
-      </c>
-      <c r="I251" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="4" t="n"/>
-      <c r="B252" s="4" t="n"/>
-      <c r="C252" s="4" t="n"/>
-      <c r="D252" s="4" t="n"/>
-      <c r="E252" s="7" t="inlineStr">
-        <is>
-          <t>19-1-2</t>
-        </is>
-      </c>
-      <c r="F252" s="7" t="inlineStr">
-        <is>
-          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
-        </is>
-      </c>
-      <c r="G252" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが本日・ステータス進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H252" s="7" t="inlineStr">
+      <c r="H249" s="7" t="inlineStr">
         <is>
           <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される。通知のdataには、plan_id・book_title・timing(on_due_date)・title(「読書期限当日のお知らせ」)・body(「「(書籍名)」の読書期限は本日までです。」)が含まれる</t>
         </is>
       </c>
-      <c r="I252" s="4" t="n"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="4" t="n"/>
-      <c r="B253" s="4" t="n"/>
-      <c r="C253" s="4" t="n"/>
-      <c r="D253" s="4" t="n"/>
-      <c r="E253" s="7" t="inlineStr">
+      <c r="I249" s="4" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="n"/>
+      <c r="B250" s="4" t="n"/>
+      <c r="C250" s="4" t="n"/>
+      <c r="D250" s="4" t="n"/>
+      <c r="E250" s="7" t="inlineStr">
         <is>
           <t>19-1-3</t>
         </is>
       </c>
-      <c r="F253" s="7" t="inlineStr">
+      <c r="F250" s="7" t="inlineStr">
         <is>
           <t>期限切れから3日後の計画に再エンゲージメント通知が送信される</t>
         </is>
       </c>
-      <c r="G253" s="7" t="inlineStr">
+      <c r="G250" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日前・ステータス期限切れの計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
+      <c r="H250" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
+        </is>
+      </c>
+      <c r="I250" s="4" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="n"/>
+      <c r="B251" s="4" t="n"/>
+      <c r="C251" s="4" t="n"/>
+      <c r="D251" s="4" t="n"/>
+      <c r="E251" s="7" t="inlineStr">
+        <is>
+          <t>19-1-4</t>
+        </is>
+      </c>
+      <c r="F251" s="7" t="inlineStr">
+        <is>
+          <t>いずれの条件にも該当しない計画には通知が送信されない</t>
+        </is>
+      </c>
+      <c r="G251" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
+2.reading-plans:dailyを実行する</t>
+        </is>
+      </c>
+      <c r="H251" s="7" t="inlineStr">
+        <is>
+          <t>その計画のユーザーに通知が送信されない</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="5" t="n"/>
+      <c r="B252" s="5" t="n"/>
+      <c r="C252" s="5" t="n"/>
+      <c r="D252" s="5" t="n"/>
+      <c r="E252" s="7" t="inlineStr">
+        <is>
+          <t>19-1-5</t>
+        </is>
+      </c>
+      <c r="F252" s="7" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」の計画には、期日の条件に合っていても通知が送信されない</t>
+        </is>
+      </c>
+      <c r="G252" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日後・本日・3日前で、ステータスが完了の計画をそれぞれ用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+        </is>
+      </c>
+      <c r="H252" s="7" t="inlineStr">
+        <is>
+          <t>いずれの計画のユーザーにも通知が送信されない</t>
+        </is>
+      </c>
+      <c r="I252" s="5" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B253" s="7" t="inlineStr">
+        <is>
+          <t>自動失効バッチ</t>
+        </is>
+      </c>
+      <c r="C253" s="7" t="inlineStr">
+        <is>
+          <t>20-1</t>
+        </is>
+      </c>
+      <c r="D253" s="7" t="inlineStr">
+        <is>
+          <t>日次バッチ(reading-plans:daily)による自動失効処理</t>
+        </is>
+      </c>
+      <c r="E253" s="7" t="inlineStr">
+        <is>
+          <t>20-1-1</t>
+        </is>
+      </c>
+      <c r="F253" s="7" t="inlineStr">
+        <is>
+          <t>期日を過ぎた「進行中」の計画が「期限切れ」に更新される</t>
+        </is>
+      </c>
+      <c r="G253" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが過去・ステータス進行中の計画を用意する
+2.reading-plans:dailyを実行する</t>
+        </is>
+      </c>
       <c r="H253" s="7" t="inlineStr">
         <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
-        </is>
-      </c>
-      <c r="I253" s="4" t="n"/>
+          <t>対象の計画のstatusが「期限切れ」に更新される</t>
+        </is>
+      </c>
+      <c r="I253" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="4" t="n"/>
@@ -8276,130 +8286,122 @@
       <c r="D254" s="4" t="n"/>
       <c r="E254" s="7" t="inlineStr">
         <is>
-          <t>19-1-4</t>
+          <t>20-1-2</t>
         </is>
       </c>
       <c r="F254" s="7" t="inlineStr">
         <is>
-          <t>いずれの条件にも該当しない計画には通知が送信されない</t>
+          <t>期日が今日以降の「進行中」の計画は失効しない</t>
         </is>
       </c>
       <c r="G254" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
+          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H254" s="7" t="inlineStr">
         <is>
-          <t>その計画のユーザーに通知が送信されない</t>
+          <t>その計画のstatusは「進行中」のまま変化しない</t>
         </is>
       </c>
       <c r="I254" s="4" t="n"/>
     </row>
     <row r="255">
-      <c r="A255" s="5" t="n"/>
-      <c r="B255" s="5" t="n"/>
-      <c r="C255" s="5" t="n"/>
-      <c r="D255" s="5" t="n"/>
+      <c r="A255" s="4" t="n"/>
+      <c r="B255" s="4" t="n"/>
+      <c r="C255" s="4" t="n"/>
+      <c r="D255" s="4" t="n"/>
       <c r="E255" s="7" t="inlineStr">
         <is>
-          <t>19-1-5</t>
+          <t>20-1-3</t>
         </is>
       </c>
       <c r="F255" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画には、期日の条件に合っていても通知が送信されない</t>
+          <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
         </is>
       </c>
       <c r="G255" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが3日後・本日・3日前で、ステータスが完了の計画をそれぞれ用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+          <t>1.完了済み・期限切れの計画をそれぞれ用意する
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H255" s="7" t="inlineStr">
         <is>
-          <t>いずれの計画のユーザーにも通知が送信されない</t>
-        </is>
-      </c>
-      <c r="I255" s="5" t="n"/>
+          <t>いずれの計画もstatusが変化しない</t>
+        </is>
+      </c>
+      <c r="I255" s="4" t="n"/>
     </row>
     <row r="256">
-      <c r="A256" s="7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B256" s="7" t="inlineStr">
-        <is>
-          <t>自動失効バッチ</t>
-        </is>
-      </c>
-      <c r="C256" s="7" t="inlineStr">
-        <is>
-          <t>20-1</t>
-        </is>
-      </c>
-      <c r="D256" s="7" t="inlineStr">
-        <is>
-          <t>日次バッチ(reading-plans:daily)による自動失効処理</t>
-        </is>
-      </c>
+      <c r="A256" s="4" t="n"/>
+      <c r="B256" s="4" t="n"/>
+      <c r="C256" s="5" t="n"/>
+      <c r="D256" s="5" t="n"/>
       <c r="E256" s="7" t="inlineStr">
         <is>
-          <t>20-1-1</t>
+          <t>20-1-4</t>
         </is>
       </c>
       <c r="F256" s="7" t="inlineStr">
         <is>
-          <t>期日を過ぎた「進行中」の計画が「期限切れ」に更新される</t>
+          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
         </is>
       </c>
       <c r="G256" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが過去・ステータス進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
+          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
+2.DBを直接確認する</t>
         </is>
       </c>
       <c r="H256" s="7" t="inlineStr">
         <is>
-          <t>対象の計画のstatusが「期限切れ」に更新される</t>
-        </is>
-      </c>
-      <c r="I256" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
-        </is>
-      </c>
+          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
+        </is>
+      </c>
+      <c r="I256" s="5" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n"/>
       <c r="B257" s="4" t="n"/>
-      <c r="C257" s="4" t="n"/>
-      <c r="D257" s="4" t="n"/>
+      <c r="C257" s="7" t="inlineStr">
+        <is>
+          <t>20-2</t>
+        </is>
+      </c>
+      <c r="D257" s="7" t="inlineStr">
+        <is>
+          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
+        </is>
+      </c>
       <c r="E257" s="7" t="inlineStr">
         <is>
-          <t>20-1-2</t>
+          <t>20-2-1</t>
         </is>
       </c>
       <c r="F257" s="7" t="inlineStr">
         <is>
-          <t>期日が今日以降の「進行中」の計画は失効しない</t>
+          <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
         </is>
       </c>
       <c r="G257" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
+          <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
       <c r="H257" s="7" t="inlineStr">
         <is>
-          <t>その計画のstatusは「進行中」のまま変化しない</t>
-        </is>
-      </c>
-      <c r="I257" s="4" t="n"/>
+          <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I257" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="4" t="n"/>
@@ -8408,23 +8410,23 @@
       <c r="D258" s="4" t="n"/>
       <c r="E258" s="7" t="inlineStr">
         <is>
-          <t>20-1-3</t>
+          <t>20-2-2</t>
         </is>
       </c>
       <c r="F258" s="7" t="inlineStr">
         <is>
-          <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
+          <t>期限切れへの更新が、通知対象の抽出より先に行われる</t>
         </is>
       </c>
       <c r="G258" s="7" t="inlineStr">
         <is>
-          <t>1.完了済み・期限切れの計画をそれぞれ用意する
-2.reading-plans:dailyを実行する</t>
+          <t>1.target_dateが3日前で、ステータスが「進行中」のまま(未更新)の計画を用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
       <c r="H258" s="7" t="inlineStr">
         <is>
-          <t>いずれの計画もstatusが変化しない</t>
+          <t>計画のstatusが「期限切れ」に更新され、そのユーザーに再エンゲージメント(re_engagement)通知が送信される</t>
         </is>
       </c>
       <c r="I258" s="4" t="n"/>
@@ -8432,199 +8434,198 @@
     <row r="259">
       <c r="A259" s="4" t="n"/>
       <c r="B259" s="4" t="n"/>
-      <c r="C259" s="5" t="n"/>
-      <c r="D259" s="5" t="n"/>
+      <c r="C259" s="4" t="n"/>
+      <c r="D259" s="4" t="n"/>
       <c r="E259" s="7" t="inlineStr">
         <is>
-          <t>20-1-4</t>
+          <t>20-2-3</t>
         </is>
       </c>
       <c r="F259" s="7" t="inlineStr">
         <is>
-          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+          <t>reading-plans:dailyが毎日20:00に実行されるようスケジュールされている</t>
         </is>
       </c>
       <c r="G259" s="7" t="inlineStr">
         <is>
-          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
-2.DBを直接確認する</t>
+          <t>1.アプリケーションのスケジュール(Illuminate\Console\Scheduling\Schedule)から、登録済みのイベントを取得する</t>
         </is>
       </c>
       <c r="H259" s="7" t="inlineStr">
         <is>
-          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
-        </is>
-      </c>
-      <c r="I259" s="5" t="n"/>
+          <t>reading-plans:dailyのイベントが登録されており、cron式が毎日20:00(0 20 * * *)になっている</t>
+        </is>
+      </c>
+      <c r="I259" s="4" t="n"/>
     </row>
     <row r="260">
-      <c r="A260" s="4" t="n"/>
-      <c r="B260" s="4" t="n"/>
-      <c r="C260" s="7" t="inlineStr">
-        <is>
-          <t>20-2</t>
-        </is>
-      </c>
-      <c r="D260" s="7" t="inlineStr">
-        <is>
-          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
-        </is>
-      </c>
+      <c r="A260" s="5" t="n"/>
+      <c r="B260" s="5" t="n"/>
+      <c r="C260" s="5" t="n"/>
+      <c r="D260" s="5" t="n"/>
       <c r="E260" s="7" t="inlineStr">
         <is>
-          <t>20-2-1</t>
+          <t>20-2-4</t>
         </is>
       </c>
       <c r="F260" s="7" t="inlineStr">
         <is>
-          <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
+          <t>日次バッチで送信した通知がnotificationsテーブルに保存され、通知一覧に表示される</t>
         </is>
       </c>
       <c r="G260" s="7" t="inlineStr">
         <is>
-          <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+          <t>1.target_dateが3日後(期日の3日前)・ステータス進行中の計画を用意する
+2.Notification::fake()を使わずに reading-plans:daily を実行する
+3.計画のユーザーで通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H260" s="7" t="inlineStr">
         <is>
-          <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I260" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
-        </is>
-      </c>
+          <t>notificationsテーブルにReadingPlanReminderの通知(未読、dataのplan_id・timingが対象の計画のもの)が1件保存され、通知一覧に「読書期限のお知らせ」と本文が未読として表示される</t>
+        </is>
+      </c>
+      <c r="I260" s="5" t="n"/>
     </row>
     <row r="261">
-      <c r="A261" s="4" t="n"/>
-      <c r="B261" s="4" t="n"/>
-      <c r="C261" s="4" t="n"/>
-      <c r="D261" s="4" t="n"/>
-      <c r="E261" s="7" t="inlineStr">
-        <is>
-          <t>20-2-2</t>
-        </is>
-      </c>
-      <c r="F261" s="7" t="inlineStr">
-        <is>
-          <t>期限切れへの更新が、通知対象の抽出より先に行われる</t>
-        </is>
-      </c>
-      <c r="G261" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが3日前で、ステータスが「進行中」のまま(未更新)の計画を用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
-        </is>
-      </c>
-      <c r="H261" s="7" t="inlineStr">
-        <is>
-          <t>計画のstatusが「期限切れ」に更新され、そのユーザーに再エンゲージメント(re_engagement)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I261" s="4" t="n"/>
+      <c r="A261" s="9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B261" s="9" t="inlineStr">
+        <is>
+          <t>通知</t>
+        </is>
+      </c>
+      <c r="C261" s="9" t="inlineStr">
+        <is>
+          <t>21-1</t>
+        </is>
+      </c>
+      <c r="D261" s="9" t="inlineStr">
+        <is>
+          <t>通知の既読化</t>
+        </is>
+      </c>
+      <c r="E261" s="9" t="inlineStr">
+        <is>
+          <t>21-1-1</t>
+        </is>
+      </c>
+      <c r="F261" s="9" t="inlineStr">
+        <is>
+          <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
+        </is>
+      </c>
+      <c r="G261" s="9" t="inlineStr">
+        <is>
+          <t>1.未ログイン状態でPOST /notifications/{id}/read に直接リクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H261" s="9" t="inlineStr">
+        <is>
+          <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
+        </is>
+      </c>
+      <c r="I261" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="4" t="n"/>
       <c r="B262" s="4" t="n"/>
       <c r="C262" s="4" t="n"/>
       <c r="D262" s="4" t="n"/>
-      <c r="E262" s="7" t="inlineStr">
-        <is>
-          <t>20-2-3</t>
-        </is>
-      </c>
-      <c r="F262" s="7" t="inlineStr">
-        <is>
-          <t>reading-plans:dailyが毎日20:00に実行されるようスケジュールされている</t>
-        </is>
-      </c>
-      <c r="G262" s="7" t="inlineStr">
-        <is>
-          <t>1.アプリケーションのスケジュール(Illuminate\Console\Scheduling\Schedule)から、登録済みのイベントを取得する</t>
-        </is>
-      </c>
-      <c r="H262" s="7" t="inlineStr">
-        <is>
-          <t>reading-plans:dailyのイベントが登録されており、cron式が毎日20:00(0 20 * * *)になっている</t>
+      <c r="E262" s="9" t="inlineStr">
+        <is>
+          <t>21-1-2</t>
+        </is>
+      </c>
+      <c r="F262" s="9" t="inlineStr">
+        <is>
+          <t>自分の通知を既読にできる</t>
+        </is>
+      </c>
+      <c r="G262" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての未読通知を用意する
+2.その通知に対してPOST /notifications/{id}/read を送信する</t>
+        </is>
+      </c>
+      <c r="H262" s="9" t="inlineStr">
+        <is>
+          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
         </is>
       </c>
       <c r="I262" s="4" t="n"/>
     </row>
     <row r="263">
-      <c r="A263" s="5" t="n"/>
-      <c r="B263" s="5" t="n"/>
+      <c r="A263" s="4" t="n"/>
+      <c r="B263" s="4" t="n"/>
       <c r="C263" s="5" t="n"/>
       <c r="D263" s="5" t="n"/>
-      <c r="E263" s="7" t="inlineStr">
-        <is>
-          <t>20-2-4</t>
-        </is>
-      </c>
-      <c r="F263" s="7" t="inlineStr">
-        <is>
-          <t>日次バッチで送信した通知がnotificationsテーブルに保存され、通知一覧に表示される</t>
-        </is>
-      </c>
-      <c r="G263" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが3日後(期日の3日前)・ステータス進行中の計画を用意する
-2.Notification::fake()を使わずに reading-plans:daily を実行する
-3.計画のユーザーで通知一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H263" s="7" t="inlineStr">
-        <is>
-          <t>notificationsテーブルにReadingPlanReminderの通知(未読、dataのplan_id・timingが対象の計画のもの)が1件保存され、通知一覧に「読書期限のお知らせ」と本文が未読として表示される</t>
+      <c r="E263" s="9" t="inlineStr">
+        <is>
+          <t>21-1-3</t>
+        </is>
+      </c>
+      <c r="F263" s="9" t="inlineStr">
+        <is>
+          <t>他ユーザーの通知は既読にできない</t>
+        </is>
+      </c>
+      <c r="G263" s="9" t="inlineStr">
+        <is>
+          <t>1.他ユーザー宛ての通知を用意する
+2.そのIDに対してPOST /notifications/{id}/read を送信する</t>
+        </is>
+      </c>
+      <c r="H263" s="9" t="inlineStr">
+        <is>
+          <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
         </is>
       </c>
       <c r="I263" s="5" t="n"/>
     </row>
     <row r="264">
-      <c r="A264" s="9" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B264" s="9" t="inlineStr">
-        <is>
-          <t>通知</t>
-        </is>
-      </c>
+      <c r="A264" s="4" t="n"/>
+      <c r="B264" s="4" t="n"/>
       <c r="C264" s="9" t="inlineStr">
         <is>
-          <t>21-1</t>
+          <t>21-2</t>
         </is>
       </c>
       <c r="D264" s="9" t="inlineStr">
         <is>
-          <t>通知の既読化</t>
+          <t>通知一覧</t>
         </is>
       </c>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>21-1-1</t>
+          <t>21-2-1</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
+          <t>未ログインの場合、通知一覧にアクセスできない</t>
         </is>
       </c>
       <c r="G264" s="9" t="inlineStr">
         <is>
-          <t>1.未ログイン状態でPOST /notifications/{id}/read に直接リクエストを送信する</t>
+          <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H264" s="9" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
+          <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
       <c r="I264" s="9" t="inlineStr">
         <is>
-          <t>tests/Feature/Notification/NotificationTest.php</t>
+          <t>tests/Feature/Notification/NotificationIndexTest.php</t>
         </is>
       </c>
     </row>
@@ -8635,23 +8636,23 @@
       <c r="D265" s="4" t="n"/>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>21-1-2</t>
+          <t>21-2-2</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>自分の通知を既読にできる</t>
+          <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
         </is>
       </c>
       <c r="G265" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての未読通知を用意する
-2.その通知に対してPOST /notifications/{id}/read を送信する</t>
+          <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
+2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H265" s="9" t="inlineStr">
         <is>
-          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
+          <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
         </is>
       </c>
       <c r="I265" s="4" t="n"/>
@@ -8659,69 +8660,58 @@
     <row r="266">
       <c r="A266" s="4" t="n"/>
       <c r="B266" s="4" t="n"/>
-      <c r="C266" s="5" t="n"/>
-      <c r="D266" s="5" t="n"/>
+      <c r="C266" s="4" t="n"/>
+      <c r="D266" s="4" t="n"/>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>21-1-3</t>
+          <t>21-2-3</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>他ユーザーの通知は既読にできない</t>
+          <t>通知が1件もない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G266" s="9" t="inlineStr">
         <is>
-          <t>1.他ユーザー宛ての通知を用意する
-2.そのIDに対してPOST /notifications/{id}/read を送信する</t>
+          <t>1.通知が1件もないユーザーでログインする
+2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H266" s="9" t="inlineStr">
         <is>
-          <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
-        </is>
-      </c>
-      <c r="I266" s="5" t="n"/>
+          <t>「通知はありません。」と表示される</t>
+        </is>
+      </c>
+      <c r="I266" s="4" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="4" t="n"/>
       <c r="B267" s="4" t="n"/>
-      <c r="C267" s="9" t="inlineStr">
-        <is>
-          <t>21-2</t>
-        </is>
-      </c>
-      <c r="D267" s="9" t="inlineStr">
-        <is>
-          <t>通知一覧</t>
-        </is>
-      </c>
+      <c r="C267" s="4" t="n"/>
+      <c r="D267" s="4" t="n"/>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>21-2-1</t>
+          <t>21-2-4</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>未ログインの場合、通知一覧にアクセスできない</t>
+          <t>通知のタイトル・本文が表示される</t>
         </is>
       </c>
       <c r="G267" s="9" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
+          <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
+2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H267" s="9" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I267" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationIndexTest.php</t>
-        </is>
-      </c>
+          <t>通知のtitleとbodyが一覧に表示される</t>
+        </is>
+      </c>
+      <c r="I267" s="4" t="n"/>
     </row>
     <row r="268">
       <c r="A268" s="4" t="n"/>
@@ -8730,23 +8720,23 @@
       <c r="D268" s="4" t="n"/>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>21-2-2</t>
+          <t>21-2-5</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
+          <t>未読と既読で表示が異なる</t>
         </is>
       </c>
       <c r="G268" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
+          <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H268" s="9" t="inlineStr">
         <is>
-          <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
+          <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
         </is>
       </c>
       <c r="I268" s="4" t="n"/>
@@ -8754,58 +8744,69 @@
     <row r="269">
       <c r="A269" s="4" t="n"/>
       <c r="B269" s="4" t="n"/>
-      <c r="C269" s="4" t="n"/>
-      <c r="D269" s="4" t="n"/>
+      <c r="C269" s="5" t="n"/>
+      <c r="D269" s="5" t="n"/>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>21-2-3</t>
+          <t>21-2-6</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>通知が1件もない場合の表示を確認する</t>
+          <t>同じ日時に作成された通知は、期日3日前→期日当日→期日3日後の順に表示される</t>
         </is>
       </c>
       <c r="G269" s="9" t="inlineStr">
         <is>
-          <t>1.通知が1件もないユーザーでログインする
+          <t>1.同じ日時に作成された、期日3日前（予告）・期日当日（最終警告）・期日3日後（再エンゲージメント）の通知と、作成日時の異なる通知を用意する
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H269" s="9" t="inlineStr">
         <is>
-          <t>「通知はありません。」と表示される</t>
-        </is>
-      </c>
-      <c r="I269" s="4" t="n"/>
+          <t>第1優先で作成日時の新しい順、作成日時が同じ通知同士は第2優先で「期日3日前→期日当日→期日3日後」の順に表示される</t>
+        </is>
+      </c>
+      <c r="I269" s="5" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="4" t="n"/>
       <c r="B270" s="4" t="n"/>
-      <c r="C270" s="4" t="n"/>
-      <c r="D270" s="4" t="n"/>
+      <c r="C270" s="9" t="inlineStr">
+        <is>
+          <t>21-3</t>
+        </is>
+      </c>
+      <c r="D270" s="9" t="inlineStr">
+        <is>
+          <t>ヘッダーの未読件数</t>
+        </is>
+      </c>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>21-2-4</t>
+          <t>21-3-1</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>通知のタイトル・本文が表示される</t>
+          <t>ヘッダーのベルアイコンに未読件数が表示される</t>
         </is>
       </c>
       <c r="G270" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
-2.通知一覧ページを開く</t>
+          <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
         </is>
       </c>
       <c r="H270" s="9" t="inlineStr">
         <is>
-          <t>通知のtitleとbodyが一覧に表示される</t>
-        </is>
-      </c>
-      <c r="I270" s="4" t="n"/>
+          <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
+        </is>
+      </c>
+      <c r="I270" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="4" t="n"/>
@@ -8814,330 +8815,232 @@
       <c r="D271" s="4" t="n"/>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>21-2-5</t>
+          <t>21-3-2</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>未読と既読で表示が異なる</t>
+          <t>通知を既読にすると、ヘッダーの未読件数が減る</t>
         </is>
       </c>
       <c r="G271" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
-2.通知一覧ページを開く</t>
+          <t>1.自分宛ての未読通知を複数件用意する
+2.そのうち1件にPOST /notifications/{id}/read を送信して既読にする
+3.画面を開き直す</t>
         </is>
       </c>
       <c r="H271" s="9" t="inlineStr">
         <is>
-          <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
+          <t>ヘッダーの未読件数が、既読にした1件分だけ減る</t>
         </is>
       </c>
       <c r="I271" s="4" t="n"/>
     </row>
     <row r="272">
-      <c r="A272" s="4" t="n"/>
-      <c r="B272" s="4" t="n"/>
+      <c r="A272" s="5" t="n"/>
+      <c r="B272" s="5" t="n"/>
       <c r="C272" s="5" t="n"/>
       <c r="D272" s="5" t="n"/>
       <c r="E272" s="9" t="inlineStr">
         <is>
-          <t>21-2-6</t>
+          <t>21-3-3</t>
         </is>
       </c>
       <c r="F272" s="9" t="inlineStr">
         <is>
-          <t>同じ日時に作成された通知は、期日3日前→期日当日→期日3日後の順に表示される</t>
+          <t>他ユーザーの通知は未読件数に含まれない</t>
         </is>
       </c>
       <c r="G272" s="9" t="inlineStr">
-        <is>
-          <t>1.同じ日時に作成された、期日3日前（予告）・期日当日（最終警告）・期日3日後（再エンゲージメント）の通知と、作成日時の異なる通知を用意する
-2.通知一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H272" s="9" t="inlineStr">
-        <is>
-          <t>第1優先で作成日時の新しい順、作成日時が同じ通知同士は第2優先で「期日3日前→期日当日→期日3日後」の順に表示される</t>
-        </is>
-      </c>
-      <c r="I272" s="5" t="n"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="4" t="n"/>
-      <c r="B273" s="4" t="n"/>
-      <c r="C273" s="9" t="inlineStr">
-        <is>
-          <t>21-3</t>
-        </is>
-      </c>
-      <c r="D273" s="9" t="inlineStr">
-        <is>
-          <t>ヘッダーの未読件数</t>
-        </is>
-      </c>
-      <c r="E273" s="9" t="inlineStr">
-        <is>
-          <t>21-3-1</t>
-        </is>
-      </c>
-      <c r="F273" s="9" t="inlineStr">
-        <is>
-          <t>ヘッダーのベルアイコンに未読件数が表示される</t>
-        </is>
-      </c>
-      <c r="G273" s="9" t="inlineStr">
-        <is>
-          <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
-        </is>
-      </c>
-      <c r="H273" s="9" t="inlineStr">
-        <is>
-          <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
-        </is>
-      </c>
-      <c r="I273" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="4" t="n"/>
-      <c r="B274" s="4" t="n"/>
-      <c r="C274" s="4" t="n"/>
-      <c r="D274" s="4" t="n"/>
-      <c r="E274" s="9" t="inlineStr">
-        <is>
-          <t>21-3-2</t>
-        </is>
-      </c>
-      <c r="F274" s="9" t="inlineStr">
-        <is>
-          <t>通知を既読にすると、ヘッダーの未読件数が減る</t>
-        </is>
-      </c>
-      <c r="G274" s="9" t="inlineStr">
-        <is>
-          <t>1.自分宛ての未読通知を複数件用意する
-2.そのうち1件にPOST /notifications/{id}/read を送信して既読にする
-3.画面を開き直す</t>
-        </is>
-      </c>
-      <c r="H274" s="9" t="inlineStr">
-        <is>
-          <t>ヘッダーの未読件数が、既読にした1件分だけ減る</t>
-        </is>
-      </c>
-      <c r="I274" s="4" t="n"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="5" t="n"/>
-      <c r="B275" s="5" t="n"/>
-      <c r="C275" s="5" t="n"/>
-      <c r="D275" s="5" t="n"/>
-      <c r="E275" s="9" t="inlineStr">
-        <is>
-          <t>21-3-3</t>
-        </is>
-      </c>
-      <c r="F275" s="9" t="inlineStr">
-        <is>
-          <t>他ユーザーの通知は未読件数に含まれない</t>
-        </is>
-      </c>
-      <c r="G275" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知と、他ユーザー宛ての未読通知をそれぞれ用意する
 2.画面を開く</t>
         </is>
       </c>
-      <c r="H275" s="9" t="inlineStr">
+      <c r="H272" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数には、自分宛ての未読通知のみが数えられる</t>
         </is>
       </c>
-      <c r="I275" s="5" t="n"/>
+      <c r="I272" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="177">
+  <mergeCells count="174">
+    <mergeCell ref="B31:B65"/>
+    <mergeCell ref="I180:I186"/>
+    <mergeCell ref="I17:I30"/>
+    <mergeCell ref="D118:D120"/>
+    <mergeCell ref="A17:A30"/>
+    <mergeCell ref="I92:I96"/>
+    <mergeCell ref="D12:D16"/>
     <mergeCell ref="B121:B124"/>
+    <mergeCell ref="B194:B201"/>
+    <mergeCell ref="I173:I179"/>
     <mergeCell ref="I70:I75"/>
-    <mergeCell ref="D267:D272"/>
-    <mergeCell ref="D164:D170"/>
-    <mergeCell ref="C216:C238"/>
+    <mergeCell ref="I97:I102"/>
+    <mergeCell ref="I209:I212"/>
+    <mergeCell ref="C121:C124"/>
+    <mergeCell ref="D253:D256"/>
+    <mergeCell ref="B236:B247"/>
+    <mergeCell ref="B173:B179"/>
+    <mergeCell ref="C31:C34"/>
+    <mergeCell ref="D173:D179"/>
+    <mergeCell ref="C89:C91"/>
     <mergeCell ref="I56:I61"/>
-    <mergeCell ref="D157:D163"/>
     <mergeCell ref="D35:D41"/>
-    <mergeCell ref="I154:I156"/>
+    <mergeCell ref="B253:B260"/>
     <mergeCell ref="C56:C61"/>
+    <mergeCell ref="A2:A16"/>
     <mergeCell ref="C42:C55"/>
-    <mergeCell ref="A2:A16"/>
-    <mergeCell ref="C157:C163"/>
+    <mergeCell ref="C161:C167"/>
+    <mergeCell ref="I253:I256"/>
+    <mergeCell ref="C118:C120"/>
     <mergeCell ref="B125:B142"/>
+    <mergeCell ref="D213:D235"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="C154:C160"/>
     <mergeCell ref="C66:C69"/>
-    <mergeCell ref="C171:C175"/>
+    <mergeCell ref="B180:B186"/>
     <mergeCell ref="D17:D30"/>
-    <mergeCell ref="C143:C145"/>
-    <mergeCell ref="C267:C272"/>
+    <mergeCell ref="D143:D150"/>
+    <mergeCell ref="A187:A193"/>
+    <mergeCell ref="I118:I120"/>
+    <mergeCell ref="C187:C193"/>
+    <mergeCell ref="C270:C272"/>
+    <mergeCell ref="I115:I117"/>
+    <mergeCell ref="I12:I16"/>
     <mergeCell ref="B111:B117"/>
-    <mergeCell ref="B212:B215"/>
-    <mergeCell ref="B216:B238"/>
-    <mergeCell ref="I143:I145"/>
+    <mergeCell ref="I76:I84"/>
+    <mergeCell ref="C115:C117"/>
+    <mergeCell ref="I248:I252"/>
+    <mergeCell ref="D85:D88"/>
+    <mergeCell ref="C35:C41"/>
+    <mergeCell ref="C180:C186"/>
     <mergeCell ref="D137:D141"/>
-    <mergeCell ref="I267:I272"/>
+    <mergeCell ref="I257:I260"/>
     <mergeCell ref="D42:D55"/>
-    <mergeCell ref="I157:I163"/>
+    <mergeCell ref="A261:A272"/>
+    <mergeCell ref="C97:C102"/>
+    <mergeCell ref="D161:D167"/>
+    <mergeCell ref="I168:I172"/>
+    <mergeCell ref="I62:I65"/>
     <mergeCell ref="D6:D8"/>
+    <mergeCell ref="I213:I235"/>
+    <mergeCell ref="I89:I91"/>
+    <mergeCell ref="I202:I208"/>
     <mergeCell ref="A111:A117"/>
-    <mergeCell ref="C154:C156"/>
-    <mergeCell ref="I89:I91"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="A202:A208"/>
+    <mergeCell ref="B89:B110"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="C248:C252"/>
     <mergeCell ref="C92:C96"/>
+    <mergeCell ref="D187:D193"/>
+    <mergeCell ref="A209:A212"/>
+    <mergeCell ref="I143:I150"/>
+    <mergeCell ref="C209:C212"/>
+    <mergeCell ref="B248:B252"/>
     <mergeCell ref="I125:I136"/>
+    <mergeCell ref="D264:D269"/>
     <mergeCell ref="D62:D65"/>
-    <mergeCell ref="A176:A182"/>
-    <mergeCell ref="D197:D204"/>
-    <mergeCell ref="D146:D153"/>
+    <mergeCell ref="C70:C75"/>
     <mergeCell ref="A31:A65"/>
     <mergeCell ref="I9:I10"/>
+    <mergeCell ref="C202:C208"/>
     <mergeCell ref="A121:A124"/>
-    <mergeCell ref="A264:A275"/>
-    <mergeCell ref="C251:C255"/>
+    <mergeCell ref="C261:C263"/>
+    <mergeCell ref="A194:A201"/>
+    <mergeCell ref="C194:C201"/>
+    <mergeCell ref="D236:D247"/>
     <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C164:C170"/>
+    <mergeCell ref="A143:A172"/>
+    <mergeCell ref="I161:I167"/>
+    <mergeCell ref="D103:D107"/>
+    <mergeCell ref="D168:D172"/>
     <mergeCell ref="I85:I88"/>
-    <mergeCell ref="I256:I259"/>
+    <mergeCell ref="C173:C179"/>
+    <mergeCell ref="B213:B235"/>
     <mergeCell ref="C85:C88"/>
+    <mergeCell ref="D89:D91"/>
     <mergeCell ref="I6:I8"/>
     <mergeCell ref="C76:C84"/>
-    <mergeCell ref="I197:I204"/>
-    <mergeCell ref="B205:B211"/>
-    <mergeCell ref="B183:B189"/>
+    <mergeCell ref="D202:D208"/>
+    <mergeCell ref="C125:C136"/>
+    <mergeCell ref="D70:D75"/>
     <mergeCell ref="B2:B16"/>
-    <mergeCell ref="D205:D211"/>
-    <mergeCell ref="C264:C266"/>
     <mergeCell ref="A125:A142"/>
+    <mergeCell ref="D209:D212"/>
+    <mergeCell ref="I187:I193"/>
+    <mergeCell ref="C108:C110"/>
     <mergeCell ref="I35:I41"/>
-    <mergeCell ref="D176:D182"/>
+    <mergeCell ref="I264:I269"/>
+    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="A180:A186"/>
     <mergeCell ref="D115:D117"/>
-    <mergeCell ref="D66:D69"/>
+    <mergeCell ref="C257:C260"/>
+    <mergeCell ref="C143:C150"/>
+    <mergeCell ref="D56:D61"/>
+    <mergeCell ref="D270:D272"/>
     <mergeCell ref="D121:D124"/>
     <mergeCell ref="D108:D110"/>
+    <mergeCell ref="A236:A247"/>
     <mergeCell ref="I111:I114"/>
+    <mergeCell ref="C236:C247"/>
+    <mergeCell ref="D194:D201"/>
+    <mergeCell ref="A66:A88"/>
     <mergeCell ref="C137:C141"/>
-    <mergeCell ref="I260:I263"/>
-    <mergeCell ref="C260:C263"/>
+    <mergeCell ref="B143:B172"/>
+    <mergeCell ref="C111:C114"/>
+    <mergeCell ref="I236:I247"/>
+    <mergeCell ref="D151:D153"/>
+    <mergeCell ref="I103:I107"/>
+    <mergeCell ref="D154:D160"/>
     <mergeCell ref="D76:D84"/>
-    <mergeCell ref="C176:C182"/>
+    <mergeCell ref="C17:C30"/>
+    <mergeCell ref="D31:D34"/>
+    <mergeCell ref="B187:B193"/>
     <mergeCell ref="I42:I55"/>
-    <mergeCell ref="I205:I211"/>
-    <mergeCell ref="C239:C250"/>
+    <mergeCell ref="D257:D260"/>
     <mergeCell ref="B118:B120"/>
+    <mergeCell ref="A89:A110"/>
+    <mergeCell ref="B261:B272"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D180:D186"/>
     <mergeCell ref="I66:I69"/>
     <mergeCell ref="D92:D96"/>
-    <mergeCell ref="I176:I182"/>
+    <mergeCell ref="B66:B88"/>
+    <mergeCell ref="I261:I263"/>
+    <mergeCell ref="D111:D114"/>
+    <mergeCell ref="I270:I272"/>
     <mergeCell ref="I121:I124"/>
+    <mergeCell ref="I108:I110"/>
+    <mergeCell ref="I137:I141"/>
     <mergeCell ref="C6:C8"/>
-    <mergeCell ref="I137:I141"/>
-    <mergeCell ref="I108:I110"/>
-    <mergeCell ref="C146:C153"/>
+    <mergeCell ref="I194:I201"/>
+    <mergeCell ref="C151:C153"/>
     <mergeCell ref="D97:D102"/>
-    <mergeCell ref="I164:I170"/>
-    <mergeCell ref="I146:I153"/>
+    <mergeCell ref="B202:B208"/>
+    <mergeCell ref="C253:C256"/>
+    <mergeCell ref="D261:D263"/>
+    <mergeCell ref="B17:B30"/>
+    <mergeCell ref="I151:I153"/>
+    <mergeCell ref="A173:A179"/>
+    <mergeCell ref="D125:D136"/>
     <mergeCell ref="A118:A120"/>
-    <mergeCell ref="D85:D88"/>
-    <mergeCell ref="B31:B65"/>
-    <mergeCell ref="A205:A211"/>
-    <mergeCell ref="C183:C189"/>
-    <mergeCell ref="A183:A189"/>
-    <mergeCell ref="I92:I96"/>
-    <mergeCell ref="A17:A30"/>
-    <mergeCell ref="I17:I30"/>
-    <mergeCell ref="D118:D120"/>
-    <mergeCell ref="D12:D16"/>
-    <mergeCell ref="D264:D266"/>
-    <mergeCell ref="D273:D275"/>
-    <mergeCell ref="I212:I215"/>
-    <mergeCell ref="I97:I102"/>
-    <mergeCell ref="C121:C124"/>
-    <mergeCell ref="A256:A263"/>
-    <mergeCell ref="C31:C34"/>
-    <mergeCell ref="C89:C91"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="B190:B196"/>
-    <mergeCell ref="D190:D196"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D260:D263"/>
-    <mergeCell ref="D183:D189"/>
-    <mergeCell ref="I118:I120"/>
-    <mergeCell ref="B239:B250"/>
-    <mergeCell ref="I115:I117"/>
-    <mergeCell ref="I12:I16"/>
-    <mergeCell ref="I264:I266"/>
-    <mergeCell ref="I76:I84"/>
-    <mergeCell ref="C205:C211"/>
-    <mergeCell ref="I273:I275"/>
-    <mergeCell ref="C115:C117"/>
-    <mergeCell ref="C35:C41"/>
-    <mergeCell ref="C256:C259"/>
-    <mergeCell ref="A197:A204"/>
-    <mergeCell ref="C97:C102"/>
-    <mergeCell ref="B251:B255"/>
-    <mergeCell ref="C197:C204"/>
-    <mergeCell ref="D251:D255"/>
-    <mergeCell ref="D216:D238"/>
-    <mergeCell ref="I62:I65"/>
-    <mergeCell ref="A216:A238"/>
-    <mergeCell ref="D212:D215"/>
-    <mergeCell ref="B89:B110"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="I183:I189"/>
-    <mergeCell ref="I239:I250"/>
-    <mergeCell ref="A239:A250"/>
-    <mergeCell ref="C70:C75"/>
-    <mergeCell ref="I171:I175"/>
-    <mergeCell ref="B256:B263"/>
-    <mergeCell ref="D103:D107"/>
-    <mergeCell ref="I216:I238"/>
-    <mergeCell ref="D89:D91"/>
-    <mergeCell ref="C125:C136"/>
-    <mergeCell ref="D70:D75"/>
-    <mergeCell ref="A190:A196"/>
-    <mergeCell ref="C108:C110"/>
-    <mergeCell ref="C190:C196"/>
-    <mergeCell ref="D56:D61"/>
-    <mergeCell ref="A66:A88"/>
-    <mergeCell ref="C111:C114"/>
-    <mergeCell ref="D256:D259"/>
-    <mergeCell ref="I103:I107"/>
-    <mergeCell ref="A251:A255"/>
-    <mergeCell ref="B197:B204"/>
-    <mergeCell ref="D171:D175"/>
-    <mergeCell ref="C17:C30"/>
-    <mergeCell ref="D31:D34"/>
-    <mergeCell ref="D143:D145"/>
-    <mergeCell ref="A212:A215"/>
-    <mergeCell ref="C212:C215"/>
-    <mergeCell ref="A89:A110"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="B66:B88"/>
-    <mergeCell ref="D111:D114"/>
-    <mergeCell ref="B264:B275"/>
-    <mergeCell ref="B143:B175"/>
-    <mergeCell ref="D239:D250"/>
-    <mergeCell ref="B17:B30"/>
-    <mergeCell ref="A143:A175"/>
-    <mergeCell ref="I251:I255"/>
-    <mergeCell ref="D125:D136"/>
-    <mergeCell ref="D154:D156"/>
+    <mergeCell ref="I154:I160"/>
+    <mergeCell ref="D248:D252"/>
+    <mergeCell ref="I31:I34"/>
+    <mergeCell ref="A253:A260"/>
     <mergeCell ref="C103:C107"/>
-    <mergeCell ref="I31:I34"/>
+    <mergeCell ref="C168:C172"/>
     <mergeCell ref="C12:C16"/>
-    <mergeCell ref="C273:C275"/>
-    <mergeCell ref="I190:I196"/>
+    <mergeCell ref="B209:B212"/>
+    <mergeCell ref="A248:A252"/>
+    <mergeCell ref="A213:A235"/>
+    <mergeCell ref="C264:C269"/>
+    <mergeCell ref="C213:C235"/>
     <mergeCell ref="C62:C65"/>
-    <mergeCell ref="B176:B182"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9197,7 +9100,7 @@
     <row r="7" ht="40" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>・「公開API」は、認証不要の書籍一覧・詳細取得API(GET /api/v1/books, /api/v1/books/{book})、Sanctumトークン認証が必要な書籍の登録・更新・削除API(POST/PUT/DELETE)、およびユーザー情報取得API(GET /api/user)を対象としています。</t>
+          <t>・「公開API」は、認証不要の書籍一覧・詳細取得API(GET /api/v1/books, /api/v1/books/{book})と、Sanctumトークン認証が必要な書籍の登録・更新・削除API(POST/PUT/DELETE)を対象としています。Laravel標準のユーザー情報取得API(GET /api/user)は本アプリでは使用していないため対象外です。</t>
         </is>
       </c>
     </row>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I272"/>
+  <dimension ref="A1:I273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -6701,10 +6701,10 @@
       <c r="I200" s="4" t="n"/>
     </row>
     <row r="201">
-      <c r="A201" s="5" t="n"/>
-      <c r="B201" s="5" t="n"/>
-      <c r="C201" s="5" t="n"/>
-      <c r="D201" s="5" t="n"/>
+      <c r="A201" s="4" t="n"/>
+      <c r="B201" s="4" t="n"/>
+      <c r="C201" s="4" t="n"/>
+      <c r="D201" s="4" t="n"/>
       <c r="E201" s="7" t="inlineStr">
         <is>
           <t>14-1-8</t>
@@ -6726,81 +6726,82 @@
           <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
         </is>
       </c>
-      <c r="I201" s="5" t="n"/>
+      <c r="I201" s="4" t="n"/>
     </row>
     <row r="202">
-      <c r="A202" s="7" t="inlineStr">
+      <c r="A202" s="5" t="n"/>
+      <c r="B202" s="5" t="n"/>
+      <c r="C202" s="5" t="n"/>
+      <c r="D202" s="5" t="n"/>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>14-1-9</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>Google Books APIに接続できない場合(接続失敗・タイムアウト)も、502エラーが返る</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>1.Http::fake()で、Google Books APIへの接続が失敗する(ConnectExceptionを投げる)ようモックする
+2.未登録ISBNでリクエストする</t>
+        </is>
+      </c>
+      <c r="H202" s="7" t="inlineStr">
+        <is>
+          <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
+        </is>
+      </c>
+      <c r="I202" s="5" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B202" s="7" t="inlineStr">
+      <c r="B203" s="7" t="inlineStr">
         <is>
           <t>マイ読書レポート</t>
         </is>
       </c>
-      <c r="C202" s="7" t="inlineStr">
+      <c r="C203" s="7" t="inlineStr">
         <is>
           <t>15-1</t>
         </is>
       </c>
-      <c r="D202" s="7" t="inlineStr">
+      <c r="D203" s="7" t="inlineStr">
         <is>
           <t>読書統計の表示</t>
         </is>
       </c>
-      <c r="E202" s="7" t="inlineStr">
+      <c r="E203" s="7" t="inlineStr">
         <is>
           <t>15-1-1</t>
         </is>
       </c>
-      <c r="F202" s="7" t="inlineStr">
+      <c r="F203" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
         </is>
       </c>
-      <c r="G202" s="7" t="inlineStr">
+      <c r="G203" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で/reportsを開く</t>
         </is>
       </c>
-      <c r="H202" s="7" t="inlineStr">
+      <c r="H203" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I202" s="7" t="inlineStr">
+      <c r="I203" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Report/ReportTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="4" t="n"/>
-      <c r="B203" s="4" t="n"/>
-      <c r="C203" s="4" t="n"/>
-      <c r="D203" s="4" t="n"/>
-      <c r="E203" s="7" t="inlineStr">
-        <is>
-          <t>15-1-2</t>
-        </is>
-      </c>
-      <c r="F203" s="7" t="inlineStr">
-        <is>
-          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
-        </is>
-      </c>
-      <c r="G203" s="7" t="inlineStr">
-        <is>
-          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
-        </is>
-      </c>
-      <c r="H203" s="7" t="inlineStr">
-        <is>
-          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
-        </is>
-      </c>
-      <c r="I203" s="4" t="n"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="n"/>
@@ -6809,22 +6810,22 @@
       <c r="D204" s="4" t="n"/>
       <c r="E204" s="7" t="inlineStr">
         <is>
-          <t>15-1-3</t>
+          <t>15-1-2</t>
         </is>
       </c>
       <c r="F204" s="7" t="inlineStr">
         <is>
-          <t>評価分布(★1〜★5)が正しく表示される</t>
+          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
         </is>
       </c>
       <c r="G204" s="7" t="inlineStr">
         <is>
-          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
+          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H204" s="7" t="inlineStr">
         <is>
-          <t>各評価の件数が実データと一致して表示される</t>
+          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
         </is>
       </c>
       <c r="I204" s="4" t="n"/>
@@ -6836,22 +6837,22 @@
       <c r="D205" s="4" t="n"/>
       <c r="E205" s="7" t="inlineStr">
         <is>
-          <t>15-1-4</t>
+          <t>15-1-3</t>
         </is>
       </c>
       <c r="F205" s="7" t="inlineStr">
         <is>
-          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
+          <t>評価分布(★1〜★5)が正しく表示される</t>
         </is>
       </c>
       <c r="G205" s="7" t="inlineStr">
         <is>
-          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
+          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H205" s="7" t="inlineStr">
         <is>
-          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
+          <t>各評価の件数が実データと一致して表示される</t>
         </is>
       </c>
       <c r="I205" s="4" t="n"/>
@@ -6863,22 +6864,22 @@
       <c r="D206" s="4" t="n"/>
       <c r="E206" s="7" t="inlineStr">
         <is>
-          <t>15-1-5</t>
+          <t>15-1-4</t>
         </is>
       </c>
       <c r="F206" s="7" t="inlineStr">
         <is>
-          <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
+          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
         </is>
       </c>
       <c r="G206" s="7" t="inlineStr">
         <is>
-          <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
+          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
+          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
         </is>
       </c>
       <c r="I206" s="4" t="n"/>
@@ -6890,127 +6891,127 @@
       <c r="D207" s="4" t="n"/>
       <c r="E207" s="7" t="inlineStr">
         <is>
+          <t>15-1-5</t>
+        </is>
+      </c>
+      <c r="F207" s="7" t="inlineStr">
+        <is>
+          <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="inlineStr">
+        <is>
+          <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
+        </is>
+      </c>
+      <c r="H207" s="7" t="inlineStr">
+        <is>
+          <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
+        </is>
+      </c>
+      <c r="I207" s="4" t="n"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="n"/>
+      <c r="B208" s="4" t="n"/>
+      <c r="C208" s="4" t="n"/>
+      <c r="D208" s="4" t="n"/>
+      <c r="E208" s="7" t="inlineStr">
+        <is>
           <t>15-1-6</t>
         </is>
       </c>
-      <c r="F207" s="7" t="inlineStr">
+      <c r="F208" s="7" t="inlineStr">
         <is>
           <t>レビューを1件も投稿していない場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G207" s="7" t="inlineStr">
+      <c r="G208" s="7" t="inlineStr">
         <is>
           <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H207" s="7" t="inlineStr">
+      <c r="H208" s="7" t="inlineStr">
         <is>
           <t>総レビュー数・読了冊数が0（平均評価の集計値は0で、画面上は「-」と表示）となり、TOP5一覧には「4星以上の書籍がありません」「ジャンルが設定された書籍のレビューがありません」と表示される</t>
         </is>
       </c>
-      <c r="I207" s="4" t="n"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="5" t="n"/>
-      <c r="B208" s="5" t="n"/>
-      <c r="C208" s="5" t="n"/>
-      <c r="D208" s="5" t="n"/>
-      <c r="E208" s="7" t="inlineStr">
+      <c r="I208" s="4" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="5" t="n"/>
+      <c r="B209" s="5" t="n"/>
+      <c r="C209" s="5" t="n"/>
+      <c r="D209" s="5" t="n"/>
+      <c r="E209" s="7" t="inlineStr">
         <is>
           <t>15-1-7</t>
         </is>
       </c>
-      <c r="F208" s="7" t="inlineStr">
+      <c r="F209" s="7" t="inlineStr">
         <is>
           <t>ジャンル別評価傾向で、平均評価が同じジャンルはレビュー件数の多い順に表示される</t>
         </is>
       </c>
-      <c r="G208" s="7" t="inlineStr">
+      <c r="G209" s="7" t="inlineStr">
         <is>
           <t>1.平均評価が同じで、レビュー件数が異なる2つのジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H208" s="7" t="inlineStr">
+      <c r="H209" s="7" t="inlineStr">
         <is>
           <t>平均評価が同じジャンル同士は、レビュー件数の多い順に表示される</t>
         </is>
       </c>
-      <c r="I208" s="5" t="n"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="7" t="inlineStr">
+      <c r="I209" s="5" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B209" s="7" t="inlineStr">
+      <c r="B210" s="7" t="inlineStr">
         <is>
           <t>Sanctum認証</t>
         </is>
       </c>
-      <c r="C209" s="7" t="inlineStr">
+      <c r="C210" s="7" t="inlineStr">
         <is>
           <t>16-1</t>
         </is>
       </c>
-      <c r="D209" s="7" t="inlineStr">
+      <c r="D210" s="7" t="inlineStr">
         <is>
           <t>AP06:SanctumAPIトークン認証</t>
         </is>
       </c>
-      <c r="E209" s="7" t="inlineStr">
+      <c r="E210" s="7" t="inlineStr">
         <is>
           <t>16-1-1</t>
         </is>
       </c>
-      <c r="F209" s="7" t="inlineStr">
+      <c r="F210" s="7" t="inlineStr">
         <is>
           <t>有効なpersonal access tokenを付与すると、書き込み系API(POST /api/v1/books)を利用できる</t>
         </is>
       </c>
-      <c r="G209" s="7" t="inlineStr">
+      <c r="G210" s="7" t="inlineStr">
         <is>
           <t>1.$user-&gt;createToken()でトークンを発行する
 2.Authorization: Bearer {token}を付与して、正しい入力値でPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
-      <c r="H209" s="7" t="inlineStr">
+      <c r="H210" s="7" t="inlineStr">
         <is>
           <t>201が返り、トークンの持ち主を登録者(user_id)として書籍が登録される</t>
         </is>
       </c>
-      <c r="I209" s="7" t="inlineStr">
+      <c r="I210" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="4" t="n"/>
-      <c r="B210" s="4" t="n"/>
-      <c r="C210" s="4" t="n"/>
-      <c r="D210" s="4" t="n"/>
-      <c r="E210" s="7" t="inlineStr">
-        <is>
-          <t>16-1-2</t>
-        </is>
-      </c>
-      <c r="F210" s="7" t="inlineStr">
-        <is>
-          <t>トークンなしで書き込み系API(POST/PUT/DELETE)にアクセスすると401が返る</t>
-        </is>
-      </c>
-      <c r="G210" s="7" t="inlineStr">
-        <is>
-          <t>1.Authorizationヘッダーを付与せずに、POST /api/v1/books、PUT・DELETE /api/v1/books/{book}にそれぞれアクセスする</t>
-        </is>
-      </c>
-      <c r="H210" s="7" t="inlineStr">
-        <is>
-          <t>いずれも401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録・更新・削除されない</t>
-        </is>
-      </c>
-      <c r="I210" s="4" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="4" t="n"/>
@@ -7019,128 +7020,127 @@
       <c r="D211" s="4" t="n"/>
       <c r="E211" s="7" t="inlineStr">
         <is>
+          <t>16-1-2</t>
+        </is>
+      </c>
+      <c r="F211" s="7" t="inlineStr">
+        <is>
+          <t>トークンなしで書き込み系API(POST/PUT/DELETE)にアクセスすると401が返る</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="inlineStr">
+        <is>
+          <t>1.Authorizationヘッダーを付与せずに、POST /api/v1/books、PUT・DELETE /api/v1/books/{book}にそれぞれアクセスする</t>
+        </is>
+      </c>
+      <c r="H211" s="7" t="inlineStr">
+        <is>
+          <t>いずれも401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録・更新・削除されない</t>
+        </is>
+      </c>
+      <c r="I211" s="4" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="n"/>
+      <c r="B212" s="4" t="n"/>
+      <c r="C212" s="4" t="n"/>
+      <c r="D212" s="4" t="n"/>
+      <c r="E212" s="7" t="inlineStr">
+        <is>
           <t>16-1-3</t>
         </is>
       </c>
-      <c r="F211" s="7" t="inlineStr">
+      <c r="F212" s="7" t="inlineStr">
         <is>
           <t>不正な(存在しない)トークンで書き込み系API(POST/PUT/DELETE)にアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G211" s="7" t="inlineStr">
+      <c r="G212" s="7" t="inlineStr">
         <is>
           <t>1.ランダムな文字列をBearerトークンとして付与し、POST /api/v1/books、PUT・DELETE /api/v1/books/{book}にそれぞれアクセスする</t>
         </is>
       </c>
-      <c r="H211" s="7" t="inlineStr">
+      <c r="H212" s="7" t="inlineStr">
         <is>
           <t>いずれも401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録・更新・削除されない</t>
         </is>
       </c>
-      <c r="I211" s="4" t="n"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="5" t="n"/>
-      <c r="B212" s="5" t="n"/>
-      <c r="C212" s="5" t="n"/>
-      <c r="D212" s="5" t="n"/>
-      <c r="E212" s="7" t="inlineStr">
+      <c r="I212" s="4" t="n"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="5" t="n"/>
+      <c r="B213" s="5" t="n"/>
+      <c r="C213" s="5" t="n"/>
+      <c r="D213" s="5" t="n"/>
+      <c r="E213" s="7" t="inlineStr">
         <is>
           <t>16-1-4</t>
         </is>
       </c>
-      <c r="F212" s="7" t="inlineStr">
+      <c r="F213" s="7" t="inlineStr">
         <is>
           <t>削除済み(失効済み)のトークンで書き込み系API(POST/PUT/DELETE)にアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G212" s="7" t="inlineStr">
+      <c r="G213" s="7" t="inlineStr">
         <is>
           <t>1.書籍の登録者のトークンを発行し、そのトークンを削除する
 2.そのトークンで、POST /api/v1/books、PUT・DELETE /api/v1/books/{book}(自分の書籍)にそれぞれアクセスする</t>
         </is>
       </c>
-      <c r="H212" s="7" t="inlineStr">
+      <c r="H213" s="7" t="inlineStr">
         <is>
           <t>いずれも401 Unauthorizedが返り、「認証が必要です」が返る。登録者本人のトークンでも、失効後は書籍を更新・削除できない</t>
         </is>
       </c>
-      <c r="I212" s="5" t="n"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="7" t="inlineStr">
+      <c r="I213" s="5" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B213" s="7" t="inlineStr">
+      <c r="B214" s="7" t="inlineStr">
         <is>
           <t>読書計画</t>
         </is>
       </c>
-      <c r="C213" s="7" t="inlineStr">
+      <c r="C214" s="7" t="inlineStr">
         <is>
           <t>17-1</t>
         </is>
       </c>
-      <c r="D213" s="7" t="inlineStr">
+      <c r="D214" s="7" t="inlineStr">
         <is>
           <t>読書計画の作成・一覧・読了・削除</t>
         </is>
       </c>
-      <c r="E213" s="7" t="inlineStr">
+      <c r="E214" s="7" t="inlineStr">
         <is>
           <t>17-1-1</t>
         </is>
       </c>
-      <c r="F213" s="7" t="inlineStr">
+      <c r="F214" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
         </is>
       </c>
-      <c r="G213" s="7" t="inlineStr">
+      <c r="G214" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H213" s="7" t="inlineStr">
+      <c r="H214" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I213" s="7" t="inlineStr">
+      <c r="I214" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="214">
-      <c r="A214" s="4" t="n"/>
-      <c r="B214" s="4" t="n"/>
-      <c r="C214" s="4" t="n"/>
-      <c r="D214" s="4" t="n"/>
-      <c r="E214" s="7" t="inlineStr">
-        <is>
-          <t>17-1-2</t>
-        </is>
-      </c>
-      <c r="F214" s="7" t="inlineStr">
-        <is>
-          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
-        </is>
-      </c>
-      <c r="G214" s="7" t="inlineStr">
-        <is>
-          <t>1.自分と他人の読書計画をそれぞれ用意する
-2.読書計画一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H214" s="7" t="inlineStr">
-        <is>
-          <t>自分の計画のみが、target_dateの昇順で表示される</t>
-        </is>
-      </c>
-      <c r="I214" s="4" t="n"/>
     </row>
     <row r="215">
       <c r="A215" s="4" t="n"/>
@@ -7149,23 +7149,23 @@
       <c r="D215" s="4" t="n"/>
       <c r="E215" s="7" t="inlineStr">
         <is>
-          <t>17-1-3</t>
+          <t>17-1-2</t>
         </is>
       </c>
       <c r="F215" s="7" t="inlineStr">
         <is>
-          <t>ステータスで絞り込んで表示できる</t>
+          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
         </is>
       </c>
       <c r="G215" s="7" t="inlineStr">
         <is>
-          <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
-2.statusパラメータを指定して一覧を開く</t>
+          <t>1.自分と他人の読書計画をそれぞれ用意する
+2.読書計画一覧ページを開く</t>
         </is>
       </c>
       <c r="H215" s="7" t="inlineStr">
         <is>
-          <t>指定したステータスの計画のみ表示される</t>
+          <t>自分の計画のみが、target_dateの昇順で表示される</t>
         </is>
       </c>
       <c r="I215" s="4" t="n"/>
@@ -7177,23 +7177,23 @@
       <c r="D216" s="4" t="n"/>
       <c r="E216" s="7" t="inlineStr">
         <is>
-          <t>17-1-4</t>
+          <t>17-1-3</t>
         </is>
       </c>
       <c r="F216" s="7" t="inlineStr">
         <is>
-          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
+          <t>ステータスで絞り込んで表示できる</t>
         </is>
       </c>
       <c r="G216" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍について進行中の計画を作成する
-2.計画作成ページを開く</t>
+          <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
+2.statusパラメータを指定して一覧を開く</t>
         </is>
       </c>
       <c r="H216" s="7" t="inlineStr">
         <is>
-          <t>書籍選択肢にその書籍が表示されない</t>
+          <t>指定したステータスの計画のみ表示される</t>
         </is>
       </c>
       <c r="I216" s="4" t="n"/>
@@ -7205,22 +7205,23 @@
       <c r="D217" s="4" t="n"/>
       <c r="E217" s="7" t="inlineStr">
         <is>
-          <t>17-1-5</t>
+          <t>17-1-4</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
+          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
         </is>
       </c>
       <c r="G217" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
+          <t>1.ある書籍について進行中の計画を作成する
+2.計画作成ページを開く</t>
         </is>
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、計画は作成されない</t>
+          <t>書籍選択肢にその書籍が表示されない</t>
         </is>
       </c>
       <c r="I217" s="4" t="n"/>
@@ -7232,23 +7233,22 @@
       <c r="D218" s="4" t="n"/>
       <c r="E218" s="7" t="inlineStr">
         <is>
-          <t>17-1-6</t>
+          <t>17-1-5</t>
         </is>
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
+          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を読了(完了)状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>新しい計画が作成される</t>
+          <t>403Forbiddenになり、計画は作成されない</t>
         </is>
       </c>
       <c r="I218" s="4" t="n"/>
@@ -7260,23 +7260,23 @@
       <c r="D219" s="4" t="n"/>
       <c r="E219" s="7" t="inlineStr">
         <is>
-          <t>17-1-7</t>
+          <t>17-1-6</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
         </is>
       </c>
       <c r="G219" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.期日を入力せずに登録する</t>
+          <t>1.ある書籍の計画を読了(完了)状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>新しい計画が作成される</t>
         </is>
       </c>
       <c r="I219" s="4" t="n"/>
@@ -7288,23 +7288,23 @@
       <c r="D220" s="4" t="n"/>
       <c r="E220" s="7" t="inlineStr">
         <is>
-          <t>17-1-8</t>
+          <t>17-1-7</t>
         </is>
       </c>
       <c r="F220" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G220" s="7" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
-2.過去の日付を期日に指定して登録する</t>
+2.期日を入力せずに登録する</t>
         </is>
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I220" s="4" t="n"/>
@@ -7316,23 +7316,23 @@
       <c r="D221" s="4" t="n"/>
       <c r="E221" s="7" t="inlineStr">
         <is>
-          <t>17-1-9</t>
+          <t>17-1-8</t>
         </is>
       </c>
       <c r="F221" s="7" t="inlineStr">
         <is>
-          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G221" s="7" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
-2.書籍・期日を正しく入力して登録する</t>
+2.過去の日付を期日に指定して登録する</t>
         </is>
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I221" s="4" t="n"/>
@@ -7344,22 +7344,23 @@
       <c r="D222" s="4" t="n"/>
       <c r="E222" s="7" t="inlineStr">
         <is>
-          <t>17-1-10</t>
+          <t>17-1-9</t>
         </is>
       </c>
       <c r="F222" s="7" t="inlineStr">
         <is>
-          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
+          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
         </is>
       </c>
       <c r="G222" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画に対して読了操作を行う</t>
+          <t>1.計画作成ページを開く
+2.書籍・期日を正しく入力して登録する</t>
         </is>
       </c>
       <c r="H222" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
         </is>
       </c>
       <c r="I222" s="4" t="n"/>
@@ -7371,22 +7372,22 @@
       <c r="D223" s="4" t="n"/>
       <c r="E223" s="7" t="inlineStr">
         <is>
-          <t>17-1-11</t>
+          <t>17-1-10</t>
         </is>
       </c>
       <c r="F223" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画は読了・削除できない</t>
+          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
         </is>
       </c>
       <c r="G223" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+          <t>1.進行中の計画に対して読了操作を行う</t>
         </is>
       </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
-          <t>いずれも403Forbiddenになる</t>
+          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
         </is>
       </c>
       <c r="I223" s="4" t="n"/>
@@ -7398,22 +7399,22 @@
       <c r="D224" s="4" t="n"/>
       <c r="E224" s="7" t="inlineStr">
         <is>
-          <t>17-1-12</t>
+          <t>17-1-11</t>
         </is>
       </c>
       <c r="F224" s="7" t="inlineStr">
         <is>
-          <t>自分が作成した読書計画は削除できる</t>
+          <t>他人が作成した読書計画は読了・削除できない</t>
         </is>
       </c>
       <c r="G224" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の削除ボタンを押す</t>
+          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
         </is>
       </c>
       <c r="H224" s="7" t="inlineStr">
         <is>
-          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
+          <t>いずれも403Forbiddenになる</t>
         </is>
       </c>
       <c r="I224" s="4" t="n"/>
@@ -7423,25 +7424,24 @@
       <c r="B225" s="4" t="n"/>
       <c r="C225" s="4" t="n"/>
       <c r="D225" s="4" t="n"/>
-      <c r="E225" s="9" t="inlineStr">
-        <is>
-          <t>17-1-13</t>
-        </is>
-      </c>
-      <c r="F225" s="9" t="inlineStr">
-        <is>
-          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
-        </is>
-      </c>
-      <c r="G225" s="9" t="inlineStr">
-        <is>
-          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
-2.その読書計画を削除する</t>
-        </is>
-      </c>
-      <c r="H225" s="9" t="inlineStr">
-        <is>
-          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
+      <c r="E225" s="7" t="inlineStr">
+        <is>
+          <t>17-1-12</t>
+        </is>
+      </c>
+      <c r="F225" s="7" t="inlineStr">
+        <is>
+          <t>自分が作成した読書計画は削除できる</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="inlineStr">
+        <is>
+          <t>1.自分が作成した計画の削除ボタンを押す</t>
+        </is>
+      </c>
+      <c r="H225" s="7" t="inlineStr">
+        <is>
+          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
         </is>
       </c>
       <c r="I225" s="4" t="n"/>
@@ -7453,22 +7453,23 @@
       <c r="D226" s="4" t="n"/>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>17-1-14</t>
+          <t>17-1-13</t>
         </is>
       </c>
       <c r="F226" s="9" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は、読了操作を行えない</t>
+          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
         </is>
       </c>
       <c r="G226" s="9" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
+          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
+2.その読書計画を削除する</t>
         </is>
       </c>
       <c r="H226" s="9" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、completed_atは変更されない</t>
+          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
         </is>
       </c>
       <c r="I226" s="4" t="n"/>
@@ -7480,23 +7481,22 @@
       <c r="D227" s="4" t="n"/>
       <c r="E227" s="9" t="inlineStr">
         <is>
-          <t>17-1-15</t>
+          <t>17-1-14</t>
         </is>
       </c>
       <c r="F227" s="9" t="inlineStr">
         <is>
-          <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
+          <t>ステータスが「完了」の計画は、読了操作を行えない</t>
         </is>
       </c>
       <c r="G227" s="9" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を「期限切れ」の状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
         </is>
       </c>
       <c r="H227" s="9" t="inlineStr">
         <is>
-          <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
+          <t>403Forbiddenになり、completed_atは変更されない</t>
         </is>
       </c>
       <c r="I227" s="4" t="n"/>
@@ -7508,23 +7508,23 @@
       <c r="D228" s="4" t="n"/>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>17-1-16</t>
+          <t>17-1-15</t>
         </is>
       </c>
       <c r="F228" s="9" t="inlineStr">
         <is>
-          <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
+          <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
         </is>
       </c>
       <c r="G228" s="9" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍を選択せずに期日を入力して登録する</t>
+          <t>1.ある書籍の計画を「期限切れ」の状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H228" s="9" t="inlineStr">
         <is>
-          <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
+          <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
         </is>
       </c>
       <c r="I228" s="4" t="n"/>
@@ -7536,22 +7536,23 @@
       <c r="D229" s="4" t="n"/>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>17-1-17</t>
+          <t>17-1-16</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
+          <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G229" s="9" t="inlineStr">
         <is>
-          <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.計画作成ページを開く
+2.書籍を選択せずに期日を入力して登録する</t>
         </is>
       </c>
       <c r="H229" s="9" t="inlineStr">
         <is>
-          <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
+          <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I229" s="4" t="n"/>
@@ -7563,22 +7564,22 @@
       <c r="D230" s="4" t="n"/>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>17-1-18</t>
+          <t>17-1-17</t>
         </is>
       </c>
       <c r="F230" s="9" t="inlineStr">
         <is>
-          <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
+          <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G230" s="9" t="inlineStr">
         <is>
-          <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H230" s="9" t="inlineStr">
         <is>
-          <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
+          <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I230" s="4" t="n"/>
@@ -7590,22 +7591,22 @@
       <c r="D231" s="4" t="n"/>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>17-1-19</t>
+          <t>17-1-18</t>
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr">
         <is>
-          <t>期日が日付形式でない場合、バリデーションメッセージが表示される</t>
+          <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G231" s="9" t="inlineStr">
         <is>
-          <t>1.書籍と、日付として不正な期日(例:abc)を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H231" s="9" t="inlineStr">
         <is>
-          <t>「正しい日付を入力してください」というバリデーションメッセージが表示される</t>
+          <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I231" s="4" t="n"/>
@@ -7617,23 +7618,22 @@
       <c r="D232" s="4" t="n"/>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>17-1-20</t>
+          <t>17-1-19</t>
         </is>
       </c>
       <c r="F232" s="9" t="inlineStr">
         <is>
-          <t>期日に今日の日付を指定した場合、計画を作成できる</t>
+          <t>期日が日付形式でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G232" s="9" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍を選択し、期日に今日の日付を指定して登録する</t>
+          <t>1.書籍と、日付として不正な期日(例:abc)を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H232" s="9" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される（今日の日付は指定可能）</t>
+          <t>「正しい日付を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I232" s="4" t="n"/>
@@ -7645,22 +7645,23 @@
       <c r="D233" s="4" t="n"/>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>17-1-21</t>
+          <t>17-1-20</t>
         </is>
       </c>
       <c r="F233" s="9" t="inlineStr">
         <is>
-          <t>同じ書籍に進行中の計画がある状態で不正な期日を指定しても、入力エラーではなく403になる</t>
+          <t>期日に今日の日付を指定した場合、計画を作成できる</t>
         </is>
       </c>
       <c r="G233" s="9" t="inlineStr">
         <is>
-          <t>1.進行中の計画がある書籍を指定し、期日を空にして直接計画作成のリクエストを送信する</t>
+          <t>1.計画作成ページを開く
+2.書籍を選択し、期日に今日の日付を指定して登録する</t>
         </is>
       </c>
       <c r="H233" s="9" t="inlineStr">
         <is>
-          <t>バリデーションエラーではなく403Forbiddenになり、計画は作成されない（認可チェックが入力チェックより先に行われる）</t>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される（今日の日付は指定可能）</t>
         </is>
       </c>
       <c r="I233" s="4" t="n"/>
@@ -7672,128 +7673,128 @@
       <c r="D234" s="4" t="n"/>
       <c r="E234" s="9" t="inlineStr">
         <is>
+          <t>17-1-21</t>
+        </is>
+      </c>
+      <c r="F234" s="9" t="inlineStr">
+        <is>
+          <t>同じ書籍に進行中の計画がある状態で不正な期日を指定しても、入力エラーではなく403になる</t>
+        </is>
+      </c>
+      <c r="G234" s="9" t="inlineStr">
+        <is>
+          <t>1.進行中の計画がある書籍を指定し、期日を空にして直接計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H234" s="9" t="inlineStr">
+        <is>
+          <t>バリデーションエラーではなく403Forbiddenになり、計画は作成されない（認可チェックが入力チェックより先に行われる）</t>
+        </is>
+      </c>
+      <c r="I234" s="4" t="n"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="n"/>
+      <c r="B235" s="4" t="n"/>
+      <c r="C235" s="4" t="n"/>
+      <c r="D235" s="4" t="n"/>
+      <c r="E235" s="9" t="inlineStr">
+        <is>
           <t>17-1-22</t>
         </is>
       </c>
-      <c r="F234" s="9" t="inlineStr">
+      <c r="F235" s="9" t="inlineStr">
         <is>
           <t>ステータスが「期限切れ」の計画は、読了操作を行える</t>
         </is>
       </c>
-      <c r="G234" s="9" t="inlineStr">
+      <c r="G235" s="9" t="inlineStr">
         <is>
           <t>1.「期限切れ」の計画に対して、読了操作を行う</t>
         </is>
       </c>
-      <c r="H234" s="9" t="inlineStr">
+      <c r="H235" s="9" t="inlineStr">
         <is>
           <t>ステータスが「完了」になり、completed_atに現在日時が記録され、「「(タイトル)」を読了しました。」と表示される</t>
         </is>
       </c>
-      <c r="I234" s="4" t="n"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="5" t="n"/>
-      <c r="B235" s="5" t="n"/>
-      <c r="C235" s="5" t="n"/>
-      <c r="D235" s="5" t="n"/>
-      <c r="E235" s="9" t="inlineStr">
+      <c r="I235" s="4" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="5" t="n"/>
+      <c r="B236" s="5" t="n"/>
+      <c r="C236" s="5" t="n"/>
+      <c r="D236" s="5" t="n"/>
+      <c r="E236" s="9" t="inlineStr">
         <is>
           <t>17-1-23</t>
         </is>
       </c>
-      <c r="F235" s="9" t="inlineStr">
+      <c r="F236" s="9" t="inlineStr">
         <is>
           <t>他のユーザーの「進行中」の計画は、自分の計画作成に影響しない</t>
         </is>
       </c>
-      <c r="G235" s="9" t="inlineStr">
+      <c r="G236" s="9" t="inlineStr">
         <is>
           <t>1.他のユーザーが「進行中」の計画を持つ書籍を用意する
 2.計画作成ページを開く
 3.その書籍で計画作成のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H235" s="9" t="inlineStr">
+      <c r="H236" s="9" t="inlineStr">
         <is>
           <t>その書籍は作成画面の選択肢に表示され、自分の計画が「進行中」で作成される（進行中の重複チェックはユーザーごとに行われる）</t>
         </is>
       </c>
-      <c r="I235" s="5" t="n"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="7" t="inlineStr">
+      <c r="I236" s="5" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="7" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B236" s="7" t="inlineStr">
+      <c r="B237" s="7" t="inlineStr">
         <is>
           <t>読書計画（期限変更）</t>
         </is>
       </c>
-      <c r="C236" s="7" t="inlineStr">
+      <c r="C237" s="7" t="inlineStr">
         <is>
           <t>18-1</t>
         </is>
       </c>
-      <c r="D236" s="7" t="inlineStr">
+      <c r="D237" s="7" t="inlineStr">
         <is>
           <t>読書計画の期日変更</t>
         </is>
       </c>
-      <c r="E236" s="7" t="inlineStr">
+      <c r="E237" s="7" t="inlineStr">
         <is>
           <t>18-1-1</t>
         </is>
       </c>
-      <c r="F236" s="7" t="inlineStr">
+      <c r="F237" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
         </is>
       </c>
-      <c r="G236" s="7" t="inlineStr">
+      <c r="G237" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H236" s="7" t="inlineStr">
+      <c r="H237" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I236" s="7" t="inlineStr">
+      <c r="I237" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="237">
-      <c r="A237" s="4" t="n"/>
-      <c r="B237" s="4" t="n"/>
-      <c r="C237" s="4" t="n"/>
-      <c r="D237" s="4" t="n"/>
-      <c r="E237" s="7" t="inlineStr">
-        <is>
-          <t>18-1-2</t>
-        </is>
-      </c>
-      <c r="F237" s="7" t="inlineStr">
-        <is>
-          <t>他人が作成した読書計画の期日は変更できない</t>
-        </is>
-      </c>
-      <c r="G237" s="7" t="inlineStr">
-        <is>
-          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H237" s="7" t="inlineStr">
-        <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
-        </is>
-      </c>
-      <c r="I237" s="4" t="n"/>
     </row>
     <row r="238">
       <c r="A238" s="4" t="n"/>
@@ -7802,22 +7803,22 @@
       <c r="D238" s="4" t="n"/>
       <c r="E238" s="7" t="inlineStr">
         <is>
-          <t>18-1-3</t>
+          <t>18-1-2</t>
         </is>
       </c>
       <c r="F238" s="7" t="inlineStr">
         <is>
-          <t>編集画面を開くと現在の期日が初期表示される</t>
+          <t>他人が作成した読書計画の期日は変更できない</t>
         </is>
       </c>
       <c r="G238" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の編集ページを開く</t>
+          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H238" s="7" t="inlineStr">
         <is>
-          <t>現在登録されている期日が入力欄に表示される</t>
+          <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
       <c r="I238" s="4" t="n"/>
@@ -7829,23 +7830,22 @@
       <c r="D239" s="4" t="n"/>
       <c r="E239" s="7" t="inlineStr">
         <is>
-          <t>18-1-4</t>
+          <t>18-1-3</t>
         </is>
       </c>
       <c r="F239" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>編集画面を開くと現在の期日が初期表示される</t>
         </is>
       </c>
       <c r="G239" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.期日を空にして更新する</t>
+          <t>1.自分が作成した計画の編集ページを開く</t>
         </is>
       </c>
       <c r="H239" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>現在登録されている期日が入力欄に表示される</t>
         </is>
       </c>
       <c r="I239" s="4" t="n"/>
@@ -7857,23 +7857,23 @@
       <c r="D240" s="4" t="n"/>
       <c r="E240" s="7" t="inlineStr">
         <is>
-          <t>18-1-5</t>
+          <t>18-1-4</t>
         </is>
       </c>
       <c r="F240" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G240" s="7" t="inlineStr">
         <is>
           <t>1.編集ページを開く
-2.過去の日付に変更して更新する</t>
+2.期日を空にして更新する</t>
         </is>
       </c>
       <c r="H240" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I240" s="4" t="n"/>
@@ -7885,23 +7885,23 @@
       <c r="D241" s="4" t="n"/>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>18-1-6</t>
+          <t>18-1-5</t>
         </is>
       </c>
       <c r="F241" s="7" t="inlineStr">
         <is>
-          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G241" s="7" t="inlineStr">
         <is>
           <t>1.編集ページを開く
-2.未来の日付に正しく変更して更新する</t>
+2.過去の日付に変更して更新する</t>
         </is>
       </c>
       <c r="H241" s="7" t="inlineStr">
         <is>
-          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I241" s="4" t="n"/>
@@ -7913,23 +7913,23 @@
       <c r="D242" s="4" t="n"/>
       <c r="E242" s="7" t="inlineStr">
         <is>
-          <t>18-1-7</t>
+          <t>18-1-6</t>
         </is>
       </c>
       <c r="F242" s="7" t="inlineStr">
         <is>
-          <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
+          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
         </is>
       </c>
       <c r="G242" s="7" t="inlineStr">
         <is>
-          <t>1.期日が過去で「進行中」の計画を用意する
-2.読書計画一覧または編集ページを開く</t>
+          <t>1.編集ページを開く
+2.未来の日付に正しく変更して更新する</t>
         </is>
       </c>
       <c r="H242" s="7" t="inlineStr">
         <is>
-          <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
+          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
         </is>
       </c>
       <c r="I242" s="4" t="n"/>
@@ -7941,22 +7941,23 @@
       <c r="D243" s="4" t="n"/>
       <c r="E243" s="7" t="inlineStr">
         <is>
-          <t>18-1-8</t>
+          <t>18-1-7</t>
         </is>
       </c>
       <c r="F243" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は期日を変更できない</t>
+          <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
         </is>
       </c>
       <c r="G243" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
+          <t>1.期日が過去で「進行中」の計画を用意する
+2.読書計画一覧または編集ページを開く</t>
         </is>
       </c>
       <c r="H243" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
+          <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
         </is>
       </c>
       <c r="I243" s="4" t="n"/>
@@ -7968,22 +7969,22 @@
       <c r="D244" s="4" t="n"/>
       <c r="E244" s="7" t="inlineStr">
         <is>
-          <t>18-1-9</t>
+          <t>18-1-8</t>
         </is>
       </c>
       <c r="F244" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
+          <t>ステータスが「完了」の計画は期日を変更できない</t>
         </is>
       </c>
       <c r="G244" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
+          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H244" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、編集ページは表示されない</t>
+          <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
       <c r="I244" s="4" t="n"/>
@@ -7995,17 +7996,17 @@
       <c r="D245" s="4" t="n"/>
       <c r="E245" s="7" t="inlineStr">
         <is>
-          <t>18-1-10</t>
+          <t>18-1-9</t>
         </is>
       </c>
       <c r="F245" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画の編集ページにはアクセスできない</t>
+          <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
         </is>
       </c>
       <c r="G245" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画の編集ページのURLに直接アクセスする</t>
+          <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H245" s="7" t="inlineStr">
@@ -8022,130 +8023,129 @@
       <c r="D246" s="4" t="n"/>
       <c r="E246" s="7" t="inlineStr">
         <is>
+          <t>18-1-10</t>
+        </is>
+      </c>
+      <c r="F246" s="7" t="inlineStr">
+        <is>
+          <t>他人が作成した読書計画の編集ページにはアクセスできない</t>
+        </is>
+      </c>
+      <c r="G246" s="7" t="inlineStr">
+        <is>
+          <t>1.他人が作成した計画の編集ページのURLに直接アクセスする</t>
+        </is>
+      </c>
+      <c r="H246" s="7" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、編集ページは表示されない</t>
+        </is>
+      </c>
+      <c r="I246" s="4" t="n"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="n"/>
+      <c r="B247" s="4" t="n"/>
+      <c r="C247" s="4" t="n"/>
+      <c r="D247" s="4" t="n"/>
+      <c r="E247" s="7" t="inlineStr">
+        <is>
           <t>18-1-11</t>
         </is>
       </c>
-      <c r="F246" s="7" t="inlineStr">
+      <c r="F247" s="7" t="inlineStr">
         <is>
           <t>同じ書籍に「進行中」の計画がある場合、「期限切れ」の計画は編集・更新できない</t>
         </is>
       </c>
-      <c r="G246" s="7" t="inlineStr">
+      <c r="G247" s="7" t="inlineStr">
         <is>
           <t>1.同じ書籍について、「期限切れ」の計画と「進行中」の計画をそれぞれ用意する
 2.「期限切れ」の計画の編集ページのURLに直接アクセスする
 3.「期限切れ」の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
-      <c r="H246" s="7" t="inlineStr">
+      <c r="H247" s="7" t="inlineStr">
         <is>
           <t>いずれも403Forbiddenになり、「期限切れ」の計画のステータス・期日は変更されない（同じ書籍の「進行中」の計画が2件になることを防ぐ）</t>
         </is>
       </c>
-      <c r="I246" s="4" t="n"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="5" t="n"/>
-      <c r="B247" s="5" t="n"/>
-      <c r="C247" s="5" t="n"/>
-      <c r="D247" s="5" t="n"/>
-      <c r="E247" s="7" t="inlineStr">
+      <c r="I247" s="4" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="5" t="n"/>
+      <c r="B248" s="5" t="n"/>
+      <c r="C248" s="5" t="n"/>
+      <c r="D248" s="5" t="n"/>
+      <c r="E248" s="7" t="inlineStr">
         <is>
           <t>18-1-12</t>
         </is>
       </c>
-      <c r="F247" s="7" t="inlineStr">
+      <c r="F248" s="7" t="inlineStr">
         <is>
           <t>他人が作成した読書計画に不正な期日で更新しようとしても、入力エラーではなく403になる</t>
         </is>
       </c>
-      <c r="G247" s="7" t="inlineStr">
+      <c r="G248" s="7" t="inlineStr">
         <is>
           <t>1.他人が作成した読書計画に対して、期日を空にして直接計画更新のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H247" s="7" t="inlineStr">
+      <c r="H248" s="7" t="inlineStr">
         <is>
           <t>バリデーションエラーではなく403Forbiddenになり、期日は変更されない（認可チェックが入力チェックより先に行われる）</t>
         </is>
       </c>
-      <c r="I247" s="5" t="n"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="7" t="inlineStr">
+      <c r="I248" s="5" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B248" s="7" t="inlineStr">
+      <c r="B249" s="7" t="inlineStr">
         <is>
           <t>リマインダーバッチ</t>
         </is>
       </c>
-      <c r="C248" s="7" t="inlineStr">
+      <c r="C249" s="7" t="inlineStr">
         <is>
           <t>19-1</t>
         </is>
       </c>
-      <c r="D248" s="7" t="inlineStr">
+      <c r="D249" s="7" t="inlineStr">
         <is>
           <t>日次バッチ(reading-plans:daily)によるリマインダー通知</t>
         </is>
       </c>
-      <c r="E248" s="7" t="inlineStr">
+      <c r="E249" s="7" t="inlineStr">
         <is>
           <t>19-1-1</t>
         </is>
       </c>
-      <c r="F248" s="7" t="inlineStr">
+      <c r="F249" s="7" t="inlineStr">
         <is>
           <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
         </is>
       </c>
-      <c r="G248" s="7" t="inlineStr">
+      <c r="G249" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日後・ステータス進行中の計画を用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
-      <c r="H248" s="7" t="inlineStr">
+      <c r="H249" s="7" t="inlineStr">
         <is>
           <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_before)・title(「読書期限のお知らせ」)・body(「「(書籍名)」の読書期限まであと3日です。」)が含まれる</t>
         </is>
       </c>
-      <c r="I248" s="7" t="inlineStr">
+      <c r="I249" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="4" t="n"/>
-      <c r="B249" s="4" t="n"/>
-      <c r="C249" s="4" t="n"/>
-      <c r="D249" s="4" t="n"/>
-      <c r="E249" s="7" t="inlineStr">
-        <is>
-          <t>19-1-2</t>
-        </is>
-      </c>
-      <c r="F249" s="7" t="inlineStr">
-        <is>
-          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
-        </is>
-      </c>
-      <c r="G249" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが本日・ステータス進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H249" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される。通知のdataには、plan_id・book_title・timing(on_due_date)・title(「読書期限当日のお知らせ」)・body(「「(書籍名)」の読書期限は本日までです。」)が含まれる</t>
-        </is>
-      </c>
-      <c r="I249" s="4" t="n"/>
     </row>
     <row r="250">
       <c r="A250" s="4" t="n"/>
@@ -8154,23 +8154,23 @@
       <c r="D250" s="4" t="n"/>
       <c r="E250" s="7" t="inlineStr">
         <is>
-          <t>19-1-3</t>
+          <t>19-1-2</t>
         </is>
       </c>
       <c r="F250" s="7" t="inlineStr">
         <is>
-          <t>期限切れから3日後の計画に再エンゲージメント通知が送信される</t>
+          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
         </is>
       </c>
       <c r="G250" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが3日前・ステータス期限切れの計画を用意する
+          <t>1.target_dateが本日・ステータス進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H250" s="7" t="inlineStr">
         <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
+          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される。通知のdataには、plan_id・book_title・timing(on_due_date)・title(「読書期限当日のお知らせ」)・body(「「(書籍名)」の読書期限は本日までです。」)が含まれる</t>
         </is>
       </c>
       <c r="I250" s="4" t="n"/>
@@ -8182,130 +8182,130 @@
       <c r="D251" s="4" t="n"/>
       <c r="E251" s="7" t="inlineStr">
         <is>
+          <t>19-1-3</t>
+        </is>
+      </c>
+      <c r="F251" s="7" t="inlineStr">
+        <is>
+          <t>期限切れから3日後の計画に再エンゲージメント通知が送信される</t>
+        </is>
+      </c>
+      <c r="G251" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日前・ステータス期限切れの計画を用意する
+2.reading-plans:dailyを実行する</t>
+        </is>
+      </c>
+      <c r="H251" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
+        </is>
+      </c>
+      <c r="I251" s="4" t="n"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="n"/>
+      <c r="B252" s="4" t="n"/>
+      <c r="C252" s="4" t="n"/>
+      <c r="D252" s="4" t="n"/>
+      <c r="E252" s="7" t="inlineStr">
+        <is>
           <t>19-1-4</t>
         </is>
       </c>
-      <c r="F251" s="7" t="inlineStr">
+      <c r="F252" s="7" t="inlineStr">
         <is>
           <t>いずれの条件にも該当しない計画には通知が送信されない</t>
         </is>
       </c>
-      <c r="G251" s="7" t="inlineStr">
+      <c r="G252" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H251" s="7" t="inlineStr">
+      <c r="H252" s="7" t="inlineStr">
         <is>
           <t>その計画のユーザーに通知が送信されない</t>
         </is>
       </c>
-      <c r="I251" s="4" t="n"/>
-    </row>
-    <row r="252">
-      <c r="A252" s="5" t="n"/>
-      <c r="B252" s="5" t="n"/>
-      <c r="C252" s="5" t="n"/>
-      <c r="D252" s="5" t="n"/>
-      <c r="E252" s="7" t="inlineStr">
+      <c r="I252" s="4" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="5" t="n"/>
+      <c r="B253" s="5" t="n"/>
+      <c r="C253" s="5" t="n"/>
+      <c r="D253" s="5" t="n"/>
+      <c r="E253" s="7" t="inlineStr">
         <is>
           <t>19-1-5</t>
         </is>
       </c>
-      <c r="F252" s="7" t="inlineStr">
+      <c r="F253" s="7" t="inlineStr">
         <is>
           <t>ステータスが「完了」の計画には、期日の条件に合っていても通知が送信されない</t>
         </is>
       </c>
-      <c r="G252" s="7" t="inlineStr">
+      <c r="G253" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日後・本日・3日前で、ステータスが完了の計画をそれぞれ用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
-      <c r="H252" s="7" t="inlineStr">
+      <c r="H253" s="7" t="inlineStr">
         <is>
           <t>いずれの計画のユーザーにも通知が送信されない</t>
         </is>
       </c>
-      <c r="I252" s="5" t="n"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="7" t="inlineStr">
+      <c r="I253" s="5" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B253" s="7" t="inlineStr">
+      <c r="B254" s="7" t="inlineStr">
         <is>
           <t>自動失効バッチ</t>
         </is>
       </c>
-      <c r="C253" s="7" t="inlineStr">
+      <c r="C254" s="7" t="inlineStr">
         <is>
           <t>20-1</t>
         </is>
       </c>
-      <c r="D253" s="7" t="inlineStr">
+      <c r="D254" s="7" t="inlineStr">
         <is>
           <t>日次バッチ(reading-plans:daily)による自動失効処理</t>
         </is>
       </c>
-      <c r="E253" s="7" t="inlineStr">
+      <c r="E254" s="7" t="inlineStr">
         <is>
           <t>20-1-1</t>
         </is>
       </c>
-      <c r="F253" s="7" t="inlineStr">
+      <c r="F254" s="7" t="inlineStr">
         <is>
           <t>期日を過ぎた「進行中」の計画が「期限切れ」に更新される</t>
         </is>
       </c>
-      <c r="G253" s="7" t="inlineStr">
+      <c r="G254" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが過去・ステータス進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H253" s="7" t="inlineStr">
+      <c r="H254" s="7" t="inlineStr">
         <is>
           <t>対象の計画のstatusが「期限切れ」に更新される</t>
         </is>
       </c>
-      <c r="I253" s="7" t="inlineStr">
+      <c r="I254" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="4" t="n"/>
-      <c r="B254" s="4" t="n"/>
-      <c r="C254" s="4" t="n"/>
-      <c r="D254" s="4" t="n"/>
-      <c r="E254" s="7" t="inlineStr">
-        <is>
-          <t>20-1-2</t>
-        </is>
-      </c>
-      <c r="F254" s="7" t="inlineStr">
-        <is>
-          <t>期日が今日以降の「進行中」の計画は失効しない</t>
-        </is>
-      </c>
-      <c r="G254" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H254" s="7" t="inlineStr">
-        <is>
-          <t>その計画のstatusは「進行中」のまま変化しない</t>
-        </is>
-      </c>
-      <c r="I254" s="4" t="n"/>
     </row>
     <row r="255">
       <c r="A255" s="4" t="n"/>
@@ -8314,23 +8314,23 @@
       <c r="D255" s="4" t="n"/>
       <c r="E255" s="7" t="inlineStr">
         <is>
-          <t>20-1-3</t>
+          <t>20-1-2</t>
         </is>
       </c>
       <c r="F255" s="7" t="inlineStr">
         <is>
-          <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
+          <t>期日が今日以降の「進行中」の計画は失効しない</t>
         </is>
       </c>
       <c r="G255" s="7" t="inlineStr">
         <is>
-          <t>1.完了済み・期限切れの計画をそれぞれ用意する
+          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H255" s="7" t="inlineStr">
         <is>
-          <t>いずれの計画もstatusが変化しない</t>
+          <t>その計画のstatusは「進行中」のまま変化しない</t>
         </is>
       </c>
       <c r="I255" s="4" t="n"/>
@@ -8338,98 +8338,98 @@
     <row r="256">
       <c r="A256" s="4" t="n"/>
       <c r="B256" s="4" t="n"/>
-      <c r="C256" s="5" t="n"/>
-      <c r="D256" s="5" t="n"/>
+      <c r="C256" s="4" t="n"/>
+      <c r="D256" s="4" t="n"/>
       <c r="E256" s="7" t="inlineStr">
         <is>
-          <t>20-1-4</t>
+          <t>20-1-3</t>
         </is>
       </c>
       <c r="F256" s="7" t="inlineStr">
         <is>
-          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+          <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
         </is>
       </c>
       <c r="G256" s="7" t="inlineStr">
         <is>
-          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
-2.DBを直接確認する</t>
+          <t>1.完了済み・期限切れの計画をそれぞれ用意する
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H256" s="7" t="inlineStr">
         <is>
-          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
-        </is>
-      </c>
-      <c r="I256" s="5" t="n"/>
+          <t>いずれの計画もstatusが変化しない</t>
+        </is>
+      </c>
+      <c r="I256" s="4" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n"/>
       <c r="B257" s="4" t="n"/>
-      <c r="C257" s="7" t="inlineStr">
-        <is>
-          <t>20-2</t>
-        </is>
-      </c>
-      <c r="D257" s="7" t="inlineStr">
-        <is>
-          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
-        </is>
-      </c>
+      <c r="C257" s="5" t="n"/>
+      <c r="D257" s="5" t="n"/>
       <c r="E257" s="7" t="inlineStr">
         <is>
-          <t>20-2-1</t>
+          <t>20-1-4</t>
         </is>
       </c>
       <c r="F257" s="7" t="inlineStr">
         <is>
-          <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
+          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
         </is>
       </c>
       <c r="G257" s="7" t="inlineStr">
         <is>
-          <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
+2.DBを直接確認する</t>
         </is>
       </c>
       <c r="H257" s="7" t="inlineStr">
         <is>
-          <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I257" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
-        </is>
-      </c>
+          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
+        </is>
+      </c>
+      <c r="I257" s="5" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="4" t="n"/>
       <c r="B258" s="4" t="n"/>
-      <c r="C258" s="4" t="n"/>
-      <c r="D258" s="4" t="n"/>
+      <c r="C258" s="7" t="inlineStr">
+        <is>
+          <t>20-2</t>
+        </is>
+      </c>
+      <c r="D258" s="7" t="inlineStr">
+        <is>
+          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
+        </is>
+      </c>
       <c r="E258" s="7" t="inlineStr">
         <is>
-          <t>20-2-2</t>
+          <t>20-2-1</t>
         </is>
       </c>
       <c r="F258" s="7" t="inlineStr">
         <is>
-          <t>期限切れへの更新が、通知対象の抽出より先に行われる</t>
+          <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
         </is>
       </c>
       <c r="G258" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが3日前で、ステータスが「進行中」のまま(未更新)の計画を用意する
+          <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
       <c r="H258" s="7" t="inlineStr">
         <is>
-          <t>計画のstatusが「期限切れ」に更新され、そのユーザーに再エンゲージメント(re_engagement)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I258" s="4" t="n"/>
+          <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I258" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n"/>
@@ -8438,224 +8438,224 @@
       <c r="D259" s="4" t="n"/>
       <c r="E259" s="7" t="inlineStr">
         <is>
+          <t>20-2-2</t>
+        </is>
+      </c>
+      <c r="F259" s="7" t="inlineStr">
+        <is>
+          <t>期限切れへの更新が、通知対象の抽出より先に行われる</t>
+        </is>
+      </c>
+      <c r="G259" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日前で、ステータスが「進行中」のまま(未更新)の計画を用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+        </is>
+      </c>
+      <c r="H259" s="7" t="inlineStr">
+        <is>
+          <t>計画のstatusが「期限切れ」に更新され、そのユーザーに再エンゲージメント(re_engagement)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I259" s="4" t="n"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="n"/>
+      <c r="B260" s="4" t="n"/>
+      <c r="C260" s="4" t="n"/>
+      <c r="D260" s="4" t="n"/>
+      <c r="E260" s="7" t="inlineStr">
+        <is>
           <t>20-2-3</t>
         </is>
       </c>
-      <c r="F259" s="7" t="inlineStr">
+      <c r="F260" s="7" t="inlineStr">
         <is>
           <t>reading-plans:dailyが毎日20:00に実行されるようスケジュールされている</t>
         </is>
       </c>
-      <c r="G259" s="7" t="inlineStr">
+      <c r="G260" s="7" t="inlineStr">
         <is>
           <t>1.アプリケーションのスケジュール(Illuminate\Console\Scheduling\Schedule)から、登録済みのイベントを取得する</t>
         </is>
       </c>
-      <c r="H259" s="7" t="inlineStr">
+      <c r="H260" s="7" t="inlineStr">
         <is>
           <t>reading-plans:dailyのイベントが登録されており、cron式が毎日20:00(0 20 * * *)になっている</t>
         </is>
       </c>
-      <c r="I259" s="4" t="n"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="5" t="n"/>
-      <c r="B260" s="5" t="n"/>
-      <c r="C260" s="5" t="n"/>
-      <c r="D260" s="5" t="n"/>
-      <c r="E260" s="7" t="inlineStr">
+      <c r="I260" s="4" t="n"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="5" t="n"/>
+      <c r="B261" s="5" t="n"/>
+      <c r="C261" s="5" t="n"/>
+      <c r="D261" s="5" t="n"/>
+      <c r="E261" s="7" t="inlineStr">
         <is>
           <t>20-2-4</t>
         </is>
       </c>
-      <c r="F260" s="7" t="inlineStr">
+      <c r="F261" s="7" t="inlineStr">
         <is>
           <t>日次バッチで送信した通知がnotificationsテーブルに保存され、通知一覧に表示される</t>
         </is>
       </c>
-      <c r="G260" s="7" t="inlineStr">
+      <c r="G261" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日後(期日の3日前)・ステータス進行中の計画を用意する
 2.Notification::fake()を使わずに reading-plans:daily を実行する
 3.計画のユーザーで通知一覧ページを開く</t>
         </is>
       </c>
-      <c r="H260" s="7" t="inlineStr">
+      <c r="H261" s="7" t="inlineStr">
         <is>
           <t>notificationsテーブルにReadingPlanReminderの通知(未読、dataのplan_id・timingが対象の計画のもの)が1件保存され、通知一覧に「読書期限のお知らせ」と本文が未読として表示される</t>
         </is>
       </c>
-      <c r="I260" s="5" t="n"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="9" t="inlineStr">
+      <c r="I261" s="5" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B261" s="9" t="inlineStr">
+      <c r="B262" s="9" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="C261" s="9" t="inlineStr">
+      <c r="C262" s="9" t="inlineStr">
         <is>
           <t>21-1</t>
         </is>
       </c>
-      <c r="D261" s="9" t="inlineStr">
+      <c r="D262" s="9" t="inlineStr">
         <is>
           <t>通知の既読化</t>
         </is>
       </c>
-      <c r="E261" s="9" t="inlineStr">
+      <c r="E262" s="9" t="inlineStr">
         <is>
           <t>21-1-1</t>
         </is>
       </c>
-      <c r="F261" s="9" t="inlineStr">
+      <c r="F262" s="9" t="inlineStr">
         <is>
           <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
         </is>
       </c>
-      <c r="G261" s="9" t="inlineStr">
+      <c r="G262" s="9" t="inlineStr">
         <is>
           <t>1.未ログイン状態でPOST /notifications/{id}/read に直接リクエストを送信する</t>
         </is>
       </c>
-      <c r="H261" s="9" t="inlineStr">
+      <c r="H262" s="9" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
         </is>
       </c>
-      <c r="I261" s="9" t="inlineStr">
+      <c r="I262" s="9" t="inlineStr">
         <is>
           <t>tests/Feature/Notification/NotificationTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="4" t="n"/>
-      <c r="B262" s="4" t="n"/>
-      <c r="C262" s="4" t="n"/>
-      <c r="D262" s="4" t="n"/>
-      <c r="E262" s="9" t="inlineStr">
-        <is>
-          <t>21-1-2</t>
-        </is>
-      </c>
-      <c r="F262" s="9" t="inlineStr">
-        <is>
-          <t>自分の通知を既読にできる</t>
-        </is>
-      </c>
-      <c r="G262" s="9" t="inlineStr">
-        <is>
-          <t>1.自分宛ての未読通知を用意する
-2.その通知に対してPOST /notifications/{id}/read を送信する</t>
-        </is>
-      </c>
-      <c r="H262" s="9" t="inlineStr">
-        <is>
-          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
-        </is>
-      </c>
-      <c r="I262" s="4" t="n"/>
     </row>
     <row r="263">
       <c r="A263" s="4" t="n"/>
       <c r="B263" s="4" t="n"/>
-      <c r="C263" s="5" t="n"/>
-      <c r="D263" s="5" t="n"/>
+      <c r="C263" s="4" t="n"/>
+      <c r="D263" s="4" t="n"/>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>21-1-3</t>
+          <t>21-1-2</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>他ユーザーの通知は既読にできない</t>
+          <t>自分の通知を既読にできる</t>
         </is>
       </c>
       <c r="G263" s="9" t="inlineStr">
         <is>
-          <t>1.他ユーザー宛ての通知を用意する
-2.そのIDに対してPOST /notifications/{id}/read を送信する</t>
+          <t>1.自分宛ての未読通知を用意する
+2.その通知に対してPOST /notifications/{id}/read を送信する</t>
         </is>
       </c>
       <c r="H263" s="9" t="inlineStr">
         <is>
-          <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
-        </is>
-      </c>
-      <c r="I263" s="5" t="n"/>
+          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
+        </is>
+      </c>
+      <c r="I263" s="4" t="n"/>
     </row>
     <row r="264">
       <c r="A264" s="4" t="n"/>
       <c r="B264" s="4" t="n"/>
-      <c r="C264" s="9" t="inlineStr">
-        <is>
-          <t>21-2</t>
-        </is>
-      </c>
-      <c r="D264" s="9" t="inlineStr">
-        <is>
-          <t>通知一覧</t>
-        </is>
-      </c>
+      <c r="C264" s="5" t="n"/>
+      <c r="D264" s="5" t="n"/>
       <c r="E264" s="9" t="inlineStr">
         <is>
-          <t>21-2-1</t>
+          <t>21-1-3</t>
         </is>
       </c>
       <c r="F264" s="9" t="inlineStr">
         <is>
-          <t>未ログインの場合、通知一覧にアクセスできない</t>
+          <t>他ユーザーの通知は既読にできない</t>
         </is>
       </c>
       <c r="G264" s="9" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
+          <t>1.他ユーザー宛ての通知を用意する
+2.そのIDに対してPOST /notifications/{id}/read を送信する</t>
         </is>
       </c>
       <c r="H264" s="9" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I264" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationIndexTest.php</t>
-        </is>
-      </c>
+          <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
+        </is>
+      </c>
+      <c r="I264" s="5" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="4" t="n"/>
       <c r="B265" s="4" t="n"/>
-      <c r="C265" s="4" t="n"/>
-      <c r="D265" s="4" t="n"/>
+      <c r="C265" s="9" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="D265" s="9" t="inlineStr">
+        <is>
+          <t>通知一覧</t>
+        </is>
+      </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>21-2-2</t>
+          <t>21-2-1</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
+          <t>未ログインの場合、通知一覧にアクセスできない</t>
         </is>
       </c>
       <c r="G265" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
-2.通知一覧ページを開く</t>
+          <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H265" s="9" t="inlineStr">
         <is>
-          <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
-        </is>
-      </c>
-      <c r="I265" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I265" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationIndexTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="4" t="n"/>
@@ -8664,23 +8664,23 @@
       <c r="D266" s="4" t="n"/>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>21-2-3</t>
+          <t>21-2-2</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>通知が1件もない場合の表示を確認する</t>
+          <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
         </is>
       </c>
       <c r="G266" s="9" t="inlineStr">
         <is>
-          <t>1.通知が1件もないユーザーでログインする
+          <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H266" s="9" t="inlineStr">
         <is>
-          <t>「通知はありません。」と表示される</t>
+          <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
         </is>
       </c>
       <c r="I266" s="4" t="n"/>
@@ -8692,23 +8692,23 @@
       <c r="D267" s="4" t="n"/>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>21-2-4</t>
+          <t>21-2-3</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>通知のタイトル・本文が表示される</t>
+          <t>通知が1件もない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G267" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
+          <t>1.通知が1件もないユーザーでログインする
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H267" s="9" t="inlineStr">
         <is>
-          <t>通知のtitleとbodyが一覧に表示される</t>
+          <t>「通知はありません。」と表示される</t>
         </is>
       </c>
       <c r="I267" s="4" t="n"/>
@@ -8720,23 +8720,23 @@
       <c r="D268" s="4" t="n"/>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>21-2-5</t>
+          <t>21-2-4</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>未読と既読で表示が異なる</t>
+          <t>通知のタイトル・本文が表示される</t>
         </is>
       </c>
       <c r="G268" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
+          <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H268" s="9" t="inlineStr">
         <is>
-          <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
+          <t>通知のtitleとbodyが一覧に表示される</t>
         </is>
       </c>
       <c r="I268" s="4" t="n"/>
@@ -8744,303 +8744,331 @@
     <row r="269">
       <c r="A269" s="4" t="n"/>
       <c r="B269" s="4" t="n"/>
-      <c r="C269" s="5" t="n"/>
-      <c r="D269" s="5" t="n"/>
+      <c r="C269" s="4" t="n"/>
+      <c r="D269" s="4" t="n"/>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>21-2-6</t>
+          <t>21-2-5</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>同じ日時に作成された通知は、期日3日前→期日当日→期日3日後の順に表示される</t>
+          <t>未読と既読で表示が異なる</t>
         </is>
       </c>
       <c r="G269" s="9" t="inlineStr">
         <is>
-          <t>1.同じ日時に作成された、期日3日前（予告）・期日当日（最終警告）・期日3日後（再エンゲージメント）の通知と、作成日時の異なる通知を用意する
+          <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H269" s="9" t="inlineStr">
         <is>
-          <t>第1優先で作成日時の新しい順、作成日時が同じ通知同士は第2優先で「期日3日前→期日当日→期日3日後」の順に表示される</t>
-        </is>
-      </c>
-      <c r="I269" s="5" t="n"/>
+          <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
+        </is>
+      </c>
+      <c r="I269" s="4" t="n"/>
     </row>
     <row r="270">
       <c r="A270" s="4" t="n"/>
       <c r="B270" s="4" t="n"/>
-      <c r="C270" s="9" t="inlineStr">
-        <is>
-          <t>21-3</t>
-        </is>
-      </c>
-      <c r="D270" s="9" t="inlineStr">
-        <is>
-          <t>ヘッダーの未読件数</t>
-        </is>
-      </c>
+      <c r="C270" s="5" t="n"/>
+      <c r="D270" s="5" t="n"/>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>21-3-1</t>
+          <t>21-2-6</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>ヘッダーのベルアイコンに未読件数が表示される</t>
+          <t>同じ日時に作成された通知は、期日3日前→期日当日→期日3日後の順に表示される</t>
         </is>
       </c>
       <c r="G270" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
+          <t>1.同じ日時に作成された、期日3日前（予告）・期日当日（最終警告）・期日3日後（再エンゲージメント）の通知と、作成日時の異なる通知を用意する
+2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H270" s="9" t="inlineStr">
         <is>
-          <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
-        </is>
-      </c>
-      <c r="I270" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
-        </is>
-      </c>
+          <t>第1優先で作成日時の新しい順、作成日時が同じ通知同士は第2優先で「期日3日前→期日当日→期日3日後」の順に表示される</t>
+        </is>
+      </c>
+      <c r="I270" s="5" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="4" t="n"/>
       <c r="B271" s="4" t="n"/>
-      <c r="C271" s="4" t="n"/>
-      <c r="D271" s="4" t="n"/>
+      <c r="C271" s="9" t="inlineStr">
+        <is>
+          <t>21-3</t>
+        </is>
+      </c>
+      <c r="D271" s="9" t="inlineStr">
+        <is>
+          <t>ヘッダーの未読件数</t>
+        </is>
+      </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
+          <t>21-3-1</t>
+        </is>
+      </c>
+      <c r="F271" s="9" t="inlineStr">
+        <is>
+          <t>ヘッダーのベルアイコンに未読件数が表示される</t>
+        </is>
+      </c>
+      <c r="G271" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
+        </is>
+      </c>
+      <c r="H271" s="9" t="inlineStr">
+        <is>
+          <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
+        </is>
+      </c>
+      <c r="I271" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="n"/>
+      <c r="B272" s="4" t="n"/>
+      <c r="C272" s="4" t="n"/>
+      <c r="D272" s="4" t="n"/>
+      <c r="E272" s="9" t="inlineStr">
+        <is>
           <t>21-3-2</t>
         </is>
       </c>
-      <c r="F271" s="9" t="inlineStr">
+      <c r="F272" s="9" t="inlineStr">
         <is>
           <t>通知を既読にすると、ヘッダーの未読件数が減る</t>
         </is>
       </c>
-      <c r="G271" s="9" t="inlineStr">
+      <c r="G272" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知を複数件用意する
 2.そのうち1件にPOST /notifications/{id}/read を送信して既読にする
 3.画面を開き直す</t>
         </is>
       </c>
-      <c r="H271" s="9" t="inlineStr">
+      <c r="H272" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数が、既読にした1件分だけ減る</t>
         </is>
       </c>
-      <c r="I271" s="4" t="n"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="5" t="n"/>
-      <c r="B272" s="5" t="n"/>
-      <c r="C272" s="5" t="n"/>
-      <c r="D272" s="5" t="n"/>
-      <c r="E272" s="9" t="inlineStr">
+      <c r="I272" s="4" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="5" t="n"/>
+      <c r="B273" s="5" t="n"/>
+      <c r="C273" s="5" t="n"/>
+      <c r="D273" s="5" t="n"/>
+      <c r="E273" s="9" t="inlineStr">
         <is>
           <t>21-3-3</t>
         </is>
       </c>
-      <c r="F272" s="9" t="inlineStr">
+      <c r="F273" s="9" t="inlineStr">
         <is>
           <t>他ユーザーの通知は未読件数に含まれない</t>
         </is>
       </c>
-      <c r="G272" s="9" t="inlineStr">
+      <c r="G273" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知と、他ユーザー宛ての未読通知をそれぞれ用意する
 2.画面を開く</t>
         </is>
       </c>
-      <c r="H272" s="9" t="inlineStr">
+      <c r="H273" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数には、自分宛ての未読通知のみが数えられる</t>
         </is>
       </c>
-      <c r="I272" s="5" t="n"/>
+      <c r="I273" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="174">
     <mergeCell ref="B31:B65"/>
+    <mergeCell ref="C210:C213"/>
+    <mergeCell ref="D118:D120"/>
+    <mergeCell ref="I17:I30"/>
     <mergeCell ref="I180:I186"/>
-    <mergeCell ref="I17:I30"/>
-    <mergeCell ref="D118:D120"/>
     <mergeCell ref="A17:A30"/>
     <mergeCell ref="I92:I96"/>
+    <mergeCell ref="B121:B124"/>
     <mergeCell ref="D12:D16"/>
-    <mergeCell ref="B121:B124"/>
-    <mergeCell ref="B194:B201"/>
     <mergeCell ref="I173:I179"/>
+    <mergeCell ref="C265:C270"/>
     <mergeCell ref="I70:I75"/>
+    <mergeCell ref="C121:C124"/>
     <mergeCell ref="I97:I102"/>
-    <mergeCell ref="I209:I212"/>
-    <mergeCell ref="C121:C124"/>
-    <mergeCell ref="D253:D256"/>
-    <mergeCell ref="B236:B247"/>
+    <mergeCell ref="B214:B236"/>
     <mergeCell ref="B173:B179"/>
     <mergeCell ref="C31:C34"/>
     <mergeCell ref="D173:D179"/>
     <mergeCell ref="C89:C91"/>
     <mergeCell ref="I56:I61"/>
+    <mergeCell ref="D262:D264"/>
     <mergeCell ref="D35:D41"/>
-    <mergeCell ref="B253:B260"/>
     <mergeCell ref="C56:C61"/>
+    <mergeCell ref="C161:C167"/>
+    <mergeCell ref="C42:C55"/>
     <mergeCell ref="A2:A16"/>
-    <mergeCell ref="C42:C55"/>
-    <mergeCell ref="C161:C167"/>
-    <mergeCell ref="I253:I256"/>
+    <mergeCell ref="B203:B209"/>
     <mergeCell ref="C118:C120"/>
+    <mergeCell ref="D203:D209"/>
     <mergeCell ref="B125:B142"/>
-    <mergeCell ref="D213:D235"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="C154:C160"/>
     <mergeCell ref="C66:C69"/>
     <mergeCell ref="B180:B186"/>
+    <mergeCell ref="I271:I273"/>
     <mergeCell ref="D17:D30"/>
+    <mergeCell ref="B254:B261"/>
+    <mergeCell ref="I118:I120"/>
+    <mergeCell ref="A187:A193"/>
     <mergeCell ref="D143:D150"/>
-    <mergeCell ref="A187:A193"/>
-    <mergeCell ref="I118:I120"/>
     <mergeCell ref="C187:C193"/>
-    <mergeCell ref="C270:C272"/>
+    <mergeCell ref="I12:I16"/>
     <mergeCell ref="I115:I117"/>
-    <mergeCell ref="I12:I16"/>
     <mergeCell ref="B111:B117"/>
     <mergeCell ref="I76:I84"/>
     <mergeCell ref="C115:C117"/>
-    <mergeCell ref="I248:I252"/>
-    <mergeCell ref="D85:D88"/>
     <mergeCell ref="C35:C41"/>
     <mergeCell ref="C180:C186"/>
+    <mergeCell ref="C254:C257"/>
     <mergeCell ref="D137:D141"/>
-    <mergeCell ref="I257:I260"/>
+    <mergeCell ref="C262:C264"/>
+    <mergeCell ref="D258:D261"/>
     <mergeCell ref="D42:D55"/>
-    <mergeCell ref="A261:A272"/>
     <mergeCell ref="C97:C102"/>
+    <mergeCell ref="I262:I264"/>
+    <mergeCell ref="A249:A253"/>
     <mergeCell ref="D161:D167"/>
+    <mergeCell ref="C249:C253"/>
+    <mergeCell ref="I258:I261"/>
     <mergeCell ref="I168:I172"/>
     <mergeCell ref="I62:I65"/>
     <mergeCell ref="D6:D8"/>
-    <mergeCell ref="I213:I235"/>
+    <mergeCell ref="B89:B110"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="A111:A117"/>
     <mergeCell ref="I89:I91"/>
-    <mergeCell ref="I202:I208"/>
-    <mergeCell ref="A111:A117"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="A202:A208"/>
-    <mergeCell ref="B89:B110"/>
     <mergeCell ref="D9:D10"/>
-    <mergeCell ref="C248:C252"/>
     <mergeCell ref="C92:C96"/>
+    <mergeCell ref="A237:A248"/>
+    <mergeCell ref="I237:I248"/>
     <mergeCell ref="D187:D193"/>
-    <mergeCell ref="A209:A212"/>
     <mergeCell ref="I143:I150"/>
-    <mergeCell ref="C209:C212"/>
-    <mergeCell ref="B248:B252"/>
     <mergeCell ref="I125:I136"/>
-    <mergeCell ref="D264:D269"/>
     <mergeCell ref="D62:D65"/>
     <mergeCell ref="C70:C75"/>
     <mergeCell ref="A31:A65"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="C202:C208"/>
+    <mergeCell ref="C62:C65"/>
     <mergeCell ref="A121:A124"/>
-    <mergeCell ref="C261:C263"/>
-    <mergeCell ref="A194:A201"/>
-    <mergeCell ref="C194:C201"/>
-    <mergeCell ref="D236:D247"/>
+    <mergeCell ref="B249:B253"/>
+    <mergeCell ref="D265:D270"/>
+    <mergeCell ref="I194:I202"/>
+    <mergeCell ref="A262:A273"/>
+    <mergeCell ref="A143:A172"/>
     <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A143:A172"/>
     <mergeCell ref="I161:I167"/>
     <mergeCell ref="D103:D107"/>
+    <mergeCell ref="I85:I88"/>
     <mergeCell ref="D168:D172"/>
-    <mergeCell ref="I85:I88"/>
     <mergeCell ref="C173:C179"/>
-    <mergeCell ref="B213:B235"/>
     <mergeCell ref="C85:C88"/>
     <mergeCell ref="D89:D91"/>
     <mergeCell ref="I6:I8"/>
+    <mergeCell ref="C194:C202"/>
     <mergeCell ref="C76:C84"/>
-    <mergeCell ref="D202:D208"/>
     <mergeCell ref="C125:C136"/>
     <mergeCell ref="D70:D75"/>
+    <mergeCell ref="D237:D248"/>
+    <mergeCell ref="I249:I253"/>
+    <mergeCell ref="A203:A209"/>
     <mergeCell ref="B2:B16"/>
+    <mergeCell ref="D271:D273"/>
+    <mergeCell ref="I187:I193"/>
     <mergeCell ref="A125:A142"/>
-    <mergeCell ref="D209:D212"/>
-    <mergeCell ref="I187:I193"/>
     <mergeCell ref="C108:C110"/>
+    <mergeCell ref="B210:B213"/>
     <mergeCell ref="I35:I41"/>
-    <mergeCell ref="I264:I269"/>
+    <mergeCell ref="A180:A186"/>
     <mergeCell ref="D66:D69"/>
-    <mergeCell ref="A180:A186"/>
     <mergeCell ref="D115:D117"/>
-    <mergeCell ref="C257:C260"/>
     <mergeCell ref="C143:C150"/>
+    <mergeCell ref="A210:A213"/>
     <mergeCell ref="D56:D61"/>
-    <mergeCell ref="D270:D272"/>
     <mergeCell ref="D121:D124"/>
+    <mergeCell ref="I111:I114"/>
     <mergeCell ref="D108:D110"/>
-    <mergeCell ref="A236:A247"/>
-    <mergeCell ref="I111:I114"/>
-    <mergeCell ref="C236:C247"/>
-    <mergeCell ref="D194:D201"/>
+    <mergeCell ref="B194:B202"/>
     <mergeCell ref="A66:A88"/>
+    <mergeCell ref="I265:I270"/>
     <mergeCell ref="C137:C141"/>
+    <mergeCell ref="A254:A261"/>
     <mergeCell ref="B143:B172"/>
+    <mergeCell ref="C258:C261"/>
     <mergeCell ref="C111:C114"/>
-    <mergeCell ref="I236:I247"/>
     <mergeCell ref="D151:D153"/>
+    <mergeCell ref="D214:D236"/>
     <mergeCell ref="I103:I107"/>
     <mergeCell ref="D154:D160"/>
+    <mergeCell ref="D194:D202"/>
+    <mergeCell ref="C237:C248"/>
     <mergeCell ref="D76:D84"/>
     <mergeCell ref="C17:C30"/>
     <mergeCell ref="D31:D34"/>
+    <mergeCell ref="I210:I213"/>
     <mergeCell ref="B187:B193"/>
     <mergeCell ref="I42:I55"/>
-    <mergeCell ref="D257:D260"/>
     <mergeCell ref="B118:B120"/>
     <mergeCell ref="A89:A110"/>
-    <mergeCell ref="B261:B272"/>
+    <mergeCell ref="C203:C209"/>
     <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D254:D257"/>
+    <mergeCell ref="A194:A202"/>
+    <mergeCell ref="I66:I69"/>
     <mergeCell ref="D180:D186"/>
-    <mergeCell ref="I66:I69"/>
     <mergeCell ref="D92:D96"/>
+    <mergeCell ref="B237:B248"/>
     <mergeCell ref="B66:B88"/>
-    <mergeCell ref="I261:I263"/>
+    <mergeCell ref="D210:D213"/>
     <mergeCell ref="D111:D114"/>
-    <mergeCell ref="I270:I272"/>
     <mergeCell ref="I121:I124"/>
+    <mergeCell ref="I137:I141"/>
     <mergeCell ref="I108:I110"/>
-    <mergeCell ref="I137:I141"/>
     <mergeCell ref="C6:C8"/>
-    <mergeCell ref="I194:I201"/>
     <mergeCell ref="C151:C153"/>
     <mergeCell ref="D97:D102"/>
-    <mergeCell ref="B202:B208"/>
-    <mergeCell ref="C253:C256"/>
-    <mergeCell ref="D261:D263"/>
+    <mergeCell ref="I254:I257"/>
+    <mergeCell ref="D249:D253"/>
     <mergeCell ref="B17:B30"/>
     <mergeCell ref="I151:I153"/>
+    <mergeCell ref="I214:I236"/>
     <mergeCell ref="A173:A179"/>
+    <mergeCell ref="A118:A120"/>
     <mergeCell ref="D125:D136"/>
-    <mergeCell ref="A118:A120"/>
+    <mergeCell ref="C271:C273"/>
     <mergeCell ref="I154:I160"/>
-    <mergeCell ref="D248:D252"/>
+    <mergeCell ref="B262:B273"/>
+    <mergeCell ref="A214:A236"/>
+    <mergeCell ref="C214:C236"/>
+    <mergeCell ref="C103:C107"/>
     <mergeCell ref="I31:I34"/>
-    <mergeCell ref="A253:A260"/>
-    <mergeCell ref="C103:C107"/>
+    <mergeCell ref="C12:C16"/>
     <mergeCell ref="C168:C172"/>
-    <mergeCell ref="C12:C16"/>
-    <mergeCell ref="B209:B212"/>
-    <mergeCell ref="A248:A252"/>
-    <mergeCell ref="A213:A235"/>
-    <mergeCell ref="C264:C269"/>
-    <mergeCell ref="C213:C235"/>
-    <mergeCell ref="C62:C65"/>
+    <mergeCell ref="I203:I209"/>
+    <mergeCell ref="D85:D88"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -5125,13 +5125,13 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>genreでジャンルIDによる絞り込みができる</t>
+          <t>genre_idでジャンルIDによる絞り込みができる</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
           <t>1.異なるジャンルの書籍を用意する
-2.genreにジャンルIDを指定してGET /api/v1/booksにアクセスする</t>
+2.genre_idにジャンルIDを指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H148" s="3" t="inlineStr">
@@ -5153,18 +5153,18 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>pageでページを移動できる(1ページ10件固定)</t>
+          <t>pageでページを移動できる(1ページ20件固定)</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>1.11件の書籍を用意する
+          <t>1.21件の書籍を用意する
 2.pageを指定せずに、およびpage=2を指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H149" s="3" t="inlineStr">
         <is>
-          <t>pageなしでは1ページ目の10件、page=2では残りの1件が返り、meta・linksにページ情報が反映される</t>
+          <t>pageなしでは1ページ目の20件、page=2では残りの1件が返り、meta・linksにページ情報が反映される</t>
         </is>
       </c>
       <c r="I149" s="4" t="n"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>1.genreに存在しないID、pageに0をそれぞれ指定してGET /api/v1/booksにアクセスする(Accept: application/json)</t>
+          <t>1.genre_idに存在しないID、pageに0をそれぞれ指定してGET /api/v1/booksにアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H150" s="3" t="inlineStr">
@@ -8897,9 +8897,9 @@
   <mergeCells count="174">
     <mergeCell ref="B31:B65"/>
     <mergeCell ref="C210:C213"/>
-    <mergeCell ref="D118:D120"/>
     <mergeCell ref="I17:I30"/>
     <mergeCell ref="I180:I186"/>
+    <mergeCell ref="D118:D120"/>
     <mergeCell ref="A17:A30"/>
     <mergeCell ref="I92:I96"/>
     <mergeCell ref="B121:B124"/>
@@ -8907,8 +8907,8 @@
     <mergeCell ref="I173:I179"/>
     <mergeCell ref="C265:C270"/>
     <mergeCell ref="I70:I75"/>
+    <mergeCell ref="I97:I102"/>
     <mergeCell ref="C121:C124"/>
-    <mergeCell ref="I97:I102"/>
     <mergeCell ref="B214:B236"/>
     <mergeCell ref="B173:B179"/>
     <mergeCell ref="C31:C34"/>
@@ -8932,12 +8932,12 @@
     <mergeCell ref="I271:I273"/>
     <mergeCell ref="D17:D30"/>
     <mergeCell ref="B254:B261"/>
+    <mergeCell ref="A187:A193"/>
     <mergeCell ref="I118:I120"/>
-    <mergeCell ref="A187:A193"/>
     <mergeCell ref="D143:D150"/>
     <mergeCell ref="C187:C193"/>
+    <mergeCell ref="I115:I117"/>
     <mergeCell ref="I12:I16"/>
-    <mergeCell ref="I115:I117"/>
     <mergeCell ref="B111:B117"/>
     <mergeCell ref="I76:I84"/>
     <mergeCell ref="C115:C117"/>
@@ -8957,14 +8957,14 @@
     <mergeCell ref="I168:I172"/>
     <mergeCell ref="I62:I65"/>
     <mergeCell ref="D6:D8"/>
-    <mergeCell ref="B89:B110"/>
+    <mergeCell ref="I89:I91"/>
     <mergeCell ref="I2:I4"/>
     <mergeCell ref="A111:A117"/>
-    <mergeCell ref="I89:I91"/>
+    <mergeCell ref="B89:B110"/>
     <mergeCell ref="D9:D10"/>
+    <mergeCell ref="I237:I248"/>
     <mergeCell ref="C92:C96"/>
     <mergeCell ref="A237:A248"/>
-    <mergeCell ref="I237:I248"/>
     <mergeCell ref="D187:D193"/>
     <mergeCell ref="I143:I150"/>
     <mergeCell ref="I125:I136"/>
@@ -8996,9 +8996,9 @@
     <mergeCell ref="I249:I253"/>
     <mergeCell ref="A203:A209"/>
     <mergeCell ref="B2:B16"/>
+    <mergeCell ref="A125:A142"/>
     <mergeCell ref="D271:D273"/>
     <mergeCell ref="I187:I193"/>
-    <mergeCell ref="A125:A142"/>
     <mergeCell ref="C108:C110"/>
     <mergeCell ref="B210:B213"/>
     <mergeCell ref="I35:I41"/>
@@ -9006,8 +9006,8 @@
     <mergeCell ref="D66:D69"/>
     <mergeCell ref="D115:D117"/>
     <mergeCell ref="C143:C150"/>
+    <mergeCell ref="D56:D61"/>
     <mergeCell ref="A210:A213"/>
-    <mergeCell ref="D56:D61"/>
     <mergeCell ref="D121:D124"/>
     <mergeCell ref="I111:I114"/>
     <mergeCell ref="D108:D110"/>
@@ -9017,8 +9017,8 @@
     <mergeCell ref="C137:C141"/>
     <mergeCell ref="A254:A261"/>
     <mergeCell ref="B143:B172"/>
+    <mergeCell ref="C111:C114"/>
     <mergeCell ref="C258:C261"/>
-    <mergeCell ref="C111:C114"/>
     <mergeCell ref="D151:D153"/>
     <mergeCell ref="D214:D236"/>
     <mergeCell ref="I103:I107"/>
@@ -9035,18 +9035,18 @@
     <mergeCell ref="A89:A110"/>
     <mergeCell ref="C203:C209"/>
     <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D180:D186"/>
     <mergeCell ref="D254:D257"/>
     <mergeCell ref="A194:A202"/>
     <mergeCell ref="I66:I69"/>
-    <mergeCell ref="D180:D186"/>
     <mergeCell ref="D92:D96"/>
     <mergeCell ref="B237:B248"/>
     <mergeCell ref="B66:B88"/>
     <mergeCell ref="D210:D213"/>
     <mergeCell ref="D111:D114"/>
     <mergeCell ref="I121:I124"/>
+    <mergeCell ref="I108:I110"/>
     <mergeCell ref="I137:I141"/>
-    <mergeCell ref="I108:I110"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C151:C153"/>
     <mergeCell ref="D97:D102"/>
@@ -9058,15 +9058,15 @@
     <mergeCell ref="A173:A179"/>
     <mergeCell ref="A118:A120"/>
     <mergeCell ref="D125:D136"/>
+    <mergeCell ref="I154:I160"/>
     <mergeCell ref="C271:C273"/>
-    <mergeCell ref="I154:I160"/>
+    <mergeCell ref="A214:A236"/>
     <mergeCell ref="B262:B273"/>
-    <mergeCell ref="A214:A236"/>
     <mergeCell ref="C214:C236"/>
+    <mergeCell ref="I31:I34"/>
     <mergeCell ref="C103:C107"/>
-    <mergeCell ref="I31:I34"/>
+    <mergeCell ref="C168:C172"/>
     <mergeCell ref="C12:C16"/>
-    <mergeCell ref="C168:C172"/>
     <mergeCell ref="I203:I209"/>
     <mergeCell ref="D85:D88"/>
   </mergeCells>

--- a/テストケース一覧.xlsx
+++ b/テストケース一覧.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I273"/>
+  <dimension ref="A1:I275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="F149" s="3" t="inlineStr">
         <is>
-          <t>pageでページを移動できる(1ページ20件固定)</t>
+          <t>pageでページを移動できる(per_page未指定の場合は1ページ20件)</t>
         </is>
       </c>
       <c r="G149" s="3" t="inlineStr">
@@ -5172,8 +5172,8 @@
     <row r="150">
       <c r="A150" s="4" t="n"/>
       <c r="B150" s="4" t="n"/>
-      <c r="C150" s="5" t="n"/>
-      <c r="D150" s="5" t="n"/>
+      <c r="C150" s="4" t="n"/>
+      <c r="D150" s="4" t="n"/>
       <c r="E150" s="3" t="inlineStr">
         <is>
           <t>10-1-8</t>
@@ -5194,196 +5194,196 @@
           <t>422が返り、「指定されたジャンルは存在しません」「ページ番号は1以上の値で指定してください」が返る</t>
         </is>
       </c>
-      <c r="I150" s="5" t="n"/>
+      <c r="I150" s="4" t="n"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="n"/>
       <c r="B151" s="4" t="n"/>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>10-2</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>AP02:書籍詳細API(GET /api/v1/books/{book})</t>
-        </is>
-      </c>
+      <c r="C151" s="4" t="n"/>
+      <c r="D151" s="4" t="n"/>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>10-2-1</t>
+          <t>10-1-9</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
-          <t>認証なしでもアクセスでき、書籍の詳細が返る</t>
+          <t>per_pageで1ページの件数を指定できる(1〜100件)</t>
         </is>
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンルとレビューを持つ書籍を用意する
-2.認証情報を付与せずGET /api/v1/books/{book}にアクセスする</t>
+          <t>1.101件の書籍を用意する
+2.per_page=1、per_page=100をそれぞれ指定してGET /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H151" s="3" t="inlineStr">
         <is>
-          <t>200が返り、書籍情報・genres・average_rating・review_countを含むJSONが返る</t>
-        </is>
-      </c>
-      <c r="I151" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiShowTest.php</t>
-        </is>
-      </c>
+          <t>per_page=1では1件(last_pageは101)、per_page=100では100件(last_pageは2)が返り、meta.per_pageに指定した件数が反映される。links.nextにもper_pageが引き継がれる</t>
+        </is>
+      </c>
+      <c r="I151" s="4" t="n"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n"/>
       <c r="B152" s="4" t="n"/>
-      <c r="C152" s="4" t="n"/>
-      <c r="D152" s="4" t="n"/>
+      <c r="C152" s="5" t="n"/>
+      <c r="D152" s="5" t="n"/>
       <c r="E152" s="3" t="inlineStr">
         <is>
-          <t>10-2-2</t>
+          <t>10-1-10</t>
         </is>
       </c>
       <c r="F152" s="3" t="inlineStr">
         <is>
-          <t>レビュー(投稿者名・評価・コメント・投稿日時)が新しい順に含まれる</t>
+          <t>per_pageが1〜100の整数でない場合、422が返る</t>
         </is>
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>1.異なる日時に投稿された複数のレビューを持つ書籍を用意する
-2.GET /api/v1/books/{book}にアクセスする</t>
+          <t>1.per_pageに0、101、abcをそれぞれ指定してGET /api/v1/booksにアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H152" s="3" t="inlineStr">
         <is>
-          <t>reviewsにuser_name・rating・comment・created_atが含まれ、投稿日時の新しい順に並ぶ</t>
-        </is>
-      </c>
-      <c r="I152" s="4" t="n"/>
+          <t>422が返り、「1ページの件数は1以上の値で指定してください」「1ページの件数は100以下の値で指定してください」「1ページの件数は整数で指定してください」が返る</t>
+        </is>
+      </c>
+      <c r="I152" s="5" t="n"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n"/>
       <c r="B153" s="4" t="n"/>
-      <c r="C153" s="5" t="n"/>
-      <c r="D153" s="5" t="n"/>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>10-2</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>AP02:書籍詳細API(GET /api/v1/books/{book})</t>
+        </is>
+      </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>10-2-3</t>
+          <t>10-2-1</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
         <is>
-          <t>存在しないIDを指定すると404が返る</t>
+          <t>認証なしでもアクセスでき、書籍の詳細が返る</t>
         </is>
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>1.存在しない書籍IDでGET /api/v1/books/{book}にアクセスする</t>
+          <t>1.ジャンルとレビューを持つ書籍を用意する
+2.認証情報を付与せずGET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H153" s="3" t="inlineStr">
         <is>
-          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
-        </is>
-      </c>
-      <c r="I153" s="5" t="n"/>
+          <t>200が返り、書籍情報・genres・average_rating・review_countを含むJSONが返る</t>
+        </is>
+      </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiShowTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="n"/>
       <c r="B154" s="4" t="n"/>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>10-3</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>AP03:書籍登録API(POST /api/v1/books)</t>
-        </is>
-      </c>
+      <c r="C154" s="4" t="n"/>
+      <c r="D154" s="4" t="n"/>
       <c r="E154" s="3" t="inlineStr">
         <is>
-          <t>10-3-1</t>
+          <t>10-2-2</t>
         </is>
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>認証なしでアクセスすると401が返る</t>
+          <t>レビュー(投稿者名・評価・コメント・投稿日時)が新しい順に含まれる</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>1.認証情報を付与せずPOST /api/v1/booksにアクセスする(Accept: application/json)</t>
+          <t>1.異なる日時に投稿された複数のレビューを持つ書籍を用意する
+2.GET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録されない</t>
-        </is>
-      </c>
-      <c r="I154" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiStoreTest.php</t>
-        </is>
-      </c>
+          <t>reviewsにuser_name・rating・comment・created_atが含まれ、投稿日時の新しい順に並ぶ</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n"/>
       <c r="B155" s="4" t="n"/>
-      <c r="C155" s="4" t="n"/>
-      <c r="D155" s="4" t="n"/>
+      <c r="C155" s="5" t="n"/>
+      <c r="D155" s="5" t="n"/>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>10-3-2</t>
+          <t>10-2-3</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
-          <t>有効なトークンで書籍を登録できる</t>
+          <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーのトークンを発行する
-2.必要項目を指定し、Bearerトークンを付与してPOST /api/v1/booksにアクセスする</t>
+          <t>1.存在しない書籍IDでGET /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr">
         <is>
-          <t>201が返り、登録内容がJSONで返る。書籍がDBに保存される</t>
-        </is>
-      </c>
-      <c r="I155" s="4" t="n"/>
+          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
+        </is>
+      </c>
+      <c r="I155" s="5" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n"/>
       <c r="B156" s="4" t="n"/>
-      <c r="C156" s="4" t="n"/>
-      <c r="D156" s="4" t="n"/>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>10-3</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>AP03:書籍登録API(POST /api/v1/books)</t>
+        </is>
+      </c>
       <c r="E156" s="3" t="inlineStr">
         <is>
-          <t>10-3-3</t>
+          <t>10-3-1</t>
         </is>
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>登録者(user_id)は、リクエストの値ではなく認証ユーザーになる</t>
+          <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>1.他のユーザーのIDをuser_idに含めて、トークンを付与しPOST /api/v1/booksにアクセスする</t>
+          <t>1.認証情報を付与せずPOST /api/v1/booksにアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H156" s="3" t="inlineStr">
         <is>
-          <t>登録された書籍のuser_idは、トークンの持ち主(認証ユーザー)のIDになる</t>
-        </is>
-      </c>
-      <c r="I156" s="4" t="n"/>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録されない</t>
+        </is>
+      </c>
+      <c r="I156" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiStoreTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="n"/>
@@ -5392,22 +5392,23 @@
       <c r="D157" s="4" t="n"/>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>10-3-4</t>
+          <t>10-3-2</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
         <is>
-          <t>選択したジャンルが書籍に紐づけられる</t>
+          <t>有効なトークンで書籍を登録できる</t>
         </is>
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>1.複数のジャンルIDをgenresに指定してPOST /api/v1/booksにアクセスする</t>
+          <t>1.ユーザーのトークンを発行する
+2.必要項目を指定し、Bearerトークンを付与してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H157" s="3" t="inlineStr">
         <is>
-          <t>中間テーブル(book_genre)に指定したジャンルが保存され、レスポンスのgenresにも含まれる</t>
+          <t>201が返り、登録内容がJSONで返る。書籍がDBに保存される</t>
         </is>
       </c>
       <c r="I157" s="4" t="n"/>
@@ -5419,22 +5420,22 @@
       <c r="D158" s="4" t="n"/>
       <c r="E158" s="3" t="inlineStr">
         <is>
-          <t>10-3-5</t>
+          <t>10-3-3</t>
         </is>
       </c>
       <c r="F158" s="3" t="inlineStr">
         <is>
-          <t>必須項目(title・author・genres)が未入力の場合、422が返る</t>
+          <t>登録者(user_id)は、リクエストの値ではなく認証ユーザーになる</t>
         </is>
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>1.title・author・genresを指定せずにPOST /api/v1/booksにアクセスする</t>
+          <t>1.他のユーザーのIDをuser_idに含めて、トークンを付与しPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H158" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「書籍タイトルを入力してください」「著者名を入力してください」「ジャンルを1つ以上選択してください」が返る</t>
+          <t>登録された書籍のuser_idは、トークンの持ち主(認証ユーザー)のIDになる</t>
         </is>
       </c>
       <c r="I158" s="4" t="n"/>
@@ -5446,23 +5447,22 @@
       <c r="D159" s="4" t="n"/>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>10-3-6</t>
+          <t>10-3-4</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
-          <t>ISBNが13桁の数字でない、または登録済みの場合、422が返る</t>
+          <t>選択したジャンルが書籍に紐づけられる</t>
         </is>
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>1.ISBNに13桁でない値を指定してPOST /api/v1/booksにアクセスする
-2.登録済みのISBNを指定して同様にアクセスする</t>
+          <t>1.複数のジャンルIDをgenresに指定してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H159" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「ISBNは13桁の数字で入力してください」「このISBNはすでに登録されています」が返る</t>
+          <t>中間テーブル(book_genre)に指定したジャンルが保存され、レスポンスのgenresにも含まれる</t>
         </is>
       </c>
       <c r="I159" s="4" t="n"/>
@@ -5470,124 +5470,123 @@
     <row r="160">
       <c r="A160" s="4" t="n"/>
       <c r="B160" s="4" t="n"/>
-      <c r="C160" s="5" t="n"/>
-      <c r="D160" s="5" t="n"/>
+      <c r="C160" s="4" t="n"/>
+      <c r="D160" s="4" t="n"/>
       <c r="E160" s="3" t="inlineStr">
         <is>
-          <t>10-3-7</t>
+          <t>10-3-5</t>
         </is>
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>存在しないジャンルIDを指定すると422が返る</t>
+          <t>必須項目(title・author・genres)が未入力の場合、422が返る</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>1.genresに存在しないジャンルIDを指定してPOST /api/v1/booksにアクセスする</t>
+          <t>1.title・author・genresを指定せずにPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H160" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「選択されたジャンルは存在しません」が返る</t>
-        </is>
-      </c>
-      <c r="I160" s="5" t="n"/>
+          <t>422が返り、「書籍タイトルを入力してください」「著者名を入力してください」「ジャンルを1つ以上選択してください」が返る</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="n"/>
       <c r="B161" s="4" t="n"/>
-      <c r="C161" s="3" t="inlineStr">
-        <is>
-          <t>10-4</t>
-        </is>
-      </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>AP04:書籍更新API(PUT /api/v1/books/{book})</t>
-        </is>
-      </c>
+      <c r="C161" s="4" t="n"/>
+      <c r="D161" s="4" t="n"/>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>10-4-1</t>
+          <t>10-3-6</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
         <is>
-          <t>認証なしでアクセスすると401が返る</t>
+          <t>ISBNが13桁の数字でない、または登録済みの場合、422が返る</t>
         </is>
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>1.認証情報を付与せずPUT /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
+          <t>1.ISBNに13桁でない値を指定してPOST /api/v1/booksにアクセスする
+2.登録済みのISBNを指定して同様にアクセスする</t>
         </is>
       </c>
       <c r="H161" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は更新されない</t>
-        </is>
-      </c>
-      <c r="I161" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiUpdateTest.php</t>
-        </is>
-      </c>
+          <t>422が返り、「ISBNは13桁の数字で入力してください」「このISBNはすでに登録されています」が返る</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="n"/>
       <c r="B162" s="4" t="n"/>
-      <c r="C162" s="4" t="n"/>
-      <c r="D162" s="4" t="n"/>
+      <c r="C162" s="5" t="n"/>
+      <c r="D162" s="5" t="n"/>
       <c r="E162" s="3" t="inlineStr">
         <is>
-          <t>10-4-2</t>
+          <t>10-3-7</t>
         </is>
       </c>
       <c r="F162" s="3" t="inlineStr">
         <is>
-          <t>自分が登録した書籍を更新できる</t>
+          <t>存在しないジャンルIDを指定すると422が返る</t>
         </is>
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーが登録した書籍を用意する
-2.そのユーザーのトークンを付与し、変更内容・ジャンルを指定してPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.genresに存在しないジャンルIDを指定してPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
       <c r="H162" s="3" t="inlineStr">
         <is>
-          <t>200が返り、更新後の内容がJSONで返る。DBの書籍情報とジャンルの紐づけが更新される</t>
-        </is>
-      </c>
-      <c r="I162" s="4" t="n"/>
+          <t>422が返り、「選択されたジャンルは存在しません」が返る</t>
+        </is>
+      </c>
+      <c r="I162" s="5" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="n"/>
       <c r="B163" s="4" t="n"/>
-      <c r="C163" s="4" t="n"/>
-      <c r="D163" s="4" t="n"/>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>10-4</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>AP04:書籍更新API(PUT /api/v1/books/{book})</t>
+        </is>
+      </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>10-4-3</t>
+          <t>10-4-1</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
         <is>
-          <t>自分の書籍のISBNを変更せずに更新しても、ISBNの重複エラーにならない</t>
+          <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーが登録した書籍(ISBNあり)を用意する
-2.ISBNを変えずに他の項目を変更してPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.認証情報を付与せずPUT /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H163" s="3" t="inlineStr">
         <is>
-          <t>200が返り、更新できる</t>
-        </is>
-      </c>
-      <c r="I163" s="4" t="n"/>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I163" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiUpdateTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="n"/>
@@ -5596,23 +5595,23 @@
       <c r="D164" s="4" t="n"/>
       <c r="E164" s="3" t="inlineStr">
         <is>
-          <t>10-4-4</t>
+          <t>10-4-2</t>
         </is>
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>他のユーザーが登録した書籍は更新できない</t>
+          <t>自分が登録した書籍を更新できる</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>1.他のユーザーが登録した書籍を用意する
-2.別のユーザーのトークンを付与してPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.ユーザーが登録した書籍を用意する
+2.そのユーザーのトークンを付与し、変更内容・ジャンルを指定してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H164" s="3" t="inlineStr">
         <is>
-          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は更新されない</t>
+          <t>200が返り、更新後の内容がJSONで返る。DBの書籍情報とジャンルの紐づけが更新される</t>
         </is>
       </c>
       <c r="I164" s="4" t="n"/>
@@ -5624,22 +5623,23 @@
       <c r="D165" s="4" t="n"/>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>10-4-5</t>
+          <t>10-4-3</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
-          <t>存在しないIDを指定すると404が返る</t>
+          <t>自分の書籍のISBNを変更せずに更新しても、ISBNの重複エラーにならない</t>
         </is>
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>1.トークンを付与し、存在しない書籍IDでPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.ユーザーが登録した書籍(ISBNあり)を用意する
+2.ISBNを変えずに他の項目を変更してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H165" s="3" t="inlineStr">
         <is>
-          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
+          <t>200が返り、更新できる</t>
         </is>
       </c>
       <c r="I165" s="4" t="n"/>
@@ -5651,22 +5651,23 @@
       <c r="D166" s="4" t="n"/>
       <c r="E166" s="3" t="inlineStr">
         <is>
-          <t>10-4-6</t>
+          <t>10-4-4</t>
         </is>
       </c>
       <c r="F166" s="3" t="inlineStr">
         <is>
-          <t>入力内容が不正な場合、422が返る</t>
+          <t>他のユーザーが登録した書籍は更新できない</t>
         </is>
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>1.自分の書籍に対し、titleを空にしてPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.他のユーザーが登録した書籍を用意する
+2.別のユーザーのトークンを付与してPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H166" s="3" t="inlineStr">
         <is>
-          <t>422が返り、「書籍タイトルを入力してください」が返る。書籍は更新されない</t>
+          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は更新されない</t>
         </is>
       </c>
       <c r="I166" s="4" t="n"/>
@@ -5674,125 +5675,123 @@
     <row r="167">
       <c r="A167" s="4" t="n"/>
       <c r="B167" s="4" t="n"/>
-      <c r="C167" s="5" t="n"/>
-      <c r="D167" s="5" t="n"/>
+      <c r="C167" s="4" t="n"/>
+      <c r="D167" s="4" t="n"/>
       <c r="E167" s="3" t="inlineStr">
         <is>
-          <t>10-4-7</t>
+          <t>10-4-5</t>
         </is>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
-          <t>他のユーザーが登録した書籍に対して不正な入力で更新しようとしても、422ではなく403が返る</t>
+          <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>1.他のユーザーが登録した書籍を用意する
-2.別のユーザーのトークンを付与し、タイトルを空にするなど不正な内容でPUT /api/v1/books/{book}にアクセスする</t>
+          <t>1.トークンを付与し、存在しない書籍IDでPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H167" s="3" t="inlineStr">
         <is>
-          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る（入力チェックより先に権限が判定される）。書籍は更新されない</t>
-        </is>
-      </c>
-      <c r="I167" s="5" t="n"/>
+          <t>404が返り、「指定された書籍が見つかりません」が返る</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="n"/>
     </row>
     <row r="168">
       <c r="A168" s="4" t="n"/>
       <c r="B168" s="4" t="n"/>
-      <c r="C168" s="3" t="inlineStr">
-        <is>
-          <t>10-5</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>AP05:書籍削除API(DELETE /api/v1/books/{book})</t>
-        </is>
-      </c>
+      <c r="C168" s="4" t="n"/>
+      <c r="D168" s="4" t="n"/>
       <c r="E168" s="3" t="inlineStr">
         <is>
-          <t>10-5-1</t>
+          <t>10-4-6</t>
         </is>
       </c>
       <c r="F168" s="3" t="inlineStr">
         <is>
-          <t>認証なしでアクセスすると401が返る</t>
+          <t>入力内容が不正な場合、422が返る</t>
         </is>
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>1.認証情報を付与せずDELETE /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
+          <t>1.自分の書籍に対し、titleを空にしてPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H168" s="3" t="inlineStr">
         <is>
-          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は削除されない</t>
-        </is>
-      </c>
-      <c r="I168" s="3" t="inlineStr">
-        <is>
-          <t>tests/Feature/PublicApi/BookApiDestroyTest.php</t>
-        </is>
-      </c>
+          <t>422が返り、「書籍タイトルを入力してください」が返る。書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="4" t="n"/>
       <c r="B169" s="4" t="n"/>
-      <c r="C169" s="4" t="n"/>
-      <c r="D169" s="4" t="n"/>
+      <c r="C169" s="5" t="n"/>
+      <c r="D169" s="5" t="n"/>
       <c r="E169" s="3" t="inlineStr">
         <is>
-          <t>10-5-2</t>
+          <t>10-4-7</t>
         </is>
       </c>
       <c r="F169" s="3" t="inlineStr">
         <is>
-          <t>自分が登録した書籍を削除できる</t>
+          <t>他のユーザーが登録した書籍に対して不正な入力で更新しようとしても、422ではなく403が返る</t>
         </is>
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>1.ユーザーが登録した書籍を用意する
-2.そのユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
+          <t>1.他のユーザーが登録した書籍を用意する
+2.別のユーザーのトークンを付与し、タイトルを空にするなど不正な内容でPUT /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
       <c r="H169" s="3" t="inlineStr">
         <is>
-          <t>204が返り(レスポンスボディなし)、書籍がDBから削除される</t>
-        </is>
-      </c>
-      <c r="I169" s="4" t="n"/>
+          <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る（入力チェックより先に権限が判定される）。書籍は更新されない</t>
+        </is>
+      </c>
+      <c r="I169" s="5" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="n"/>
       <c r="B170" s="4" t="n"/>
-      <c r="C170" s="4" t="n"/>
-      <c r="D170" s="4" t="n"/>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>10-5</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>AP05:書籍削除API(DELETE /api/v1/books/{book})</t>
+        </is>
+      </c>
       <c r="E170" s="3" t="inlineStr">
         <is>
-          <t>10-5-3</t>
+          <t>10-5-1</t>
         </is>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
-          <t>書籍を削除すると、関連するデータも一緒に削除される</t>
+          <t>認証なしでアクセスすると401が返る</t>
         </is>
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>1.ジャンルの紐づけ・レビュー・お気に入り・レビューへのいいねを持つ書籍を用意する
-2.所有者のトークンでDELETE /api/v1/books/{book}にアクセスする</t>
+          <t>1.認証情報を付与せずDELETE /api/v1/books/{book}にアクセスする(Accept: application/json)</t>
         </is>
       </c>
       <c r="H170" s="3" t="inlineStr">
         <is>
-          <t>book_genre・reviews・favorites・review_likesの該当データも削除される</t>
-        </is>
-      </c>
-      <c r="I170" s="4" t="n"/>
+          <t>401 Unauthorizedが返り、「認証が必要です」が返る。書籍は削除されない</t>
+        </is>
+      </c>
+      <c r="I170" s="3" t="inlineStr">
+        <is>
+          <t>tests/Feature/PublicApi/BookApiDestroyTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="n"/>
@@ -5801,157 +5800,157 @@
       <c r="D171" s="4" t="n"/>
       <c r="E171" s="3" t="inlineStr">
         <is>
+          <t>10-5-2</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="inlineStr">
+        <is>
+          <t>自分が登録した書籍を削除できる</t>
+        </is>
+      </c>
+      <c r="G171" s="3" t="inlineStr">
+        <is>
+          <t>1.ユーザーが登録した書籍を用意する
+2.そのユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H171" s="3" t="inlineStr">
+        <is>
+          <t>204が返り(レスポンスボディなし)、書籍がDBから削除される</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="n"/>
+      <c r="B172" s="4" t="n"/>
+      <c r="C172" s="4" t="n"/>
+      <c r="D172" s="4" t="n"/>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>10-5-3</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="inlineStr">
+        <is>
+          <t>書籍を削除すると、関連するデータも一緒に削除される</t>
+        </is>
+      </c>
+      <c r="G172" s="3" t="inlineStr">
+        <is>
+          <t>1.ジャンルの紐づけ・レビュー・お気に入り・レビューへのいいねを持つ書籍を用意する
+2.所有者のトークンでDELETE /api/v1/books/{book}にアクセスする</t>
+        </is>
+      </c>
+      <c r="H172" s="3" t="inlineStr">
+        <is>
+          <t>book_genre・reviews・favorites・review_likesの該当データも削除される</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="n"/>
+      <c r="B173" s="4" t="n"/>
+      <c r="C173" s="4" t="n"/>
+      <c r="D173" s="4" t="n"/>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
           <t>10-5-4</t>
         </is>
       </c>
-      <c r="F171" s="3" t="inlineStr">
+      <c r="F173" s="3" t="inlineStr">
         <is>
           <t>他のユーザーが登録した書籍は削除できない</t>
         </is>
       </c>
-      <c r="G171" s="3" t="inlineStr">
+      <c r="G173" s="3" t="inlineStr">
         <is>
           <t>1.他のユーザーが登録した書籍を用意する
 2.別のユーザーのトークンを付与してDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H171" s="3" t="inlineStr">
+      <c r="H173" s="3" t="inlineStr">
         <is>
           <t>403 Forbiddenが返り、「この操作を行う権限がありません」が返る。書籍は削除されない</t>
         </is>
       </c>
-      <c r="I171" s="4" t="n"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="5" t="n"/>
-      <c r="B172" s="5" t="n"/>
-      <c r="C172" s="5" t="n"/>
-      <c r="D172" s="5" t="n"/>
-      <c r="E172" s="3" t="inlineStr">
+      <c r="I173" s="4" t="n"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="5" t="n"/>
+      <c r="B174" s="5" t="n"/>
+      <c r="C174" s="5" t="n"/>
+      <c r="D174" s="5" t="n"/>
+      <c r="E174" s="3" t="inlineStr">
         <is>
           <t>10-5-5</t>
         </is>
       </c>
-      <c r="F172" s="3" t="inlineStr">
+      <c r="F174" s="3" t="inlineStr">
         <is>
           <t>存在しないIDを指定すると404が返る</t>
         </is>
       </c>
-      <c r="G172" s="3" t="inlineStr">
+      <c r="G174" s="3" t="inlineStr">
         <is>
           <t>1.トークンを付与し、存在しない書籍IDでDELETE /api/v1/books/{book}にアクセスする</t>
         </is>
       </c>
-      <c r="H172" s="3" t="inlineStr">
+      <c r="H174" s="3" t="inlineStr">
         <is>
           <t>404が返り、「指定された書籍が見つかりません」が返る</t>
         </is>
       </c>
-      <c r="I172" s="5" t="n"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="7" t="inlineStr">
+      <c r="I174" s="5" t="n"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="7" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B173" s="7" t="inlineStr">
+      <c r="B175" s="7" t="inlineStr">
         <is>
           <t>検索・フィルタ</t>
         </is>
       </c>
-      <c r="C173" s="7" t="inlineStr">
+      <c r="C175" s="7" t="inlineStr">
         <is>
           <t>11-1</t>
         </is>
       </c>
-      <c r="D173" s="7" t="inlineStr">
+      <c r="D175" s="7" t="inlineStr">
         <is>
           <t>書籍のキーワード検索・ジャンル絞り込み</t>
         </is>
       </c>
-      <c r="E173" s="7" t="inlineStr">
+      <c r="E175" s="7" t="inlineStr">
         <is>
           <t>11-1-1</t>
         </is>
       </c>
-      <c r="F173" s="7" t="inlineStr">
+      <c r="F175" s="7" t="inlineStr">
         <is>
           <t>タイトルにキーワードを含む書籍が検索結果に表示される</t>
         </is>
       </c>
-      <c r="G173" s="7" t="inlineStr">
+      <c r="G175" s="7" t="inlineStr">
         <is>
           <t>1.タイトルにキーワードを含む書籍を用意する
 2.書籍一覧ページでkeywordにそのキーワードを指定して検索する</t>
         </is>
       </c>
-      <c r="H173" s="7" t="inlineStr">
+      <c r="H175" s="7" t="inlineStr">
         <is>
           <t>該当する書籍が検索結果に表示される</t>
         </is>
       </c>
-      <c r="I173" s="7" t="inlineStr">
+      <c r="I175" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Search/SearchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="4" t="n"/>
-      <c r="B174" s="4" t="n"/>
-      <c r="C174" s="4" t="n"/>
-      <c r="D174" s="4" t="n"/>
-      <c r="E174" s="7" t="inlineStr">
-        <is>
-          <t>11-1-2</t>
-        </is>
-      </c>
-      <c r="F174" s="7" t="inlineStr">
-        <is>
-          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="G174" s="7" t="inlineStr">
-        <is>
-          <t>1.著者名にキーワードを含む書籍を用意する
-2.同キーワードで検索する</t>
-        </is>
-      </c>
-      <c r="H174" s="7" t="inlineStr">
-        <is>
-          <t>該当する書籍が検索結果に表示される</t>
-        </is>
-      </c>
-      <c r="I174" s="4" t="n"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="4" t="n"/>
-      <c r="B175" s="4" t="n"/>
-      <c r="C175" s="4" t="n"/>
-      <c r="D175" s="4" t="n"/>
-      <c r="E175" s="7" t="inlineStr">
-        <is>
-          <t>11-1-3</t>
-        </is>
-      </c>
-      <c r="F175" s="7" t="inlineStr">
-        <is>
-          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
-        </is>
-      </c>
-      <c r="G175" s="7" t="inlineStr">
-        <is>
-          <t>1.キーワードに一致しない書籍を用意する
-2.検索する</t>
-        </is>
-      </c>
-      <c r="H175" s="7" t="inlineStr">
-        <is>
-          <t>その書籍は検索結果に表示されない</t>
-        </is>
-      </c>
-      <c r="I175" s="4" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="n"/>
@@ -5960,22 +5959,23 @@
       <c r="D176" s="4" t="n"/>
       <c r="E176" s="7" t="inlineStr">
         <is>
-          <t>11-1-4</t>
+          <t>11-1-2</t>
         </is>
       </c>
       <c r="F176" s="7" t="inlineStr">
         <is>
-          <t>キーワード未入力の場合は全件が表示される</t>
+          <t>著者名にキーワードを含む書籍が検索結果に表示される</t>
         </is>
       </c>
       <c r="G176" s="7" t="inlineStr">
         <is>
-          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
+          <t>1.著者名にキーワードを含む書籍を用意する
+2.同キーワードで検索する</t>
         </is>
       </c>
       <c r="H176" s="7" t="inlineStr">
         <is>
-          <t>登録されている全ての書籍が表示される</t>
+          <t>該当する書籍が検索結果に表示される</t>
         </is>
       </c>
       <c r="I176" s="4" t="n"/>
@@ -5987,23 +5987,23 @@
       <c r="D177" s="4" t="n"/>
       <c r="E177" s="7" t="inlineStr">
         <is>
-          <t>11-1-5</t>
+          <t>11-1-3</t>
         </is>
       </c>
       <c r="F177" s="7" t="inlineStr">
         <is>
-          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
+          <t>キーワードに一致しない書籍は検索結果に表示されない</t>
         </is>
       </c>
       <c r="G177" s="7" t="inlineStr">
         <is>
-          <t>1.複数ジャンルの書籍を用意する
-2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
+          <t>1.キーワードに一致しない書籍を用意する
+2.検索する</t>
         </is>
       </c>
       <c r="H177" s="7" t="inlineStr">
         <is>
-          <t>指定したジャンルに紐づく書籍のみ表示される</t>
+          <t>その書籍は検索結果に表示されない</t>
         </is>
       </c>
       <c r="I177" s="4" t="n"/>
@@ -6015,156 +6015,155 @@
       <c r="D178" s="4" t="n"/>
       <c r="E178" s="7" t="inlineStr">
         <is>
+          <t>11-1-4</t>
+        </is>
+      </c>
+      <c r="F178" s="7" t="inlineStr">
+        <is>
+          <t>キーワード未入力の場合は全件が表示される</t>
+        </is>
+      </c>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>1.keywordを指定せずに書籍一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H178" s="7" t="inlineStr">
+        <is>
+          <t>登録されている全ての書籍が表示される</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="n"/>
+      <c r="B179" s="4" t="n"/>
+      <c r="C179" s="4" t="n"/>
+      <c r="D179" s="4" t="n"/>
+      <c r="E179" s="7" t="inlineStr">
+        <is>
+          <t>11-1-5</t>
+        </is>
+      </c>
+      <c r="F179" s="7" t="inlineStr">
+        <is>
+          <t>ジャンルで絞り込むと、そのジャンルに紐づく書籍のみ表示される</t>
+        </is>
+      </c>
+      <c r="G179" s="7" t="inlineStr">
+        <is>
+          <t>1.複数ジャンルの書籍を用意する
+2.genreパラメータに1つのジャンルIDを指定して一覧を開く</t>
+        </is>
+      </c>
+      <c r="H179" s="7" t="inlineStr">
+        <is>
+          <t>指定したジャンルに紐づく書籍のみ表示される</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="n"/>
+      <c r="B180" s="4" t="n"/>
+      <c r="C180" s="4" t="n"/>
+      <c r="D180" s="4" t="n"/>
+      <c r="E180" s="7" t="inlineStr">
+        <is>
           <t>11-1-6</t>
         </is>
       </c>
-      <c r="F178" s="7" t="inlineStr">
+      <c r="F180" s="7" t="inlineStr">
         <is>
           <t>キーワード検索とジャンル絞り込みを組み合わせて使用できる</t>
         </is>
       </c>
-      <c r="G178" s="7" t="inlineStr">
+      <c r="G180" s="7" t="inlineStr">
         <is>
           <t>1.keywordとgenreの両方を指定して一覧を開く</t>
         </is>
       </c>
-      <c r="H178" s="7" t="inlineStr">
+      <c r="H180" s="7" t="inlineStr">
         <is>
           <t>キーワードとジャンルの両方の条件に一致する書籍のみ表示される</t>
         </is>
       </c>
-      <c r="I178" s="4" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="5" t="n"/>
-      <c r="B179" s="5" t="n"/>
-      <c r="C179" s="5" t="n"/>
-      <c r="D179" s="5" t="n"/>
-      <c r="E179" s="7" t="inlineStr">
+      <c r="I180" s="4" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="5" t="n"/>
+      <c r="B181" s="5" t="n"/>
+      <c r="C181" s="5" t="n"/>
+      <c r="D181" s="5" t="n"/>
+      <c r="E181" s="7" t="inlineStr">
         <is>
           <t>11-1-7</t>
         </is>
       </c>
-      <c r="F179" s="7" t="inlineStr">
+      <c r="F181" s="7" t="inlineStr">
         <is>
           <t>検索結果が0件の場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G179" s="7" t="inlineStr">
+      <c r="G181" s="7" t="inlineStr">
         <is>
           <t>1.どの書籍にも一致しないキーワードで検索する</t>
         </is>
       </c>
-      <c r="H179" s="7" t="inlineStr">
+      <c r="H181" s="7" t="inlineStr">
         <is>
           <t>「条件に一致する書籍が見つかりませんでした。」と表示される</t>
         </is>
       </c>
-      <c r="I179" s="5" t="n"/>
-    </row>
-    <row r="180">
-      <c r="A180" s="7" t="inlineStr">
+      <c r="I181" s="5" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B180" s="7" t="inlineStr">
+      <c r="B182" s="7" t="inlineStr">
         <is>
           <t>ソート</t>
         </is>
       </c>
-      <c r="C180" s="7" t="inlineStr">
+      <c r="C182" s="7" t="inlineStr">
         <is>
           <t>12-1</t>
         </is>
       </c>
-      <c r="D180" s="7" t="inlineStr">
+      <c r="D182" s="7" t="inlineStr">
         <is>
           <t>書籍一覧の並び替え</t>
         </is>
       </c>
-      <c r="E180" s="7" t="inlineStr">
+      <c r="E182" s="7" t="inlineStr">
         <is>
           <t>12-1-1</t>
         </is>
       </c>
-      <c r="F180" s="7" t="inlineStr">
+      <c r="F182" s="7" t="inlineStr">
         <is>
           <t>並び替え未指定時は新着順(登録が新しい順)で表示される</t>
         </is>
       </c>
-      <c r="G180" s="7" t="inlineStr">
+      <c r="G182" s="7" t="inlineStr">
         <is>
           <t>1.複数の書籍を異なる日時で登録する
 2.sortを指定せずに書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H180" s="7" t="inlineStr">
+      <c r="H182" s="7" t="inlineStr">
         <is>
           <t>登録日時が新しい順に表示される</t>
         </is>
       </c>
-      <c r="I180" s="7" t="inlineStr">
+      <c r="I182" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Sort/SortTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="4" t="n"/>
-      <c r="B181" s="4" t="n"/>
-      <c r="C181" s="4" t="n"/>
-      <c r="D181" s="4" t="n"/>
-      <c r="E181" s="7" t="inlineStr">
-        <is>
-          <t>12-1-2</t>
-        </is>
-      </c>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
-          <t>sort=oldestを指定すると登録が古い順に表示される</t>
-        </is>
-      </c>
-      <c r="G181" s="7" t="inlineStr">
-        <is>
-          <t>1.複数の書籍を異なる日時で登録する
-2.sort=oldestを指定して書籍一覧を開く</t>
-        </is>
-      </c>
-      <c r="H181" s="7" t="inlineStr">
-        <is>
-          <t>登録日時が古い順に表示される</t>
-        </is>
-      </c>
-      <c r="I181" s="4" t="n"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="4" t="n"/>
-      <c r="B182" s="4" t="n"/>
-      <c r="C182" s="4" t="n"/>
-      <c r="D182" s="4" t="n"/>
-      <c r="E182" s="7" t="inlineStr">
-        <is>
-          <t>12-1-3</t>
-        </is>
-      </c>
-      <c r="F182" s="7" t="inlineStr">
-        <is>
-          <t>sort=titleを指定するとタイトルの昇順で表示される</t>
-        </is>
-      </c>
-      <c r="G182" s="7" t="inlineStr">
-        <is>
-          <t>1.複数の書籍を用意する
-2.sort=titleを指定して書籍一覧を開く</t>
-        </is>
-      </c>
-      <c r="H182" s="7" t="inlineStr">
-        <is>
-          <t>タイトルの昇順で表示される</t>
-        </is>
-      </c>
-      <c r="I182" s="4" t="n"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="n"/>
@@ -6173,23 +6172,23 @@
       <c r="D183" s="4" t="n"/>
       <c r="E183" s="7" t="inlineStr">
         <is>
-          <t>12-1-4</t>
+          <t>12-1-2</t>
         </is>
       </c>
       <c r="F183" s="7" t="inlineStr">
         <is>
-          <t>sort=ratingを指定すると平均評価が高い順に表示される</t>
+          <t>sort=oldestを指定すると登録が古い順に表示される</t>
         </is>
       </c>
       <c r="G183" s="7" t="inlineStr">
         <is>
-          <t>1.平均評価が異なる複数の書籍を用意する
-2.sort=ratingを指定して書籍一覧を開く</t>
+          <t>1.複数の書籍を異なる日時で登録する
+2.sort=oldestを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H183" s="7" t="inlineStr">
         <is>
-          <t>平均評価が高い順に表示される</t>
+          <t>登録日時が古い順に表示される</t>
         </is>
       </c>
       <c r="I183" s="4" t="n"/>
@@ -6201,23 +6200,23 @@
       <c r="D184" s="4" t="n"/>
       <c r="E184" s="7" t="inlineStr">
         <is>
-          <t>12-1-5</t>
+          <t>12-1-3</t>
         </is>
       </c>
       <c r="F184" s="7" t="inlineStr">
         <is>
-          <t>sort=rating指定時、平均評価が同じ書籍は新着順で表示される</t>
+          <t>sort=titleを指定するとタイトルの昇順で表示される</t>
         </is>
       </c>
       <c r="G184" s="7" t="inlineStr">
         <is>
-          <t>1.平均評価が同じ複数の書籍を、異なる登録日時で用意する
-2.sort=ratingを指定して書籍一覧を開く</t>
+          <t>1.複数の書籍を用意する
+2.sort=titleを指定して書籍一覧を開く</t>
         </is>
       </c>
       <c r="H184" s="7" t="inlineStr">
         <is>
-          <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
+          <t>タイトルの昇順で表示される</t>
         </is>
       </c>
       <c r="I184" s="4" t="n"/>
@@ -6229,155 +6228,157 @@
       <c r="D185" s="4" t="n"/>
       <c r="E185" s="7" t="inlineStr">
         <is>
+          <t>12-1-4</t>
+        </is>
+      </c>
+      <c r="F185" s="7" t="inlineStr">
+        <is>
+          <t>sort=ratingを指定すると平均評価が高い順に表示される</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="inlineStr">
+        <is>
+          <t>1.平均評価が異なる複数の書籍を用意する
+2.sort=ratingを指定して書籍一覧を開く</t>
+        </is>
+      </c>
+      <c r="H185" s="7" t="inlineStr">
+        <is>
+          <t>平均評価が高い順に表示される</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="n"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n"/>
+      <c r="B186" s="4" t="n"/>
+      <c r="C186" s="4" t="n"/>
+      <c r="D186" s="4" t="n"/>
+      <c r="E186" s="7" t="inlineStr">
+        <is>
+          <t>12-1-5</t>
+        </is>
+      </c>
+      <c r="F186" s="7" t="inlineStr">
+        <is>
+          <t>sort=rating指定時、平均評価が同じ書籍は新着順で表示される</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="inlineStr">
+        <is>
+          <t>1.平均評価が同じ複数の書籍を、異なる登録日時で用意する
+2.sort=ratingを指定して書籍一覧を開く</t>
+        </is>
+      </c>
+      <c r="H186" s="7" t="inlineStr">
+        <is>
+          <t>平均評価が同じ書籍同士は、登録が新しい順に表示される</t>
+        </is>
+      </c>
+      <c r="I186" s="4" t="n"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n"/>
+      <c r="B187" s="4" t="n"/>
+      <c r="C187" s="4" t="n"/>
+      <c r="D187" s="4" t="n"/>
+      <c r="E187" s="7" t="inlineStr">
+        <is>
           <t>12-1-6</t>
         </is>
       </c>
-      <c r="F185" s="7" t="inlineStr">
+      <c r="F187" s="7" t="inlineStr">
         <is>
           <t>登録日時が同じ書籍は、IDの順に並ぶ(新しい順はIDの降順、古い順はIDの昇順)</t>
         </is>
       </c>
-      <c r="G185" s="7" t="inlineStr">
+      <c r="G187" s="7" t="inlineStr">
         <is>
           <t>1.登録日時が同じ書籍を複数用意する
 2.sort=latest、sort=oldestをそれぞれ指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H185" s="7" t="inlineStr">
+      <c r="H187" s="7" t="inlineStr">
         <is>
           <t>新しい順ではIDの降順(後に登録した順)、古い順ではIDの昇順(先に登録した順)に表示される</t>
         </is>
       </c>
-      <c r="I185" s="4" t="n"/>
-    </row>
-    <row r="186">
-      <c r="A186" s="5" t="n"/>
-      <c r="B186" s="5" t="n"/>
-      <c r="C186" s="5" t="n"/>
-      <c r="D186" s="5" t="n"/>
-      <c r="E186" s="7" t="inlineStr">
+      <c r="I187" s="4" t="n"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="5" t="n"/>
+      <c r="B188" s="5" t="n"/>
+      <c r="C188" s="5" t="n"/>
+      <c r="D188" s="5" t="n"/>
+      <c r="E188" s="7" t="inlineStr">
         <is>
           <t>12-1-7</t>
         </is>
       </c>
-      <c r="F186" s="7" t="inlineStr">
+      <c r="F188" s="7" t="inlineStr">
         <is>
           <t>sort=rating指定時、レビューがない書籍は最後に表示される</t>
         </is>
       </c>
-      <c r="G186" s="7" t="inlineStr">
+      <c r="G188" s="7" t="inlineStr">
         <is>
           <t>1.レビューがある書籍と、レビューがない書籍(登録が最も新しい)を用意する
 2.sort=ratingを指定して書籍一覧を開く</t>
         </is>
       </c>
-      <c r="H186" s="7" t="inlineStr">
+      <c r="H188" s="7" t="inlineStr">
         <is>
           <t>レビューがある書籍が平均評価の高い順に表示され、レビューがない書籍は最後に表示される</t>
         </is>
       </c>
-      <c r="I186" s="5" t="n"/>
-    </row>
-    <row r="187">
-      <c r="A187" s="7" t="inlineStr">
+      <c r="I188" s="5" t="n"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="7" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B187" s="7" t="inlineStr">
+      <c r="B189" s="7" t="inlineStr">
         <is>
           <t>書籍CRUD（認可の詳細テスト）</t>
         </is>
       </c>
-      <c r="C187" s="7" t="inlineStr">
+      <c r="C189" s="7" t="inlineStr">
         <is>
           <t>13-1</t>
         </is>
       </c>
-      <c r="D187" s="7" t="inlineStr">
+      <c r="D189" s="7" t="inlineStr">
         <is>
           <t>BookPolicyの認可ロジック</t>
         </is>
       </c>
-      <c r="E187" s="7" t="inlineStr">
+      <c r="E189" s="7" t="inlineStr">
         <is>
           <t>13-1-1</t>
         </is>
       </c>
-      <c r="F187" s="7" t="inlineStr">
+      <c r="F189" s="7" t="inlineStr">
         <is>
           <t>ログインユーザーは誰でも書籍を作成できる</t>
         </is>
       </c>
-      <c r="G187" s="7" t="inlineStr">
+      <c r="G189" s="7" t="inlineStr">
         <is>
           <t>1.任意のログインユーザーで BookPolicy::create() を確認する</t>
         </is>
       </c>
-      <c r="H187" s="7" t="inlineStr">
+      <c r="H189" s="7" t="inlineStr">
         <is>
           <t>trueが返り、作成が許可される</t>
         </is>
       </c>
-      <c r="I187" s="7" t="inlineStr">
+      <c r="I189" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/BookAuthorization/BookAuthorizationTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="4" t="n"/>
-      <c r="B188" s="4" t="n"/>
-      <c r="C188" s="4" t="n"/>
-      <c r="D188" s="4" t="n"/>
-      <c r="E188" s="7" t="inlineStr">
-        <is>
-          <t>13-1-2</t>
-        </is>
-      </c>
-      <c r="F188" s="7" t="inlineStr">
-        <is>
-          <t>書籍の登録者本人は更新が許可される</t>
-        </is>
-      </c>
-      <c r="G188" s="7" t="inlineStr">
-        <is>
-          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
-        </is>
-      </c>
-      <c r="H188" s="7" t="inlineStr">
-        <is>
-          <t>trueが返る</t>
-        </is>
-      </c>
-      <c r="I188" s="4" t="n"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="4" t="n"/>
-      <c r="B189" s="4" t="n"/>
-      <c r="C189" s="4" t="n"/>
-      <c r="D189" s="4" t="n"/>
-      <c r="E189" s="7" t="inlineStr">
-        <is>
-          <t>13-1-3</t>
-        </is>
-      </c>
-      <c r="F189" s="7" t="inlineStr">
-        <is>
-          <t>書籍の登録者以外は更新が許可されない</t>
-        </is>
-      </c>
-      <c r="G189" s="7" t="inlineStr">
-        <is>
-          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
-        </is>
-      </c>
-      <c r="H189" s="7" t="inlineStr">
-        <is>
-          <t>falseが返る</t>
-        </is>
-      </c>
-      <c r="I189" s="4" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="n"/>
@@ -6386,17 +6387,17 @@
       <c r="D190" s="4" t="n"/>
       <c r="E190" s="7" t="inlineStr">
         <is>
-          <t>13-1-4</t>
+          <t>13-1-2</t>
         </is>
       </c>
       <c r="F190" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者本人は削除が許可される</t>
+          <t>書籍の登録者本人は更新が許可される</t>
         </is>
       </c>
       <c r="G190" s="7" t="inlineStr">
         <is>
-          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
+          <t>1.書籍の登録者本人でBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H190" s="7" t="inlineStr">
@@ -6413,17 +6414,17 @@
       <c r="D191" s="4" t="n"/>
       <c r="E191" s="7" t="inlineStr">
         <is>
-          <t>13-1-5</t>
+          <t>13-1-3</t>
         </is>
       </c>
       <c r="F191" s="7" t="inlineStr">
         <is>
-          <t>書籍の登録者以外は削除が許可されない</t>
+          <t>書籍の登録者以外は更新が許可されない</t>
         </is>
       </c>
       <c r="G191" s="7" t="inlineStr">
         <is>
-          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
+          <t>1.別ユーザーでBookPolicy::update()を確認する</t>
         </is>
       </c>
       <c r="H191" s="7" t="inlineStr">
@@ -6440,154 +6441,153 @@
       <c r="D192" s="4" t="n"/>
       <c r="E192" s="7" t="inlineStr">
         <is>
+          <t>13-1-4</t>
+        </is>
+      </c>
+      <c r="F192" s="7" t="inlineStr">
+        <is>
+          <t>書籍の登録者本人は削除が許可される</t>
+        </is>
+      </c>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>1.書籍の登録者本人でBookPolicy::delete()を確認する</t>
+        </is>
+      </c>
+      <c r="H192" s="7" t="inlineStr">
+        <is>
+          <t>trueが返る</t>
+        </is>
+      </c>
+      <c r="I192" s="4" t="n"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="n"/>
+      <c r="B193" s="4" t="n"/>
+      <c r="C193" s="4" t="n"/>
+      <c r="D193" s="4" t="n"/>
+      <c r="E193" s="7" t="inlineStr">
+        <is>
+          <t>13-1-5</t>
+        </is>
+      </c>
+      <c r="F193" s="7" t="inlineStr">
+        <is>
+          <t>書籍の登録者以外は削除が許可されない</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="inlineStr">
+        <is>
+          <t>1.別ユーザーでBookPolicy::delete()を確認する</t>
+        </is>
+      </c>
+      <c r="H193" s="7" t="inlineStr">
+        <is>
+          <t>falseが返る</t>
+        </is>
+      </c>
+      <c r="I193" s="4" t="n"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="n"/>
+      <c r="B194" s="4" t="n"/>
+      <c r="C194" s="4" t="n"/>
+      <c r="D194" s="4" t="n"/>
+      <c r="E194" s="7" t="inlineStr">
+        <is>
           <t>13-1-6</t>
         </is>
       </c>
-      <c r="F192" s="7" t="inlineStr">
+      <c r="F194" s="7" t="inlineStr">
         <is>
           <t>フォームを介さない直接のPUT/DELETEリクエストでも他人の書籍は操作できない</t>
         </is>
       </c>
-      <c r="G192" s="7" t="inlineStr">
+      <c r="G194" s="7" t="inlineStr">
         <is>
           <t>1.他人が登録した書籍に対して、直接PUT・DELETEリクエストを送信する</t>
         </is>
       </c>
-      <c r="H192" s="7" t="inlineStr">
+      <c r="H194" s="7" t="inlineStr">
         <is>
           <t>いずれも403Forbiddenになり、データは変更されない</t>
         </is>
       </c>
-      <c r="I192" s="4" t="n"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="5" t="n"/>
-      <c r="B193" s="5" t="n"/>
-      <c r="C193" s="5" t="n"/>
-      <c r="D193" s="5" t="n"/>
-      <c r="E193" s="7" t="inlineStr">
+      <c r="I194" s="4" t="n"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="5" t="n"/>
+      <c r="B195" s="5" t="n"/>
+      <c r="C195" s="5" t="n"/>
+      <c r="D195" s="5" t="n"/>
+      <c r="E195" s="7" t="inlineStr">
         <is>
           <t>13-1-7</t>
         </is>
       </c>
-      <c r="F193" s="7" t="inlineStr">
+      <c r="F195" s="7" t="inlineStr">
         <is>
           <t>他人の書籍に対して不正な入力を直接PUTしても、入力エラーではなく403になる</t>
         </is>
       </c>
-      <c r="G193" s="7" t="inlineStr">
+      <c r="G195" s="7" t="inlineStr">
         <is>
           <t>1.他人が登録した書籍に対して、タイトルを空にするなど不正な内容で、直接PUTリクエストを送信する</t>
         </is>
       </c>
-      <c r="H193" s="7" t="inlineStr">
+      <c r="H195" s="7" t="inlineStr">
         <is>
           <t>バリデーションエラーにはならず、403Forbiddenになる（入力チェックより先に権限が判定される）。データは変更されない</t>
         </is>
       </c>
-      <c r="I193" s="5" t="n"/>
-    </row>
-    <row r="194">
-      <c r="A194" s="7" t="inlineStr">
+      <c r="I195" s="5" t="n"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="7" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B194" s="7" t="inlineStr">
+      <c r="B196" s="7" t="inlineStr">
         <is>
           <t>ISBN検索</t>
         </is>
       </c>
-      <c r="C194" s="7" t="inlineStr">
+      <c r="C196" s="7" t="inlineStr">
         <is>
           <t>14-1</t>
         </is>
       </c>
-      <c r="D194" s="7" t="inlineStr">
+      <c r="D196" s="7" t="inlineStr">
         <is>
           <t>ISBNからの書籍情報取得(外部API連携)</t>
         </is>
       </c>
-      <c r="E194" s="7" t="inlineStr">
+      <c r="E196" s="7" t="inlineStr">
         <is>
           <t>14-1-1</t>
         </is>
       </c>
-      <c r="F194" s="7" t="inlineStr">
+      <c r="F196" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、ISBN検索エンドポイントにアクセスできない</t>
         </is>
       </c>
-      <c r="G194" s="7" t="inlineStr">
+      <c r="G196" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態でGET /books/isbn/{isbn} にアクセスする</t>
         </is>
       </c>
-      <c r="H194" s="7" t="inlineStr">
+      <c r="H196" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I194" s="7" t="inlineStr">
+      <c r="I196" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Isbn/IsbnSearchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="4" t="n"/>
-      <c r="B195" s="4" t="n"/>
-      <c r="C195" s="4" t="n"/>
-      <c r="D195" s="4" t="n"/>
-      <c r="E195" s="7" t="inlineStr">
-        <is>
-          <t>14-1-2</t>
-        </is>
-      </c>
-      <c r="F195" s="7" t="inlineStr">
-        <is>
-          <t>ISBNが空(空白のみ)の場合、バリデーションエラーが返る</t>
-        </is>
-      </c>
-      <c r="G195" s="7" t="inlineStr">
-        <is>
-          <t>1.ログイン状態で、ISBN部分を半角スペースのみにしてGET /books/isbn/%20 にリクエストする
-※ISBN部分を完全に空にするとURLが /books/isbn となり、このルートに一致しないため空白で代用する</t>
-        </is>
-      </c>
-      <c r="H195" s="7" t="inlineStr">
-        <is>
-          <t>422が返り、「ISBNを入力してください」が返る</t>
-        </is>
-      </c>
-      <c r="I195" s="4" t="n"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="4" t="n"/>
-      <c r="B196" s="4" t="n"/>
-      <c r="C196" s="4" t="n"/>
-      <c r="D196" s="4" t="n"/>
-      <c r="E196" s="7" t="inlineStr">
-        <is>
-          <t>14-1-3</t>
-        </is>
-      </c>
-      <c r="F196" s="7" t="inlineStr">
-        <is>
-          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
-        </is>
-      </c>
-      <c r="G196" s="7" t="inlineStr">
-        <is>
-          <t>1.13桁でないISBNでリクエストする</t>
-        </is>
-      </c>
-      <c r="H196" s="7" t="inlineStr">
-        <is>
-          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
-        </is>
-      </c>
-      <c r="I196" s="4" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="4" t="n"/>
@@ -6596,22 +6596,23 @@
       <c r="D197" s="4" t="n"/>
       <c r="E197" s="7" t="inlineStr">
         <is>
-          <t>14-1-4</t>
+          <t>14-1-2</t>
         </is>
       </c>
       <c r="F197" s="7" t="inlineStr">
         <is>
-          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
+          <t>ISBNが空(空白のみ)の場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G197" s="7" t="inlineStr">
         <is>
-          <t>1.登録済みのISBNでリクエストする</t>
+          <t>1.ログイン状態で、ISBN部分を半角スペースのみにしてGET /books/isbn/%20 にリクエストする
+※ISBN部分を完全に空にするとURLが /books/isbn となり、このルートに一致しないため空白で代用する</t>
         </is>
       </c>
       <c r="H197" s="7" t="inlineStr">
         <is>
-          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
+          <t>422が返り、「ISBNを入力してください」が返る</t>
         </is>
       </c>
       <c r="I197" s="4" t="n"/>
@@ -6623,23 +6624,22 @@
       <c r="D198" s="4" t="n"/>
       <c r="E198" s="7" t="inlineStr">
         <is>
-          <t>14-1-5</t>
+          <t>14-1-3</t>
         </is>
       </c>
       <c r="F198" s="7" t="inlineStr">
         <is>
-          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
+          <t>ISBNが13桁の数字でない場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G198" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
-2.未登録ISBNでリクエストする</t>
+          <t>1.13桁でないISBNでリクエストする</t>
         </is>
       </c>
       <c r="H198" s="7" t="inlineStr">
         <is>
-          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
+          <t>422が返り、「ISBNは13桁の数字で入力してください」が返る</t>
         </is>
       </c>
       <c r="I198" s="4" t="n"/>
@@ -6651,23 +6651,22 @@
       <c r="D199" s="4" t="n"/>
       <c r="E199" s="7" t="inlineStr">
         <is>
-          <t>14-1-6</t>
+          <t>14-1-4</t>
         </is>
       </c>
       <c r="F199" s="7" t="inlineStr">
         <is>
-          <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
+          <t>既に登録済みのISBNの場合、バリデーションエラーが返る</t>
         </is>
       </c>
       <c r="G199" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でitemsが空のレスポンスをモックする
-2.未登録ISBNでリクエストする</t>
+          <t>1.登録済みのISBNでリクエストする</t>
         </is>
       </c>
       <c r="H199" s="7" t="inlineStr">
         <is>
-          <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
+          <t>422が返り、「このISBNはすでに登録されています」が返る</t>
         </is>
       </c>
       <c r="I199" s="4" t="n"/>
@@ -6679,23 +6678,23 @@
       <c r="D200" s="4" t="n"/>
       <c r="E200" s="7" t="inlineStr">
         <is>
-          <t>14-1-7</t>
+          <t>14-1-5</t>
         </is>
       </c>
       <c r="F200" s="7" t="inlineStr">
         <is>
-          <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
+          <t>Google Books APIをHttp::fake()でモック化し、書籍が見つかった場合に情報が返る</t>
         </is>
       </c>
       <c r="G200" s="7" t="inlineStr">
         <is>
-          <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
+          <t>1.Http::fake()でGoogle Books APIのレスポンスをモックする(titleやauthors等を含むitemsを返す)
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
-          <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
+          <t>200が返り、title・author・description・image_url・published_dateがJSONで返る</t>
         </is>
       </c>
       <c r="I200" s="4" t="n"/>
@@ -6707,155 +6706,157 @@
       <c r="D201" s="4" t="n"/>
       <c r="E201" s="7" t="inlineStr">
         <is>
+          <t>14-1-6</t>
+        </is>
+      </c>
+      <c r="F201" s="7" t="inlineStr">
+        <is>
+          <t>Http::fake()でitemsが空(該当書籍なし)の場合、404エラーが返る</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="inlineStr">
+        <is>
+          <t>1.Http::fake()でitemsが空のレスポンスをモックする
+2.未登録ISBNでリクエストする</t>
+        </is>
+      </c>
+      <c r="H201" s="7" t="inlineStr">
+        <is>
+          <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
+        </is>
+      </c>
+      <c r="I201" s="4" t="n"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="n"/>
+      <c r="B202" s="4" t="n"/>
+      <c r="C202" s="4" t="n"/>
+      <c r="D202" s="4" t="n"/>
+      <c r="E202" s="7" t="inlineStr">
+        <is>
+          <t>14-1-7</t>
+        </is>
+      </c>
+      <c r="F202" s="7" t="inlineStr">
+        <is>
+          <t>Http::fake()でAPI呼び出し自体が失敗した場合、502エラーが返る</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="inlineStr">
+        <is>
+          <t>1.Http::fake()でGoogle Books APIが失敗レスポンス(例: 500)を返すようモックする
+2.未登録ISBNでリクエストする</t>
+        </is>
+      </c>
+      <c r="H202" s="7" t="inlineStr">
+        <is>
+          <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
+        </is>
+      </c>
+      <c r="I202" s="4" t="n"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="n"/>
+      <c r="B203" s="4" t="n"/>
+      <c r="C203" s="4" t="n"/>
+      <c r="D203" s="4" t="n"/>
+      <c r="E203" s="7" t="inlineStr">
+        <is>
           <t>14-1-8</t>
         </is>
       </c>
-      <c r="F201" s="7" t="inlineStr">
+      <c r="F203" s="7" t="inlineStr">
         <is>
           <t>APIの検索結果はあるが、ISBNが一致する書籍がない場合も404エラーが返る</t>
         </is>
       </c>
-      <c r="G201" s="7" t="inlineStr">
+      <c r="G203" s="7" t="inlineStr">
         <is>
           <t>1.Http::fake()で、別のISBNを持つ書籍のみを含むitemsを返すようモックする
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H201" s="7" t="inlineStr">
+      <c r="H203" s="7" t="inlineStr">
         <is>
           <t>404が返り、「該当する書籍が見つかりませんでした。」が返る</t>
         </is>
       </c>
-      <c r="I201" s="4" t="n"/>
-    </row>
-    <row r="202">
-      <c r="A202" s="5" t="n"/>
-      <c r="B202" s="5" t="n"/>
-      <c r="C202" s="5" t="n"/>
-      <c r="D202" s="5" t="n"/>
-      <c r="E202" s="7" t="inlineStr">
+      <c r="I203" s="4" t="n"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="n"/>
+      <c r="B204" s="5" t="n"/>
+      <c r="C204" s="5" t="n"/>
+      <c r="D204" s="5" t="n"/>
+      <c r="E204" s="7" t="inlineStr">
         <is>
           <t>14-1-9</t>
         </is>
       </c>
-      <c r="F202" s="7" t="inlineStr">
+      <c r="F204" s="7" t="inlineStr">
         <is>
           <t>Google Books APIに接続できない場合(接続失敗・タイムアウト)も、502エラーが返る</t>
         </is>
       </c>
-      <c r="G202" s="7" t="inlineStr">
+      <c r="G204" s="7" t="inlineStr">
         <is>
           <t>1.Http::fake()で、Google Books APIへの接続が失敗する(ConnectExceptionを投げる)ようモックする
 2.未登録ISBNでリクエストする</t>
         </is>
       </c>
-      <c r="H202" s="7" t="inlineStr">
+      <c r="H204" s="7" t="inlineStr">
         <is>
           <t>502が返り、「書籍情報の取得中にエラーが発生しました。」が返る</t>
         </is>
       </c>
-      <c r="I202" s="5" t="n"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="7" t="inlineStr">
+      <c r="I204" s="5" t="n"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B203" s="7" t="inlineStr">
+      <c r="B205" s="7" t="inlineStr">
         <is>
           <t>マイ読書レポート</t>
         </is>
       </c>
-      <c r="C203" s="7" t="inlineStr">
+      <c r="C205" s="7" t="inlineStr">
         <is>
           <t>15-1</t>
         </is>
       </c>
-      <c r="D203" s="7" t="inlineStr">
+      <c r="D205" s="7" t="inlineStr">
         <is>
           <t>読書統計の表示</t>
         </is>
       </c>
-      <c r="E203" s="7" t="inlineStr">
+      <c r="E205" s="7" t="inlineStr">
         <is>
           <t>15-1-1</t>
         </is>
       </c>
-      <c r="F203" s="7" t="inlineStr">
+      <c r="F205" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、マイ読書レポートページにアクセスできない</t>
         </is>
       </c>
-      <c r="G203" s="7" t="inlineStr">
+      <c r="G205" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で/reportsを開く</t>
         </is>
       </c>
-      <c r="H203" s="7" t="inlineStr">
+      <c r="H205" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I203" s="7" t="inlineStr">
+      <c r="I205" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/Report/ReportTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="4" t="n"/>
-      <c r="B204" s="4" t="n"/>
-      <c r="C204" s="4" t="n"/>
-      <c r="D204" s="4" t="n"/>
-      <c r="E204" s="7" t="inlineStr">
-        <is>
-          <t>15-1-2</t>
-        </is>
-      </c>
-      <c r="F204" s="7" t="inlineStr">
-        <is>
-          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
-        </is>
-      </c>
-      <c r="G204" s="7" t="inlineStr">
-        <is>
-          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
-        </is>
-      </c>
-      <c r="H204" s="7" t="inlineStr">
-        <is>
-          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
-        </is>
-      </c>
-      <c r="I204" s="4" t="n"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="4" t="n"/>
-      <c r="B205" s="4" t="n"/>
-      <c r="C205" s="4" t="n"/>
-      <c r="D205" s="4" t="n"/>
-      <c r="E205" s="7" t="inlineStr">
-        <is>
-          <t>15-1-3</t>
-        </is>
-      </c>
-      <c r="F205" s="7" t="inlineStr">
-        <is>
-          <t>評価分布(★1〜★5)が正しく表示される</t>
-        </is>
-      </c>
-      <c r="G205" s="7" t="inlineStr">
-        <is>
-          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
-        </is>
-      </c>
-      <c r="H205" s="7" t="inlineStr">
-        <is>
-          <t>各評価の件数が実データと一致して表示される</t>
-        </is>
-      </c>
-      <c r="I205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="4" t="n"/>
@@ -6864,22 +6865,22 @@
       <c r="D206" s="4" t="n"/>
       <c r="E206" s="7" t="inlineStr">
         <is>
-          <t>15-1-4</t>
+          <t>15-1-2</t>
         </is>
       </c>
       <c r="F206" s="7" t="inlineStr">
         <is>
-          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
+          <t>レビュー投稿件数・読了冊数・平均評価が正しく集計される</t>
         </is>
       </c>
       <c r="G206" s="7" t="inlineStr">
         <is>
-          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
+          <t>1.複数のレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H206" s="7" t="inlineStr">
         <is>
-          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
+          <t>総レビュー数・ユニーク書籍数(読了冊数)・平均評価が実データと一致して表示される</t>
         </is>
       </c>
       <c r="I206" s="4" t="n"/>
@@ -6891,22 +6892,22 @@
       <c r="D207" s="4" t="n"/>
       <c r="E207" s="7" t="inlineStr">
         <is>
-          <t>15-1-5</t>
+          <t>15-1-3</t>
         </is>
       </c>
       <c r="F207" s="7" t="inlineStr">
         <is>
-          <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
+          <t>評価分布(★1〜★5)が正しく表示される</t>
         </is>
       </c>
       <c r="G207" s="7" t="inlineStr">
         <is>
-          <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
+          <t>1.評価1〜5のレビューをそれぞれ投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
       <c r="H207" s="7" t="inlineStr">
         <is>
-          <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
+          <t>各評価の件数が実データと一致して表示される</t>
         </is>
       </c>
       <c r="I207" s="4" t="n"/>
@@ -6918,285 +6919,283 @@
       <c r="D208" s="4" t="n"/>
       <c r="E208" s="7" t="inlineStr">
         <is>
+          <t>15-1-4</t>
+        </is>
+      </c>
+      <c r="F208" s="7" t="inlineStr">
+        <is>
+          <t>高評価書籍TOP5(評価4以上)が評価順に表示される</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="inlineStr">
+        <is>
+          <t>1.評価4以上のレビューを6件以上投稿したユーザーで/reportsを開く</t>
+        </is>
+      </c>
+      <c r="H208" s="7" t="inlineStr">
+        <is>
+          <t>評価が高い順(同評価は新しい順)に最大5件表示される</t>
+        </is>
+      </c>
+      <c r="I208" s="4" t="n"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="n"/>
+      <c r="B209" s="4" t="n"/>
+      <c r="C209" s="4" t="n"/>
+      <c r="D209" s="4" t="n"/>
+      <c r="E209" s="7" t="inlineStr">
+        <is>
+          <t>15-1-5</t>
+        </is>
+      </c>
+      <c r="F209" s="7" t="inlineStr">
+        <is>
+          <t>ジャンル別評価傾向TOP5が平均評価順に表示される</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="inlineStr">
+        <is>
+          <t>1.複数ジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
+        </is>
+      </c>
+      <c r="H209" s="7" t="inlineStr">
+        <is>
+          <t>ジャンルごとの平均評価が高い順に最大5件表示される</t>
+        </is>
+      </c>
+      <c r="I209" s="4" t="n"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="n"/>
+      <c r="B210" s="4" t="n"/>
+      <c r="C210" s="4" t="n"/>
+      <c r="D210" s="4" t="n"/>
+      <c r="E210" s="7" t="inlineStr">
+        <is>
           <t>15-1-6</t>
         </is>
       </c>
-      <c r="F208" s="7" t="inlineStr">
+      <c r="F210" s="7" t="inlineStr">
         <is>
           <t>レビューを1件も投稿していない場合の表示を確認する</t>
         </is>
       </c>
-      <c r="G208" s="7" t="inlineStr">
+      <c r="G210" s="7" t="inlineStr">
         <is>
           <t>1.レビューを1件も投稿していないユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H208" s="7" t="inlineStr">
+      <c r="H210" s="7" t="inlineStr">
         <is>
           <t>総レビュー数・読了冊数が0（平均評価の集計値は0で、画面上は「-」と表示）となり、TOP5一覧には「4星以上の書籍がありません」「ジャンルが設定された書籍のレビューがありません」と表示される</t>
         </is>
       </c>
-      <c r="I208" s="4" t="n"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="5" t="n"/>
-      <c r="B209" s="5" t="n"/>
-      <c r="C209" s="5" t="n"/>
-      <c r="D209" s="5" t="n"/>
-      <c r="E209" s="7" t="inlineStr">
+      <c r="I210" s="4" t="n"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="5" t="n"/>
+      <c r="B211" s="5" t="n"/>
+      <c r="C211" s="5" t="n"/>
+      <c r="D211" s="5" t="n"/>
+      <c r="E211" s="7" t="inlineStr">
         <is>
           <t>15-1-7</t>
         </is>
       </c>
-      <c r="F209" s="7" t="inlineStr">
+      <c r="F211" s="7" t="inlineStr">
         <is>
           <t>ジャンル別評価傾向で、平均評価が同じジャンルはレビュー件数の多い順に表示される</t>
         </is>
       </c>
-      <c r="G209" s="7" t="inlineStr">
+      <c r="G211" s="7" t="inlineStr">
         <is>
           <t>1.平均評価が同じで、レビュー件数が異なる2つのジャンルの書籍にレビューを投稿したユーザーで/reportsを開く</t>
         </is>
       </c>
-      <c r="H209" s="7" t="inlineStr">
+      <c r="H211" s="7" t="inlineStr">
         <is>
           <t>平均評価が同じジャンル同士は、レビュー件数の多い順に表示される</t>
         </is>
       </c>
-      <c r="I209" s="5" t="n"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="7" t="inlineStr">
+      <c r="I211" s="5" t="n"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B210" s="7" t="inlineStr">
+      <c r="B212" s="7" t="inlineStr">
         <is>
           <t>Sanctum認証</t>
         </is>
       </c>
-      <c r="C210" s="7" t="inlineStr">
+      <c r="C212" s="7" t="inlineStr">
         <is>
           <t>16-1</t>
         </is>
       </c>
-      <c r="D210" s="7" t="inlineStr">
+      <c r="D212" s="7" t="inlineStr">
         <is>
           <t>AP06:SanctumAPIトークン認証</t>
         </is>
       </c>
-      <c r="E210" s="7" t="inlineStr">
+      <c r="E212" s="7" t="inlineStr">
         <is>
           <t>16-1-1</t>
         </is>
       </c>
-      <c r="F210" s="7" t="inlineStr">
+      <c r="F212" s="7" t="inlineStr">
         <is>
           <t>有効なpersonal access tokenを付与すると、書き込み系API(POST /api/v1/books)を利用できる</t>
         </is>
       </c>
-      <c r="G210" s="7" t="inlineStr">
+      <c r="G212" s="7" t="inlineStr">
         <is>
           <t>1.$user-&gt;createToken()でトークンを発行する
 2.Authorization: Bearer {token}を付与して、正しい入力値でPOST /api/v1/booksにアクセスする</t>
         </is>
       </c>
-      <c r="H210" s="7" t="inlineStr">
+      <c r="H212" s="7" t="inlineStr">
         <is>
           <t>201が返り、トークンの持ち主を登録者(user_id)として書籍が登録される</t>
         </is>
       </c>
-      <c r="I210" s="7" t="inlineStr">
+      <c r="I212" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/SanctumAuth/SanctumAuthTest.php</t>
         </is>
       </c>
     </row>
-    <row r="211">
-      <c r="A211" s="4" t="n"/>
-      <c r="B211" s="4" t="n"/>
-      <c r="C211" s="4" t="n"/>
-      <c r="D211" s="4" t="n"/>
-      <c r="E211" s="7" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="4" t="n"/>
+      <c r="B213" s="4" t="n"/>
+      <c r="C213" s="4" t="n"/>
+      <c r="D213" s="4" t="n"/>
+      <c r="E213" s="7" t="inlineStr">
         <is>
           <t>16-1-2</t>
         </is>
       </c>
-      <c r="F211" s="7" t="inlineStr">
+      <c r="F213" s="7" t="inlineStr">
         <is>
           <t>トークンなしで書き込み系API(POST/PUT/DELETE)にアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G211" s="7" t="inlineStr">
+      <c r="G213" s="7" t="inlineStr">
         <is>
           <t>1.Authorizationヘッダーを付与せずに、POST /api/v1/books、PUT・DELETE /api/v1/books/{book}にそれぞれアクセスする</t>
         </is>
       </c>
-      <c r="H211" s="7" t="inlineStr">
+      <c r="H213" s="7" t="inlineStr">
         <is>
           <t>いずれも401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録・更新・削除されない</t>
         </is>
       </c>
-      <c r="I211" s="4" t="n"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="4" t="n"/>
-      <c r="B212" s="4" t="n"/>
-      <c r="C212" s="4" t="n"/>
-      <c r="D212" s="4" t="n"/>
-      <c r="E212" s="7" t="inlineStr">
+      <c r="I213" s="4" t="n"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="n"/>
+      <c r="B214" s="4" t="n"/>
+      <c r="C214" s="4" t="n"/>
+      <c r="D214" s="4" t="n"/>
+      <c r="E214" s="7" t="inlineStr">
         <is>
           <t>16-1-3</t>
         </is>
       </c>
-      <c r="F212" s="7" t="inlineStr">
+      <c r="F214" s="7" t="inlineStr">
         <is>
           <t>不正な(存在しない)トークンで書き込み系API(POST/PUT/DELETE)にアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G212" s="7" t="inlineStr">
+      <c r="G214" s="7" t="inlineStr">
         <is>
           <t>1.ランダムな文字列をBearerトークンとして付与し、POST /api/v1/books、PUT・DELETE /api/v1/books/{book}にそれぞれアクセスする</t>
         </is>
       </c>
-      <c r="H212" s="7" t="inlineStr">
+      <c r="H214" s="7" t="inlineStr">
         <is>
           <t>いずれも401 Unauthorizedが返り、「認証が必要です」が返る。書籍は登録・更新・削除されない</t>
         </is>
       </c>
-      <c r="I212" s="4" t="n"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="5" t="n"/>
-      <c r="B213" s="5" t="n"/>
-      <c r="C213" s="5" t="n"/>
-      <c r="D213" s="5" t="n"/>
-      <c r="E213" s="7" t="inlineStr">
+      <c r="I214" s="4" t="n"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="5" t="n"/>
+      <c r="B215" s="5" t="n"/>
+      <c r="C215" s="5" t="n"/>
+      <c r="D215" s="5" t="n"/>
+      <c r="E215" s="7" t="inlineStr">
         <is>
           <t>16-1-4</t>
         </is>
       </c>
-      <c r="F213" s="7" t="inlineStr">
+      <c r="F215" s="7" t="inlineStr">
         <is>
           <t>削除済み(失効済み)のトークンで書き込み系API(POST/PUT/DELETE)にアクセスすると401が返る</t>
         </is>
       </c>
-      <c r="G213" s="7" t="inlineStr">
+      <c r="G215" s="7" t="inlineStr">
         <is>
           <t>1.書籍の登録者のトークンを発行し、そのトークンを削除する
 2.そのトークンで、POST /api/v1/books、PUT・DELETE /api/v1/books/{book}(自分の書籍)にそれぞれアクセスする</t>
         </is>
       </c>
-      <c r="H213" s="7" t="inlineStr">
+      <c r="H215" s="7" t="inlineStr">
         <is>
           <t>いずれも401 Unauthorizedが返り、「認証が必要です」が返る。登録者本人のトークンでも、失効後は書籍を更新・削除できない</t>
         </is>
       </c>
-      <c r="I213" s="5" t="n"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="7" t="inlineStr">
+      <c r="I215" s="5" t="n"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B214" s="7" t="inlineStr">
+      <c r="B216" s="7" t="inlineStr">
         <is>
           <t>読書計画</t>
         </is>
       </c>
-      <c r="C214" s="7" t="inlineStr">
+      <c r="C216" s="7" t="inlineStr">
         <is>
           <t>17-1</t>
         </is>
       </c>
-      <c r="D214" s="7" t="inlineStr">
+      <c r="D216" s="7" t="inlineStr">
         <is>
           <t>読書計画の作成・一覧・読了・削除</t>
         </is>
       </c>
-      <c r="E214" s="7" t="inlineStr">
+      <c r="E216" s="7" t="inlineStr">
         <is>
           <t>17-1-1</t>
         </is>
       </c>
-      <c r="F214" s="7" t="inlineStr">
+      <c r="F216" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、読書計画関連ページ・操作にアクセスできない</t>
         </is>
       </c>
-      <c r="G214" s="7" t="inlineStr">
+      <c r="G216" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で/reading-plans関連のURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H214" s="7" t="inlineStr">
+      <c r="H216" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I214" s="7" t="inlineStr">
+      <c r="I216" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReadingPlan/ReadingPlanTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="215">
-      <c r="A215" s="4" t="n"/>
-      <c r="B215" s="4" t="n"/>
-      <c r="C215" s="4" t="n"/>
-      <c r="D215" s="4" t="n"/>
-      <c r="E215" s="7" t="inlineStr">
-        <is>
-          <t>17-1-2</t>
-        </is>
-      </c>
-      <c r="F215" s="7" t="inlineStr">
-        <is>
-          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
-        </is>
-      </c>
-      <c r="G215" s="7" t="inlineStr">
-        <is>
-          <t>1.自分と他人の読書計画をそれぞれ用意する
-2.読書計画一覧ページを開く</t>
-        </is>
-      </c>
-      <c r="H215" s="7" t="inlineStr">
-        <is>
-          <t>自分の計画のみが、target_dateの昇順で表示される</t>
-        </is>
-      </c>
-      <c r="I215" s="4" t="n"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="4" t="n"/>
-      <c r="B216" s="4" t="n"/>
-      <c r="C216" s="4" t="n"/>
-      <c r="D216" s="4" t="n"/>
-      <c r="E216" s="7" t="inlineStr">
-        <is>
-          <t>17-1-3</t>
-        </is>
-      </c>
-      <c r="F216" s="7" t="inlineStr">
-        <is>
-          <t>ステータスで絞り込んで表示できる</t>
-        </is>
-      </c>
-      <c r="G216" s="7" t="inlineStr">
-        <is>
-          <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
-2.statusパラメータを指定して一覧を開く</t>
-        </is>
-      </c>
-      <c r="H216" s="7" t="inlineStr">
-        <is>
-          <t>指定したステータスの計画のみ表示される</t>
-        </is>
-      </c>
-      <c r="I216" s="4" t="n"/>
     </row>
     <row r="217">
       <c r="A217" s="4" t="n"/>
@@ -7205,23 +7204,23 @@
       <c r="D217" s="4" t="n"/>
       <c r="E217" s="7" t="inlineStr">
         <is>
-          <t>17-1-4</t>
+          <t>17-1-2</t>
         </is>
       </c>
       <c r="F217" s="7" t="inlineStr">
         <is>
-          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
+          <t>読書計画一覧には自分が作成した計画のみが期日の昇順で表示される</t>
         </is>
       </c>
       <c r="G217" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍について進行中の計画を作成する
-2.計画作成ページを開く</t>
+          <t>1.自分と他人の読書計画をそれぞれ用意する
+2.読書計画一覧ページを開く</t>
         </is>
       </c>
       <c r="H217" s="7" t="inlineStr">
         <is>
-          <t>書籍選択肢にその書籍が表示されない</t>
+          <t>自分の計画のみが、target_dateの昇順で表示される</t>
         </is>
       </c>
       <c r="I217" s="4" t="n"/>
@@ -7233,22 +7232,23 @@
       <c r="D218" s="4" t="n"/>
       <c r="E218" s="7" t="inlineStr">
         <is>
-          <t>17-1-5</t>
+          <t>17-1-3</t>
         </is>
       </c>
       <c r="F218" s="7" t="inlineStr">
         <is>
-          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
+          <t>ステータスで絞り込んで表示できる</t>
         </is>
       </c>
       <c r="G218" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
+          <t>1.進行中・完了・期限切れの計画をそれぞれ用意する
+2.statusパラメータを指定して一覧を開く</t>
         </is>
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、計画は作成されない</t>
+          <t>指定したステータスの計画のみ表示される</t>
         </is>
       </c>
       <c r="I218" s="4" t="n"/>
@@ -7260,23 +7260,23 @@
       <c r="D219" s="4" t="n"/>
       <c r="E219" s="7" t="inlineStr">
         <is>
-          <t>17-1-6</t>
+          <t>17-1-4</t>
         </is>
       </c>
       <c r="F219" s="7" t="inlineStr">
         <is>
-          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
+          <t>既に「進行中」の計画がある書籍は作成画面の選択肢から除外される</t>
         </is>
       </c>
       <c r="G219" s="7" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を読了(完了)状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.ある書籍について進行中の計画を作成する
+2.計画作成ページを開く</t>
         </is>
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>新しい計画が作成される</t>
+          <t>書籍選択肢にその書籍が表示されない</t>
         </is>
       </c>
       <c r="I219" s="4" t="n"/>
@@ -7288,23 +7288,22 @@
       <c r="D220" s="4" t="n"/>
       <c r="E220" s="7" t="inlineStr">
         <is>
-          <t>17-1-7</t>
+          <t>17-1-5</t>
         </is>
       </c>
       <c r="F220" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>同じ書籍に進行中の計画がある状態で作成しようとすると認可エラーになる</t>
         </is>
       </c>
       <c r="G220" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.期日を入力せずに登録する</t>
+          <t>1.進行中の計画がある書籍に対して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H220" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>403Forbiddenになり、計画は作成されない</t>
         </is>
       </c>
       <c r="I220" s="4" t="n"/>
@@ -7316,23 +7315,23 @@
       <c r="D221" s="4" t="n"/>
       <c r="E221" s="7" t="inlineStr">
         <is>
-          <t>17-1-8</t>
+          <t>17-1-6</t>
         </is>
       </c>
       <c r="F221" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>完了済みの計画がある書籍は再度計画を作成できる</t>
         </is>
       </c>
       <c r="G221" s="7" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.過去の日付を期日に指定して登録する</t>
+          <t>1.ある書籍の計画を読了(完了)状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H221" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>新しい計画が作成される</t>
         </is>
       </c>
       <c r="I221" s="4" t="n"/>
@@ -7344,23 +7343,23 @@
       <c r="D222" s="4" t="n"/>
       <c r="E222" s="7" t="inlineStr">
         <is>
-          <t>17-1-9</t>
+          <t>17-1-7</t>
         </is>
       </c>
       <c r="F222" s="7" t="inlineStr">
         <is>
-          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G222" s="7" t="inlineStr">
         <is>
           <t>1.計画作成ページを開く
-2.書籍・期日を正しく入力して登録する</t>
+2.期日を入力せずに登録する</t>
         </is>
       </c>
       <c r="H222" s="7" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I222" s="4" t="n"/>
@@ -7372,22 +7371,23 @@
       <c r="D223" s="4" t="n"/>
       <c r="E223" s="7" t="inlineStr">
         <is>
-          <t>17-1-10</t>
+          <t>17-1-8</t>
         </is>
       </c>
       <c r="F223" s="7" t="inlineStr">
         <is>
-          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G223" s="7" t="inlineStr">
         <is>
-          <t>1.進行中の計画に対して読了操作を行う</t>
+          <t>1.計画作成ページを開く
+2.過去の日付を期日に指定して登録する</t>
         </is>
       </c>
       <c r="H223" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I223" s="4" t="n"/>
@@ -7399,22 +7399,23 @@
       <c r="D224" s="4" t="n"/>
       <c r="E224" s="7" t="inlineStr">
         <is>
-          <t>17-1-11</t>
+          <t>17-1-9</t>
         </is>
       </c>
       <c r="F224" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画は読了・削除できない</t>
+          <t>全ての項目が正しく入力されている場合、読書計画が作成される</t>
         </is>
       </c>
       <c r="G224" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+          <t>1.計画作成ページを開く
+2.書籍・期日を正しく入力して登録する</t>
         </is>
       </c>
       <c r="H224" s="7" t="inlineStr">
         <is>
-          <t>いずれも403Forbiddenになる</t>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される</t>
         </is>
       </c>
       <c r="I224" s="4" t="n"/>
@@ -7426,22 +7427,22 @@
       <c r="D225" s="4" t="n"/>
       <c r="E225" s="7" t="inlineStr">
         <is>
-          <t>17-1-12</t>
+          <t>17-1-10</t>
         </is>
       </c>
       <c r="F225" s="7" t="inlineStr">
         <is>
-          <t>自分が作成した読書計画は削除できる</t>
+          <t>「読了」操作を行うとステータスが「完了」になりcompleted_atが記録される</t>
         </is>
       </c>
       <c r="G225" s="7" t="inlineStr">
         <is>
-          <t>1.自分が作成した計画の削除ボタンを押す</t>
+          <t>1.進行中の計画に対して読了操作を行う</t>
         </is>
       </c>
       <c r="H225" s="7" t="inlineStr">
         <is>
-          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
+          <t>ステータスが「完了」になり、completed_atに現在日時が記録される</t>
         </is>
       </c>
       <c r="I225" s="4" t="n"/>
@@ -7451,25 +7452,24 @@
       <c r="B226" s="4" t="n"/>
       <c r="C226" s="4" t="n"/>
       <c r="D226" s="4" t="n"/>
-      <c r="E226" s="9" t="inlineStr">
-        <is>
-          <t>17-1-13</t>
-        </is>
-      </c>
-      <c r="F226" s="9" t="inlineStr">
-        <is>
-          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
-        </is>
-      </c>
-      <c r="G226" s="9" t="inlineStr">
-        <is>
-          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
-2.その読書計画を削除する</t>
-        </is>
-      </c>
-      <c r="H226" s="9" t="inlineStr">
-        <is>
-          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
+      <c r="E226" s="7" t="inlineStr">
+        <is>
+          <t>17-1-11</t>
+        </is>
+      </c>
+      <c r="F226" s="7" t="inlineStr">
+        <is>
+          <t>他人が作成した読書計画は読了・削除できない</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="inlineStr">
+        <is>
+          <t>1.他人が作成した計画に対して、読了・削除のリクエストを直接送信する</t>
+        </is>
+      </c>
+      <c r="H226" s="7" t="inlineStr">
+        <is>
+          <t>いずれも403Forbiddenになる</t>
         </is>
       </c>
       <c r="I226" s="4" t="n"/>
@@ -7479,24 +7479,24 @@
       <c r="B227" s="4" t="n"/>
       <c r="C227" s="4" t="n"/>
       <c r="D227" s="4" t="n"/>
-      <c r="E227" s="9" t="inlineStr">
-        <is>
-          <t>17-1-14</t>
-        </is>
-      </c>
-      <c r="F227" s="9" t="inlineStr">
-        <is>
-          <t>ステータスが「完了」の計画は、読了操作を行えない</t>
-        </is>
-      </c>
-      <c r="G227" s="9" t="inlineStr">
-        <is>
-          <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H227" s="9" t="inlineStr">
-        <is>
-          <t>403Forbiddenになり、completed_atは変更されない</t>
+      <c r="E227" s="7" t="inlineStr">
+        <is>
+          <t>17-1-12</t>
+        </is>
+      </c>
+      <c r="F227" s="7" t="inlineStr">
+        <is>
+          <t>自分が作成した読書計画は削除できる</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="inlineStr">
+        <is>
+          <t>1.自分が作成した計画の削除ボタンを押す</t>
+        </is>
+      </c>
+      <c r="H227" s="7" t="inlineStr">
+        <is>
+          <t>計画が削除され、「読書計画を削除しました。」と表示される</t>
         </is>
       </c>
       <c r="I227" s="4" t="n"/>
@@ -7508,23 +7508,23 @@
       <c r="D228" s="4" t="n"/>
       <c r="E228" s="9" t="inlineStr">
         <is>
-          <t>17-1-15</t>
+          <t>17-1-13</t>
         </is>
       </c>
       <c r="F228" s="9" t="inlineStr">
         <is>
-          <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
+          <t>読書計画削除時に、関連するリマインダー通知も同時に削除される</t>
         </is>
       </c>
       <c r="G228" s="9" t="inlineStr">
         <is>
-          <t>1.ある書籍の計画を「期限切れ」の状態にする
-2.同じ書籍で再度計画作成のリクエストを送信する</t>
+          <t>1.リマインダー通知(ReadingPlanReminder)が送信済み(notificationsテーブルにレコードがある状態)の読書計画を用意する
+2.その読書計画を削除する</t>
         </is>
       </c>
       <c r="H228" s="9" t="inlineStr">
         <is>
-          <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
+          <t>読書計画が削除されるとともに、その計画に紐づくリマインダー通知(notifications.data中のplan_idが一致するレコード)も削除される</t>
         </is>
       </c>
       <c r="I228" s="4" t="n"/>
@@ -7536,23 +7536,22 @@
       <c r="D229" s="4" t="n"/>
       <c r="E229" s="9" t="inlineStr">
         <is>
-          <t>17-1-16</t>
+          <t>17-1-14</t>
         </is>
       </c>
       <c r="F229" s="9" t="inlineStr">
         <is>
-          <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
+          <t>ステータスが「完了」の計画は、読了操作を行えない</t>
         </is>
       </c>
       <c r="G229" s="9" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍を選択せずに期日を入力して登録する</t>
+          <t>1.読了済み(完了)の計画に対して、直接読了のリクエストを送信する</t>
         </is>
       </c>
       <c r="H229" s="9" t="inlineStr">
         <is>
-          <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
+          <t>403Forbiddenになり、completed_atは変更されない</t>
         </is>
       </c>
       <c r="I229" s="4" t="n"/>
@@ -7564,22 +7563,23 @@
       <c r="D230" s="4" t="n"/>
       <c r="E230" s="9" t="inlineStr">
         <is>
-          <t>17-1-17</t>
+          <t>17-1-15</t>
         </is>
       </c>
       <c r="F230" s="9" t="inlineStr">
         <is>
-          <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
+          <t>「期限切れ」の計画がある書籍は、再度計画を作成できる</t>
         </is>
       </c>
       <c r="G230" s="9" t="inlineStr">
         <is>
-          <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.ある書籍の計画を「期限切れ」の状態にする
+2.同じ書籍で再度計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H230" s="9" t="inlineStr">
         <is>
-          <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
+          <t>新しい計画が「進行中」で作成される（「期限切れ」の計画はそのまま残る）</t>
         </is>
       </c>
       <c r="I230" s="4" t="n"/>
@@ -7591,22 +7591,23 @@
       <c r="D231" s="4" t="n"/>
       <c r="E231" s="9" t="inlineStr">
         <is>
-          <t>17-1-18</t>
+          <t>17-1-16</t>
         </is>
       </c>
       <c r="F231" s="9" t="inlineStr">
         <is>
-          <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
+          <t>書籍が選択されていない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G231" s="9" t="inlineStr">
         <is>
-          <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.計画作成ページを開く
+2.書籍を選択せずに期日を入力して登録する</t>
         </is>
       </c>
       <c r="H231" s="9" t="inlineStr">
         <is>
-          <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
+          <t>「書籍を選択してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I231" s="4" t="n"/>
@@ -7618,22 +7619,22 @@
       <c r="D232" s="4" t="n"/>
       <c r="E232" s="9" t="inlineStr">
         <is>
-          <t>17-1-19</t>
+          <t>17-1-17</t>
         </is>
       </c>
       <c r="F232" s="9" t="inlineStr">
         <is>
-          <t>期日が日付形式でない場合、バリデーションメッセージが表示される</t>
+          <t>存在しない書籍IDを指定した場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G232" s="9" t="inlineStr">
         <is>
-          <t>1.書籍と、日付として不正な期日(例:abc)を指定して、直接計画作成のリクエストを送信する</t>
+          <t>1.存在しない書籍IDと期日を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H232" s="9" t="inlineStr">
         <is>
-          <t>「正しい日付を入力してください」というバリデーションメッセージが表示される</t>
+          <t>「選択された書籍が見つかりません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I232" s="4" t="n"/>
@@ -7645,23 +7646,22 @@
       <c r="D233" s="4" t="n"/>
       <c r="E233" s="9" t="inlineStr">
         <is>
-          <t>17-1-20</t>
+          <t>17-1-18</t>
         </is>
       </c>
       <c r="F233" s="9" t="inlineStr">
         <is>
-          <t>期日に今日の日付を指定した場合、計画を作成できる</t>
+          <t>書籍IDが整数でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G233" s="9" t="inlineStr">
         <is>
-          <t>1.計画作成ページを開く
-2.書籍を選択し、期日に今日の日付を指定して登録する</t>
+          <t>1.書籍IDに整数でない値(例:abc)と期日を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H233" s="9" t="inlineStr">
         <is>
-          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される（今日の日付は指定可能）</t>
+          <t>「書籍の指定が正しくありません」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I233" s="4" t="n"/>
@@ -7673,22 +7673,22 @@
       <c r="D234" s="4" t="n"/>
       <c r="E234" s="9" t="inlineStr">
         <is>
-          <t>17-1-21</t>
+          <t>17-1-19</t>
         </is>
       </c>
       <c r="F234" s="9" t="inlineStr">
         <is>
-          <t>同じ書籍に進行中の計画がある状態で不正な期日を指定しても、入力エラーではなく403になる</t>
+          <t>期日が日付形式でない場合、バリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="G234" s="9" t="inlineStr">
         <is>
-          <t>1.進行中の計画がある書籍を指定し、期日を空にして直接計画作成のリクエストを送信する</t>
+          <t>1.書籍と、日付として不正な期日(例:abc)を指定して、直接計画作成のリクエストを送信する</t>
         </is>
       </c>
       <c r="H234" s="9" t="inlineStr">
         <is>
-          <t>バリデーションエラーではなく403Forbiddenになり、計画は作成されない（認可チェックが入力チェックより先に行われる）</t>
+          <t>「正しい日付を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I234" s="4" t="n"/>
@@ -7700,155 +7700,156 @@
       <c r="D235" s="4" t="n"/>
       <c r="E235" s="9" t="inlineStr">
         <is>
+          <t>17-1-20</t>
+        </is>
+      </c>
+      <c r="F235" s="9" t="inlineStr">
+        <is>
+          <t>期日に今日の日付を指定した場合、計画を作成できる</t>
+        </is>
+      </c>
+      <c r="G235" s="9" t="inlineStr">
+        <is>
+          <t>1.計画作成ページを開く
+2.書籍を選択し、期日に今日の日付を指定して登録する</t>
+        </is>
+      </c>
+      <c r="H235" s="9" t="inlineStr">
+        <is>
+          <t>読書計画が作成され、「「(タイトル)」の読書計画を作成しました。」と表示される（今日の日付は指定可能）</t>
+        </is>
+      </c>
+      <c r="I235" s="4" t="n"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="n"/>
+      <c r="B236" s="4" t="n"/>
+      <c r="C236" s="4" t="n"/>
+      <c r="D236" s="4" t="n"/>
+      <c r="E236" s="9" t="inlineStr">
+        <is>
+          <t>17-1-21</t>
+        </is>
+      </c>
+      <c r="F236" s="9" t="inlineStr">
+        <is>
+          <t>同じ書籍に進行中の計画がある状態で不正な期日を指定しても、入力エラーではなく403になる</t>
+        </is>
+      </c>
+      <c r="G236" s="9" t="inlineStr">
+        <is>
+          <t>1.進行中の計画がある書籍を指定し、期日を空にして直接計画作成のリクエストを送信する</t>
+        </is>
+      </c>
+      <c r="H236" s="9" t="inlineStr">
+        <is>
+          <t>バリデーションエラーではなく403Forbiddenになり、計画は作成されない（認可チェックが入力チェックより先に行われる）</t>
+        </is>
+      </c>
+      <c r="I236" s="4" t="n"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="n"/>
+      <c r="B237" s="4" t="n"/>
+      <c r="C237" s="4" t="n"/>
+      <c r="D237" s="4" t="n"/>
+      <c r="E237" s="9" t="inlineStr">
+        <is>
           <t>17-1-22</t>
         </is>
       </c>
-      <c r="F235" s="9" t="inlineStr">
+      <c r="F237" s="9" t="inlineStr">
         <is>
           <t>ステータスが「期限切れ」の計画は、読了操作を行える</t>
         </is>
       </c>
-      <c r="G235" s="9" t="inlineStr">
+      <c r="G237" s="9" t="inlineStr">
         <is>
           <t>1.「期限切れ」の計画に対して、読了操作を行う</t>
         </is>
       </c>
-      <c r="H235" s="9" t="inlineStr">
+      <c r="H237" s="9" t="inlineStr">
         <is>
           <t>ステータスが「完了」になり、completed_atに現在日時が記録され、「「(タイトル)」を読了しました。」と表示される</t>
         </is>
       </c>
-      <c r="I235" s="4" t="n"/>
-    </row>
-    <row r="236">
-      <c r="A236" s="5" t="n"/>
-      <c r="B236" s="5" t="n"/>
-      <c r="C236" s="5" t="n"/>
-      <c r="D236" s="5" t="n"/>
-      <c r="E236" s="9" t="inlineStr">
+      <c r="I237" s="4" t="n"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="n"/>
+      <c r="B238" s="5" t="n"/>
+      <c r="C238" s="5" t="n"/>
+      <c r="D238" s="5" t="n"/>
+      <c r="E238" s="9" t="inlineStr">
         <is>
           <t>17-1-23</t>
         </is>
       </c>
-      <c r="F236" s="9" t="inlineStr">
+      <c r="F238" s="9" t="inlineStr">
         <is>
           <t>他のユーザーの「進行中」の計画は、自分の計画作成に影響しない</t>
         </is>
       </c>
-      <c r="G236" s="9" t="inlineStr">
+      <c r="G238" s="9" t="inlineStr">
         <is>
           <t>1.他のユーザーが「進行中」の計画を持つ書籍を用意する
 2.計画作成ページを開く
 3.その書籍で計画作成のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H236" s="9" t="inlineStr">
+      <c r="H238" s="9" t="inlineStr">
         <is>
           <t>その書籍は作成画面の選択肢に表示され、自分の計画が「進行中」で作成される（進行中の重複チェックはユーザーごとに行われる）</t>
         </is>
       </c>
-      <c r="I236" s="5" t="n"/>
-    </row>
-    <row r="237">
-      <c r="A237" s="7" t="inlineStr">
+      <c r="I238" s="5" t="n"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="7" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B237" s="7" t="inlineStr">
+      <c r="B239" s="7" t="inlineStr">
         <is>
           <t>読書計画（期限変更）</t>
         </is>
       </c>
-      <c r="C237" s="7" t="inlineStr">
+      <c r="C239" s="7" t="inlineStr">
         <is>
           <t>18-1</t>
         </is>
       </c>
-      <c r="D237" s="7" t="inlineStr">
+      <c r="D239" s="7" t="inlineStr">
         <is>
           <t>読書計画の期日変更</t>
         </is>
       </c>
-      <c r="E237" s="7" t="inlineStr">
+      <c r="E239" s="7" t="inlineStr">
         <is>
           <t>18-1-1</t>
         </is>
       </c>
-      <c r="F237" s="7" t="inlineStr">
+      <c r="F239" s="7" t="inlineStr">
         <is>
           <t>未ログインの場合、読書計画編集ページにアクセスできない</t>
         </is>
       </c>
-      <c r="G237" s="7" t="inlineStr">
+      <c r="G239" s="7" t="inlineStr">
         <is>
           <t>1.未ログイン状態で読書計画編集ページのURLに直接アクセスする</t>
         </is>
       </c>
-      <c r="H237" s="7" t="inlineStr">
+      <c r="H239" s="7" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる</t>
         </is>
       </c>
-      <c r="I237" s="7" t="inlineStr">
+      <c r="I239" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReadingPlanDeadline/ReadingPlanDeadlineTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="4" t="n"/>
-      <c r="B238" s="4" t="n"/>
-      <c r="C238" s="4" t="n"/>
-      <c r="D238" s="4" t="n"/>
-      <c r="E238" s="7" t="inlineStr">
-        <is>
-          <t>18-1-2</t>
-        </is>
-      </c>
-      <c r="F238" s="7" t="inlineStr">
-        <is>
-          <t>他人が作成した読書計画の期日は変更できない</t>
-        </is>
-      </c>
-      <c r="G238" s="7" t="inlineStr">
-        <is>
-          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
-        </is>
-      </c>
-      <c r="H238" s="7" t="inlineStr">
-        <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
-        </is>
-      </c>
-      <c r="I238" s="4" t="n"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="4" t="n"/>
-      <c r="B239" s="4" t="n"/>
-      <c r="C239" s="4" t="n"/>
-      <c r="D239" s="4" t="n"/>
-      <c r="E239" s="7" t="inlineStr">
-        <is>
-          <t>18-1-3</t>
-        </is>
-      </c>
-      <c r="F239" s="7" t="inlineStr">
-        <is>
-          <t>編集画面を開くと現在の期日が初期表示される</t>
-        </is>
-      </c>
-      <c r="G239" s="7" t="inlineStr">
-        <is>
-          <t>1.自分が作成した計画の編集ページを開く</t>
-        </is>
-      </c>
-      <c r="H239" s="7" t="inlineStr">
-        <is>
-          <t>現在登録されている期日が入力欄に表示される</t>
-        </is>
-      </c>
-      <c r="I239" s="4" t="n"/>
     </row>
     <row r="240">
       <c r="A240" s="4" t="n"/>
@@ -7857,23 +7858,22 @@
       <c r="D240" s="4" t="n"/>
       <c r="E240" s="7" t="inlineStr">
         <is>
-          <t>18-1-4</t>
+          <t>18-1-2</t>
         </is>
       </c>
       <c r="F240" s="7" t="inlineStr">
         <is>
-          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
+          <t>他人が作成した読書計画の期日は変更できない</t>
         </is>
       </c>
       <c r="G240" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.期日を空にして更新する</t>
+          <t>1.他人が作成した計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H240" s="7" t="inlineStr">
         <is>
-          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
+          <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
       <c r="I240" s="4" t="n"/>
@@ -7885,23 +7885,22 @@
       <c r="D241" s="4" t="n"/>
       <c r="E241" s="7" t="inlineStr">
         <is>
-          <t>18-1-5</t>
+          <t>18-1-3</t>
         </is>
       </c>
       <c r="F241" s="7" t="inlineStr">
         <is>
-          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
+          <t>編集画面を開くと現在の期日が初期表示される</t>
         </is>
       </c>
       <c r="G241" s="7" t="inlineStr">
         <is>
-          <t>1.編集ページを開く
-2.過去の日付に変更して更新する</t>
+          <t>1.自分が作成した計画の編集ページを開く</t>
         </is>
       </c>
       <c r="H241" s="7" t="inlineStr">
         <is>
-          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
+          <t>現在登録されている期日が入力欄に表示される</t>
         </is>
       </c>
       <c r="I241" s="4" t="n"/>
@@ -7913,23 +7912,23 @@
       <c r="D242" s="4" t="n"/>
       <c r="E242" s="7" t="inlineStr">
         <is>
-          <t>18-1-6</t>
+          <t>18-1-4</t>
         </is>
       </c>
       <c r="F242" s="7" t="inlineStr">
         <is>
-          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
+          <t>期日が入力されていない場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G242" s="7" t="inlineStr">
         <is>
           <t>1.編集ページを開く
-2.未来の日付に正しく変更して更新する</t>
+2.期日を空にして更新する</t>
         </is>
       </c>
       <c r="H242" s="7" t="inlineStr">
         <is>
-          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
+          <t>「期日を入力してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I242" s="4" t="n"/>
@@ -7941,23 +7940,23 @@
       <c r="D243" s="4" t="n"/>
       <c r="E243" s="7" t="inlineStr">
         <is>
-          <t>18-1-7</t>
+          <t>18-1-5</t>
         </is>
       </c>
       <c r="F243" s="7" t="inlineStr">
         <is>
-          <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
+          <t>期日に今日より前の日付を指定した場合、バリデーションエラーが表示される</t>
         </is>
       </c>
       <c r="G243" s="7" t="inlineStr">
         <is>
-          <t>1.期日が過去で「進行中」の計画を用意する
-2.読書計画一覧または編集ページを開く</t>
+          <t>1.編集ページを開く
+2.過去の日付に変更して更新する</t>
         </is>
       </c>
       <c r="H243" s="7" t="inlineStr">
         <is>
-          <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
+          <t>「期日には今日以降の日付を指定してください」というバリデーションメッセージが表示される</t>
         </is>
       </c>
       <c r="I243" s="4" t="n"/>
@@ -7969,22 +7968,23 @@
       <c r="D244" s="4" t="n"/>
       <c r="E244" s="7" t="inlineStr">
         <is>
-          <t>18-1-8</t>
+          <t>18-1-6</t>
         </is>
       </c>
       <c r="F244" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は期日を変更できない</t>
+          <t>期日を正しく変更すると、計画が更新されステータスが「進行中」に戻る</t>
         </is>
       </c>
       <c r="G244" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
+          <t>1.編集ページを開く
+2.未来の日付に正しく変更して更新する</t>
         </is>
       </c>
       <c r="H244" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、期日は変更されない</t>
+          <t>計画のtarget_dateが更新され、ステータスが「進行中」になり「読書計画を更新しました。」と表示される</t>
         </is>
       </c>
       <c r="I244" s="4" t="n"/>
@@ -7996,22 +7996,23 @@
       <c r="D245" s="4" t="n"/>
       <c r="E245" s="7" t="inlineStr">
         <is>
-          <t>18-1-9</t>
+          <t>18-1-7</t>
         </is>
       </c>
       <c r="F245" s="7" t="inlineStr">
         <is>
-          <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
+          <t>一覧・編集画面を表示しても、期日を過ぎた「進行中」の計画のステータスは変更されない</t>
         </is>
       </c>
       <c r="G245" s="7" t="inlineStr">
         <is>
-          <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
+          <t>1.期日が過去で「進行中」の計画を用意する
+2.読書計画一覧または編集ページを開く</t>
         </is>
       </c>
       <c r="H245" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、編集ページは表示されない</t>
+          <t>計画のステータスは「進行中」のまま変化しない（「期限切れ」への更新は毎日20:00の日次バッチ reading-plans:daily でのみ行われる）</t>
         </is>
       </c>
       <c r="I245" s="4" t="n"/>
@@ -8023,22 +8024,22 @@
       <c r="D246" s="4" t="n"/>
       <c r="E246" s="7" t="inlineStr">
         <is>
-          <t>18-1-10</t>
+          <t>18-1-8</t>
         </is>
       </c>
       <c r="F246" s="7" t="inlineStr">
         <is>
-          <t>他人が作成した読書計画の編集ページにはアクセスできない</t>
+          <t>ステータスが「完了」の計画は期日を変更できない</t>
         </is>
       </c>
       <c r="G246" s="7" t="inlineStr">
         <is>
-          <t>1.他人が作成した計画の編集ページのURLに直接アクセスする</t>
+          <t>1.読了済み(完了)の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
       <c r="H246" s="7" t="inlineStr">
         <is>
-          <t>403Forbiddenになり、編集ページは表示されない</t>
+          <t>403Forbiddenになり、期日は変更されない</t>
         </is>
       </c>
       <c r="I246" s="4" t="n"/>
@@ -8050,158 +8051,156 @@
       <c r="D247" s="4" t="n"/>
       <c r="E247" s="7" t="inlineStr">
         <is>
+          <t>18-1-9</t>
+        </is>
+      </c>
+      <c r="F247" s="7" t="inlineStr">
+        <is>
+          <t>ステータスが「完了」の計画は、編集ページにも直接アクセスできない</t>
+        </is>
+      </c>
+      <c r="G247" s="7" t="inlineStr">
+        <is>
+          <t>1.読了済み(完了)の計画の編集ページのURLに直接アクセスする</t>
+        </is>
+      </c>
+      <c r="H247" s="7" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、編集ページは表示されない</t>
+        </is>
+      </c>
+      <c r="I247" s="4" t="n"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="n"/>
+      <c r="B248" s="4" t="n"/>
+      <c r="C248" s="4" t="n"/>
+      <c r="D248" s="4" t="n"/>
+      <c r="E248" s="7" t="inlineStr">
+        <is>
+          <t>18-1-10</t>
+        </is>
+      </c>
+      <c r="F248" s="7" t="inlineStr">
+        <is>
+          <t>他人が作成した読書計画の編集ページにはアクセスできない</t>
+        </is>
+      </c>
+      <c r="G248" s="7" t="inlineStr">
+        <is>
+          <t>1.他人が作成した計画の編集ページのURLに直接アクセスする</t>
+        </is>
+      </c>
+      <c r="H248" s="7" t="inlineStr">
+        <is>
+          <t>403Forbiddenになり、編集ページは表示されない</t>
+        </is>
+      </c>
+      <c r="I248" s="4" t="n"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="n"/>
+      <c r="B249" s="4" t="n"/>
+      <c r="C249" s="4" t="n"/>
+      <c r="D249" s="4" t="n"/>
+      <c r="E249" s="7" t="inlineStr">
+        <is>
           <t>18-1-11</t>
         </is>
       </c>
-      <c r="F247" s="7" t="inlineStr">
+      <c r="F249" s="7" t="inlineStr">
         <is>
           <t>同じ書籍に「進行中」の計画がある場合、「期限切れ」の計画は編集・更新できない</t>
         </is>
       </c>
-      <c r="G247" s="7" t="inlineStr">
+      <c r="G249" s="7" t="inlineStr">
         <is>
           <t>1.同じ書籍について、「期限切れ」の計画と「進行中」の計画をそれぞれ用意する
 2.「期限切れ」の計画の編集ページのURLに直接アクセスする
 3.「期限切れ」の計画に対して、直接更新リクエストを送信する</t>
         </is>
       </c>
-      <c r="H247" s="7" t="inlineStr">
+      <c r="H249" s="7" t="inlineStr">
         <is>
           <t>いずれも403Forbiddenになり、「期限切れ」の計画のステータス・期日は変更されない（同じ書籍の「進行中」の計画が2件になることを防ぐ）</t>
         </is>
       </c>
-      <c r="I247" s="4" t="n"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="5" t="n"/>
-      <c r="B248" s="5" t="n"/>
-      <c r="C248" s="5" t="n"/>
-      <c r="D248" s="5" t="n"/>
-      <c r="E248" s="7" t="inlineStr">
+      <c r="I249" s="4" t="n"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="5" t="n"/>
+      <c r="B250" s="5" t="n"/>
+      <c r="C250" s="5" t="n"/>
+      <c r="D250" s="5" t="n"/>
+      <c r="E250" s="7" t="inlineStr">
         <is>
           <t>18-1-12</t>
         </is>
       </c>
-      <c r="F248" s="7" t="inlineStr">
+      <c r="F250" s="7" t="inlineStr">
         <is>
           <t>他人が作成した読書計画に不正な期日で更新しようとしても、入力エラーではなく403になる</t>
         </is>
       </c>
-      <c r="G248" s="7" t="inlineStr">
+      <c r="G250" s="7" t="inlineStr">
         <is>
           <t>1.他人が作成した読書計画に対して、期日を空にして直接計画更新のリクエストを送信する</t>
         </is>
       </c>
-      <c r="H248" s="7" t="inlineStr">
+      <c r="H250" s="7" t="inlineStr">
         <is>
           <t>バリデーションエラーではなく403Forbiddenになり、期日は変更されない（認可チェックが入力チェックより先に行われる）</t>
         </is>
       </c>
-      <c r="I248" s="5" t="n"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="7" t="inlineStr">
+      <c r="I250" s="5" t="n"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="7" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B249" s="7" t="inlineStr">
+      <c r="B251" s="7" t="inlineStr">
         <is>
           <t>リマインダーバッチ</t>
         </is>
       </c>
-      <c r="C249" s="7" t="inlineStr">
+      <c r="C251" s="7" t="inlineStr">
         <is>
           <t>19-1</t>
         </is>
       </c>
-      <c r="D249" s="7" t="inlineStr">
+      <c r="D251" s="7" t="inlineStr">
         <is>
           <t>日次バッチ(reading-plans:daily)によるリマインダー通知</t>
         </is>
       </c>
-      <c r="E249" s="7" t="inlineStr">
+      <c r="E251" s="7" t="inlineStr">
         <is>
           <t>19-1-1</t>
         </is>
       </c>
-      <c r="F249" s="7" t="inlineStr">
+      <c r="F251" s="7" t="inlineStr">
         <is>
           <t>期日の3日前かつ進行中の計画に予告リマインダー通知が送信される</t>
         </is>
       </c>
-      <c r="G249" s="7" t="inlineStr">
+      <c r="G251" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日後・ステータス進行中の計画を用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
-      <c r="H249" s="7" t="inlineStr">
+      <c r="H251" s="7" t="inlineStr">
         <is>
           <t>対象ユーザーにReadingPlanReminder(種別:upcoming)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_before)・title(「読書期限のお知らせ」)・body(「「(書籍名)」の読書期限まであと3日です。」)が含まれる</t>
         </is>
       </c>
-      <c r="I249" s="7" t="inlineStr">
+      <c r="I251" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/ReminderBatch/ReminderBatchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="4" t="n"/>
-      <c r="B250" s="4" t="n"/>
-      <c r="C250" s="4" t="n"/>
-      <c r="D250" s="4" t="n"/>
-      <c r="E250" s="7" t="inlineStr">
-        <is>
-          <t>19-1-2</t>
-        </is>
-      </c>
-      <c r="F250" s="7" t="inlineStr">
-        <is>
-          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
-        </is>
-      </c>
-      <c r="G250" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが本日・ステータス進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H250" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される。通知のdataには、plan_id・book_title・timing(on_due_date)・title(「読書期限当日のお知らせ」)・body(「「(書籍名)」の読書期限は本日までです。」)が含まれる</t>
-        </is>
-      </c>
-      <c r="I250" s="4" t="n"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="4" t="n"/>
-      <c r="B251" s="4" t="n"/>
-      <c r="C251" s="4" t="n"/>
-      <c r="D251" s="4" t="n"/>
-      <c r="E251" s="7" t="inlineStr">
-        <is>
-          <t>19-1-3</t>
-        </is>
-      </c>
-      <c r="F251" s="7" t="inlineStr">
-        <is>
-          <t>期限切れから3日後の計画に再エンゲージメント通知が送信される</t>
-        </is>
-      </c>
-      <c r="G251" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが3日前・ステータス期限切れの計画を用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H251" s="7" t="inlineStr">
-        <is>
-          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
-        </is>
-      </c>
-      <c r="I251" s="4" t="n"/>
     </row>
     <row r="252">
       <c r="A252" s="4" t="n"/>
@@ -8210,508 +8209,508 @@
       <c r="D252" s="4" t="n"/>
       <c r="E252" s="7" t="inlineStr">
         <is>
+          <t>19-1-2</t>
+        </is>
+      </c>
+      <c r="F252" s="7" t="inlineStr">
+        <is>
+          <t>期日当日かつ進行中の計画に最終警告リマインダー通知が送信される</t>
+        </is>
+      </c>
+      <c r="G252" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが本日・ステータス進行中の計画を用意する
+2.reading-plans:dailyを実行する</t>
+        </is>
+      </c>
+      <c r="H252" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:final)通知が送信される。通知のdataには、plan_id・book_title・timing(on_due_date)・title(「読書期限当日のお知らせ」)・body(「「(書籍名)」の読書期限は本日までです。」)が含まれる</t>
+        </is>
+      </c>
+      <c r="I252" s="4" t="n"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="n"/>
+      <c r="B253" s="4" t="n"/>
+      <c r="C253" s="4" t="n"/>
+      <c r="D253" s="4" t="n"/>
+      <c r="E253" s="7" t="inlineStr">
+        <is>
+          <t>19-1-3</t>
+        </is>
+      </c>
+      <c r="F253" s="7" t="inlineStr">
+        <is>
+          <t>期限切れから3日後の計画に再エンゲージメント通知が送信される</t>
+        </is>
+      </c>
+      <c r="G253" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日前・ステータス期限切れの計画を用意する
+2.reading-plans:dailyを実行する</t>
+        </is>
+      </c>
+      <c r="H253" s="7" t="inlineStr">
+        <is>
+          <t>対象ユーザーにReadingPlanReminder(種別:re_engagement)通知が送信される。通知のdataには、plan_id・book_title・timing(three_days_after)・title(「読書計画見直しのお知らせ」)・body(「「(書籍名)」の読書期限を過ぎています。計画を見直しませんか？」)が含まれる</t>
+        </is>
+      </c>
+      <c r="I253" s="4" t="n"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="n"/>
+      <c r="B254" s="4" t="n"/>
+      <c r="C254" s="4" t="n"/>
+      <c r="D254" s="4" t="n"/>
+      <c r="E254" s="7" t="inlineStr">
+        <is>
           <t>19-1-4</t>
         </is>
       </c>
-      <c r="F252" s="7" t="inlineStr">
+      <c r="F254" s="7" t="inlineStr">
         <is>
           <t>いずれの条件にも該当しない計画には通知が送信されない</t>
         </is>
       </c>
-      <c r="G252" s="7" t="inlineStr">
+      <c r="G254" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが1週間後など対象日に該当しない進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H252" s="7" t="inlineStr">
+      <c r="H254" s="7" t="inlineStr">
         <is>
           <t>その計画のユーザーに通知が送信されない</t>
         </is>
       </c>
-      <c r="I252" s="4" t="n"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="5" t="n"/>
-      <c r="B253" s="5" t="n"/>
-      <c r="C253" s="5" t="n"/>
-      <c r="D253" s="5" t="n"/>
-      <c r="E253" s="7" t="inlineStr">
+      <c r="I254" s="4" t="n"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="5" t="n"/>
+      <c r="B255" s="5" t="n"/>
+      <c r="C255" s="5" t="n"/>
+      <c r="D255" s="5" t="n"/>
+      <c r="E255" s="7" t="inlineStr">
         <is>
           <t>19-1-5</t>
         </is>
       </c>
-      <c r="F253" s="7" t="inlineStr">
+      <c r="F255" s="7" t="inlineStr">
         <is>
           <t>ステータスが「完了」の計画には、期日の条件に合っていても通知が送信されない</t>
         </is>
       </c>
-      <c r="G253" s="7" t="inlineStr">
+      <c r="G255" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日後・本日・3日前で、ステータスが完了の計画をそれぞれ用意する
 2.Notification::fake()を設定し reading-plans:daily を実行する</t>
         </is>
       </c>
-      <c r="H253" s="7" t="inlineStr">
+      <c r="H255" s="7" t="inlineStr">
         <is>
           <t>いずれの計画のユーザーにも通知が送信されない</t>
         </is>
       </c>
-      <c r="I253" s="5" t="n"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="7" t="inlineStr">
+      <c r="I255" s="5" t="n"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="B254" s="7" t="inlineStr">
+      <c r="B256" s="7" t="inlineStr">
         <is>
           <t>自動失効バッチ</t>
         </is>
       </c>
-      <c r="C254" s="7" t="inlineStr">
+      <c r="C256" s="7" t="inlineStr">
         <is>
           <t>20-1</t>
         </is>
       </c>
-      <c r="D254" s="7" t="inlineStr">
+      <c r="D256" s="7" t="inlineStr">
         <is>
           <t>日次バッチ(reading-plans:daily)による自動失効処理</t>
         </is>
       </c>
-      <c r="E254" s="7" t="inlineStr">
+      <c r="E256" s="7" t="inlineStr">
         <is>
           <t>20-1-1</t>
         </is>
       </c>
-      <c r="F254" s="7" t="inlineStr">
+      <c r="F256" s="7" t="inlineStr">
         <is>
           <t>期日を過ぎた「進行中」の計画が「期限切れ」に更新される</t>
         </is>
       </c>
-      <c r="G254" s="7" t="inlineStr">
+      <c r="G256" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが過去・ステータス進行中の計画を用意する
 2.reading-plans:dailyを実行する</t>
         </is>
       </c>
-      <c r="H254" s="7" t="inlineStr">
+      <c r="H256" s="7" t="inlineStr">
         <is>
           <t>対象の計画のstatusが「期限切れ」に更新される</t>
         </is>
       </c>
-      <c r="I254" s="7" t="inlineStr">
+      <c r="I256" s="7" t="inlineStr">
         <is>
           <t>tests/Feature/AutoExpireBatch/AutoExpireBatchTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="4" t="n"/>
-      <c r="B255" s="4" t="n"/>
-      <c r="C255" s="4" t="n"/>
-      <c r="D255" s="4" t="n"/>
-      <c r="E255" s="7" t="inlineStr">
-        <is>
-          <t>20-1-2</t>
-        </is>
-      </c>
-      <c r="F255" s="7" t="inlineStr">
-        <is>
-          <t>期日が今日以降の「進行中」の計画は失効しない</t>
-        </is>
-      </c>
-      <c r="G255" s="7" t="inlineStr">
-        <is>
-          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H255" s="7" t="inlineStr">
-        <is>
-          <t>その計画のstatusは「進行中」のまま変化しない</t>
-        </is>
-      </c>
-      <c r="I255" s="4" t="n"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="4" t="n"/>
-      <c r="B256" s="4" t="n"/>
-      <c r="C256" s="4" t="n"/>
-      <c r="D256" s="4" t="n"/>
-      <c r="E256" s="7" t="inlineStr">
-        <is>
-          <t>20-1-3</t>
-        </is>
-      </c>
-      <c r="F256" s="7" t="inlineStr">
-        <is>
-          <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
-        </is>
-      </c>
-      <c r="G256" s="7" t="inlineStr">
-        <is>
-          <t>1.完了済み・期限切れの計画をそれぞれ用意する
-2.reading-plans:dailyを実行する</t>
-        </is>
-      </c>
-      <c r="H256" s="7" t="inlineStr">
-        <is>
-          <t>いずれの計画もstatusが変化しない</t>
-        </is>
-      </c>
-      <c r="I256" s="4" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="4" t="n"/>
       <c r="B257" s="4" t="n"/>
-      <c r="C257" s="5" t="n"/>
-      <c r="D257" s="5" t="n"/>
+      <c r="C257" s="4" t="n"/>
+      <c r="D257" s="4" t="n"/>
       <c r="E257" s="7" t="inlineStr">
         <is>
-          <t>20-1-4</t>
+          <t>20-1-2</t>
         </is>
       </c>
       <c r="F257" s="7" t="inlineStr">
         <is>
-          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
+          <t>期日が今日以降の「進行中」の計画は失効しない</t>
         </is>
       </c>
       <c r="G257" s="7" t="inlineStr">
         <is>
-          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
-2.DBを直接確認する</t>
+          <t>1.target_dateが今日以降・ステータス進行中の計画を用意する
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H257" s="7" t="inlineStr">
         <is>
-          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
-        </is>
-      </c>
-      <c r="I257" s="5" t="n"/>
+          <t>その計画のstatusは「進行中」のまま変化しない</t>
+        </is>
+      </c>
+      <c r="I257" s="4" t="n"/>
     </row>
     <row r="258">
       <c r="A258" s="4" t="n"/>
       <c r="B258" s="4" t="n"/>
-      <c r="C258" s="7" t="inlineStr">
-        <is>
-          <t>20-2</t>
-        </is>
-      </c>
-      <c r="D258" s="7" t="inlineStr">
-        <is>
-          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
-        </is>
-      </c>
+      <c r="C258" s="4" t="n"/>
+      <c r="D258" s="4" t="n"/>
       <c r="E258" s="7" t="inlineStr">
         <is>
-          <t>20-2-1</t>
+          <t>20-1-3</t>
         </is>
       </c>
       <c r="F258" s="7" t="inlineStr">
         <is>
-          <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
+          <t>既に「完了」または「期限切れ」の計画は対象外(重複更新されない)</t>
         </is>
       </c>
       <c r="G258" s="7" t="inlineStr">
         <is>
-          <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+          <t>1.完了済み・期限切れの計画をそれぞれ用意する
+2.reading-plans:dailyを実行する</t>
         </is>
       </c>
       <c r="H258" s="7" t="inlineStr">
         <is>
-          <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I258" s="7" t="inlineStr">
-        <is>
-          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
-        </is>
-      </c>
+          <t>いずれの計画もstatusが変化しない</t>
+        </is>
+      </c>
+      <c r="I258" s="4" t="n"/>
     </row>
     <row r="259">
       <c r="A259" s="4" t="n"/>
       <c r="B259" s="4" t="n"/>
-      <c r="C259" s="4" t="n"/>
-      <c r="D259" s="4" t="n"/>
+      <c r="C259" s="5" t="n"/>
+      <c r="D259" s="5" t="n"/>
       <c r="E259" s="7" t="inlineStr">
         <is>
-          <t>20-2-2</t>
+          <t>20-1-4</t>
         </is>
       </c>
       <c r="F259" s="7" t="inlineStr">
         <is>
-          <t>期限切れへの更新が、通知対象の抽出より先に行われる</t>
+          <t>コマンド実行後、対象データのステータスがDBに正しく保存されている</t>
         </is>
       </c>
       <c r="G259" s="7" t="inlineStr">
         <is>
-          <t>1.target_dateが3日前で、ステータスが「進行中」のまま(未更新)の計画を用意する
-2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+          <t>1.失効対象の計画を用意し reading-plans:daily を実行する
+2.DBを直接確認する</t>
         </is>
       </c>
       <c r="H259" s="7" t="inlineStr">
         <is>
-          <t>計画のstatusが「期限切れ」に更新され、そのユーザーに再エンゲージメント(re_engagement)通知が送信される</t>
-        </is>
-      </c>
-      <c r="I259" s="4" t="n"/>
+          <t>assertDatabaseHasでstatus=expiredが確認できる</t>
+        </is>
+      </c>
+      <c r="I259" s="5" t="n"/>
     </row>
     <row r="260">
       <c r="A260" s="4" t="n"/>
       <c r="B260" s="4" t="n"/>
-      <c r="C260" s="4" t="n"/>
-      <c r="D260" s="4" t="n"/>
+      <c r="C260" s="7" t="inlineStr">
+        <is>
+          <t>20-2</t>
+        </is>
+      </c>
+      <c r="D260" s="7" t="inlineStr">
+        <is>
+          <t>日次バッチ(reading-plans:daily)の実行順・スケジュール</t>
+        </is>
+      </c>
       <c r="E260" s="7" t="inlineStr">
         <is>
+          <t>20-2-1</t>
+        </is>
+      </c>
+      <c r="F260" s="7" t="inlineStr">
+        <is>
+          <t>reading-plans:dailyを実行すると、期限切れへの更新と通知の送信の両方が行われる</t>
+        </is>
+      </c>
+      <c r="G260" s="7" t="inlineStr">
+        <is>
+          <t>1.期日を過ぎた進行中の計画と、target_dateが3日後(期日の3日前)の進行中の計画をそれぞれ用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+        </is>
+      </c>
+      <c r="H260" s="7" t="inlineStr">
+        <is>
+          <t>期日を過ぎた計画のstatusが「期限切れ」に更新され、期日の3日前の計画のユーザーに予告リマインダー(upcoming)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I260" s="7" t="inlineStr">
+        <is>
+          <t>tests/Feature/AutoExpireBatch/DailyBatchTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="n"/>
+      <c r="B261" s="4" t="n"/>
+      <c r="C261" s="4" t="n"/>
+      <c r="D261" s="4" t="n"/>
+      <c r="E261" s="7" t="inlineStr">
+        <is>
+          <t>20-2-2</t>
+        </is>
+      </c>
+      <c r="F261" s="7" t="inlineStr">
+        <is>
+          <t>期限切れへの更新が、通知対象の抽出より先に行われる</t>
+        </is>
+      </c>
+      <c r="G261" s="7" t="inlineStr">
+        <is>
+          <t>1.target_dateが3日前で、ステータスが「進行中」のまま(未更新)の計画を用意する
+2.Notification::fake()を設定し reading-plans:daily を実行する</t>
+        </is>
+      </c>
+      <c r="H261" s="7" t="inlineStr">
+        <is>
+          <t>計画のstatusが「期限切れ」に更新され、そのユーザーに再エンゲージメント(re_engagement)通知が送信される</t>
+        </is>
+      </c>
+      <c r="I261" s="4" t="n"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="n"/>
+      <c r="B262" s="4" t="n"/>
+      <c r="C262" s="4" t="n"/>
+      <c r="D262" s="4" t="n"/>
+      <c r="E262" s="7" t="inlineStr">
+        <is>
           <t>20-2-3</t>
         </is>
       </c>
-      <c r="F260" s="7" t="inlineStr">
+      <c r="F262" s="7" t="inlineStr">
         <is>
           <t>reading-plans:dailyが毎日20:00に実行されるようスケジュールされている</t>
         </is>
       </c>
-      <c r="G260" s="7" t="inlineStr">
+      <c r="G262" s="7" t="inlineStr">
         <is>
           <t>1.アプリケーションのスケジュール(Illuminate\Console\Scheduling\Schedule)から、登録済みのイベントを取得する</t>
         </is>
       </c>
-      <c r="H260" s="7" t="inlineStr">
+      <c r="H262" s="7" t="inlineStr">
         <is>
           <t>reading-plans:dailyのイベントが登録されており、cron式が毎日20:00(0 20 * * *)になっている</t>
         </is>
       </c>
-      <c r="I260" s="4" t="n"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="5" t="n"/>
-      <c r="B261" s="5" t="n"/>
-      <c r="C261" s="5" t="n"/>
-      <c r="D261" s="5" t="n"/>
-      <c r="E261" s="7" t="inlineStr">
+      <c r="I262" s="4" t="n"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="5" t="n"/>
+      <c r="B263" s="5" t="n"/>
+      <c r="C263" s="5" t="n"/>
+      <c r="D263" s="5" t="n"/>
+      <c r="E263" s="7" t="inlineStr">
         <is>
           <t>20-2-4</t>
         </is>
       </c>
-      <c r="F261" s="7" t="inlineStr">
+      <c r="F263" s="7" t="inlineStr">
         <is>
           <t>日次バッチで送信した通知がnotificationsテーブルに保存され、通知一覧に表示される</t>
         </is>
       </c>
-      <c r="G261" s="7" t="inlineStr">
+      <c r="G263" s="7" t="inlineStr">
         <is>
           <t>1.target_dateが3日後(期日の3日前)・ステータス進行中の計画を用意する
 2.Notification::fake()を使わずに reading-plans:daily を実行する
 3.計画のユーザーで通知一覧ページを開く</t>
         </is>
       </c>
-      <c r="H261" s="7" t="inlineStr">
+      <c r="H263" s="7" t="inlineStr">
         <is>
           <t>notificationsテーブルにReadingPlanReminderの通知(未読、dataのplan_id・timingが対象の計画のもの)が1件保存され、通知一覧に「読書期限のお知らせ」と本文が未読として表示される</t>
         </is>
       </c>
-      <c r="I261" s="5" t="n"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="9" t="inlineStr">
+      <c r="I263" s="5" t="n"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="B262" s="9" t="inlineStr">
+      <c r="B264" s="9" t="inlineStr">
         <is>
           <t>通知</t>
         </is>
       </c>
-      <c r="C262" s="9" t="inlineStr">
+      <c r="C264" s="9" t="inlineStr">
         <is>
           <t>21-1</t>
         </is>
       </c>
-      <c r="D262" s="9" t="inlineStr">
+      <c r="D264" s="9" t="inlineStr">
         <is>
           <t>通知の既読化</t>
         </is>
       </c>
-      <c r="E262" s="9" t="inlineStr">
+      <c r="E264" s="9" t="inlineStr">
         <is>
           <t>21-1-1</t>
         </is>
       </c>
-      <c r="F262" s="9" t="inlineStr">
+      <c r="F264" s="9" t="inlineStr">
         <is>
           <t>未ログインの場合、通知の既読化操作にアクセスできない</t>
         </is>
       </c>
-      <c r="G262" s="9" t="inlineStr">
+      <c r="G264" s="9" t="inlineStr">
         <is>
           <t>1.未ログイン状態でPOST /notifications/{id}/read に直接リクエストを送信する</t>
         </is>
       </c>
-      <c r="H262" s="9" t="inlineStr">
+      <c r="H264" s="9" t="inlineStr">
         <is>
           <t>ログインページにリダイレクトされる（未読状態は変化しない）</t>
         </is>
       </c>
-      <c r="I262" s="9" t="inlineStr">
+      <c r="I264" s="9" t="inlineStr">
         <is>
           <t>tests/Feature/Notification/NotificationTest.php</t>
         </is>
       </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="4" t="n"/>
-      <c r="B263" s="4" t="n"/>
-      <c r="C263" s="4" t="n"/>
-      <c r="D263" s="4" t="n"/>
-      <c r="E263" s="9" t="inlineStr">
-        <is>
-          <t>21-1-2</t>
-        </is>
-      </c>
-      <c r="F263" s="9" t="inlineStr">
-        <is>
-          <t>自分の通知を既読にできる</t>
-        </is>
-      </c>
-      <c r="G263" s="9" t="inlineStr">
-        <is>
-          <t>1.自分宛ての未読通知を用意する
-2.その通知に対してPOST /notifications/{id}/read を送信する</t>
-        </is>
-      </c>
-      <c r="H263" s="9" t="inlineStr">
-        <is>
-          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
-        </is>
-      </c>
-      <c r="I263" s="4" t="n"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="4" t="n"/>
-      <c r="B264" s="4" t="n"/>
-      <c r="C264" s="5" t="n"/>
-      <c r="D264" s="5" t="n"/>
-      <c r="E264" s="9" t="inlineStr">
-        <is>
-          <t>21-1-3</t>
-        </is>
-      </c>
-      <c r="F264" s="9" t="inlineStr">
-        <is>
-          <t>他ユーザーの通知は既読にできない</t>
-        </is>
-      </c>
-      <c r="G264" s="9" t="inlineStr">
-        <is>
-          <t>1.他ユーザー宛ての通知を用意する
-2.そのIDに対してPOST /notifications/{id}/read を送信する</t>
-        </is>
-      </c>
-      <c r="H264" s="9" t="inlineStr">
-        <is>
-          <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
-        </is>
-      </c>
-      <c r="I264" s="5" t="n"/>
     </row>
     <row r="265">
       <c r="A265" s="4" t="n"/>
       <c r="B265" s="4" t="n"/>
-      <c r="C265" s="9" t="inlineStr">
-        <is>
-          <t>21-2</t>
-        </is>
-      </c>
-      <c r="D265" s="9" t="inlineStr">
-        <is>
-          <t>通知一覧</t>
-        </is>
-      </c>
+      <c r="C265" s="4" t="n"/>
+      <c r="D265" s="4" t="n"/>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>21-2-1</t>
+          <t>21-1-2</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>未ログインの場合、通知一覧にアクセスできない</t>
+          <t>自分の通知を既読にできる</t>
         </is>
       </c>
       <c r="G265" s="9" t="inlineStr">
         <is>
-          <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
+          <t>1.自分宛ての未読通知を用意する
+2.その通知に対してPOST /notifications/{id}/read を送信する</t>
         </is>
       </c>
       <c r="H265" s="9" t="inlineStr">
         <is>
-          <t>ログインページにリダイレクトされる</t>
-        </is>
-      </c>
-      <c r="I265" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationIndexTest.php</t>
-        </is>
-      </c>
+          <t>通知が既読になる（read_atが記録され、通知一覧で未読表示が消える）。あわせて「「(書籍名)」の通知を既読にしました。」というメッセージが画面上部に表示される</t>
+        </is>
+      </c>
+      <c r="I265" s="4" t="n"/>
     </row>
     <row r="266">
       <c r="A266" s="4" t="n"/>
       <c r="B266" s="4" t="n"/>
-      <c r="C266" s="4" t="n"/>
-      <c r="D266" s="4" t="n"/>
+      <c r="C266" s="5" t="n"/>
+      <c r="D266" s="5" t="n"/>
       <c r="E266" s="9" t="inlineStr">
         <is>
-          <t>21-2-2</t>
+          <t>21-1-3</t>
         </is>
       </c>
       <c r="F266" s="9" t="inlineStr">
         <is>
-          <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
+          <t>他ユーザーの通知は既読にできない</t>
         </is>
       </c>
       <c r="G266" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
-2.通知一覧ページを開く</t>
+          <t>1.他ユーザー宛ての通知を用意する
+2.そのIDに対してPOST /notifications/{id}/read を送信する</t>
         </is>
       </c>
       <c r="H266" s="9" t="inlineStr">
         <is>
-          <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
-        </is>
-      </c>
-      <c r="I266" s="4" t="n"/>
+          <t>既読化はauth()-&gt;user()-&gt;notifications()の範囲でしか行えないため404Not Foundになり、対象の通知は未読のまま変化しない</t>
+        </is>
+      </c>
+      <c r="I266" s="5" t="n"/>
     </row>
     <row r="267">
       <c r="A267" s="4" t="n"/>
       <c r="B267" s="4" t="n"/>
-      <c r="C267" s="4" t="n"/>
-      <c r="D267" s="4" t="n"/>
+      <c r="C267" s="9" t="inlineStr">
+        <is>
+          <t>21-2</t>
+        </is>
+      </c>
+      <c r="D267" s="9" t="inlineStr">
+        <is>
+          <t>通知一覧</t>
+        </is>
+      </c>
       <c r="E267" s="9" t="inlineStr">
         <is>
-          <t>21-2-3</t>
+          <t>21-2-1</t>
         </is>
       </c>
       <c r="F267" s="9" t="inlineStr">
         <is>
-          <t>通知が1件もない場合の表示を確認する</t>
+          <t>未ログインの場合、通知一覧にアクセスできない</t>
         </is>
       </c>
       <c r="G267" s="9" t="inlineStr">
         <is>
-          <t>1.通知が1件もないユーザーでログインする
-2.通知一覧ページを開く</t>
+          <t>1.未ログイン状態で通知一覧ページ(/notifications)のURLに直接アクセスする</t>
         </is>
       </c>
       <c r="H267" s="9" t="inlineStr">
         <is>
-          <t>「通知はありません。」と表示される</t>
-        </is>
-      </c>
-      <c r="I267" s="4" t="n"/>
+          <t>ログインページにリダイレクトされる</t>
+        </is>
+      </c>
+      <c r="I267" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationIndexTest.php</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="4" t="n"/>
@@ -8720,23 +8719,23 @@
       <c r="D268" s="4" t="n"/>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>21-2-4</t>
+          <t>21-2-2</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
         <is>
-          <t>通知のタイトル・本文が表示される</t>
+          <t>通知一覧には自分宛ての通知のみが新しい順に表示される</t>
         </is>
       </c>
       <c r="G268" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
+          <t>1.自分宛ての通知(作成日時が異なる複数件)と、他ユーザー宛ての通知を用意する
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H268" s="9" t="inlineStr">
         <is>
-          <t>通知のtitleとbodyが一覧に表示される</t>
+          <t>他ユーザー宛ての通知は表示されず、自分宛ての通知が作成日時の新しい順に表示される</t>
         </is>
       </c>
       <c r="I268" s="4" t="n"/>
@@ -8748,23 +8747,23 @@
       <c r="D269" s="4" t="n"/>
       <c r="E269" s="9" t="inlineStr">
         <is>
-          <t>21-2-5</t>
+          <t>21-2-3</t>
         </is>
       </c>
       <c r="F269" s="9" t="inlineStr">
         <is>
-          <t>未読と既読で表示が異なる</t>
+          <t>通知が1件もない場合の表示を確認する</t>
         </is>
       </c>
       <c r="G269" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
+          <t>1.通知が1件もないユーザーでログインする
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H269" s="9" t="inlineStr">
         <is>
-          <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
+          <t>「通知はありません。」と表示される</t>
         </is>
       </c>
       <c r="I269" s="4" t="n"/>
@@ -8772,303 +8771,359 @@
     <row r="270">
       <c r="A270" s="4" t="n"/>
       <c r="B270" s="4" t="n"/>
-      <c r="C270" s="5" t="n"/>
-      <c r="D270" s="5" t="n"/>
+      <c r="C270" s="4" t="n"/>
+      <c r="D270" s="4" t="n"/>
       <c r="E270" s="9" t="inlineStr">
         <is>
-          <t>21-2-6</t>
+          <t>21-2-4</t>
         </is>
       </c>
       <c r="F270" s="9" t="inlineStr">
         <is>
-          <t>同じ日時に作成された通知は、期日3日前→期日当日→期日3日後の順に表示される</t>
+          <t>通知のタイトル・本文が表示される</t>
         </is>
       </c>
       <c r="G270" s="9" t="inlineStr">
         <is>
-          <t>1.同じ日時に作成された、期日3日前（予告）・期日当日（最終警告）・期日3日後（再エンゲージメント）の通知と、作成日時の異なる通知を用意する
+          <t>1.自分宛ての通知(dataにtitle・bodyを持つ)を用意する
 2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H270" s="9" t="inlineStr">
         <is>
-          <t>第1優先で作成日時の新しい順、作成日時が同じ通知同士は第2優先で「期日3日前→期日当日→期日3日後」の順に表示される</t>
-        </is>
-      </c>
-      <c r="I270" s="5" t="n"/>
+          <t>通知のtitleとbodyが一覧に表示される</t>
+        </is>
+      </c>
+      <c r="I270" s="4" t="n"/>
     </row>
     <row r="271">
       <c r="A271" s="4" t="n"/>
       <c r="B271" s="4" t="n"/>
-      <c r="C271" s="9" t="inlineStr">
-        <is>
-          <t>21-3</t>
-        </is>
-      </c>
-      <c r="D271" s="9" t="inlineStr">
-        <is>
-          <t>ヘッダーの未読件数</t>
-        </is>
-      </c>
+      <c r="C271" s="4" t="n"/>
+      <c r="D271" s="4" t="n"/>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>21-3-1</t>
+          <t>21-2-5</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>ヘッダーのベルアイコンに未読件数が表示される</t>
+          <t>未読と既読で表示が異なる</t>
         </is>
       </c>
       <c r="G271" s="9" t="inlineStr">
         <is>
-          <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
+          <t>1.自分宛ての未読通知と既読通知をそれぞれ用意する
+2.通知一覧ページを開く</t>
         </is>
       </c>
       <c r="H271" s="9" t="inlineStr">
         <is>
-          <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
-        </is>
-      </c>
-      <c r="I271" s="9" t="inlineStr">
-        <is>
-          <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
-        </is>
-      </c>
+          <t>未読の通知には「未読」バッジと「既読にする」ボタンが表示され、既読の通知には表示されない</t>
+        </is>
+      </c>
+      <c r="I271" s="4" t="n"/>
     </row>
     <row r="272">
       <c r="A272" s="4" t="n"/>
       <c r="B272" s="4" t="n"/>
-      <c r="C272" s="4" t="n"/>
-      <c r="D272" s="4" t="n"/>
+      <c r="C272" s="5" t="n"/>
+      <c r="D272" s="5" t="n"/>
       <c r="E272" s="9" t="inlineStr">
         <is>
+          <t>21-2-6</t>
+        </is>
+      </c>
+      <c r="F272" s="9" t="inlineStr">
+        <is>
+          <t>同じ日時に作成された通知は、期日3日前→期日当日→期日3日後の順に表示される</t>
+        </is>
+      </c>
+      <c r="G272" s="9" t="inlineStr">
+        <is>
+          <t>1.同じ日時に作成された、期日3日前（予告）・期日当日（最終警告）・期日3日後（再エンゲージメント）の通知と、作成日時の異なる通知を用意する
+2.通知一覧ページを開く</t>
+        </is>
+      </c>
+      <c r="H272" s="9" t="inlineStr">
+        <is>
+          <t>第1優先で作成日時の新しい順、作成日時が同じ通知同士は第2優先で「期日3日前→期日当日→期日3日後」の順に表示される</t>
+        </is>
+      </c>
+      <c r="I272" s="5" t="n"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="n"/>
+      <c r="B273" s="4" t="n"/>
+      <c r="C273" s="9" t="inlineStr">
+        <is>
+          <t>21-3</t>
+        </is>
+      </c>
+      <c r="D273" s="9" t="inlineStr">
+        <is>
+          <t>ヘッダーの未読件数</t>
+        </is>
+      </c>
+      <c r="E273" s="9" t="inlineStr">
+        <is>
+          <t>21-3-1</t>
+        </is>
+      </c>
+      <c r="F273" s="9" t="inlineStr">
+        <is>
+          <t>ヘッダーのベルアイコンに未読件数が表示される</t>
+        </is>
+      </c>
+      <c r="G273" s="9" t="inlineStr">
+        <is>
+          <t>1.自分宛ての未読通知がある状態と、未読通知が0件の状態で、それぞれ画面を開く</t>
+        </is>
+      </c>
+      <c r="H273" s="9" t="inlineStr">
+        <is>
+          <t>未読通知がある場合はベルアイコンに未読件数のバッジが表示され、0件の場合はバッジが表示されない</t>
+        </is>
+      </c>
+      <c r="I273" s="9" t="inlineStr">
+        <is>
+          <t>tests/Feature/Notification/NotificationBadgeTest.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="n"/>
+      <c r="B274" s="4" t="n"/>
+      <c r="C274" s="4" t="n"/>
+      <c r="D274" s="4" t="n"/>
+      <c r="E274" s="9" t="inlineStr">
+        <is>
           <t>21-3-2</t>
         </is>
       </c>
-      <c r="F272" s="9" t="inlineStr">
+      <c r="F274" s="9" t="inlineStr">
         <is>
           <t>通知を既読にすると、ヘッダーの未読件数が減る</t>
         </is>
       </c>
-      <c r="G272" s="9" t="inlineStr">
+      <c r="G274" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知を複数件用意する
 2.そのうち1件にPOST /notifications/{id}/read を送信して既読にする
 3.画面を開き直す</t>
         </is>
       </c>
-      <c r="H272" s="9" t="inlineStr">
+      <c r="H274" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数が、既読にした1件分だけ減る</t>
         </is>
       </c>
-      <c r="I272" s="4" t="n"/>
-    </row>
-    <row r="273">
-      <c r="A273" s="5" t="n"/>
-      <c r="B273" s="5" t="n"/>
-      <c r="C273" s="5" t="n"/>
-      <c r="D273" s="5" t="n"/>
-      <c r="E273" s="9" t="inlineStr">
+      <c r="I274" s="4" t="n"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="5" t="n"/>
+      <c r="B275" s="5" t="n"/>
+      <c r="C275" s="5" t="n"/>
+      <c r="D275" s="5" t="n"/>
+      <c r="E275" s="9" t="inlineStr">
         <is>
           <t>21-3-3</t>
         </is>
       </c>
-      <c r="F273" s="9" t="inlineStr">
+      <c r="F275" s="9" t="inlineStr">
         <is>
           <t>他ユーザーの通知は未読件数に含まれない</t>
         </is>
       </c>
-      <c r="G273" s="9" t="inlineStr">
+      <c r="G275" s="9" t="inlineStr">
         <is>
           <t>1.自分宛ての未読通知と、他ユーザー宛ての未読通知をそれぞれ用意する
 2.画面を開く</t>
         </is>
       </c>
-      <c r="H273" s="9" t="inlineStr">
+      <c r="H275" s="9" t="inlineStr">
         <is>
           <t>ヘッダーの未読件数には、自分宛ての未読通知のみが数えられる</t>
         </is>
       </c>
-      <c r="I273" s="5" t="n"/>
+      <c r="I275" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="174">
     <mergeCell ref="B31:B65"/>
-    <mergeCell ref="C210:C213"/>
+    <mergeCell ref="A205:A211"/>
+    <mergeCell ref="D118:D120"/>
     <mergeCell ref="I17:I30"/>
-    <mergeCell ref="I180:I186"/>
-    <mergeCell ref="D118:D120"/>
     <mergeCell ref="A17:A30"/>
     <mergeCell ref="I92:I96"/>
+    <mergeCell ref="C153:C155"/>
+    <mergeCell ref="D12:D16"/>
     <mergeCell ref="B121:B124"/>
-    <mergeCell ref="D12:D16"/>
-    <mergeCell ref="I173:I179"/>
-    <mergeCell ref="C265:C270"/>
+    <mergeCell ref="D264:D266"/>
+    <mergeCell ref="D273:D275"/>
+    <mergeCell ref="I182:I188"/>
+    <mergeCell ref="I212:I215"/>
     <mergeCell ref="I70:I75"/>
+    <mergeCell ref="D267:D272"/>
+    <mergeCell ref="I153:I155"/>
+    <mergeCell ref="A175:A181"/>
     <mergeCell ref="I97:I102"/>
     <mergeCell ref="C121:C124"/>
-    <mergeCell ref="B214:B236"/>
-    <mergeCell ref="B173:B179"/>
+    <mergeCell ref="A256:A263"/>
+    <mergeCell ref="C170:C174"/>
     <mergeCell ref="C31:C34"/>
-    <mergeCell ref="D173:D179"/>
+    <mergeCell ref="C216:C238"/>
     <mergeCell ref="C89:C91"/>
     <mergeCell ref="I56:I61"/>
-    <mergeCell ref="D262:D264"/>
     <mergeCell ref="D35:D41"/>
     <mergeCell ref="C56:C61"/>
-    <mergeCell ref="C161:C167"/>
+    <mergeCell ref="A2:A16"/>
     <mergeCell ref="C42:C55"/>
-    <mergeCell ref="A2:A16"/>
-    <mergeCell ref="B203:B209"/>
     <mergeCell ref="C118:C120"/>
-    <mergeCell ref="D203:D209"/>
     <mergeCell ref="B125:B142"/>
     <mergeCell ref="D2:D4"/>
-    <mergeCell ref="C154:C160"/>
     <mergeCell ref="C66:C69"/>
-    <mergeCell ref="B180:B186"/>
-    <mergeCell ref="I271:I273"/>
+    <mergeCell ref="D260:D263"/>
     <mergeCell ref="D17:D30"/>
-    <mergeCell ref="B254:B261"/>
-    <mergeCell ref="A187:A193"/>
     <mergeCell ref="I118:I120"/>
-    <mergeCell ref="D143:D150"/>
-    <mergeCell ref="C187:C193"/>
+    <mergeCell ref="C267:C272"/>
+    <mergeCell ref="C156:C162"/>
+    <mergeCell ref="B239:B250"/>
+    <mergeCell ref="I12:I16"/>
     <mergeCell ref="I115:I117"/>
-    <mergeCell ref="I12:I16"/>
     <mergeCell ref="B111:B117"/>
+    <mergeCell ref="B182:B188"/>
     <mergeCell ref="I76:I84"/>
+    <mergeCell ref="I273:I275"/>
     <mergeCell ref="C115:C117"/>
+    <mergeCell ref="I264:I266"/>
+    <mergeCell ref="B212:B215"/>
+    <mergeCell ref="C205:C211"/>
+    <mergeCell ref="D85:D88"/>
     <mergeCell ref="C35:C41"/>
-    <mergeCell ref="C180:C186"/>
-    <mergeCell ref="C254:C257"/>
+    <mergeCell ref="A189:A195"/>
+    <mergeCell ref="D143:D152"/>
+    <mergeCell ref="B216:B238"/>
     <mergeCell ref="D137:D141"/>
-    <mergeCell ref="C262:C264"/>
-    <mergeCell ref="D258:D261"/>
+    <mergeCell ref="B175:B181"/>
+    <mergeCell ref="I267:I272"/>
+    <mergeCell ref="I156:I162"/>
+    <mergeCell ref="D175:D181"/>
+    <mergeCell ref="A143:A174"/>
+    <mergeCell ref="C182:C188"/>
+    <mergeCell ref="C256:C259"/>
     <mergeCell ref="D42:D55"/>
     <mergeCell ref="C97:C102"/>
-    <mergeCell ref="I262:I264"/>
-    <mergeCell ref="A249:A253"/>
-    <mergeCell ref="D161:D167"/>
-    <mergeCell ref="C249:C253"/>
-    <mergeCell ref="I258:I261"/>
-    <mergeCell ref="I168:I172"/>
+    <mergeCell ref="B251:B255"/>
+    <mergeCell ref="D251:D255"/>
+    <mergeCell ref="D216:D238"/>
     <mergeCell ref="I62:I65"/>
     <mergeCell ref="D6:D8"/>
+    <mergeCell ref="A216:A238"/>
+    <mergeCell ref="I2:I4"/>
     <mergeCell ref="I89:I91"/>
-    <mergeCell ref="I2:I4"/>
     <mergeCell ref="A111:A117"/>
     <mergeCell ref="B89:B110"/>
     <mergeCell ref="D9:D10"/>
-    <mergeCell ref="I237:I248"/>
+    <mergeCell ref="D212:D215"/>
     <mergeCell ref="C92:C96"/>
-    <mergeCell ref="A237:A248"/>
-    <mergeCell ref="D187:D193"/>
-    <mergeCell ref="I143:I150"/>
+    <mergeCell ref="C143:C152"/>
     <mergeCell ref="I125:I136"/>
+    <mergeCell ref="I239:I250"/>
     <mergeCell ref="D62:D65"/>
+    <mergeCell ref="A239:A250"/>
     <mergeCell ref="C70:C75"/>
+    <mergeCell ref="C273:C275"/>
+    <mergeCell ref="D189:D195"/>
     <mergeCell ref="A31:A65"/>
     <mergeCell ref="I9:I10"/>
+    <mergeCell ref="I143:I152"/>
     <mergeCell ref="C62:C65"/>
     <mergeCell ref="A121:A124"/>
-    <mergeCell ref="B249:B253"/>
-    <mergeCell ref="D265:D270"/>
-    <mergeCell ref="I194:I202"/>
-    <mergeCell ref="A262:A273"/>
-    <mergeCell ref="A143:A172"/>
+    <mergeCell ref="I175:I181"/>
+    <mergeCell ref="B143:B174"/>
+    <mergeCell ref="A264:A275"/>
+    <mergeCell ref="D163:D169"/>
+    <mergeCell ref="C251:C255"/>
     <mergeCell ref="C2:C4"/>
-    <mergeCell ref="I161:I167"/>
+    <mergeCell ref="B256:B263"/>
     <mergeCell ref="D103:D107"/>
+    <mergeCell ref="I216:I238"/>
+    <mergeCell ref="I256:I259"/>
     <mergeCell ref="I85:I88"/>
-    <mergeCell ref="D168:D172"/>
-    <mergeCell ref="C173:C179"/>
     <mergeCell ref="C85:C88"/>
     <mergeCell ref="D89:D91"/>
+    <mergeCell ref="C76:C84"/>
+    <mergeCell ref="C163:C169"/>
     <mergeCell ref="I6:I8"/>
-    <mergeCell ref="C194:C202"/>
-    <mergeCell ref="C76:C84"/>
     <mergeCell ref="C125:C136"/>
+    <mergeCell ref="B205:B211"/>
+    <mergeCell ref="B2:B16"/>
     <mergeCell ref="D70:D75"/>
-    <mergeCell ref="D237:D248"/>
-    <mergeCell ref="I249:I253"/>
-    <mergeCell ref="A203:A209"/>
-    <mergeCell ref="B2:B16"/>
+    <mergeCell ref="D205:D211"/>
+    <mergeCell ref="D153:D155"/>
+    <mergeCell ref="C264:C266"/>
     <mergeCell ref="A125:A142"/>
-    <mergeCell ref="D271:D273"/>
-    <mergeCell ref="I187:I193"/>
     <mergeCell ref="C108:C110"/>
-    <mergeCell ref="B210:B213"/>
     <mergeCell ref="I35:I41"/>
-    <mergeCell ref="A180:A186"/>
+    <mergeCell ref="D115:D117"/>
     <mergeCell ref="D66:D69"/>
-    <mergeCell ref="D115:D117"/>
-    <mergeCell ref="C143:C150"/>
+    <mergeCell ref="I189:I195"/>
     <mergeCell ref="D56:D61"/>
-    <mergeCell ref="A210:A213"/>
+    <mergeCell ref="I196:I204"/>
     <mergeCell ref="D121:D124"/>
+    <mergeCell ref="D108:D110"/>
     <mergeCell ref="I111:I114"/>
-    <mergeCell ref="D108:D110"/>
-    <mergeCell ref="B194:B202"/>
+    <mergeCell ref="A182:A188"/>
     <mergeCell ref="A66:A88"/>
-    <mergeCell ref="I265:I270"/>
+    <mergeCell ref="I163:I169"/>
     <mergeCell ref="C137:C141"/>
-    <mergeCell ref="A254:A261"/>
-    <mergeCell ref="B143:B172"/>
+    <mergeCell ref="C175:C181"/>
     <mergeCell ref="C111:C114"/>
-    <mergeCell ref="C258:C261"/>
-    <mergeCell ref="D151:D153"/>
-    <mergeCell ref="D214:D236"/>
+    <mergeCell ref="D256:D259"/>
     <mergeCell ref="I103:I107"/>
-    <mergeCell ref="D154:D160"/>
-    <mergeCell ref="D194:D202"/>
-    <mergeCell ref="C237:C248"/>
+    <mergeCell ref="I260:I263"/>
+    <mergeCell ref="C260:C263"/>
+    <mergeCell ref="A251:A255"/>
     <mergeCell ref="D76:D84"/>
     <mergeCell ref="C17:C30"/>
     <mergeCell ref="D31:D34"/>
-    <mergeCell ref="I210:I213"/>
-    <mergeCell ref="B187:B193"/>
+    <mergeCell ref="I170:I174"/>
     <mergeCell ref="I42:I55"/>
+    <mergeCell ref="I205:I211"/>
+    <mergeCell ref="D156:D162"/>
+    <mergeCell ref="C239:C250"/>
     <mergeCell ref="B118:B120"/>
+    <mergeCell ref="A212:A215"/>
+    <mergeCell ref="C212:C215"/>
     <mergeCell ref="A89:A110"/>
-    <mergeCell ref="C203:C209"/>
     <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D180:D186"/>
-    <mergeCell ref="D254:D257"/>
-    <mergeCell ref="A194:A202"/>
     <mergeCell ref="I66:I69"/>
+    <mergeCell ref="B189:B195"/>
     <mergeCell ref="D92:D96"/>
-    <mergeCell ref="B237:B248"/>
     <mergeCell ref="B66:B88"/>
-    <mergeCell ref="D210:D213"/>
+    <mergeCell ref="B196:B204"/>
+    <mergeCell ref="D196:D204"/>
     <mergeCell ref="D111:D114"/>
     <mergeCell ref="I121:I124"/>
     <mergeCell ref="I108:I110"/>
+    <mergeCell ref="D182:D188"/>
     <mergeCell ref="I137:I141"/>
     <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C151:C153"/>
+    <mergeCell ref="B264:B275"/>
+    <mergeCell ref="C189:C195"/>
     <mergeCell ref="D97:D102"/>
-    <mergeCell ref="I254:I257"/>
-    <mergeCell ref="D249:D253"/>
+    <mergeCell ref="D239:D250"/>
     <mergeCell ref="B17:B30"/>
-    <mergeCell ref="I151:I153"/>
-    <mergeCell ref="I214:I236"/>
-    <mergeCell ref="A173:A179"/>
+    <mergeCell ref="I251:I255"/>
+    <mergeCell ref="D125:D136"/>
     <mergeCell ref="A118:A120"/>
-    <mergeCell ref="D125:D136"/>
-    <mergeCell ref="I154:I160"/>
-    <mergeCell ref="C271:C273"/>
-    <mergeCell ref="A214:A236"/>
-    <mergeCell ref="B262:B273"/>
-    <mergeCell ref="C214:C236"/>
     <mergeCell ref="I31:I34"/>
+    <mergeCell ref="D170:D174"/>
     <mergeCell ref="C103:C107"/>
-    <mergeCell ref="C168:C172"/>
     <mergeCell ref="C12:C16"/>
-    <mergeCell ref="I203:I209"/>
-    <mergeCell ref="D85:D88"/>
+    <mergeCell ref="A196:A204"/>
+    <mergeCell ref="C196:C204"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
